--- a/src/test/java/TestData/Scenario_TestData.xlsx
+++ b/src/test/java/TestData/Scenario_TestData.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\COPA Automation Final\Copa_API_WebServices\src\test\java\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D97B913E-73FD-4A51-8F17-8920476609A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E77A43E1-52D9-4FB6-A87F-00EE18CDCAB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="5" activeTab="8" xr2:uid="{5D5A4724-D560-4FC2-9708-4BBF1DBA0B11}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="8" activeTab="10" xr2:uid="{5D5A4724-D560-4FC2-9708-4BBF1DBA0B11}"/>
   </bookViews>
   <sheets>
     <sheet name="AdvancePassengerInfo" sheetId="1" r:id="rId1"/>
@@ -22,11 +22,13 @@
     <sheet name="CreateBookingService" sheetId="7" r:id="rId7"/>
     <sheet name="ModifyInventoryService" sheetId="8" r:id="rId8"/>
     <sheet name="ModifyBookingSer_CancelBooking" sheetId="9" r:id="rId9"/>
-    <sheet name="ReferenceService" sheetId="10" r:id="rId10"/>
+    <sheet name="PassengerListService" sheetId="11" r:id="rId10"/>
+    <sheet name="DisplayLoyaltyAccountService" sheetId="12" r:id="rId11"/>
+    <sheet name="ReferenceService" sheetId="10" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -45,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="146">
   <si>
     <t>DepartureDateTime</t>
   </si>
@@ -404,24 +406,15 @@
     <t>2023-02-18T08:32:00</t>
   </si>
   <si>
-    <t>AJAGSO</t>
-  </si>
-  <si>
     <t>2023-02-13T07:48:00</t>
   </si>
   <si>
     <t>2023-02-13T10:57:00</t>
   </si>
   <si>
-    <t>AJAGST</t>
-  </si>
-  <si>
     <t>Other Changes</t>
   </si>
   <si>
-    <t>AJAJHL</t>
-  </si>
-  <si>
     <t>ID</t>
   </si>
   <si>
@@ -452,24 +445,6 @@
     <t>C01</t>
   </si>
   <si>
-    <t>AJAJ0Z</t>
-  </si>
-  <si>
-    <t>AJAKCM</t>
-  </si>
-  <si>
-    <t>AJAKI5</t>
-  </si>
-  <si>
-    <t>AJAKJ1</t>
-  </si>
-  <si>
-    <t>AJAKSO</t>
-  </si>
-  <si>
-    <t>AJAKYW</t>
-  </si>
-  <si>
     <t>AJAKY4</t>
   </si>
   <si>
@@ -477,13 +452,45 @@
   </si>
   <si>
     <t>AJAKZ3</t>
+  </si>
+  <si>
+    <t>Display the passenger list "All" option</t>
+  </si>
+  <si>
+    <t>Multiple passenger list request</t>
+  </si>
+  <si>
+    <t>Display the passenger list "Inbound connection" option</t>
+  </si>
+  <si>
+    <t>Create Booking</t>
+  </si>
+  <si>
+    <t>2023-02-15T05:03:00</t>
+  </si>
+  <si>
+    <t>2023-02-15T06:54:00</t>
+  </si>
+  <si>
+    <t>AJHUPU</t>
+  </si>
+  <si>
+    <t>Display loyalty account</t>
+  </si>
+  <si>
+    <t>UniqueID</t>
+  </si>
+  <si>
+    <t>230021925</t>
+  </si>
+  <si>
+    <t>Error on displayLoyaltyAccount - Invalid loyalty account</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="8">
     <font>
       <sz val="11"/>
@@ -648,7 +655,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -700,6 +707,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1020,20 +1029,20 @@
   <dimension ref="A1:P15"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="52.90625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="18.36328125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="12.08984375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="15.36328125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="9.453125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="10.453125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="11.26953125"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="10.453125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="11.26953125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="10.453125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="11.26953125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="15.08984375"/>
+    <col min="1" max="1" width="52.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1191,6 +1200,211 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ADD4D69-5509-440B-8A9B-EB710BB5A12A}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="32.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.36328125" customWidth="1"/>
+    <col min="5" max="5" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1</v>
+      </c>
+      <c r="F4" s="35" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4" s="36" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" s="3">
+        <v>2</v>
+      </c>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3">
+        <v>2</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51EE6AAF-837D-4C0C-BD88-9AF62A29B7BB}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="32.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>144</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A51EFA8C-67A7-4B7E-8EF6-A12213F165A5}">
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -1200,24 +1414,24 @@
         <v>11</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -1225,17 +1439,17 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B3" s="34"/>
       <c r="C3" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -1251,11 +1465,11 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="57.453125"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="15.54296875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="7.7265625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="11.1796875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="11.26953125"/>
+    <col min="1" max="1" width="57.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1372,30 +1586,30 @@
   <dimension ref="A1:AG4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="49.7265625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="4.81640625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="9.7265625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="4.453125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="9.7265625"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="4.453125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="9.7265625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="4.453125"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="9.7265625"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="4.453125"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="9.7265625"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="4.453125"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="9.7265625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="4.453125"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="9.7265625"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="4.453125"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="1" max="1" width="49.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="5.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33">
@@ -1707,14 +1921,14 @@
   <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="39.36328125"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="21.81640625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="12.08984375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="15.36328125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="9.453125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="6.36328125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="18.36328125"/>
+    <col min="1" max="1" width="39.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1814,11 +2028,11 @@
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="39.36328125"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="13.54296875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="7.7265625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="9.7265625"/>
+    <col min="1" max="1" width="39.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1886,19 +2100,19 @@
   <dimension ref="A1:O3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="42.0"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="18.36328125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="12.08984375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="15.36328125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="9.453125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="10.453125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="11.26953125"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="10.453125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="11.26953125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="10.453125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="8.26953125"/>
-    <col min="15" max="15" customWidth="true" width="13.0"/>
+    <col min="1" max="1" width="42" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -2029,29 +2243,29 @@
   <dimension ref="A1:AB4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="44.7265625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.7265625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="8.1796875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="11.26953125"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="10.453125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="13.54296875"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="12.08984375"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="17.7265625"/>
-    <col min="11" max="12" bestFit="true" customWidth="true" width="11.26953125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="18.08984375"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="7.7265625"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="11.26953125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="8.26953125"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="11.26953125"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="11.26953125"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="14.26953125"/>
-    <col min="27" max="28" bestFit="true" customWidth="true" width="12.90625"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="14.26953125"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="12.90625"/>
+    <col min="1" max="1" width="44.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28">
@@ -2367,10 +2581,10 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="76.1796875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="12.08984375"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="13.36328125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="12.08984375"/>
+    <col min="1" max="1" width="76.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2447,23 +2661,26 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{336A478E-B1CE-4C1B-A488-66A00AABA472}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:T6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="51.7265625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="12.08984375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="9.36328125"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="12.08984375"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="18.36328125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="12.08984375"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="14.36328125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="15.36328125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="18.36328125"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="18.36328125"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="1" max="1" width="51.7265625" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
@@ -2557,22 +2774,22 @@
         <v>7</v>
       </c>
       <c r="J2" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="K2" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>121</v>
-      </c>
       <c r="N2" s="3" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P2" s="3" t="s">
         <v>117</v>
@@ -2651,16 +2868,16 @@
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>55</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N4" s="3" t="s">
         <v>7</v>
@@ -2695,7 +2912,7 @@
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>115</v>
@@ -2720,7 +2937,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="28" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B6" s="18">
         <v>0</v>
@@ -2743,16 +2960,16 @@
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>55</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N6" s="3" t="s">
         <v>7</v>

--- a/src/test/java/TestData/Scenario_TestData.xlsx
+++ b/src/test/java/TestData/Scenario_TestData.xlsx
@@ -8,37 +8,42 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\COPA Automation Final\Copa_API_WebServices\src\test\java\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA946282-597F-4D1F-B2AE-3911839DF532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00A0AB71-91C3-48C1-A416-63E249A1D32E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="21" activeTab="24" xr2:uid="{5D5A4724-D560-4FC2-9708-4BBF1DBA0B11}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="11" xr2:uid="{5D5A4724-D560-4FC2-9708-4BBF1DBA0B11}"/>
   </bookViews>
   <sheets>
     <sheet name="AdvancePassengerInfo" sheetId="1" r:id="rId1"/>
-    <sheet name="Boarding" sheetId="5" r:id="rId2"/>
-    <sheet name="AirInventoryService" sheetId="2" r:id="rId3"/>
-    <sheet name="AirportPassengerList" sheetId="3" r:id="rId4"/>
-    <sheet name="Availability" sheetId="4" r:id="rId5"/>
+    <sheet name="AirInventoryService" sheetId="2" r:id="rId2"/>
+    <sheet name="AirportPassengerList" sheetId="3" r:id="rId3"/>
+    <sheet name="Availability" sheetId="4" r:id="rId4"/>
+    <sheet name="Boarding" sheetId="5" r:id="rId5"/>
     <sheet name="CheckIn" sheetId="6" r:id="rId6"/>
     <sheet name="CreateBookingServiceOld" sheetId="7" r:id="rId7"/>
     <sheet name="CreateBookingService" sheetId="24" r:id="rId8"/>
-    <sheet name="ModifyInventoryService" sheetId="8" r:id="rId9"/>
-    <sheet name="ModifyBookingSer_CancelBooking" sheetId="9" r:id="rId10"/>
-    <sheet name="PassengerListService" sheetId="11" r:id="rId11"/>
-    <sheet name="DisplayLoyaltyAccountService" sheetId="12" r:id="rId12"/>
-    <sheet name="DepartureControlService" sheetId="13" r:id="rId13"/>
-    <sheet name="ScreenTextService" sheetId="14" r:id="rId14"/>
-    <sheet name="ModifyTicketingService" sheetId="19" r:id="rId15"/>
-    <sheet name="EncodeDecodeService" sheetId="15" r:id="rId16"/>
-    <sheet name="FlightDepartureInfoService" sheetId="16" r:id="rId17"/>
-    <sheet name="AuthorizationService" sheetId="17" r:id="rId18"/>
-    <sheet name="SeatMapService" sheetId="18" r:id="rId19"/>
-    <sheet name="EMDAirlineSystemUpdate" sheetId="21" r:id="rId20"/>
-    <sheet name="TicketingService" sheetId="22" r:id="rId21"/>
-    <sheet name="TicketControlService" sheetId="20" r:id="rId22"/>
-    <sheet name="AirScheduleService" sheetId="23" r:id="rId23"/>
-    <sheet name="SynchronizeTicketService" sheetId="25" r:id="rId24"/>
-    <sheet name="DisplayBookingService" sheetId="26" r:id="rId25"/>
-    <sheet name="ReferenceService" sheetId="10" r:id="rId26"/>
+    <sheet name="DepartureControlService" sheetId="13" r:id="rId9"/>
+    <sheet name="DisplayBookingService" sheetId="26" r:id="rId10"/>
+    <sheet name="ManageSessions" sheetId="27" r:id="rId11"/>
+    <sheet name="DisplayTicketService" sheetId="31" r:id="rId12"/>
+    <sheet name="FlifoService" sheetId="28" r:id="rId13"/>
+    <sheet name="ModifyBookingSer_CancelBooking" sheetId="9" r:id="rId14"/>
+    <sheet name="ModifyInventoryService" sheetId="8" r:id="rId15"/>
+    <sheet name="QueueService" sheetId="29" r:id="rId16"/>
+    <sheet name="ScreenTextService" sheetId="14" r:id="rId17"/>
+    <sheet name="SeatMapService" sheetId="18" r:id="rId18"/>
+    <sheet name="AirScheduleService" sheetId="23" r:id="rId19"/>
+    <sheet name="TicketingService" sheetId="22" r:id="rId20"/>
+    <sheet name="FlightDepartureInfoService" sheetId="16" r:id="rId21"/>
+    <sheet name="AuthorizationService" sheetId="17" r:id="rId22"/>
+    <sheet name="EMDAirlineSystemUpdate" sheetId="21" r:id="rId23"/>
+    <sheet name="EncodeDecodeService" sheetId="15" r:id="rId24"/>
+    <sheet name="ModifyTicketingService" sheetId="19" r:id="rId25"/>
+    <sheet name="TicketControlService" sheetId="20" r:id="rId26"/>
+    <sheet name="DisplayLoyaltyAccountService" sheetId="12" r:id="rId27"/>
+    <sheet name="ReferenceService" sheetId="10" r:id="rId28"/>
+    <sheet name="TimaticService" sheetId="30" r:id="rId29"/>
+    <sheet name="PassengerListService" sheetId="11" r:id="rId30"/>
+    <sheet name="SynchronizeTicketService" sheetId="25" r:id="rId31"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -61,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1318" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1874" uniqueCount="652">
   <si>
     <t>Scenario</t>
   </si>
@@ -1272,22 +1277,751 @@
     <t>BLQQGW</t>
   </si>
   <si>
-    <t>BLQSFU</t>
-  </si>
-  <si>
     <t>1931</t>
   </si>
   <si>
-    <t>BLQTWX</t>
-  </si>
-  <si>
     <t>BLQURE</t>
   </si>
   <si>
-    <t>BLQU4W</t>
-  </si>
-  <si>
     <t>BLQU5S</t>
+  </si>
+  <si>
+    <t>TransactionIdentifier</t>
+  </si>
+  <si>
+    <t>Airline Code</t>
+  </si>
+  <si>
+    <t>Modify_Booking</t>
+  </si>
+  <si>
+    <t>97C6BC48CMCMRPCT083ADC3BAA</t>
+  </si>
+  <si>
+    <t>BLQJ3A</t>
+  </si>
+  <si>
+    <t>Create_a_booking_for_a_group</t>
+  </si>
+  <si>
+    <t>8F4F96CECMCMRPCT05409404B2</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Create_a_booking_for_two_segments</t>
+  </si>
+  <si>
+    <t>D25C161ACMCMRPCT07BE802116</t>
+  </si>
+  <si>
+    <t>AirlineVendorID</t>
+  </si>
+  <si>
+    <t>DepartureTime</t>
+  </si>
+  <si>
+    <t>Flifo_for_one_flight_specifying_departure_arrival_city_actual_times</t>
+  </si>
+  <si>
+    <t>Flifo_for_Two_flights</t>
+  </si>
+  <si>
+    <t>Flifo_for_codeshare_flight</t>
+  </si>
+  <si>
+    <t>Country Code</t>
+  </si>
+  <si>
+    <t>QueueNumber</t>
+  </si>
+  <si>
+    <t>End</t>
+  </si>
+  <si>
+    <t>Display_queue_booking_all_items_full_data_format_not_remove_from_queue</t>
+  </si>
+  <si>
+    <t>Display_queue_booking_from_empty_queue</t>
+  </si>
+  <si>
+    <t>Queue_booking</t>
+  </si>
+  <si>
+    <t>Display_message</t>
+  </si>
+  <si>
+    <t>Display_And_Remove_Message_Default_City</t>
+  </si>
+  <si>
+    <t>Display_and_remove_message</t>
+  </si>
+  <si>
+    <t>Queue_Multiple_Messages</t>
+  </si>
+  <si>
+    <t>Transfer_Queue_Today_to_End_Date</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>01-06-2023</t>
+  </si>
+  <si>
+    <t>Abort_schedule_change_queue_transfer</t>
+  </si>
+  <si>
+    <t>Sort_Queue</t>
+  </si>
+  <si>
+    <t>Display_Booking_queue_count_for_a_given_city</t>
+  </si>
+  <si>
+    <t>Display_queue_count_for_Booking_Message_Queues</t>
+  </si>
+  <si>
+    <t>Queue_Passenger_List</t>
+  </si>
+  <si>
+    <t>Queue_a_specific_passenger_list</t>
+  </si>
+  <si>
+    <t>Request_Visa_Info_one_destination_transit_visited_point</t>
+  </si>
+  <si>
+    <t>Visa_singlepoint_normal_request</t>
+  </si>
+  <si>
+    <t>Visa_singlepoint_seaman_request</t>
+  </si>
+  <si>
+    <t>Both_DEorTR_missing_request</t>
+  </si>
+  <si>
+    <t>Health_DEorTR_missing_request</t>
+  </si>
+  <si>
+    <t>Visa_DEorTR_missing_request</t>
+  </si>
+  <si>
+    <t>Both_multipoint_gov_request</t>
+  </si>
+  <si>
+    <t>Both_multipoint_normal_request</t>
+  </si>
+  <si>
+    <t>Both_multipoint_seaman_request</t>
+  </si>
+  <si>
+    <t>Display_Country_List_in_a_Group</t>
+  </si>
+  <si>
+    <t>Display_Rules_with_Rule_Index</t>
+  </si>
+  <si>
+    <t>Display_the_List_of_News_Items</t>
+  </si>
+  <si>
+    <t>Display_City_list_by_Country_code</t>
+  </si>
+  <si>
+    <t>Display_for_section_Passport_with_its_subsection</t>
+  </si>
+  <si>
+    <t>Display_for_section_Currency_with_its_subsection</t>
+  </si>
+  <si>
+    <t>Display_all_sections_for_a_country</t>
+  </si>
+  <si>
+    <t>Ticket Number 1</t>
+  </si>
+  <si>
+    <t>Ticket Number 2</t>
+  </si>
+  <si>
+    <t>Search_for_a_non_existent_PNR</t>
+  </si>
+  <si>
+    <t>Search_for_a_PNR_with_no_ETKT</t>
+  </si>
+  <si>
+    <t>Retrieve_E_Ticket_History_information_for_a_given_PNR</t>
+  </si>
+  <si>
+    <t>Booking_multiple_tickets</t>
+  </si>
+  <si>
+    <t>BPHLTF</t>
+  </si>
+  <si>
+    <t>2302181199430</t>
+  </si>
+  <si>
+    <t>2302181199431</t>
+  </si>
+  <si>
+    <t>Bulk_Ticket</t>
+  </si>
+  <si>
+    <t>BOCZVC</t>
+  </si>
+  <si>
+    <t>BOCZWU</t>
+  </si>
+  <si>
+    <t>BOCZW0</t>
+  </si>
+  <si>
+    <t>BOCZXB</t>
+  </si>
+  <si>
+    <t>BOCZZD</t>
+  </si>
+  <si>
+    <t>2023-05-18T14:30:46</t>
+  </si>
+  <si>
+    <t>BOCZ34</t>
+  </si>
+  <si>
+    <t>2023-05-18T14:30:53</t>
+  </si>
+  <si>
+    <t>BOC0AQ</t>
+  </si>
+  <si>
+    <t>BOC0BS</t>
+  </si>
+  <si>
+    <t>BOC0CY</t>
+  </si>
+  <si>
+    <t>2302181833965</t>
+  </si>
+  <si>
+    <t>BOC0IU</t>
+  </si>
+  <si>
+    <t>2302181833970</t>
+  </si>
+  <si>
+    <t>BOC0UW</t>
+  </si>
+  <si>
+    <t>2302181833972</t>
+  </si>
+  <si>
+    <t>BOC00G</t>
+  </si>
+  <si>
+    <t>2302181833973</t>
+  </si>
+  <si>
+    <t>BOC015</t>
+  </si>
+  <si>
+    <t>2302181833974</t>
+  </si>
+  <si>
+    <t>BOC03M</t>
+  </si>
+  <si>
+    <t>2302181833975</t>
+  </si>
+  <si>
+    <t>BOC041</t>
+  </si>
+  <si>
+    <t>2302181833976</t>
+  </si>
+  <si>
+    <t>BOC1C2</t>
+  </si>
+  <si>
+    <t>BOC1E2</t>
+  </si>
+  <si>
+    <t>BOC1FN</t>
+  </si>
+  <si>
+    <t>BOC1GI</t>
+  </si>
+  <si>
+    <t>BOC1HO</t>
+  </si>
+  <si>
+    <t>BOC1HY</t>
+  </si>
+  <si>
+    <t>2302181833978</t>
+  </si>
+  <si>
+    <t>BOC1H5</t>
+  </si>
+  <si>
+    <t>BOC1LY</t>
+  </si>
+  <si>
+    <t>2302181833979</t>
+  </si>
+  <si>
+    <t>BOC1NK</t>
+  </si>
+  <si>
+    <t>BOC1N4</t>
+  </si>
+  <si>
+    <t>BOC1OI</t>
+  </si>
+  <si>
+    <t>2302181833982</t>
+  </si>
+  <si>
+    <t>BOC1O0</t>
+  </si>
+  <si>
+    <t>2302181833983</t>
+  </si>
+  <si>
+    <t>BOC1RH</t>
+  </si>
+  <si>
+    <t>2302181833986</t>
+  </si>
+  <si>
+    <t>BOC1SS</t>
+  </si>
+  <si>
+    <t>BOC1TN</t>
+  </si>
+  <si>
+    <t>2302181833987</t>
+  </si>
+  <si>
+    <t>BOC1WD</t>
+  </si>
+  <si>
+    <t>EA79875ECMCMRPCT06AE946B61</t>
+  </si>
+  <si>
+    <t>6244B83CCMCMRPCT085EB41F86</t>
+  </si>
+  <si>
+    <t>89B4E13ECMCMRPCT08446A5E88</t>
+  </si>
+  <si>
+    <t>BOC22U</t>
+  </si>
+  <si>
+    <t>2023-05-19T09:56:00</t>
+  </si>
+  <si>
+    <t>2023-05-19T13:57:00</t>
+  </si>
+  <si>
+    <t>2023-05-23T13:16:00</t>
+  </si>
+  <si>
+    <t>2023-05-23T15:21:00</t>
+  </si>
+  <si>
+    <t>BOC24F</t>
+  </si>
+  <si>
+    <t>2023-05-21T07:48:00</t>
+  </si>
+  <si>
+    <t>2023-05-21T11:54:00</t>
+  </si>
+  <si>
+    <t>BOC3C4</t>
+  </si>
+  <si>
+    <t>2023-05-19T07:50:00</t>
+  </si>
+  <si>
+    <t>2023-05-19T09:29:00</t>
+  </si>
+  <si>
+    <t>BOC3D4</t>
+  </si>
+  <si>
+    <t>2024-03-09T20:51:00</t>
+  </si>
+  <si>
+    <t>2024-03-10T06:42:00</t>
+  </si>
+  <si>
+    <t>BOC3ES</t>
+  </si>
+  <si>
+    <t>2302181834007</t>
+  </si>
+  <si>
+    <t>BOC3FZ</t>
+  </si>
+  <si>
+    <t>BOC3GM</t>
+  </si>
+  <si>
+    <t>BOC3HN</t>
+  </si>
+  <si>
+    <t>BOC3LG</t>
+  </si>
+  <si>
+    <t>2302181834013</t>
+  </si>
+  <si>
+    <t>BOC3OZ</t>
+  </si>
+  <si>
+    <t>2302181834014</t>
+  </si>
+  <si>
+    <t>BOC3RZ</t>
+  </si>
+  <si>
+    <t>2023-05-19T07:56:00</t>
+  </si>
+  <si>
+    <t>2023-05-19T12:35:00</t>
+  </si>
+  <si>
+    <t>2023-05-19T14:06:00</t>
+  </si>
+  <si>
+    <t>2023-05-19T15:40:00</t>
+  </si>
+  <si>
+    <t>2302181834017</t>
+  </si>
+  <si>
+    <t>BODJXX</t>
+  </si>
+  <si>
+    <t>BODJYB</t>
+  </si>
+  <si>
+    <t>BODJYD</t>
+  </si>
+  <si>
+    <t>BODJZF</t>
+  </si>
+  <si>
+    <t>BODJ3C</t>
+  </si>
+  <si>
+    <t>2023-05-18T15:09:06</t>
+  </si>
+  <si>
+    <t>BODKGK</t>
+  </si>
+  <si>
+    <t>2023-05-18T15:09:14</t>
+  </si>
+  <si>
+    <t>BODKTO</t>
+  </si>
+  <si>
+    <t>BODKW0</t>
+  </si>
+  <si>
+    <t>BODKYM</t>
+  </si>
+  <si>
+    <t>2302181834306</t>
+  </si>
+  <si>
+    <t>BODK0Y</t>
+  </si>
+  <si>
+    <t>2302181834307</t>
+  </si>
+  <si>
+    <t>BODLES</t>
+  </si>
+  <si>
+    <t>2302181834309</t>
+  </si>
+  <si>
+    <t>BODLK4</t>
+  </si>
+  <si>
+    <t>2302181834310</t>
+  </si>
+  <si>
+    <t>BODLLJ</t>
+  </si>
+  <si>
+    <t>2302181834311</t>
+  </si>
+  <si>
+    <t>BODLMC</t>
+  </si>
+  <si>
+    <t>2302181834312</t>
+  </si>
+  <si>
+    <t>BODLNY</t>
+  </si>
+  <si>
+    <t>2302181834313</t>
+  </si>
+  <si>
+    <t>BODLO1</t>
+  </si>
+  <si>
+    <t>BODLP5</t>
+  </si>
+  <si>
+    <t>BODLRI</t>
+  </si>
+  <si>
+    <t>BODLTC</t>
+  </si>
+  <si>
+    <t>BODLU4</t>
+  </si>
+  <si>
+    <t>BODLVV</t>
+  </si>
+  <si>
+    <t>2302181834318</t>
+  </si>
+  <si>
+    <t>BODLWJ</t>
+  </si>
+  <si>
+    <t>BODL0A</t>
+  </si>
+  <si>
+    <t>2302181834319</t>
+  </si>
+  <si>
+    <t>BODL1K</t>
+  </si>
+  <si>
+    <t>BODL1T</t>
+  </si>
+  <si>
+    <t>BODL51</t>
+  </si>
+  <si>
+    <t>22EE7770CMCMRPCT05339998DA</t>
+  </si>
+  <si>
+    <t>80CA5544CMCMRPCT06F5059406</t>
+  </si>
+  <si>
+    <t>B0A4D95ECMCMRPCT08D51EEDEF</t>
+  </si>
+  <si>
+    <t>BODNR1</t>
+  </si>
+  <si>
+    <t>BODNWG</t>
+  </si>
+  <si>
+    <t>BODNY1</t>
+  </si>
+  <si>
+    <t>BODNZL</t>
+  </si>
+  <si>
+    <t>BODN0O</t>
+  </si>
+  <si>
+    <t>2302181834325</t>
+  </si>
+  <si>
+    <t>BODN5B</t>
+  </si>
+  <si>
+    <t>2302181834326</t>
+  </si>
+  <si>
+    <t>BODOEH</t>
+  </si>
+  <si>
+    <t>2302181834330</t>
+  </si>
+  <si>
+    <t>AEEZ0N</t>
+  </si>
+  <si>
+    <t>AEEZ1U</t>
+  </si>
+  <si>
+    <t>AEEZ2U</t>
+  </si>
+  <si>
+    <t>AEEZ3E</t>
+  </si>
+  <si>
+    <t>AEEZ5C</t>
+  </si>
+  <si>
+    <t>2023-06-01T06:39:06</t>
+  </si>
+  <si>
+    <t>AEE0AE</t>
+  </si>
+  <si>
+    <t>2023-06-01T06:39:13</t>
+  </si>
+  <si>
+    <t>AEE0DJ</t>
+  </si>
+  <si>
+    <t>AEE0EF</t>
+  </si>
+  <si>
+    <t>AEE0FZ</t>
+  </si>
+  <si>
+    <t>2302181859845</t>
+  </si>
+  <si>
+    <t>AEE0LA</t>
+  </si>
+  <si>
+    <t>2302181859846</t>
+  </si>
+  <si>
+    <t>AEE0OT</t>
+  </si>
+  <si>
+    <t>2302181859847</t>
+  </si>
+  <si>
+    <t>AEE0PG</t>
+  </si>
+  <si>
+    <t>2302181859848</t>
+  </si>
+  <si>
+    <t>AEE0QL</t>
+  </si>
+  <si>
+    <t>2302181859849</t>
+  </si>
+  <si>
+    <t>AEE0RU</t>
+  </si>
+  <si>
+    <t>2302181859850</t>
+  </si>
+  <si>
+    <t>AEE0SJ</t>
+  </si>
+  <si>
+    <t>AEE0TP</t>
+  </si>
+  <si>
+    <t>AEE0UB</t>
+  </si>
+  <si>
+    <t>AEE0VF</t>
+  </si>
+  <si>
+    <t>AEE0WG</t>
+  </si>
+  <si>
+    <t>AEE0WN</t>
+  </si>
+  <si>
+    <t>2302181859851</t>
+  </si>
+  <si>
+    <t>AEE0XP</t>
+  </si>
+  <si>
+    <t>AEE0YP</t>
+  </si>
+  <si>
+    <t>2302181859852</t>
+  </si>
+  <si>
+    <t>AEE0ZV</t>
+  </si>
+  <si>
+    <t>AEE0ZY</t>
+  </si>
+  <si>
+    <t>AEE00K</t>
+  </si>
+  <si>
+    <t>2302181859853</t>
+  </si>
+  <si>
+    <t>AEE00Z</t>
+  </si>
+  <si>
+    <t>2302181859854</t>
+  </si>
+  <si>
+    <t>AEE01R</t>
+  </si>
+  <si>
+    <t>2302181859855</t>
+  </si>
+  <si>
+    <t>AEE02Y</t>
+  </si>
+  <si>
+    <t>AEE03H</t>
+  </si>
+  <si>
+    <t>2302181859856</t>
+  </si>
+  <si>
+    <t>5953A61ECMCMRPCT05BA12EE48</t>
+  </si>
+  <si>
+    <t>BC0E61FCCMCMRPCT0622E94D6C</t>
+  </si>
+  <si>
+    <t>AEE4KI</t>
+  </si>
+  <si>
+    <t>2023-06-02T07:55:00</t>
+  </si>
+  <si>
+    <t>2023-06-02T09:29:00</t>
+  </si>
+  <si>
+    <t>AEE4PJ</t>
+  </si>
+  <si>
+    <t>AEE4S1</t>
+  </si>
+  <si>
+    <t>2302181859867</t>
+  </si>
+  <si>
+    <t>AEE4WE</t>
+  </si>
+  <si>
+    <t>AEE4XT</t>
+  </si>
+  <si>
+    <t>AEE4YV</t>
+  </si>
+  <si>
+    <t>AEE5HK</t>
+  </si>
+  <si>
+    <t>2302181859873</t>
+  </si>
+  <si>
+    <t>AEE5L5</t>
+  </si>
+  <si>
+    <t>2302181859874</t>
   </si>
 </sst>
 </file>
@@ -1478,7 +2212,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1563,6 +2297,14 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1969,24 +2711,24 @@
         <v>16</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>17</v>
+        <v>596</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>18</v>
+        <v>323</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>19</v>
+        <v>324</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>20</v>
+        <v>323</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>21</v>
+        <v>324</v>
       </c>
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
       <c r="O2" s="3" t="s">
-        <v>22</v>
+        <v>597</v>
       </c>
       <c r="P2" s="24"/>
     </row>
@@ -2054,6 +2796,1262 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C501783-003E-43C7-BF08-448ED073E85B}">
+  <dimension ref="A1:U22"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="10" max="10" style="45" width="8.7265625"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="9.81640625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21">
+      <c r="A1" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="E1" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="F1" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="I1" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="J1" s="40" t="s">
+        <v>194</v>
+      </c>
+      <c r="K1" s="54" t="s">
+        <v>105</v>
+      </c>
+      <c r="L1" s="54" t="s">
+        <v>275</v>
+      </c>
+      <c r="M1" s="40" t="s">
+        <v>358</v>
+      </c>
+      <c r="N1" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="P1" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q1" s="36" t="s">
+        <v>361</v>
+      </c>
+      <c r="R1" s="47" t="s">
+        <v>214</v>
+      </c>
+      <c r="S1" s="46" t="s">
+        <v>369</v>
+      </c>
+      <c r="T1" s="47" t="s">
+        <v>396</v>
+      </c>
+      <c r="U1" s="47" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21">
+      <c r="A2" s="53" t="s">
+        <v>332</v>
+      </c>
+      <c r="B2" s="48">
+        <v>1</v>
+      </c>
+      <c r="C2" s="50" t="s">
+        <v>353</v>
+      </c>
+      <c r="D2" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="48">
+        <v>2</v>
+      </c>
+      <c r="G2" s="50" t="s">
+        <v>354</v>
+      </c>
+      <c r="H2" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="I2" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48" t="s">
+        <v>355</v>
+      </c>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="37"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+    </row>
+    <row r="3" spans="1:21">
+      <c r="A3" s="53" t="s">
+        <v>333</v>
+      </c>
+      <c r="B3" s="48">
+        <v>1</v>
+      </c>
+      <c r="C3" s="50" t="s">
+        <v>353</v>
+      </c>
+      <c r="D3" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="48"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48">
+        <v>0</v>
+      </c>
+      <c r="K3" s="48" t="s">
+        <v>621</v>
+      </c>
+      <c r="L3" s="48" t="s">
+        <v>622</v>
+      </c>
+      <c r="M3" s="48"/>
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+    </row>
+    <row r="4" spans="1:21">
+      <c r="A4" s="53" t="s">
+        <v>334</v>
+      </c>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="48"/>
+      <c r="L4" s="48"/>
+      <c r="M4" s="48" t="s">
+        <v>359</v>
+      </c>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="37"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+    </row>
+    <row r="5" spans="1:21">
+      <c r="A5" s="53" t="s">
+        <v>335</v>
+      </c>
+      <c r="B5" s="48">
+        <v>1</v>
+      </c>
+      <c r="C5" s="50" t="s">
+        <v>353</v>
+      </c>
+      <c r="D5" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="48"/>
+      <c r="K5" s="48" t="s">
+        <v>624</v>
+      </c>
+      <c r="L5" s="48" t="s">
+        <v>625</v>
+      </c>
+      <c r="M5" s="48"/>
+      <c r="N5" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="O5" s="48" t="s">
+        <v>360</v>
+      </c>
+      <c r="P5" s="48" t="s">
+        <v>400</v>
+      </c>
+      <c r="Q5" s="37"/>
+      <c r="R5" s="48"/>
+      <c r="S5" s="48"/>
+      <c r="T5" s="48" t="s">
+        <v>398</v>
+      </c>
+      <c r="U5" s="48" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
+      <c r="A6" s="53" t="s">
+        <v>336</v>
+      </c>
+      <c r="B6" s="48">
+        <v>1</v>
+      </c>
+      <c r="C6" s="50" t="s">
+        <v>353</v>
+      </c>
+      <c r="D6" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="48" t="s">
+        <v>626</v>
+      </c>
+      <c r="L6" s="48"/>
+      <c r="M6" s="48"/>
+      <c r="N6" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="O6" s="48" t="s">
+        <v>360</v>
+      </c>
+      <c r="P6" s="48" t="s">
+        <v>627</v>
+      </c>
+      <c r="Q6" s="37"/>
+      <c r="R6" s="48"/>
+      <c r="S6" s="48"/>
+      <c r="T6" s="48" t="s">
+        <v>398</v>
+      </c>
+      <c r="U6" s="48" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
+      <c r="A7" s="53" t="s">
+        <v>337</v>
+      </c>
+      <c r="B7" s="48">
+        <v>1</v>
+      </c>
+      <c r="C7" s="50" t="s">
+        <v>353</v>
+      </c>
+      <c r="D7" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="48"/>
+      <c r="K7" s="48" t="s">
+        <v>628</v>
+      </c>
+      <c r="L7" s="48" t="s">
+        <v>629</v>
+      </c>
+      <c r="M7" s="48"/>
+      <c r="N7" s="48" t="s">
+        <v>362</v>
+      </c>
+      <c r="O7" s="48" t="s">
+        <v>360</v>
+      </c>
+      <c r="P7" s="48" t="s">
+        <v>630</v>
+      </c>
+      <c r="Q7" s="55" t="s">
+        <v>131</v>
+      </c>
+      <c r="R7" s="48" t="s">
+        <v>631</v>
+      </c>
+      <c r="S7" s="48"/>
+      <c r="T7" s="48"/>
+      <c r="U7" s="48"/>
+    </row>
+    <row r="8" spans="1:21">
+      <c r="A8" s="53" t="s">
+        <v>338</v>
+      </c>
+      <c r="B8" s="48">
+        <v>1</v>
+      </c>
+      <c r="C8" s="50" t="s">
+        <v>353</v>
+      </c>
+      <c r="D8" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="48">
+        <v>2</v>
+      </c>
+      <c r="G8" s="50" t="s">
+        <v>354</v>
+      </c>
+      <c r="H8" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="I8" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="48"/>
+      <c r="K8" s="48" t="s">
+        <v>632</v>
+      </c>
+      <c r="L8" s="48" t="s">
+        <v>633</v>
+      </c>
+      <c r="M8" s="48"/>
+      <c r="N8" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="O8" s="48" t="s">
+        <v>364</v>
+      </c>
+      <c r="P8" s="48"/>
+      <c r="Q8" s="37"/>
+      <c r="R8" s="48"/>
+      <c r="S8" s="48"/>
+      <c r="T8" s="48"/>
+      <c r="U8" s="48"/>
+    </row>
+    <row r="9" spans="1:21">
+      <c r="A9" s="53" t="s">
+        <v>339</v>
+      </c>
+      <c r="B9" s="48">
+        <v>1</v>
+      </c>
+      <c r="C9" s="50" t="s">
+        <v>353</v>
+      </c>
+      <c r="D9" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+      <c r="J9" s="48"/>
+      <c r="K9" s="48" t="s">
+        <v>634</v>
+      </c>
+      <c r="L9" s="48"/>
+      <c r="M9" s="48"/>
+      <c r="N9" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="O9" s="48" t="s">
+        <v>367</v>
+      </c>
+      <c r="P9" s="48"/>
+      <c r="Q9" s="37"/>
+      <c r="R9" s="48"/>
+      <c r="S9" s="48"/>
+      <c r="T9" s="48"/>
+      <c r="U9" s="48"/>
+    </row>
+    <row r="10" spans="1:21">
+      <c r="A10" s="53" t="s">
+        <v>340</v>
+      </c>
+      <c r="B10" s="48">
+        <v>1</v>
+      </c>
+      <c r="C10" s="50" t="s">
+        <v>353</v>
+      </c>
+      <c r="D10" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" s="48"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="48"/>
+      <c r="I10" s="48"/>
+      <c r="J10" s="48"/>
+      <c r="K10" s="48" t="s">
+        <v>635</v>
+      </c>
+      <c r="L10" s="48" t="s">
+        <v>636</v>
+      </c>
+      <c r="M10" s="48"/>
+      <c r="N10" s="48"/>
+      <c r="O10" s="48"/>
+      <c r="P10" s="48"/>
+      <c r="Q10" s="37"/>
+      <c r="R10" s="48"/>
+      <c r="S10" s="50" t="s">
+        <v>370</v>
+      </c>
+      <c r="T10" s="48"/>
+      <c r="U10" s="48"/>
+    </row>
+    <row r="11" spans="1:21">
+      <c r="A11" s="53" t="s">
+        <v>341</v>
+      </c>
+      <c r="B11" s="48">
+        <v>1</v>
+      </c>
+      <c r="C11" s="50" t="s">
+        <v>353</v>
+      </c>
+      <c r="D11" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="48"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="48"/>
+      <c r="K11" s="48" t="s">
+        <v>608</v>
+      </c>
+      <c r="L11" s="48" t="s">
+        <v>609</v>
+      </c>
+      <c r="M11" s="48"/>
+      <c r="N11" s="48"/>
+      <c r="O11" s="48"/>
+      <c r="P11" s="48"/>
+      <c r="Q11" s="37"/>
+      <c r="R11" s="48"/>
+      <c r="S11" s="50" t="s">
+        <v>370</v>
+      </c>
+      <c r="T11" s="48"/>
+      <c r="U11" s="48"/>
+    </row>
+    <row r="12" spans="1:21">
+      <c r="A12" s="53" t="s">
+        <v>342</v>
+      </c>
+      <c r="B12" s="48">
+        <v>1</v>
+      </c>
+      <c r="C12" s="50" t="s">
+        <v>353</v>
+      </c>
+      <c r="D12" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12" s="48"/>
+      <c r="G12" s="48"/>
+      <c r="H12" s="48"/>
+      <c r="I12" s="48"/>
+      <c r="J12" s="48"/>
+      <c r="K12" s="48" t="s">
+        <v>610</v>
+      </c>
+      <c r="L12" s="48" t="s">
+        <v>611</v>
+      </c>
+      <c r="M12" s="48"/>
+      <c r="N12" s="48" t="s">
+        <v>362</v>
+      </c>
+      <c r="O12" s="48" t="s">
+        <v>374</v>
+      </c>
+      <c r="P12" s="48"/>
+      <c r="Q12" s="55" t="s">
+        <v>131</v>
+      </c>
+      <c r="R12" s="48"/>
+      <c r="S12" s="48"/>
+      <c r="T12" s="48"/>
+      <c r="U12" s="48"/>
+    </row>
+    <row r="13" spans="1:21">
+      <c r="A13" s="53" t="s">
+        <v>343</v>
+      </c>
+      <c r="B13" s="48">
+        <v>1</v>
+      </c>
+      <c r="C13" s="50" t="s">
+        <v>353</v>
+      </c>
+      <c r="D13" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="F13" s="48"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="48"/>
+      <c r="I13" s="48"/>
+      <c r="J13" s="48"/>
+      <c r="K13" s="48" t="s">
+        <v>612</v>
+      </c>
+      <c r="L13" s="48" t="s">
+        <v>613</v>
+      </c>
+      <c r="M13" s="48"/>
+      <c r="N13" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="O13" s="48" t="s">
+        <v>360</v>
+      </c>
+      <c r="P13" s="48"/>
+      <c r="Q13" s="37"/>
+      <c r="R13" s="48"/>
+      <c r="S13" s="50" t="s">
+        <v>370</v>
+      </c>
+      <c r="T13" s="48"/>
+      <c r="U13" s="48"/>
+    </row>
+    <row r="14" spans="1:21">
+      <c r="A14" s="53" t="s">
+        <v>344</v>
+      </c>
+      <c r="B14" s="48">
+        <v>1</v>
+      </c>
+      <c r="C14" s="50" t="s">
+        <v>353</v>
+      </c>
+      <c r="D14" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="48"/>
+      <c r="K14" s="48"/>
+      <c r="L14" s="48"/>
+      <c r="M14" s="48"/>
+      <c r="N14" s="48"/>
+      <c r="O14" s="48"/>
+      <c r="P14" s="48"/>
+      <c r="Q14" s="37"/>
+      <c r="R14" s="48"/>
+      <c r="S14" s="50" t="s">
+        <v>384</v>
+      </c>
+      <c r="T14" s="48"/>
+      <c r="U14" s="48"/>
+    </row>
+    <row r="15" spans="1:21">
+      <c r="A15" s="53" t="s">
+        <v>345</v>
+      </c>
+      <c r="B15" s="48">
+        <v>1</v>
+      </c>
+      <c r="C15" s="50" t="s">
+        <v>353</v>
+      </c>
+      <c r="D15" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="F15" s="48"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="48"/>
+      <c r="J15" s="48"/>
+      <c r="K15" s="48" t="s">
+        <v>614</v>
+      </c>
+      <c r="L15" s="48" t="s">
+        <v>615</v>
+      </c>
+      <c r="M15" s="48"/>
+      <c r="N15" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="O15" s="48" t="s">
+        <v>360</v>
+      </c>
+      <c r="P15" s="48"/>
+      <c r="Q15" s="37"/>
+      <c r="R15" s="48"/>
+      <c r="S15" s="50" t="s">
+        <v>370</v>
+      </c>
+      <c r="T15" s="48"/>
+      <c r="U15" s="48"/>
+    </row>
+    <row r="16" spans="1:21">
+      <c r="A16" s="53" t="s">
+        <v>346</v>
+      </c>
+      <c r="B16" s="48">
+        <v>1</v>
+      </c>
+      <c r="C16" s="50" t="s">
+        <v>353</v>
+      </c>
+      <c r="D16" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="F16" s="48"/>
+      <c r="G16" s="48"/>
+      <c r="H16" s="48"/>
+      <c r="I16" s="48"/>
+      <c r="J16" s="48"/>
+      <c r="K16" s="48" t="s">
+        <v>616</v>
+      </c>
+      <c r="L16" s="48"/>
+      <c r="M16" s="48"/>
+      <c r="N16" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="O16" s="48" t="s">
+        <v>387</v>
+      </c>
+      <c r="P16" s="48"/>
+      <c r="Q16" s="37"/>
+      <c r="R16" s="48"/>
+      <c r="S16" s="48"/>
+      <c r="T16" s="48"/>
+      <c r="U16" s="48"/>
+    </row>
+    <row r="17" spans="1:21">
+      <c r="A17" s="53" t="s">
+        <v>347</v>
+      </c>
+      <c r="B17" s="48">
+        <v>1</v>
+      </c>
+      <c r="C17" s="50" t="s">
+        <v>353</v>
+      </c>
+      <c r="D17" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" s="48"/>
+      <c r="G17" s="48"/>
+      <c r="H17" s="48"/>
+      <c r="I17" s="48"/>
+      <c r="J17" s="48"/>
+      <c r="K17" s="48" t="s">
+        <v>617</v>
+      </c>
+      <c r="L17" s="48"/>
+      <c r="M17" s="48"/>
+      <c r="N17" s="48"/>
+      <c r="O17" s="48"/>
+      <c r="P17" s="48"/>
+      <c r="Q17" s="37"/>
+      <c r="R17" s="48"/>
+      <c r="S17" s="48"/>
+      <c r="T17" s="48"/>
+      <c r="U17" s="48"/>
+    </row>
+    <row r="18" spans="1:21">
+      <c r="A18" s="53" t="s">
+        <v>348</v>
+      </c>
+      <c r="B18" s="48">
+        <v>1</v>
+      </c>
+      <c r="C18" s="50" t="s">
+        <v>353</v>
+      </c>
+      <c r="D18" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" s="48">
+        <v>2</v>
+      </c>
+      <c r="G18" s="50" t="s">
+        <v>354</v>
+      </c>
+      <c r="H18" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="I18" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="J18" s="48"/>
+      <c r="K18" s="48" t="s">
+        <v>618</v>
+      </c>
+      <c r="L18" s="48"/>
+      <c r="M18" s="48"/>
+      <c r="N18" s="48" t="s">
+        <v>390</v>
+      </c>
+      <c r="O18" s="48" t="s">
+        <v>391</v>
+      </c>
+      <c r="P18" s="48"/>
+      <c r="Q18" s="37"/>
+      <c r="R18" s="48"/>
+      <c r="S18" s="48"/>
+      <c r="T18" s="48"/>
+      <c r="U18" s="48"/>
+    </row>
+    <row r="19" spans="1:21">
+      <c r="A19" s="53" t="s">
+        <v>349</v>
+      </c>
+      <c r="B19" s="48">
+        <v>1</v>
+      </c>
+      <c r="C19" s="50" t="s">
+        <v>353</v>
+      </c>
+      <c r="D19" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="48"/>
+      <c r="K19" s="48" t="s">
+        <v>619</v>
+      </c>
+      <c r="L19" s="48"/>
+      <c r="M19" s="48"/>
+      <c r="N19" s="48" t="s">
+        <v>393</v>
+      </c>
+      <c r="O19" s="48" t="s">
+        <v>394</v>
+      </c>
+      <c r="P19" s="48"/>
+      <c r="Q19" s="37"/>
+      <c r="R19" s="48"/>
+      <c r="S19" s="48"/>
+      <c r="T19" s="48"/>
+      <c r="U19" s="48"/>
+    </row>
+    <row r="20" spans="1:21">
+      <c r="A20" s="53" t="s">
+        <v>350</v>
+      </c>
+      <c r="B20" s="48">
+        <v>1</v>
+      </c>
+      <c r="C20" s="50" t="s">
+        <v>353</v>
+      </c>
+      <c r="D20" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="F20" s="48"/>
+      <c r="G20" s="48"/>
+      <c r="H20" s="48"/>
+      <c r="I20" s="48"/>
+      <c r="J20" s="48"/>
+      <c r="K20" s="48" t="s">
+        <v>620</v>
+      </c>
+      <c r="L20" s="48"/>
+      <c r="M20" s="48"/>
+      <c r="N20" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="O20" s="48" t="s">
+        <v>360</v>
+      </c>
+      <c r="P20" s="48"/>
+      <c r="Q20" s="37"/>
+      <c r="R20" s="48"/>
+      <c r="S20" s="48"/>
+      <c r="T20" s="48"/>
+      <c r="U20" s="48"/>
+    </row>
+    <row r="21" spans="1:21">
+      <c r="A21" s="53" t="s">
+        <v>351</v>
+      </c>
+      <c r="B21" s="48">
+        <v>1</v>
+      </c>
+      <c r="C21" s="50" t="s">
+        <v>403</v>
+      </c>
+      <c r="D21" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="48" t="s">
+        <v>218</v>
+      </c>
+      <c r="F21" s="48"/>
+      <c r="G21" s="48"/>
+      <c r="H21" s="48"/>
+      <c r="I21" s="48"/>
+      <c r="J21" s="48"/>
+      <c r="K21" s="48" t="s">
+        <v>623</v>
+      </c>
+      <c r="L21" s="48"/>
+      <c r="M21" s="48"/>
+      <c r="N21" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="O21" s="48" t="s">
+        <v>360</v>
+      </c>
+      <c r="P21" s="48"/>
+      <c r="Q21" s="37"/>
+      <c r="R21" s="48"/>
+      <c r="S21" s="48"/>
+      <c r="T21" s="48"/>
+      <c r="U21" s="48"/>
+    </row>
+    <row r="22" spans="1:21">
+      <c r="A22" s="53" t="s">
+        <v>352</v>
+      </c>
+      <c r="B22" s="48">
+        <v>1</v>
+      </c>
+      <c r="C22" s="50" t="s">
+        <v>353</v>
+      </c>
+      <c r="D22" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="F22" s="48"/>
+      <c r="G22" s="48"/>
+      <c r="H22" s="48"/>
+      <c r="I22" s="48"/>
+      <c r="J22" s="48"/>
+      <c r="K22" s="48"/>
+      <c r="L22" s="48"/>
+      <c r="M22" s="48"/>
+      <c r="N22" s="48"/>
+      <c r="O22" s="48"/>
+      <c r="P22" s="48"/>
+      <c r="Q22" s="37"/>
+      <c r="R22" s="48"/>
+      <c r="S22" s="48"/>
+      <c r="T22" s="48"/>
+      <c r="U22" s="48"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2EA1F88-8B75-4AAD-A17A-063CA3659CA4}">
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="32.90625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="14.36328125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="30.36328125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="6.90625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="10.90625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="61" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="58" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" s="59" t="s">
+        <v>406</v>
+      </c>
+      <c r="E1" s="59" t="s">
+        <v>105</v>
+      </c>
+      <c r="F1" s="58" t="s">
+        <v>407</v>
+      </c>
+      <c r="G1" s="63"/>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="63" t="s">
+        <v>408</v>
+      </c>
+      <c r="B2" s="60">
+        <v>2</v>
+      </c>
+      <c r="C2" s="60">
+        <v>2</v>
+      </c>
+      <c r="D2" s="62" t="s">
+        <v>581</v>
+      </c>
+      <c r="E2" s="62" t="s">
+        <v>580</v>
+      </c>
+      <c r="F2" s="60"/>
+      <c r="G2" s="63"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="60" t="s">
+        <v>411</v>
+      </c>
+      <c r="B3" s="60">
+        <v>2</v>
+      </c>
+      <c r="C3" s="60">
+        <v>2</v>
+      </c>
+      <c r="D3" s="62" t="s">
+        <v>637</v>
+      </c>
+      <c r="E3" s="62" t="s">
+        <v>413</v>
+      </c>
+      <c r="F3" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="G3" s="63"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="60" t="s">
+        <v>414</v>
+      </c>
+      <c r="B4" s="60">
+        <v>2</v>
+      </c>
+      <c r="C4" s="60">
+        <v>2</v>
+      </c>
+      <c r="D4" s="62" t="s">
+        <v>638</v>
+      </c>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="G4" s="63"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88414653-50FA-4845-96AF-5B777BBDF907}">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" style="57" width="18.26953125"/>
+    <col min="2" max="2" customWidth="true" style="57" width="16.54296875"/>
+    <col min="3" max="3" customWidth="true" style="57" width="19.90625"/>
+    <col min="4" max="4" customWidth="true" style="57" width="18.81640625"/>
+    <col min="5" max="5" customWidth="true" style="57" width="12.90625"/>
+    <col min="6" max="8" customWidth="true" hidden="true" style="57" width="0.0"/>
+    <col min="9" max="9" style="57" width="8.7265625"/>
+    <col min="10" max="10" customWidth="true" style="57" width="17.90625"/>
+    <col min="11" max="11" customWidth="true" style="57" width="14.26953125"/>
+    <col min="12" max="16384" style="57" width="8.7265625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="61" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="58" t="s">
+        <v>421</v>
+      </c>
+      <c r="C1" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="58" t="s">
+        <v>194</v>
+      </c>
+      <c r="E1" s="58" t="s">
+        <v>322</v>
+      </c>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="59" t="s">
+        <v>105</v>
+      </c>
+      <c r="J1" s="59" t="s">
+        <v>456</v>
+      </c>
+      <c r="K1" s="59" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="60" t="s">
+        <v>458</v>
+      </c>
+      <c r="B2" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="60" t="s">
+        <v>459</v>
+      </c>
+      <c r="B3" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="60"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="60"/>
+      <c r="K3" s="60"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="60" t="s">
+        <v>460</v>
+      </c>
+      <c r="B4" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="60"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="60" t="s">
+        <v>461</v>
+      </c>
+      <c r="B5" s="60"/>
+      <c r="C5" s="62">
+        <v>2</v>
+      </c>
+      <c r="D5" s="60">
+        <v>2</v>
+      </c>
+      <c r="E5" s="60">
+        <v>2</v>
+      </c>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60" t="s">
+        <v>462</v>
+      </c>
+      <c r="J5" s="60" t="s">
+        <v>463</v>
+      </c>
+      <c r="K5" s="60" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="60" t="s">
+        <v>465</v>
+      </c>
+      <c r="B6" s="60"/>
+      <c r="C6" s="60">
+        <v>1</v>
+      </c>
+      <c r="D6" s="60">
+        <v>1</v>
+      </c>
+      <c r="E6" s="60">
+        <v>1</v>
+      </c>
+      <c r="F6" s="60"/>
+      <c r="G6" s="60"/>
+      <c r="H6" s="60"/>
+      <c r="I6" s="60"/>
+      <c r="J6" s="60"/>
+      <c r="K6" s="60"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1F0BBC0-8387-4A2B-855A-0B1CE735F165}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" style="57" width="15.08984375"/>
+    <col min="2" max="2" customWidth="true" style="57" width="15.7265625"/>
+    <col min="3" max="3" customWidth="true" style="57" width="17.81640625"/>
+    <col min="4" max="4" customWidth="true" style="57" width="16.7265625"/>
+    <col min="5" max="5" customWidth="true" style="57" width="15.6328125"/>
+    <col min="6" max="16384" style="57" width="8.7265625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="61" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="58" t="s">
+        <v>322</v>
+      </c>
+      <c r="C1" s="58" t="s">
+        <v>416</v>
+      </c>
+      <c r="D1" s="58" t="s">
+        <v>417</v>
+      </c>
+      <c r="E1" s="58" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="62" t="s">
+        <v>418</v>
+      </c>
+      <c r="B2" s="62">
+        <v>1</v>
+      </c>
+      <c r="C2" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="D2" s="60">
+        <v>1</v>
+      </c>
+      <c r="E2" s="60"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="62" t="s">
+        <v>419</v>
+      </c>
+      <c r="B3" s="60">
+        <v>1</v>
+      </c>
+      <c r="C3" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="62" t="s">
+        <v>420</v>
+      </c>
+      <c r="B4" s="60">
+        <v>1</v>
+      </c>
+      <c r="C4" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{336A478E-B1CE-4C1B-A488-66A00AABA472}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -2262,16 +4260,16 @@
         <v>13</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>270</v>
+        <v>584</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>266</v>
+        <v>516</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>264</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>267</v>
+        <v>517</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>13</v>
@@ -2280,13 +4278,13 @@
         <v>14</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>268</v>
+        <v>518</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>265</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>269</v>
+        <v>519</v>
       </c>
       <c r="S3" s="3" t="s">
         <v>14</v>
@@ -2392,16 +4390,16 @@
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>120</v>
+        <v>585</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>121</v>
+        <v>521</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>24</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>122</v>
+        <v>522</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>13</v>
@@ -2485,683 +4483,290 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ADD4D69-5509-440B-8A9B-EB710BB5A12A}">
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7BF278-0258-4060-BA3D-743DBF61A856}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="32.26953125"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="76.1796875"/>
     <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="4" max="4" customWidth="true" width="15.453125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="13.453125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="12.1796875"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:5">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3">
-        <v>2</v>
-      </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="3" t="s">
-        <v>126</v>
+      <c r="C1" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="E1" s="28" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="31">
+        <v>1</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="29" t="s">
+        <v>101</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3">
-        <v>2</v>
-      </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="3" t="s">
-        <v>127</v>
+        <v>44</v>
+      </c>
+      <c r="C3" s="31">
+        <v>1</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="3">
-        <v>1</v>
-      </c>
-      <c r="F4" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="I4" s="3">
-        <v>2</v>
-      </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3">
-        <v>2</v>
-      </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
+        <v>44</v>
+      </c>
+      <c r="C4" s="31">
+        <v>1</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEA2AF7E-AC89-4B47-B4D7-D3496E5327D5}">
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" style="57" width="18.453125"/>
+    <col min="2" max="2" customWidth="true" style="57" width="12.54296875"/>
+    <col min="3" max="3" customWidth="true" style="57" width="14.81640625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="57" width="11.7265625"/>
+    <col min="5" max="5" customWidth="true" style="57" width="18.1796875"/>
+    <col min="6" max="16384" style="57" width="8.7265625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="61" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="58" t="s">
+        <v>421</v>
+      </c>
+      <c r="C1" s="58" t="s">
+        <v>422</v>
+      </c>
+      <c r="D1" s="58" t="s">
+        <v>423</v>
+      </c>
+      <c r="E1" s="58" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="60" t="s">
+        <v>424</v>
+      </c>
+      <c r="B2" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="60" t="s">
+        <v>425</v>
+      </c>
+      <c r="B3" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="60" t="s">
+        <v>426</v>
+      </c>
+      <c r="B4" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="60" t="s">
+        <v>427</v>
+      </c>
+      <c r="B5" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="60" t="s">
+        <v>428</v>
+      </c>
+      <c r="B6" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="C6" s="60"/>
+      <c r="D6" s="60"/>
+      <c r="E6" s="60"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="60" t="s">
+        <v>429</v>
+      </c>
+      <c r="B7" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="60"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="60" t="s">
+        <v>430</v>
+      </c>
+      <c r="B8" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="C8" s="60"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="60" t="s">
+        <v>431</v>
+      </c>
+      <c r="B9" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="C9" s="62" t="s">
+        <v>432</v>
+      </c>
+      <c r="D9" s="56" t="s">
+        <v>433</v>
+      </c>
+      <c r="E9" s="60"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="60" t="s">
+        <v>434</v>
+      </c>
+      <c r="B10" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="C10" s="60"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="60" t="s">
+        <v>435</v>
+      </c>
+      <c r="B11" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="C11" s="60"/>
+      <c r="D11" s="60"/>
+      <c r="E11" s="60"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="60" t="s">
+        <v>436</v>
+      </c>
+      <c r="B12" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="C12" s="60"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="60" t="s">
+        <v>437</v>
+      </c>
+      <c r="B13" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="C13" s="60"/>
+      <c r="D13" s="60"/>
+      <c r="E13" s="60"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="60" t="s">
+        <v>438</v>
+      </c>
+      <c r="B14" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="C14" s="60"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="60" t="s">
+        <v>439</v>
+      </c>
+      <c r="B15" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
+      <c r="E15" s="62">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51EE6AAF-837D-4C0C-BD88-9AF62A29B7BB}">
-  <sheetPr>
-    <tabColor rgb="FF92D050"/>
-  </sheetPr>
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="32.26953125"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>131</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D801678A-93DD-4A10-BD7A-B4F1484B5E45}">
-  <sheetPr>
-    <tabColor rgb="FF92D050"/>
-  </sheetPr>
-  <dimension ref="A1:S20"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="53.81640625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="3" max="4" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="5" max="7" customWidth="true" width="12.1796875"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="12.1796875"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:19">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19">
-      <c r="A2" s="34" t="s">
-        <v>135</v>
-      </c>
-      <c r="B2" s="3">
-        <v>2</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-    </row>
-    <row r="3" spans="1:19">
-      <c r="A3" s="34" t="s">
-        <v>136</v>
-      </c>
-      <c r="B3" s="3">
-        <v>2</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-    </row>
-    <row r="4" spans="1:19">
-      <c r="A4" s="34" t="s">
-        <v>138</v>
-      </c>
-      <c r="B4" s="3">
-        <v>2</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-    </row>
-    <row r="5" spans="1:19">
-      <c r="A5" s="34" t="s">
-        <v>139</v>
-      </c>
-      <c r="B5" s="3">
-        <v>2</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
-    </row>
-    <row r="6" spans="1:19">
-      <c r="A6" s="34" t="s">
-        <v>141</v>
-      </c>
-      <c r="B6" s="3">
-        <v>0</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-    </row>
-    <row r="7" spans="1:19">
-      <c r="A7" s="34" t="s">
-        <v>142</v>
-      </c>
-      <c r="B7" s="3">
-        <v>2</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="G7" s="3"/>
-    </row>
-    <row r="8" spans="1:19">
-      <c r="A8" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="B8" s="3">
-        <v>2</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="G8" s="3"/>
-    </row>
-    <row r="9" spans="1:19">
-      <c r="A9" s="34" t="s">
-        <v>144</v>
-      </c>
-      <c r="B9" s="3">
-        <v>2</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="G9" s="3"/>
-    </row>
-    <row r="10" spans="1:19">
-      <c r="A10" s="34" t="s">
-        <v>145</v>
-      </c>
-      <c r="B10" s="3">
-        <v>2</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="18" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19">
-      <c r="A11" s="35" t="s">
-        <v>146</v>
-      </c>
-      <c r="B11" s="3">
-        <v>2</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="18" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19">
-      <c r="A12" s="34" t="s">
-        <v>147</v>
-      </c>
-      <c r="B12" s="26">
-        <v>0</v>
-      </c>
-      <c r="C12" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19">
-      <c r="A13" s="34" t="s">
-        <v>148</v>
-      </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-    </row>
-    <row r="14" spans="1:19">
-      <c r="A14" s="34" t="s">
-        <v>149</v>
-      </c>
-      <c r="B14" s="3">
-        <v>2</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-    </row>
-    <row r="15" spans="1:19">
-      <c r="A15" s="34" t="s">
-        <v>150</v>
-      </c>
-      <c r="B15" s="3">
-        <v>2</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-    </row>
-    <row r="16" spans="1:19">
-      <c r="A16" s="34" t="s">
-        <v>151</v>
-      </c>
-      <c r="B16" s="26">
-        <v>0</v>
-      </c>
-      <c r="C16" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-    </row>
-    <row r="17" spans="1:19">
-      <c r="A17" s="34" t="s">
-        <v>152</v>
-      </c>
-      <c r="B17" s="26">
-        <v>0</v>
-      </c>
-      <c r="C17" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="D17" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-    </row>
-    <row r="20" spans="1:19">
-      <c r="A20" s="34" t="s">
-        <v>153</v>
-      </c>
-      <c r="B20" s="3">
-        <v>1</v>
-      </c>
-      <c r="C20" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J20" s="3">
-        <v>2</v>
-      </c>
-      <c r="K20" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F1569B0-3564-4B84-A0FB-9681D32A0E6D}">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -3199,574 +4804,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55103D89-E5B2-47D3-956F-E8E1CB3BB167}">
-  <sheetPr>
-    <tabColor rgb="FF92D050"/>
-  </sheetPr>
-  <dimension ref="A1:R6"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="12.0"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="9.453125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="6.26953125"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="13.81640625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="7.453125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="18.453125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="18.453125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="11.81640625"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:18">
-      <c r="A1" s="39" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="40" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="40" t="s">
-        <v>103</v>
-      </c>
-      <c r="E1" s="40" t="s">
-        <v>104</v>
-      </c>
-      <c r="F1" s="38" t="s">
-        <v>194</v>
-      </c>
-      <c r="G1" s="40" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="40" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="40" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="K1" s="32" t="s">
-        <v>105</v>
-      </c>
-      <c r="L1" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="M1" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="N1" s="32" t="s">
-        <v>106</v>
-      </c>
-      <c r="O1" s="32" t="s">
-        <v>3</v>
-      </c>
-      <c r="P1" s="32" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q1" s="32" t="s">
-        <v>213</v>
-      </c>
-      <c r="R1" s="32" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18">
-      <c r="A2" s="28" t="s">
-        <v>195</v>
-      </c>
-      <c r="B2" s="18">
-        <v>1</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="18">
-        <v>0</v>
-      </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-    </row>
-    <row r="3" spans="1:18">
-      <c r="A3" s="28" t="s">
-        <v>209</v>
-      </c>
-      <c r="B3" s="18">
-        <v>7</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="18">
-        <v>6</v>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18">
-      <c r="A4" s="28" t="s">
-        <v>210</v>
-      </c>
-      <c r="B4" s="18">
-        <v>1</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="18">
-        <v>0</v>
-      </c>
-      <c r="G4" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="J4" s="3">
-        <v>2</v>
-      </c>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
-    </row>
-    <row r="5" spans="1:18">
-      <c r="A5" s="28" t="s">
-        <v>211</v>
-      </c>
-      <c r="B5" s="18">
-        <v>1</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="18">
-        <v>0</v>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-    </row>
-    <row r="6" spans="1:18">
-      <c r="A6" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="B6" s="18">
-        <v>1</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="18">
-        <v>0</v>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51F26840-7703-45A5-AB34-582BA93F27A0}">
-  <sheetPr>
-    <tabColor rgb="FF92D050"/>
-  </sheetPr>
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="63.7265625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="10.7265625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="19.453125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="15.54296875"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="8" max="9" bestFit="true" customWidth="true" width="19.453125"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="34" t="s">
-        <v>162</v>
-      </c>
-      <c r="B2" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="B3" s="37" t="s">
-        <v>164</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="B4" s="37" t="s">
-        <v>166</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29EECB68-AFA6-4B7C-B9A3-85863070956A}">
-  <sheetPr>
-    <tabColor rgb="FF92D050"/>
-  </sheetPr>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="35.26953125"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="11.54296875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="13.453125"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="34" t="s">
-        <v>176</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="E2" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="34" t="s">
-        <v>179</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="E3" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="34" t="s">
-        <v>180</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>181</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="E4" s="3">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB53E397-0E70-4FE2-8956-CAC505C79FBA}">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="33.54296875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="13.453125"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="34" t="s">
-        <v>187</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E2" s="18" t="s">
-        <v>191</v>
-      </c>
-      <c r="F2" s="18" t="s">
-        <v>192</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02A4FAA4-EFC6-47D3-BDEE-7F4F3353F3CD}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -3817,1282 +4855,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9A5054F-4F2A-4BA5-95CD-184527D8553F}">
-  <sheetPr>
-    <tabColor rgb="FF92D050"/>
-  </sheetPr>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="57.453125"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="15.54296875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="7.7265625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="11.1796875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="11.26953125"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" s="16">
-        <v>2</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="16">
-        <v>1</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" s="3"/>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" s="16">
-        <v>1</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" s="16">
-        <v>1</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" s="16">
-        <v>1</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71142910-3363-4189-996E-89090332A376}">
-  <dimension ref="A1:AC4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <cols>
-    <col min="5" max="5" customWidth="true" width="6.26953125"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="13.90625"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:29">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="W1" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="X1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z1" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="AA1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC1" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="2" spans="1:29">
-      <c r="A2" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B2" s="3">
-        <v>1</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F2" s="3">
-        <v>0</v>
-      </c>
-      <c r="G2" s="18"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
-      <c r="V2" s="3"/>
-      <c r="W2" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="X2" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="Y2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z2" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC2" s="3" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="3" spans="1:29">
-      <c r="A3" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="B3" s="3">
-        <v>2</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>252</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="3">
-        <v>0</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="J3" s="18">
-        <v>3</v>
-      </c>
-      <c r="K3" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="N3">
-        <v>4</v>
-      </c>
-      <c r="O3" s="18" t="s">
-        <v>253</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="R3" s="3">
-        <v>5</v>
-      </c>
-      <c r="S3" s="18"/>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
-      <c r="W3" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="X3" s="3"/>
-      <c r="Y3" s="3"/>
-      <c r="Z3" s="3"/>
-      <c r="AA3" s="3"/>
-      <c r="AB3" s="3"/>
-      <c r="AC3" s="3" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29">
-      <c r="A4" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="B4" s="3">
-        <v>1</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F4" s="3">
-        <v>0</v>
-      </c>
-      <c r="G4" s="18"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
-      <c r="U4" s="3"/>
-      <c r="V4" s="3"/>
-      <c r="W4" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="X4" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="Y4" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z4" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="AA4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="AB4" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC4" s="3" t="s">
-        <v>228</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4903F224-3652-48FB-81A7-CAF06A9D7463}">
-  <dimension ref="A1:AD9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:30">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:30">
-      <c r="A2" s="14" t="s">
-        <v>229</v>
-      </c>
-      <c r="B2" s="3">
-        <v>1</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F2" s="3">
-        <v>0</v>
-      </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
-      <c r="V2" s="3"/>
-      <c r="W2" s="3"/>
-      <c r="X2" s="3"/>
-      <c r="Y2" s="3"/>
-      <c r="Z2" s="3"/>
-      <c r="AA2" s="3"/>
-      <c r="AB2" s="3"/>
-      <c r="AC2" s="3"/>
-      <c r="AD2" s="3"/>
-    </row>
-    <row r="3" spans="1:30">
-      <c r="A3" s="14" t="s">
-        <v>230</v>
-      </c>
-      <c r="B3" s="3">
-        <v>1</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>244</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="3">
-        <v>0</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J3" s="3">
-        <v>2</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="S3" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="U3">
-        <v>3</v>
-      </c>
-      <c r="V3" s="3"/>
-      <c r="W3" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="X3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y3" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z3">
-        <v>4</v>
-      </c>
-      <c r="AA3" s="18" t="s">
-        <v>246</v>
-      </c>
-      <c r="AB3" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="AD3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:30">
-      <c r="A4" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="B4" s="3">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
-      <c r="U4" s="3"/>
-      <c r="V4" s="3"/>
-      <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
-      <c r="Y4" s="3"/>
-      <c r="Z4" s="3"/>
-      <c r="AA4" s="3"/>
-      <c r="AB4" s="3"/>
-      <c r="AC4" s="3"/>
-      <c r="AD4" s="3"/>
-    </row>
-    <row r="5" spans="1:30">
-      <c r="A5" s="14" t="s">
-        <v>232</v>
-      </c>
-      <c r="B5" s="3">
-        <v>1</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F5" s="3">
-        <v>0</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>243</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="J5" s="3">
-        <v>5</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="R5" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="S5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="T5" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="U5">
-        <v>1</v>
-      </c>
-      <c r="V5" s="3">
-        <v>1</v>
-      </c>
-      <c r="W5" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="X5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y5" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z5">
-        <v>1</v>
-      </c>
-      <c r="AA5" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="AB5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="AC5" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="AD5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:30">
-      <c r="A6" s="14" t="s">
-        <v>233</v>
-      </c>
-      <c r="B6" s="3">
-        <v>1</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F6" s="3">
-        <v>0</v>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
-      <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
-      <c r="W6" s="3"/>
-      <c r="X6" s="3"/>
-      <c r="Y6" s="3"/>
-      <c r="Z6" s="3"/>
-      <c r="AA6" s="3"/>
-      <c r="AB6" s="3"/>
-      <c r="AC6" s="3"/>
-      <c r="AD6" s="3"/>
-    </row>
-    <row r="7" spans="1:30">
-      <c r="A7" s="14" t="s">
-        <v>234</v>
-      </c>
-      <c r="B7" s="3">
-        <v>1</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F7" s="3">
-        <v>0</v>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
-      <c r="T7" s="3"/>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
-      <c r="W7" s="3"/>
-      <c r="X7" s="3"/>
-      <c r="Y7" s="3"/>
-      <c r="Z7" s="3"/>
-      <c r="AA7" s="3"/>
-      <c r="AB7" s="3"/>
-      <c r="AC7" s="3"/>
-      <c r="AD7" s="3"/>
-    </row>
-    <row r="8" spans="1:30">
-      <c r="A8" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="B8" s="3">
-        <v>1</v>
-      </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
-      <c r="S8" s="3"/>
-      <c r="T8" s="3"/>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
-      <c r="W8" s="3"/>
-      <c r="X8" s="3"/>
-      <c r="Y8" s="3"/>
-      <c r="Z8" s="3"/>
-      <c r="AA8" s="3"/>
-      <c r="AB8" s="3"/>
-      <c r="AC8" s="3"/>
-      <c r="AD8" s="3"/>
-    </row>
-    <row r="9" spans="1:30">
-      <c r="A9" s="14" t="s">
-        <v>236</v>
-      </c>
-      <c r="B9" s="3">
-        <v>1</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9" s="3">
-        <v>0</v>
-      </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
-      <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
-      <c r="Y9" s="3"/>
-      <c r="Z9" s="3"/>
-      <c r="AA9" s="3"/>
-      <c r="AB9" s="3"/>
-      <c r="AC9" s="3"/>
-      <c r="AD9" s="3"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42BBEF64-F0EA-4EA8-9A62-F5A7DF1E4869}">
-  <dimension ref="A1:U13"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <sheetData>
-    <row r="1" spans="1:21">
-      <c r="A1" s="39" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="40" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="40" t="s">
-        <v>103</v>
-      </c>
-      <c r="E1" s="40" t="s">
-        <v>104</v>
-      </c>
-      <c r="F1" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="40" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="40" t="s">
-        <v>103</v>
-      </c>
-      <c r="I1" s="40" t="s">
-        <v>104</v>
-      </c>
-      <c r="J1" s="32" t="s">
-        <v>105</v>
-      </c>
-      <c r="K1" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="L1" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="M1" s="32" t="s">
-        <v>106</v>
-      </c>
-      <c r="N1" s="32" t="s">
-        <v>3</v>
-      </c>
-      <c r="O1" s="32" t="s">
-        <v>4</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21">
-      <c r="A2" s="28" t="s">
-        <v>215</v>
-      </c>
-      <c r="B2" s="50">
-        <v>1</v>
-      </c>
-      <c r="C2" s="48" t="s">
-        <v>328</v>
-      </c>
-      <c r="D2" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="48" t="s">
-        <v>329</v>
-      </c>
-      <c r="F2" s="50">
-        <v>1</v>
-      </c>
-      <c r="G2" s="48" t="s">
-        <v>330</v>
-      </c>
-      <c r="H2" s="48" t="s">
-        <v>329</v>
-      </c>
-      <c r="I2" s="48" t="s">
-        <v>218</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="U2" s="3" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21">
-      <c r="A3" s="28" t="s">
-        <v>258</v>
-      </c>
-      <c r="B3" s="50">
-        <v>1</v>
-      </c>
-      <c r="C3" s="48" t="s">
-        <v>328</v>
-      </c>
-      <c r="D3" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="48" t="s">
-        <v>329</v>
-      </c>
-      <c r="F3" s="50">
-        <v>1</v>
-      </c>
-      <c r="G3" s="48" t="s">
-        <v>331</v>
-      </c>
-      <c r="H3" s="48" t="s">
-        <v>329</v>
-      </c>
-      <c r="I3" s="48" t="s">
-        <v>218</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="S3" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="U3" s="3" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21">
-      <c r="B8" s="18">
-        <v>1</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>216</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="F8" s="18">
-        <v>4</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21">
-      <c r="B9" s="18">
-        <v>1</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>216</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="F9" s="18">
-        <v>4</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21">
-      <c r="B12" s="18">
-        <v>1</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="18">
-        <v>1</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21">
-      <c r="B13" s="18">
-        <v>1</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="18">
-        <v>1</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA6A106B-75A4-4F54-9508-A66A4AEED06E}">
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -5191,1292 +4954,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C03B3B8-DBFD-430F-BAEF-858DA603C137}">
-  <dimension ref="A1:V8"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <sheetData>
-    <row r="1" spans="1:22">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22">
-      <c r="A2" s="41" t="s">
-        <v>297</v>
-      </c>
-      <c r="B2" s="3">
-        <v>1</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F2" s="3">
-        <v>2</v>
-      </c>
-      <c r="G2" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="3">
-        <v>1</v>
-      </c>
-      <c r="K2" s="3"/>
-      <c r="L2" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="O2" s="3">
-        <v>2</v>
-      </c>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="T2" s="3">
-        <v>0</v>
-      </c>
-      <c r="U2" s="3"/>
-      <c r="V2" s="3"/>
-    </row>
-    <row r="3" spans="1:22">
-      <c r="A3" s="41" t="s">
-        <v>298</v>
-      </c>
-      <c r="B3" s="3">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3">
-        <v>1</v>
-      </c>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
-    </row>
-    <row r="4" spans="1:22">
-      <c r="A4" s="41" t="s">
-        <v>299</v>
-      </c>
-      <c r="B4" s="3">
-        <v>1</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F4" s="3">
-        <v>2</v>
-      </c>
-      <c r="G4" s="18" t="s">
-        <v>300</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="J4" s="3">
-        <v>1</v>
-      </c>
-      <c r="K4" s="3">
-        <v>1</v>
-      </c>
-      <c r="L4" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="O4" s="3">
-        <v>3</v>
-      </c>
-      <c r="P4" s="3">
-        <v>3</v>
-      </c>
-      <c r="Q4" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="R4" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="T4" s="3">
-        <v>0</v>
-      </c>
-      <c r="U4" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="V4" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22">
-      <c r="A8" s="41" t="s">
-        <v>299</v>
-      </c>
-      <c r="B8" s="3">
-        <v>1</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F8" s="3">
-        <v>3</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>303</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J8" s="3">
-        <v>1</v>
-      </c>
-      <c r="K8" s="3">
-        <v>1</v>
-      </c>
-      <c r="L8" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="O8" s="3">
-        <v>5</v>
-      </c>
-      <c r="P8" s="3">
-        <v>5</v>
-      </c>
-      <c r="Q8" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="T8" s="3">
-        <v>0</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>302</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C501783-003E-43C7-BF08-448ED073E85B}">
-  <dimension ref="A1:U22"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <cols>
-    <col min="10" max="10" style="45" width="8.7265625"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="9.81640625"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:21">
-      <c r="A1" s="39" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="40" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="40" t="s">
-        <v>103</v>
-      </c>
-      <c r="E1" s="40" t="s">
-        <v>104</v>
-      </c>
-      <c r="F1" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="40" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="40" t="s">
-        <v>103</v>
-      </c>
-      <c r="I1" s="40" t="s">
-        <v>104</v>
-      </c>
-      <c r="J1" s="40" t="s">
-        <v>194</v>
-      </c>
-      <c r="K1" s="54" t="s">
-        <v>105</v>
-      </c>
-      <c r="L1" s="54" t="s">
-        <v>275</v>
-      </c>
-      <c r="M1" s="40" t="s">
-        <v>358</v>
-      </c>
-      <c r="N1" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="O1" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="P1" s="47" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q1" s="36" t="s">
-        <v>361</v>
-      </c>
-      <c r="R1" s="47" t="s">
-        <v>214</v>
-      </c>
-      <c r="S1" s="46" t="s">
-        <v>369</v>
-      </c>
-      <c r="T1" s="47" t="s">
-        <v>396</v>
-      </c>
-      <c r="U1" s="47" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21">
-      <c r="A2" s="53" t="s">
-        <v>332</v>
-      </c>
-      <c r="B2" s="48">
-        <v>1</v>
-      </c>
-      <c r="C2" s="50" t="s">
-        <v>353</v>
-      </c>
-      <c r="D2" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="F2" s="48">
-        <v>2</v>
-      </c>
-      <c r="G2" s="50" t="s">
-        <v>354</v>
-      </c>
-      <c r="H2" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="I2" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48" t="s">
-        <v>355</v>
-      </c>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="48"/>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="37"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-    </row>
-    <row r="3" spans="1:21">
-      <c r="A3" s="53" t="s">
-        <v>333</v>
-      </c>
-      <c r="B3" s="48">
-        <v>1</v>
-      </c>
-      <c r="C3" s="50" t="s">
-        <v>353</v>
-      </c>
-      <c r="D3" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" s="48"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48">
-        <v>0</v>
-      </c>
-      <c r="K3" s="48" t="s">
-        <v>356</v>
-      </c>
-      <c r="L3" s="48" t="s">
-        <v>357</v>
-      </c>
-      <c r="M3" s="48"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="37"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-    </row>
-    <row r="4" spans="1:21">
-      <c r="A4" s="53" t="s">
-        <v>334</v>
-      </c>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
-      <c r="K4" s="48"/>
-      <c r="L4" s="48"/>
-      <c r="M4" s="48" t="s">
-        <v>359</v>
-      </c>
-      <c r="N4" s="48"/>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="37"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-    </row>
-    <row r="5" spans="1:21">
-      <c r="A5" s="53" t="s">
-        <v>335</v>
-      </c>
-      <c r="B5" s="48">
-        <v>1</v>
-      </c>
-      <c r="C5" s="50" t="s">
-        <v>353</v>
-      </c>
-      <c r="D5" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
-      <c r="K5" s="48" t="s">
-        <v>399</v>
-      </c>
-      <c r="L5" s="48" t="s">
-        <v>363</v>
-      </c>
-      <c r="M5" s="48"/>
-      <c r="N5" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="O5" s="48" t="s">
-        <v>360</v>
-      </c>
-      <c r="P5" s="48" t="s">
-        <v>400</v>
-      </c>
-      <c r="Q5" s="37"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48" t="s">
-        <v>398</v>
-      </c>
-      <c r="U5" s="48" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21">
-      <c r="A6" s="53" t="s">
-        <v>336</v>
-      </c>
-      <c r="B6" s="48">
-        <v>1</v>
-      </c>
-      <c r="C6" s="50" t="s">
-        <v>353</v>
-      </c>
-      <c r="D6" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48" t="s">
-        <v>401</v>
-      </c>
-      <c r="L6" s="48"/>
-      <c r="M6" s="48"/>
-      <c r="N6" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="O6" s="48" t="s">
-        <v>360</v>
-      </c>
-      <c r="P6" s="48" t="s">
-        <v>402</v>
-      </c>
-      <c r="Q6" s="37"/>
-      <c r="R6" s="48"/>
-      <c r="S6" s="48"/>
-      <c r="T6" s="48" t="s">
-        <v>398</v>
-      </c>
-      <c r="U6" s="48" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21">
-      <c r="A7" s="53" t="s">
-        <v>337</v>
-      </c>
-      <c r="B7" s="48">
-        <v>1</v>
-      </c>
-      <c r="C7" s="50" t="s">
-        <v>353</v>
-      </c>
-      <c r="D7" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="F7" s="48"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="48" t="s">
-        <v>378</v>
-      </c>
-      <c r="L7" s="48" t="s">
-        <v>379</v>
-      </c>
-      <c r="M7" s="48"/>
-      <c r="N7" s="48" t="s">
-        <v>362</v>
-      </c>
-      <c r="O7" s="48" t="s">
-        <v>360</v>
-      </c>
-      <c r="P7" s="48" t="s">
-        <v>380</v>
-      </c>
-      <c r="Q7" s="55" t="s">
-        <v>131</v>
-      </c>
-      <c r="R7" s="48" t="s">
-        <v>381</v>
-      </c>
-      <c r="S7" s="48"/>
-      <c r="T7" s="48"/>
-      <c r="U7" s="48"/>
-    </row>
-    <row r="8" spans="1:21">
-      <c r="A8" s="53" t="s">
-        <v>338</v>
-      </c>
-      <c r="B8" s="48">
-        <v>1</v>
-      </c>
-      <c r="C8" s="50" t="s">
-        <v>353</v>
-      </c>
-      <c r="D8" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="F8" s="48">
-        <v>2</v>
-      </c>
-      <c r="G8" s="50" t="s">
-        <v>354</v>
-      </c>
-      <c r="H8" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="I8" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="J8" s="48"/>
-      <c r="K8" s="48" t="s">
-        <v>365</v>
-      </c>
-      <c r="L8" s="48" t="s">
-        <v>366</v>
-      </c>
-      <c r="M8" s="48"/>
-      <c r="N8" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="O8" s="48" t="s">
-        <v>364</v>
-      </c>
-      <c r="P8" s="48"/>
-      <c r="Q8" s="37"/>
-      <c r="R8" s="48"/>
-      <c r="S8" s="48"/>
-      <c r="T8" s="48"/>
-      <c r="U8" s="48"/>
-    </row>
-    <row r="9" spans="1:21">
-      <c r="A9" s="53" t="s">
-        <v>339</v>
-      </c>
-      <c r="B9" s="48">
-        <v>1</v>
-      </c>
-      <c r="C9" s="50" t="s">
-        <v>353</v>
-      </c>
-      <c r="D9" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="48"/>
-      <c r="J9" s="48"/>
-      <c r="K9" s="48" t="s">
-        <v>368</v>
-      </c>
-      <c r="L9" s="48"/>
-      <c r="M9" s="48"/>
-      <c r="N9" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="O9" s="48" t="s">
-        <v>367</v>
-      </c>
-      <c r="P9" s="48"/>
-      <c r="Q9" s="37"/>
-      <c r="R9" s="48"/>
-      <c r="S9" s="48"/>
-      <c r="T9" s="48"/>
-      <c r="U9" s="48"/>
-    </row>
-    <row r="10" spans="1:21">
-      <c r="A10" s="53" t="s">
-        <v>340</v>
-      </c>
-      <c r="B10" s="48">
-        <v>1</v>
-      </c>
-      <c r="C10" s="50" t="s">
-        <v>353</v>
-      </c>
-      <c r="D10" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="F10" s="48"/>
-      <c r="G10" s="48"/>
-      <c r="H10" s="48"/>
-      <c r="I10" s="48"/>
-      <c r="J10" s="48"/>
-      <c r="K10" s="48" t="s">
-        <v>376</v>
-      </c>
-      <c r="L10" s="48" t="s">
-        <v>377</v>
-      </c>
-      <c r="M10" s="48"/>
-      <c r="N10" s="48"/>
-      <c r="O10" s="48"/>
-      <c r="P10" s="48"/>
-      <c r="Q10" s="37"/>
-      <c r="R10" s="48"/>
-      <c r="S10" s="50" t="s">
-        <v>370</v>
-      </c>
-      <c r="T10" s="48"/>
-      <c r="U10" s="48"/>
-    </row>
-    <row r="11" spans="1:21">
-      <c r="A11" s="53" t="s">
-        <v>341</v>
-      </c>
-      <c r="B11" s="48">
-        <v>1</v>
-      </c>
-      <c r="C11" s="50" t="s">
-        <v>353</v>
-      </c>
-      <c r="D11" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="48"/>
-      <c r="G11" s="48"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="48"/>
-      <c r="J11" s="48"/>
-      <c r="K11" s="48" t="s">
-        <v>371</v>
-      </c>
-      <c r="L11" s="48" t="s">
-        <v>372</v>
-      </c>
-      <c r="M11" s="48"/>
-      <c r="N11" s="48"/>
-      <c r="O11" s="48"/>
-      <c r="P11" s="48"/>
-      <c r="Q11" s="37"/>
-      <c r="R11" s="48"/>
-      <c r="S11" s="50" t="s">
-        <v>370</v>
-      </c>
-      <c r="T11" s="48"/>
-      <c r="U11" s="48"/>
-    </row>
-    <row r="12" spans="1:21">
-      <c r="A12" s="53" t="s">
-        <v>342</v>
-      </c>
-      <c r="B12" s="48">
-        <v>1</v>
-      </c>
-      <c r="C12" s="50" t="s">
-        <v>353</v>
-      </c>
-      <c r="D12" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="F12" s="48"/>
-      <c r="G12" s="48"/>
-      <c r="H12" s="48"/>
-      <c r="I12" s="48"/>
-      <c r="J12" s="48"/>
-      <c r="K12" s="48" t="s">
-        <v>373</v>
-      </c>
-      <c r="L12" s="48" t="s">
-        <v>375</v>
-      </c>
-      <c r="M12" s="48"/>
-      <c r="N12" s="48" t="s">
-        <v>362</v>
-      </c>
-      <c r="O12" s="48" t="s">
-        <v>374</v>
-      </c>
-      <c r="P12" s="48"/>
-      <c r="Q12" s="55" t="s">
-        <v>131</v>
-      </c>
-      <c r="R12" s="48"/>
-      <c r="S12" s="48"/>
-      <c r="T12" s="48"/>
-      <c r="U12" s="48"/>
-    </row>
-    <row r="13" spans="1:21">
-      <c r="A13" s="53" t="s">
-        <v>343</v>
-      </c>
-      <c r="B13" s="48">
-        <v>1</v>
-      </c>
-      <c r="C13" s="50" t="s">
-        <v>353</v>
-      </c>
-      <c r="D13" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="F13" s="48"/>
-      <c r="G13" s="48"/>
-      <c r="H13" s="48"/>
-      <c r="I13" s="48"/>
-      <c r="J13" s="48"/>
-      <c r="K13" s="48" t="s">
-        <v>382</v>
-      </c>
-      <c r="L13" s="48" t="s">
-        <v>383</v>
-      </c>
-      <c r="M13" s="48"/>
-      <c r="N13" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="O13" s="48" t="s">
-        <v>360</v>
-      </c>
-      <c r="P13" s="48"/>
-      <c r="Q13" s="37"/>
-      <c r="R13" s="48"/>
-      <c r="S13" s="50" t="s">
-        <v>370</v>
-      </c>
-      <c r="T13" s="48"/>
-      <c r="U13" s="48"/>
-    </row>
-    <row r="14" spans="1:21">
-      <c r="A14" s="53" t="s">
-        <v>344</v>
-      </c>
-      <c r="B14" s="48">
-        <v>1</v>
-      </c>
-      <c r="C14" s="50" t="s">
-        <v>353</v>
-      </c>
-      <c r="D14" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="H14" s="48"/>
-      <c r="I14" s="48"/>
-      <c r="J14" s="48"/>
-      <c r="K14" s="48"/>
-      <c r="L14" s="48"/>
-      <c r="M14" s="48"/>
-      <c r="N14" s="48"/>
-      <c r="O14" s="48"/>
-      <c r="P14" s="48"/>
-      <c r="Q14" s="37"/>
-      <c r="R14" s="48"/>
-      <c r="S14" s="50" t="s">
-        <v>384</v>
-      </c>
-      <c r="T14" s="48"/>
-      <c r="U14" s="48"/>
-    </row>
-    <row r="15" spans="1:21">
-      <c r="A15" s="53" t="s">
-        <v>345</v>
-      </c>
-      <c r="B15" s="48">
-        <v>1</v>
-      </c>
-      <c r="C15" s="50" t="s">
-        <v>353</v>
-      </c>
-      <c r="D15" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="F15" s="48"/>
-      <c r="G15" s="48"/>
-      <c r="H15" s="48"/>
-      <c r="I15" s="48"/>
-      <c r="J15" s="48"/>
-      <c r="K15" s="48" t="s">
-        <v>385</v>
-      </c>
-      <c r="L15" s="48" t="s">
-        <v>386</v>
-      </c>
-      <c r="M15" s="48"/>
-      <c r="N15" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="O15" s="48" t="s">
-        <v>360</v>
-      </c>
-      <c r="P15" s="48"/>
-      <c r="Q15" s="37"/>
-      <c r="R15" s="48"/>
-      <c r="S15" s="50" t="s">
-        <v>370</v>
-      </c>
-      <c r="T15" s="48"/>
-      <c r="U15" s="48"/>
-    </row>
-    <row r="16" spans="1:21">
-      <c r="A16" s="53" t="s">
-        <v>346</v>
-      </c>
-      <c r="B16" s="48">
-        <v>1</v>
-      </c>
-      <c r="C16" s="50" t="s">
-        <v>353</v>
-      </c>
-      <c r="D16" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="F16" s="48"/>
-      <c r="G16" s="48"/>
-      <c r="H16" s="48"/>
-      <c r="I16" s="48"/>
-      <c r="J16" s="48"/>
-      <c r="K16" s="48" t="s">
-        <v>388</v>
-      </c>
-      <c r="L16" s="48"/>
-      <c r="M16" s="48"/>
-      <c r="N16" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="O16" s="48" t="s">
-        <v>387</v>
-      </c>
-      <c r="P16" s="48"/>
-      <c r="Q16" s="37"/>
-      <c r="R16" s="48"/>
-      <c r="S16" s="48"/>
-      <c r="T16" s="48"/>
-      <c r="U16" s="48"/>
-    </row>
-    <row r="17" spans="1:21">
-      <c r="A17" s="53" t="s">
-        <v>347</v>
-      </c>
-      <c r="B17" s="48">
-        <v>1</v>
-      </c>
-      <c r="C17" s="50" t="s">
-        <v>353</v>
-      </c>
-      <c r="D17" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="F17" s="48"/>
-      <c r="G17" s="48"/>
-      <c r="H17" s="48"/>
-      <c r="I17" s="48"/>
-      <c r="J17" s="48"/>
-      <c r="K17" s="48" t="s">
-        <v>389</v>
-      </c>
-      <c r="L17" s="48"/>
-      <c r="M17" s="48"/>
-      <c r="N17" s="48"/>
-      <c r="O17" s="48"/>
-      <c r="P17" s="48"/>
-      <c r="Q17" s="37"/>
-      <c r="R17" s="48"/>
-      <c r="S17" s="48"/>
-      <c r="T17" s="48"/>
-      <c r="U17" s="48"/>
-    </row>
-    <row r="18" spans="1:21">
-      <c r="A18" s="53" t="s">
-        <v>348</v>
-      </c>
-      <c r="B18" s="48">
-        <v>1</v>
-      </c>
-      <c r="C18" s="50" t="s">
-        <v>353</v>
-      </c>
-      <c r="D18" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="F18" s="48">
-        <v>2</v>
-      </c>
-      <c r="G18" s="50" t="s">
-        <v>354</v>
-      </c>
-      <c r="H18" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="I18" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="J18" s="48"/>
-      <c r="K18" s="48" t="s">
-        <v>392</v>
-      </c>
-      <c r="L18" s="48"/>
-      <c r="M18" s="48"/>
-      <c r="N18" s="48" t="s">
-        <v>390</v>
-      </c>
-      <c r="O18" s="48" t="s">
-        <v>391</v>
-      </c>
-      <c r="P18" s="48"/>
-      <c r="Q18" s="37"/>
-      <c r="R18" s="48"/>
-      <c r="S18" s="48"/>
-      <c r="T18" s="48"/>
-      <c r="U18" s="48"/>
-    </row>
-    <row r="19" spans="1:21">
-      <c r="A19" s="53" t="s">
-        <v>349</v>
-      </c>
-      <c r="B19" s="48">
-        <v>1</v>
-      </c>
-      <c r="C19" s="50" t="s">
-        <v>353</v>
-      </c>
-      <c r="D19" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="F19" s="48"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="48"/>
-      <c r="I19" s="48"/>
-      <c r="J19" s="48"/>
-      <c r="K19" s="48" t="s">
-        <v>395</v>
-      </c>
-      <c r="L19" s="48"/>
-      <c r="M19" s="48"/>
-      <c r="N19" s="48" t="s">
-        <v>393</v>
-      </c>
-      <c r="O19" s="48" t="s">
-        <v>394</v>
-      </c>
-      <c r="P19" s="48"/>
-      <c r="Q19" s="37"/>
-      <c r="R19" s="48"/>
-      <c r="S19" s="48"/>
-      <c r="T19" s="48"/>
-      <c r="U19" s="48"/>
-    </row>
-    <row r="20" spans="1:21">
-      <c r="A20" s="53" t="s">
-        <v>350</v>
-      </c>
-      <c r="B20" s="48">
-        <v>1</v>
-      </c>
-      <c r="C20" s="50" t="s">
-        <v>353</v>
-      </c>
-      <c r="D20" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="F20" s="48"/>
-      <c r="G20" s="48"/>
-      <c r="H20" s="48"/>
-      <c r="I20" s="48"/>
-      <c r="J20" s="48"/>
-      <c r="K20" s="48" t="s">
-        <v>406</v>
-      </c>
-      <c r="L20" s="48"/>
-      <c r="M20" s="48"/>
-      <c r="N20" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="O20" s="48" t="s">
-        <v>360</v>
-      </c>
-      <c r="P20" s="48"/>
-      <c r="Q20" s="37"/>
-      <c r="R20" s="48"/>
-      <c r="S20" s="48"/>
-      <c r="T20" s="48"/>
-      <c r="U20" s="48"/>
-    </row>
-    <row r="21" spans="1:21">
-      <c r="A21" s="53" t="s">
-        <v>351</v>
-      </c>
-      <c r="B21" s="48">
-        <v>1</v>
-      </c>
-      <c r="C21" s="50" t="s">
-        <v>404</v>
-      </c>
-      <c r="D21" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="48" t="s">
-        <v>218</v>
-      </c>
-      <c r="F21" s="48"/>
-      <c r="G21" s="48"/>
-      <c r="H21" s="48"/>
-      <c r="I21" s="48"/>
-      <c r="J21" s="48"/>
-      <c r="K21" s="48" t="s">
-        <v>408</v>
-      </c>
-      <c r="L21" s="48"/>
-      <c r="M21" s="48"/>
-      <c r="N21" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="O21" s="48" t="s">
-        <v>360</v>
-      </c>
-      <c r="P21" s="48"/>
-      <c r="Q21" s="37"/>
-      <c r="R21" s="48"/>
-      <c r="S21" s="48"/>
-      <c r="T21" s="48"/>
-      <c r="U21" s="48"/>
-    </row>
-    <row r="22" spans="1:21">
-      <c r="A22" s="53" t="s">
-        <v>352</v>
-      </c>
-      <c r="B22" s="48">
-        <v>1</v>
-      </c>
-      <c r="C22" s="50" t="s">
-        <v>353</v>
-      </c>
-      <c r="D22" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="E22" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="F22" s="48"/>
-      <c r="G22" s="48"/>
-      <c r="H22" s="48"/>
-      <c r="I22" s="48"/>
-      <c r="J22" s="48"/>
-      <c r="K22" s="48"/>
-      <c r="L22" s="48"/>
-      <c r="M22" s="48"/>
-      <c r="N22" s="48"/>
-      <c r="O22" s="48"/>
-      <c r="P22" s="48"/>
-      <c r="Q22" s="37"/>
-      <c r="R22" s="48"/>
-      <c r="S22" s="48"/>
-      <c r="T22" s="48"/>
-      <c r="U22" s="48"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A51EFA8C-67A7-4B7E-8EF6-A12213F165A5}">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="B3" s="33"/>
-      <c r="C3" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE832A03-E635-4A62-818A-B14E9D4AA5F6}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -6811,7 +5289,2038 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4903F224-3652-48FB-81A7-CAF06A9D7463}">
+  <dimension ref="A1:AD9"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:30">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30">
+      <c r="A2" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="B2" s="3">
+        <v>1</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="3"/>
+      <c r="AA2" s="3"/>
+      <c r="AB2" s="3"/>
+      <c r="AC2" s="3"/>
+      <c r="AD2" s="3"/>
+    </row>
+    <row r="3" spans="1:30">
+      <c r="A3" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="B3" s="3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>244</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J3" s="3">
+        <v>2</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="U3">
+        <v>3</v>
+      </c>
+      <c r="V3" s="3"/>
+      <c r="W3" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y3" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z3">
+        <v>4</v>
+      </c>
+      <c r="AA3" s="18" t="s">
+        <v>246</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30">
+      <c r="A4" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="B4" s="3">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3"/>
+      <c r="X4" s="3"/>
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
+      <c r="AB4" s="3"/>
+      <c r="AC4" s="3"/>
+      <c r="AD4" s="3"/>
+    </row>
+    <row r="5" spans="1:30">
+      <c r="A5" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="J5" s="3">
+        <v>5</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="R5" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="S5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="U5">
+        <v>1</v>
+      </c>
+      <c r="V5" s="3">
+        <v>1</v>
+      </c>
+      <c r="W5" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="X5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z5">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AC5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AD5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30">
+      <c r="A6" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3"/>
+      <c r="W6" s="3"/>
+      <c r="X6" s="3"/>
+      <c r="Y6" s="3"/>
+      <c r="Z6" s="3"/>
+      <c r="AA6" s="3"/>
+      <c r="AB6" s="3"/>
+      <c r="AC6" s="3"/>
+      <c r="AD6" s="3"/>
+    </row>
+    <row r="7" spans="1:30">
+      <c r="A7" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
+      <c r="U7" s="3"/>
+      <c r="V7" s="3"/>
+      <c r="W7" s="3"/>
+      <c r="X7" s="3"/>
+      <c r="Y7" s="3"/>
+      <c r="Z7" s="3"/>
+      <c r="AA7" s="3"/>
+      <c r="AB7" s="3"/>
+      <c r="AC7" s="3"/>
+      <c r="AD7" s="3"/>
+    </row>
+    <row r="8" spans="1:30">
+      <c r="A8" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="B8" s="3">
+        <v>1</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
+      <c r="U8" s="3"/>
+      <c r="V8" s="3"/>
+      <c r="W8" s="3"/>
+      <c r="X8" s="3"/>
+      <c r="Y8" s="3"/>
+      <c r="Z8" s="3"/>
+      <c r="AA8" s="3"/>
+      <c r="AB8" s="3"/>
+      <c r="AC8" s="3"/>
+      <c r="AD8" s="3"/>
+    </row>
+    <row r="9" spans="1:30">
+      <c r="A9" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="B9" s="3">
+        <v>1</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="S9" s="3"/>
+      <c r="T9" s="3"/>
+      <c r="U9" s="3"/>
+      <c r="V9" s="3"/>
+      <c r="W9" s="3"/>
+      <c r="X9" s="3"/>
+      <c r="Y9" s="3"/>
+      <c r="Z9" s="3"/>
+      <c r="AA9" s="3"/>
+      <c r="AB9" s="3"/>
+      <c r="AC9" s="3"/>
+      <c r="AD9" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29EECB68-AFA6-4B7C-B9A3-85863070956A}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="35.26953125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="11.54296875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="13.453125"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E2" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="34" t="s">
+        <v>179</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB53E397-0E70-4FE2-8956-CAC505C79FBA}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="33.54296875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="13.453125"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>192</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71142910-3363-4189-996E-89090332A376}">
+  <dimension ref="A1:AC4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="5" max="5" customWidth="true" width="6.26953125"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="13.90625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:29">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29">
+      <c r="A2" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B2" s="3">
+        <v>1</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2" s="18"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="X2" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="Y2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z2" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC2" s="3" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29">
+      <c r="A3" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B3" s="3">
+        <v>2</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>252</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="J3" s="18">
+        <v>3</v>
+      </c>
+      <c r="K3" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N3">
+        <v>4</v>
+      </c>
+      <c r="O3" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="R3" s="3">
+        <v>5</v>
+      </c>
+      <c r="S3" s="18"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="3"/>
+      <c r="AB3" s="3"/>
+      <c r="AC3" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29">
+      <c r="A4" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B4" s="3">
+        <v>1</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="18"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="X4" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="Y4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z4" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="AA4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC4" s="3" t="s">
+        <v>651</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51F26840-7703-45A5-AB34-582BA93F27A0}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="63.7265625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="10.7265625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="19.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="15.54296875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="8" max="9" bestFit="true" customWidth="true" width="19.453125"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="34" t="s">
+        <v>162</v>
+      </c>
+      <c r="B2" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>164</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B4" s="37" t="s">
+        <v>166</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55103D89-E5B2-47D3-956F-E8E1CB3BB167}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:R6"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="12.0"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="9.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="6.26953125"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="13.81640625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="7.453125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="18.453125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="18.453125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="11.81640625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18">
+      <c r="A1" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="E1" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="F1" s="38" t="s">
+        <v>194</v>
+      </c>
+      <c r="G1" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="40" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="L1" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="N1" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="O1" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="P1" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q1" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="R1" s="32" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
+      <c r="A2" s="28" t="s">
+        <v>195</v>
+      </c>
+      <c r="B2" s="18">
+        <v>1</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="18">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+    </row>
+    <row r="3" spans="1:18">
+      <c r="A3" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="B3" s="18">
+        <v>7</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="18">
+        <v>6</v>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
+      <c r="A4" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="B4" s="18">
+        <v>1</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="18">
+        <v>0</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="J4" s="3">
+        <v>2</v>
+      </c>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="A5" s="28" t="s">
+        <v>211</v>
+      </c>
+      <c r="B5" s="18">
+        <v>1</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="18">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="A6" s="28" t="s">
+        <v>212</v>
+      </c>
+      <c r="B6" s="18">
+        <v>1</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="18">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42BBEF64-F0EA-4EA8-9A62-F5A7DF1E4869}">
+  <dimension ref="A1:U13"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:21">
+      <c r="A1" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="E1" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="F1" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="I1" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="J1" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="K1" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="L1" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="M1" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="N1" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="O1" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21">
+      <c r="A2" s="28" t="s">
+        <v>215</v>
+      </c>
+      <c r="B2" s="50">
+        <v>1</v>
+      </c>
+      <c r="C2" s="48" t="s">
+        <v>328</v>
+      </c>
+      <c r="D2" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="48" t="s">
+        <v>329</v>
+      </c>
+      <c r="F2" s="50">
+        <v>1</v>
+      </c>
+      <c r="G2" s="48" t="s">
+        <v>330</v>
+      </c>
+      <c r="H2" s="48" t="s">
+        <v>329</v>
+      </c>
+      <c r="I2" s="48" t="s">
+        <v>218</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
+      <c r="A3" s="28" t="s">
+        <v>258</v>
+      </c>
+      <c r="B3" s="50">
+        <v>1</v>
+      </c>
+      <c r="C3" s="48" t="s">
+        <v>328</v>
+      </c>
+      <c r="D3" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="48" t="s">
+        <v>329</v>
+      </c>
+      <c r="F3" s="50">
+        <v>1</v>
+      </c>
+      <c r="G3" s="48" t="s">
+        <v>331</v>
+      </c>
+      <c r="H3" s="48" t="s">
+        <v>329</v>
+      </c>
+      <c r="I3" s="48" t="s">
+        <v>218</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="U3" s="3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
+      <c r="B8" s="18">
+        <v>1</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>216</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="F8" s="18">
+        <v>4</v>
+      </c>
+      <c r="G8" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
+      <c r="B9" s="18">
+        <v>1</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>216</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="F9" s="18">
+        <v>4</v>
+      </c>
+      <c r="G9" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
+      <c r="B12" s="18">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="18">
+        <v>1</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
+      <c r="B13" s="18">
+        <v>1</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="18">
+        <v>1</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51EE6AAF-837D-4C0C-BD88-9AF62A29B7BB}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="32.26953125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>131</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A51EFA8C-67A7-4B7E-8EF6-A12213F165A5}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFCF6FDB-3B87-457C-A3CA-7B39CE849651}">
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" style="57" width="24.90625"/>
+    <col min="2" max="2" customWidth="true" style="57" width="17.453125"/>
+    <col min="3" max="16384" style="57" width="8.7265625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="61" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="58" t="s">
+        <v>421</v>
+      </c>
+      <c r="C1" s="60" t="s">
+        <v>200</v>
+      </c>
+      <c r="D1" s="60" t="s">
+        <v>201</v>
+      </c>
+      <c r="E1" s="60" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="60" t="s">
+        <v>440</v>
+      </c>
+      <c r="B2" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="60" t="s">
+        <v>441</v>
+      </c>
+      <c r="B3" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="60" t="s">
+        <v>442</v>
+      </c>
+      <c r="B4" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="60" t="s">
+        <v>443</v>
+      </c>
+      <c r="B5" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="60" t="s">
+        <v>444</v>
+      </c>
+      <c r="B6" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="C6" s="60"/>
+      <c r="D6" s="60"/>
+      <c r="E6" s="60"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="60" t="s">
+        <v>445</v>
+      </c>
+      <c r="B7" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="60"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="60" t="s">
+        <v>446</v>
+      </c>
+      <c r="B8" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="C8" s="60"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="60" t="s">
+        <v>447</v>
+      </c>
+      <c r="B9" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="C9" s="60"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="60" t="s">
+        <v>448</v>
+      </c>
+      <c r="B10" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="C10" s="60"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="60" t="s">
+        <v>449</v>
+      </c>
+      <c r="B11" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="C11" s="60"/>
+      <c r="D11" s="60"/>
+      <c r="E11" s="60"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="60" t="s">
+        <v>450</v>
+      </c>
+      <c r="B12" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="C12" s="60"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="60" t="s">
+        <v>451</v>
+      </c>
+      <c r="B13" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="C13" s="60"/>
+      <c r="D13" s="60"/>
+      <c r="E13" s="60"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="60" t="s">
+        <v>452</v>
+      </c>
+      <c r="B14" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="C14" s="60"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="60" t="s">
+        <v>453</v>
+      </c>
+      <c r="B15" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
+      <c r="E15" s="60"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="60" t="s">
+        <v>454</v>
+      </c>
+      <c r="B16" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="C16" s="60"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="60"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="60" t="s">
+        <v>455</v>
+      </c>
+      <c r="B17" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="C17" s="60"/>
+      <c r="D17" s="60"/>
+      <c r="E17" s="60"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DDD085C-F9E3-44F9-93E4-153774C9882E}">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
@@ -6881,10 +7390,10 @@
         <v>70</v>
       </c>
       <c r="H2" s="26" t="s">
-        <v>71</v>
+        <v>600</v>
       </c>
       <c r="I2" s="26" t="s">
-        <v>72</v>
+        <v>601</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -6918,7 +7427,478 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ADD4D69-5509-440B-8A9B-EB710BB5A12A}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="32.26953125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="4" max="4" customWidth="true" width="15.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="17.54296875"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="I4" s="3">
+        <v>2</v>
+      </c>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3">
+        <v>2</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C03B3B8-DBFD-430F-BAEF-858DA603C137}">
+  <dimension ref="A1:V8"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:22">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22">
+      <c r="A2" s="41" t="s">
+        <v>297</v>
+      </c>
+      <c r="B2" s="3">
+        <v>1</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="3">
+        <v>2</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="3">
+        <v>1</v>
+      </c>
+      <c r="K2" s="3"/>
+      <c r="L2" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="O2" s="3">
+        <v>2</v>
+      </c>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="T2" s="3">
+        <v>0</v>
+      </c>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+    </row>
+    <row r="3" spans="1:22">
+      <c r="A3" s="41" t="s">
+        <v>298</v>
+      </c>
+      <c r="B3" s="3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3">
+        <v>1</v>
+      </c>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
+    </row>
+    <row r="4" spans="1:22">
+      <c r="A4" s="41" t="s">
+        <v>299</v>
+      </c>
+      <c r="B4" s="3">
+        <v>1</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" s="3">
+        <v>2</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>300</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="J4" s="3">
+        <v>1</v>
+      </c>
+      <c r="K4" s="3">
+        <v>1</v>
+      </c>
+      <c r="L4" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="O4" s="3">
+        <v>3</v>
+      </c>
+      <c r="P4" s="3">
+        <v>3</v>
+      </c>
+      <c r="Q4" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="T4" s="3">
+        <v>0</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22">
+      <c r="A8" s="41" t="s">
+        <v>299</v>
+      </c>
+      <c r="B8" s="3">
+        <v>1</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" s="3">
+        <v>3</v>
+      </c>
+      <c r="G8" s="18" t="s">
+        <v>303</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J8" s="3">
+        <v>1</v>
+      </c>
+      <c r="K8" s="3">
+        <v>1</v>
+      </c>
+      <c r="L8" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="O8" s="3">
+        <v>5</v>
+      </c>
+      <c r="P8" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q8" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56B70778-466E-461B-A65C-951E1AD4EBAD}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -6982,6 +7962,127 @@
       </c>
       <c r="E3" s="14" t="s">
         <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9A5054F-4F2A-4BA5-95CD-184527D8553F}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="57.453125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="15.54296875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="7.7265625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="11.26953125"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="16">
+        <v>2</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="16">
+        <v>1</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="16">
+        <v>1</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="16">
+        <v>1</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="16">
+        <v>1</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -7100,7 +8201,7 @@
       <c r="M2" s="48"/>
       <c r="N2" s="48"/>
       <c r="O2" s="48" t="s">
-        <v>325</v>
+        <v>603</v>
       </c>
       <c r="P2" s="48"/>
     </row>
@@ -7701,10 +8802,10 @@
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
       <c r="R2" s="3" t="s">
-        <v>276</v>
+        <v>604</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>277</v>
+        <v>605</v>
       </c>
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
@@ -7963,10 +9064,10 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3" t="s">
-        <v>288</v>
+        <v>606</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>289</v>
+        <v>607</v>
       </c>
       <c r="T8" s="3">
         <v>0</v>
@@ -8291,10 +9392,10 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3" t="s">
-        <v>295</v>
+        <v>556</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>296</v>
+        <v>557</v>
       </c>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
@@ -8342,87 +9443,461 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7BF278-0258-4060-BA3D-743DBF61A856}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D801678A-93DD-4A10-BD7A-B4F1484B5E45}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="76.1796875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="13.453125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="53.81640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="3" max="4" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="5" max="7" customWidth="true" width="12.1796875"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="12.1796875"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:19">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="D1" s="28" t="s">
-        <v>98</v>
-      </c>
-      <c r="E1" s="28" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="B2" s="30" t="s">
+      <c r="D1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
+      <c r="A2" s="34" t="s">
+        <v>135</v>
+      </c>
+      <c r="B2" s="3">
+        <v>2</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3" spans="1:19">
+      <c r="A3" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="B3" s="3">
+        <v>2</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+    </row>
+    <row r="4" spans="1:19">
+      <c r="A4" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+    </row>
+    <row r="5" spans="1:19">
+      <c r="A5" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="B5" s="3">
+        <v>2</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+      <c r="S5" s="3"/>
+    </row>
+    <row r="6" spans="1:19">
+      <c r="A6" s="34" t="s">
+        <v>141</v>
+      </c>
+      <c r="B6" s="3">
+        <v>0</v>
+      </c>
+      <c r="C6" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="31">
-        <v>1</v>
-      </c>
-      <c r="D2" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="3"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="29" t="s">
-        <v>101</v>
-      </c>
-      <c r="B3" s="18" t="s">
+      <c r="D6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7" spans="1:19">
+      <c r="A7" s="34" t="s">
+        <v>142</v>
+      </c>
+      <c r="B7" s="3">
+        <v>2</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G7" s="3"/>
+    </row>
+    <row r="8" spans="1:19">
+      <c r="A8" s="34" t="s">
+        <v>143</v>
+      </c>
+      <c r="B8" s="3">
+        <v>2</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G8" s="3"/>
+    </row>
+    <row r="9" spans="1:19">
+      <c r="A9" s="34" t="s">
+        <v>144</v>
+      </c>
+      <c r="B9" s="3">
+        <v>2</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G9" s="3"/>
+    </row>
+    <row r="10" spans="1:19">
+      <c r="A10" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="B10" s="3">
+        <v>2</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="18" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
+      <c r="A11" s="35" t="s">
+        <v>146</v>
+      </c>
+      <c r="B11" s="3">
+        <v>2</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="18" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
+      <c r="A12" s="34" t="s">
+        <v>147</v>
+      </c>
+      <c r="B12" s="26">
+        <v>0</v>
+      </c>
+      <c r="C12" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="31">
-        <v>1</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="B4" s="18" t="s">
+      <c r="D12" s="26" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19">
+      <c r="A13" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+    </row>
+    <row r="14" spans="1:19">
+      <c r="A14" s="34" t="s">
+        <v>149</v>
+      </c>
+      <c r="B14" s="3">
+        <v>2</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+    </row>
+    <row r="15" spans="1:19">
+      <c r="A15" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="B15" s="3">
+        <v>2</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+    </row>
+    <row r="16" spans="1:19">
+      <c r="A16" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="B16" s="26">
+        <v>0</v>
+      </c>
+      <c r="C16" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="31">
-        <v>1</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>41</v>
+      <c r="D16" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+    </row>
+    <row r="17" spans="1:19">
+      <c r="A17" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="B17" s="26">
+        <v>0</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+    </row>
+    <row r="20" spans="1:19">
+      <c r="A20" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="B20" s="3">
+        <v>1</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J20" s="3">
+        <v>2</v>
+      </c>
+      <c r="K20" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/src/test/java/TestData/Scenario_TestData.xlsx
+++ b/src/test/java/TestData/Scenario_TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\COPA Automation Final\Copa_API_WebServices\src\test\java\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00A0AB71-91C3-48C1-A416-63E249A1D32E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{819B26A9-F34C-4039-A732-7E8C24DC73EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="11" xr2:uid="{5D5A4724-D560-4FC2-9708-4BBF1DBA0B11}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="27" activeTab="30" xr2:uid="{5D5A4724-D560-4FC2-9708-4BBF1DBA0B11}"/>
   </bookViews>
   <sheets>
     <sheet name="AdvancePassengerInfo" sheetId="1" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1874" uniqueCount="652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1619" uniqueCount="567">
   <si>
     <t>Scenario</t>
   </si>
@@ -119,24 +119,9 @@
     <t>1</t>
   </si>
   <si>
-    <t>BGUFSD</t>
-  </si>
-  <si>
-    <t>PHILLIP</t>
-  </si>
-  <si>
     <t>MORRIS</t>
   </si>
   <si>
-    <t>JACK</t>
-  </si>
-  <si>
-    <t>RYAN</t>
-  </si>
-  <si>
-    <t>BGUFVA</t>
-  </si>
-  <si>
     <t>Create_booking_multiplepax_with_same_surname(3 PAX)</t>
   </si>
   <si>
@@ -281,12 +266,6 @@
     <t>2</t>
   </si>
   <si>
-    <t>BG1UUO</t>
-  </si>
-  <si>
-    <t>2023-01-31T17:01:50</t>
-  </si>
-  <si>
     <t>Code_12_Passengers_with_advance_seats</t>
   </si>
   <si>
@@ -428,15 +407,6 @@
     <t>Reduce PNR</t>
   </si>
   <si>
-    <t>AJAKZ3</t>
-  </si>
-  <si>
-    <t>2023-02-16T07:48:00</t>
-  </si>
-  <si>
-    <t>2023-02-16T10:57:00</t>
-  </si>
-  <si>
     <t>Other Changes</t>
   </si>
   <si>
@@ -737,24 +707,6 @@
     <t>Disassociation: EMD coupon 1 with ETKT coupon 1</t>
   </si>
   <si>
-    <t>2023-03-07T07:51:00</t>
-  </si>
-  <si>
-    <t>2023-03-07T09:31:00</t>
-  </si>
-  <si>
-    <t>BGD0H4</t>
-  </si>
-  <si>
-    <t>2302181176745</t>
-  </si>
-  <si>
-    <t>BGFE5Z</t>
-  </si>
-  <si>
-    <t>2302181176768</t>
-  </si>
-  <si>
     <t>Ticket a booking with one flight, one passenger with credit card form of payment</t>
   </si>
   <si>
@@ -779,24 +731,6 @@
     <t>Issue ticket for a booking with an infant</t>
   </si>
   <si>
-    <t>2023-03-08T07:51:00</t>
-  </si>
-  <si>
-    <t>2023-03-08T09:31:00</t>
-  </si>
-  <si>
-    <t>BHFNK1</t>
-  </si>
-  <si>
-    <t>BH3JYD</t>
-  </si>
-  <si>
-    <t>2023-03-09T07:51:00</t>
-  </si>
-  <si>
-    <t>2023-03-09T09:31:00</t>
-  </si>
-  <si>
     <t>332</t>
   </si>
   <si>
@@ -809,21 +743,6 @@
     <t>495</t>
   </si>
   <si>
-    <t>BIOOMO</t>
-  </si>
-  <si>
-    <t>2302181182797</t>
-  </si>
-  <si>
-    <t>BIOYNR</t>
-  </si>
-  <si>
-    <t>2023-03-09T21:15:00</t>
-  </si>
-  <si>
-    <t>2023-03-10T06:39:00</t>
-  </si>
-  <si>
     <t>333</t>
   </si>
   <si>
@@ -866,21 +785,6 @@
     <t>410</t>
   </si>
   <si>
-    <t>2023-03-16T09:56:00</t>
-  </si>
-  <si>
-    <t>2023-03-16T14:03:00</t>
-  </si>
-  <si>
-    <t>2023-03-20T13:15:00</t>
-  </si>
-  <si>
-    <t>2023-03-20T15:20:00</t>
-  </si>
-  <si>
-    <t>BPGQR2</t>
-  </si>
-  <si>
     <t>Check for invalid Ticketing in request</t>
   </si>
   <si>
@@ -896,12 +800,6 @@
     <t>TicketNumber</t>
   </si>
   <si>
-    <t>AB0QAC</t>
-  </si>
-  <si>
-    <t>2302181241864</t>
-  </si>
-  <si>
     <t>Create a booking with 1 segment, 1 passenger, stored fare (1 fare basis code, base fare, not valid before/after date, fare calculation line, bagagge allowance, sale location, 1 free-flow remark, tour code and form of payment CASH) and time limit.</t>
   </si>
   <si>
@@ -932,12 +830,6 @@
     <t>Add the Form Of Payment remark and the FOP in the stored fare</t>
   </si>
   <si>
-    <t>AB3ZI2</t>
-  </si>
-  <si>
-    <t>2302181241898</t>
-  </si>
-  <si>
     <t>NotValidAfter/Before</t>
   </si>
   <si>
@@ -953,39 +845,6 @@
     <t>2302181242853</t>
   </si>
   <si>
-    <t>ADQEDZ</t>
-  </si>
-  <si>
-    <t>2302181245752</t>
-  </si>
-  <si>
-    <t>Adjust Name</t>
-  </si>
-  <si>
-    <t>Adjust Class of service</t>
-  </si>
-  <si>
-    <t>Adjust flight number and flight date</t>
-  </si>
-  <si>
-    <t>322</t>
-  </si>
-  <si>
-    <t>AGNL2W</t>
-  </si>
-  <si>
-    <t>2302181255119</t>
-  </si>
-  <si>
-    <t>136</t>
-  </si>
-  <si>
-    <t>AGN3GO</t>
-  </si>
-  <si>
-    <t>2302181255444</t>
-  </si>
-  <si>
     <t>AJKWFN</t>
   </si>
   <si>
@@ -1010,9 +869,6 @@
     <t>GUA</t>
   </si>
   <si>
-    <t>AKDLJJ</t>
-  </si>
-  <si>
     <t>2023-03-29T11:44:00</t>
   </si>
   <si>
@@ -1025,9 +881,6 @@
     <t>2023-04-01T16:33:00</t>
   </si>
   <si>
-    <t>2302181263794</t>
-  </si>
-  <si>
     <t>AKDLK0</t>
   </si>
   <si>
@@ -1043,9 +896,6 @@
     <t>ONE</t>
   </si>
   <si>
-    <t>AGAKNH</t>
-  </si>
-  <si>
     <t>Error_Change_seatInvalid</t>
   </si>
   <si>
@@ -1136,12 +986,6 @@
     <t>AS3P4S</t>
   </si>
   <si>
-    <t>AS51AY</t>
-  </si>
-  <si>
-    <t>2302181280247</t>
-  </si>
-  <si>
     <t>Instance</t>
   </si>
   <si>
@@ -1157,105 +1001,39 @@
     <t>CARLOS</t>
   </si>
   <si>
-    <t>2302181281719</t>
-  </si>
-  <si>
     <t>JACKMAN</t>
   </si>
   <si>
-    <t>ATM53Y</t>
-  </si>
-  <si>
-    <t>2302181281885</t>
-  </si>
-  <si>
     <t>WILSON</t>
   </si>
   <si>
-    <t>ATOMOC</t>
-  </si>
-  <si>
     <t>CreditCard</t>
   </si>
   <si>
     <t>4000400012345678</t>
   </si>
   <si>
-    <t>ATP4Q4</t>
-  </si>
-  <si>
-    <t>2302181282180</t>
-  </si>
-  <si>
-    <t>ATQBLV</t>
-  </si>
-  <si>
     <t>PONSE</t>
   </si>
   <si>
-    <t>2302181282289</t>
-  </si>
-  <si>
-    <t>ATQEB0</t>
-  </si>
-  <si>
-    <t>2302181282306</t>
-  </si>
-  <si>
-    <t>ATQE0B</t>
-  </si>
-  <si>
-    <t>2302181282324</t>
-  </si>
-  <si>
-    <t>ATQE1E</t>
-  </si>
-  <si>
-    <t>2302181282327</t>
-  </si>
-  <si>
-    <t>ATQ1VN</t>
-  </si>
-  <si>
-    <t>2302181282595</t>
-  </si>
-  <si>
     <t>1234567890123456</t>
   </si>
   <si>
-    <t>ATRGAV</t>
-  </si>
-  <si>
-    <t>2302181283095</t>
-  </si>
-  <si>
     <t>DOE</t>
   </si>
   <si>
-    <t>AT1HJF</t>
-  </si>
-  <si>
-    <t>AT1IJK</t>
-  </si>
-  <si>
     <t>BOOKING</t>
   </si>
   <si>
     <t>CANCEL</t>
   </si>
   <si>
-    <t>AUAVIX</t>
-  </si>
-  <si>
     <t>KYLE</t>
   </si>
   <si>
     <t>BROFLOVSKY</t>
   </si>
   <si>
-    <t>AUA5TF</t>
-  </si>
-  <si>
     <t>GivenNamePNR2</t>
   </si>
   <si>
@@ -1265,27 +1043,12 @@
     <t>RICK</t>
   </si>
   <si>
-    <t>BLQN32</t>
-  </si>
-  <si>
     <t>BLQN35</t>
   </si>
   <si>
-    <t>BLQQGU</t>
-  </si>
-  <si>
-    <t>BLQQGW</t>
-  </si>
-  <si>
     <t>1931</t>
   </si>
   <si>
-    <t>BLQURE</t>
-  </si>
-  <si>
-    <t>BLQU5S</t>
-  </si>
-  <si>
     <t>TransactionIdentifier</t>
   </si>
   <si>
@@ -1295,27 +1058,15 @@
     <t>Modify_Booking</t>
   </si>
   <si>
-    <t>97C6BC48CMCMRPCT083ADC3BAA</t>
-  </si>
-  <si>
-    <t>BLQJ3A</t>
-  </si>
-  <si>
     <t>Create_a_booking_for_a_group</t>
   </si>
   <si>
-    <t>8F4F96CECMCMRPCT05409404B2</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
     <t>Create_a_booking_for_two_segments</t>
   </si>
   <si>
-    <t>D25C161ACMCMRPCT07BE802116</t>
-  </si>
-  <si>
     <t>AirlineVendorID</t>
   </si>
   <si>
@@ -1466,156 +1217,6 @@
     <t>Bulk_Ticket</t>
   </si>
   <si>
-    <t>BOCZVC</t>
-  </si>
-  <si>
-    <t>BOCZWU</t>
-  </si>
-  <si>
-    <t>BOCZW0</t>
-  </si>
-  <si>
-    <t>BOCZXB</t>
-  </si>
-  <si>
-    <t>BOCZZD</t>
-  </si>
-  <si>
-    <t>2023-05-18T14:30:46</t>
-  </si>
-  <si>
-    <t>BOCZ34</t>
-  </si>
-  <si>
-    <t>2023-05-18T14:30:53</t>
-  </si>
-  <si>
-    <t>BOC0AQ</t>
-  </si>
-  <si>
-    <t>BOC0BS</t>
-  </si>
-  <si>
-    <t>BOC0CY</t>
-  </si>
-  <si>
-    <t>2302181833965</t>
-  </si>
-  <si>
-    <t>BOC0IU</t>
-  </si>
-  <si>
-    <t>2302181833970</t>
-  </si>
-  <si>
-    <t>BOC0UW</t>
-  </si>
-  <si>
-    <t>2302181833972</t>
-  </si>
-  <si>
-    <t>BOC00G</t>
-  </si>
-  <si>
-    <t>2302181833973</t>
-  </si>
-  <si>
-    <t>BOC015</t>
-  </si>
-  <si>
-    <t>2302181833974</t>
-  </si>
-  <si>
-    <t>BOC03M</t>
-  </si>
-  <si>
-    <t>2302181833975</t>
-  </si>
-  <si>
-    <t>BOC041</t>
-  </si>
-  <si>
-    <t>2302181833976</t>
-  </si>
-  <si>
-    <t>BOC1C2</t>
-  </si>
-  <si>
-    <t>BOC1E2</t>
-  </si>
-  <si>
-    <t>BOC1FN</t>
-  </si>
-  <si>
-    <t>BOC1GI</t>
-  </si>
-  <si>
-    <t>BOC1HO</t>
-  </si>
-  <si>
-    <t>BOC1HY</t>
-  </si>
-  <si>
-    <t>2302181833978</t>
-  </si>
-  <si>
-    <t>BOC1H5</t>
-  </si>
-  <si>
-    <t>BOC1LY</t>
-  </si>
-  <si>
-    <t>2302181833979</t>
-  </si>
-  <si>
-    <t>BOC1NK</t>
-  </si>
-  <si>
-    <t>BOC1N4</t>
-  </si>
-  <si>
-    <t>BOC1OI</t>
-  </si>
-  <si>
-    <t>2302181833982</t>
-  </si>
-  <si>
-    <t>BOC1O0</t>
-  </si>
-  <si>
-    <t>2302181833983</t>
-  </si>
-  <si>
-    <t>BOC1RH</t>
-  </si>
-  <si>
-    <t>2302181833986</t>
-  </si>
-  <si>
-    <t>BOC1SS</t>
-  </si>
-  <si>
-    <t>BOC1TN</t>
-  </si>
-  <si>
-    <t>2302181833987</t>
-  </si>
-  <si>
-    <t>BOC1WD</t>
-  </si>
-  <si>
-    <t>EA79875ECMCMRPCT06AE946B61</t>
-  </si>
-  <si>
-    <t>6244B83CCMCMRPCT085EB41F86</t>
-  </si>
-  <si>
-    <t>89B4E13ECMCMRPCT08446A5E88</t>
-  </si>
-  <si>
-    <t>BOC22U</t>
-  </si>
-  <si>
     <t>2023-05-19T09:56:00</t>
   </si>
   <si>
@@ -1628,63 +1229,12 @@
     <t>2023-05-23T15:21:00</t>
   </si>
   <si>
-    <t>BOC24F</t>
-  </si>
-  <si>
-    <t>2023-05-21T07:48:00</t>
-  </si>
-  <si>
-    <t>2023-05-21T11:54:00</t>
-  </si>
-  <si>
-    <t>BOC3C4</t>
-  </si>
-  <si>
-    <t>2023-05-19T07:50:00</t>
-  </si>
-  <si>
-    <t>2023-05-19T09:29:00</t>
-  </si>
-  <si>
-    <t>BOC3D4</t>
-  </si>
-  <si>
     <t>2024-03-09T20:51:00</t>
   </si>
   <si>
     <t>2024-03-10T06:42:00</t>
   </si>
   <si>
-    <t>BOC3ES</t>
-  </si>
-  <si>
-    <t>2302181834007</t>
-  </si>
-  <si>
-    <t>BOC3FZ</t>
-  </si>
-  <si>
-    <t>BOC3GM</t>
-  </si>
-  <si>
-    <t>BOC3HN</t>
-  </si>
-  <si>
-    <t>BOC3LG</t>
-  </si>
-  <si>
-    <t>2302181834013</t>
-  </si>
-  <si>
-    <t>BOC3OZ</t>
-  </si>
-  <si>
-    <t>2302181834014</t>
-  </si>
-  <si>
-    <t>BOC3RZ</t>
-  </si>
-  <si>
     <t>2023-05-19T07:56:00</t>
   </si>
   <si>
@@ -1697,261 +1247,27 @@
     <t>2023-05-19T15:40:00</t>
   </si>
   <si>
-    <t>2302181834017</t>
-  </si>
-  <si>
-    <t>BODJXX</t>
-  </si>
-  <si>
-    <t>BODJYB</t>
-  </si>
-  <si>
-    <t>BODJYD</t>
-  </si>
-  <si>
-    <t>BODJZF</t>
-  </si>
-  <si>
-    <t>BODJ3C</t>
-  </si>
-  <si>
-    <t>2023-05-18T15:09:06</t>
-  </si>
-  <si>
-    <t>BODKGK</t>
-  </si>
-  <si>
-    <t>2023-05-18T15:09:14</t>
-  </si>
-  <si>
-    <t>BODKTO</t>
-  </si>
-  <si>
-    <t>BODKW0</t>
-  </si>
-  <si>
-    <t>BODKYM</t>
-  </si>
-  <si>
-    <t>2302181834306</t>
-  </si>
-  <si>
     <t>BODK0Y</t>
   </si>
   <si>
     <t>2302181834307</t>
   </si>
   <si>
-    <t>BODLES</t>
-  </si>
-  <si>
-    <t>2302181834309</t>
-  </si>
-  <si>
-    <t>BODLK4</t>
-  </si>
-  <si>
-    <t>2302181834310</t>
-  </si>
-  <si>
-    <t>BODLLJ</t>
-  </si>
-  <si>
-    <t>2302181834311</t>
-  </si>
-  <si>
-    <t>BODLMC</t>
-  </si>
-  <si>
-    <t>2302181834312</t>
-  </si>
-  <si>
-    <t>BODLNY</t>
-  </si>
-  <si>
-    <t>2302181834313</t>
-  </si>
-  <si>
-    <t>BODLO1</t>
-  </si>
-  <si>
-    <t>BODLP5</t>
-  </si>
-  <si>
-    <t>BODLRI</t>
-  </si>
-  <si>
-    <t>BODLTC</t>
-  </si>
-  <si>
-    <t>BODLU4</t>
-  </si>
-  <si>
-    <t>BODLVV</t>
-  </si>
-  <si>
-    <t>2302181834318</t>
-  </si>
-  <si>
-    <t>BODLWJ</t>
-  </si>
-  <si>
-    <t>BODL0A</t>
-  </si>
-  <si>
-    <t>2302181834319</t>
-  </si>
-  <si>
-    <t>BODL1K</t>
-  </si>
-  <si>
-    <t>BODL1T</t>
-  </si>
-  <si>
     <t>BODL51</t>
   </si>
   <si>
     <t>22EE7770CMCMRPCT05339998DA</t>
   </si>
   <si>
-    <t>80CA5544CMCMRPCT06F5059406</t>
-  </si>
-  <si>
-    <t>B0A4D95ECMCMRPCT08D51EEDEF</t>
-  </si>
-  <si>
     <t>BODNR1</t>
   </si>
   <si>
-    <t>BODNWG</t>
-  </si>
-  <si>
-    <t>BODNY1</t>
-  </si>
-  <si>
-    <t>BODNZL</t>
-  </si>
-  <si>
-    <t>BODN0O</t>
-  </si>
-  <si>
-    <t>2302181834325</t>
-  </si>
-  <si>
-    <t>BODN5B</t>
-  </si>
-  <si>
-    <t>2302181834326</t>
-  </si>
-  <si>
     <t>BODOEH</t>
   </si>
   <si>
     <t>2302181834330</t>
   </si>
   <si>
-    <t>AEEZ0N</t>
-  </si>
-  <si>
-    <t>AEEZ1U</t>
-  </si>
-  <si>
-    <t>AEEZ2U</t>
-  </si>
-  <si>
-    <t>AEEZ3E</t>
-  </si>
-  <si>
-    <t>AEEZ5C</t>
-  </si>
-  <si>
-    <t>2023-06-01T06:39:06</t>
-  </si>
-  <si>
-    <t>AEE0AE</t>
-  </si>
-  <si>
-    <t>2023-06-01T06:39:13</t>
-  </si>
-  <si>
-    <t>AEE0DJ</t>
-  </si>
-  <si>
-    <t>AEE0EF</t>
-  </si>
-  <si>
-    <t>AEE0FZ</t>
-  </si>
-  <si>
-    <t>2302181859845</t>
-  </si>
-  <si>
-    <t>AEE0LA</t>
-  </si>
-  <si>
-    <t>2302181859846</t>
-  </si>
-  <si>
-    <t>AEE0OT</t>
-  </si>
-  <si>
-    <t>2302181859847</t>
-  </si>
-  <si>
-    <t>AEE0PG</t>
-  </si>
-  <si>
-    <t>2302181859848</t>
-  </si>
-  <si>
-    <t>AEE0QL</t>
-  </si>
-  <si>
-    <t>2302181859849</t>
-  </si>
-  <si>
-    <t>AEE0RU</t>
-  </si>
-  <si>
-    <t>2302181859850</t>
-  </si>
-  <si>
-    <t>AEE0SJ</t>
-  </si>
-  <si>
-    <t>AEE0TP</t>
-  </si>
-  <si>
-    <t>AEE0UB</t>
-  </si>
-  <si>
-    <t>AEE0VF</t>
-  </si>
-  <si>
-    <t>AEE0WG</t>
-  </si>
-  <si>
-    <t>AEE0WN</t>
-  </si>
-  <si>
-    <t>2302181859851</t>
-  </si>
-  <si>
-    <t>AEE0XP</t>
-  </si>
-  <si>
-    <t>AEE0YP</t>
-  </si>
-  <si>
-    <t>2302181859852</t>
-  </si>
-  <si>
-    <t>AEE0ZV</t>
-  </si>
-  <si>
-    <t>AEE0ZY</t>
-  </si>
-  <si>
     <t>AEE00K</t>
   </si>
   <si>
@@ -1964,64 +1280,493 @@
     <t>2302181859854</t>
   </si>
   <si>
-    <t>AEE01R</t>
-  </si>
-  <si>
-    <t>2302181859855</t>
-  </si>
-  <si>
-    <t>AEE02Y</t>
-  </si>
-  <si>
-    <t>AEE03H</t>
-  </si>
-  <si>
-    <t>2302181859856</t>
-  </si>
-  <si>
-    <t>5953A61ECMCMRPCT05BA12EE48</t>
-  </si>
-  <si>
-    <t>BC0E61FCCMCMRPCT0622E94D6C</t>
-  </si>
-  <si>
-    <t>AEE4KI</t>
-  </si>
-  <si>
-    <t>2023-06-02T07:55:00</t>
-  </si>
-  <si>
-    <t>2023-06-02T09:29:00</t>
-  </si>
-  <si>
-    <t>AEE4PJ</t>
-  </si>
-  <si>
-    <t>AEE4S1</t>
-  </si>
-  <si>
-    <t>2302181859867</t>
-  </si>
-  <si>
-    <t>AEE4WE</t>
-  </si>
-  <si>
-    <t>AEE4XT</t>
-  </si>
-  <si>
-    <t>AEE4YV</t>
-  </si>
-  <si>
-    <t>AEE5HK</t>
-  </si>
-  <si>
-    <t>2302181859873</t>
-  </si>
-  <si>
-    <t>AEE5L5</t>
-  </si>
-  <si>
-    <t>2302181859874</t>
+    <t>AE40MU</t>
+  </si>
+  <si>
+    <t>AE40NF</t>
+  </si>
+  <si>
+    <t>AE40OY</t>
+  </si>
+  <si>
+    <t>2023-06-02T06:21:30</t>
+  </si>
+  <si>
+    <t>AE40UK</t>
+  </si>
+  <si>
+    <t>AE40UZ</t>
+  </si>
+  <si>
+    <t>2302181862749</t>
+  </si>
+  <si>
+    <t>AE40XX</t>
+  </si>
+  <si>
+    <t>2302181862750</t>
+  </si>
+  <si>
+    <t>AE401F</t>
+  </si>
+  <si>
+    <t>2302181862753</t>
+  </si>
+  <si>
+    <t>AE404A</t>
+  </si>
+  <si>
+    <t>2302181862756</t>
+  </si>
+  <si>
+    <t>AE41CN</t>
+  </si>
+  <si>
+    <t>2302181862757</t>
+  </si>
+  <si>
+    <t>AE41D5</t>
+  </si>
+  <si>
+    <t>2302181862758</t>
+  </si>
+  <si>
+    <t>AE41EM</t>
+  </si>
+  <si>
+    <t>AE41FG</t>
+  </si>
+  <si>
+    <t>AE41FS</t>
+  </si>
+  <si>
+    <t>AE41II</t>
+  </si>
+  <si>
+    <t>AE41KD</t>
+  </si>
+  <si>
+    <t>AE41KP</t>
+  </si>
+  <si>
+    <t>2302181862759</t>
+  </si>
+  <si>
+    <t>AE41LH</t>
+  </si>
+  <si>
+    <t>AE41MP</t>
+  </si>
+  <si>
+    <t>2302181862760</t>
+  </si>
+  <si>
+    <t>AE41NE</t>
+  </si>
+  <si>
+    <t>AE41NJ</t>
+  </si>
+  <si>
+    <t>AE41T0</t>
+  </si>
+  <si>
+    <t>2302181862761</t>
+  </si>
+  <si>
+    <t>AE41UT</t>
+  </si>
+  <si>
+    <t>AE41WE</t>
+  </si>
+  <si>
+    <t>2302181862762</t>
+  </si>
+  <si>
+    <t>C7D87262CMCMRPCT061B0D311A</t>
+  </si>
+  <si>
+    <t>5966EED0CMCMRPCT05BA05D4AF</t>
+  </si>
+  <si>
+    <t>AE42NH</t>
+  </si>
+  <si>
+    <t>2023-06-05T07:53:00</t>
+  </si>
+  <si>
+    <t>2023-06-05T11:56:00</t>
+  </si>
+  <si>
+    <t>AE42PG</t>
+  </si>
+  <si>
+    <t>2023-06-03T07:55:00</t>
+  </si>
+  <si>
+    <t>2023-06-03T09:29:00</t>
+  </si>
+  <si>
+    <t>AE42PU</t>
+  </si>
+  <si>
+    <t>AE42P3</t>
+  </si>
+  <si>
+    <t>2302181862768</t>
+  </si>
+  <si>
+    <t>AE42RO</t>
+  </si>
+  <si>
+    <t>AE42SV</t>
+  </si>
+  <si>
+    <t>2302181862776</t>
+  </si>
+  <si>
+    <t>AE42TI</t>
+  </si>
+  <si>
+    <t>2302181862777</t>
+  </si>
+  <si>
+    <t>Carrier Code</t>
+  </si>
+  <si>
+    <t>Updated Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Updated Flight </t>
+  </si>
+  <si>
+    <t>Sync Flight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAME </t>
+  </si>
+  <si>
+    <t>SURNAME</t>
+  </si>
+  <si>
+    <t>Add Flight</t>
+  </si>
+  <si>
+    <t>AGY2HS</t>
+  </si>
+  <si>
+    <t>Add Name</t>
+  </si>
+  <si>
+    <t>AGY2JA</t>
+  </si>
+  <si>
+    <t>FOX</t>
+  </si>
+  <si>
+    <t>MUDLER</t>
+  </si>
+  <si>
+    <t>Add Class</t>
+  </si>
+  <si>
+    <t>AGY2KG</t>
+  </si>
+  <si>
+    <t>AGY3OI</t>
+  </si>
+  <si>
+    <t>AGY3QR</t>
+  </si>
+  <si>
+    <t>AGY3RY</t>
+  </si>
+  <si>
+    <t>AG3ZTC</t>
+  </si>
+  <si>
+    <t>AG3ZTN</t>
+  </si>
+  <si>
+    <t>AG3ZTO</t>
+  </si>
+  <si>
+    <t>AG3ZTP</t>
+  </si>
+  <si>
+    <t>AIOGZH</t>
+  </si>
+  <si>
+    <t>2302181869630</t>
+  </si>
+  <si>
+    <t>AIOG2P</t>
+  </si>
+  <si>
+    <t>2302181869631</t>
+  </si>
+  <si>
+    <t>AIOHAQ</t>
+  </si>
+  <si>
+    <t>2302181869632</t>
+  </si>
+  <si>
+    <t>AIOHBA</t>
+  </si>
+  <si>
+    <t>2302181869633</t>
+  </si>
+  <si>
+    <t>AIOHB3</t>
+  </si>
+  <si>
+    <t>2302181869634</t>
+  </si>
+  <si>
+    <t>AIOHDQ</t>
+  </si>
+  <si>
+    <t>2302181869635</t>
+  </si>
+  <si>
+    <t>AIOHEY</t>
+  </si>
+  <si>
+    <t>AIOHGT</t>
+  </si>
+  <si>
+    <t>AIOHHI</t>
+  </si>
+  <si>
+    <t>AIOHH5</t>
+  </si>
+  <si>
+    <t>AIOHKI</t>
+  </si>
+  <si>
+    <t>AIOHKX</t>
+  </si>
+  <si>
+    <t>2302181869636</t>
+  </si>
+  <si>
+    <t>AIOHL5</t>
+  </si>
+  <si>
+    <t>AIOHMU</t>
+  </si>
+  <si>
+    <t>2302181869637</t>
+  </si>
+  <si>
+    <t>AIOHNA</t>
+  </si>
+  <si>
+    <t>AIOHND</t>
+  </si>
+  <si>
+    <t>AIOHOA</t>
+  </si>
+  <si>
+    <t>2302181869638</t>
+  </si>
+  <si>
+    <t>AIOHOQ</t>
+  </si>
+  <si>
+    <t>2302181869639</t>
+  </si>
+  <si>
+    <t>AIOHPG</t>
+  </si>
+  <si>
+    <t>2302181869640</t>
+  </si>
+  <si>
+    <t>AIOHQS</t>
+  </si>
+  <si>
+    <t>AIOHRU</t>
+  </si>
+  <si>
+    <t>2302181869641</t>
+  </si>
+  <si>
+    <t>8AD54668CMCMRPCT0543C365BD</t>
+  </si>
+  <si>
+    <t>E2190C22CMCMRPCT0609952907</t>
+  </si>
+  <si>
+    <t>AIOIXA</t>
+  </si>
+  <si>
+    <t>2023-06-08T07:55:00</t>
+  </si>
+  <si>
+    <t>2023-06-08T09:29:00</t>
+  </si>
+  <si>
+    <t>AIOIYA</t>
+  </si>
+  <si>
+    <t>AIOIYZ</t>
+  </si>
+  <si>
+    <t>2302181869645</t>
+  </si>
+  <si>
+    <t>AIOI0F</t>
+  </si>
+  <si>
+    <t>AIOI02</t>
+  </si>
+  <si>
+    <t>AIOI1L</t>
+  </si>
+  <si>
+    <t>AIOI24</t>
+  </si>
+  <si>
+    <t>2302181869651</t>
+  </si>
+  <si>
+    <t>AIOI3U</t>
+  </si>
+  <si>
+    <t>2302181869652</t>
+  </si>
+  <si>
+    <t>AIOJAN</t>
+  </si>
+  <si>
+    <t>2023-06-08T07:38:00</t>
+  </si>
+  <si>
+    <t>2023-06-08T12:03:00</t>
+  </si>
+  <si>
+    <t>2023-06-08T14:09:00</t>
+  </si>
+  <si>
+    <t>2023-06-08T15:40:00</t>
+  </si>
+  <si>
+    <t>2302181869653</t>
+  </si>
+  <si>
+    <t>AISCAS</t>
+  </si>
+  <si>
+    <t>2302181869713</t>
+  </si>
+  <si>
+    <t>AISCFT</t>
+  </si>
+  <si>
+    <t>2302181869714</t>
+  </si>
+  <si>
+    <t>AISCG0</t>
+  </si>
+  <si>
+    <t>2302181869715</t>
+  </si>
+  <si>
+    <t>AISCHD</t>
+  </si>
+  <si>
+    <t>2302181869716</t>
+  </si>
+  <si>
+    <t>AISCKP</t>
+  </si>
+  <si>
+    <t>2302181869717</t>
+  </si>
+  <si>
+    <t>AISCQA</t>
+  </si>
+  <si>
+    <t>2302181869718</t>
+  </si>
+  <si>
+    <t>AISCUB</t>
+  </si>
+  <si>
+    <t>AISCVB</t>
+  </si>
+  <si>
+    <t>AISCY0</t>
+  </si>
+  <si>
+    <t>AISCZL</t>
+  </si>
+  <si>
+    <t>AISCZQ</t>
+  </si>
+  <si>
+    <t>AISCZ0</t>
+  </si>
+  <si>
+    <t>2302181869719</t>
+  </si>
+  <si>
+    <t>AISCZ4</t>
+  </si>
+  <si>
+    <t>AISC0X</t>
+  </si>
+  <si>
+    <t>2302181869720</t>
+  </si>
+  <si>
+    <t>AISC15</t>
+  </si>
+  <si>
+    <t>AISC2A</t>
+  </si>
+  <si>
+    <t>AISC2B</t>
+  </si>
+  <si>
+    <t>2302181869721</t>
+  </si>
+  <si>
+    <t>AISC2H</t>
+  </si>
+  <si>
+    <t>2302181869722</t>
+  </si>
+  <si>
+    <t>AISC3D</t>
+  </si>
+  <si>
+    <t>2302181869723</t>
+  </si>
+  <si>
+    <t>AISC3T</t>
+  </si>
+  <si>
+    <t>AISC3Z</t>
+  </si>
+  <si>
+    <t>2302181869724</t>
+  </si>
+  <si>
+    <t>9C754478CMCMRPCT073803E992</t>
+  </si>
+  <si>
+    <t>F87B0BF4CMCMRPCT07FAAA301D</t>
+  </si>
+  <si>
+    <t>AISDCT</t>
+  </si>
+  <si>
+    <t>AISDC1</t>
+  </si>
+  <si>
+    <t>2302181869727</t>
   </si>
 </sst>
 </file>
@@ -2711,36 +2456,36 @@
         <v>16</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>596</v>
+        <v>473</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>323</v>
+        <v>274</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>324</v>
+        <v>275</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>323</v>
+        <v>274</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>324</v>
+        <v>275</v>
       </c>
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
       <c r="O2" s="3" t="s">
-        <v>597</v>
+        <v>474</v>
       </c>
       <c r="P2" s="24"/>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B3" s="3">
         <v>4</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>13</v>
@@ -2752,41 +2497,41 @@
         <v>15</v>
       </c>
       <c r="G3" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="N3" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="O3" s="3"/>
     </row>
     <row r="14" spans="1:16">
       <c r="G14" s="1"/>
       <c r="H14" s="3" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:16">
       <c r="G15" s="5"/>
       <c r="H15" s="3" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -2815,10 +2560,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="40" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="E1" s="40" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F1" s="40" t="s">
         <v>1</v>
@@ -2827,22 +2572,22 @@
         <v>2</v>
       </c>
       <c r="H1" s="40" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="I1" s="40" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="J1" s="40" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="K1" s="54" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="L1" s="54" t="s">
-        <v>275</v>
+        <v>243</v>
       </c>
       <c r="M1" s="40" t="s">
-        <v>358</v>
+        <v>306</v>
       </c>
       <c r="N1" s="32" t="s">
         <v>8</v>
@@ -2854,52 +2599,52 @@
         <v>10</v>
       </c>
       <c r="Q1" s="36" t="s">
-        <v>361</v>
+        <v>309</v>
       </c>
       <c r="R1" s="47" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="S1" s="46" t="s">
-        <v>369</v>
+        <v>313</v>
       </c>
       <c r="T1" s="47" t="s">
-        <v>396</v>
+        <v>322</v>
       </c>
       <c r="U1" s="47" t="s">
-        <v>397</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" spans="1:21">
       <c r="A2" s="53" t="s">
-        <v>332</v>
+        <v>282</v>
       </c>
       <c r="B2" s="48">
         <v>1</v>
       </c>
       <c r="C2" s="50" t="s">
-        <v>353</v>
+        <v>303</v>
       </c>
       <c r="D2" s="48" t="s">
         <v>13</v>
       </c>
       <c r="E2" s="48" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F2" s="48">
         <v>2</v>
       </c>
       <c r="G2" s="50" t="s">
-        <v>354</v>
+        <v>304</v>
       </c>
       <c r="H2" s="48" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="I2" s="48" t="s">
         <v>13</v>
       </c>
       <c r="J2" s="48"/>
       <c r="K2" s="48" t="s">
-        <v>355</v>
+        <v>305</v>
       </c>
       <c r="L2" s="48"/>
       <c r="M2" s="48"/>
@@ -2914,19 +2659,19 @@
     </row>
     <row r="3" spans="1:21">
       <c r="A3" s="53" t="s">
-        <v>333</v>
+        <v>283</v>
       </c>
       <c r="B3" s="48">
         <v>1</v>
       </c>
       <c r="C3" s="50" t="s">
-        <v>353</v>
+        <v>303</v>
       </c>
       <c r="D3" s="48" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="48" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F3" s="48"/>
       <c r="G3" s="50"/>
@@ -2936,10 +2681,10 @@
         <v>0</v>
       </c>
       <c r="K3" s="48" t="s">
-        <v>621</v>
+        <v>546</v>
       </c>
       <c r="L3" s="48" t="s">
-        <v>622</v>
+        <v>547</v>
       </c>
       <c r="M3" s="48"/>
       <c r="N3" s="48"/>
@@ -2953,7 +2698,7 @@
     </row>
     <row r="4" spans="1:21">
       <c r="A4" s="53" t="s">
-        <v>334</v>
+        <v>284</v>
       </c>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
@@ -2967,7 +2712,7 @@
       <c r="K4" s="48"/>
       <c r="L4" s="48"/>
       <c r="M4" s="48" t="s">
-        <v>359</v>
+        <v>307</v>
       </c>
       <c r="N4" s="48"/>
       <c r="O4" s="48"/>
@@ -2980,19 +2725,19 @@
     </row>
     <row r="5" spans="1:21">
       <c r="A5" s="53" t="s">
-        <v>335</v>
+        <v>285</v>
       </c>
       <c r="B5" s="48">
         <v>1</v>
       </c>
       <c r="C5" s="50" t="s">
-        <v>353</v>
+        <v>303</v>
       </c>
       <c r="D5" s="48" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="48" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F5" s="48"/>
       <c r="G5" s="48"/>
@@ -3000,46 +2745,46 @@
       <c r="I5" s="48"/>
       <c r="J5" s="48"/>
       <c r="K5" s="48" t="s">
-        <v>624</v>
+        <v>549</v>
       </c>
       <c r="L5" s="48" t="s">
-        <v>625</v>
+        <v>550</v>
       </c>
       <c r="M5" s="48"/>
       <c r="N5" s="48" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O5" s="48" t="s">
-        <v>360</v>
+        <v>308</v>
       </c>
       <c r="P5" s="48" t="s">
-        <v>400</v>
+        <v>325</v>
       </c>
       <c r="Q5" s="37"/>
       <c r="R5" s="48"/>
       <c r="S5" s="48"/>
       <c r="T5" s="48" t="s">
-        <v>398</v>
+        <v>324</v>
       </c>
       <c r="U5" s="48" t="s">
-        <v>360</v>
+        <v>308</v>
       </c>
     </row>
     <row r="6" spans="1:21">
       <c r="A6" s="53" t="s">
-        <v>336</v>
+        <v>286</v>
       </c>
       <c r="B6" s="48">
         <v>1</v>
       </c>
       <c r="C6" s="50" t="s">
-        <v>353</v>
+        <v>303</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="48" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F6" s="48"/>
       <c r="G6" s="48"/>
@@ -3047,44 +2792,44 @@
       <c r="I6" s="48"/>
       <c r="J6" s="48"/>
       <c r="K6" s="48" t="s">
-        <v>626</v>
+        <v>551</v>
       </c>
       <c r="L6" s="48"/>
       <c r="M6" s="48"/>
       <c r="N6" s="48" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O6" s="48" t="s">
-        <v>360</v>
+        <v>308</v>
       </c>
       <c r="P6" s="48" t="s">
-        <v>627</v>
+        <v>552</v>
       </c>
       <c r="Q6" s="37"/>
       <c r="R6" s="48"/>
       <c r="S6" s="48"/>
       <c r="T6" s="48" t="s">
-        <v>398</v>
+        <v>324</v>
       </c>
       <c r="U6" s="48" t="s">
-        <v>360</v>
+        <v>308</v>
       </c>
     </row>
     <row r="7" spans="1:21">
       <c r="A7" s="53" t="s">
-        <v>337</v>
+        <v>287</v>
       </c>
       <c r="B7" s="48">
         <v>1</v>
       </c>
       <c r="C7" s="50" t="s">
-        <v>353</v>
+        <v>303</v>
       </c>
       <c r="D7" s="48" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="48" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F7" s="48"/>
       <c r="G7" s="48"/>
@@ -3092,26 +2837,26 @@
       <c r="I7" s="48"/>
       <c r="J7" s="48"/>
       <c r="K7" s="48" t="s">
-        <v>628</v>
+        <v>553</v>
       </c>
       <c r="L7" s="48" t="s">
-        <v>629</v>
+        <v>554</v>
       </c>
       <c r="M7" s="48"/>
       <c r="N7" s="48" t="s">
-        <v>362</v>
+        <v>310</v>
       </c>
       <c r="O7" s="48" t="s">
-        <v>360</v>
+        <v>308</v>
       </c>
       <c r="P7" s="48" t="s">
-        <v>630</v>
+        <v>555</v>
       </c>
       <c r="Q7" s="55" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="R7" s="48" t="s">
-        <v>631</v>
+        <v>556</v>
       </c>
       <c r="S7" s="48"/>
       <c r="T7" s="48"/>
@@ -3119,45 +2864,45 @@
     </row>
     <row r="8" spans="1:21">
       <c r="A8" s="53" t="s">
-        <v>338</v>
+        <v>288</v>
       </c>
       <c r="B8" s="48">
         <v>1</v>
       </c>
       <c r="C8" s="50" t="s">
-        <v>353</v>
+        <v>303</v>
       </c>
       <c r="D8" s="48" t="s">
         <v>13</v>
       </c>
       <c r="E8" s="48" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F8" s="48">
         <v>2</v>
       </c>
       <c r="G8" s="50" t="s">
-        <v>354</v>
+        <v>304</v>
       </c>
       <c r="H8" s="48" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="I8" s="48" t="s">
         <v>13</v>
       </c>
       <c r="J8" s="48"/>
       <c r="K8" s="48" t="s">
-        <v>632</v>
+        <v>557</v>
       </c>
       <c r="L8" s="48" t="s">
-        <v>633</v>
+        <v>558</v>
       </c>
       <c r="M8" s="48"/>
       <c r="N8" s="48" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O8" s="48" t="s">
-        <v>364</v>
+        <v>311</v>
       </c>
       <c r="P8" s="48"/>
       <c r="Q8" s="37"/>
@@ -3168,19 +2913,19 @@
     </row>
     <row r="9" spans="1:21">
       <c r="A9" s="53" t="s">
-        <v>339</v>
+        <v>289</v>
       </c>
       <c r="B9" s="48">
         <v>1</v>
       </c>
       <c r="C9" s="50" t="s">
-        <v>353</v>
+        <v>303</v>
       </c>
       <c r="D9" s="48" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="48" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F9" s="48"/>
       <c r="G9" s="48"/>
@@ -3188,15 +2933,15 @@
       <c r="I9" s="48"/>
       <c r="J9" s="48"/>
       <c r="K9" s="48" t="s">
-        <v>634</v>
+        <v>559</v>
       </c>
       <c r="L9" s="48"/>
       <c r="M9" s="48"/>
       <c r="N9" s="48" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O9" s="48" t="s">
-        <v>367</v>
+        <v>312</v>
       </c>
       <c r="P9" s="48"/>
       <c r="Q9" s="37"/>
@@ -3207,19 +2952,19 @@
     </row>
     <row r="10" spans="1:21">
       <c r="A10" s="53" t="s">
-        <v>340</v>
+        <v>290</v>
       </c>
       <c r="B10" s="48">
         <v>1</v>
       </c>
       <c r="C10" s="50" t="s">
-        <v>353</v>
+        <v>303</v>
       </c>
       <c r="D10" s="48" t="s">
         <v>13</v>
       </c>
       <c r="E10" s="48" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F10" s="48"/>
       <c r="G10" s="48"/>
@@ -3227,10 +2972,10 @@
       <c r="I10" s="48"/>
       <c r="J10" s="48"/>
       <c r="K10" s="48" t="s">
-        <v>635</v>
+        <v>560</v>
       </c>
       <c r="L10" s="48" t="s">
-        <v>636</v>
+        <v>561</v>
       </c>
       <c r="M10" s="48"/>
       <c r="N10" s="48"/>
@@ -3239,26 +2984,26 @@
       <c r="Q10" s="37"/>
       <c r="R10" s="48"/>
       <c r="S10" s="50" t="s">
-        <v>370</v>
+        <v>314</v>
       </c>
       <c r="T10" s="48"/>
       <c r="U10" s="48"/>
     </row>
     <row r="11" spans="1:21">
       <c r="A11" s="53" t="s">
-        <v>341</v>
+        <v>291</v>
       </c>
       <c r="B11" s="48">
         <v>1</v>
       </c>
       <c r="C11" s="50" t="s">
-        <v>353</v>
+        <v>303</v>
       </c>
       <c r="D11" s="48" t="s">
         <v>13</v>
       </c>
       <c r="E11" s="48" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F11" s="48"/>
       <c r="G11" s="48"/>
@@ -3266,10 +3011,10 @@
       <c r="I11" s="48"/>
       <c r="J11" s="48"/>
       <c r="K11" s="48" t="s">
-        <v>608</v>
+        <v>533</v>
       </c>
       <c r="L11" s="48" t="s">
-        <v>609</v>
+        <v>534</v>
       </c>
       <c r="M11" s="48"/>
       <c r="N11" s="48"/>
@@ -3278,26 +3023,26 @@
       <c r="Q11" s="37"/>
       <c r="R11" s="48"/>
       <c r="S11" s="50" t="s">
-        <v>370</v>
+        <v>314</v>
       </c>
       <c r="T11" s="48"/>
       <c r="U11" s="48"/>
     </row>
     <row r="12" spans="1:21">
       <c r="A12" s="53" t="s">
-        <v>342</v>
+        <v>292</v>
       </c>
       <c r="B12" s="48">
         <v>1</v>
       </c>
       <c r="C12" s="50" t="s">
-        <v>353</v>
+        <v>303</v>
       </c>
       <c r="D12" s="48" t="s">
         <v>13</v>
       </c>
       <c r="E12" s="48" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F12" s="48"/>
       <c r="G12" s="48"/>
@@ -3305,21 +3050,21 @@
       <c r="I12" s="48"/>
       <c r="J12" s="48"/>
       <c r="K12" s="48" t="s">
-        <v>610</v>
+        <v>535</v>
       </c>
       <c r="L12" s="48" t="s">
-        <v>611</v>
+        <v>536</v>
       </c>
       <c r="M12" s="48"/>
       <c r="N12" s="48" t="s">
-        <v>362</v>
+        <v>310</v>
       </c>
       <c r="O12" s="48" t="s">
-        <v>374</v>
+        <v>315</v>
       </c>
       <c r="P12" s="48"/>
       <c r="Q12" s="55" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="R12" s="48"/>
       <c r="S12" s="48"/>
@@ -3328,19 +3073,19 @@
     </row>
     <row r="13" spans="1:21">
       <c r="A13" s="53" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
       <c r="B13" s="48">
         <v>1</v>
       </c>
       <c r="C13" s="50" t="s">
-        <v>353</v>
+        <v>303</v>
       </c>
       <c r="D13" s="48" t="s">
         <v>13</v>
       </c>
       <c r="E13" s="48" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F13" s="48"/>
       <c r="G13" s="48"/>
@@ -3348,42 +3093,42 @@
       <c r="I13" s="48"/>
       <c r="J13" s="48"/>
       <c r="K13" s="48" t="s">
-        <v>612</v>
+        <v>537</v>
       </c>
       <c r="L13" s="48" t="s">
-        <v>613</v>
+        <v>538</v>
       </c>
       <c r="M13" s="48"/>
       <c r="N13" s="48" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O13" s="48" t="s">
-        <v>360</v>
+        <v>308</v>
       </c>
       <c r="P13" s="48"/>
       <c r="Q13" s="37"/>
       <c r="R13" s="48"/>
       <c r="S13" s="50" t="s">
-        <v>370</v>
+        <v>314</v>
       </c>
       <c r="T13" s="48"/>
       <c r="U13" s="48"/>
     </row>
     <row r="14" spans="1:21">
       <c r="A14" s="53" t="s">
-        <v>344</v>
+        <v>294</v>
       </c>
       <c r="B14" s="48">
         <v>1</v>
       </c>
       <c r="C14" s="50" t="s">
-        <v>353</v>
+        <v>303</v>
       </c>
       <c r="D14" s="48" t="s">
         <v>13</v>
       </c>
       <c r="E14" s="48" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F14" s="48"/>
       <c r="G14" s="48"/>
@@ -3399,26 +3144,26 @@
       <c r="Q14" s="37"/>
       <c r="R14" s="48"/>
       <c r="S14" s="50" t="s">
-        <v>384</v>
+        <v>316</v>
       </c>
       <c r="T14" s="48"/>
       <c r="U14" s="48"/>
     </row>
     <row r="15" spans="1:21">
       <c r="A15" s="53" t="s">
-        <v>345</v>
+        <v>295</v>
       </c>
       <c r="B15" s="48">
         <v>1</v>
       </c>
       <c r="C15" s="50" t="s">
-        <v>353</v>
+        <v>303</v>
       </c>
       <c r="D15" s="48" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="48" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F15" s="48"/>
       <c r="G15" s="48"/>
@@ -3426,42 +3171,42 @@
       <c r="I15" s="48"/>
       <c r="J15" s="48"/>
       <c r="K15" s="48" t="s">
-        <v>614</v>
+        <v>539</v>
       </c>
       <c r="L15" s="48" t="s">
-        <v>615</v>
+        <v>540</v>
       </c>
       <c r="M15" s="48"/>
       <c r="N15" s="48" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O15" s="48" t="s">
-        <v>360</v>
+        <v>308</v>
       </c>
       <c r="P15" s="48"/>
       <c r="Q15" s="37"/>
       <c r="R15" s="48"/>
       <c r="S15" s="50" t="s">
-        <v>370</v>
+        <v>314</v>
       </c>
       <c r="T15" s="48"/>
       <c r="U15" s="48"/>
     </row>
     <row r="16" spans="1:21">
       <c r="A16" s="53" t="s">
-        <v>346</v>
+        <v>296</v>
       </c>
       <c r="B16" s="48">
         <v>1</v>
       </c>
       <c r="C16" s="50" t="s">
-        <v>353</v>
+        <v>303</v>
       </c>
       <c r="D16" s="48" t="s">
         <v>13</v>
       </c>
       <c r="E16" s="48" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F16" s="48"/>
       <c r="G16" s="48"/>
@@ -3469,15 +3214,15 @@
       <c r="I16" s="48"/>
       <c r="J16" s="48"/>
       <c r="K16" s="48" t="s">
-        <v>616</v>
+        <v>541</v>
       </c>
       <c r="L16" s="48"/>
       <c r="M16" s="48"/>
       <c r="N16" s="48" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O16" s="48" t="s">
-        <v>387</v>
+        <v>317</v>
       </c>
       <c r="P16" s="48"/>
       <c r="Q16" s="37"/>
@@ -3488,19 +3233,19 @@
     </row>
     <row r="17" spans="1:21">
       <c r="A17" s="53" t="s">
-        <v>347</v>
+        <v>297</v>
       </c>
       <c r="B17" s="48">
         <v>1</v>
       </c>
       <c r="C17" s="50" t="s">
-        <v>353</v>
+        <v>303</v>
       </c>
       <c r="D17" s="48" t="s">
         <v>13</v>
       </c>
       <c r="E17" s="48" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F17" s="48"/>
       <c r="G17" s="48"/>
@@ -3508,7 +3253,7 @@
       <c r="I17" s="48"/>
       <c r="J17" s="48"/>
       <c r="K17" s="48" t="s">
-        <v>617</v>
+        <v>542</v>
       </c>
       <c r="L17" s="48"/>
       <c r="M17" s="48"/>
@@ -3523,43 +3268,43 @@
     </row>
     <row r="18" spans="1:21">
       <c r="A18" s="53" t="s">
-        <v>348</v>
+        <v>298</v>
       </c>
       <c r="B18" s="48">
         <v>1</v>
       </c>
       <c r="C18" s="50" t="s">
-        <v>353</v>
+        <v>303</v>
       </c>
       <c r="D18" s="48" t="s">
         <v>13</v>
       </c>
       <c r="E18" s="48" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F18" s="48">
         <v>2</v>
       </c>
       <c r="G18" s="50" t="s">
-        <v>354</v>
+        <v>304</v>
       </c>
       <c r="H18" s="48" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="I18" s="48" t="s">
         <v>13</v>
       </c>
       <c r="J18" s="48"/>
       <c r="K18" s="48" t="s">
-        <v>618</v>
+        <v>543</v>
       </c>
       <c r="L18" s="48"/>
       <c r="M18" s="48"/>
       <c r="N18" s="48" t="s">
-        <v>390</v>
+        <v>318</v>
       </c>
       <c r="O18" s="48" t="s">
-        <v>391</v>
+        <v>319</v>
       </c>
       <c r="P18" s="48"/>
       <c r="Q18" s="37"/>
@@ -3570,19 +3315,19 @@
     </row>
     <row r="19" spans="1:21">
       <c r="A19" s="53" t="s">
-        <v>349</v>
+        <v>299</v>
       </c>
       <c r="B19" s="48">
         <v>1</v>
       </c>
       <c r="C19" s="50" t="s">
-        <v>353</v>
+        <v>303</v>
       </c>
       <c r="D19" s="48" t="s">
         <v>13</v>
       </c>
       <c r="E19" s="48" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F19" s="48"/>
       <c r="G19" s="48"/>
@@ -3590,15 +3335,15 @@
       <c r="I19" s="48"/>
       <c r="J19" s="48"/>
       <c r="K19" s="48" t="s">
-        <v>619</v>
+        <v>544</v>
       </c>
       <c r="L19" s="48"/>
       <c r="M19" s="48"/>
       <c r="N19" s="48" t="s">
-        <v>393</v>
+        <v>320</v>
       </c>
       <c r="O19" s="48" t="s">
-        <v>394</v>
+        <v>321</v>
       </c>
       <c r="P19" s="48"/>
       <c r="Q19" s="37"/>
@@ -3609,19 +3354,19 @@
     </row>
     <row r="20" spans="1:21">
       <c r="A20" s="53" t="s">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="B20" s="48">
         <v>1</v>
       </c>
       <c r="C20" s="50" t="s">
-        <v>353</v>
+        <v>303</v>
       </c>
       <c r="D20" s="48" t="s">
         <v>13</v>
       </c>
       <c r="E20" s="48" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F20" s="48"/>
       <c r="G20" s="48"/>
@@ -3629,15 +3374,15 @@
       <c r="I20" s="48"/>
       <c r="J20" s="48"/>
       <c r="K20" s="48" t="s">
-        <v>620</v>
+        <v>545</v>
       </c>
       <c r="L20" s="48"/>
       <c r="M20" s="48"/>
       <c r="N20" s="48" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O20" s="48" t="s">
-        <v>360</v>
+        <v>308</v>
       </c>
       <c r="P20" s="48"/>
       <c r="Q20" s="37"/>
@@ -3648,19 +3393,19 @@
     </row>
     <row r="21" spans="1:21">
       <c r="A21" s="53" t="s">
-        <v>351</v>
+        <v>301</v>
       </c>
       <c r="B21" s="48">
         <v>1</v>
       </c>
       <c r="C21" s="50" t="s">
-        <v>403</v>
+        <v>326</v>
       </c>
       <c r="D21" s="48" t="s">
         <v>13</v>
       </c>
       <c r="E21" s="48" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="F21" s="48"/>
       <c r="G21" s="48"/>
@@ -3668,15 +3413,15 @@
       <c r="I21" s="48"/>
       <c r="J21" s="48"/>
       <c r="K21" s="48" t="s">
-        <v>623</v>
+        <v>548</v>
       </c>
       <c r="L21" s="48"/>
       <c r="M21" s="48"/>
       <c r="N21" s="48" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O21" s="48" t="s">
-        <v>360</v>
+        <v>308</v>
       </c>
       <c r="P21" s="48"/>
       <c r="Q21" s="37"/>
@@ -3687,19 +3432,19 @@
     </row>
     <row r="22" spans="1:21">
       <c r="A22" s="53" t="s">
-        <v>352</v>
+        <v>302</v>
       </c>
       <c r="B22" s="48">
         <v>1</v>
       </c>
       <c r="C22" s="50" t="s">
-        <v>353</v>
+        <v>303</v>
       </c>
       <c r="D22" s="48" t="s">
         <v>13</v>
       </c>
       <c r="E22" s="48" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F22" s="48"/>
       <c r="G22" s="48"/>
@@ -3744,22 +3489,22 @@
         <v>1</v>
       </c>
       <c r="C1" s="58" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D1" s="59" t="s">
-        <v>406</v>
+        <v>327</v>
       </c>
       <c r="E1" s="59" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="F1" s="58" t="s">
-        <v>407</v>
+        <v>328</v>
       </c>
       <c r="G1" s="63"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="63" t="s">
-        <v>408</v>
+        <v>329</v>
       </c>
       <c r="B2" s="60">
         <v>2</v>
@@ -3768,17 +3513,17 @@
         <v>2</v>
       </c>
       <c r="D2" s="62" t="s">
-        <v>581</v>
+        <v>396</v>
       </c>
       <c r="E2" s="62" t="s">
-        <v>580</v>
+        <v>395</v>
       </c>
       <c r="F2" s="60"/>
       <c r="G2" s="63"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="60" t="s">
-        <v>411</v>
+        <v>330</v>
       </c>
       <c r="B3" s="60">
         <v>2</v>
@@ -3787,19 +3532,19 @@
         <v>2</v>
       </c>
       <c r="D3" s="62" t="s">
-        <v>637</v>
+        <v>562</v>
       </c>
       <c r="E3" s="62" t="s">
-        <v>413</v>
+        <v>331</v>
       </c>
       <c r="F3" s="60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="G3" s="63"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="60" t="s">
-        <v>414</v>
+        <v>332</v>
       </c>
       <c r="B4" s="60">
         <v>2</v>
@@ -3808,11 +3553,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="62" t="s">
-        <v>638</v>
+        <v>563</v>
       </c>
       <c r="E4" s="60"/>
       <c r="F4" s="60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="G4" s="63"/>
     </row>
@@ -3843,36 +3588,36 @@
         <v>0</v>
       </c>
       <c r="B1" s="58" t="s">
-        <v>421</v>
+        <v>338</v>
       </c>
       <c r="C1" s="58" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="58" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E1" s="58" t="s">
-        <v>322</v>
+        <v>273</v>
       </c>
       <c r="F1" s="60"/>
       <c r="G1" s="60"/>
       <c r="H1" s="60"/>
       <c r="I1" s="59" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="J1" s="59" t="s">
-        <v>456</v>
+        <v>373</v>
       </c>
       <c r="K1" s="59" t="s">
-        <v>457</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="60" t="s">
-        <v>458</v>
+        <v>375</v>
       </c>
       <c r="B2" s="60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C2" s="60"/>
       <c r="D2" s="60"/>
@@ -3886,10 +3631,10 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="60" t="s">
-        <v>459</v>
+        <v>376</v>
       </c>
       <c r="B3" s="60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C3" s="60"/>
       <c r="D3" s="60"/>
@@ -3903,10 +3648,10 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="60" t="s">
-        <v>460</v>
+        <v>377</v>
       </c>
       <c r="B4" s="60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C4" s="60"/>
       <c r="D4" s="60"/>
@@ -3920,7 +3665,7 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="60" t="s">
-        <v>461</v>
+        <v>378</v>
       </c>
       <c r="B5" s="60"/>
       <c r="C5" s="62">
@@ -3936,18 +3681,18 @@
       <c r="G5" s="60"/>
       <c r="H5" s="60"/>
       <c r="I5" s="60" t="s">
-        <v>462</v>
+        <v>379</v>
       </c>
       <c r="J5" s="60" t="s">
-        <v>463</v>
+        <v>380</v>
       </c>
       <c r="K5" s="60" t="s">
-        <v>464</v>
+        <v>381</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="60" t="s">
-        <v>465</v>
+        <v>382</v>
       </c>
       <c r="B6" s="60"/>
       <c r="C6" s="60">
@@ -3989,27 +3734,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="58" t="s">
-        <v>322</v>
+        <v>273</v>
       </c>
       <c r="C1" s="58" t="s">
-        <v>416</v>
+        <v>333</v>
       </c>
       <c r="D1" s="58" t="s">
-        <v>417</v>
+        <v>334</v>
       </c>
       <c r="E1" s="58" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="62" t="s">
-        <v>418</v>
+        <v>335</v>
       </c>
       <c r="B2" s="62">
         <v>1</v>
       </c>
       <c r="C2" s="60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="D2" s="60">
         <v>1</v>
@@ -4018,13 +3763,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="62" t="s">
-        <v>419</v>
+        <v>336</v>
       </c>
       <c r="B3" s="60">
         <v>1</v>
       </c>
       <c r="C3" s="60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="D3" s="60"/>
       <c r="E3" s="60">
@@ -4033,13 +3778,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="62" t="s">
-        <v>420</v>
+        <v>337</v>
       </c>
       <c r="B4" s="60">
         <v>1</v>
       </c>
       <c r="C4" s="60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="D4" s="60"/>
       <c r="E4" s="60">
@@ -4086,10 +3831,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>1</v>
@@ -4098,13 +3843,13 @@
         <v>2</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="J1" s="32" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="K1" s="32" t="s">
         <v>1</v>
@@ -4113,7 +3858,7 @@
         <v>2</v>
       </c>
       <c r="M1" s="32" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="N1" s="32" t="s">
         <v>3</v>
@@ -4128,7 +3873,7 @@
         <v>2</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="S1" s="2" t="s">
         <v>3</v>
@@ -4163,13 +3908,13 @@
     </row>
     <row r="2" spans="1:28">
       <c r="A2" s="7" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="B2" s="18">
         <v>1</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>13</v>
@@ -4181,7 +3926,7 @@
         <v>5</v>
       </c>
       <c r="G2" s="18" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>14</v>
@@ -4190,31 +3935,31 @@
         <v>13</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="S2" s="3" t="s">
         <v>14</v>
@@ -4233,13 +3978,13 @@
     </row>
     <row r="3" spans="1:28">
       <c r="A3" s="7" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B3" s="18">
         <v>1</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>264</v>
+        <v>237</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>13</v>
@@ -4251,7 +3996,7 @@
         <v>5</v>
       </c>
       <c r="G3" s="18" t="s">
-        <v>265</v>
+        <v>238</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>14</v>
@@ -4260,16 +4005,16 @@
         <v>13</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>584</v>
+        <v>397</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>516</v>
+        <v>383</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>264</v>
+        <v>237</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>517</v>
+        <v>384</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>13</v>
@@ -4278,13 +4023,13 @@
         <v>14</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>518</v>
+        <v>385</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>265</v>
+        <v>238</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>519</v>
+        <v>386</v>
       </c>
       <c r="S3" s="3" t="s">
         <v>14</v>
@@ -4296,7 +4041,7 @@
         <v>6</v>
       </c>
       <c r="V3" s="18" t="s">
-        <v>264</v>
+        <v>237</v>
       </c>
       <c r="W3" s="3" t="s">
         <v>13</v>
@@ -4308,7 +4053,7 @@
         <v>7</v>
       </c>
       <c r="Z3" s="18" t="s">
-        <v>265</v>
+        <v>238</v>
       </c>
       <c r="AA3" s="3" t="s">
         <v>14</v>
@@ -4319,13 +4064,13 @@
     </row>
     <row r="4" spans="1:28">
       <c r="A4" s="28" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="B4" s="18">
         <v>1</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>13</v>
@@ -4338,16 +4083,16 @@
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="N4" s="3" t="s">
         <v>13</v>
@@ -4371,13 +4116,13 @@
     </row>
     <row r="5" spans="1:28">
       <c r="A5" s="28" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="B5" s="18">
         <v>3</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>13</v>
@@ -4390,16 +4135,16 @@
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>585</v>
+        <v>440</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>521</v>
+        <v>441</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>522</v>
+        <v>442</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>13</v>
@@ -4423,13 +4168,13 @@
     </row>
     <row r="6" spans="1:28">
       <c r="A6" s="28" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="B6" s="18">
         <v>1</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>13</v>
@@ -4441,21 +4186,21 @@
         <v>5</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="N6" s="3" t="s">
         <v>13</v>
@@ -4505,21 +4250,21 @@
         <v>2</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="7" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="B2" s="30" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C2" s="31">
         <v>1</v>
@@ -4531,10 +4276,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="29" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C3" s="31">
         <v>1</v>
@@ -4543,15 +4288,15 @@
         <v>13</v>
       </c>
       <c r="E3" s="18" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="7" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C4" s="31">
         <v>1</v>
@@ -4560,7 +4305,7 @@
         <v>13</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -4587,13 +4332,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="58" t="s">
-        <v>421</v>
+        <v>338</v>
       </c>
       <c r="C1" s="58" t="s">
-        <v>422</v>
+        <v>339</v>
       </c>
       <c r="D1" s="58" t="s">
-        <v>423</v>
+        <v>340</v>
       </c>
       <c r="E1" s="58" t="s">
         <v>1</v>
@@ -4601,10 +4346,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="60" t="s">
-        <v>424</v>
+        <v>341</v>
       </c>
       <c r="B2" s="60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C2" s="60"/>
       <c r="D2" s="60"/>
@@ -4612,10 +4357,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="60" t="s">
-        <v>425</v>
+        <v>342</v>
       </c>
       <c r="B3" s="60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C3" s="60"/>
       <c r="D3" s="60"/>
@@ -4623,10 +4368,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="60" t="s">
-        <v>426</v>
+        <v>343</v>
       </c>
       <c r="B4" s="60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C4" s="60"/>
       <c r="D4" s="60"/>
@@ -4634,10 +4379,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="60" t="s">
-        <v>427</v>
+        <v>344</v>
       </c>
       <c r="B5" s="60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C5" s="60"/>
       <c r="D5" s="60"/>
@@ -4645,10 +4390,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="60" t="s">
-        <v>428</v>
+        <v>345</v>
       </c>
       <c r="B6" s="60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C6" s="60"/>
       <c r="D6" s="60"/>
@@ -4656,10 +4401,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="60" t="s">
-        <v>429</v>
+        <v>346</v>
       </c>
       <c r="B7" s="60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C7" s="60"/>
       <c r="D7" s="60"/>
@@ -4667,10 +4412,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="60" t="s">
-        <v>430</v>
+        <v>347</v>
       </c>
       <c r="B8" s="60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C8" s="60"/>
       <c r="D8" s="60"/>
@@ -4678,25 +4423,25 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="60" t="s">
-        <v>431</v>
+        <v>348</v>
       </c>
       <c r="B9" s="60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C9" s="62" t="s">
-        <v>432</v>
+        <v>349</v>
       </c>
       <c r="D9" s="56" t="s">
-        <v>433</v>
+        <v>350</v>
       </c>
       <c r="E9" s="60"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="60" t="s">
-        <v>434</v>
+        <v>351</v>
       </c>
       <c r="B10" s="60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C10" s="60"/>
       <c r="D10" s="60"/>
@@ -4704,10 +4449,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="60" t="s">
-        <v>435</v>
+        <v>352</v>
       </c>
       <c r="B11" s="60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C11" s="60"/>
       <c r="D11" s="60"/>
@@ -4715,10 +4460,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="60" t="s">
-        <v>436</v>
+        <v>353</v>
       </c>
       <c r="B12" s="60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C12" s="60"/>
       <c r="D12" s="60"/>
@@ -4726,10 +4471,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="60" t="s">
-        <v>437</v>
+        <v>354</v>
       </c>
       <c r="B13" s="60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C13" s="60"/>
       <c r="D13" s="60"/>
@@ -4737,10 +4482,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="60" t="s">
-        <v>438</v>
+        <v>355</v>
       </c>
       <c r="B14" s="60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C14" s="60"/>
       <c r="D14" s="60"/>
@@ -4750,10 +4495,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="60" t="s">
-        <v>439</v>
+        <v>356</v>
       </c>
       <c r="B15" s="60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C15" s="60"/>
       <c r="D15" s="60"/>
@@ -4780,23 +4525,23 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="34" t="s">
-        <v>262</v>
+        <v>235</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>263</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="34" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -4821,7 +4566,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -4835,16 +4580,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="34" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>13</v>
@@ -4868,21 +4613,21 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="41" t="s">
-        <v>259</v>
+        <v>232</v>
       </c>
       <c r="B2" s="48">
         <v>3</v>
       </c>
       <c r="C2" s="48" t="s">
-        <v>313</v>
+        <v>266</v>
       </c>
       <c r="D2" s="48" t="s">
         <v>13</v>
@@ -4890,13 +4635,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="41" t="s">
-        <v>260</v>
+        <v>233</v>
       </c>
       <c r="B3" s="48">
         <v>3</v>
       </c>
       <c r="C3" s="48" t="s">
-        <v>313</v>
+        <v>266</v>
       </c>
       <c r="D3" s="48" t="s">
         <v>13</v>
@@ -4904,13 +4649,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="41" t="s">
-        <v>261</v>
+        <v>234</v>
       </c>
       <c r="B4" s="48">
         <v>0</v>
       </c>
       <c r="C4" s="48" t="s">
-        <v>313</v>
+        <v>266</v>
       </c>
       <c r="D4" s="48" t="s">
         <v>13</v>
@@ -4993,111 +4738,111 @@
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="J1" s="12" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L1" s="12" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="M1" s="12" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N1" s="9" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="P1" s="9" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="Q1" s="9" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="R1" s="12" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="S1" s="11" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="T1" s="12" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="U1" s="12" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="V1" s="9" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="W1" s="8" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="X1" s="9" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="Y1" s="9" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="Z1" s="12" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="AA1" s="11" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AB1" s="12" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="AC1" s="12" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="AD1" s="9" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="AE1" s="8" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AF1" s="9" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="AG1" s="9" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:33">
       <c r="A2" s="7" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B2" s="22">
         <v>1</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D2" s="13"/>
       <c r="E2" s="13"/>
@@ -5132,19 +4877,19 @@
     </row>
     <row r="3" spans="1:33">
       <c r="A3" s="7" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B3" s="22">
         <v>-9</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F3" s="10"/>
       <c r="G3" s="10"/>
@@ -5177,39 +4922,39 @@
     </row>
     <row r="4" spans="1:33">
       <c r="A4" s="7" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B4" s="22">
         <v>1</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F4" s="10">
         <f>B4</f>
         <v>1</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H4" s="10" t="s">
         <v>13</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="J4" s="13">
         <f>B4</f>
         <v>1</v>
       </c>
       <c r="K4" s="19" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="L4" s="13" t="s">
         <v>13</v>
@@ -5222,65 +4967,65 @@
         <v>1</v>
       </c>
       <c r="O4" s="21" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="P4" s="10" t="s">
         <v>13</v>
       </c>
       <c r="Q4" s="10" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="R4" s="13">
         <f>B4</f>
         <v>1</v>
       </c>
       <c r="S4" s="19" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="T4" s="13" t="s">
         <v>13</v>
       </c>
       <c r="U4" s="13" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="V4" s="10">
         <f>B4</f>
         <v>1</v>
       </c>
       <c r="W4" s="21" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="X4" s="10" t="s">
         <v>13</v>
       </c>
       <c r="Y4" s="10" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="Z4" s="13">
         <f>B4</f>
         <v>1</v>
       </c>
       <c r="AA4" s="19" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="AB4" s="13" t="s">
         <v>13</v>
       </c>
       <c r="AC4" s="13" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AD4" s="10">
         <f>B4</f>
         <v>1</v>
       </c>
       <c r="AE4" s="21" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="AF4" s="10" t="s">
         <v>13</v>
       </c>
       <c r="AG4" s="10" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -5308,13 +5053,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>2</v>
@@ -5329,7 +5074,7 @@
         <v>1</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>1</v>
@@ -5338,7 +5083,7 @@
         <v>2</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>3</v>
@@ -5347,7 +5092,7 @@
         <v>4</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>2</v>
@@ -5362,7 +5107,7 @@
         <v>1</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="W1" s="1" t="s">
         <v>2</v>
@@ -5391,19 +5136,19 @@
     </row>
     <row r="2" spans="1:30">
       <c r="A2" s="14" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F2" s="3">
         <v>0</v>
@@ -5413,22 +5158,22 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3" t="s">
-        <v>639</v>
+        <v>510</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>640</v>
+        <v>511</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>641</v>
+        <v>512</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="Q2" s="3"/>
       <c r="R2" s="3"/>
@@ -5447,16 +5192,16 @@
     </row>
     <row r="3" spans="1:30">
       <c r="A3" s="14" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="B3" s="3">
         <v>1</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>244</v>
+        <v>222</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>13</v>
@@ -5465,41 +5210,41 @@
         <v>0</v>
       </c>
       <c r="G3" s="18" t="s">
-        <v>245</v>
+        <v>223</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="J3" s="3">
         <v>2</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>642</v>
+        <v>564</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>527</v>
+        <v>387</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>244</v>
+        <v>222</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>528</v>
+        <v>388</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="P3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="Q3" s="3"/>
       <c r="R3" s="18" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="T3" s="3" t="s">
         <v>13</v>
@@ -5509,22 +5254,22 @@
       </c>
       <c r="V3" s="3"/>
       <c r="W3" s="18" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="X3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="Y3" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="Z3">
         <v>4</v>
       </c>
       <c r="AA3" s="18" t="s">
-        <v>246</v>
+        <v>224</v>
       </c>
       <c r="AB3" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="AC3" s="3" t="s">
         <v>13</v>
@@ -5535,7 +5280,7 @@
     </row>
     <row r="4" spans="1:30">
       <c r="A4" s="14" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="B4" s="3">
         <v>1</v>
@@ -5571,64 +5316,64 @@
     </row>
     <row r="5" spans="1:30">
       <c r="A5" s="14" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F5" s="3">
         <v>0</v>
       </c>
       <c r="G5" s="18" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="J5" s="3">
         <v>5</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>643</v>
+        <v>514</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>640</v>
+        <v>511</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>641</v>
+        <v>512</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>644</v>
+        <v>515</v>
       </c>
       <c r="R5" s="18" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="S5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="U5">
         <v>1</v>
@@ -5637,25 +5382,25 @@
         <v>1</v>
       </c>
       <c r="W5" s="18" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="X5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="Y5" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="Z5">
         <v>1</v>
       </c>
       <c r="AA5" s="18" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="AB5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="AC5" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="AD5">
         <v>1</v>
@@ -5663,19 +5408,19 @@
     </row>
     <row r="6" spans="1:30">
       <c r="A6" s="14" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F6" s="3">
         <v>0</v>
@@ -5707,19 +5452,19 @@
     </row>
     <row r="7" spans="1:30">
       <c r="A7" s="14" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F7" s="3">
         <v>0</v>
@@ -5751,7 +5496,7 @@
     </row>
     <row r="8" spans="1:30">
       <c r="A8" s="14" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -5787,19 +5532,19 @@
     </row>
     <row r="9" spans="1:30">
       <c r="A9" s="14" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F9" s="3">
         <v>0</v>
@@ -5809,22 +5554,22 @@
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3" t="s">
-        <v>647</v>
+        <v>518</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>640</v>
+        <v>511</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>641</v>
+        <v>512</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
@@ -5872,24 +5617,24 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="34" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="E2" s="3">
         <v>1</v>
@@ -5897,16 +5642,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="34" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="E3" s="3">
         <v>1</v>
@@ -5914,16 +5659,16 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="34" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="E4" s="3">
         <v>1</v>
@@ -5948,39 +5693,39 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="34" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -6008,13 +5753,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>2</v>
@@ -6065,7 +5810,7 @@
         <v>1</v>
       </c>
       <c r="W1" s="2" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="X1" s="2" t="s">
         <v>1</v>
@@ -6074,7 +5819,7 @@
         <v>2</v>
       </c>
       <c r="Z1" s="2" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="AA1" s="2" t="s">
         <v>3</v>
@@ -6083,24 +5828,24 @@
         <v>4</v>
       </c>
       <c r="AC1" s="2" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2" spans="1:29">
       <c r="A2" s="3" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F2" s="3">
         <v>0</v>
@@ -6122,36 +5867,36 @@
       <c r="U2" s="3"/>
       <c r="V2" s="3"/>
       <c r="W2" s="3" t="s">
-        <v>648</v>
+        <v>519</v>
       </c>
       <c r="X2" s="3" t="s">
-        <v>640</v>
+        <v>511</v>
       </c>
       <c r="Y2" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="Z2" s="3" t="s">
-        <v>641</v>
+        <v>512</v>
       </c>
       <c r="AA2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="AC2" s="3" t="s">
-        <v>649</v>
+        <v>520</v>
       </c>
     </row>
     <row r="3" spans="1:29">
       <c r="A3" s="3" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="B3" s="3">
         <v>2</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>252</v>
+        <v>225</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>14</v>
@@ -6163,22 +5908,22 @@
         <v>0</v>
       </c>
       <c r="G3" s="18" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="J3" s="18">
         <v>3</v>
       </c>
       <c r="K3" s="18" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>13</v>
@@ -6187,7 +5932,7 @@
         <v>4</v>
       </c>
       <c r="O3" s="18" t="s">
-        <v>253</v>
+        <v>226</v>
       </c>
       <c r="P3" s="3" t="s">
         <v>13</v>
@@ -6203,7 +5948,7 @@
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
       <c r="W3" s="3" t="s">
-        <v>254</v>
+        <v>227</v>
       </c>
       <c r="X3" s="3"/>
       <c r="Y3" s="3"/>
@@ -6211,24 +5956,24 @@
       <c r="AA3" s="3"/>
       <c r="AB3" s="3"/>
       <c r="AC3" s="3" t="s">
-        <v>255</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4" spans="1:29">
       <c r="A4" s="3" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="B4" s="3">
         <v>1</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F4" s="3">
         <v>0</v>
@@ -6250,25 +5995,25 @@
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="s">
-        <v>650</v>
+        <v>521</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>640</v>
+        <v>511</v>
       </c>
       <c r="Y4" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="Z4" s="3" t="s">
-        <v>641</v>
+        <v>512</v>
       </c>
       <c r="AA4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="AB4" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="AC4" s="3" t="s">
-        <v>651</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
@@ -6299,36 +6044,36 @@
         <v>0</v>
       </c>
       <c r="B1" s="36" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="34" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -6340,10 +6085,10 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="3" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="B3" s="37" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -6355,10 +6100,10 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="3" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="B4" s="37" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -6370,37 +6115,37 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="3" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="3" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -6454,13 +6199,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="40" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="E1" s="40" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F1" s="38" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="G1" s="40" t="s">
         <v>2</v>
@@ -6475,7 +6220,7 @@
         <v>1</v>
       </c>
       <c r="K1" s="32" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="L1" s="32" t="s">
         <v>1</v>
@@ -6484,7 +6229,7 @@
         <v>2</v>
       </c>
       <c r="N1" s="32" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="O1" s="32" t="s">
         <v>3</v>
@@ -6493,21 +6238,21 @@
         <v>4</v>
       </c>
       <c r="Q1" s="32" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="R1" s="32" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="28" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="B2" s="18">
         <v>1</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>13</v>
@@ -6523,16 +6268,16 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>13</v>
@@ -6545,13 +6290,13 @@
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="28" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="B3" s="18">
         <v>7</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>13</v>
@@ -6567,16 +6312,16 @@
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3" t="s">
-        <v>306</v>
+        <v>259</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>307</v>
+        <v>260</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>308</v>
+        <v>261</v>
       </c>
       <c r="O3" s="3" t="s">
         <v>13</v>
@@ -6585,21 +6330,21 @@
         <v>14</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>309</v>
+        <v>262</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>310</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="28" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="B4" s="18">
         <v>1</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>13</v>
@@ -6611,13 +6356,13 @@
         <v>0</v>
       </c>
       <c r="G4" s="18" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="J4" s="3">
         <v>2</v>
@@ -6633,13 +6378,13 @@
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="28" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="B5" s="18">
         <v>1</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>13</v>
@@ -6665,13 +6410,13 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="28" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="B6" s="18">
         <v>1</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>13</v>
@@ -6717,10 +6462,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="40" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="E1" s="40" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F1" s="40" t="s">
         <v>1</v>
@@ -6729,13 +6474,13 @@
         <v>2</v>
       </c>
       <c r="H1" s="40" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="I1" s="40" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="J1" s="32" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="K1" s="32" t="s">
         <v>1</v>
@@ -6744,7 +6489,7 @@
         <v>2</v>
       </c>
       <c r="M1" s="32" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="N1" s="32" t="s">
         <v>3</v>
@@ -6759,7 +6504,7 @@
         <v>2</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="S1" s="2" t="s">
         <v>3</v>
@@ -6768,137 +6513,137 @@
         <v>4</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2" spans="1:21">
       <c r="A2" s="28" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="B2" s="50">
         <v>1</v>
       </c>
       <c r="C2" s="48" t="s">
-        <v>328</v>
+        <v>278</v>
       </c>
       <c r="D2" s="48" t="s">
         <v>13</v>
       </c>
       <c r="E2" s="48" t="s">
-        <v>329</v>
+        <v>279</v>
       </c>
       <c r="F2" s="50">
         <v>1</v>
       </c>
       <c r="G2" s="48" t="s">
-        <v>330</v>
+        <v>280</v>
       </c>
       <c r="H2" s="48" t="s">
-        <v>329</v>
+        <v>279</v>
       </c>
       <c r="I2" s="48" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>592</v>
+        <v>565</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>539</v>
+        <v>524</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>328</v>
+        <v>278</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>540</v>
+        <v>525</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>329</v>
+        <v>279</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>541</v>
+        <v>526</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>330</v>
+        <v>280</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>329</v>
+        <v>279</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>593</v>
+        <v>566</v>
       </c>
     </row>
     <row r="3" spans="1:21">
       <c r="A3" s="28" t="s">
-        <v>258</v>
+        <v>231</v>
       </c>
       <c r="B3" s="50">
         <v>1</v>
       </c>
       <c r="C3" s="48" t="s">
-        <v>328</v>
+        <v>278</v>
       </c>
       <c r="D3" s="48" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="48" t="s">
-        <v>329</v>
+        <v>279</v>
       </c>
       <c r="F3" s="50">
         <v>1</v>
       </c>
       <c r="G3" s="48" t="s">
-        <v>331</v>
+        <v>281</v>
       </c>
       <c r="H3" s="48" t="s">
-        <v>329</v>
+        <v>279</v>
       </c>
       <c r="I3" s="48" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>320</v>
+        <v>271</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>315</v>
+        <v>267</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>316</v>
+        <v>268</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>317</v>
+        <v>269</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>318</v>
+        <v>270</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>321</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:21">
@@ -6906,25 +6651,25 @@
         <v>1</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="F8" s="18">
         <v>4</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9" spans="1:21">
@@ -6932,25 +6677,25 @@
         <v>1</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="F9" s="18">
         <v>4</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12" spans="1:21">
@@ -6958,10 +6703,10 @@
         <v>1</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>311</v>
+        <v>264</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>312</v>
+        <v>265</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>13</v>
@@ -6970,13 +6715,13 @@
         <v>1</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:21">
@@ -6984,10 +6729,10 @@
         <v>1</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>311</v>
+        <v>264</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>312</v>
+        <v>265</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>13</v>
@@ -6996,13 +6741,13 @@
         <v>1</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -7027,31 +6772,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>256</v>
+        <v>229</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>257</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="3" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -7069,24 +6814,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -7094,17 +6839,17 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="B3" s="33"/>
       <c r="C3" s="3" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -7127,24 +6872,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="58" t="s">
-        <v>421</v>
+        <v>338</v>
       </c>
       <c r="C1" s="60" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="D1" s="60" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="E1" s="60" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="60" t="s">
-        <v>440</v>
+        <v>357</v>
       </c>
       <c r="B2" s="60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C2" s="60"/>
       <c r="D2" s="60"/>
@@ -7152,10 +6897,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="60" t="s">
-        <v>441</v>
+        <v>358</v>
       </c>
       <c r="B3" s="60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C3" s="60"/>
       <c r="D3" s="60"/>
@@ -7163,10 +6908,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="60" t="s">
-        <v>442</v>
+        <v>359</v>
       </c>
       <c r="B4" s="60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C4" s="60"/>
       <c r="D4" s="60"/>
@@ -7174,10 +6919,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="60" t="s">
-        <v>443</v>
+        <v>360</v>
       </c>
       <c r="B5" s="60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C5" s="60"/>
       <c r="D5" s="60"/>
@@ -7185,10 +6930,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="60" t="s">
-        <v>444</v>
+        <v>361</v>
       </c>
       <c r="B6" s="60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C6" s="60"/>
       <c r="D6" s="60"/>
@@ -7196,10 +6941,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="60" t="s">
-        <v>445</v>
+        <v>362</v>
       </c>
       <c r="B7" s="60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C7" s="60"/>
       <c r="D7" s="60"/>
@@ -7207,10 +6952,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="60" t="s">
-        <v>446</v>
+        <v>363</v>
       </c>
       <c r="B8" s="60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C8" s="60"/>
       <c r="D8" s="60"/>
@@ -7218,10 +6963,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="60" t="s">
-        <v>447</v>
+        <v>364</v>
       </c>
       <c r="B9" s="60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C9" s="60"/>
       <c r="D9" s="60"/>
@@ -7229,10 +6974,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="60" t="s">
-        <v>448</v>
+        <v>365</v>
       </c>
       <c r="B10" s="60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C10" s="60"/>
       <c r="D10" s="60"/>
@@ -7240,10 +6985,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="60" t="s">
-        <v>449</v>
+        <v>366</v>
       </c>
       <c r="B11" s="60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C11" s="60"/>
       <c r="D11" s="60"/>
@@ -7251,10 +6996,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="60" t="s">
-        <v>450</v>
+        <v>367</v>
       </c>
       <c r="B12" s="60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C12" s="60"/>
       <c r="D12" s="60"/>
@@ -7262,10 +7007,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="60" t="s">
-        <v>451</v>
+        <v>368</v>
       </c>
       <c r="B13" s="60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C13" s="60"/>
       <c r="D13" s="60"/>
@@ -7273,10 +7018,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="60" t="s">
-        <v>452</v>
+        <v>369</v>
       </c>
       <c r="B14" s="60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C14" s="60"/>
       <c r="D14" s="60"/>
@@ -7284,10 +7029,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="60" t="s">
-        <v>453</v>
+        <v>370</v>
       </c>
       <c r="B15" s="60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C15" s="60"/>
       <c r="D15" s="60"/>
@@ -7295,10 +7040,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="60" t="s">
-        <v>454</v>
+        <v>371</v>
       </c>
       <c r="B16" s="60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C16" s="60"/>
       <c r="D16" s="60"/>
@@ -7306,10 +7051,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="60" t="s">
-        <v>455</v>
+        <v>372</v>
       </c>
       <c r="B17" s="60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C17" s="60"/>
       <c r="D17" s="60"/>
@@ -7364,12 +7109,12 @@
         <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="25" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B2" s="26">
         <v>2</v>
@@ -7387,18 +7132,18 @@
         <v>15</v>
       </c>
       <c r="G2" s="27" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H2" s="26" t="s">
-        <v>600</v>
+        <v>406</v>
       </c>
       <c r="I2" s="26" t="s">
-        <v>601</v>
+        <v>407</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="28" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B3" s="3">
         <v>2</v>
@@ -7413,10 +7158,10 @@
         <v>14</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G3" s="18" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
@@ -7475,7 +7220,7 @@
         <v>1</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>1</v>
@@ -7484,15 +7229,15 @@
         <v>2</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="3" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>13</v>
@@ -7512,10 +7257,10 @@
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="3" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>13</v>
@@ -7535,13 +7280,13 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>13</v>
@@ -7550,13 +7295,13 @@
         <v>1</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="I4" s="3">
         <v>2</v>
@@ -7568,10 +7313,10 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>13</v>
@@ -7596,302 +7341,140 @@
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C03B3B8-DBFD-430F-BAEF-858DA603C137}">
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" style="57" width="17.90625"/>
+    <col min="2" max="2" customWidth="true" style="57" width="11.81640625"/>
+    <col min="3" max="3" customWidth="true" style="57" width="13.0"/>
+    <col min="4" max="4" customWidth="true" style="57" width="16.54296875"/>
+    <col min="5" max="5" customWidth="true" style="57" width="15.81640625"/>
+    <col min="6" max="6" style="57" width="8.7265625"/>
+    <col min="7" max="7" customWidth="true" style="57" width="17.81640625"/>
+    <col min="8" max="8" customWidth="true" style="57" width="15.453125"/>
+    <col min="9" max="9" customWidth="true" style="57" width="11.54296875"/>
+    <col min="10" max="16384" style="57" width="8.7265625"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:22">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:11">
+      <c r="A1" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="61" t="s">
+        <v>454</v>
+      </c>
+      <c r="C1" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="61" t="s">
+        <v>184</v>
+      </c>
+      <c r="F1" s="61" t="s">
+        <v>98</v>
+      </c>
+      <c r="G1" s="61" t="s">
+        <v>455</v>
+      </c>
+      <c r="H1" s="61" t="s">
+        <v>456</v>
+      </c>
+      <c r="I1" s="61" t="s">
+        <v>457</v>
+      </c>
+      <c r="J1" s="61" t="s">
+        <v>458</v>
+      </c>
+      <c r="K1" s="61" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="60" t="s">
+        <v>460</v>
+      </c>
+      <c r="B2" s="60" t="s">
+        <v>194</v>
+      </c>
+      <c r="C2" s="60">
+        <v>1</v>
+      </c>
+      <c r="D2" s="60">
+        <v>1</v>
+      </c>
+      <c r="E2" s="60">
+        <v>1</v>
+      </c>
+      <c r="F2" s="60" t="s">
+        <v>468</v>
+      </c>
+      <c r="G2" s="60">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="T1" s="1" t="s">
+      <c r="H2" s="62" t="s">
+        <v>50</v>
+      </c>
+      <c r="I2" s="62" t="s">
+        <v>223</v>
+      </c>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="60" t="s">
+        <v>462</v>
+      </c>
+      <c r="B3" s="60" t="s">
         <v>194</v>
       </c>
-      <c r="U1" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22">
-      <c r="A2" s="41" t="s">
-        <v>297</v>
-      </c>
-      <c r="B2" s="3">
-        <v>1</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F2" s="3">
-        <v>2</v>
-      </c>
-      <c r="G2" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="3">
-        <v>1</v>
-      </c>
-      <c r="K2" s="3"/>
-      <c r="L2" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="O2" s="3">
-        <v>2</v>
-      </c>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="T2" s="3">
-        <v>0</v>
-      </c>
-      <c r="U2" s="3"/>
-      <c r="V2" s="3"/>
-    </row>
-    <row r="3" spans="1:22">
-      <c r="A3" s="41" t="s">
-        <v>298</v>
-      </c>
-      <c r="B3" s="3">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3">
-        <v>1</v>
-      </c>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
-    </row>
-    <row r="4" spans="1:22">
-      <c r="A4" s="41" t="s">
-        <v>299</v>
-      </c>
-      <c r="B4" s="3">
-        <v>1</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F4" s="3">
-        <v>2</v>
-      </c>
-      <c r="G4" s="18" t="s">
-        <v>300</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="J4" s="3">
-        <v>1</v>
-      </c>
-      <c r="K4" s="3">
-        <v>1</v>
-      </c>
-      <c r="L4" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="O4" s="3">
-        <v>3</v>
-      </c>
-      <c r="P4" s="3">
-        <v>3</v>
-      </c>
-      <c r="Q4" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="R4" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="T4" s="3">
-        <v>0</v>
-      </c>
-      <c r="U4" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="V4" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22">
-      <c r="A8" s="41" t="s">
-        <v>299</v>
-      </c>
-      <c r="B8" s="3">
-        <v>1</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F8" s="3">
-        <v>3</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>303</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J8" s="3">
-        <v>1</v>
-      </c>
-      <c r="K8" s="3">
-        <v>1</v>
-      </c>
-      <c r="L8" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="O8" s="3">
-        <v>5</v>
-      </c>
-      <c r="P8" s="3">
-        <v>5</v>
-      </c>
-      <c r="Q8" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="T8" s="3">
-        <v>0</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>302</v>
-      </c>
+      <c r="C3" s="60">
+        <v>1</v>
+      </c>
+      <c r="D3" s="60">
+        <v>1</v>
+      </c>
+      <c r="E3" s="60">
+        <v>1</v>
+      </c>
+      <c r="F3" s="60" t="s">
+        <v>469</v>
+      </c>
+      <c r="G3" s="60"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="62" t="s">
+        <v>464</v>
+      </c>
+      <c r="K3" s="60" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="60" t="s">
+        <v>466</v>
+      </c>
+      <c r="B4" s="60" t="s">
+        <v>194</v>
+      </c>
+      <c r="C4" s="60">
+        <v>1</v>
+      </c>
+      <c r="D4" s="60">
+        <v>1</v>
+      </c>
+      <c r="E4" s="60">
+        <v>1</v>
+      </c>
+      <c r="F4" s="60" t="s">
+        <v>470</v>
+      </c>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="60"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7918,50 +7501,50 @@
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="7" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B2" s="7">
         <v>1</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="7" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B3" s="7">
         <v>1</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -7990,99 +7573,99 @@
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="16" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B2" s="16">
         <v>2</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D2" s="14" t="s">
         <v>13</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="16" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B3" s="16">
         <v>1</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="16" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B4" s="16">
         <v>1</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D4" s="14" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="16" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B5" s="16">
         <v>1</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D5" s="14" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="16" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B6" s="16">
         <v>1</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D6" s="14" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -8164,7 +7747,7 @@
         <v>10</v>
       </c>
       <c r="P1" s="47" t="s">
-        <v>322</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -8193,27 +7776,27 @@
       <c r="I2" s="48"/>
       <c r="J2" s="48"/>
       <c r="K2" s="52" t="s">
-        <v>323</v>
+        <v>274</v>
       </c>
       <c r="L2" s="52" t="s">
-        <v>324</v>
+        <v>275</v>
       </c>
       <c r="M2" s="48"/>
       <c r="N2" s="48"/>
       <c r="O2" s="48" t="s">
-        <v>603</v>
+        <v>408</v>
       </c>
       <c r="P2" s="48"/>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="49" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B3" s="48">
         <v>2</v>
       </c>
       <c r="C3" s="50" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D3" s="48" t="s">
         <v>13</v>
@@ -8225,7 +7808,7 @@
         <v>15</v>
       </c>
       <c r="G3" s="50" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H3" s="48"/>
       <c r="I3" s="48"/>
@@ -8239,13 +7822,13 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="52" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
       <c r="B4" s="48">
         <v>2</v>
       </c>
       <c r="C4" s="50" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D4" s="48" t="s">
         <v>13</v>
@@ -8265,13 +7848,13 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="52" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
       <c r="B5" s="48">
         <v>2</v>
       </c>
       <c r="C5" s="50" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D5" s="48" t="s">
         <v>13</v>
@@ -8283,10 +7866,10 @@
       <c r="I5" s="48"/>
       <c r="J5" s="48"/>
       <c r="K5" s="52" t="s">
-        <v>323</v>
+        <v>274</v>
       </c>
       <c r="L5" s="52" t="s">
-        <v>324</v>
+        <v>275</v>
       </c>
       <c r="M5" s="48"/>
       <c r="N5" s="48"/>
@@ -8341,10 +7924,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E1" s="15" t="s">
         <v>4</v>
@@ -8359,10 +7942,10 @@
         <v>1</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="J1" s="15" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="K1" s="15" t="s">
         <v>4</v>
@@ -8377,10 +7960,10 @@
         <v>1</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="P1" s="15" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="Q1" s="15" t="s">
         <v>4</v>
@@ -8395,10 +7978,10 @@
         <v>1</v>
       </c>
       <c r="U1" s="6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="V1" s="15" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="W1" s="15" t="s">
         <v>4</v>
@@ -8410,36 +7993,36 @@
         <v>9</v>
       </c>
       <c r="Z1" s="6" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="AA1" s="6" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AB1" s="6" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:28">
       <c r="A2" s="7" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B2" s="23">
         <v>2</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H2" s="23"/>
       <c r="I2" s="21"/>
@@ -8471,73 +8054,73 @@
     </row>
     <row r="3" spans="1:28">
       <c r="A3" s="7" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B3" s="23">
         <v>11</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="H3" s="23">
         <v>11</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="J3" s="10" t="s">
         <v>13</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N3" s="23">
         <v>11</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="P3" s="10" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="Q3" s="10" t="s">
         <v>13</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="T3" s="23">
         <v>11</v>
       </c>
       <c r="U3" s="21" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="V3" s="10" t="s">
         <v>13</v>
       </c>
       <c r="W3" s="10" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="X3" s="3"/>
       <c r="Y3" s="3"/>
@@ -8548,78 +8131,78 @@
         <v>9</v>
       </c>
       <c r="AB3" s="17" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:28">
       <c r="A4" s="7" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="B4" s="23">
         <v>11</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="H4" s="23">
         <v>11</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="J4" s="10" t="s">
         <v>13</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N4" s="23">
         <v>11</v>
       </c>
       <c r="O4" s="21" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="P4" s="10" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="Q4" s="10" t="s">
         <v>13</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="T4" s="23">
         <v>11</v>
       </c>
       <c r="U4" s="21" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="V4" s="10" t="s">
         <v>13</v>
       </c>
       <c r="W4" s="10" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
@@ -8630,18 +8213,18 @@
         <v>9</v>
       </c>
       <c r="AB4" s="17" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:28">
       <c r="A5" s="42" t="s">
-        <v>271</v>
+        <v>239</v>
       </c>
       <c r="B5" s="18">
         <v>1</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>264</v>
+        <v>237</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>13</v>
@@ -8652,13 +8235,13 @@
     </row>
     <row r="6" spans="1:28">
       <c r="A6" s="42" t="s">
-        <v>272</v>
+        <v>240</v>
       </c>
       <c r="B6" s="18">
         <v>1</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>264</v>
+        <v>237</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>13</v>
@@ -8669,13 +8252,13 @@
     </row>
     <row r="7" spans="1:28">
       <c r="A7" s="42" t="s">
-        <v>273</v>
+        <v>241</v>
       </c>
       <c r="B7" s="18">
         <v>1</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>264</v>
+        <v>237</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>13</v>
@@ -8710,10 +8293,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E1" s="15" t="s">
         <v>4</v>
@@ -8722,10 +8305,10 @@
         <v>1</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H1" s="15" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="I1" s="15" t="s">
         <v>4</v>
@@ -8734,10 +8317,10 @@
         <v>1</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L1" s="15" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="M1" s="15" t="s">
         <v>4</v>
@@ -8746,42 +8329,42 @@
         <v>1</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="P1" s="15" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="Q1" s="15" t="s">
         <v>4</v>
       </c>
       <c r="R1" s="43" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="S1" s="43" t="s">
-        <v>275</v>
+        <v>243</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>290</v>
+        <v>254</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:23">
       <c r="A2" s="7" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B2" s="23">
         <v>1</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>14</v>
@@ -8802,10 +8385,10 @@
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
       <c r="R2" s="3" t="s">
-        <v>604</v>
+        <v>529</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>605</v>
+        <v>530</v>
       </c>
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
@@ -8814,13 +8397,13 @@
     </row>
     <row r="3" spans="1:23">
       <c r="A3" s="7" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B3" s="23">
         <v>1</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>14</v>
@@ -8832,22 +8415,22 @@
         <v>2</v>
       </c>
       <c r="G3" s="18" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="J3" s="3">
         <v>3</v>
       </c>
       <c r="K3" s="18" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>13</v>
@@ -8856,7 +8439,7 @@
         <v>4</v>
       </c>
       <c r="O3" s="18" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="P3" s="3" t="s">
         <v>13</v>
@@ -8873,13 +8456,13 @@
     </row>
     <row r="4" spans="1:23">
       <c r="A4" s="7" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="B4" s="23">
         <v>1</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>14</v>
@@ -8891,22 +8474,22 @@
         <v>2</v>
       </c>
       <c r="G4" s="18" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="J4" s="3">
         <v>3</v>
       </c>
       <c r="K4" s="18" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>13</v>
@@ -8915,7 +8498,7 @@
         <v>4</v>
       </c>
       <c r="O4" s="18" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="P4" s="3" t="s">
         <v>13</v>
@@ -8932,13 +8515,13 @@
     </row>
     <row r="5" spans="1:23">
       <c r="A5" s="44" t="s">
-        <v>271</v>
+        <v>239</v>
       </c>
       <c r="B5" s="18">
         <v>1</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>264</v>
+        <v>237</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>13</v>
@@ -8967,13 +8550,13 @@
     </row>
     <row r="6" spans="1:23">
       <c r="A6" s="44" t="s">
-        <v>272</v>
+        <v>240</v>
       </c>
       <c r="B6" s="18">
         <v>1</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>264</v>
+        <v>237</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>13</v>
@@ -9002,13 +8585,13 @@
     </row>
     <row r="7" spans="1:23">
       <c r="A7" s="44" t="s">
-        <v>273</v>
+        <v>241</v>
       </c>
       <c r="B7" s="18">
         <v>1</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>264</v>
+        <v>237</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>13</v>
@@ -9037,13 +8620,13 @@
     </row>
     <row r="8" spans="1:23">
       <c r="A8" s="44" t="s">
-        <v>278</v>
+        <v>244</v>
       </c>
       <c r="B8" s="23">
         <v>1</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>14</v>
@@ -9064,10 +8647,10 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3" t="s">
-        <v>606</v>
+        <v>531</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>607</v>
+        <v>532</v>
       </c>
       <c r="T8" s="3">
         <v>0</v>
@@ -9078,13 +8661,13 @@
     </row>
     <row r="9" spans="1:23">
       <c r="A9" s="44" t="s">
-        <v>279</v>
+        <v>245</v>
       </c>
       <c r="B9" s="23">
         <v>1</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>13</v>
@@ -9096,7 +8679,7 @@
         <v>2</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>14</v>
@@ -9113,10 +8696,10 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3" t="s">
-        <v>291</v>
+        <v>255</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>292</v>
+        <v>256</v>
       </c>
       <c r="T9" s="3"/>
       <c r="U9" s="3">
@@ -9131,13 +8714,13 @@
     </row>
     <row r="10" spans="1:23">
       <c r="A10" s="44" t="s">
-        <v>280</v>
+        <v>246</v>
       </c>
       <c r="B10" s="23">
         <v>1</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>13</v>
@@ -9149,7 +8732,7 @@
         <v>2</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>14</v>
@@ -9166,10 +8749,10 @@
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3" t="s">
-        <v>293</v>
+        <v>257</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>294</v>
+        <v>258</v>
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
@@ -9178,19 +8761,19 @@
     </row>
     <row r="11" spans="1:23">
       <c r="A11" s="44" t="s">
-        <v>281</v>
+        <v>247</v>
       </c>
       <c r="B11" s="23">
         <v>1</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
@@ -9215,19 +8798,19 @@
     </row>
     <row r="12" spans="1:23">
       <c r="A12" s="44" t="s">
-        <v>282</v>
+        <v>248</v>
       </c>
       <c r="B12" s="23">
         <v>1</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
@@ -9250,19 +8833,19 @@
     </row>
     <row r="13" spans="1:23">
       <c r="A13" s="44" t="s">
-        <v>283</v>
+        <v>249</v>
       </c>
       <c r="B13" s="23">
         <v>1</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
@@ -9287,19 +8870,19 @@
     </row>
     <row r="14" spans="1:23">
       <c r="A14" s="44" t="s">
-        <v>284</v>
+        <v>250</v>
       </c>
       <c r="B14" s="23">
         <v>1</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
@@ -9322,19 +8905,19 @@
     </row>
     <row r="15" spans="1:23">
       <c r="A15" s="44" t="s">
-        <v>285</v>
+        <v>251</v>
       </c>
       <c r="B15" s="23">
         <v>1</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
@@ -9357,28 +8940,28 @@
     </row>
     <row r="16" spans="1:23">
       <c r="A16" s="44" t="s">
-        <v>286</v>
+        <v>252</v>
       </c>
       <c r="B16" s="23">
         <v>1</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D16" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F16" s="3">
         <v>2</v>
       </c>
       <c r="G16" s="18" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>13</v>
@@ -9392,10 +8975,10 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3" t="s">
-        <v>556</v>
+        <v>393</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>557</v>
+        <v>394</v>
       </c>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
@@ -9404,19 +8987,19 @@
     </row>
     <row r="17" spans="1:23">
       <c r="A17" s="44" t="s">
-        <v>287</v>
+        <v>253</v>
       </c>
       <c r="B17" s="23">
         <v>1</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D17" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
@@ -9473,16 +9056,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -9503,7 +9086,7 @@
         <v>4</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>1</v>
@@ -9512,7 +9095,7 @@
         <v>2</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="R1" s="2" t="s">
         <v>3</v>
@@ -9523,13 +9106,13 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="34" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="B2" s="3">
         <v>2</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>13</v>
@@ -9552,19 +9135,19 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="34" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="B3" s="3">
         <v>2</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="18" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="F3" s="18"/>
       <c r="G3" s="18"/>
@@ -9583,16 +9166,16 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="34" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B4" s="3">
         <v>2</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -9612,20 +9195,20 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="34" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -9643,13 +9226,13 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" s="34" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>13</v>
@@ -9660,70 +9243,70 @@
     </row>
     <row r="7" spans="1:19">
       <c r="A7" s="34" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="G7" s="3"/>
     </row>
     <row r="8" spans="1:19">
       <c r="A8" s="34" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="G8" s="3"/>
     </row>
     <row r="9" spans="1:19">
       <c r="A9" s="34" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="G9" s="3"/>
     </row>
     <row r="10" spans="1:19">
       <c r="A10" s="34" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>13</v>
@@ -9731,18 +9314,18 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="18" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:19">
       <c r="A11" s="35" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>13</v>
@@ -9750,18 +9333,18 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="18" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:19">
       <c r="A12" s="34" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="B12" s="26">
         <v>0</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D12" s="26" t="s">
         <v>13</v>
@@ -9769,7 +9352,7 @@
     </row>
     <row r="13" spans="1:19">
       <c r="A13" s="34" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -9780,13 +9363,13 @@
     </row>
     <row r="14" spans="1:19">
       <c r="A14" s="34" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>13</v>
@@ -9797,13 +9380,13 @@
     </row>
     <row r="15" spans="1:19">
       <c r="A15" s="34" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>13</v>
@@ -9814,13 +9397,13 @@
     </row>
     <row r="16" spans="1:19">
       <c r="A16" s="34" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="B16" s="26">
         <v>0</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D16" s="26" t="s">
         <v>13</v>
@@ -9831,13 +9414,13 @@
     </row>
     <row r="17" spans="1:19">
       <c r="A17" s="34" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="B17" s="26">
         <v>0</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D17" s="26" t="s">
         <v>13</v>
@@ -9848,20 +9431,20 @@
     </row>
     <row r="20" spans="1:19">
       <c r="A20" s="34" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="B20" s="3">
         <v>1</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>13</v>
@@ -9870,28 +9453,28 @@
         <v>2</v>
       </c>
       <c r="K20" s="18" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>13</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>13</v>

--- a/src/test/java/TestData/Scenario_TestData.xlsx
+++ b/src/test/java/TestData/Scenario_TestData.xlsx
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1619" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1721" uniqueCount="614">
   <si>
     <t>Scenario</t>
   </si>
@@ -1767,6 +1767,147 @@
   </si>
   <si>
     <t>2302181869727</t>
+  </si>
+  <si>
+    <t>AWMGIE</t>
+  </si>
+  <si>
+    <t>2023-06-29T07:55:00</t>
+  </si>
+  <si>
+    <t>2023-06-29T09:29:00</t>
+  </si>
+  <si>
+    <t>2302181931004</t>
+  </si>
+  <si>
+    <t>AWMGI1</t>
+  </si>
+  <si>
+    <t>2302181931005</t>
+  </si>
+  <si>
+    <t>ACR3YZ</t>
+  </si>
+  <si>
+    <t>2302181955113</t>
+  </si>
+  <si>
+    <t>ACR3ZE</t>
+  </si>
+  <si>
+    <t>2302181955114</t>
+  </si>
+  <si>
+    <t>ACR4MQ</t>
+  </si>
+  <si>
+    <t>2302181955115</t>
+  </si>
+  <si>
+    <t>ACR4WT</t>
+  </si>
+  <si>
+    <t>2302181955116</t>
+  </si>
+  <si>
+    <t>ACR5AG</t>
+  </si>
+  <si>
+    <t>ACR5AJ</t>
+  </si>
+  <si>
+    <t>ACR5AK</t>
+  </si>
+  <si>
+    <t>ACR5AM</t>
+  </si>
+  <si>
+    <t>ACR5CF</t>
+  </si>
+  <si>
+    <t>ACR5CL</t>
+  </si>
+  <si>
+    <t>2302181955117</t>
+  </si>
+  <si>
+    <t>ACR5C4</t>
+  </si>
+  <si>
+    <t>ACR5EH</t>
+  </si>
+  <si>
+    <t>2302181955118</t>
+  </si>
+  <si>
+    <t>ACR5FY</t>
+  </si>
+  <si>
+    <t>ACR5FZ</t>
+  </si>
+  <si>
+    <t>ACR5F0</t>
+  </si>
+  <si>
+    <t>2302181955119</t>
+  </si>
+  <si>
+    <t>ACR5GD</t>
+  </si>
+  <si>
+    <t>2302181955120</t>
+  </si>
+  <si>
+    <t>ACR5GO</t>
+  </si>
+  <si>
+    <t>2302181955121</t>
+  </si>
+  <si>
+    <t>ACR5HN</t>
+  </si>
+  <si>
+    <t>ACR5IE</t>
+  </si>
+  <si>
+    <t>2302181955122</t>
+  </si>
+  <si>
+    <t>F2D74284CMCMRPCT05A93C421D</t>
+  </si>
+  <si>
+    <t>64CDDA06CMCMRPCT0807F2389E</t>
+  </si>
+  <si>
+    <t>ACSDT4</t>
+  </si>
+  <si>
+    <t>2023-07-10T07:53:00</t>
+  </si>
+  <si>
+    <t>2023-07-10T11:56:00</t>
+  </si>
+  <si>
+    <t>ACSDVL</t>
+  </si>
+  <si>
+    <t>ACSFKM</t>
+  </si>
+  <si>
+    <t>2023-07-08T07:38:00</t>
+  </si>
+  <si>
+    <t>2023-07-08T12:03:00</t>
+  </si>
+  <si>
+    <t>2023-07-08T14:02:00</t>
+  </si>
+  <si>
+    <t>2023-07-08T15:33:00</t>
+  </si>
+  <si>
+    <t>2302181955125</t>
   </si>
 </sst>
 </file>
@@ -2681,10 +2822,10 @@
         <v>0</v>
       </c>
       <c r="K3" s="48" t="s">
-        <v>546</v>
+        <v>586</v>
       </c>
       <c r="L3" s="48" t="s">
-        <v>547</v>
+        <v>587</v>
       </c>
       <c r="M3" s="48"/>
       <c r="N3" s="48"/>
@@ -2745,10 +2886,10 @@
       <c r="I5" s="48"/>
       <c r="J5" s="48"/>
       <c r="K5" s="48" t="s">
-        <v>549</v>
+        <v>589</v>
       </c>
       <c r="L5" s="48" t="s">
-        <v>550</v>
+        <v>590</v>
       </c>
       <c r="M5" s="48"/>
       <c r="N5" s="48" t="s">
@@ -2792,7 +2933,7 @@
       <c r="I6" s="48"/>
       <c r="J6" s="48"/>
       <c r="K6" s="48" t="s">
-        <v>551</v>
+        <v>591</v>
       </c>
       <c r="L6" s="48"/>
       <c r="M6" s="48"/>
@@ -2803,7 +2944,7 @@
         <v>308</v>
       </c>
       <c r="P6" s="48" t="s">
-        <v>552</v>
+        <v>592</v>
       </c>
       <c r="Q6" s="37"/>
       <c r="R6" s="48"/>
@@ -2837,10 +2978,10 @@
       <c r="I7" s="48"/>
       <c r="J7" s="48"/>
       <c r="K7" s="48" t="s">
-        <v>553</v>
+        <v>593</v>
       </c>
       <c r="L7" s="48" t="s">
-        <v>554</v>
+        <v>594</v>
       </c>
       <c r="M7" s="48"/>
       <c r="N7" s="48" t="s">
@@ -2850,13 +2991,13 @@
         <v>308</v>
       </c>
       <c r="P7" s="48" t="s">
-        <v>555</v>
+        <v>595</v>
       </c>
       <c r="Q7" s="55" t="s">
         <v>121</v>
       </c>
       <c r="R7" s="48" t="s">
-        <v>556</v>
+        <v>596</v>
       </c>
       <c r="S7" s="48"/>
       <c r="T7" s="48"/>
@@ -2892,10 +3033,10 @@
       </c>
       <c r="J8" s="48"/>
       <c r="K8" s="48" t="s">
-        <v>557</v>
+        <v>597</v>
       </c>
       <c r="L8" s="48" t="s">
-        <v>558</v>
+        <v>598</v>
       </c>
       <c r="M8" s="48"/>
       <c r="N8" s="48" t="s">
@@ -2933,7 +3074,7 @@
       <c r="I9" s="48"/>
       <c r="J9" s="48"/>
       <c r="K9" s="48" t="s">
-        <v>559</v>
+        <v>599</v>
       </c>
       <c r="L9" s="48"/>
       <c r="M9" s="48"/>
@@ -2972,10 +3113,10 @@
       <c r="I10" s="48"/>
       <c r="J10" s="48"/>
       <c r="K10" s="48" t="s">
-        <v>560</v>
+        <v>600</v>
       </c>
       <c r="L10" s="48" t="s">
-        <v>561</v>
+        <v>601</v>
       </c>
       <c r="M10" s="48"/>
       <c r="N10" s="48"/>
@@ -3011,10 +3152,10 @@
       <c r="I11" s="48"/>
       <c r="J11" s="48"/>
       <c r="K11" s="48" t="s">
-        <v>533</v>
+        <v>573</v>
       </c>
       <c r="L11" s="48" t="s">
-        <v>534</v>
+        <v>574</v>
       </c>
       <c r="M11" s="48"/>
       <c r="N11" s="48"/>
@@ -3050,10 +3191,10 @@
       <c r="I12" s="48"/>
       <c r="J12" s="48"/>
       <c r="K12" s="48" t="s">
-        <v>535</v>
+        <v>575</v>
       </c>
       <c r="L12" s="48" t="s">
-        <v>536</v>
+        <v>576</v>
       </c>
       <c r="M12" s="48"/>
       <c r="N12" s="48" t="s">
@@ -3093,10 +3234,10 @@
       <c r="I13" s="48"/>
       <c r="J13" s="48"/>
       <c r="K13" s="48" t="s">
-        <v>537</v>
+        <v>577</v>
       </c>
       <c r="L13" s="48" t="s">
-        <v>538</v>
+        <v>578</v>
       </c>
       <c r="M13" s="48"/>
       <c r="N13" s="48" t="s">
@@ -3171,10 +3312,10 @@
       <c r="I15" s="48"/>
       <c r="J15" s="48"/>
       <c r="K15" s="48" t="s">
-        <v>539</v>
+        <v>579</v>
       </c>
       <c r="L15" s="48" t="s">
-        <v>540</v>
+        <v>580</v>
       </c>
       <c r="M15" s="48"/>
       <c r="N15" s="48" t="s">
@@ -3214,7 +3355,7 @@
       <c r="I16" s="48"/>
       <c r="J16" s="48"/>
       <c r="K16" s="48" t="s">
-        <v>541</v>
+        <v>581</v>
       </c>
       <c r="L16" s="48"/>
       <c r="M16" s="48"/>
@@ -3253,7 +3394,7 @@
       <c r="I17" s="48"/>
       <c r="J17" s="48"/>
       <c r="K17" s="48" t="s">
-        <v>542</v>
+        <v>582</v>
       </c>
       <c r="L17" s="48"/>
       <c r="M17" s="48"/>
@@ -3296,7 +3437,7 @@
       </c>
       <c r="J18" s="48"/>
       <c r="K18" s="48" t="s">
-        <v>543</v>
+        <v>583</v>
       </c>
       <c r="L18" s="48"/>
       <c r="M18" s="48"/>
@@ -3335,7 +3476,7 @@
       <c r="I19" s="48"/>
       <c r="J19" s="48"/>
       <c r="K19" s="48" t="s">
-        <v>544</v>
+        <v>584</v>
       </c>
       <c r="L19" s="48"/>
       <c r="M19" s="48"/>
@@ -3374,7 +3515,7 @@
       <c r="I20" s="48"/>
       <c r="J20" s="48"/>
       <c r="K20" s="48" t="s">
-        <v>545</v>
+        <v>585</v>
       </c>
       <c r="L20" s="48"/>
       <c r="M20" s="48"/>
@@ -3413,7 +3554,7 @@
       <c r="I21" s="48"/>
       <c r="J21" s="48"/>
       <c r="K21" s="48" t="s">
-        <v>548</v>
+        <v>588</v>
       </c>
       <c r="L21" s="48"/>
       <c r="M21" s="48"/>
@@ -3532,7 +3673,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="62" t="s">
-        <v>562</v>
+        <v>602</v>
       </c>
       <c r="E3" s="62" t="s">
         <v>331</v>
@@ -3553,7 +3694,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="62" t="s">
-        <v>563</v>
+        <v>603</v>
       </c>
       <c r="E4" s="60"/>
       <c r="F4" s="60" t="s">
@@ -4135,16 +4276,16 @@
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>440</v>
+        <v>604</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>441</v>
+        <v>605</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>19</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>442</v>
+        <v>606</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>13</v>
@@ -5222,7 +5363,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>564</v>
+        <v>607</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>387</v>
@@ -5867,16 +6008,16 @@
       <c r="U2" s="3"/>
       <c r="V2" s="3"/>
       <c r="W2" s="3" t="s">
-        <v>519</v>
+        <v>567</v>
       </c>
       <c r="X2" s="3" t="s">
-        <v>511</v>
+        <v>568</v>
       </c>
       <c r="Y2" s="3" t="s">
         <v>48</v>
       </c>
       <c r="Z2" s="3" t="s">
-        <v>512</v>
+        <v>569</v>
       </c>
       <c r="AA2" s="3" t="s">
         <v>13</v>
@@ -5885,7 +6026,7 @@
         <v>49</v>
       </c>
       <c r="AC2" s="3" t="s">
-        <v>520</v>
+        <v>570</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -5995,16 +6136,16 @@
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="s">
-        <v>521</v>
+        <v>571</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>511</v>
+        <v>568</v>
       </c>
       <c r="Y4" s="3" t="s">
         <v>48</v>
       </c>
       <c r="Z4" s="3" t="s">
-        <v>512</v>
+        <v>569</v>
       </c>
       <c r="AA4" s="3" t="s">
         <v>13</v>
@@ -6013,7 +6154,7 @@
         <v>49</v>
       </c>
       <c r="AC4" s="3" t="s">
-        <v>522</v>
+        <v>572</v>
       </c>
     </row>
   </sheetData>
@@ -6545,16 +6686,16 @@
         <v>208</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>565</v>
+        <v>608</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>524</v>
+        <v>609</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>278</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>525</v>
+        <v>610</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>13</v>
@@ -6563,13 +6704,13 @@
         <v>279</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>526</v>
+        <v>611</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>280</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>527</v>
+        <v>612</v>
       </c>
       <c r="S2" s="3" t="s">
         <v>279</v>
@@ -6578,7 +6719,7 @@
         <v>208</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>566</v>
+        <v>613</v>
       </c>
     </row>
     <row r="3" spans="1:21">

--- a/src/test/java/TestData/Scenario_TestData.xlsx
+++ b/src/test/java/TestData/Scenario_TestData.xlsx
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1721" uniqueCount="614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1844" uniqueCount="675">
   <si>
     <t>Scenario</t>
   </si>
@@ -1908,6 +1908,189 @@
   </si>
   <si>
     <t>2302181955125</t>
+  </si>
+  <si>
+    <t>BKPAAC</t>
+  </si>
+  <si>
+    <t>BKPAIQ</t>
+  </si>
+  <si>
+    <t>BKPAME</t>
+  </si>
+  <si>
+    <t>BKPAO5</t>
+  </si>
+  <si>
+    <t>BKPAU4</t>
+  </si>
+  <si>
+    <t>2023-07-14T06:11:10</t>
+  </si>
+  <si>
+    <t>BKPA4Y</t>
+  </si>
+  <si>
+    <t>2023-07-14T06:11:18</t>
+  </si>
+  <si>
+    <t>BKPB2R</t>
+  </si>
+  <si>
+    <t>BKPB5B</t>
+  </si>
+  <si>
+    <t>BKPCA2</t>
+  </si>
+  <si>
+    <t>2302182476441</t>
+  </si>
+  <si>
+    <t>BKPCXW</t>
+  </si>
+  <si>
+    <t>2302182476442</t>
+  </si>
+  <si>
+    <t>BKPDLD</t>
+  </si>
+  <si>
+    <t>2302182476443</t>
+  </si>
+  <si>
+    <t>BKPEPN</t>
+  </si>
+  <si>
+    <t>2302182476444</t>
+  </si>
+  <si>
+    <t>BKPETM</t>
+  </si>
+  <si>
+    <t>2302182476445</t>
+  </si>
+  <si>
+    <t>BKPE5K</t>
+  </si>
+  <si>
+    <t>BKPFHW</t>
+  </si>
+  <si>
+    <t>BKPFK2</t>
+  </si>
+  <si>
+    <t>BKPFNZ</t>
+  </si>
+  <si>
+    <t>BKPFZ4</t>
+  </si>
+  <si>
+    <t>2302182476446</t>
+  </si>
+  <si>
+    <t>2302182476447</t>
+  </si>
+  <si>
+    <t>BKPF25</t>
+  </si>
+  <si>
+    <t>2302182476448</t>
+  </si>
+  <si>
+    <t>2302182476449</t>
+  </si>
+  <si>
+    <t>BKPGBF</t>
+  </si>
+  <si>
+    <t>3703101DCMCMRPCT08267CAF51</t>
+  </si>
+  <si>
+    <t>B1085BD4CMCMRPCT05D527ED98</t>
+  </si>
+  <si>
+    <t>CBBFCA1ECMCMRPCT07C358FC56</t>
+  </si>
+  <si>
+    <t>BKPK4O</t>
+  </si>
+  <si>
+    <t>2023-07-17T07:59:00</t>
+  </si>
+  <si>
+    <t>2023-07-17T12:07:00</t>
+  </si>
+  <si>
+    <t>BKPLOU</t>
+  </si>
+  <si>
+    <t>BKPW1B</t>
+  </si>
+  <si>
+    <t>BKPW2B</t>
+  </si>
+  <si>
+    <t>BKPW20</t>
+  </si>
+  <si>
+    <t>BKPW3E</t>
+  </si>
+  <si>
+    <t>BKPW4K</t>
+  </si>
+  <si>
+    <t>2023-07-14T06:25:26</t>
+  </si>
+  <si>
+    <t>BKPXAH</t>
+  </si>
+  <si>
+    <t>2023-07-14T06:25:34</t>
+  </si>
+  <si>
+    <t>BKPXGF</t>
+  </si>
+  <si>
+    <t>BKPXHF</t>
+  </si>
+  <si>
+    <t>BKPXWJ</t>
+  </si>
+  <si>
+    <t>BKPXYY</t>
+  </si>
+  <si>
+    <t>2302182476464</t>
+  </si>
+  <si>
+    <t>2302182476465</t>
+  </si>
+  <si>
+    <t>BKPXZN</t>
+  </si>
+  <si>
+    <t>2302182476466</t>
+  </si>
+  <si>
+    <t>2302182476467</t>
+  </si>
+  <si>
+    <t>BKPX0J</t>
+  </si>
+  <si>
+    <t>852B3E82CMCMRPCT0547B6E4F8</t>
+  </si>
+  <si>
+    <t>A2CB4E0ACMCMRPCT0633F7CA6D</t>
+  </si>
+  <si>
+    <t>AFA405E6CMCMRPCT0580BBCD97</t>
+  </si>
+  <si>
+    <t>BKPZKG</t>
+  </si>
+  <si>
+    <t>BKPZPD</t>
   </si>
 </sst>
 </file>
@@ -2597,7 +2780,7 @@
         <v>16</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>473</v>
+        <v>654</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>274</v>
@@ -2614,7 +2797,7 @@
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
       <c r="O2" s="3" t="s">
-        <v>474</v>
+        <v>655</v>
       </c>
       <c r="P2" s="24"/>
     </row>
@@ -3152,10 +3335,10 @@
       <c r="I11" s="48"/>
       <c r="J11" s="48"/>
       <c r="K11" s="48" t="s">
-        <v>573</v>
+        <v>628</v>
       </c>
       <c r="L11" s="48" t="s">
-        <v>574</v>
+        <v>629</v>
       </c>
       <c r="M11" s="48"/>
       <c r="N11" s="48"/>
@@ -3234,10 +3417,10 @@
       <c r="I13" s="48"/>
       <c r="J13" s="48"/>
       <c r="K13" s="48" t="s">
-        <v>577</v>
+        <v>630</v>
       </c>
       <c r="L13" s="48" t="s">
-        <v>578</v>
+        <v>631</v>
       </c>
       <c r="M13" s="48"/>
       <c r="N13" s="48" t="s">
@@ -3312,10 +3495,10 @@
       <c r="I15" s="48"/>
       <c r="J15" s="48"/>
       <c r="K15" s="48" t="s">
-        <v>579</v>
+        <v>632</v>
       </c>
       <c r="L15" s="48" t="s">
-        <v>580</v>
+        <v>633</v>
       </c>
       <c r="M15" s="48"/>
       <c r="N15" s="48" t="s">
@@ -3355,7 +3538,7 @@
       <c r="I16" s="48"/>
       <c r="J16" s="48"/>
       <c r="K16" s="48" t="s">
-        <v>581</v>
+        <v>634</v>
       </c>
       <c r="L16" s="48"/>
       <c r="M16" s="48"/>
@@ -3437,7 +3620,7 @@
       </c>
       <c r="J18" s="48"/>
       <c r="K18" s="48" t="s">
-        <v>583</v>
+        <v>635</v>
       </c>
       <c r="L18" s="48"/>
       <c r="M18" s="48"/>
@@ -3515,7 +3698,7 @@
       <c r="I20" s="48"/>
       <c r="J20" s="48"/>
       <c r="K20" s="48" t="s">
-        <v>585</v>
+        <v>636</v>
       </c>
       <c r="L20" s="48"/>
       <c r="M20" s="48"/>
@@ -3554,7 +3737,7 @@
       <c r="I21" s="48"/>
       <c r="J21" s="48"/>
       <c r="K21" s="48" t="s">
-        <v>588</v>
+        <v>662</v>
       </c>
       <c r="L21" s="48"/>
       <c r="M21" s="48"/>
@@ -3654,10 +3837,10 @@
         <v>2</v>
       </c>
       <c r="D2" s="62" t="s">
-        <v>396</v>
+        <v>670</v>
       </c>
       <c r="E2" s="62" t="s">
-        <v>395</v>
+        <v>669</v>
       </c>
       <c r="F2" s="60"/>
       <c r="G2" s="63"/>
@@ -3673,7 +3856,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="62" t="s">
-        <v>602</v>
+        <v>671</v>
       </c>
       <c r="E3" s="62" t="s">
         <v>331</v>
@@ -3694,7 +3877,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="62" t="s">
-        <v>603</v>
+        <v>672</v>
       </c>
       <c r="E4" s="60"/>
       <c r="F4" s="60" t="s">
@@ -3822,13 +4005,13 @@
       <c r="G5" s="60"/>
       <c r="H5" s="60"/>
       <c r="I5" s="60" t="s">
-        <v>379</v>
+        <v>666</v>
       </c>
       <c r="J5" s="60" t="s">
-        <v>380</v>
+        <v>667</v>
       </c>
       <c r="K5" s="60" t="s">
-        <v>381</v>
+        <v>668</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -4276,16 +4459,16 @@
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>604</v>
+        <v>673</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>605</v>
+        <v>649</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>19</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>606</v>
+        <v>650</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>13</v>
@@ -5363,7 +5546,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>607</v>
+        <v>674</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>387</v>
@@ -7276,10 +7459,10 @@
         <v>65</v>
       </c>
       <c r="H2" s="26" t="s">
-        <v>406</v>
+        <v>658</v>
       </c>
       <c r="I2" s="26" t="s">
-        <v>407</v>
+        <v>659</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -7925,7 +8108,7 @@
       <c r="M2" s="48"/>
       <c r="N2" s="48"/>
       <c r="O2" s="48" t="s">
-        <v>408</v>
+        <v>661</v>
       </c>
       <c r="P2" s="48"/>
     </row>
@@ -8526,10 +8709,10 @@
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
       <c r="R2" s="3" t="s">
-        <v>529</v>
+        <v>624</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>530</v>
+        <v>625</v>
       </c>
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
@@ -8788,10 +8971,10 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3" t="s">
-        <v>531</v>
+        <v>626</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>532</v>
+        <v>627</v>
       </c>
       <c r="T8" s="3">
         <v>0</v>

--- a/src/test/java/TestData/Scenario_TestData.xlsx
+++ b/src/test/java/TestData/Scenario_TestData.xlsx
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1844" uniqueCount="675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1888" uniqueCount="696">
   <si>
     <t>Scenario</t>
   </si>
@@ -2091,6 +2091,69 @@
   </si>
   <si>
     <t>BKPZPD</t>
+  </si>
+  <si>
+    <t>BKSL1S</t>
+  </si>
+  <si>
+    <t>BKSMTH</t>
+  </si>
+  <si>
+    <t>BKSNAA</t>
+  </si>
+  <si>
+    <t>BKSNK3</t>
+  </si>
+  <si>
+    <t>BKSOQM</t>
+  </si>
+  <si>
+    <t>2023-07-14T07:36:46</t>
+  </si>
+  <si>
+    <t>BKSO3R</t>
+  </si>
+  <si>
+    <t>2023-07-14T07:36:55</t>
+  </si>
+  <si>
+    <t>BKSTSP</t>
+  </si>
+  <si>
+    <t>BKSUQJ</t>
+  </si>
+  <si>
+    <t>2302182476517</t>
+  </si>
+  <si>
+    <t>2302182476518</t>
+  </si>
+  <si>
+    <t>BKSUWK</t>
+  </si>
+  <si>
+    <t>2302182476519</t>
+  </si>
+  <si>
+    <t>2302182476520</t>
+  </si>
+  <si>
+    <t>BKSU3W</t>
+  </si>
+  <si>
+    <t>438C0373CMCMRPCT05C8D23EE3</t>
+  </si>
+  <si>
+    <t>3A9DD03ACMCMRPCT06CEC75A1A</t>
+  </si>
+  <si>
+    <t>87FF72DDCMCMRPCT05F085B079</t>
+  </si>
+  <si>
+    <t>BKS5ZE</t>
+  </si>
+  <si>
+    <t>BKTAYM</t>
   </si>
 </sst>
 </file>
@@ -2780,7 +2843,7 @@
         <v>16</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>654</v>
+        <v>677</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>274</v>
@@ -2797,7 +2860,7 @@
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
       <c r="O2" s="3" t="s">
-        <v>655</v>
+        <v>678</v>
       </c>
       <c r="P2" s="24"/>
     </row>
@@ -3737,7 +3800,7 @@
       <c r="I21" s="48"/>
       <c r="J21" s="48"/>
       <c r="K21" s="48" t="s">
-        <v>662</v>
+        <v>683</v>
       </c>
       <c r="L21" s="48"/>
       <c r="M21" s="48"/>
@@ -3837,10 +3900,10 @@
         <v>2</v>
       </c>
       <c r="D2" s="62" t="s">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="E2" s="62" t="s">
-        <v>669</v>
+        <v>690</v>
       </c>
       <c r="F2" s="60"/>
       <c r="G2" s="63"/>
@@ -3856,7 +3919,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="62" t="s">
-        <v>671</v>
+        <v>692</v>
       </c>
       <c r="E3" s="62" t="s">
         <v>331</v>
@@ -3877,7 +3940,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="62" t="s">
-        <v>672</v>
+        <v>693</v>
       </c>
       <c r="E4" s="60"/>
       <c r="F4" s="60" t="s">
@@ -4005,13 +4068,13 @@
       <c r="G5" s="60"/>
       <c r="H5" s="60"/>
       <c r="I5" s="60" t="s">
-        <v>666</v>
+        <v>687</v>
       </c>
       <c r="J5" s="60" t="s">
-        <v>667</v>
+        <v>688</v>
       </c>
       <c r="K5" s="60" t="s">
-        <v>668</v>
+        <v>689</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -4459,7 +4522,7 @@
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>673</v>
+        <v>694</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>649</v>
@@ -5546,7 +5609,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>674</v>
+        <v>695</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>387</v>
@@ -7459,10 +7522,10 @@
         <v>65</v>
       </c>
       <c r="H2" s="26" t="s">
-        <v>658</v>
+        <v>681</v>
       </c>
       <c r="I2" s="26" t="s">
-        <v>659</v>
+        <v>682</v>
       </c>
     </row>
     <row r="3" spans="1:9">

--- a/src/test/java/TestData/Scenario_TestData.xlsx
+++ b/src/test/java/TestData/Scenario_TestData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\COPA Automation Final\Copa_API_WebServices\src\test\java\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ArunJK\Arun\Copa_SHDWebservices\src\test\java\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{819B26A9-F34C-4039-A732-7E8C24DC73EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82EFF842-C683-47FF-ACC8-4B571910F53C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="27" activeTab="30" xr2:uid="{5D5A4724-D560-4FC2-9708-4BBF1DBA0B11}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{5D5A4724-D560-4FC2-9708-4BBF1DBA0B11}"/>
   </bookViews>
   <sheets>
     <sheet name="AdvancePassengerInfo" sheetId="1" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1888" uniqueCount="696">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="544">
   <si>
     <t>Scenario</t>
   </si>
@@ -1205,15 +1205,6 @@
     <t>Booking_multiple_tickets</t>
   </si>
   <si>
-    <t>BPHLTF</t>
-  </si>
-  <si>
-    <t>2302181199430</t>
-  </si>
-  <si>
-    <t>2302181199431</t>
-  </si>
-  <si>
     <t>Bulk_Ticket</t>
   </si>
   <si>
@@ -1235,201 +1226,15 @@
     <t>2024-03-10T06:42:00</t>
   </si>
   <si>
-    <t>2023-05-19T07:56:00</t>
-  </si>
-  <si>
-    <t>2023-05-19T12:35:00</t>
-  </si>
-  <si>
-    <t>2023-05-19T14:06:00</t>
-  </si>
-  <si>
-    <t>2023-05-19T15:40:00</t>
-  </si>
-  <si>
     <t>BODK0Y</t>
   </si>
   <si>
     <t>2302181834307</t>
   </si>
   <si>
-    <t>BODL51</t>
-  </si>
-  <si>
-    <t>22EE7770CMCMRPCT05339998DA</t>
-  </si>
-  <si>
     <t>BODNR1</t>
   </si>
   <si>
-    <t>BODOEH</t>
-  </si>
-  <si>
-    <t>2302181834330</t>
-  </si>
-  <si>
-    <t>AEE00K</t>
-  </si>
-  <si>
-    <t>2302181859853</t>
-  </si>
-  <si>
-    <t>AEE00Z</t>
-  </si>
-  <si>
-    <t>2302181859854</t>
-  </si>
-  <si>
-    <t>AE40MU</t>
-  </si>
-  <si>
-    <t>AE40NF</t>
-  </si>
-  <si>
-    <t>AE40OY</t>
-  </si>
-  <si>
-    <t>2023-06-02T06:21:30</t>
-  </si>
-  <si>
-    <t>AE40UK</t>
-  </si>
-  <si>
-    <t>AE40UZ</t>
-  </si>
-  <si>
-    <t>2302181862749</t>
-  </si>
-  <si>
-    <t>AE40XX</t>
-  </si>
-  <si>
-    <t>2302181862750</t>
-  </si>
-  <si>
-    <t>AE401F</t>
-  </si>
-  <si>
-    <t>2302181862753</t>
-  </si>
-  <si>
-    <t>AE404A</t>
-  </si>
-  <si>
-    <t>2302181862756</t>
-  </si>
-  <si>
-    <t>AE41CN</t>
-  </si>
-  <si>
-    <t>2302181862757</t>
-  </si>
-  <si>
-    <t>AE41D5</t>
-  </si>
-  <si>
-    <t>2302181862758</t>
-  </si>
-  <si>
-    <t>AE41EM</t>
-  </si>
-  <si>
-    <t>AE41FG</t>
-  </si>
-  <si>
-    <t>AE41FS</t>
-  </si>
-  <si>
-    <t>AE41II</t>
-  </si>
-  <si>
-    <t>AE41KD</t>
-  </si>
-  <si>
-    <t>AE41KP</t>
-  </si>
-  <si>
-    <t>2302181862759</t>
-  </si>
-  <si>
-    <t>AE41LH</t>
-  </si>
-  <si>
-    <t>AE41MP</t>
-  </si>
-  <si>
-    <t>2302181862760</t>
-  </si>
-  <si>
-    <t>AE41NE</t>
-  </si>
-  <si>
-    <t>AE41NJ</t>
-  </si>
-  <si>
-    <t>AE41T0</t>
-  </si>
-  <si>
-    <t>2302181862761</t>
-  </si>
-  <si>
-    <t>AE41UT</t>
-  </si>
-  <si>
-    <t>AE41WE</t>
-  </si>
-  <si>
-    <t>2302181862762</t>
-  </si>
-  <si>
-    <t>C7D87262CMCMRPCT061B0D311A</t>
-  </si>
-  <si>
-    <t>5966EED0CMCMRPCT05BA05D4AF</t>
-  </si>
-  <si>
-    <t>AE42NH</t>
-  </si>
-  <si>
-    <t>2023-06-05T07:53:00</t>
-  </si>
-  <si>
-    <t>2023-06-05T11:56:00</t>
-  </si>
-  <si>
-    <t>AE42PG</t>
-  </si>
-  <si>
-    <t>2023-06-03T07:55:00</t>
-  </si>
-  <si>
-    <t>2023-06-03T09:29:00</t>
-  </si>
-  <si>
-    <t>AE42PU</t>
-  </si>
-  <si>
-    <t>AE42P3</t>
-  </si>
-  <si>
-    <t>2302181862768</t>
-  </si>
-  <si>
-    <t>AE42RO</t>
-  </si>
-  <si>
-    <t>AE42SV</t>
-  </si>
-  <si>
-    <t>2302181862776</t>
-  </si>
-  <si>
-    <t>AE42TI</t>
-  </si>
-  <si>
-    <t>2302181862777</t>
-  </si>
-  <si>
     <t>Carrier Code</t>
   </si>
   <si>
@@ -1451,15 +1256,9 @@
     <t>Add Flight</t>
   </si>
   <si>
-    <t>AGY2HS</t>
-  </si>
-  <si>
     <t>Add Name</t>
   </si>
   <si>
-    <t>AGY2JA</t>
-  </si>
-  <si>
     <t>FOX</t>
   </si>
   <si>
@@ -1469,9 +1268,6 @@
     <t>Add Class</t>
   </si>
   <si>
-    <t>AGY2KG</t>
-  </si>
-  <si>
     <t>AGY3OI</t>
   </si>
   <si>
@@ -1481,123 +1277,6 @@
     <t>AGY3RY</t>
   </si>
   <si>
-    <t>AG3ZTC</t>
-  </si>
-  <si>
-    <t>AG3ZTN</t>
-  </si>
-  <si>
-    <t>AG3ZTO</t>
-  </si>
-  <si>
-    <t>AG3ZTP</t>
-  </si>
-  <si>
-    <t>AIOGZH</t>
-  </si>
-  <si>
-    <t>2302181869630</t>
-  </si>
-  <si>
-    <t>AIOG2P</t>
-  </si>
-  <si>
-    <t>2302181869631</t>
-  </si>
-  <si>
-    <t>AIOHAQ</t>
-  </si>
-  <si>
-    <t>2302181869632</t>
-  </si>
-  <si>
-    <t>AIOHBA</t>
-  </si>
-  <si>
-    <t>2302181869633</t>
-  </si>
-  <si>
-    <t>AIOHB3</t>
-  </si>
-  <si>
-    <t>2302181869634</t>
-  </si>
-  <si>
-    <t>AIOHDQ</t>
-  </si>
-  <si>
-    <t>2302181869635</t>
-  </si>
-  <si>
-    <t>AIOHEY</t>
-  </si>
-  <si>
-    <t>AIOHGT</t>
-  </si>
-  <si>
-    <t>AIOHHI</t>
-  </si>
-  <si>
-    <t>AIOHH5</t>
-  </si>
-  <si>
-    <t>AIOHKI</t>
-  </si>
-  <si>
-    <t>AIOHKX</t>
-  </si>
-  <si>
-    <t>2302181869636</t>
-  </si>
-  <si>
-    <t>AIOHL5</t>
-  </si>
-  <si>
-    <t>AIOHMU</t>
-  </si>
-  <si>
-    <t>2302181869637</t>
-  </si>
-  <si>
-    <t>AIOHNA</t>
-  </si>
-  <si>
-    <t>AIOHND</t>
-  </si>
-  <si>
-    <t>AIOHOA</t>
-  </si>
-  <si>
-    <t>2302181869638</t>
-  </si>
-  <si>
-    <t>AIOHOQ</t>
-  </si>
-  <si>
-    <t>2302181869639</t>
-  </si>
-  <si>
-    <t>AIOHPG</t>
-  </si>
-  <si>
-    <t>2302181869640</t>
-  </si>
-  <si>
-    <t>AIOHQS</t>
-  </si>
-  <si>
-    <t>AIOHRU</t>
-  </si>
-  <si>
-    <t>2302181869641</t>
-  </si>
-  <si>
-    <t>8AD54668CMCMRPCT0543C365BD</t>
-  </si>
-  <si>
-    <t>E2190C22CMCMRPCT0609952907</t>
-  </si>
-  <si>
     <t>AIOIXA</t>
   </si>
   <si>
@@ -1607,168 +1286,15 @@
     <t>2023-06-08T09:29:00</t>
   </si>
   <si>
-    <t>AIOIYA</t>
-  </si>
-  <si>
     <t>AIOIYZ</t>
   </si>
   <si>
     <t>2302181869645</t>
   </si>
   <si>
-    <t>AIOI0F</t>
-  </si>
-  <si>
-    <t>AIOI02</t>
-  </si>
-  <si>
     <t>AIOI1L</t>
   </si>
   <si>
-    <t>AIOI24</t>
-  </si>
-  <si>
-    <t>2302181869651</t>
-  </si>
-  <si>
-    <t>AIOI3U</t>
-  </si>
-  <si>
-    <t>2302181869652</t>
-  </si>
-  <si>
-    <t>AIOJAN</t>
-  </si>
-  <si>
-    <t>2023-06-08T07:38:00</t>
-  </si>
-  <si>
-    <t>2023-06-08T12:03:00</t>
-  </si>
-  <si>
-    <t>2023-06-08T14:09:00</t>
-  </si>
-  <si>
-    <t>2023-06-08T15:40:00</t>
-  </si>
-  <si>
-    <t>2302181869653</t>
-  </si>
-  <si>
-    <t>AISCAS</t>
-  </si>
-  <si>
-    <t>2302181869713</t>
-  </si>
-  <si>
-    <t>AISCFT</t>
-  </si>
-  <si>
-    <t>2302181869714</t>
-  </si>
-  <si>
-    <t>AISCG0</t>
-  </si>
-  <si>
-    <t>2302181869715</t>
-  </si>
-  <si>
-    <t>AISCHD</t>
-  </si>
-  <si>
-    <t>2302181869716</t>
-  </si>
-  <si>
-    <t>AISCKP</t>
-  </si>
-  <si>
-    <t>2302181869717</t>
-  </si>
-  <si>
-    <t>AISCQA</t>
-  </si>
-  <si>
-    <t>2302181869718</t>
-  </si>
-  <si>
-    <t>AISCUB</t>
-  </si>
-  <si>
-    <t>AISCVB</t>
-  </si>
-  <si>
-    <t>AISCY0</t>
-  </si>
-  <si>
-    <t>AISCZL</t>
-  </si>
-  <si>
-    <t>AISCZQ</t>
-  </si>
-  <si>
-    <t>AISCZ0</t>
-  </si>
-  <si>
-    <t>2302181869719</t>
-  </si>
-  <si>
-    <t>AISCZ4</t>
-  </si>
-  <si>
-    <t>AISC0X</t>
-  </si>
-  <si>
-    <t>2302181869720</t>
-  </si>
-  <si>
-    <t>AISC15</t>
-  </si>
-  <si>
-    <t>AISC2A</t>
-  </si>
-  <si>
-    <t>AISC2B</t>
-  </si>
-  <si>
-    <t>2302181869721</t>
-  </si>
-  <si>
-    <t>AISC2H</t>
-  </si>
-  <si>
-    <t>2302181869722</t>
-  </si>
-  <si>
-    <t>AISC3D</t>
-  </si>
-  <si>
-    <t>2302181869723</t>
-  </si>
-  <si>
-    <t>AISC3T</t>
-  </si>
-  <si>
-    <t>AISC3Z</t>
-  </si>
-  <si>
-    <t>2302181869724</t>
-  </si>
-  <si>
-    <t>9C754478CMCMRPCT073803E992</t>
-  </si>
-  <si>
-    <t>F87B0BF4CMCMRPCT07FAAA301D</t>
-  </si>
-  <si>
-    <t>AISDCT</t>
-  </si>
-  <si>
-    <t>AISDC1</t>
-  </si>
-  <si>
-    <t>2302181869727</t>
-  </si>
-  <si>
     <t>AWMGIE</t>
   </si>
   <si>
@@ -1787,54 +1313,24 @@
     <t>2302181931005</t>
   </si>
   <si>
-    <t>ACR3YZ</t>
-  </si>
-  <si>
-    <t>2302181955113</t>
-  </si>
-  <si>
     <t>ACR3ZE</t>
   </si>
   <si>
     <t>2302181955114</t>
   </si>
   <si>
-    <t>ACR4MQ</t>
-  </si>
-  <si>
-    <t>2302181955115</t>
-  </si>
-  <si>
-    <t>ACR4WT</t>
-  </si>
-  <si>
-    <t>2302181955116</t>
-  </si>
-  <si>
-    <t>ACR5AG</t>
-  </si>
-  <si>
     <t>ACR5AJ</t>
   </si>
   <si>
-    <t>ACR5AK</t>
-  </si>
-  <si>
     <t>ACR5AM</t>
   </si>
   <si>
-    <t>ACR5CF</t>
-  </si>
-  <si>
     <t>ACR5CL</t>
   </si>
   <si>
     <t>2302181955117</t>
   </si>
   <si>
-    <t>ACR5C4</t>
-  </si>
-  <si>
     <t>ACR5EH</t>
   </si>
   <si>
@@ -1874,24 +1370,6 @@
     <t>2302181955122</t>
   </si>
   <si>
-    <t>F2D74284CMCMRPCT05A93C421D</t>
-  </si>
-  <si>
-    <t>64CDDA06CMCMRPCT0807F2389E</t>
-  </si>
-  <si>
-    <t>ACSDT4</t>
-  </si>
-  <si>
-    <t>2023-07-10T07:53:00</t>
-  </si>
-  <si>
-    <t>2023-07-10T11:56:00</t>
-  </si>
-  <si>
-    <t>ACSDVL</t>
-  </si>
-  <si>
     <t>ACSFKM</t>
   </si>
   <si>
@@ -1910,36 +1388,6 @@
     <t>2302181955125</t>
   </si>
   <si>
-    <t>BKPAAC</t>
-  </si>
-  <si>
-    <t>BKPAIQ</t>
-  </si>
-  <si>
-    <t>BKPAME</t>
-  </si>
-  <si>
-    <t>BKPAO5</t>
-  </si>
-  <si>
-    <t>BKPAU4</t>
-  </si>
-  <si>
-    <t>2023-07-14T06:11:10</t>
-  </si>
-  <si>
-    <t>BKPA4Y</t>
-  </si>
-  <si>
-    <t>2023-07-14T06:11:18</t>
-  </si>
-  <si>
-    <t>BKPB2R</t>
-  </si>
-  <si>
-    <t>BKPB5B</t>
-  </si>
-  <si>
     <t>BKPCA2</t>
   </si>
   <si>
@@ -1979,138 +1427,15 @@
     <t>BKPFK2</t>
   </si>
   <si>
-    <t>BKPFNZ</t>
-  </si>
-  <si>
-    <t>BKPFZ4</t>
-  </si>
-  <si>
-    <t>2302182476446</t>
-  </si>
-  <si>
-    <t>2302182476447</t>
-  </si>
-  <si>
-    <t>BKPF25</t>
-  </si>
-  <si>
-    <t>2302182476448</t>
-  </si>
-  <si>
-    <t>2302182476449</t>
-  </si>
-  <si>
-    <t>BKPGBF</t>
-  </si>
-  <si>
-    <t>3703101DCMCMRPCT08267CAF51</t>
-  </si>
-  <si>
-    <t>B1085BD4CMCMRPCT05D527ED98</t>
-  </si>
-  <si>
-    <t>CBBFCA1ECMCMRPCT07C358FC56</t>
-  </si>
-  <si>
-    <t>BKPK4O</t>
-  </si>
-  <si>
     <t>2023-07-17T07:59:00</t>
   </si>
   <si>
     <t>2023-07-17T12:07:00</t>
   </si>
   <si>
-    <t>BKPLOU</t>
-  </si>
-  <si>
-    <t>BKPW1B</t>
-  </si>
-  <si>
-    <t>BKPW2B</t>
-  </si>
-  <si>
-    <t>BKPW20</t>
-  </si>
-  <si>
-    <t>BKPW3E</t>
-  </si>
-  <si>
-    <t>BKPW4K</t>
-  </si>
-  <si>
-    <t>2023-07-14T06:25:26</t>
-  </si>
-  <si>
-    <t>BKPXAH</t>
-  </si>
-  <si>
-    <t>2023-07-14T06:25:34</t>
-  </si>
-  <si>
-    <t>BKPXGF</t>
-  </si>
-  <si>
     <t>BKPXHF</t>
   </si>
   <si>
-    <t>BKPXWJ</t>
-  </si>
-  <si>
-    <t>BKPXYY</t>
-  </si>
-  <si>
-    <t>2302182476464</t>
-  </si>
-  <si>
-    <t>2302182476465</t>
-  </si>
-  <si>
-    <t>BKPXZN</t>
-  </si>
-  <si>
-    <t>2302182476466</t>
-  </si>
-  <si>
-    <t>2302182476467</t>
-  </si>
-  <si>
-    <t>BKPX0J</t>
-  </si>
-  <si>
-    <t>852B3E82CMCMRPCT0547B6E4F8</t>
-  </si>
-  <si>
-    <t>A2CB4E0ACMCMRPCT0633F7CA6D</t>
-  </si>
-  <si>
-    <t>AFA405E6CMCMRPCT0580BBCD97</t>
-  </si>
-  <si>
-    <t>BKPZKG</t>
-  </si>
-  <si>
-    <t>BKPZPD</t>
-  </si>
-  <si>
-    <t>BKSL1S</t>
-  </si>
-  <si>
-    <t>BKSMTH</t>
-  </si>
-  <si>
-    <t>BKSNAA</t>
-  </si>
-  <si>
-    <t>BKSNK3</t>
-  </si>
-  <si>
-    <t>BKSOQM</t>
-  </si>
-  <si>
-    <t>2023-07-14T07:36:46</t>
-  </si>
-  <si>
     <t>BKSO3R</t>
   </si>
   <si>
@@ -2120,15 +1445,6 @@
     <t>BKSTSP</t>
   </si>
   <si>
-    <t>BKSUQJ</t>
-  </si>
-  <si>
-    <t>2302182476517</t>
-  </si>
-  <si>
-    <t>2302182476518</t>
-  </si>
-  <si>
     <t>BKSUWK</t>
   </si>
   <si>
@@ -2154,6 +1470,234 @@
   </si>
   <si>
     <t>BKTAYM</t>
+  </si>
+  <si>
+    <t>BOFXGU</t>
+  </si>
+  <si>
+    <t>BOFXGV</t>
+  </si>
+  <si>
+    <t>BOHBI2</t>
+  </si>
+  <si>
+    <t>BOHBYS</t>
+  </si>
+  <si>
+    <t>BOHB4D</t>
+  </si>
+  <si>
+    <t>BOHB5M</t>
+  </si>
+  <si>
+    <t>BO2Z2E</t>
+  </si>
+  <si>
+    <t>BO2Z3G</t>
+  </si>
+  <si>
+    <t>2023-07-21T07:59:00</t>
+  </si>
+  <si>
+    <t>2023-07-21T12:07:00</t>
+  </si>
+  <si>
+    <t>2023-07-25T06:22:00</t>
+  </si>
+  <si>
+    <t>2023-07-25T08:32:00</t>
+  </si>
+  <si>
+    <t>BO2Z33</t>
+  </si>
+  <si>
+    <t>BO2Z4L</t>
+  </si>
+  <si>
+    <t>BO2Z4T</t>
+  </si>
+  <si>
+    <t>BO2Z5V</t>
+  </si>
+  <si>
+    <t>2023-07-20T06:19:55</t>
+  </si>
+  <si>
+    <t>BO20EG</t>
+  </si>
+  <si>
+    <t>2023-07-20T06:20:03</t>
+  </si>
+  <si>
+    <t>BO20IH</t>
+  </si>
+  <si>
+    <t>BO20IZ</t>
+  </si>
+  <si>
+    <t>BO20JR</t>
+  </si>
+  <si>
+    <t>2302182500173</t>
+  </si>
+  <si>
+    <t>BO20OM</t>
+  </si>
+  <si>
+    <t>2302182500174</t>
+  </si>
+  <si>
+    <t>BO20PH</t>
+  </si>
+  <si>
+    <t>2302182500175</t>
+  </si>
+  <si>
+    <t>BO20VH</t>
+  </si>
+  <si>
+    <t>2302182500177</t>
+  </si>
+  <si>
+    <t>BO20XK</t>
+  </si>
+  <si>
+    <t>2302182500178</t>
+  </si>
+  <si>
+    <t>BO20YY</t>
+  </si>
+  <si>
+    <t>2302182500179</t>
+  </si>
+  <si>
+    <t>BO201E</t>
+  </si>
+  <si>
+    <t>2302182500180</t>
+  </si>
+  <si>
+    <t>BO203N</t>
+  </si>
+  <si>
+    <t>BO2042</t>
+  </si>
+  <si>
+    <t>BO205P</t>
+  </si>
+  <si>
+    <t>BO21AP</t>
+  </si>
+  <si>
+    <t>BO21B2</t>
+  </si>
+  <si>
+    <t>BO21C3</t>
+  </si>
+  <si>
+    <t>2302182500181</t>
+  </si>
+  <si>
+    <t>BO21EE</t>
+  </si>
+  <si>
+    <t>BO21E5</t>
+  </si>
+  <si>
+    <t>2302182500182</t>
+  </si>
+  <si>
+    <t>BO21F4</t>
+  </si>
+  <si>
+    <t>BO21GG</t>
+  </si>
+  <si>
+    <t>BO21G0</t>
+  </si>
+  <si>
+    <t>2302182500183</t>
+  </si>
+  <si>
+    <t>BO21IJ</t>
+  </si>
+  <si>
+    <t>2302182500184</t>
+  </si>
+  <si>
+    <t>BO21JO</t>
+  </si>
+  <si>
+    <t>2302182500185</t>
+  </si>
+  <si>
+    <t>BO21KR</t>
+  </si>
+  <si>
+    <t>BO21L4</t>
+  </si>
+  <si>
+    <t>2302182500186</t>
+  </si>
+  <si>
+    <t>BO21NY</t>
+  </si>
+  <si>
+    <t>2302182500187</t>
+  </si>
+  <si>
+    <t>2302182500188</t>
+  </si>
+  <si>
+    <t>BO21QA</t>
+  </si>
+  <si>
+    <t>2302182500189</t>
+  </si>
+  <si>
+    <t>2302182500190</t>
+  </si>
+  <si>
+    <t>BO21TA</t>
+  </si>
+  <si>
+    <t>8B3FE1E8CMCMRPCT069905EE9C</t>
+  </si>
+  <si>
+    <t>6A2E6A7ECMCMRPCT07AF12B404</t>
+  </si>
+  <si>
+    <t>96D65F1ACMCMRPCT053BF6616C</t>
+  </si>
+  <si>
+    <t>BO223M</t>
+  </si>
+  <si>
+    <t>2023-07-23T07:59:00</t>
+  </si>
+  <si>
+    <t>2023-07-23T12:07:00</t>
+  </si>
+  <si>
+    <t>BO23AW</t>
+  </si>
+  <si>
+    <t>BO23JG</t>
+  </si>
+  <si>
+    <t>2023-07-21T07:47:00</t>
+  </si>
+  <si>
+    <t>2023-07-21T12:23:00</t>
+  </si>
+  <si>
+    <t>2023-07-21T14:02:00</t>
+  </si>
+  <si>
+    <t>2023-07-21T15:33:00</t>
+  </si>
+  <si>
+    <t>2302182500195</t>
   </si>
 </sst>
 </file>
@@ -2755,22 +2299,22 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:P15"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="52.81640625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="18.453125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="9.453125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="10.453125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="11.26953125"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="10.453125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="11.26953125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="10.453125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="11.26953125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="15.1796875"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="52.77734375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="18.44140625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.21875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="15.44140625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="12.21875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="9.44140625"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="17.5546875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="10.44140625"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="11.21875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="10.44140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="11.21875"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="10.44140625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="11.21875"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="15.21875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2827,7 +2371,7 @@
       <c r="B2" s="3">
         <v>2</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="62" t="s">
         <v>12</v>
       </c>
       <c r="D2" s="3" t="s">
@@ -2843,7 +2387,7 @@
         <v>16</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>677</v>
+        <v>481</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>274</v>
@@ -2860,7 +2404,7 @@
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
       <c r="O2" s="3" t="s">
-        <v>678</v>
+        <v>482</v>
       </c>
       <c r="P2" s="24"/>
     </row>
@@ -2871,7 +2415,7 @@
       <c r="B3" s="3">
         <v>4</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="62" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="3" t="s">
@@ -2930,10 +2474,10 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C501783-003E-43C7-BF08-448ED073E85B}">
   <dimension ref="A1:U22"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="10" max="10" style="45" width="8.7265625"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="10" max="10" style="45" width="8.77734375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="9.77734375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
@@ -3068,10 +2612,10 @@
         <v>0</v>
       </c>
       <c r="K3" s="48" t="s">
-        <v>586</v>
+        <v>508</v>
       </c>
       <c r="L3" s="48" t="s">
-        <v>587</v>
+        <v>509</v>
       </c>
       <c r="M3" s="48"/>
       <c r="N3" s="48"/>
@@ -3132,10 +2676,10 @@
       <c r="I5" s="48"/>
       <c r="J5" s="48"/>
       <c r="K5" s="48" t="s">
-        <v>589</v>
+        <v>511</v>
       </c>
       <c r="L5" s="48" t="s">
-        <v>590</v>
+        <v>512</v>
       </c>
       <c r="M5" s="48"/>
       <c r="N5" s="48" t="s">
@@ -3179,7 +2723,7 @@
       <c r="I6" s="48"/>
       <c r="J6" s="48"/>
       <c r="K6" s="48" t="s">
-        <v>591</v>
+        <v>513</v>
       </c>
       <c r="L6" s="48"/>
       <c r="M6" s="48"/>
@@ -3190,7 +2734,7 @@
         <v>308</v>
       </c>
       <c r="P6" s="48" t="s">
-        <v>592</v>
+        <v>514</v>
       </c>
       <c r="Q6" s="37"/>
       <c r="R6" s="48"/>
@@ -3224,10 +2768,10 @@
       <c r="I7" s="48"/>
       <c r="J7" s="48"/>
       <c r="K7" s="48" t="s">
-        <v>593</v>
+        <v>515</v>
       </c>
       <c r="L7" s="48" t="s">
-        <v>594</v>
+        <v>516</v>
       </c>
       <c r="M7" s="48"/>
       <c r="N7" s="48" t="s">
@@ -3237,13 +2781,13 @@
         <v>308</v>
       </c>
       <c r="P7" s="48" t="s">
-        <v>595</v>
+        <v>517</v>
       </c>
       <c r="Q7" s="55" t="s">
         <v>121</v>
       </c>
       <c r="R7" s="48" t="s">
-        <v>596</v>
+        <v>518</v>
       </c>
       <c r="S7" s="48"/>
       <c r="T7" s="48"/>
@@ -3279,10 +2823,10 @@
       </c>
       <c r="J8" s="48"/>
       <c r="K8" s="48" t="s">
-        <v>597</v>
+        <v>519</v>
       </c>
       <c r="L8" s="48" t="s">
-        <v>598</v>
+        <v>520</v>
       </c>
       <c r="M8" s="48"/>
       <c r="N8" s="48" t="s">
@@ -3320,7 +2864,7 @@
       <c r="I9" s="48"/>
       <c r="J9" s="48"/>
       <c r="K9" s="48" t="s">
-        <v>599</v>
+        <v>521</v>
       </c>
       <c r="L9" s="48"/>
       <c r="M9" s="48"/>
@@ -3359,10 +2903,10 @@
       <c r="I10" s="48"/>
       <c r="J10" s="48"/>
       <c r="K10" s="48" t="s">
-        <v>600</v>
+        <v>522</v>
       </c>
       <c r="L10" s="48" t="s">
-        <v>601</v>
+        <v>523</v>
       </c>
       <c r="M10" s="48"/>
       <c r="N10" s="48"/>
@@ -3398,10 +2942,10 @@
       <c r="I11" s="48"/>
       <c r="J11" s="48"/>
       <c r="K11" s="48" t="s">
-        <v>628</v>
+        <v>495</v>
       </c>
       <c r="L11" s="48" t="s">
-        <v>629</v>
+        <v>496</v>
       </c>
       <c r="M11" s="48"/>
       <c r="N11" s="48"/>
@@ -3437,10 +2981,10 @@
       <c r="I12" s="48"/>
       <c r="J12" s="48"/>
       <c r="K12" s="48" t="s">
-        <v>575</v>
+        <v>497</v>
       </c>
       <c r="L12" s="48" t="s">
-        <v>576</v>
+        <v>498</v>
       </c>
       <c r="M12" s="48"/>
       <c r="N12" s="48" t="s">
@@ -3480,10 +3024,10 @@
       <c r="I13" s="48"/>
       <c r="J13" s="48"/>
       <c r="K13" s="48" t="s">
-        <v>630</v>
+        <v>499</v>
       </c>
       <c r="L13" s="48" t="s">
-        <v>631</v>
+        <v>500</v>
       </c>
       <c r="M13" s="48"/>
       <c r="N13" s="48" t="s">
@@ -3558,10 +3102,10 @@
       <c r="I15" s="48"/>
       <c r="J15" s="48"/>
       <c r="K15" s="48" t="s">
-        <v>632</v>
+        <v>501</v>
       </c>
       <c r="L15" s="48" t="s">
-        <v>633</v>
+        <v>502</v>
       </c>
       <c r="M15" s="48"/>
       <c r="N15" s="48" t="s">
@@ -3601,7 +3145,7 @@
       <c r="I16" s="48"/>
       <c r="J16" s="48"/>
       <c r="K16" s="48" t="s">
-        <v>634</v>
+        <v>503</v>
       </c>
       <c r="L16" s="48"/>
       <c r="M16" s="48"/>
@@ -3640,7 +3184,7 @@
       <c r="I17" s="48"/>
       <c r="J17" s="48"/>
       <c r="K17" s="48" t="s">
-        <v>582</v>
+        <v>504</v>
       </c>
       <c r="L17" s="48"/>
       <c r="M17" s="48"/>
@@ -3683,7 +3227,7 @@
       </c>
       <c r="J18" s="48"/>
       <c r="K18" s="48" t="s">
-        <v>635</v>
+        <v>505</v>
       </c>
       <c r="L18" s="48"/>
       <c r="M18" s="48"/>
@@ -3722,7 +3266,7 @@
       <c r="I19" s="48"/>
       <c r="J19" s="48"/>
       <c r="K19" s="48" t="s">
-        <v>584</v>
+        <v>506</v>
       </c>
       <c r="L19" s="48"/>
       <c r="M19" s="48"/>
@@ -3761,7 +3305,7 @@
       <c r="I20" s="48"/>
       <c r="J20" s="48"/>
       <c r="K20" s="48" t="s">
-        <v>636</v>
+        <v>507</v>
       </c>
       <c r="L20" s="48"/>
       <c r="M20" s="48"/>
@@ -3800,7 +3344,7 @@
       <c r="I21" s="48"/>
       <c r="J21" s="48"/>
       <c r="K21" s="48" t="s">
-        <v>683</v>
+        <v>510</v>
       </c>
       <c r="L21" s="48"/>
       <c r="M21" s="48"/>
@@ -3858,14 +3402,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2EA1F88-8B75-4AAD-A17A-063CA3659CA4}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="32.90625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="14.36328125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="30.36328125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="6.90625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="10.90625"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="32.88671875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.5546875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="14.33203125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="30.33203125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="6.88671875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="10.88671875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -3900,10 +3444,10 @@
         <v>2</v>
       </c>
       <c r="D2" s="62" t="s">
-        <v>691</v>
+        <v>531</v>
       </c>
       <c r="E2" s="62" t="s">
-        <v>690</v>
+        <v>530</v>
       </c>
       <c r="F2" s="60"/>
       <c r="G2" s="63"/>
@@ -3919,7 +3463,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="62" t="s">
-        <v>692</v>
+        <v>532</v>
       </c>
       <c r="E3" s="62" t="s">
         <v>331</v>
@@ -3940,7 +3484,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="62" t="s">
-        <v>693</v>
+        <v>533</v>
       </c>
       <c r="E4" s="60"/>
       <c r="F4" s="60" t="s">
@@ -3956,18 +3500,18 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88414653-50FA-4845-96AF-5B777BBDF907}">
   <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="57" width="18.26953125"/>
-    <col min="2" max="2" customWidth="true" style="57" width="16.54296875"/>
-    <col min="3" max="3" customWidth="true" style="57" width="19.90625"/>
-    <col min="4" max="4" customWidth="true" style="57" width="18.81640625"/>
-    <col min="5" max="5" customWidth="true" style="57" width="12.90625"/>
+    <col min="1" max="1" customWidth="true" style="57" width="18.21875"/>
+    <col min="2" max="2" customWidth="true" style="57" width="16.5546875"/>
+    <col min="3" max="3" customWidth="true" style="57" width="19.88671875"/>
+    <col min="4" max="4" customWidth="true" style="57" width="18.77734375"/>
+    <col min="5" max="5" customWidth="true" style="57" width="12.88671875"/>
     <col min="6" max="8" customWidth="true" hidden="true" style="57" width="0.0"/>
-    <col min="9" max="9" style="57" width="8.7265625"/>
-    <col min="10" max="10" customWidth="true" style="57" width="17.90625"/>
-    <col min="11" max="11" customWidth="true" style="57" width="14.26953125"/>
-    <col min="12" max="16384" style="57" width="8.7265625"/>
+    <col min="9" max="9" style="57" width="8.77734375"/>
+    <col min="10" max="10" customWidth="true" style="57" width="17.88671875"/>
+    <col min="11" max="11" customWidth="true" style="57" width="14.21875"/>
+    <col min="12" max="16384" style="57" width="8.77734375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -4068,18 +3612,18 @@
       <c r="G5" s="60"/>
       <c r="H5" s="60"/>
       <c r="I5" s="60" t="s">
-        <v>687</v>
+        <v>527</v>
       </c>
       <c r="J5" s="60" t="s">
-        <v>688</v>
+        <v>528</v>
       </c>
       <c r="K5" s="60" t="s">
-        <v>689</v>
+        <v>529</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="60" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B6" s="60"/>
       <c r="C6" s="60">
@@ -4106,14 +3650,14 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1F0BBC0-8387-4A2B-855A-0B1CE735F165}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="57" width="15.08984375"/>
-    <col min="2" max="2" customWidth="true" style="57" width="15.7265625"/>
-    <col min="3" max="3" customWidth="true" style="57" width="17.81640625"/>
-    <col min="4" max="4" customWidth="true" style="57" width="16.7265625"/>
-    <col min="5" max="5" customWidth="true" style="57" width="15.6328125"/>
-    <col min="6" max="16384" style="57" width="8.7265625"/>
+    <col min="1" max="1" customWidth="true" style="57" width="15.109375"/>
+    <col min="2" max="2" customWidth="true" style="57" width="15.77734375"/>
+    <col min="3" max="3" customWidth="true" style="57" width="17.77734375"/>
+    <col min="4" max="4" customWidth="true" style="57" width="16.77734375"/>
+    <col min="5" max="5" customWidth="true" style="57" width="15.6640625"/>
+    <col min="6" max="16384" style="57" width="8.77734375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4189,22 +3733,22 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:AB6"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="51.7265625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="9.453125"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="18.453125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="14.453125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="18.453125"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="18.453125"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="1" max="1" customWidth="true" width="51.77734375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.5546875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.21875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="9.44140625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="17.5546875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="12.21875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="18.44140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="12.21875"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="14.44140625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="15.44140625"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="12.21875"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="18.44140625"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="18.44140625"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="12.21875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28">
@@ -4322,31 +3866,31 @@
         <v>13</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>102</v>
+        <v>475</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>103</v>
+        <v>476</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>104</v>
+        <v>477</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>105</v>
+        <v>478</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>101</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>106</v>
+        <v>479</v>
       </c>
       <c r="S2" s="3" t="s">
         <v>14</v>
@@ -4392,16 +3936,16 @@
         <v>13</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>237</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>13</v>
@@ -4410,13 +3954,13 @@
         <v>14</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>238</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="S3" s="3" t="s">
         <v>14</v>
@@ -4522,16 +4066,16 @@
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>694</v>
+        <v>534</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>649</v>
+        <v>535</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>19</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>650</v>
+        <v>536</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>13</v>
@@ -4621,12 +4165,12 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="76.1796875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="13.453125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="76.21875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.21875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="13.44140625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="12.21875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4704,14 +4248,14 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEA2AF7E-AC89-4B47-B4D7-D3496E5327D5}">
   <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="57" width="18.453125"/>
-    <col min="2" max="2" customWidth="true" style="57" width="12.54296875"/>
-    <col min="3" max="3" customWidth="true" style="57" width="14.81640625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="57" width="11.7265625"/>
-    <col min="5" max="5" customWidth="true" style="57" width="18.1796875"/>
-    <col min="6" max="16384" style="57" width="8.7265625"/>
+    <col min="1" max="1" customWidth="true" style="57" width="18.44140625"/>
+    <col min="2" max="2" customWidth="true" style="57" width="12.5546875"/>
+    <col min="3" max="3" customWidth="true" style="57" width="14.77734375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="57" width="11.77734375"/>
+    <col min="5" max="5" customWidth="true" style="57" width="18.21875"/>
+    <col min="6" max="16384" style="57" width="8.77734375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4901,10 +4445,10 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F1569B0-3564-4B84-A0FB-9681D32A0E6D}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="12.54296875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="12.5546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.5546875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -4939,13 +4483,13 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02A4FAA4-EFC6-47D3-BDEE-7F4F3353F3CD}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="33.54296875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="13.453125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="33.5546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="13.44140625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.21875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="15.44140625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="12.21875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4990,7 +4534,7 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA6A106B-75A4-4F54-9508-A66A4AEED06E}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="6" t="s">
@@ -5092,32 +4636,32 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:AG4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="49.7265625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="4.81640625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="9.7265625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="4.453125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="9.7265625"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="4.453125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="9.7265625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="4.453125"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="9.7265625"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="4.453125"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="9.7265625"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="4.453125"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="9.7265625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="4.453125"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="9.7265625"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="4.453125"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="49.77734375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="4.77734375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="5.44140625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="9.77734375"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="4.44140625"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="5.44140625"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="9.77734375"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="4.44140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="5.44140625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="9.77734375"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="4.44140625"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="5.44140625"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="9.77734375"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="4.44140625"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="5.44140625"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="9.77734375"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="4.44140625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="5.44140625"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="9.77734375"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="4.44140625"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" width="5.44140625"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="9.77734375"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="4.44140625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" width="5.44140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33">
@@ -5424,9 +4968,9 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4903F224-3652-48FB-81A7-CAF06A9D7463}">
   <dimension ref="A1:AD9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.5546875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30">
@@ -5545,16 +5089,16 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3" t="s">
-        <v>510</v>
+        <v>403</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>511</v>
+        <v>404</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>48</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>512</v>
+        <v>405</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>13</v>
@@ -5609,16 +5153,16 @@
         <v>2</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>695</v>
+        <v>537</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>222</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="O3" s="3" t="s">
         <v>36</v>
@@ -5733,16 +5277,16 @@
         <v>5</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>514</v>
+        <v>406</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>511</v>
+        <v>404</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>48</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>512</v>
+        <v>405</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>13</v>
@@ -5751,7 +5295,7 @@
         <v>49</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>515</v>
+        <v>407</v>
       </c>
       <c r="R5" s="18" t="s">
         <v>48</v>
@@ -5941,16 +5485,16 @@
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3" t="s">
-        <v>518</v>
+        <v>408</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>511</v>
+        <v>404</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>48</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>512</v>
+        <v>405</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>13</v>
@@ -5984,13 +5528,13 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="35.26953125"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="11.54296875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="13.453125"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="35.21875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.21875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="15.44140625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="11.5546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="13.44140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -6069,10 +5613,10 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB53E397-0E70-4FE2-8956-CAC505C79FBA}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="33.54296875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="13.453125"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="33.5546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="13.44140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -6123,10 +5667,10 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71142910-3363-4189-996E-89090332A376}">
   <dimension ref="A1:AC4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="5" max="5" customWidth="true" width="6.26953125"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="13.90625"/>
+    <col min="5" max="5" customWidth="true" width="6.21875"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="13.88671875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -6254,16 +5798,16 @@
       <c r="U2" s="3"/>
       <c r="V2" s="3"/>
       <c r="W2" s="3" t="s">
-        <v>567</v>
+        <v>409</v>
       </c>
       <c r="X2" s="3" t="s">
-        <v>568</v>
+        <v>410</v>
       </c>
       <c r="Y2" s="3" t="s">
         <v>48</v>
       </c>
       <c r="Z2" s="3" t="s">
-        <v>569</v>
+        <v>411</v>
       </c>
       <c r="AA2" s="3" t="s">
         <v>13</v>
@@ -6272,7 +5816,7 @@
         <v>49</v>
       </c>
       <c r="AC2" s="3" t="s">
-        <v>570</v>
+        <v>412</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -6382,16 +5926,16 @@
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="s">
-        <v>571</v>
+        <v>413</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>568</v>
+        <v>410</v>
       </c>
       <c r="Y4" s="3" t="s">
         <v>48</v>
       </c>
       <c r="Z4" s="3" t="s">
-        <v>569</v>
+        <v>411</v>
       </c>
       <c r="AA4" s="3" t="s">
         <v>13</v>
@@ -6400,7 +5944,7 @@
         <v>49</v>
       </c>
       <c r="AC4" s="3" t="s">
-        <v>572</v>
+        <v>414</v>
       </c>
     </row>
   </sheetData>
@@ -6414,16 +5958,16 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="63.7265625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="10.7265625"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="63.77734375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="10.77734375"/>
     <col min="3" max="3" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="19.453125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="19.44140625"/>
     <col min="5" max="5" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="15.54296875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="15.5546875"/>
     <col min="7" max="7" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="8" max="9" bestFit="true" customWidth="true" width="19.453125"/>
+    <col min="8" max="9" bestFit="true" customWidth="true" width="19.44140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -6554,25 +6098,25 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:R6"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="12.0"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="9.453125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="6.26953125"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="13.81640625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="7.453125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="18.453125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="18.453125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="11.81640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.5546875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.21875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="9.44140625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="6.21875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="13.77734375"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="12.21875"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="15.44140625"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="12.21875"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="17.5546875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="7.44140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="18.44140625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="12.21875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="18.44140625"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="15.44140625"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="12.21875"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="11.77734375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -6836,7 +6380,7 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42BBEF64-F0EA-4EA8-9A62-F5A7DF1E4869}">
   <dimension ref="A1:U13"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:21">
       <c r="A1" s="39" t="s">
@@ -6932,16 +6476,16 @@
         <v>208</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>608</v>
+        <v>538</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>609</v>
+        <v>539</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>278</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>610</v>
+        <v>540</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>13</v>
@@ -6950,13 +6494,13 @@
         <v>279</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>611</v>
+        <v>541</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>280</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>612</v>
+        <v>542</v>
       </c>
       <c r="S2" s="3" t="s">
         <v>279</v>
@@ -6965,7 +6509,7 @@
         <v>208</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>613</v>
+        <v>543</v>
       </c>
     </row>
     <row r="3" spans="1:21">
@@ -7148,10 +6692,10 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="32.26953125"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="32.21875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.21875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -7194,7 +6738,7 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A51EFA8C-67A7-4B7E-8EF6-A12213F165A5}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="6" t="s">
@@ -7247,11 +6791,11 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFCF6FDB-3B87-457C-A3CA-7B39CE849651}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="57" width="24.90625"/>
-    <col min="2" max="2" customWidth="true" style="57" width="17.453125"/>
-    <col min="3" max="16384" style="57" width="8.7265625"/>
+    <col min="1" max="1" customWidth="true" style="57" width="24.88671875"/>
+    <col min="2" max="2" customWidth="true" style="57" width="17.44140625"/>
+    <col min="3" max="16384" style="57" width="8.77734375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -7458,16 +7002,16 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="39.453125"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="21.81640625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="9.453125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="6.453125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="18.453125"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="39.44140625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="21.77734375"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.21875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="15.44140625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="12.21875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="9.44140625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="6.44140625"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="18.44140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -7522,10 +7066,10 @@
         <v>65</v>
       </c>
       <c r="H2" s="26" t="s">
-        <v>681</v>
+        <v>485</v>
       </c>
       <c r="I2" s="26" t="s">
-        <v>682</v>
+        <v>486</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -7565,17 +7109,17 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="32.26953125"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="4" max="4" customWidth="true" width="15.453125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="32.21875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.21875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="15.44140625"/>
+    <col min="4" max="4" customWidth="true" width="15.44140625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="17.5546875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="12.21875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="15.44140625"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="12.21875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="17.5546875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -7729,18 +7273,18 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C03B3B8-DBFD-430F-BAEF-858DA603C137}">
   <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="57" width="17.90625"/>
-    <col min="2" max="2" customWidth="true" style="57" width="11.81640625"/>
+    <col min="1" max="1" customWidth="true" style="57" width="17.88671875"/>
+    <col min="2" max="2" customWidth="true" style="57" width="11.77734375"/>
     <col min="3" max="3" customWidth="true" style="57" width="13.0"/>
-    <col min="4" max="4" customWidth="true" style="57" width="16.54296875"/>
-    <col min="5" max="5" customWidth="true" style="57" width="15.81640625"/>
-    <col min="6" max="6" style="57" width="8.7265625"/>
-    <col min="7" max="7" customWidth="true" style="57" width="17.81640625"/>
-    <col min="8" max="8" customWidth="true" style="57" width="15.453125"/>
-    <col min="9" max="9" customWidth="true" style="57" width="11.54296875"/>
-    <col min="10" max="16384" style="57" width="8.7265625"/>
+    <col min="4" max="4" customWidth="true" style="57" width="16.5546875"/>
+    <col min="5" max="5" customWidth="true" style="57" width="15.77734375"/>
+    <col min="6" max="6" style="57" width="8.77734375"/>
+    <col min="7" max="7" customWidth="true" style="57" width="17.77734375"/>
+    <col min="8" max="8" customWidth="true" style="57" width="15.44140625"/>
+    <col min="9" max="9" customWidth="true" style="57" width="11.5546875"/>
+    <col min="10" max="16384" style="57" width="8.77734375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -7748,7 +7292,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="61" t="s">
-        <v>454</v>
+        <v>389</v>
       </c>
       <c r="C1" s="61" t="s">
         <v>1</v>
@@ -7763,24 +7307,24 @@
         <v>98</v>
       </c>
       <c r="G1" s="61" t="s">
-        <v>455</v>
+        <v>390</v>
       </c>
       <c r="H1" s="61" t="s">
-        <v>456</v>
+        <v>391</v>
       </c>
       <c r="I1" s="61" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="J1" s="61" t="s">
-        <v>458</v>
+        <v>393</v>
       </c>
       <c r="K1" s="61" t="s">
-        <v>459</v>
+        <v>394</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="60" t="s">
-        <v>460</v>
+        <v>395</v>
       </c>
       <c r="B2" s="60" t="s">
         <v>194</v>
@@ -7795,7 +7339,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="60" t="s">
-        <v>468</v>
+        <v>400</v>
       </c>
       <c r="G2" s="60">
         <v>2</v>
@@ -7811,7 +7355,7 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="60" t="s">
-        <v>462</v>
+        <v>396</v>
       </c>
       <c r="B3" s="60" t="s">
         <v>194</v>
@@ -7826,21 +7370,21 @@
         <v>1</v>
       </c>
       <c r="F3" s="60" t="s">
-        <v>469</v>
+        <v>401</v>
       </c>
       <c r="G3" s="60"/>
       <c r="H3" s="60"/>
       <c r="I3" s="60"/>
       <c r="J3" s="62" t="s">
-        <v>464</v>
+        <v>397</v>
       </c>
       <c r="K3" s="60" t="s">
-        <v>465</v>
+        <v>398</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="60" t="s">
-        <v>466</v>
+        <v>399</v>
       </c>
       <c r="B4" s="60" t="s">
         <v>194</v>
@@ -7855,7 +7399,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="60" t="s">
-        <v>470</v>
+        <v>402</v>
       </c>
       <c r="G4" s="60"/>
       <c r="H4" s="60"/>
@@ -7874,13 +7418,13 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="39.453125"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="13.54296875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="7.7265625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="9.7265625"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="39.44140625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="13.5546875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="7.77734375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="5.44140625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="9.77734375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -7946,13 +7490,12 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="57.453125"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="15.54296875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="7.7265625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="11.1796875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="11.26953125"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="57.44140625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="15.5546875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="7.77734375"/>
+    <col min="4" max="5" bestFit="true" customWidth="true" width="11.21875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -8067,24 +7610,24 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:P5"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" style="45" width="42.0"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="45" width="18.36328125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="45" width="12.08984375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="45" width="15.36328125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="45" width="12.1796875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="45" width="9.453125"/>
-    <col min="7" max="8" style="45" width="8.7265625"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="45" width="10.453125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="45" width="11.26953125"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="45" width="10.453125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="45" width="11.26953125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="45" width="10.453125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="45" width="8.26953125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="45" width="18.33203125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="45" width="12.109375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="45" width="15.33203125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="45" width="12.21875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="45" width="9.44140625"/>
+    <col min="7" max="8" style="45" width="8.77734375"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="45" width="10.44140625"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="45" width="11.21875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="45" width="10.44140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="45" width="11.21875"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="45" width="10.44140625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="45" width="8.21875"/>
     <col min="15" max="15" customWidth="true" style="45" width="13.0"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" style="45" width="10.1796875"/>
-    <col min="17" max="16384" style="45" width="8.7265625"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="45" width="10.21875"/>
+    <col min="17" max="16384" style="45" width="8.77734375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -8171,7 +7714,7 @@
       <c r="M2" s="48"/>
       <c r="N2" s="48"/>
       <c r="O2" s="48" t="s">
-        <v>661</v>
+        <v>488</v>
       </c>
       <c r="P2" s="48"/>
     </row>
@@ -8276,31 +7819,31 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:AB7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="44.7265625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.7265625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="8.1796875"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="44.77734375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.77734375"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="8.21875"/>
     <col min="4" max="4" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="11.26953125"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="10.453125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="13.54296875"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="17.7265625"/>
-    <col min="11" max="12" bestFit="true" customWidth="true" width="11.26953125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="18.1796875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="11.21875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="10.44140625"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="13.5546875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="12.21875"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="17.77734375"/>
+    <col min="11" max="12" bestFit="true" customWidth="true" width="11.21875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="18.21875"/>
     <col min="16" max="16" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="7.7265625"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="11.26953125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="8.26953125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="7.77734375"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="11.21875"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="8.21875"/>
     <col min="22" max="22" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="11.26953125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="11.21875"/>
     <col min="24" max="24" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="11.26953125"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="14.26953125"/>
-    <col min="27" max="28" bestFit="true" customWidth="true" width="12.81640625"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="14.26953125"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="12.81640625"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="11.21875"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="14.21875"/>
+    <col min="27" max="28" bestFit="true" customWidth="true" width="12.77734375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="14.21875"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="12.77734375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28">
@@ -8665,11 +8208,11 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:W17"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="54.36328125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="13.90625"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="13.81640625"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="54.33203125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="13.88671875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="13.77734375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -8772,10 +8315,10 @@
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
       <c r="R2" s="3" t="s">
-        <v>624</v>
+        <v>489</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>625</v>
+        <v>490</v>
       </c>
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
@@ -9034,10 +8577,10 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3" t="s">
-        <v>626</v>
+        <v>491</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>627</v>
+        <v>492</v>
       </c>
       <c r="T8" s="3">
         <v>0</v>
@@ -9083,10 +8626,10 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3" t="s">
-        <v>255</v>
+        <v>493</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>256</v>
+        <v>494</v>
       </c>
       <c r="T9" s="3"/>
       <c r="U9" s="3">
@@ -9362,10 +8905,10 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
@@ -9418,18 +8961,18 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:S20"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="53.81640625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="3" max="4" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="5" max="7" customWidth="true" width="12.1796875"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="53.77734375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.5546875"/>
+    <col min="3" max="4" bestFit="true" customWidth="true" width="12.21875"/>
+    <col min="5" max="7" customWidth="true" width="12.21875"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="15.44140625"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="12.21875"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="17.5546875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="12.21875"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="15.44140625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="12.21875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19">

--- a/src/test/java/TestData/Scenario_TestData.xlsx
+++ b/src/test/java/TestData/Scenario_TestData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ArunJK\Arun\Copa_SHDWebservices\src\test\java\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Copa_SHD_WebServices\src\test\java\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82EFF842-C683-47FF-ACC8-4B571910F53C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AC08DA2-780B-4877-BF49-1094BB8DC7B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{5D5A4724-D560-4FC2-9708-4BBF1DBA0B11}"/>
+    <workbookView xWindow="3470" yWindow="2840" windowWidth="14400" windowHeight="7360" activeTab="2" xr2:uid="{5D5A4724-D560-4FC2-9708-4BBF1DBA0B11}"/>
   </bookViews>
   <sheets>
     <sheet name="AdvancePassengerInfo" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1385" uniqueCount="470">
   <si>
     <t>Scenario</t>
   </si>
@@ -269,9 +269,6 @@
     <t>Code_12_Passengers_with_advance_seats</t>
   </si>
   <si>
-    <t>K</t>
-  </si>
-  <si>
     <t>DepartureDate</t>
   </si>
   <si>
@@ -374,21 +371,6 @@
     <t>173</t>
   </si>
   <si>
-    <t>AJHUPU</t>
-  </si>
-  <si>
-    <t>2023-02-15T05:03:00</t>
-  </si>
-  <si>
-    <t>2023-02-15T06:54:00</t>
-  </si>
-  <si>
-    <t>2023-02-18T05:15:00</t>
-  </si>
-  <si>
-    <t>2023-02-18T08:32:00</t>
-  </si>
-  <si>
     <t>Itinerary Changes</t>
   </si>
   <si>
@@ -833,12 +815,6 @@
     <t>NotValidAfter/Before</t>
   </si>
   <si>
-    <t>ACHZQK</t>
-  </si>
-  <si>
-    <t>2302181242495</t>
-  </si>
-  <si>
     <t>ACJERP</t>
   </si>
   <si>
@@ -1313,186 +1289,6 @@
     <t>2302181931005</t>
   </si>
   <si>
-    <t>ACR3ZE</t>
-  </si>
-  <si>
-    <t>2302181955114</t>
-  </si>
-  <si>
-    <t>ACR5AJ</t>
-  </si>
-  <si>
-    <t>ACR5AM</t>
-  </si>
-  <si>
-    <t>ACR5CL</t>
-  </si>
-  <si>
-    <t>2302181955117</t>
-  </si>
-  <si>
-    <t>ACR5EH</t>
-  </si>
-  <si>
-    <t>2302181955118</t>
-  </si>
-  <si>
-    <t>ACR5FY</t>
-  </si>
-  <si>
-    <t>ACR5FZ</t>
-  </si>
-  <si>
-    <t>ACR5F0</t>
-  </si>
-  <si>
-    <t>2302181955119</t>
-  </si>
-  <si>
-    <t>ACR5GD</t>
-  </si>
-  <si>
-    <t>2302181955120</t>
-  </si>
-  <si>
-    <t>ACR5GO</t>
-  </si>
-  <si>
-    <t>2302181955121</t>
-  </si>
-  <si>
-    <t>ACR5HN</t>
-  </si>
-  <si>
-    <t>ACR5IE</t>
-  </si>
-  <si>
-    <t>2302181955122</t>
-  </si>
-  <si>
-    <t>ACSFKM</t>
-  </si>
-  <si>
-    <t>2023-07-08T07:38:00</t>
-  </si>
-  <si>
-    <t>2023-07-08T12:03:00</t>
-  </si>
-  <si>
-    <t>2023-07-08T14:02:00</t>
-  </si>
-  <si>
-    <t>2023-07-08T15:33:00</t>
-  </si>
-  <si>
-    <t>2302181955125</t>
-  </si>
-  <si>
-    <t>BKPCA2</t>
-  </si>
-  <si>
-    <t>2302182476441</t>
-  </si>
-  <si>
-    <t>BKPCXW</t>
-  </si>
-  <si>
-    <t>2302182476442</t>
-  </si>
-  <si>
-    <t>BKPDLD</t>
-  </si>
-  <si>
-    <t>2302182476443</t>
-  </si>
-  <si>
-    <t>BKPEPN</t>
-  </si>
-  <si>
-    <t>2302182476444</t>
-  </si>
-  <si>
-    <t>BKPETM</t>
-  </si>
-  <si>
-    <t>2302182476445</t>
-  </si>
-  <si>
-    <t>BKPE5K</t>
-  </si>
-  <si>
-    <t>BKPFHW</t>
-  </si>
-  <si>
-    <t>BKPFK2</t>
-  </si>
-  <si>
-    <t>2023-07-17T07:59:00</t>
-  </si>
-  <si>
-    <t>2023-07-17T12:07:00</t>
-  </si>
-  <si>
-    <t>BKPXHF</t>
-  </si>
-  <si>
-    <t>BKSO3R</t>
-  </si>
-  <si>
-    <t>2023-07-14T07:36:55</t>
-  </si>
-  <si>
-    <t>BKSTSP</t>
-  </si>
-  <si>
-    <t>BKSUWK</t>
-  </si>
-  <si>
-    <t>2302182476519</t>
-  </si>
-  <si>
-    <t>2302182476520</t>
-  </si>
-  <si>
-    <t>BKSU3W</t>
-  </si>
-  <si>
-    <t>438C0373CMCMRPCT05C8D23EE3</t>
-  </si>
-  <si>
-    <t>3A9DD03ACMCMRPCT06CEC75A1A</t>
-  </si>
-  <si>
-    <t>87FF72DDCMCMRPCT05F085B079</t>
-  </si>
-  <si>
-    <t>BKS5ZE</t>
-  </si>
-  <si>
-    <t>BKTAYM</t>
-  </si>
-  <si>
-    <t>BOFXGU</t>
-  </si>
-  <si>
-    <t>BOFXGV</t>
-  </si>
-  <si>
-    <t>BOHBI2</t>
-  </si>
-  <si>
-    <t>BOHBYS</t>
-  </si>
-  <si>
-    <t>BOHB4D</t>
-  </si>
-  <si>
-    <t>BOHB5M</t>
-  </si>
-  <si>
-    <t>BO2Z2E</t>
-  </si>
-  <si>
     <t>BO2Z3G</t>
   </si>
   <si>
@@ -1508,99 +1304,15 @@
     <t>2023-07-25T08:32:00</t>
   </si>
   <si>
-    <t>BO2Z33</t>
-  </si>
-  <si>
-    <t>BO2Z4L</t>
-  </si>
-  <si>
-    <t>BO2Z4T</t>
-  </si>
-  <si>
-    <t>BO2Z5V</t>
-  </si>
-  <si>
-    <t>2023-07-20T06:19:55</t>
-  </si>
-  <si>
-    <t>BO20EG</t>
-  </si>
-  <si>
-    <t>2023-07-20T06:20:03</t>
-  </si>
-  <si>
-    <t>BO20IH</t>
-  </si>
-  <si>
-    <t>BO20IZ</t>
-  </si>
-  <si>
-    <t>BO20JR</t>
-  </si>
-  <si>
-    <t>2302182500173</t>
-  </si>
-  <si>
-    <t>BO20OM</t>
-  </si>
-  <si>
-    <t>2302182500174</t>
-  </si>
-  <si>
     <t>BO20PH</t>
   </si>
   <si>
     <t>2302182500175</t>
   </si>
   <si>
-    <t>BO20VH</t>
-  </si>
-  <si>
-    <t>2302182500177</t>
-  </si>
-  <si>
-    <t>BO20XK</t>
-  </si>
-  <si>
-    <t>2302182500178</t>
-  </si>
-  <si>
-    <t>BO20YY</t>
-  </si>
-  <si>
-    <t>2302182500179</t>
-  </si>
-  <si>
-    <t>BO201E</t>
-  </si>
-  <si>
-    <t>2302182500180</t>
-  </si>
-  <si>
-    <t>BO203N</t>
-  </si>
-  <si>
-    <t>BO2042</t>
-  </si>
-  <si>
-    <t>BO205P</t>
-  </si>
-  <si>
     <t>BO21AP</t>
   </si>
   <si>
-    <t>BO21B2</t>
-  </si>
-  <si>
-    <t>BO21C3</t>
-  </si>
-  <si>
-    <t>2302182500181</t>
-  </si>
-  <si>
-    <t>BO21EE</t>
-  </si>
-  <si>
     <t>BO21E5</t>
   </si>
   <si>
@@ -1640,51 +1352,12 @@
     <t>2302182500186</t>
   </si>
   <si>
-    <t>BO21NY</t>
-  </si>
-  <si>
-    <t>2302182500187</t>
-  </si>
-  <si>
-    <t>2302182500188</t>
-  </si>
-  <si>
-    <t>BO21QA</t>
-  </si>
-  <si>
-    <t>2302182500189</t>
-  </si>
-  <si>
-    <t>2302182500190</t>
-  </si>
-  <si>
-    <t>BO21TA</t>
-  </si>
-  <si>
-    <t>8B3FE1E8CMCMRPCT069905EE9C</t>
-  </si>
-  <si>
-    <t>6A2E6A7ECMCMRPCT07AF12B404</t>
-  </si>
-  <si>
-    <t>96D65F1ACMCMRPCT053BF6616C</t>
-  </si>
-  <si>
-    <t>BO223M</t>
-  </si>
-  <si>
     <t>2023-07-23T07:59:00</t>
   </si>
   <si>
     <t>2023-07-23T12:07:00</t>
   </si>
   <si>
-    <t>BO23AW</t>
-  </si>
-  <si>
-    <t>BO23JG</t>
-  </si>
-  <si>
     <t>2023-07-21T07:47:00</t>
   </si>
   <si>
@@ -1697,14 +1370,118 @@
     <t>2023-07-21T15:33:00</t>
   </si>
   <si>
-    <t>2302182500195</t>
+    <t>BPG42L</t>
+  </si>
+  <si>
+    <t>BPG42T</t>
+  </si>
+  <si>
+    <t>BPG5BB</t>
+  </si>
+  <si>
+    <t>BPG5CJ</t>
+  </si>
+  <si>
+    <t>2302182501288</t>
+  </si>
+  <si>
+    <t>BPG5HG</t>
+  </si>
+  <si>
+    <t>2302182501289</t>
+  </si>
+  <si>
+    <t>BPG5JC</t>
+  </si>
+  <si>
+    <t>2302182501291</t>
+  </si>
+  <si>
+    <t>BPG5JL</t>
+  </si>
+  <si>
+    <t>2302182501292</t>
+  </si>
+  <si>
+    <t>BPG5KA</t>
+  </si>
+  <si>
+    <t>2302182501293</t>
+  </si>
+  <si>
+    <t>BPG5KT</t>
+  </si>
+  <si>
+    <t>2302182501294</t>
+  </si>
+  <si>
+    <t>BPG5LH</t>
+  </si>
+  <si>
+    <t>BPG5NX</t>
+  </si>
+  <si>
+    <t>BPG5P5</t>
+  </si>
+  <si>
+    <t>BPG5TC</t>
+  </si>
+  <si>
+    <t>BPG5T3</t>
+  </si>
+  <si>
+    <t>2302182501298</t>
+  </si>
+  <si>
+    <t>BPG5VP</t>
+  </si>
+  <si>
+    <t>BPG51D</t>
+  </si>
+  <si>
+    <t>2302182501311</t>
+  </si>
+  <si>
+    <t>2302182501312</t>
+  </si>
+  <si>
+    <t>BPG512</t>
+  </si>
+  <si>
+    <t>C0E16F02CMCMRPCT071FF18293</t>
+  </si>
+  <si>
+    <t>DBAD02D0CMCMRPCT0663B7D5C5</t>
+  </si>
+  <si>
+    <t>D9BDC8EFCMCMRPCT080F5FAFAB</t>
+  </si>
+  <si>
+    <t>BPHAW2</t>
+  </si>
+  <si>
+    <t>BPHAZZ</t>
+  </si>
+  <si>
+    <t>BPHA3T</t>
+  </si>
+  <si>
+    <t>2302182501332</t>
+  </si>
+  <si>
+    <t>BRHYDG</t>
+  </si>
+  <si>
+    <t>2023-07-23T14:29:21</t>
+  </si>
+  <si>
+    <t>C</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="9">
     <font>
       <sz val="11"/>
@@ -2299,22 +2076,22 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:P15"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="52.77734375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="18.44140625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="15.44140625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="9.44140625"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="17.5546875"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="10.44140625"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="11.21875"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="10.44140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="11.21875"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="10.44140625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="11.21875"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="15.21875"/>
+    <col min="1" max="1" width="52.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2387,24 +2164,24 @@
         <v>16</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>481</v>
+        <v>434</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
       <c r="O2" s="3" t="s">
-        <v>482</v>
+        <v>435</v>
       </c>
       <c r="P2" s="24"/>
     </row>
@@ -2474,10 +2251,10 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C501783-003E-43C7-BF08-448ED073E85B}">
   <dimension ref="A1:U22"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="10" max="10" style="45" width="8.77734375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="9.77734375"/>
+    <col min="10" max="10" width="8.81640625" style="45"/>
+    <col min="17" max="17" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
@@ -2491,10 +2268,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="40" t="s">
+        <v>95</v>
+      </c>
+      <c r="E1" s="40" t="s">
         <v>96</v>
-      </c>
-      <c r="E1" s="40" t="s">
-        <v>97</v>
       </c>
       <c r="F1" s="40" t="s">
         <v>1</v>
@@ -2503,22 +2280,22 @@
         <v>2</v>
       </c>
       <c r="H1" s="40" t="s">
+        <v>95</v>
+      </c>
+      <c r="I1" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="I1" s="40" t="s">
+      <c r="J1" s="40" t="s">
+        <v>178</v>
+      </c>
+      <c r="K1" s="54" t="s">
         <v>97</v>
       </c>
-      <c r="J1" s="40" t="s">
-        <v>184</v>
-      </c>
-      <c r="K1" s="54" t="s">
-        <v>98</v>
-      </c>
       <c r="L1" s="54" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="M1" s="40" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="N1" s="32" t="s">
         <v>8</v>
@@ -2530,30 +2307,30 @@
         <v>10</v>
       </c>
       <c r="Q1" s="36" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="R1" s="47" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="S1" s="46" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="T1" s="47" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="U1" s="47" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2" spans="1:21">
       <c r="A2" s="53" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="B2" s="48">
         <v>1</v>
       </c>
       <c r="C2" s="50" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D2" s="48" t="s">
         <v>13</v>
@@ -2565,7 +2342,7 @@
         <v>2</v>
       </c>
       <c r="G2" s="50" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="H2" s="48" t="s">
         <v>49</v>
@@ -2575,7 +2352,7 @@
       </c>
       <c r="J2" s="48"/>
       <c r="K2" s="48" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="L2" s="48"/>
       <c r="M2" s="48"/>
@@ -2590,13 +2367,13 @@
     </row>
     <row r="3" spans="1:21">
       <c r="A3" s="53" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="B3" s="48">
         <v>1</v>
       </c>
       <c r="C3" s="50" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D3" s="48" t="s">
         <v>13</v>
@@ -2612,10 +2389,10 @@
         <v>0</v>
       </c>
       <c r="K3" s="48" t="s">
-        <v>508</v>
+        <v>453</v>
       </c>
       <c r="L3" s="48" t="s">
-        <v>509</v>
+        <v>454</v>
       </c>
       <c r="M3" s="48"/>
       <c r="N3" s="48"/>
@@ -2629,7 +2406,7 @@
     </row>
     <row r="4" spans="1:21">
       <c r="A4" s="53" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
@@ -2643,7 +2420,7 @@
       <c r="K4" s="48"/>
       <c r="L4" s="48"/>
       <c r="M4" s="48" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="N4" s="48"/>
       <c r="O4" s="48"/>
@@ -2656,13 +2433,13 @@
     </row>
     <row r="5" spans="1:21">
       <c r="A5" s="53" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="B5" s="48">
         <v>1</v>
       </c>
       <c r="C5" s="50" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D5" s="48" t="s">
         <v>13</v>
@@ -2676,40 +2453,40 @@
       <c r="I5" s="48"/>
       <c r="J5" s="48"/>
       <c r="K5" s="48" t="s">
-        <v>511</v>
+        <v>415</v>
       </c>
       <c r="L5" s="48" t="s">
-        <v>512</v>
+        <v>416</v>
       </c>
       <c r="M5" s="48"/>
       <c r="N5" s="48" t="s">
         <v>22</v>
       </c>
       <c r="O5" s="48" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="P5" s="48" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="Q5" s="37"/>
       <c r="R5" s="48"/>
       <c r="S5" s="48"/>
       <c r="T5" s="48" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="U5" s="48" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6" spans="1:21">
       <c r="A6" s="53" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="B6" s="48">
         <v>1</v>
       </c>
       <c r="C6" s="50" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>13</v>
@@ -2723,7 +2500,7 @@
       <c r="I6" s="48"/>
       <c r="J6" s="48"/>
       <c r="K6" s="48" t="s">
-        <v>513</v>
+        <v>417</v>
       </c>
       <c r="L6" s="48"/>
       <c r="M6" s="48"/>
@@ -2731,30 +2508,30 @@
         <v>22</v>
       </c>
       <c r="O6" s="48" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="P6" s="48" t="s">
-        <v>514</v>
+        <v>418</v>
       </c>
       <c r="Q6" s="37"/>
       <c r="R6" s="48"/>
       <c r="S6" s="48"/>
       <c r="T6" s="48" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="U6" s="48" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7" spans="1:21">
       <c r="A7" s="53" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="B7" s="48">
         <v>1</v>
       </c>
       <c r="C7" s="50" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D7" s="48" t="s">
         <v>13</v>
@@ -2768,26 +2545,26 @@
       <c r="I7" s="48"/>
       <c r="J7" s="48"/>
       <c r="K7" s="48" t="s">
-        <v>515</v>
+        <v>419</v>
       </c>
       <c r="L7" s="48" t="s">
-        <v>516</v>
+        <v>420</v>
       </c>
       <c r="M7" s="48"/>
       <c r="N7" s="48" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="O7" s="48" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="P7" s="48" t="s">
-        <v>517</v>
+        <v>421</v>
       </c>
       <c r="Q7" s="55" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="R7" s="48" t="s">
-        <v>518</v>
+        <v>422</v>
       </c>
       <c r="S7" s="48"/>
       <c r="T7" s="48"/>
@@ -2795,13 +2572,13 @@
     </row>
     <row r="8" spans="1:21">
       <c r="A8" s="53" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="B8" s="48">
         <v>1</v>
       </c>
       <c r="C8" s="50" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D8" s="48" t="s">
         <v>13</v>
@@ -2813,7 +2590,7 @@
         <v>2</v>
       </c>
       <c r="G8" s="50" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="H8" s="48" t="s">
         <v>49</v>
@@ -2823,17 +2600,17 @@
       </c>
       <c r="J8" s="48"/>
       <c r="K8" s="48" t="s">
-        <v>519</v>
+        <v>423</v>
       </c>
       <c r="L8" s="48" t="s">
-        <v>520</v>
+        <v>424</v>
       </c>
       <c r="M8" s="48"/>
       <c r="N8" s="48" t="s">
         <v>22</v>
       </c>
       <c r="O8" s="48" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="P8" s="48"/>
       <c r="Q8" s="37"/>
@@ -2844,13 +2621,13 @@
     </row>
     <row r="9" spans="1:21">
       <c r="A9" s="53" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="B9" s="48">
         <v>1</v>
       </c>
       <c r="C9" s="50" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D9" s="48" t="s">
         <v>13</v>
@@ -2864,7 +2641,7 @@
       <c r="I9" s="48"/>
       <c r="J9" s="48"/>
       <c r="K9" s="48" t="s">
-        <v>521</v>
+        <v>425</v>
       </c>
       <c r="L9" s="48"/>
       <c r="M9" s="48"/>
@@ -2872,7 +2649,7 @@
         <v>22</v>
       </c>
       <c r="O9" s="48" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="P9" s="48"/>
       <c r="Q9" s="37"/>
@@ -2883,13 +2660,13 @@
     </row>
     <row r="10" spans="1:21">
       <c r="A10" s="53" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="B10" s="48">
         <v>1</v>
       </c>
       <c r="C10" s="50" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D10" s="48" t="s">
         <v>13</v>
@@ -2903,10 +2680,10 @@
       <c r="I10" s="48"/>
       <c r="J10" s="48"/>
       <c r="K10" s="48" t="s">
-        <v>522</v>
+        <v>426</v>
       </c>
       <c r="L10" s="48" t="s">
-        <v>523</v>
+        <v>427</v>
       </c>
       <c r="M10" s="48"/>
       <c r="N10" s="48"/>
@@ -2915,20 +2692,20 @@
       <c r="Q10" s="37"/>
       <c r="R10" s="48"/>
       <c r="S10" s="50" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="T10" s="48"/>
       <c r="U10" s="48"/>
     </row>
     <row r="11" spans="1:21">
       <c r="A11" s="53" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="B11" s="48">
         <v>1</v>
       </c>
       <c r="C11" s="50" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D11" s="48" t="s">
         <v>13</v>
@@ -2942,10 +2719,10 @@
       <c r="I11" s="48"/>
       <c r="J11" s="48"/>
       <c r="K11" s="48" t="s">
-        <v>495</v>
+        <v>441</v>
       </c>
       <c r="L11" s="48" t="s">
-        <v>496</v>
+        <v>442</v>
       </c>
       <c r="M11" s="48"/>
       <c r="N11" s="48"/>
@@ -2954,20 +2731,20 @@
       <c r="Q11" s="37"/>
       <c r="R11" s="48"/>
       <c r="S11" s="50" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="T11" s="48"/>
       <c r="U11" s="48"/>
     </row>
     <row r="12" spans="1:21">
       <c r="A12" s="53" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="B12" s="48">
         <v>1</v>
       </c>
       <c r="C12" s="50" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D12" s="48" t="s">
         <v>13</v>
@@ -2981,21 +2758,21 @@
       <c r="I12" s="48"/>
       <c r="J12" s="48"/>
       <c r="K12" s="48" t="s">
-        <v>497</v>
+        <v>443</v>
       </c>
       <c r="L12" s="48" t="s">
-        <v>498</v>
+        <v>444</v>
       </c>
       <c r="M12" s="48"/>
       <c r="N12" s="48" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="O12" s="48" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="P12" s="48"/>
       <c r="Q12" s="55" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="R12" s="48"/>
       <c r="S12" s="48"/>
@@ -3004,13 +2781,13 @@
     </row>
     <row r="13" spans="1:21">
       <c r="A13" s="53" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="B13" s="48">
         <v>1</v>
       </c>
       <c r="C13" s="50" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D13" s="48" t="s">
         <v>13</v>
@@ -3024,36 +2801,36 @@
       <c r="I13" s="48"/>
       <c r="J13" s="48"/>
       <c r="K13" s="48" t="s">
-        <v>499</v>
+        <v>445</v>
       </c>
       <c r="L13" s="48" t="s">
-        <v>500</v>
+        <v>446</v>
       </c>
       <c r="M13" s="48"/>
       <c r="N13" s="48" t="s">
         <v>22</v>
       </c>
       <c r="O13" s="48" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="P13" s="48"/>
       <c r="Q13" s="37"/>
       <c r="R13" s="48"/>
       <c r="S13" s="50" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="T13" s="48"/>
       <c r="U13" s="48"/>
     </row>
     <row r="14" spans="1:21">
       <c r="A14" s="53" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="B14" s="48">
         <v>1</v>
       </c>
       <c r="C14" s="50" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D14" s="48" t="s">
         <v>13</v>
@@ -3075,20 +2852,20 @@
       <c r="Q14" s="37"/>
       <c r="R14" s="48"/>
       <c r="S14" s="50" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="T14" s="48"/>
       <c r="U14" s="48"/>
     </row>
     <row r="15" spans="1:21">
       <c r="A15" s="53" t="s">
+        <v>287</v>
+      </c>
+      <c r="B15" s="48">
+        <v>1</v>
+      </c>
+      <c r="C15" s="50" t="s">
         <v>295</v>
-      </c>
-      <c r="B15" s="48">
-        <v>1</v>
-      </c>
-      <c r="C15" s="50" t="s">
-        <v>303</v>
       </c>
       <c r="D15" s="48" t="s">
         <v>13</v>
@@ -3102,36 +2879,36 @@
       <c r="I15" s="48"/>
       <c r="J15" s="48"/>
       <c r="K15" s="48" t="s">
-        <v>501</v>
+        <v>447</v>
       </c>
       <c r="L15" s="48" t="s">
-        <v>502</v>
+        <v>448</v>
       </c>
       <c r="M15" s="48"/>
       <c r="N15" s="48" t="s">
         <v>22</v>
       </c>
       <c r="O15" s="48" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="P15" s="48"/>
       <c r="Q15" s="37"/>
       <c r="R15" s="48"/>
       <c r="S15" s="50" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="T15" s="48"/>
       <c r="U15" s="48"/>
     </row>
     <row r="16" spans="1:21">
       <c r="A16" s="53" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="B16" s="48">
         <v>1</v>
       </c>
       <c r="C16" s="50" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D16" s="48" t="s">
         <v>13</v>
@@ -3145,7 +2922,7 @@
       <c r="I16" s="48"/>
       <c r="J16" s="48"/>
       <c r="K16" s="48" t="s">
-        <v>503</v>
+        <v>449</v>
       </c>
       <c r="L16" s="48"/>
       <c r="M16" s="48"/>
@@ -3153,7 +2930,7 @@
         <v>22</v>
       </c>
       <c r="O16" s="48" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="P16" s="48"/>
       <c r="Q16" s="37"/>
@@ -3164,13 +2941,13 @@
     </row>
     <row r="17" spans="1:21">
       <c r="A17" s="53" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="B17" s="48">
         <v>1</v>
       </c>
       <c r="C17" s="50" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D17" s="48" t="s">
         <v>13</v>
@@ -3184,7 +2961,7 @@
       <c r="I17" s="48"/>
       <c r="J17" s="48"/>
       <c r="K17" s="48" t="s">
-        <v>504</v>
+        <v>450</v>
       </c>
       <c r="L17" s="48"/>
       <c r="M17" s="48"/>
@@ -3199,13 +2976,13 @@
     </row>
     <row r="18" spans="1:21">
       <c r="A18" s="53" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="B18" s="48">
         <v>1</v>
       </c>
       <c r="C18" s="50" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D18" s="48" t="s">
         <v>13</v>
@@ -3217,7 +2994,7 @@
         <v>2</v>
       </c>
       <c r="G18" s="50" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="H18" s="48" t="s">
         <v>49</v>
@@ -3227,15 +3004,15 @@
       </c>
       <c r="J18" s="48"/>
       <c r="K18" s="48" t="s">
-        <v>505</v>
+        <v>451</v>
       </c>
       <c r="L18" s="48"/>
       <c r="M18" s="48"/>
       <c r="N18" s="48" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="O18" s="48" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="P18" s="48"/>
       <c r="Q18" s="37"/>
@@ -3246,13 +3023,13 @@
     </row>
     <row r="19" spans="1:21">
       <c r="A19" s="53" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="B19" s="48">
         <v>1</v>
       </c>
       <c r="C19" s="50" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D19" s="48" t="s">
         <v>13</v>
@@ -3266,15 +3043,15 @@
       <c r="I19" s="48"/>
       <c r="J19" s="48"/>
       <c r="K19" s="48" t="s">
-        <v>506</v>
+        <v>414</v>
       </c>
       <c r="L19" s="48"/>
       <c r="M19" s="48"/>
       <c r="N19" s="48" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="O19" s="48" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="P19" s="48"/>
       <c r="Q19" s="37"/>
@@ -3285,13 +3062,13 @@
     </row>
     <row r="20" spans="1:21">
       <c r="A20" s="53" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="B20" s="48">
         <v>1</v>
       </c>
       <c r="C20" s="50" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D20" s="48" t="s">
         <v>13</v>
@@ -3305,7 +3082,7 @@
       <c r="I20" s="48"/>
       <c r="J20" s="48"/>
       <c r="K20" s="48" t="s">
-        <v>507</v>
+        <v>452</v>
       </c>
       <c r="L20" s="48"/>
       <c r="M20" s="48"/>
@@ -3313,7 +3090,7 @@
         <v>22</v>
       </c>
       <c r="O20" s="48" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="P20" s="48"/>
       <c r="Q20" s="37"/>
@@ -3324,19 +3101,19 @@
     </row>
     <row r="21" spans="1:21">
       <c r="A21" s="53" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="B21" s="48">
         <v>1</v>
       </c>
       <c r="C21" s="50" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="D21" s="48" t="s">
         <v>13</v>
       </c>
       <c r="E21" s="48" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="F21" s="48"/>
       <c r="G21" s="48"/>
@@ -3344,7 +3121,7 @@
       <c r="I21" s="48"/>
       <c r="J21" s="48"/>
       <c r="K21" s="48" t="s">
-        <v>510</v>
+        <v>455</v>
       </c>
       <c r="L21" s="48"/>
       <c r="M21" s="48"/>
@@ -3352,7 +3129,7 @@
         <v>22</v>
       </c>
       <c r="O21" s="48" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="P21" s="48"/>
       <c r="Q21" s="37"/>
@@ -3363,13 +3140,13 @@
     </row>
     <row r="22" spans="1:21">
       <c r="A22" s="53" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="B22" s="48">
         <v>1</v>
       </c>
       <c r="C22" s="50" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D22" s="48" t="s">
         <v>13</v>
@@ -3402,14 +3179,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2EA1F88-8B75-4AAD-A17A-063CA3659CA4}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="32.88671875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.5546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="14.33203125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="30.33203125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="6.88671875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="10.88671875"/>
+    <col min="1" max="1" width="32.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -3420,22 +3197,22 @@
         <v>1</v>
       </c>
       <c r="C1" s="58" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D1" s="59" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="E1" s="59" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F1" s="58" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="G1" s="63"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="63" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="B2" s="60">
         <v>2</v>
@@ -3444,17 +3221,17 @@
         <v>2</v>
       </c>
       <c r="D2" s="62" t="s">
-        <v>531</v>
+        <v>460</v>
       </c>
       <c r="E2" s="62" t="s">
-        <v>530</v>
+        <v>459</v>
       </c>
       <c r="F2" s="60"/>
       <c r="G2" s="63"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="60" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="B3" s="60">
         <v>2</v>
@@ -3463,19 +3240,19 @@
         <v>2</v>
       </c>
       <c r="D3" s="62" t="s">
-        <v>532</v>
+        <v>461</v>
       </c>
       <c r="E3" s="62" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="F3" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="G3" s="63"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="60" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="B4" s="60">
         <v>2</v>
@@ -3484,11 +3261,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="62" t="s">
-        <v>533</v>
+        <v>462</v>
       </c>
       <c r="E4" s="60"/>
       <c r="F4" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="G4" s="63"/>
     </row>
@@ -3500,18 +3277,18 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88414653-50FA-4845-96AF-5B777BBDF907}">
   <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="57" width="18.21875"/>
-    <col min="2" max="2" customWidth="true" style="57" width="16.5546875"/>
-    <col min="3" max="3" customWidth="true" style="57" width="19.88671875"/>
-    <col min="4" max="4" customWidth="true" style="57" width="18.77734375"/>
-    <col min="5" max="5" customWidth="true" style="57" width="12.88671875"/>
-    <col min="6" max="8" customWidth="true" hidden="true" style="57" width="0.0"/>
-    <col min="9" max="9" style="57" width="8.77734375"/>
-    <col min="10" max="10" customWidth="true" style="57" width="17.88671875"/>
-    <col min="11" max="11" customWidth="true" style="57" width="14.21875"/>
-    <col min="12" max="16384" style="57" width="8.77734375"/>
+    <col min="1" max="1" width="18.1796875" style="57" customWidth="1"/>
+    <col min="2" max="2" width="16.54296875" style="57" customWidth="1"/>
+    <col min="3" max="3" width="19.90625" style="57" customWidth="1"/>
+    <col min="4" max="4" width="18.81640625" style="57" customWidth="1"/>
+    <col min="5" max="5" width="12.90625" style="57" customWidth="1"/>
+    <col min="6" max="8" width="0" style="57" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="8.81640625" style="57"/>
+    <col min="10" max="10" width="17.90625" style="57" customWidth="1"/>
+    <col min="11" max="11" width="14.1796875" style="57" customWidth="1"/>
+    <col min="12" max="16384" width="8.81640625" style="57"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -3519,36 +3296,36 @@
         <v>0</v>
       </c>
       <c r="B1" s="58" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="C1" s="58" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="58" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="E1" s="58" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F1" s="60"/>
       <c r="G1" s="60"/>
       <c r="H1" s="60"/>
       <c r="I1" s="59" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J1" s="59" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="K1" s="59" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="60" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="B2" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C2" s="60"/>
       <c r="D2" s="60"/>
@@ -3562,10 +3339,10 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="60" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="B3" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C3" s="60"/>
       <c r="D3" s="60"/>
@@ -3579,10 +3356,10 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="60" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="B4" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C4" s="60"/>
       <c r="D4" s="60"/>
@@ -3596,7 +3373,7 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="60" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="B5" s="60"/>
       <c r="C5" s="62">
@@ -3612,18 +3389,18 @@
       <c r="G5" s="60"/>
       <c r="H5" s="60"/>
       <c r="I5" s="60" t="s">
-        <v>527</v>
+        <v>456</v>
       </c>
       <c r="J5" s="60" t="s">
-        <v>528</v>
+        <v>457</v>
       </c>
       <c r="K5" s="60" t="s">
-        <v>529</v>
+        <v>458</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="60" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="B6" s="60"/>
       <c r="C6" s="60">
@@ -3650,14 +3427,14 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1F0BBC0-8387-4A2B-855A-0B1CE735F165}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="57" width="15.109375"/>
-    <col min="2" max="2" customWidth="true" style="57" width="15.77734375"/>
-    <col min="3" max="3" customWidth="true" style="57" width="17.77734375"/>
-    <col min="4" max="4" customWidth="true" style="57" width="16.77734375"/>
-    <col min="5" max="5" customWidth="true" style="57" width="15.6640625"/>
-    <col min="6" max="16384" style="57" width="8.77734375"/>
+    <col min="1" max="1" width="15.08984375" style="57" customWidth="1"/>
+    <col min="2" max="2" width="15.81640625" style="57" customWidth="1"/>
+    <col min="3" max="3" width="17.81640625" style="57" customWidth="1"/>
+    <col min="4" max="4" width="16.81640625" style="57" customWidth="1"/>
+    <col min="5" max="5" width="15.6328125" style="57" customWidth="1"/>
+    <col min="6" max="16384" width="8.81640625" style="57"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -3665,27 +3442,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="58" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="C1" s="58" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="D1" s="58" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="E1" s="58" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="62" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="B2" s="62">
         <v>1</v>
       </c>
       <c r="C2" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D2" s="60">
         <v>1</v>
@@ -3694,13 +3471,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="62" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="B3" s="60">
         <v>1</v>
       </c>
       <c r="C3" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D3" s="60"/>
       <c r="E3" s="60">
@@ -3709,13 +3486,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="62" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="B4" s="60">
         <v>1</v>
       </c>
       <c r="C4" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D4" s="60"/>
       <c r="E4" s="60">
@@ -3733,22 +3510,22 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:AB6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="51.77734375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.5546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="9.44140625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="17.5546875"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="18.44140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="14.44140625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="15.44140625"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="18.44140625"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="18.44140625"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="12.21875"/>
+    <col min="1" max="1" width="51.81640625" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28">
@@ -3762,10 +3539,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>1</v>
@@ -3774,13 +3551,13 @@
         <v>2</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="32" t="s">
         <v>97</v>
-      </c>
-      <c r="J1" s="32" t="s">
-        <v>98</v>
       </c>
       <c r="K1" s="32" t="s">
         <v>1</v>
@@ -3789,7 +3566,7 @@
         <v>2</v>
       </c>
       <c r="M1" s="32" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="N1" s="32" t="s">
         <v>3</v>
@@ -3804,7 +3581,7 @@
         <v>2</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="S1" s="2" t="s">
         <v>3</v>
@@ -3839,7 +3616,7 @@
     </row>
     <row r="2" spans="1:28">
       <c r="A2" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B2" s="18">
         <v>1</v>
@@ -3857,7 +3634,7 @@
         <v>5</v>
       </c>
       <c r="G2" s="18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>14</v>
@@ -3866,16 +3643,16 @@
         <v>13</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>475</v>
+        <v>407</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>476</v>
+        <v>408</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>19</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>477</v>
+        <v>409</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>13</v>
@@ -3884,13 +3661,13 @@
         <v>14</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>478</v>
+        <v>410</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>479</v>
+        <v>411</v>
       </c>
       <c r="S2" s="3" t="s">
         <v>14</v>
@@ -3909,13 +3686,13 @@
     </row>
     <row r="3" spans="1:28">
       <c r="A3" s="7" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B3" s="18">
         <v>1</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>13</v>
@@ -3927,7 +3704,7 @@
         <v>5</v>
       </c>
       <c r="G3" s="18" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>14</v>
@@ -3936,16 +3713,16 @@
         <v>13</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>13</v>
@@ -3954,13 +3731,13 @@
         <v>14</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="S3" s="3" t="s">
         <v>14</v>
@@ -3972,7 +3749,7 @@
         <v>6</v>
       </c>
       <c r="V3" s="18" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="W3" s="3" t="s">
         <v>13</v>
@@ -3984,7 +3761,7 @@
         <v>7</v>
       </c>
       <c r="Z3" s="18" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="AA3" s="3" t="s">
         <v>14</v>
@@ -3995,7 +3772,7 @@
     </row>
     <row r="4" spans="1:28">
       <c r="A4" s="28" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="B4" s="18">
         <v>1</v>
@@ -4014,16 +3791,16 @@
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>19</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="N4" s="3" t="s">
         <v>13</v>
@@ -4047,7 +3824,7 @@
     </row>
     <row r="5" spans="1:28">
       <c r="A5" s="28" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="B5" s="18">
         <v>3</v>
@@ -4066,16 +3843,16 @@
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>534</v>
+        <v>463</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>535</v>
+        <v>428</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>19</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>536</v>
+        <v>429</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>13</v>
@@ -4099,7 +3876,7 @@
     </row>
     <row r="6" spans="1:28">
       <c r="A6" s="28" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B6" s="18">
         <v>1</v>
@@ -4117,21 +3894,21 @@
         <v>5</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>19</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="N6" s="3" t="s">
         <v>13</v>
@@ -4165,12 +3942,12 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="76.21875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="13.44140625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="12.21875"/>
+    <col min="1" max="1" width="76.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4181,18 +3958,18 @@
         <v>2</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D1" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="E1" s="28" t="s">
         <v>91</v>
-      </c>
-      <c r="E1" s="28" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B2" s="30" t="s">
         <v>39</v>
@@ -4207,7 +3984,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="29" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B3" s="18" t="s">
         <v>39</v>
@@ -4224,7 +4001,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B4" s="18" t="s">
         <v>39</v>
@@ -4248,14 +4025,14 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEA2AF7E-AC89-4B47-B4D7-D3496E5327D5}">
   <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="57" width="18.44140625"/>
-    <col min="2" max="2" customWidth="true" style="57" width="12.5546875"/>
-    <col min="3" max="3" customWidth="true" style="57" width="14.77734375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="57" width="11.77734375"/>
-    <col min="5" max="5" customWidth="true" style="57" width="18.21875"/>
-    <col min="6" max="16384" style="57" width="8.77734375"/>
+    <col min="1" max="1" width="18.453125" style="57" customWidth="1"/>
+    <col min="2" max="2" width="12.54296875" style="57" customWidth="1"/>
+    <col min="3" max="3" width="14.81640625" style="57" customWidth="1"/>
+    <col min="4" max="4" width="11.81640625" style="57" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.1796875" style="57" customWidth="1"/>
+    <col min="6" max="16384" width="8.81640625" style="57"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4263,13 +4040,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="58" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="C1" s="58" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="D1" s="58" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="E1" s="58" t="s">
         <v>1</v>
@@ -4277,10 +4054,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="60" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B2" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C2" s="60"/>
       <c r="D2" s="60"/>
@@ -4288,10 +4065,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="60" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="B3" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C3" s="60"/>
       <c r="D3" s="60"/>
@@ -4299,10 +4076,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="60" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="B4" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C4" s="60"/>
       <c r="D4" s="60"/>
@@ -4310,10 +4087,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="60" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="B5" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C5" s="60"/>
       <c r="D5" s="60"/>
@@ -4321,10 +4098,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="60" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="B6" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C6" s="60"/>
       <c r="D6" s="60"/>
@@ -4332,10 +4109,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="60" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="B7" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C7" s="60"/>
       <c r="D7" s="60"/>
@@ -4343,10 +4120,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="60" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="B8" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C8" s="60"/>
       <c r="D8" s="60"/>
@@ -4354,25 +4131,25 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="60" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="B9" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C9" s="62" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="D9" s="56" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="E9" s="60"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="60" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="B10" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C10" s="60"/>
       <c r="D10" s="60"/>
@@ -4380,10 +4157,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="60" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="B11" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C11" s="60"/>
       <c r="D11" s="60"/>
@@ -4391,10 +4168,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="60" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="B12" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C12" s="60"/>
       <c r="D12" s="60"/>
@@ -4402,10 +4179,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="60" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="B13" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C13" s="60"/>
       <c r="D13" s="60"/>
@@ -4413,10 +4190,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="60" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="B14" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C14" s="60"/>
       <c r="D14" s="60"/>
@@ -4426,10 +4203,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="60" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="B15" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C15" s="60"/>
       <c r="D15" s="60"/>
@@ -4445,10 +4222,10 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F1569B0-3564-4B84-A0FB-9681D32A0E6D}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="12.5546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.5546875"/>
+    <col min="1" max="1" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -4456,23 +4233,23 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="34" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="34" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -4483,13 +4260,13 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02A4FAA4-EFC6-47D3-BDEE-7F4F3353F3CD}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="33.5546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="13.44140625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="15.44140625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="12.21875"/>
+    <col min="1" max="1" width="33.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4497,7 +4274,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -4511,13 +4288,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="34" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>36</v>
@@ -4534,7 +4311,7 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA6A106B-75A4-4F54-9508-A66A4AEED06E}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="6" t="s">
@@ -4544,21 +4321,21 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="41" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B2" s="48">
         <v>3</v>
       </c>
       <c r="C2" s="48" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="D2" s="48" t="s">
         <v>13</v>
@@ -4566,13 +4343,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="41" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B3" s="48">
         <v>3</v>
       </c>
       <c r="C3" s="48" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="D3" s="48" t="s">
         <v>13</v>
@@ -4580,13 +4357,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="41" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="B4" s="48">
         <v>0</v>
       </c>
       <c r="C4" s="48" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="D4" s="48" t="s">
         <v>13</v>
@@ -4636,32 +4413,32 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:AG4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="49.77734375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="4.77734375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="5.44140625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="9.77734375"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="4.44140625"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="5.44140625"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="9.77734375"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="4.44140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="5.44140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="9.77734375"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="4.44140625"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="5.44140625"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="9.77734375"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="4.44140625"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="5.44140625"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="9.77734375"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="4.44140625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="5.44140625"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="9.77734375"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="4.44140625"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" width="5.44140625"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="9.77734375"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="4.44140625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" width="5.44140625"/>
+    <col min="1" max="1" width="49.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="5.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33">
@@ -4968,9 +4745,9 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4903F224-3652-48FB-81A7-CAF06A9D7463}">
   <dimension ref="A1:AD9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.5546875"/>
+    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30">
@@ -4984,13 +4761,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>97</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>2</v>
@@ -5005,7 +4782,7 @@
         <v>1</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>1</v>
@@ -5014,7 +4791,7 @@
         <v>2</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>3</v>
@@ -5023,7 +4800,7 @@
         <v>4</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>2</v>
@@ -5038,7 +4815,7 @@
         <v>1</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="W1" s="1" t="s">
         <v>2</v>
@@ -5067,7 +4844,7 @@
     </row>
     <row r="2" spans="1:30">
       <c r="A2" s="14" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
@@ -5089,16 +4866,16 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>48</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>13</v>
@@ -5123,13 +4900,13 @@
     </row>
     <row r="3" spans="1:30">
       <c r="A3" s="14" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B3" s="3">
         <v>1</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>36</v>
@@ -5141,7 +4918,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="18" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>13</v>
@@ -5153,16 +4930,16 @@
         <v>2</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>537</v>
+        <v>464</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="O3" s="3" t="s">
         <v>36</v>
@@ -5172,7 +4949,7 @@
       </c>
       <c r="Q3" s="3"/>
       <c r="R3" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="S3" s="3" t="s">
         <v>51</v>
@@ -5197,7 +4974,7 @@
         <v>4</v>
       </c>
       <c r="AA3" s="18" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="AB3" s="3" t="s">
         <v>49</v>
@@ -5211,7 +4988,7 @@
     </row>
     <row r="4" spans="1:30">
       <c r="A4" s="14" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B4" s="3">
         <v>1</v>
@@ -5247,7 +5024,7 @@
     </row>
     <row r="5" spans="1:30">
       <c r="A5" s="14" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -5265,7 +5042,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="18" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>13</v>
@@ -5277,16 +5054,16 @@
         <v>5</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>48</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>13</v>
@@ -5295,7 +5072,7 @@
         <v>49</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="R5" s="18" t="s">
         <v>48</v>
@@ -5339,7 +5116,7 @@
     </row>
     <row r="6" spans="1:30">
       <c r="A6" s="14" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -5383,7 +5160,7 @@
     </row>
     <row r="7" spans="1:30">
       <c r="A7" s="14" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -5427,7 +5204,7 @@
     </row>
     <row r="8" spans="1:30">
       <c r="A8" s="14" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -5463,7 +5240,7 @@
     </row>
     <row r="9" spans="1:30">
       <c r="A9" s="14" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -5485,16 +5262,16 @@
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>48</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>13</v>
@@ -5528,13 +5305,13 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="35.21875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="15.44140625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="11.5546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="13.44140625"/>
+    <col min="1" max="1" width="35.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -5548,24 +5325,24 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="34" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="E2" s="3">
         <v>1</v>
@@ -5573,7 +5350,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="34" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B3" s="18" t="s">
         <v>39</v>
@@ -5582,7 +5359,7 @@
         <v>13</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="E3" s="3">
         <v>1</v>
@@ -5590,16 +5367,16 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="34" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="E4" s="3">
         <v>1</v>
@@ -5613,10 +5390,10 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB53E397-0E70-4FE2-8956-CAC505C79FBA}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="33.5546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="13.44140625"/>
+    <col min="1" max="1" width="33.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5624,39 +5401,39 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="34" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -5667,10 +5444,10 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71142910-3363-4189-996E-89090332A376}">
   <dimension ref="A1:AC4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="5" max="5" customWidth="true" width="6.21875"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="13.88671875"/>
+    <col min="5" max="5" width="6.1796875" customWidth="1"/>
+    <col min="29" max="29" width="13.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -5684,13 +5461,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>97</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>2</v>
@@ -5741,7 +5518,7 @@
         <v>1</v>
       </c>
       <c r="W1" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="X1" s="2" t="s">
         <v>1</v>
@@ -5750,7 +5527,7 @@
         <v>2</v>
       </c>
       <c r="Z1" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AA1" s="2" t="s">
         <v>3</v>
@@ -5759,12 +5536,12 @@
         <v>4</v>
       </c>
       <c r="AC1" s="2" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:29">
       <c r="A2" s="3" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
@@ -5798,16 +5575,16 @@
       <c r="U2" s="3"/>
       <c r="V2" s="3"/>
       <c r="W2" s="3" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="X2" s="3" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="Y2" s="3" t="s">
         <v>48</v>
       </c>
       <c r="Z2" s="3" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="AA2" s="3" t="s">
         <v>13</v>
@@ -5816,18 +5593,18 @@
         <v>49</v>
       </c>
       <c r="AC2" s="3" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
     </row>
     <row r="3" spans="1:29">
       <c r="A3" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B3" s="3">
         <v>2</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>14</v>
@@ -5851,7 +5628,7 @@
         <v>3</v>
       </c>
       <c r="K3" s="18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>49</v>
@@ -5863,7 +5640,7 @@
         <v>4</v>
       </c>
       <c r="O3" s="18" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="P3" s="3" t="s">
         <v>13</v>
@@ -5879,7 +5656,7 @@
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
       <c r="W3" s="3" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="X3" s="3"/>
       <c r="Y3" s="3"/>
@@ -5887,12 +5664,12 @@
       <c r="AA3" s="3"/>
       <c r="AB3" s="3"/>
       <c r="AC3" s="3" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" spans="1:29">
       <c r="A4" s="3" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="B4" s="3">
         <v>1</v>
@@ -5926,16 +5703,16 @@
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="Y4" s="3" t="s">
         <v>48</v>
       </c>
       <c r="Z4" s="3" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="AA4" s="3" t="s">
         <v>13</v>
@@ -5944,7 +5721,7 @@
         <v>49</v>
       </c>
       <c r="AC4" s="3" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
     </row>
   </sheetData>
@@ -5958,16 +5735,16 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="63.77734375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="10.77734375"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="19.44140625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="15.5546875"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="8" max="9" bestFit="true" customWidth="true" width="19.44140625"/>
+    <col min="1" max="1" width="63.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="19.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -5975,33 +5752,33 @@
         <v>0</v>
       </c>
       <c r="B1" s="36" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="34" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B2" s="37" t="s">
         <v>36</v>
@@ -6016,10 +5793,10 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B3" s="37" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -6031,10 +5808,10 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="3" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B4" s="37" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -6046,37 +5823,37 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="3" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="3" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -6098,25 +5875,25 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:R6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="12.0"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.5546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="9.44140625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="6.21875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="13.77734375"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="15.44140625"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="17.5546875"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="7.44140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="18.44140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="18.44140625"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="15.44140625"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="11.77734375"/>
+    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -6130,13 +5907,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="40" t="s">
+        <v>95</v>
+      </c>
+      <c r="E1" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="E1" s="40" t="s">
-        <v>97</v>
-      </c>
       <c r="F1" s="38" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="G1" s="40" t="s">
         <v>2</v>
@@ -6151,7 +5928,7 @@
         <v>1</v>
       </c>
       <c r="K1" s="32" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L1" s="32" t="s">
         <v>1</v>
@@ -6160,7 +5937,7 @@
         <v>2</v>
       </c>
       <c r="N1" s="32" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O1" s="32" t="s">
         <v>3</v>
@@ -6169,15 +5946,15 @@
         <v>4</v>
       </c>
       <c r="Q1" s="32" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="R1" s="32" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="28" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="B2" s="18">
         <v>1</v>
@@ -6199,16 +5976,16 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>19</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>13</v>
@@ -6221,7 +5998,7 @@
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="28" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B3" s="18">
         <v>7</v>
@@ -6243,16 +6020,16 @@
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>19</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="O3" s="3" t="s">
         <v>13</v>
@@ -6261,15 +6038,15 @@
         <v>14</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="28" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B4" s="18">
         <v>1</v>
@@ -6309,7 +6086,7 @@
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="28" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B5" s="18">
         <v>1</v>
@@ -6341,7 +6118,7 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="28" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B6" s="18">
         <v>1</v>
@@ -6380,7 +6157,7 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42BBEF64-F0EA-4EA8-9A62-F5A7DF1E4869}">
   <dimension ref="A1:U13"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:21">
       <c r="A1" s="39" t="s">
@@ -6393,10 +6170,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="40" t="s">
+        <v>95</v>
+      </c>
+      <c r="E1" s="40" t="s">
         <v>96</v>
-      </c>
-      <c r="E1" s="40" t="s">
-        <v>97</v>
       </c>
       <c r="F1" s="40" t="s">
         <v>1</v>
@@ -6405,13 +6182,13 @@
         <v>2</v>
       </c>
       <c r="H1" s="40" t="s">
+        <v>95</v>
+      </c>
+      <c r="I1" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="I1" s="40" t="s">
+      <c r="J1" s="32" t="s">
         <v>97</v>
-      </c>
-      <c r="J1" s="32" t="s">
-        <v>98</v>
       </c>
       <c r="K1" s="32" t="s">
         <v>1</v>
@@ -6420,7 +6197,7 @@
         <v>2</v>
       </c>
       <c r="M1" s="32" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="N1" s="32" t="s">
         <v>3</v>
@@ -6435,7 +6212,7 @@
         <v>2</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="S1" s="2" t="s">
         <v>3</v>
@@ -6444,137 +6221,137 @@
         <v>4</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:21">
       <c r="A2" s="28" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="B2" s="50">
         <v>1</v>
       </c>
       <c r="C2" s="48" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="D2" s="48" t="s">
         <v>13</v>
       </c>
       <c r="E2" s="48" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="F2" s="50">
         <v>1</v>
       </c>
       <c r="G2" s="48" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="H2" s="48" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="I2" s="48" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>538</v>
+        <v>465</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>539</v>
+        <v>430</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>540</v>
+        <v>431</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>541</v>
+        <v>432</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>542</v>
+        <v>433</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>543</v>
+        <v>466</v>
       </c>
     </row>
     <row r="3" spans="1:21">
       <c r="A3" s="28" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B3" s="50">
         <v>1</v>
       </c>
       <c r="C3" s="48" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="D3" s="48" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="48" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="F3" s="50">
         <v>1</v>
       </c>
       <c r="G3" s="48" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="H3" s="48" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="I3" s="48" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8" spans="1:21">
@@ -6582,25 +6359,25 @@
         <v>1</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="F8" s="18">
         <v>4</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9" spans="1:21">
@@ -6608,25 +6385,25 @@
         <v>1</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="F9" s="18">
         <v>4</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12" spans="1:21">
@@ -6634,10 +6411,10 @@
         <v>1</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>13</v>
@@ -6646,7 +6423,7 @@
         <v>1</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>13</v>
@@ -6660,10 +6437,10 @@
         <v>1</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>13</v>
@@ -6672,7 +6449,7 @@
         <v>1</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>13</v>
@@ -6692,10 +6469,10 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="32.21875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="12.21875"/>
+    <col min="1" max="1" width="32.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -6703,31 +6480,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="3" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -6738,31 +6515,31 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A51EFA8C-67A7-4B7E-8EF6-A12213F165A5}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -6770,17 +6547,17 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="B3" s="33"/>
       <c r="C3" s="3" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -6791,11 +6568,11 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFCF6FDB-3B87-457C-A3CA-7B39CE849651}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="57" width="24.88671875"/>
-    <col min="2" max="2" customWidth="true" style="57" width="17.44140625"/>
-    <col min="3" max="16384" style="57" width="8.77734375"/>
+    <col min="1" max="1" width="24.90625" style="57" customWidth="1"/>
+    <col min="2" max="2" width="17.453125" style="57" customWidth="1"/>
+    <col min="3" max="16384" width="8.81640625" style="57"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -6803,24 +6580,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="58" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="C1" s="60" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D1" s="60" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="E1" s="60" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="60" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="B2" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C2" s="60"/>
       <c r="D2" s="60"/>
@@ -6828,10 +6605,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="60" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="B3" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C3" s="60"/>
       <c r="D3" s="60"/>
@@ -6839,10 +6616,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="60" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="B4" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C4" s="60"/>
       <c r="D4" s="60"/>
@@ -6850,10 +6627,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="60" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="B5" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C5" s="60"/>
       <c r="D5" s="60"/>
@@ -6861,10 +6638,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="60" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="B6" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C6" s="60"/>
       <c r="D6" s="60"/>
@@ -6872,10 +6649,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="60" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="B7" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C7" s="60"/>
       <c r="D7" s="60"/>
@@ -6883,10 +6660,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="60" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="B8" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C8" s="60"/>
       <c r="D8" s="60"/>
@@ -6894,10 +6671,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="60" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="B9" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C9" s="60"/>
       <c r="D9" s="60"/>
@@ -6905,10 +6682,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="60" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="B10" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C10" s="60"/>
       <c r="D10" s="60"/>
@@ -6916,10 +6693,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="60" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="B11" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C11" s="60"/>
       <c r="D11" s="60"/>
@@ -6927,10 +6704,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="60" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="B12" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C12" s="60"/>
       <c r="D12" s="60"/>
@@ -6938,10 +6715,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="60" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="B13" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C13" s="60"/>
       <c r="D13" s="60"/>
@@ -6949,10 +6726,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="60" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="B14" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C14" s="60"/>
       <c r="D14" s="60"/>
@@ -6960,10 +6737,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="60" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="B15" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C15" s="60"/>
       <c r="D15" s="60"/>
@@ -6971,10 +6748,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="60" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="B16" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C16" s="60"/>
       <c r="D16" s="60"/>
@@ -6982,10 +6759,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="60" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="B17" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C17" s="60"/>
       <c r="D17" s="60"/>
@@ -6999,19 +6776,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DDD085C-F9E3-44F9-93E4-153774C9882E}">
   <sheetPr>
-    <tabColor rgb="FFFFC000"/>
+    <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="39.44140625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="21.77734375"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="15.44140625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="9.44140625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="6.44140625"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="18.44140625"/>
+    <col min="1" max="1" width="39.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -7066,10 +6843,10 @@
         <v>65</v>
       </c>
       <c r="H2" s="26" t="s">
-        <v>485</v>
+        <v>467</v>
       </c>
       <c r="I2" s="26" t="s">
-        <v>486</v>
+        <v>468</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -7089,7 +6866,7 @@
         <v>14</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>67</v>
+        <v>469</v>
       </c>
       <c r="G3" s="18" t="s">
         <v>65</v>
@@ -7109,17 +6886,17 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="32.21875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="15.44140625"/>
-    <col min="4" max="4" customWidth="true" width="15.44140625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="17.5546875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="15.44140625"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="17.5546875"/>
+    <col min="1" max="1" width="32.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.453125" customWidth="1"/>
+    <col min="5" max="5" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -7151,7 +6928,7 @@
         <v>1</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>1</v>
@@ -7160,12 +6937,12 @@
         <v>2</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="3" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="B2" s="18" t="s">
         <v>19</v>
@@ -7188,7 +6965,7 @@
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="3" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B3" s="18" t="s">
         <v>19</v>
@@ -7211,10 +6988,10 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>49</v>
@@ -7244,7 +7021,7 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="3" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B5" s="18" t="s">
         <v>19</v>
@@ -7273,18 +7050,18 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C03B3B8-DBFD-430F-BAEF-858DA603C137}">
   <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="57" width="17.88671875"/>
-    <col min="2" max="2" customWidth="true" style="57" width="11.77734375"/>
-    <col min="3" max="3" customWidth="true" style="57" width="13.0"/>
-    <col min="4" max="4" customWidth="true" style="57" width="16.5546875"/>
-    <col min="5" max="5" customWidth="true" style="57" width="15.77734375"/>
-    <col min="6" max="6" style="57" width="8.77734375"/>
-    <col min="7" max="7" customWidth="true" style="57" width="17.77734375"/>
-    <col min="8" max="8" customWidth="true" style="57" width="15.44140625"/>
-    <col min="9" max="9" customWidth="true" style="57" width="11.5546875"/>
-    <col min="10" max="16384" style="57" width="8.77734375"/>
+    <col min="1" max="1" width="17.90625" style="57" customWidth="1"/>
+    <col min="2" max="2" width="11.81640625" style="57" customWidth="1"/>
+    <col min="3" max="3" width="13" style="57" customWidth="1"/>
+    <col min="4" max="4" width="16.54296875" style="57" customWidth="1"/>
+    <col min="5" max="5" width="15.81640625" style="57" customWidth="1"/>
+    <col min="6" max="6" width="8.81640625" style="57"/>
+    <col min="7" max="7" width="17.81640625" style="57" customWidth="1"/>
+    <col min="8" max="8" width="15.453125" style="57" customWidth="1"/>
+    <col min="9" max="9" width="11.54296875" style="57" customWidth="1"/>
+    <col min="10" max="16384" width="8.81640625" style="57"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -7292,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="61" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="C1" s="61" t="s">
         <v>1</v>
@@ -7301,33 +7078,33 @@
         <v>1</v>
       </c>
       <c r="E1" s="61" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="F1" s="61" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G1" s="61" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="H1" s="61" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="I1" s="61" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="J1" s="61" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="K1" s="61" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="60" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="B2" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C2" s="60">
         <v>1</v>
@@ -7339,7 +7116,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="60" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="G2" s="60">
         <v>2</v>
@@ -7348,17 +7125,17 @@
         <v>50</v>
       </c>
       <c r="I2" s="62" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="J2" s="60"/>
       <c r="K2" s="60"/>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="60" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="B3" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C3" s="60">
         <v>1</v>
@@ -7370,24 +7147,24 @@
         <v>1</v>
       </c>
       <c r="F3" s="60" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="G3" s="60"/>
       <c r="H3" s="60"/>
       <c r="I3" s="60"/>
       <c r="J3" s="62" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="K3" s="60" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="60" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="B4" s="60" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C4" s="60">
         <v>1</v>
@@ -7399,7 +7176,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="60" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="G4" s="60"/>
       <c r="H4" s="60"/>
@@ -7418,13 +7195,13 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="39.44140625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="13.5546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="7.77734375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="5.44140625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="9.77734375"/>
+    <col min="1" max="1" width="39.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -7432,7 +7209,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>29</v>
@@ -7446,7 +7223,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B2" s="7">
         <v>1</v>
@@ -7458,12 +7235,12 @@
         <v>36</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B3" s="7">
         <v>1</v>
@@ -7490,12 +7267,12 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="57.44140625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="15.5546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="7.77734375"/>
-    <col min="4" max="5" bestFit="true" customWidth="true" width="11.21875"/>
+    <col min="1" max="1" width="57.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -7610,24 +7387,24 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:P5"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="45" width="42.0"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="45" width="18.33203125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="45" width="12.109375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="45" width="15.33203125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="45" width="12.21875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="45" width="9.44140625"/>
-    <col min="7" max="8" style="45" width="8.77734375"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="45" width="10.44140625"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="45" width="11.21875"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="45" width="10.44140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="45" width="11.21875"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="45" width="10.44140625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="45" width="8.21875"/>
-    <col min="15" max="15" customWidth="true" style="45" width="13.0"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" style="45" width="10.21875"/>
-    <col min="17" max="16384" style="45" width="8.77734375"/>
+    <col min="1" max="1" width="42" style="45" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.36328125" style="45" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.08984375" style="45" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.36328125" style="45" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1796875" style="45" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.453125" style="45" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="8.81640625" style="45"/>
+    <col min="9" max="9" width="10.453125" style="45" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.1796875" style="45" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.453125" style="45" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.1796875" style="45" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.453125" style="45" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.1796875" style="45" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13" style="45" customWidth="1"/>
+    <col min="16" max="16" width="10.1796875" style="45" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="8.81640625" style="45"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -7677,7 +7454,7 @@
         <v>10</v>
       </c>
       <c r="P1" s="47" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -7706,15 +7483,15 @@
       <c r="I2" s="48"/>
       <c r="J2" s="48"/>
       <c r="K2" s="52" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="L2" s="52" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="M2" s="48"/>
       <c r="N2" s="48"/>
       <c r="O2" s="48" t="s">
-        <v>488</v>
+        <v>436</v>
       </c>
       <c r="P2" s="48"/>
     </row>
@@ -7752,7 +7529,7 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="52" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="B4" s="48">
         <v>2</v>
@@ -7778,7 +7555,7 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="52" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="B5" s="48">
         <v>2</v>
@@ -7796,10 +7573,10 @@
       <c r="I5" s="48"/>
       <c r="J5" s="48"/>
       <c r="K5" s="52" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="L5" s="52" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="M5" s="48"/>
       <c r="N5" s="48"/>
@@ -7819,31 +7596,31 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:AB7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="44.77734375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.77734375"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="8.21875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="11.21875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="10.44140625"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="13.5546875"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="17.77734375"/>
-    <col min="11" max="12" bestFit="true" customWidth="true" width="11.21875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="18.21875"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="7.77734375"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="11.21875"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="8.21875"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="11.21875"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="11.21875"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="14.21875"/>
-    <col min="27" max="28" bestFit="true" customWidth="true" width="12.77734375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="14.21875"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="12.77734375"/>
+    <col min="1" max="1" width="44.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28">
@@ -7857,7 +7634,7 @@
         <v>29</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E1" s="15" t="s">
         <v>4</v>
@@ -7875,7 +7652,7 @@
         <v>29</v>
       </c>
       <c r="J1" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K1" s="15" t="s">
         <v>4</v>
@@ -7893,7 +7670,7 @@
         <v>29</v>
       </c>
       <c r="P1" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q1" s="15" t="s">
         <v>4</v>
@@ -7911,7 +7688,7 @@
         <v>29</v>
       </c>
       <c r="V1" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="W1" s="15" t="s">
         <v>4</v>
@@ -7923,18 +7700,18 @@
         <v>9</v>
       </c>
       <c r="Z1" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA1" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AB1" s="6" t="s">
         <v>74</v>
-      </c>
-      <c r="AB1" s="6" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:28">
       <c r="A2" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B2" s="23">
         <v>2</v>
@@ -7949,10 +7726,10 @@
         <v>36</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>78</v>
       </c>
       <c r="H2" s="23"/>
       <c r="I2" s="21"/>
@@ -7984,13 +7761,13 @@
     </row>
     <row r="3" spans="1:28">
       <c r="A3" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B3" s="23">
         <v>11</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>36</v>
@@ -7999,16 +7776,16 @@
         <v>13</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="H3" s="23">
         <v>11</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J3" s="10" t="s">
         <v>13</v>
@@ -8017,7 +7794,7 @@
         <v>49</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>17</v>
@@ -8026,7 +7803,7 @@
         <v>11</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P3" s="10" t="s">
         <v>49</v>
@@ -8035,7 +7812,7 @@
         <v>13</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="S3" s="3" t="s">
         <v>17</v>
@@ -8066,13 +7843,13 @@
     </row>
     <row r="4" spans="1:28">
       <c r="A4" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B4" s="23">
         <v>11</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>51</v>
@@ -8081,25 +7858,25 @@
         <v>13</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="H4" s="23">
         <v>11</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J4" s="10" t="s">
         <v>13</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>17</v>
@@ -8108,16 +7885,16 @@
         <v>11</v>
       </c>
       <c r="O4" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P4" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q4" s="10" t="s">
         <v>13</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="S4" s="3" t="s">
         <v>17</v>
@@ -8148,13 +7925,13 @@
     </row>
     <row r="5" spans="1:28">
       <c r="A5" s="42" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B5" s="18">
         <v>1</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>13</v>
@@ -8165,13 +7942,13 @@
     </row>
     <row r="6" spans="1:28">
       <c r="A6" s="42" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B6" s="18">
         <v>1</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>13</v>
@@ -8182,13 +7959,13 @@
     </row>
     <row r="7" spans="1:28">
       <c r="A7" s="42" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="B7" s="18">
         <v>1</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>13</v>
@@ -8208,11 +7985,11 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:W17"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="54.33203125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="13.88671875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="13.77734375"/>
+    <col min="1" max="1" width="54.36328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -8226,7 +8003,7 @@
         <v>29</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E1" s="15" t="s">
         <v>4</v>
@@ -8238,7 +8015,7 @@
         <v>29</v>
       </c>
       <c r="H1" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I1" s="15" t="s">
         <v>4</v>
@@ -8250,7 +8027,7 @@
         <v>29</v>
       </c>
       <c r="L1" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M1" s="15" t="s">
         <v>4</v>
@@ -8262,39 +8039,39 @@
         <v>29</v>
       </c>
       <c r="P1" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q1" s="15" t="s">
         <v>4</v>
       </c>
       <c r="R1" s="43" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="S1" s="43" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="U1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:23">
       <c r="A2" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B2" s="23">
         <v>1</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>14</v>
@@ -8315,10 +8092,10 @@
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
       <c r="R2" s="3" t="s">
-        <v>489</v>
+        <v>437</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>490</v>
+        <v>438</v>
       </c>
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
@@ -8327,13 +8104,13 @@
     </row>
     <row r="3" spans="1:23">
       <c r="A3" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B3" s="23">
         <v>1</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>14</v>
@@ -8357,7 +8134,7 @@
         <v>3</v>
       </c>
       <c r="K3" s="18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>49</v>
@@ -8386,13 +8163,13 @@
     </row>
     <row r="4" spans="1:23">
       <c r="A4" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B4" s="23">
         <v>1</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>14</v>
@@ -8416,7 +8193,7 @@
         <v>3</v>
       </c>
       <c r="K4" s="18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>49</v>
@@ -8445,13 +8222,13 @@
     </row>
     <row r="5" spans="1:23">
       <c r="A5" s="44" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B5" s="18">
         <v>1</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>13</v>
@@ -8480,13 +8257,13 @@
     </row>
     <row r="6" spans="1:23">
       <c r="A6" s="44" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B6" s="18">
         <v>1</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>13</v>
@@ -8515,13 +8292,13 @@
     </row>
     <row r="7" spans="1:23">
       <c r="A7" s="44" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="B7" s="18">
         <v>1</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>13</v>
@@ -8550,13 +8327,13 @@
     </row>
     <row r="8" spans="1:23">
       <c r="A8" s="44" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B8" s="23">
         <v>1</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>14</v>
@@ -8577,10 +8354,10 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3" t="s">
-        <v>491</v>
+        <v>439</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>492</v>
+        <v>440</v>
       </c>
       <c r="T8" s="3">
         <v>0</v>
@@ -8591,7 +8368,7 @@
     </row>
     <row r="9" spans="1:23">
       <c r="A9" s="44" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B9" s="23">
         <v>1</v>
@@ -8609,7 +8386,7 @@
         <v>2</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>14</v>
@@ -8626,10 +8403,10 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3" t="s">
-        <v>493</v>
+        <v>412</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>494</v>
+        <v>413</v>
       </c>
       <c r="T9" s="3"/>
       <c r="U9" s="3">
@@ -8644,7 +8421,7 @@
     </row>
     <row r="10" spans="1:23">
       <c r="A10" s="44" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B10" s="23">
         <v>1</v>
@@ -8662,7 +8439,7 @@
         <v>2</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>14</v>
@@ -8679,10 +8456,10 @@
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
@@ -8691,7 +8468,7 @@
     </row>
     <row r="11" spans="1:23">
       <c r="A11" s="44" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B11" s="23">
         <v>1</v>
@@ -8728,7 +8505,7 @@
     </row>
     <row r="12" spans="1:23">
       <c r="A12" s="44" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="B12" s="23">
         <v>1</v>
@@ -8763,7 +8540,7 @@
     </row>
     <row r="13" spans="1:23">
       <c r="A13" s="44" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B13" s="23">
         <v>1</v>
@@ -8800,7 +8577,7 @@
     </row>
     <row r="14" spans="1:23">
       <c r="A14" s="44" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="B14" s="23">
         <v>1</v>
@@ -8835,7 +8612,7 @@
     </row>
     <row r="15" spans="1:23">
       <c r="A15" s="44" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B15" s="23">
         <v>1</v>
@@ -8870,7 +8647,7 @@
     </row>
     <row r="16" spans="1:23">
       <c r="A16" s="44" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="B16" s="23">
         <v>1</v>
@@ -8888,7 +8665,7 @@
         <v>2</v>
       </c>
       <c r="G16" s="18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>49</v>
@@ -8905,10 +8682,10 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
@@ -8917,7 +8694,7 @@
     </row>
     <row r="17" spans="1:23">
       <c r="A17" s="44" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="B17" s="23">
         <v>1</v>
@@ -8961,18 +8738,18 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:S20"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="53.77734375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.5546875"/>
-    <col min="3" max="4" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="5" max="7" customWidth="true" width="12.21875"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="15.44140625"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="17.5546875"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="15.44140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="12.21875"/>
+    <col min="1" max="1" width="53.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="12.1796875" customWidth="1"/>
+    <col min="8" max="8" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
@@ -8989,13 +8766,13 @@
         <v>30</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -9016,7 +8793,7 @@
         <v>4</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>1</v>
@@ -9025,7 +8802,7 @@
         <v>2</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="R1" s="2" t="s">
         <v>3</v>
@@ -9036,7 +8813,7 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="34" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B2" s="3">
         <v>2</v>
@@ -9065,7 +8842,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="34" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B3" s="3">
         <v>2</v>
@@ -9077,7 +8854,7 @@
         <v>13</v>
       </c>
       <c r="E3" s="18" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="F3" s="18"/>
       <c r="G3" s="18"/>
@@ -9096,13 +8873,13 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="34" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B4" s="3">
         <v>2</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>36</v>
@@ -9125,7 +8902,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="34" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -9138,7 +8915,7 @@
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -9156,7 +8933,7 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" s="34" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
@@ -9173,7 +8950,7 @@
     </row>
     <row r="7" spans="1:19">
       <c r="A7" s="34" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -9186,13 +8963,13 @@
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="G7" s="3"/>
     </row>
     <row r="8" spans="1:19">
       <c r="A8" s="34" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -9205,13 +8982,13 @@
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="G8" s="3"/>
     </row>
     <row r="9" spans="1:19">
       <c r="A9" s="34" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -9224,19 +9001,19 @@
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="G9" s="3"/>
     </row>
     <row r="10" spans="1:19">
       <c r="A10" s="34" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>13</v>
@@ -9244,18 +9021,18 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:19">
       <c r="A11" s="35" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>13</v>
@@ -9263,12 +9040,12 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:19">
       <c r="A12" s="34" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="B12" s="26">
         <v>0</v>
@@ -9282,7 +9059,7 @@
     </row>
     <row r="13" spans="1:19">
       <c r="A13" s="34" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -9293,7 +9070,7 @@
     </row>
     <row r="14" spans="1:19">
       <c r="A14" s="34" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -9310,7 +9087,7 @@
     </row>
     <row r="15" spans="1:19">
       <c r="A15" s="34" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -9327,7 +9104,7 @@
     </row>
     <row r="16" spans="1:19">
       <c r="A16" s="34" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="B16" s="26">
         <v>0</v>
@@ -9344,7 +9121,7 @@
     </row>
     <row r="17" spans="1:19">
       <c r="A17" s="34" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="B17" s="26">
         <v>0</v>
@@ -9361,7 +9138,7 @@
     </row>
     <row r="20" spans="1:19">
       <c r="A20" s="34" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="B20" s="3">
         <v>1</v>
@@ -9383,7 +9160,7 @@
         <v>2</v>
       </c>
       <c r="K20" s="18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>13</v>
@@ -9392,16 +9169,16 @@
         <v>49</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>48</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>49</v>

--- a/src/test/java/TestData/Scenario_TestData.xlsx
+++ b/src/test/java/TestData/Scenario_TestData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Copa_SHD_WebServices\src\test\java\TestData\"/>
     </mc:Choice>
@@ -47,7 +47,7 @@
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1385" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1417" uniqueCount="482">
   <si>
     <t>Scenario</t>
   </si>
@@ -1476,12 +1476,49 @@
   </si>
   <si>
     <t>C</t>
+  </si>
+  <si>
+    <t>ACYUM3</t>
+  </si>
+  <si>
+    <t>ACYXQA</t>
+  </si>
+  <si>
+    <t>ACYX1J</t>
+  </si>
+  <si>
+    <t>ACYZAP</t>
+  </si>
+  <si>
+    <t>ACYZCC</t>
+  </si>
+  <si>
+    <t>2023-07-28T07:59:00</t>
+  </si>
+  <si>
+    <t>2023-07-28T12:07:00</t>
+  </si>
+  <si>
+    <t>2023-08-01T06:26:00</t>
+  </si>
+  <si>
+    <t>2023-08-01T08:32:00</t>
+  </si>
+  <si>
+    <t>ACYZC4</t>
+  </si>
+  <si>
+    <t>ACYZDF</t>
+  </si>
+  <si>
+    <t>ACYZEH</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="9">
     <font>
       <sz val="11"/>
@@ -2078,20 +2115,20 @@
   <dimension ref="A1:P15"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="52.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="52.81640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="18.453125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="9.453125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="10.453125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="10.453125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="10.453125"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="15.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2164,7 +2201,7 @@
         <v>16</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>434</v>
+        <v>480</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>266</v>
@@ -2181,7 +2218,7 @@
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
       <c r="O2" s="3" t="s">
-        <v>435</v>
+        <v>481</v>
       </c>
       <c r="P2" s="24"/>
     </row>
@@ -2253,8 +2290,8 @@
   <dimension ref="A1:U22"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="10" max="10" width="8.81640625" style="45"/>
-    <col min="17" max="17" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" style="45" width="8.81640625"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="9.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
@@ -3181,12 +3218,12 @@
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="32.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="32.90625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="14.36328125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="30.36328125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="6.90625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="10.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -3279,16 +3316,16 @@
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="18.1796875" style="57" customWidth="1"/>
-    <col min="2" max="2" width="16.54296875" style="57" customWidth="1"/>
-    <col min="3" max="3" width="19.90625" style="57" customWidth="1"/>
-    <col min="4" max="4" width="18.81640625" style="57" customWidth="1"/>
-    <col min="5" max="5" width="12.90625" style="57" customWidth="1"/>
-    <col min="6" max="8" width="0" style="57" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="8.81640625" style="57"/>
-    <col min="10" max="10" width="17.90625" style="57" customWidth="1"/>
-    <col min="11" max="11" width="14.1796875" style="57" customWidth="1"/>
-    <col min="12" max="16384" width="8.81640625" style="57"/>
+    <col min="1" max="1" customWidth="true" style="57" width="18.1796875"/>
+    <col min="2" max="2" customWidth="true" style="57" width="16.54296875"/>
+    <col min="3" max="3" customWidth="true" style="57" width="19.90625"/>
+    <col min="4" max="4" customWidth="true" style="57" width="18.81640625"/>
+    <col min="5" max="5" customWidth="true" style="57" width="12.90625"/>
+    <col min="6" max="8" customWidth="true" hidden="true" style="57" width="0.0"/>
+    <col min="9" max="9" style="57" width="8.81640625"/>
+    <col min="10" max="10" customWidth="true" style="57" width="17.90625"/>
+    <col min="11" max="11" customWidth="true" style="57" width="14.1796875"/>
+    <col min="12" max="16384" style="57" width="8.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -3429,12 +3466,12 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="15.08984375" style="57" customWidth="1"/>
-    <col min="2" max="2" width="15.81640625" style="57" customWidth="1"/>
-    <col min="3" max="3" width="17.81640625" style="57" customWidth="1"/>
-    <col min="4" max="4" width="16.81640625" style="57" customWidth="1"/>
-    <col min="5" max="5" width="15.6328125" style="57" customWidth="1"/>
-    <col min="6" max="16384" width="8.81640625" style="57"/>
+    <col min="1" max="1" customWidth="true" style="57" width="15.08984375"/>
+    <col min="2" max="2" customWidth="true" style="57" width="15.81640625"/>
+    <col min="3" max="3" customWidth="true" style="57" width="17.81640625"/>
+    <col min="4" max="4" customWidth="true" style="57" width="16.81640625"/>
+    <col min="5" max="5" customWidth="true" style="57" width="15.6328125"/>
+    <col min="6" max="16384" style="57" width="8.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -3512,20 +3549,20 @@
   <dimension ref="A1:AB6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="51.81640625" customWidth="1"/>
-    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="51.81640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="9.453125"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="18.453125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="14.453125"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="18.453125"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="18.453125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="12.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28">
@@ -3643,16 +3680,16 @@
         <v>13</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>407</v>
+        <v>474</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>408</v>
+        <v>475</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>19</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>409</v>
+        <v>476</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>13</v>
@@ -3661,13 +3698,13 @@
         <v>14</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>410</v>
+        <v>477</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>100</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>411</v>
+        <v>478</v>
       </c>
       <c r="S2" s="3" t="s">
         <v>14</v>
@@ -3944,10 +3981,10 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="76.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="76.1796875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="13.453125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="12.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4027,12 +4064,12 @@
   <dimension ref="A1:E15"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="18.453125" style="57" customWidth="1"/>
-    <col min="2" max="2" width="12.54296875" style="57" customWidth="1"/>
-    <col min="3" max="3" width="14.81640625" style="57" customWidth="1"/>
-    <col min="4" max="4" width="11.81640625" style="57" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.1796875" style="57" customWidth="1"/>
-    <col min="6" max="16384" width="8.81640625" style="57"/>
+    <col min="1" max="1" customWidth="true" style="57" width="18.453125"/>
+    <col min="2" max="2" customWidth="true" style="57" width="12.54296875"/>
+    <col min="3" max="3" customWidth="true" style="57" width="14.81640625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="57" width="11.81640625"/>
+    <col min="5" max="5" customWidth="true" style="57" width="18.1796875"/>
+    <col min="6" max="16384" style="57" width="8.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4224,8 +4261,8 @@
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="12.54296875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -4262,11 +4299,11 @@
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="33.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="33.54296875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="13.453125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="12.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4415,30 +4452,30 @@
   <dimension ref="A1:AG4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="49.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="49.81640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="4.81640625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="4.453125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="4.453125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="4.453125"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="4.453125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="4.453125"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="4.453125"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="4.453125"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" width="5.453125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33">
@@ -4747,7 +4784,7 @@
   <dimension ref="A1:AD9"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30">
@@ -5307,11 +5344,11 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="35.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="35.1796875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="11.54296875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="13.453125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -5392,8 +5429,8 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="33.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="33.54296875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="13.453125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5446,8 +5483,8 @@
   <dimension ref="A1:AC4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="5" max="5" width="6.1796875" customWidth="1"/>
-    <col min="29" max="29" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" customWidth="true" width="6.1796875"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="13.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -5737,14 +5774,14 @@
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="63.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="63.81640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="10.81640625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="19.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="15.54296875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="8" max="9" bestFit="true" customWidth="true" width="19.453125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -5877,23 +5914,23 @@
   <dimension ref="A1:R6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="12.0"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="9.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="6.1796875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="13.81640625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="7.453125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="18.453125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="18.453125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="11.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -6471,8 +6508,8 @@
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="32.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="32.1796875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -6570,9 +6607,9 @@
   <dimension ref="A1:E17"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="24.90625" style="57" customWidth="1"/>
-    <col min="2" max="2" width="17.453125" style="57" customWidth="1"/>
-    <col min="3" max="16384" width="8.81640625" style="57"/>
+    <col min="1" max="1" customWidth="true" style="57" width="24.90625"/>
+    <col min="2" max="2" customWidth="true" style="57" width="17.453125"/>
+    <col min="3" max="16384" style="57" width="8.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -6781,14 +6818,14 @@
   <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="39.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="39.453125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="21.81640625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="9.453125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="6.453125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="18.453125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -6888,15 +6925,15 @@
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="32.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.453125" customWidth="1"/>
-    <col min="5" max="5" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="32.1796875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="4" max="4" customWidth="true" width="15.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="17.54296875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -7052,16 +7089,16 @@
   <dimension ref="A1:K4"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.90625" style="57" customWidth="1"/>
-    <col min="2" max="2" width="11.81640625" style="57" customWidth="1"/>
-    <col min="3" max="3" width="13" style="57" customWidth="1"/>
-    <col min="4" max="4" width="16.54296875" style="57" customWidth="1"/>
-    <col min="5" max="5" width="15.81640625" style="57" customWidth="1"/>
-    <col min="6" max="6" width="8.81640625" style="57"/>
-    <col min="7" max="7" width="17.81640625" style="57" customWidth="1"/>
-    <col min="8" max="8" width="15.453125" style="57" customWidth="1"/>
-    <col min="9" max="9" width="11.54296875" style="57" customWidth="1"/>
-    <col min="10" max="16384" width="8.81640625" style="57"/>
+    <col min="1" max="1" customWidth="true" style="57" width="17.90625"/>
+    <col min="2" max="2" customWidth="true" style="57" width="11.81640625"/>
+    <col min="3" max="3" customWidth="true" style="57" width="13.0"/>
+    <col min="4" max="4" customWidth="true" style="57" width="16.54296875"/>
+    <col min="5" max="5" customWidth="true" style="57" width="15.81640625"/>
+    <col min="6" max="6" style="57" width="8.81640625"/>
+    <col min="7" max="7" customWidth="true" style="57" width="17.81640625"/>
+    <col min="8" max="8" customWidth="true" style="57" width="15.453125"/>
+    <col min="9" max="9" customWidth="true" style="57" width="11.54296875"/>
+    <col min="10" max="16384" style="57" width="8.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -7197,11 +7234,11 @@
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="39.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="39.453125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="13.54296875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="7.81640625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="9.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -7269,10 +7306,10 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="57.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="57.453125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="15.54296875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="7.81640625"/>
+    <col min="4" max="5" bestFit="true" customWidth="true" width="11.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -7389,22 +7426,22 @@
   <dimension ref="A1:P5"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="42" style="45" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.36328125" style="45" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.08984375" style="45" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.36328125" style="45" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.1796875" style="45" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.453125" style="45" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="8.81640625" style="45"/>
-    <col min="9" max="9" width="10.453125" style="45" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.1796875" style="45" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.453125" style="45" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.1796875" style="45" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.453125" style="45" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.1796875" style="45" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13" style="45" customWidth="1"/>
-    <col min="16" max="16" width="10.1796875" style="45" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.81640625" style="45"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="45" width="42.0"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="45" width="18.36328125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="45" width="12.08984375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="45" width="15.36328125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="45" width="12.1796875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="45" width="9.453125"/>
+    <col min="7" max="8" style="45" width="8.81640625"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="45" width="10.453125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="45" width="11.1796875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="45" width="10.453125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="45" width="11.1796875"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="45" width="10.453125"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="45" width="8.1796875"/>
+    <col min="15" max="15" customWidth="true" style="45" width="13.0"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="45" width="10.1796875"/>
+    <col min="17" max="16384" style="45" width="8.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -7598,29 +7635,29 @@
   <dimension ref="A1:AB7"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="44.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="44.81640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.81640625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="8.1796875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="10.453125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="13.54296875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="17.81640625"/>
+    <col min="11" max="12" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="18.1796875"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="7.81640625"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="8.1796875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="14.1796875"/>
+    <col min="27" max="28" bestFit="true" customWidth="true" width="12.81640625"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="14.1796875"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="12.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28">
@@ -7987,9 +8024,9 @@
   <dimension ref="A1:W17"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="54.36328125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="54.36328125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="13.90625"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="13.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -8740,16 +8777,16 @@
   <dimension ref="A1:S20"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="53.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="12.1796875" customWidth="1"/>
-    <col min="8" max="8" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="53.81640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="3" max="4" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="5" max="7" customWidth="true" width="12.1796875"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="12.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19">

--- a/src/test/java/TestData/Scenario_TestData.xlsx
+++ b/src/test/java/TestData/Scenario_TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Copa_SHD_WebServices\src\test\java\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AC08DA2-780B-4877-BF49-1094BB8DC7B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E40A3E90-F46D-4840-8EF9-19D47CE0FD36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3470" yWindow="2840" windowWidth="14400" windowHeight="7360" activeTab="2" xr2:uid="{5D5A4724-D560-4FC2-9708-4BBF1DBA0B11}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="10" activeTab="13" xr2:uid="{5D5A4724-D560-4FC2-9708-4BBF1DBA0B11}"/>
   </bookViews>
   <sheets>
     <sheet name="AdvancePassengerInfo" sheetId="1" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1417" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="475">
   <si>
     <t>Scenario</t>
   </si>
@@ -1289,21 +1289,6 @@
     <t>2302181931005</t>
   </si>
   <si>
-    <t>BO2Z3G</t>
-  </si>
-  <si>
-    <t>2023-07-21T07:59:00</t>
-  </si>
-  <si>
-    <t>2023-07-21T12:07:00</t>
-  </si>
-  <si>
-    <t>2023-07-25T06:22:00</t>
-  </si>
-  <si>
-    <t>2023-07-25T08:32:00</t>
-  </si>
-  <si>
     <t>BO20PH</t>
   </si>
   <si>
@@ -1370,12 +1355,6 @@
     <t>2023-07-21T15:33:00</t>
   </si>
   <si>
-    <t>BPG42L</t>
-  </si>
-  <si>
-    <t>BPG42T</t>
-  </si>
-  <si>
     <t>BPG5BB</t>
   </si>
   <si>
@@ -1478,18 +1457,6 @@
     <t>C</t>
   </si>
   <si>
-    <t>ACYUM3</t>
-  </si>
-  <si>
-    <t>ACYXQA</t>
-  </si>
-  <si>
-    <t>ACYX1J</t>
-  </si>
-  <si>
-    <t>ACYZAP</t>
-  </si>
-  <si>
     <t>ACYZCC</t>
   </si>
   <si>
@@ -1505,13 +1472,25 @@
     <t>2023-08-01T08:32:00</t>
   </si>
   <si>
-    <t>ACYZC4</t>
-  </si>
-  <si>
-    <t>ACYZDF</t>
-  </si>
-  <si>
-    <t>ACYZEH</t>
+    <t>AT5VTL</t>
+  </si>
+  <si>
+    <t>AT5VTO</t>
+  </si>
+  <si>
+    <t>472</t>
+  </si>
+  <si>
+    <t>473</t>
+  </si>
+  <si>
+    <t>AT5XDJ</t>
+  </si>
+  <si>
+    <t>AT5XFV</t>
+  </si>
+  <si>
+    <t>AT5XGP</t>
   </si>
 </sst>
 </file>
@@ -2201,7 +2180,7 @@
         <v>16</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>266</v>
@@ -2218,7 +2197,7 @@
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
       <c r="O2" s="3" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="P2" s="24"/>
     </row>
@@ -2426,10 +2405,10 @@
         <v>0</v>
       </c>
       <c r="K3" s="48" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="L3" s="48" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="M3" s="48"/>
       <c r="N3" s="48"/>
@@ -2490,10 +2469,10 @@
       <c r="I5" s="48"/>
       <c r="J5" s="48"/>
       <c r="K5" s="48" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="L5" s="48" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="M5" s="48"/>
       <c r="N5" s="48" t="s">
@@ -2537,7 +2516,7 @@
       <c r="I6" s="48"/>
       <c r="J6" s="48"/>
       <c r="K6" s="48" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="L6" s="48"/>
       <c r="M6" s="48"/>
@@ -2548,7 +2527,7 @@
         <v>300</v>
       </c>
       <c r="P6" s="48" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="Q6" s="37"/>
       <c r="R6" s="48"/>
@@ -2582,10 +2561,10 @@
       <c r="I7" s="48"/>
       <c r="J7" s="48"/>
       <c r="K7" s="48" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="L7" s="48" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="M7" s="48"/>
       <c r="N7" s="48" t="s">
@@ -2595,13 +2574,13 @@
         <v>300</v>
       </c>
       <c r="P7" s="48" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="Q7" s="55" t="s">
         <v>115</v>
       </c>
       <c r="R7" s="48" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="S7" s="48"/>
       <c r="T7" s="48"/>
@@ -2637,10 +2616,10 @@
       </c>
       <c r="J8" s="48"/>
       <c r="K8" s="48" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="L8" s="48" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="M8" s="48"/>
       <c r="N8" s="48" t="s">
@@ -2678,7 +2657,7 @@
       <c r="I9" s="48"/>
       <c r="J9" s="48"/>
       <c r="K9" s="48" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="L9" s="48"/>
       <c r="M9" s="48"/>
@@ -2717,10 +2696,10 @@
       <c r="I10" s="48"/>
       <c r="J10" s="48"/>
       <c r="K10" s="48" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="L10" s="48" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="M10" s="48"/>
       <c r="N10" s="48"/>
@@ -2756,10 +2735,10 @@
       <c r="I11" s="48"/>
       <c r="J11" s="48"/>
       <c r="K11" s="48" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="L11" s="48" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="M11" s="48"/>
       <c r="N11" s="48"/>
@@ -2795,10 +2774,10 @@
       <c r="I12" s="48"/>
       <c r="J12" s="48"/>
       <c r="K12" s="48" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="L12" s="48" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="M12" s="48"/>
       <c r="N12" s="48" t="s">
@@ -2838,10 +2817,10 @@
       <c r="I13" s="48"/>
       <c r="J13" s="48"/>
       <c r="K13" s="48" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="L13" s="48" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="M13" s="48"/>
       <c r="N13" s="48" t="s">
@@ -2916,10 +2895,10 @@
       <c r="I15" s="48"/>
       <c r="J15" s="48"/>
       <c r="K15" s="48" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="L15" s="48" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="M15" s="48"/>
       <c r="N15" s="48" t="s">
@@ -2959,7 +2938,7 @@
       <c r="I16" s="48"/>
       <c r="J16" s="48"/>
       <c r="K16" s="48" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="L16" s="48"/>
       <c r="M16" s="48"/>
@@ -2998,7 +2977,7 @@
       <c r="I17" s="48"/>
       <c r="J17" s="48"/>
       <c r="K17" s="48" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="L17" s="48"/>
       <c r="M17" s="48"/>
@@ -3041,7 +3020,7 @@
       </c>
       <c r="J18" s="48"/>
       <c r="K18" s="48" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="L18" s="48"/>
       <c r="M18" s="48"/>
@@ -3080,7 +3059,7 @@
       <c r="I19" s="48"/>
       <c r="J19" s="48"/>
       <c r="K19" s="48" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="L19" s="48"/>
       <c r="M19" s="48"/>
@@ -3119,7 +3098,7 @@
       <c r="I20" s="48"/>
       <c r="J20" s="48"/>
       <c r="K20" s="48" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="L20" s="48"/>
       <c r="M20" s="48"/>
@@ -3158,7 +3137,7 @@
       <c r="I21" s="48"/>
       <c r="J21" s="48"/>
       <c r="K21" s="48" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="L21" s="48"/>
       <c r="M21" s="48"/>
@@ -3258,10 +3237,10 @@
         <v>2</v>
       </c>
       <c r="D2" s="62" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="E2" s="62" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="F2" s="60"/>
       <c r="G2" s="63"/>
@@ -3277,7 +3256,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="62" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="E3" s="62" t="s">
         <v>323</v>
@@ -3298,7 +3277,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="62" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="E4" s="60"/>
       <c r="F4" s="60" t="s">
@@ -3426,13 +3405,13 @@
       <c r="G5" s="60"/>
       <c r="H5" s="60"/>
       <c r="I5" s="60" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="J5" s="60" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="K5" s="60" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -3658,38 +3637,38 @@
       <c r="B2" s="18">
         <v>1</v>
       </c>
-      <c r="C2" s="18" t="s">
-        <v>19</v>
+      <c r="C2" s="62" t="s">
+        <v>470</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F2" s="18">
-        <v>5</v>
-      </c>
-      <c r="G2" s="18" t="s">
-        <v>100</v>
+        <v>2</v>
+      </c>
+      <c r="G2" s="62" t="s">
+        <v>471</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>19</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>13</v>
@@ -3698,13 +3677,13 @@
         <v>14</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>100</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="S2" s="3" t="s">
         <v>14</v>
@@ -3880,16 +3859,16 @@
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>19</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>13</v>
@@ -4967,7 +4946,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>376</v>
@@ -6290,16 +6269,16 @@
         <v>202</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>270</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>13</v>
@@ -6308,13 +6287,13 @@
         <v>271</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>272</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="S2" s="3" t="s">
         <v>271</v>
@@ -6323,7 +6302,7 @@
         <v>202</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="3" spans="1:21">
@@ -6880,10 +6859,10 @@
         <v>65</v>
       </c>
       <c r="H2" s="26" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="I2" s="26" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -6903,7 +6882,7 @@
         <v>14</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="G3" s="18" t="s">
         <v>65</v>
@@ -7528,7 +7507,7 @@
       <c r="M2" s="48"/>
       <c r="N2" s="48"/>
       <c r="O2" s="48" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="P2" s="48"/>
     </row>
@@ -8129,10 +8108,10 @@
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
       <c r="R2" s="3" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
@@ -8391,10 +8370,10 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="T8" s="3">
         <v>0</v>
@@ -8440,10 +8419,10 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="T9" s="3"/>
       <c r="U9" s="3">

--- a/src/test/java/TestData/Scenario_TestData.xlsx
+++ b/src/test/java/TestData/Scenario_TestData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ArunJK\Arun\Copa_SHDWebservices\src\test\java\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Copa_SHD_WebServices\src\test\java\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E662EAE1-32DF-47F1-A381-E410889821C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C83B784-0081-406B-869E-EC4C530DFF3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{5D5A4724-D560-4FC2-9708-4BBF1DBA0B11}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="2" activeTab="5" xr2:uid="{5D5A4724-D560-4FC2-9708-4BBF1DBA0B11}"/>
   </bookViews>
   <sheets>
     <sheet name="AdvancePassengerInfo" sheetId="1" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1534" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1648" uniqueCount="553">
   <si>
     <t>Scenario</t>
   </si>
@@ -1145,9 +1145,6 @@
     <t>2023-08-10T07:52:56</t>
   </si>
   <si>
-    <t>AVDA0V</t>
-  </si>
-  <si>
     <t>AVDPLZ</t>
   </si>
   <si>
@@ -1520,27 +1517,15 @@
     <t>AVXXET</t>
   </si>
   <si>
-    <t>AVX1LH</t>
-  </si>
-  <si>
-    <t>AVX1NK</t>
-  </si>
-  <si>
     <t>AVX1NQ</t>
   </si>
   <si>
     <t>Modify_API_for_deleting_API_data</t>
   </si>
   <si>
-    <t>AVXDLD</t>
-  </si>
-  <si>
     <t>Collect_API_for_a_Single_passenger</t>
   </si>
   <si>
-    <t>AVWCZ2</t>
-  </si>
-  <si>
     <t>ELON</t>
   </si>
   <si>
@@ -1560,6 +1545,186 @@
   </si>
   <si>
     <t>AVX2H3</t>
+  </si>
+  <si>
+    <t>AgencyName</t>
+  </si>
+  <si>
+    <t>AgencyName1</t>
+  </si>
+  <si>
+    <t>192</t>
+  </si>
+  <si>
+    <t>AXAW2F</t>
+  </si>
+  <si>
+    <t>BKPXHF</t>
+  </si>
+  <si>
+    <t>JOE</t>
+  </si>
+  <si>
+    <t>ROCK</t>
+  </si>
+  <si>
+    <t>430</t>
+  </si>
+  <si>
+    <t>Create_booking_service_3pax</t>
+  </si>
+  <si>
+    <t>851</t>
+  </si>
+  <si>
+    <t>AVVBPK</t>
+  </si>
+  <si>
+    <t>HELLO</t>
+  </si>
+  <si>
+    <t>JOKER</t>
+  </si>
+  <si>
+    <t>Create_booking_service_add_passenger_message</t>
+  </si>
+  <si>
+    <t>AVVGCZ</t>
+  </si>
+  <si>
+    <t>VASUDHA</t>
+  </si>
+  <si>
+    <t>SARADAGI</t>
+  </si>
+  <si>
+    <t>Create_booking_service_cancel_held_seats</t>
+  </si>
+  <si>
+    <t>460</t>
+  </si>
+  <si>
+    <t>AVU5YY</t>
+  </si>
+  <si>
+    <t>MARINO</t>
+  </si>
+  <si>
+    <t>MIKKEL</t>
+  </si>
+  <si>
+    <t>Basic seat change</t>
+  </si>
+  <si>
+    <t>371</t>
+  </si>
+  <si>
+    <t>HAV</t>
+  </si>
+  <si>
+    <t>AXCAP5</t>
+  </si>
+  <si>
+    <t>JACK</t>
+  </si>
+  <si>
+    <t>SPARROW</t>
+  </si>
+  <si>
+    <t>PAOU</t>
+  </si>
+  <si>
+    <t>CUIN</t>
+  </si>
+  <si>
+    <t>10E</t>
+  </si>
+  <si>
+    <t>Thru_checkin_Seg1</t>
+  </si>
+  <si>
+    <t>AW44YC</t>
+  </si>
+  <si>
+    <t>ABCDEFGH</t>
+  </si>
+  <si>
+    <t>IJKLMN</t>
+  </si>
+  <si>
+    <t>XYZLMNOP</t>
+  </si>
+  <si>
+    <t>USSF</t>
+  </si>
+  <si>
+    <t>USIN</t>
+  </si>
+  <si>
+    <t>Thru_checkin_Seg2</t>
+  </si>
+  <si>
+    <t>782</t>
+  </si>
+  <si>
+    <t>Check_in_FF_pax</t>
+  </si>
+  <si>
+    <t>AW413R</t>
+  </si>
+  <si>
+    <t>null</t>
+  </si>
+  <si>
+    <t>AgencyName2</t>
+  </si>
+  <si>
+    <t>Check_in_Non_Revenue_pax</t>
+  </si>
+  <si>
+    <t>AXAB3T</t>
+  </si>
+  <si>
+    <t>KLABEN</t>
+  </si>
+  <si>
+    <t>SHANE</t>
+  </si>
+  <si>
+    <t>Error_check_in_invalid_pax</t>
+  </si>
+  <si>
+    <t>Check_in_specific_pax_in_group</t>
+  </si>
+  <si>
+    <t>AW41YI</t>
+  </si>
+  <si>
+    <t>MYBIGFAMILY</t>
+  </si>
+  <si>
+    <t>AXGZ5A</t>
+  </si>
+  <si>
+    <t>AXG0A0</t>
+  </si>
+  <si>
+    <t>AXG0BB</t>
+  </si>
+  <si>
+    <t>AXG0CN</t>
+  </si>
+  <si>
+    <t>AXG0MH</t>
+  </si>
+  <si>
+    <t>AXG1IY</t>
+  </si>
+  <si>
+    <t>AXG1S5</t>
+  </si>
+  <si>
+    <t>AXG5CQ</t>
   </si>
 </sst>
 </file>
@@ -1759,7 +1924,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1846,6 +2011,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2164,22 +2331,22 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:P15"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="52.77734375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="18.44140625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="15.44140625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="9.44140625"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="17.5546875"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="10.44140625"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="11.21875"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="10.44140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="11.21875"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="10.44140625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="11.21875"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="15.21875"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="52.81640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="18.453125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="9.453125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="10.453125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="10.453125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="10.453125"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="15.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2252,7 +2419,7 @@
         <v>15</v>
       </c>
       <c r="H2" s="49" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="I2" s="49" t="s">
         <v>212</v>
@@ -2269,7 +2436,7 @@
       <c r="M2" s="49"/>
       <c r="N2" s="49"/>
       <c r="O2" s="49" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="P2" s="56"/>
     </row>
@@ -2320,19 +2487,19 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="55" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="B4" s="55">
         <v>0</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="D4" s="55" t="s">
         <v>12</v>
       </c>
       <c r="E4" s="55" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F4" s="55" t="s">
         <v>14</v>
@@ -2341,13 +2508,13 @@
         <v>15</v>
       </c>
       <c r="H4" s="55" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="I4" s="55" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="J4" s="55" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="K4" s="49"/>
       <c r="L4" s="49"/>
@@ -2357,19 +2524,19 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="55" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B5" s="55">
         <v>0</v>
       </c>
       <c r="C5" s="57" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="D5" s="55" t="s">
         <v>12</v>
       </c>
       <c r="E5" s="55" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F5" s="55" t="s">
         <v>14</v>
@@ -2378,7 +2545,7 @@
         <v>15</v>
       </c>
       <c r="H5" s="55" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="I5" s="49"/>
       <c r="J5" s="49"/>
@@ -2409,11 +2576,11 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C501783-003E-43C7-BF08-448ED073E85B}">
   <dimension ref="A1:U22"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="10" max="10" style="36" width="8.77734375"/>
-    <col min="12" max="12" customWidth="true" width="15.88671875"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="9.77734375"/>
+    <col min="10" max="10" style="36" width="8.81640625"/>
+    <col min="12" max="12" customWidth="true" width="15.90625"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="9.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
@@ -2501,7 +2668,7 @@
         <v>3</v>
       </c>
       <c r="G2" s="53" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2" s="46" t="s">
         <v>12</v>
@@ -2511,7 +2678,7 @@
       </c>
       <c r="J2" s="39"/>
       <c r="K2" s="39" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L2" s="39"/>
       <c r="M2" s="39"/>
@@ -2548,10 +2715,10 @@
         <v>0</v>
       </c>
       <c r="K3" s="39" t="s">
+        <v>395</v>
+      </c>
+      <c r="L3" s="39" t="s">
         <v>396</v>
-      </c>
-      <c r="L3" s="39" t="s">
-        <v>397</v>
       </c>
       <c r="M3" s="39"/>
       <c r="N3" s="39"/>
@@ -2628,10 +2795,10 @@
       </c>
       <c r="J5" s="39"/>
       <c r="K5" s="39" t="s">
+        <v>398</v>
+      </c>
+      <c r="L5" s="39" t="s">
         <v>399</v>
-      </c>
-      <c r="L5" s="39" t="s">
-        <v>400</v>
       </c>
       <c r="M5" s="39"/>
       <c r="N5" s="39" t="s">
@@ -2675,7 +2842,7 @@
       <c r="I6" s="46"/>
       <c r="J6" s="39"/>
       <c r="K6" s="39" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="L6" s="39"/>
       <c r="M6" s="39"/>
@@ -2686,7 +2853,7 @@
         <v>243</v>
       </c>
       <c r="P6" s="39" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="Q6" s="28"/>
       <c r="R6" s="39"/>
@@ -2720,10 +2887,10 @@
       <c r="I7" s="46"/>
       <c r="J7" s="39"/>
       <c r="K7" s="39" t="s">
+        <v>402</v>
+      </c>
+      <c r="L7" s="39" t="s">
         <v>403</v>
-      </c>
-      <c r="L7" s="39" t="s">
-        <v>404</v>
       </c>
       <c r="M7" s="39"/>
       <c r="N7" s="39" t="s">
@@ -2733,13 +2900,13 @@
         <v>243</v>
       </c>
       <c r="P7" s="39" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="Q7" s="45" t="s">
         <v>87</v>
       </c>
       <c r="R7" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="S7" s="39"/>
       <c r="T7" s="39"/>
@@ -2765,7 +2932,7 @@
         <v>3</v>
       </c>
       <c r="G8" s="53" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H8" s="46" t="s">
         <v>12</v>
@@ -2775,10 +2942,10 @@
       </c>
       <c r="J8" s="39"/>
       <c r="K8" s="39" t="s">
+        <v>423</v>
+      </c>
+      <c r="L8" s="39" t="s">
         <v>424</v>
-      </c>
-      <c r="L8" s="39" t="s">
-        <v>425</v>
       </c>
       <c r="M8" s="39"/>
       <c r="N8" s="39" t="s">
@@ -2816,7 +2983,7 @@
       <c r="I9" s="46"/>
       <c r="J9" s="39"/>
       <c r="K9" s="39" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="L9" s="39"/>
       <c r="M9" s="39"/>
@@ -2855,10 +3022,10 @@
       <c r="I10" s="46"/>
       <c r="J10" s="39"/>
       <c r="K10" s="39" t="s">
+        <v>407</v>
+      </c>
+      <c r="L10" s="39" t="s">
         <v>408</v>
-      </c>
-      <c r="L10" s="39" t="s">
-        <v>409</v>
       </c>
       <c r="M10" s="39"/>
       <c r="N10" s="39"/>
@@ -2902,10 +3069,10 @@
       </c>
       <c r="J11" s="39"/>
       <c r="K11" s="39" t="s">
+        <v>383</v>
+      </c>
+      <c r="L11" s="39" t="s">
         <v>384</v>
-      </c>
-      <c r="L11" s="39" t="s">
-        <v>385</v>
       </c>
       <c r="M11" s="39"/>
       <c r="N11" s="39"/>
@@ -2941,10 +3108,10 @@
       <c r="I12" s="46"/>
       <c r="J12" s="39"/>
       <c r="K12" s="39" t="s">
+        <v>385</v>
+      </c>
+      <c r="L12" s="39" t="s">
         <v>386</v>
-      </c>
-      <c r="L12" s="39" t="s">
-        <v>387</v>
       </c>
       <c r="M12" s="39"/>
       <c r="N12" s="39" t="s">
@@ -2984,10 +3151,10 @@
       <c r="I13" s="46"/>
       <c r="J13" s="39"/>
       <c r="K13" s="39" t="s">
+        <v>387</v>
+      </c>
+      <c r="L13" s="39" t="s">
         <v>388</v>
-      </c>
-      <c r="L13" s="39" t="s">
-        <v>389</v>
       </c>
       <c r="M13" s="39"/>
       <c r="N13" s="39" t="s">
@@ -3062,10 +3229,10 @@
       <c r="I15" s="46"/>
       <c r="J15" s="39"/>
       <c r="K15" s="39" t="s">
+        <v>389</v>
+      </c>
+      <c r="L15" s="39" t="s">
         <v>390</v>
-      </c>
-      <c r="L15" s="39" t="s">
-        <v>391</v>
       </c>
       <c r="M15" s="39"/>
       <c r="N15" s="39" t="s">
@@ -3105,7 +3272,7 @@
       <c r="I16" s="46"/>
       <c r="J16" s="39"/>
       <c r="K16" s="39" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="L16" s="39"/>
       <c r="M16" s="39"/>
@@ -3144,7 +3311,7 @@
       <c r="I17" s="46"/>
       <c r="J17" s="39"/>
       <c r="K17" s="39" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L17" s="39"/>
       <c r="M17" s="39"/>
@@ -3177,7 +3344,7 @@
         <v>3</v>
       </c>
       <c r="G18" s="53" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H18" s="46" t="s">
         <v>12</v>
@@ -3187,7 +3354,7 @@
       </c>
       <c r="J18" s="39"/>
       <c r="K18" s="39" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="L18" s="39"/>
       <c r="M18" s="39"/>
@@ -3226,7 +3393,7 @@
       <c r="I19" s="46"/>
       <c r="J19" s="39"/>
       <c r="K19" s="39" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="L19" s="39"/>
       <c r="M19" s="39"/>
@@ -3265,7 +3432,7 @@
       <c r="I20" s="46"/>
       <c r="J20" s="39"/>
       <c r="K20" s="39" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L20" s="39"/>
       <c r="M20" s="39"/>
@@ -3312,7 +3479,7 @@
       </c>
       <c r="J21" s="39"/>
       <c r="K21" s="39" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="L21" s="39"/>
       <c r="M21" s="39"/>
@@ -3349,7 +3516,7 @@
         <v>3</v>
       </c>
       <c r="G22" s="53" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H22" s="46" t="s">
         <v>12</v>
@@ -3359,7 +3526,7 @@
       </c>
       <c r="J22" s="39"/>
       <c r="K22" s="39" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="L22" s="39"/>
       <c r="M22" s="39"/>
@@ -3384,18 +3551,18 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2EA1F88-8B75-4AAD-A17A-063CA3659CA4}">
   <dimension ref="A1:N4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="32.88671875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.5546875"/>
-    <col min="3" max="3" customWidth="true" style="46" width="17.5546875"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="32.90625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="3" max="3" customWidth="true" style="46" width="17.54296875"/>
     <col min="4" max="4" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="5" max="5" customWidth="true" width="13.77734375"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="14.33203125"/>
-    <col min="7" max="11" customWidth="true" style="46" width="14.33203125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="30.33203125"/>
-    <col min="13" max="13" customWidth="true" width="8.44140625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="10.88671875"/>
+    <col min="5" max="5" customWidth="true" width="13.81640625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="14.36328125"/>
+    <col min="7" max="11" customWidth="true" style="46" width="14.36328125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="30.36328125"/>
+    <col min="13" max="13" customWidth="true" width="8.453125"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="10.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -3450,7 +3617,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="51" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D2" s="52" t="s">
         <v>12</v>
@@ -3477,10 +3644,10 @@
         <v>6</v>
       </c>
       <c r="L2" s="51" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="M2" s="51" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="N2" s="49"/>
     </row>
@@ -3492,7 +3659,7 @@
         <v>4</v>
       </c>
       <c r="C3" s="51" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D3" s="52" t="s">
         <v>12</v>
@@ -3519,7 +3686,7 @@
         <v>6</v>
       </c>
       <c r="L3" s="51" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="M3" s="51" t="s">
         <v>265</v>
@@ -3536,7 +3703,7 @@
         <v>4</v>
       </c>
       <c r="C4" s="51" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D4" s="52" t="s">
         <v>12</v>
@@ -3563,7 +3730,7 @@
         <v>6</v>
       </c>
       <c r="L4" s="51" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="M4" s="49"/>
       <c r="N4" s="49" t="s">
@@ -3578,19 +3745,19 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88414653-50FA-4845-96AF-5B777BBDF907}">
   <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="46" width="21.77734375"/>
-    <col min="2" max="2" customWidth="true" style="46" width="16.5546875"/>
-    <col min="3" max="3" customWidth="true" style="46" width="19.88671875"/>
-    <col min="4" max="4" customWidth="true" style="46" width="18.77734375"/>
-    <col min="5" max="6" customWidth="true" style="46" width="12.88671875"/>
+    <col min="1" max="1" customWidth="true" style="46" width="21.81640625"/>
+    <col min="2" max="2" customWidth="true" style="46" width="16.54296875"/>
+    <col min="3" max="3" customWidth="true" style="46" width="19.90625"/>
+    <col min="4" max="4" customWidth="true" style="46" width="18.81640625"/>
+    <col min="5" max="6" customWidth="true" style="46" width="12.90625"/>
     <col min="7" max="7" bestFit="true" customWidth="true" style="46" width="15.0"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="46" width="11.88671875"/>
-    <col min="9" max="9" style="46" width="8.77734375"/>
-    <col min="10" max="10" customWidth="true" style="46" width="17.88671875"/>
-    <col min="11" max="11" customWidth="true" style="46" width="14.21875"/>
-    <col min="12" max="16384" style="46" width="8.77734375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="46" width="11.90625"/>
+    <col min="9" max="9" style="46" width="8.81640625"/>
+    <col min="10" max="10" customWidth="true" style="46" width="17.90625"/>
+    <col min="11" max="11" customWidth="true" style="46" width="14.1796875"/>
+    <col min="12" max="16384" style="46" width="8.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -3703,13 +3870,13 @@
         <v>12</v>
       </c>
       <c r="I5" s="49" t="s">
+        <v>438</v>
+      </c>
+      <c r="J5" s="49" t="s">
         <v>439</v>
       </c>
-      <c r="J5" s="49" t="s">
+      <c r="K5" s="49" t="s">
         <v>440</v>
-      </c>
-      <c r="K5" s="49" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -3736,10 +3903,10 @@
         <v>12</v>
       </c>
       <c r="I6" s="49" t="s">
+        <v>441</v>
+      </c>
+      <c r="J6" s="49" t="s">
         <v>442</v>
-      </c>
-      <c r="J6" s="49" t="s">
-        <v>443</v>
       </c>
       <c r="K6" s="49"/>
     </row>
@@ -3754,14 +3921,14 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="46" width="42.21875"/>
-    <col min="2" max="2" customWidth="true" style="46" width="15.77734375"/>
-    <col min="3" max="3" customWidth="true" style="46" width="17.77734375"/>
-    <col min="4" max="4" customWidth="true" style="46" width="16.77734375"/>
-    <col min="5" max="5" customWidth="true" style="46" width="15.6640625"/>
-    <col min="6" max="16384" style="46" width="8.77734375"/>
+    <col min="1" max="1" customWidth="true" style="46" width="42.1796875"/>
+    <col min="2" max="2" customWidth="true" style="46" width="15.81640625"/>
+    <col min="3" max="3" customWidth="true" style="46" width="17.81640625"/>
+    <col min="4" max="4" customWidth="true" style="46" width="16.81640625"/>
+    <col min="5" max="5" customWidth="true" style="46" width="15.6328125"/>
+    <col min="6" max="16384" style="46" width="8.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -3828,7 +3995,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="55" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B5" s="55"/>
       <c r="C5" s="55" t="s">
@@ -3839,7 +4006,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="55" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B6" s="55"/>
       <c r="C6" s="55" t="s">
@@ -3852,7 +4019,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="55" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B7" s="55"/>
       <c r="C7" s="55" t="s">
@@ -3874,22 +4041,22 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:AB6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="51.77734375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.5546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="9.44140625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="17.5546875"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="18.44140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="14.44140625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="15.44140625"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="18.44140625"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="18.44140625"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="12.21875"/>
+    <col min="1" max="1" customWidth="true" width="51.81640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="9.453125"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="18.453125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="14.453125"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="18.453125"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="18.453125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="12.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28">
@@ -4007,16 +4174,16 @@
         <v>12</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>32</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>12</v>
@@ -4025,13 +4192,13 @@
         <v>34</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>343</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="S2" s="3" t="s">
         <v>34</v>
@@ -4077,7 +4244,7 @@
         <v>45</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>355</v>
@@ -4095,13 +4262,13 @@
         <v>12</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>338</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="S3" s="3" t="s">
         <v>12</v>
@@ -4155,16 +4322,16 @@
       <c r="H4" s="46"/>
       <c r="I4" s="46"/>
       <c r="J4" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>364</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>365</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>333</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="N4" s="3" t="s">
         <v>210</v>
@@ -4207,16 +4374,16 @@
       <c r="H5" s="46"/>
       <c r="I5" s="46"/>
       <c r="J5" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>367</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>368</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>335</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>210</v>
@@ -4267,7 +4434,7 @@
         <v>45</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>353</v>
@@ -4310,12 +4477,12 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="76.21875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="13.44140625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="12.21875"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="76.1796875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="13.453125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="12.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4395,14 +4562,14 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEA2AF7E-AC89-4B47-B4D7-D3496E5327D5}">
   <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="46" width="18.44140625"/>
-    <col min="2" max="2" customWidth="true" style="46" width="12.5546875"/>
-    <col min="3" max="3" customWidth="true" style="46" width="14.77734375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="46" width="11.77734375"/>
-    <col min="5" max="5" customWidth="true" style="46" width="18.21875"/>
-    <col min="6" max="16384" style="46" width="8.77734375"/>
+    <col min="1" max="1" customWidth="true" style="46" width="18.453125"/>
+    <col min="2" max="2" customWidth="true" style="46" width="12.54296875"/>
+    <col min="3" max="3" customWidth="true" style="46" width="14.81640625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="46" width="11.81640625"/>
+    <col min="5" max="5" customWidth="true" style="46" width="18.1796875"/>
+    <col min="6" max="16384" style="46" width="8.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4592,10 +4759,10 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F1569B0-3564-4B84-A0FB-9681D32A0E6D}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="12.5546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.5546875"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="12.54296875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -4630,13 +4797,13 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02A4FAA4-EFC6-47D3-BDEE-7F4F3353F3CD}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="33.5546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="13.44140625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="15.44140625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="12.21875"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="33.54296875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="13.453125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="12.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4681,7 +4848,7 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA6A106B-75A4-4F54-9508-A66A4AEED06E}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="5" t="s">
@@ -4783,32 +4950,32 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:AG4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="49.77734375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="4.77734375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="5.44140625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="9.77734375"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="4.44140625"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="5.44140625"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="9.77734375"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="4.44140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="5.44140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="9.77734375"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="4.44140625"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="5.44140625"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="9.77734375"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="4.44140625"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="5.44140625"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="9.77734375"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="4.44140625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="5.44140625"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="9.77734375"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="4.44140625"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" width="5.44140625"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="9.77734375"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="4.44140625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" width="5.44140625"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="49.81640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="4.81640625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="4.453125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="4.453125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="4.453125"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="4.453125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="4.453125"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="4.453125"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="4.453125"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" width="5.453125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33">
@@ -5108,9 +5275,9 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4903F224-3652-48FB-81A7-CAF06A9D7463}">
   <dimension ref="A1:AD9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.5546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30">
@@ -5229,16 +5396,16 @@
       <c r="I2" s="46"/>
       <c r="J2" s="46"/>
       <c r="K2" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>411</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>412</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>333</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>210</v>
@@ -5293,7 +5460,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>313</v>
@@ -5425,16 +5592,16 @@
       <c r="I5" s="46"/>
       <c r="J5" s="46"/>
       <c r="K5" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>333</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>210</v>
@@ -5443,7 +5610,7 @@
         <v>12</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="R5" s="16" t="s">
         <v>44</v>
@@ -5625,7 +5792,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="51" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>12</v>
@@ -5641,16 +5808,16 @@
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="L9" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="N9" s="3" t="s">
         <v>417</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>418</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>12</v>
@@ -5684,13 +5851,13 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="35.21875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="15.44140625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="11.5546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="13.44140625"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="35.1796875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="11.54296875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="13.453125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -5769,10 +5936,10 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB53E397-0E70-4FE2-8956-CAC505C79FBA}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="33.5546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="13.44140625"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="33.54296875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="13.453125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5823,10 +5990,10 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71142910-3363-4189-996E-89090332A376}">
   <dimension ref="A1:AC4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="5" max="5" customWidth="true" width="6.21875"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="13.88671875"/>
+    <col min="5" max="5" customWidth="true" width="6.1796875"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="13.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -5954,16 +6121,16 @@
       <c r="U2" s="3"/>
       <c r="V2" s="3"/>
       <c r="W2" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="X2" s="3" t="s">
         <v>444</v>
-      </c>
-      <c r="X2" s="3" t="s">
-        <v>445</v>
       </c>
       <c r="Y2" s="3" t="s">
         <v>334</v>
       </c>
       <c r="Z2" s="3" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AA2" s="3" t="s">
         <v>210</v>
@@ -5972,7 +6139,7 @@
         <v>12</v>
       </c>
       <c r="AC2" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -5983,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="53" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D3" s="46" t="s">
         <v>12</v>
@@ -5995,7 +6162,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="53" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H3" s="46" t="s">
         <v>45</v>
@@ -6007,7 +6174,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="51" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>12</v>
@@ -6019,7 +6186,7 @@
         <v>3</v>
       </c>
       <c r="O3" s="51" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="P3" s="3" t="s">
         <v>13</v>
@@ -6090,16 +6257,16 @@
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Y4" s="3" t="s">
         <v>334</v>
       </c>
       <c r="Z4" s="3" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AA4" s="3" t="s">
         <v>210</v>
@@ -6108,7 +6275,7 @@
         <v>12</v>
       </c>
       <c r="AC4" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
   </sheetData>
@@ -6122,16 +6289,16 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="63.77734375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="10.77734375"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="63.81640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="10.81640625"/>
     <col min="3" max="3" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="19.44140625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="19.453125"/>
     <col min="5" max="5" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="15.5546875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="15.54296875"/>
     <col min="7" max="7" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="8" max="9" bestFit="true" customWidth="true" width="19.44140625"/>
+    <col min="8" max="9" bestFit="true" customWidth="true" width="19.453125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -6264,25 +6431,25 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:R6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="12.0"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.5546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="9.44140625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="6.21875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="13.77734375"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="15.44140625"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="17.5546875"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="7.44140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="18.44140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="18.44140625"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="15.44140625"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="11.77734375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="9.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="6.1796875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="13.81640625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="7.453125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="18.453125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="18.453125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="11.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -6365,16 +6532,16 @@
       <c r="I2" s="46"/>
       <c r="J2" s="46"/>
       <c r="K2" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>334</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>210</v>
@@ -6383,7 +6550,7 @@
         <v>12</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="R2" s="3"/>
     </row>
@@ -6411,16 +6578,16 @@
       <c r="I3" s="46"/>
       <c r="J3" s="46"/>
       <c r="K3" s="3" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>334</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="O3" s="3" t="s">
         <v>210</v>
@@ -6429,10 +6596,10 @@
         <v>12</v>
       </c>
       <c r="Q3" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="R3" s="3" t="s">
         <v>471</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -6455,7 +6622,7 @@
         <v>3</v>
       </c>
       <c r="G4" s="53" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H4" s="46" t="s">
         <v>12</v>
@@ -6467,16 +6634,16 @@
         <v>4</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>334</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>210</v>
@@ -6485,7 +6652,7 @@
         <v>12</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="R4" s="3"/>
     </row>
@@ -6513,16 +6680,16 @@
       <c r="I5" s="46"/>
       <c r="J5" s="46"/>
       <c r="K5" s="3" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>334</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>210</v>
@@ -6531,7 +6698,7 @@
         <v>12</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R5" s="3"/>
     </row>
@@ -6559,16 +6726,16 @@
       <c r="I6" s="46"/>
       <c r="J6" s="46"/>
       <c r="K6" s="3" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>334</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="O6" s="3" t="s">
         <v>210</v>
@@ -6577,7 +6744,7 @@
         <v>12</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="R6" s="3"/>
     </row>
@@ -6590,7 +6757,7 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42BBEF64-F0EA-4EA8-9A62-F5A7DF1E4869}">
   <dimension ref="A1:U13"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:21">
       <c r="A1" s="30" t="s">
@@ -6686,16 +6853,16 @@
         <v>164</v>
       </c>
       <c r="J2" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>372</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>373</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>349</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>12</v>
@@ -6704,13 +6871,13 @@
         <v>217</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>350</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="S2" s="3" t="s">
         <v>217</v>
@@ -6719,7 +6886,7 @@
         <v>164</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="3" spans="1:21">
@@ -6751,16 +6918,16 @@
         <v>164</v>
       </c>
       <c r="J3" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>378</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>379</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>216</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>12</v>
@@ -6769,13 +6936,13 @@
         <v>217</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>218</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="S3" s="3" t="s">
         <v>217</v>
@@ -6784,7 +6951,7 @@
         <v>164</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="8" spans="1:21">
@@ -6902,10 +7069,10 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="32.21875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="12.21875"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="32.1796875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -6948,7 +7115,7 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A51EFA8C-67A7-4B7E-8EF6-A12213F165A5}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="5" t="s">
@@ -7001,11 +7168,11 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFCF6FDB-3B87-457C-A3CA-7B39CE849651}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="46" width="24.88671875"/>
-    <col min="2" max="2" customWidth="true" style="46" width="17.44140625"/>
-    <col min="3" max="16384" style="46" width="8.77734375"/>
+    <col min="1" max="1" customWidth="true" style="46" width="24.90625"/>
+    <col min="2" max="2" customWidth="true" style="46" width="17.453125"/>
+    <col min="3" max="16384" style="46" width="8.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -7212,16 +7379,16 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="39.44140625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="21.77734375"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="15.44140625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="9.44140625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="6.44140625"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="18.44140625"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="39.453125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="21.81640625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="9.453125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="6.453125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="18.453125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -7319,20 +7486,20 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="32.21875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="15.44140625"/>
-    <col min="4" max="4" customWidth="true" width="15.44140625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="17.5546875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="15.44140625"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="17.5546875"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="17.33203125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="11.88671875"/>
-    <col min="13" max="13" customWidth="true" width="15.109375"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="32.1796875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="4" max="4" customWidth="true" width="15.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="17.36328125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="13" max="13" customWidth="true" width="15.08984375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -7486,16 +7653,16 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="52" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B6" s="54" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C6" s="52" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="49" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E6" s="52">
         <v>1</v>
@@ -7505,7 +7672,7 @@
       <c r="H6" s="49"/>
       <c r="I6" s="49"/>
       <c r="J6" s="49" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="K6" s="49"/>
       <c r="L6" s="49"/>
@@ -7519,18 +7686,18 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C03B3B8-DBFD-430F-BAEF-858DA603C137}">
   <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="46" width="17.88671875"/>
-    <col min="2" max="2" customWidth="true" style="46" width="11.77734375"/>
+    <col min="1" max="1" customWidth="true" style="46" width="17.90625"/>
+    <col min="2" max="2" customWidth="true" style="46" width="11.81640625"/>
     <col min="3" max="3" customWidth="true" style="46" width="13.0"/>
-    <col min="4" max="4" customWidth="true" style="46" width="16.5546875"/>
-    <col min="5" max="5" customWidth="true" style="46" width="15.77734375"/>
-    <col min="6" max="6" style="46" width="8.77734375"/>
-    <col min="7" max="7" customWidth="true" style="46" width="17.77734375"/>
-    <col min="8" max="8" customWidth="true" style="46" width="15.44140625"/>
-    <col min="9" max="9" customWidth="true" style="46" width="11.5546875"/>
-    <col min="10" max="16384" style="46" width="8.77734375"/>
+    <col min="4" max="4" customWidth="true" style="46" width="16.54296875"/>
+    <col min="5" max="5" customWidth="true" style="46" width="15.81640625"/>
+    <col min="6" max="6" style="46" width="8.81640625"/>
+    <col min="7" max="7" customWidth="true" style="46" width="17.81640625"/>
+    <col min="8" max="8" customWidth="true" style="46" width="15.453125"/>
+    <col min="9" max="9" customWidth="true" style="46" width="11.54296875"/>
+    <col min="10" max="16384" style="46" width="8.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -7585,7 +7752,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="49" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="G2" s="49">
         <v>2</v>
@@ -7616,7 +7783,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="49" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G3" s="49"/>
       <c r="H3" s="49"/>
@@ -7645,7 +7812,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="49" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="G4" s="49"/>
       <c r="H4" s="49"/>
@@ -7664,13 +7831,13 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="39.44140625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="13.5546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="7.77734375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="5.44140625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="9.77734375"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="39.453125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="13.54296875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="7.81640625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="9.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -7736,12 +7903,12 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="57.44140625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="15.5546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="7.77734375"/>
-    <col min="4" max="5" bestFit="true" customWidth="true" width="11.21875"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="57.453125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="15.54296875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="7.81640625"/>
+    <col min="4" max="5" bestFit="true" customWidth="true" width="11.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -7855,209 +8022,712 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D652E5C-6044-45E9-B3D7-DB9F9312DD9D}">
   <sheetPr>
-    <tabColor rgb="FFFF0000"/>
+    <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <dimension ref="A1:V15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="36" width="42.0"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="36" width="18.33203125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="36" width="12.109375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="36" width="15.33203125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="36" width="12.21875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="36" width="9.44140625"/>
-    <col min="7" max="8" style="36" width="8.77734375"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="36" width="10.44140625"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="36" width="11.21875"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="36" width="10.44140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="36" width="11.21875"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="36" width="10.44140625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="36" width="8.21875"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="36" width="50.0"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="36" width="18.36328125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="36" width="12.08984375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="36" width="15.36328125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="36" width="12.1796875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="36" width="9.453125"/>
+    <col min="7" max="8" style="36" width="8.81640625"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="36" width="10.453125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="36" width="12.6328125"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="36" width="10.453125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="36" width="11.1796875"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="36" width="10.453125"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="36" width="8.26953125"/>
     <col min="15" max="15" customWidth="true" style="36" width="13.0"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" style="36" width="10.21875"/>
-    <col min="17" max="16384" style="36" width="8.77734375"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="36" width="10.1796875"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="36" width="10.453125"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="36" width="9.26953125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="36" width="11.6328125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="36" width="12.6328125"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="36" width="11.1796875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="36" width="12.6328125"/>
+    <col min="23" max="16384" style="36" width="8.81640625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
-      <c r="A1" s="37" t="s">
+    <row r="1" spans="1:22">
+      <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="37" t="s">
+      <c r="B1" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="37" t="s">
+      <c r="E1" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="37" t="s">
+      <c r="F1" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="37" t="s">
+      <c r="G1" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="38" t="s">
+      <c r="H1" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="38" t="s">
+      <c r="I1" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="38" t="s">
+      <c r="J1" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="38" t="s">
+      <c r="K1" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="38" t="s">
+      <c r="L1" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="38" t="s">
+      <c r="M1" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="38" t="s">
+      <c r="N1" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="38" t="s">
+      <c r="O1" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="38" t="s">
+      <c r="P1" s="48" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" s="40" t="s">
+      <c r="Q1" s="47" t="s">
+        <v>8</v>
+      </c>
+      <c r="R1" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="S1" s="47" t="s">
+        <v>493</v>
+      </c>
+      <c r="T1" s="47" t="s">
+        <v>494</v>
+      </c>
+      <c r="U1" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="V1" s="47" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22">
+      <c r="A2" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="46">
-        <v>0</v>
-      </c>
-      <c r="C2" s="46" t="s">
-        <v>332</v>
-      </c>
-      <c r="D2" s="46" t="s">
-        <v>210</v>
-      </c>
-      <c r="E2" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="46" t="s">
+      <c r="B2" s="58">
+        <v>1</v>
+      </c>
+      <c r="C2" s="51" t="s">
+        <v>495</v>
+      </c>
+      <c r="D2" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="49" t="s">
+        <v>456</v>
+      </c>
+      <c r="F2" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="46" t="s">
+      <c r="G2" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
+      <c r="H2" s="49" t="s">
+        <v>496</v>
+      </c>
+      <c r="I2" s="49" t="s">
+        <v>212</v>
+      </c>
+      <c r="J2" s="49" t="s">
+        <v>213</v>
+      </c>
       <c r="K2" s="42" t="s">
         <v>212</v>
       </c>
       <c r="L2" s="42" t="s">
         <v>213</v>
       </c>
-      <c r="M2" s="39"/>
-      <c r="N2" s="39"/>
-      <c r="O2" s="39" t="s">
-        <v>359</v>
-      </c>
-      <c r="P2" s="39"/>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="A3" s="40" t="s">
+      <c r="M2" s="49"/>
+      <c r="N2" s="49"/>
+      <c r="O2" s="49" t="s">
+        <v>547</v>
+      </c>
+      <c r="P2" s="49"/>
+      <c r="Q2" s="49" t="s">
+        <v>498</v>
+      </c>
+      <c r="R2" s="49" t="s">
+        <v>499</v>
+      </c>
+      <c r="S2" s="49"/>
+      <c r="T2" s="49"/>
+      <c r="U2" s="49"/>
+      <c r="V2" s="49"/>
+    </row>
+    <row r="3" spans="1:22">
+      <c r="A3" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="46">
-        <v>0</v>
-      </c>
-      <c r="C3" s="46" t="s">
-        <v>332</v>
-      </c>
-      <c r="D3" s="46" t="s">
-        <v>210</v>
-      </c>
-      <c r="E3" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="46" t="s">
+      <c r="B3" s="49">
+        <v>2</v>
+      </c>
+      <c r="C3" s="51" t="s">
+        <v>500</v>
+      </c>
+      <c r="D3" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="49" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="46" t="s">
+      <c r="G3" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="39"/>
-      <c r="M3" s="39"/>
-      <c r="N3" s="39"/>
-      <c r="O3" s="39"/>
-      <c r="P3" s="39"/>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="A4" s="42" t="s">
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="49"/>
+      <c r="M3" s="49"/>
+      <c r="N3" s="49"/>
+      <c r="O3" s="49"/>
+      <c r="P3" s="49"/>
+      <c r="Q3" s="49"/>
+      <c r="R3" s="49"/>
+      <c r="S3" s="49"/>
+      <c r="T3" s="49"/>
+      <c r="U3" s="49"/>
+      <c r="V3" s="49"/>
+    </row>
+    <row r="4" spans="1:22">
+      <c r="A4" s="59" t="s">
         <v>214</v>
       </c>
-      <c r="B4" s="39">
+      <c r="B4" s="49">
         <v>2</v>
       </c>
-      <c r="C4" s="41" t="s">
+      <c r="C4" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="39" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="39"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="39"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="39"/>
-      <c r="K4" s="39"/>
-      <c r="L4" s="39"/>
-      <c r="M4" s="39"/>
-      <c r="N4" s="39"/>
-      <c r="O4" s="39"/>
-      <c r="P4" s="39"/>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="A5" s="42" t="s">
+      <c r="D4" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="49"/>
+      <c r="K4" s="49"/>
+      <c r="L4" s="49"/>
+      <c r="M4" s="49"/>
+      <c r="N4" s="49"/>
+      <c r="O4" s="49"/>
+      <c r="P4" s="49"/>
+      <c r="Q4" s="49"/>
+      <c r="R4" s="49"/>
+      <c r="S4" s="49"/>
+      <c r="T4" s="49"/>
+      <c r="U4" s="49"/>
+      <c r="V4" s="49"/>
+    </row>
+    <row r="5" spans="1:22">
+      <c r="A5" s="59" t="s">
         <v>215</v>
       </c>
-      <c r="B5" s="39">
+      <c r="B5" s="49">
         <v>2</v>
       </c>
-      <c r="C5" s="41" t="s">
+      <c r="C5" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="39" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="39"/>
-      <c r="J5" s="39"/>
+      <c r="D5" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
       <c r="K5" s="42" t="s">
         <v>212</v>
       </c>
       <c r="L5" s="42" t="s">
         <v>213</v>
       </c>
-      <c r="M5" s="39"/>
-      <c r="N5" s="39"/>
-      <c r="O5" s="39"/>
-      <c r="P5" s="39">
+      <c r="M5" s="49"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49">
         <v>0</v>
       </c>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
+    </row>
+    <row r="6" spans="1:22" s="46" customFormat="1">
+      <c r="A6" s="49" t="s">
+        <v>537</v>
+      </c>
+      <c r="B6" s="49">
+        <v>1</v>
+      </c>
+      <c r="C6" s="51" t="s">
+        <v>488</v>
+      </c>
+      <c r="D6" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="49" t="s">
+        <v>456</v>
+      </c>
+      <c r="F6" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="49" t="s">
+        <v>548</v>
+      </c>
+      <c r="I6" s="49" t="s">
+        <v>539</v>
+      </c>
+      <c r="J6" s="49" t="s">
+        <v>540</v>
+      </c>
+      <c r="K6" s="49"/>
+      <c r="L6" s="49"/>
+      <c r="M6" s="49"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="49"/>
+      <c r="P6" s="49"/>
+      <c r="Q6" s="49"/>
+      <c r="R6" s="49"/>
+      <c r="S6" s="49"/>
+      <c r="T6" s="49"/>
+      <c r="U6" s="49"/>
+      <c r="V6" s="49"/>
+    </row>
+    <row r="7" spans="1:22">
+      <c r="A7" s="59" t="s">
+        <v>501</v>
+      </c>
+      <c r="B7" s="49">
+        <v>1</v>
+      </c>
+      <c r="C7" s="51" t="s">
+        <v>502</v>
+      </c>
+      <c r="D7" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="49" t="s">
+        <v>456</v>
+      </c>
+      <c r="F7" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" s="49" t="s">
+        <v>551</v>
+      </c>
+      <c r="I7" s="49" t="s">
+        <v>504</v>
+      </c>
+      <c r="J7" s="49" t="s">
+        <v>505</v>
+      </c>
+      <c r="K7" s="49"/>
+      <c r="L7" s="49"/>
+      <c r="M7" s="49"/>
+      <c r="N7" s="49"/>
+      <c r="O7" s="49"/>
+      <c r="P7" s="49"/>
+      <c r="Q7" s="49"/>
+      <c r="R7" s="49"/>
+      <c r="S7" s="49"/>
+      <c r="T7" s="49"/>
+      <c r="U7" s="49"/>
+      <c r="V7" s="49"/>
+    </row>
+    <row r="8" spans="1:22" s="46" customFormat="1">
+      <c r="A8" s="49" t="s">
+        <v>541</v>
+      </c>
+      <c r="B8" s="49">
+        <v>1</v>
+      </c>
+      <c r="C8" s="51" t="s">
+        <v>488</v>
+      </c>
+      <c r="D8" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="49"/>
+      <c r="J8" s="49"/>
+      <c r="K8" s="49"/>
+      <c r="L8" s="49"/>
+      <c r="M8" s="49"/>
+      <c r="N8" s="49"/>
+      <c r="O8" s="49"/>
+      <c r="P8" s="49"/>
+      <c r="Q8" s="49"/>
+      <c r="R8" s="49"/>
+      <c r="S8" s="49"/>
+      <c r="T8" s="49"/>
+      <c r="U8" s="49"/>
+      <c r="V8" s="49"/>
+    </row>
+    <row r="9" spans="1:22">
+      <c r="A9" s="59" t="s">
+        <v>506</v>
+      </c>
+      <c r="B9" s="49">
+        <v>2</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>488</v>
+      </c>
+      <c r="D9" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="49" t="s">
+        <v>456</v>
+      </c>
+      <c r="F9" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="49" t="s">
+        <v>507</v>
+      </c>
+      <c r="I9" s="49" t="s">
+        <v>508</v>
+      </c>
+      <c r="J9" s="49" t="s">
+        <v>509</v>
+      </c>
+      <c r="K9" s="49"/>
+      <c r="L9" s="49"/>
+      <c r="M9" s="49"/>
+      <c r="N9" s="49"/>
+      <c r="O9" s="49"/>
+      <c r="P9" s="49"/>
+      <c r="Q9" s="49"/>
+      <c r="R9" s="49"/>
+      <c r="S9" s="49"/>
+      <c r="T9" s="49"/>
+      <c r="U9" s="49"/>
+      <c r="V9" s="49"/>
+    </row>
+    <row r="10" spans="1:22" s="46" customFormat="1">
+      <c r="A10" s="49" t="s">
+        <v>542</v>
+      </c>
+      <c r="B10" s="49">
+        <v>1</v>
+      </c>
+      <c r="C10" s="51" t="s">
+        <v>516</v>
+      </c>
+      <c r="D10" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="49" t="s">
+        <v>517</v>
+      </c>
+      <c r="F10" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="49"/>
+      <c r="H10" s="49" t="s">
+        <v>543</v>
+      </c>
+      <c r="I10" s="49"/>
+      <c r="J10" s="49" t="s">
+        <v>544</v>
+      </c>
+      <c r="K10" s="49"/>
+      <c r="L10" s="49"/>
+      <c r="M10" s="49"/>
+      <c r="N10" s="49"/>
+      <c r="O10" s="49"/>
+      <c r="P10" s="49"/>
+      <c r="Q10" s="49"/>
+      <c r="R10" s="49"/>
+      <c r="S10" s="49" t="s">
+        <v>521</v>
+      </c>
+      <c r="T10" s="49" t="s">
+        <v>522</v>
+      </c>
+      <c r="U10" s="49"/>
+      <c r="V10" s="49" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22">
+      <c r="A11" s="59" t="s">
+        <v>515</v>
+      </c>
+      <c r="B11" s="49">
+        <v>1</v>
+      </c>
+      <c r="C11" s="51" t="s">
+        <v>516</v>
+      </c>
+      <c r="D11" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="49" t="s">
+        <v>517</v>
+      </c>
+      <c r="F11" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="49" t="s">
+        <v>552</v>
+      </c>
+      <c r="I11" s="49" t="s">
+        <v>212</v>
+      </c>
+      <c r="J11" s="49" t="s">
+        <v>213</v>
+      </c>
+      <c r="K11" s="49"/>
+      <c r="L11" s="49"/>
+      <c r="M11" s="49"/>
+      <c r="N11" s="49"/>
+      <c r="O11" s="49"/>
+      <c r="P11" s="49"/>
+      <c r="Q11" s="49" t="s">
+        <v>519</v>
+      </c>
+      <c r="R11" s="49" t="s">
+        <v>520</v>
+      </c>
+      <c r="S11" s="49" t="s">
+        <v>521</v>
+      </c>
+      <c r="T11" s="49" t="s">
+        <v>522</v>
+      </c>
+      <c r="U11" s="49" t="s">
+        <v>523</v>
+      </c>
+      <c r="V11" s="49"/>
+    </row>
+    <row r="12" spans="1:22">
+      <c r="A12" s="59" t="s">
+        <v>524</v>
+      </c>
+      <c r="B12" s="49">
+        <v>1</v>
+      </c>
+      <c r="C12" s="51" t="s">
+        <v>216</v>
+      </c>
+      <c r="D12" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="49" t="s">
+        <v>217</v>
+      </c>
+      <c r="F12" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="49"/>
+      <c r="H12" s="49" t="s">
+        <v>549</v>
+      </c>
+      <c r="I12" s="49" t="s">
+        <v>526</v>
+      </c>
+      <c r="J12" s="49" t="s">
+        <v>527</v>
+      </c>
+      <c r="K12" s="49" t="s">
+        <v>528</v>
+      </c>
+      <c r="L12" s="49" t="s">
+        <v>527</v>
+      </c>
+      <c r="M12" s="49"/>
+      <c r="N12" s="49"/>
+      <c r="O12" s="49"/>
+      <c r="P12" s="49"/>
+      <c r="Q12" s="49"/>
+      <c r="R12" s="49"/>
+      <c r="S12" s="49" t="s">
+        <v>529</v>
+      </c>
+      <c r="T12" s="49" t="s">
+        <v>521</v>
+      </c>
+      <c r="U12" s="49"/>
+      <c r="V12" s="49" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22">
+      <c r="A13" s="59" t="s">
+        <v>531</v>
+      </c>
+      <c r="B13" s="49">
+        <v>2</v>
+      </c>
+      <c r="C13" s="51" t="s">
+        <v>532</v>
+      </c>
+      <c r="D13" s="49" t="s">
+        <v>217</v>
+      </c>
+      <c r="E13" s="49" t="s">
+        <v>164</v>
+      </c>
+      <c r="F13" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="49"/>
+      <c r="H13" s="49"/>
+      <c r="I13" s="49"/>
+      <c r="J13" s="49"/>
+      <c r="K13" s="49"/>
+      <c r="L13" s="49"/>
+      <c r="M13" s="49"/>
+      <c r="N13" s="49"/>
+      <c r="O13" s="49"/>
+      <c r="P13" s="49"/>
+      <c r="Q13" s="49"/>
+      <c r="R13" s="49"/>
+      <c r="S13" s="49"/>
+      <c r="T13" s="49"/>
+      <c r="U13" s="49"/>
+      <c r="V13" s="49"/>
+    </row>
+    <row r="14" spans="1:22">
+      <c r="A14" s="59" t="s">
+        <v>533</v>
+      </c>
+      <c r="B14" s="49">
+        <v>1</v>
+      </c>
+      <c r="C14" s="51" t="s">
+        <v>516</v>
+      </c>
+      <c r="D14" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="49" t="s">
+        <v>517</v>
+      </c>
+      <c r="F14" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="49"/>
+      <c r="H14" s="49" t="s">
+        <v>550</v>
+      </c>
+      <c r="I14" s="49" t="s">
+        <v>245</v>
+      </c>
+      <c r="J14" s="49" t="s">
+        <v>250</v>
+      </c>
+      <c r="K14" s="49"/>
+      <c r="L14" s="49"/>
+      <c r="M14" s="49"/>
+      <c r="N14" s="49"/>
+      <c r="O14" s="49"/>
+      <c r="P14" s="49"/>
+      <c r="Q14" s="49"/>
+      <c r="R14" s="49"/>
+      <c r="S14" s="49" t="s">
+        <v>521</v>
+      </c>
+      <c r="T14" s="49" t="s">
+        <v>522</v>
+      </c>
+      <c r="U14" s="49"/>
+      <c r="V14" s="49" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" s="46" customFormat="1">
+      <c r="A15" s="59" t="s">
+        <v>510</v>
+      </c>
+      <c r="B15" s="49">
+        <v>2</v>
+      </c>
+      <c r="C15" s="51" t="s">
+        <v>511</v>
+      </c>
+      <c r="D15" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="49" t="s">
+        <v>456</v>
+      </c>
+      <c r="F15" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="49" t="s">
+        <v>546</v>
+      </c>
+      <c r="I15" s="49" t="s">
+        <v>513</v>
+      </c>
+      <c r="J15" s="49" t="s">
+        <v>514</v>
+      </c>
+      <c r="K15" s="49"/>
+      <c r="L15" s="49"/>
+      <c r="M15" s="49"/>
+      <c r="N15" s="49"/>
+      <c r="O15" s="49"/>
+      <c r="P15" s="49"/>
+      <c r="Q15" s="49"/>
+      <c r="R15" s="49"/>
+      <c r="S15" s="49"/>
+      <c r="T15" s="49"/>
+      <c r="U15" s="49"/>
+      <c r="V15" s="49"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8067,31 +8737,31 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:AB7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="44.77734375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.77734375"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="8.21875"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="44.81640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.81640625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="8.1796875"/>
     <col min="4" max="4" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="11.21875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="10.44140625"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="13.5546875"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="17.77734375"/>
-    <col min="11" max="12" bestFit="true" customWidth="true" width="11.21875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="18.21875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="10.453125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="13.54296875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="17.81640625"/>
+    <col min="11" max="12" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="18.1796875"/>
     <col min="16" max="16" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="7.77734375"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="11.21875"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="8.21875"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="7.81640625"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="8.1796875"/>
     <col min="22" max="22" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="11.21875"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="11.1796875"/>
     <col min="24" max="24" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="11.21875"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="14.21875"/>
-    <col min="27" max="28" bestFit="true" customWidth="true" width="12.77734375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="14.21875"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="12.77734375"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="14.1796875"/>
+    <col min="27" max="28" bestFit="true" customWidth="true" width="12.81640625"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="14.1796875"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="12.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28">
@@ -8488,11 +9158,11 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:W17"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="54.33203125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="13.88671875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="13.77734375"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="54.36328125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="13.90625"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="13.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -8595,10 +9265,10 @@
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
       <c r="R2" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="S2" s="3" t="s">
         <v>420</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>421</v>
       </c>
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
@@ -8857,10 +9527,10 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="S8" s="3" t="s">
         <v>430</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>431</v>
       </c>
       <c r="T8" s="3">
         <v>0</v>
@@ -8877,22 +9547,22 @@
         <v>1</v>
       </c>
       <c r="C9" s="51" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F9" s="3">
         <v>2</v>
       </c>
       <c r="G9" s="51" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>12</v>
@@ -8906,10 +9576,10 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="S9" s="3" t="s">
         <v>432</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>433</v>
       </c>
       <c r="T9" s="3"/>
       <c r="U9" s="3">
@@ -8930,22 +9600,22 @@
         <v>1</v>
       </c>
       <c r="C10" s="51" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F10" s="3">
         <v>2</v>
       </c>
       <c r="G10" s="51" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>12</v>
@@ -8959,10 +9629,10 @@
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="S10" s="3" t="s">
         <v>434</v>
-      </c>
-      <c r="S10" s="3" t="s">
-        <v>435</v>
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
@@ -9156,22 +9826,22 @@
         <v>1</v>
       </c>
       <c r="C16" s="51" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D16" s="49" t="s">
         <v>12</v>
       </c>
       <c r="E16" s="49" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F16" s="49">
         <v>2</v>
       </c>
       <c r="G16" s="51" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H16" s="49" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="I16" s="49" t="s">
         <v>12</v>
@@ -9185,10 +9855,10 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="S16" s="3" t="s">
         <v>437</v>
-      </c>
-      <c r="S16" s="3" t="s">
-        <v>438</v>
       </c>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
@@ -9241,18 +9911,18 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:S20"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="53.77734375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.5546875"/>
-    <col min="3" max="4" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="5" max="7" customWidth="true" width="12.21875"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="15.44140625"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="17.5546875"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="12.21875"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="15.44140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="12.21875"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="53.81640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="3" max="4" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="5" max="7" customWidth="true" width="12.1796875"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="12.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19">

--- a/src/test/java/TestData/Scenario_TestData.xlsx
+++ b/src/test/java/TestData/Scenario_TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Copa_SHD_WebServices\src\test\java\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C83B784-0081-406B-869E-EC4C530DFF3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8C891FA-BDDC-4E79-915E-0E7881B71B53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="2" activeTab="5" xr2:uid="{5D5A4724-D560-4FC2-9708-4BBF1DBA0B11}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="5" activeTab="5" xr2:uid="{5D5A4724-D560-4FC2-9708-4BBF1DBA0B11}"/>
   </bookViews>
   <sheets>
     <sheet name="AdvancePassengerInfo" sheetId="1" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1648" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1622" uniqueCount="545">
   <si>
     <t>Scenario</t>
   </si>
@@ -1517,9 +1517,6 @@
     <t>AVXXET</t>
   </si>
   <si>
-    <t>AVX1NQ</t>
-  </si>
-  <si>
     <t>Modify_API_for_deleting_API_data</t>
   </si>
   <si>
@@ -1535,18 +1532,9 @@
     <t>787</t>
   </si>
   <si>
-    <t>AVX2E3</t>
-  </si>
-  <si>
     <t>AVX2FA</t>
   </si>
   <si>
-    <t>AVX2HC</t>
-  </si>
-  <si>
-    <t>AVX2H3</t>
-  </si>
-  <si>
     <t>AgencyName</t>
   </si>
   <si>
@@ -1559,9 +1547,6 @@
     <t>AXAW2F</t>
   </si>
   <si>
-    <t>BKPXHF</t>
-  </si>
-  <si>
     <t>JOE</t>
   </si>
   <si>
@@ -1577,9 +1562,6 @@
     <t>851</t>
   </si>
   <si>
-    <t>AVVBPK</t>
-  </si>
-  <si>
     <t>HELLO</t>
   </si>
   <si>
@@ -1601,12 +1583,6 @@
     <t>Create_booking_service_cancel_held_seats</t>
   </si>
   <si>
-    <t>460</t>
-  </si>
-  <si>
-    <t>AVU5YY</t>
-  </si>
-  <si>
     <t>MARINO</t>
   </si>
   <si>
@@ -1622,9 +1598,6 @@
     <t>HAV</t>
   </si>
   <si>
-    <t>AXCAP5</t>
-  </si>
-  <si>
     <t>JACK</t>
   </si>
   <si>
@@ -1643,9 +1616,6 @@
     <t>Thru_checkin_Seg1</t>
   </si>
   <si>
-    <t>AW44YC</t>
-  </si>
-  <si>
     <t>ABCDEFGH</t>
   </si>
   <si>
@@ -1670,9 +1640,6 @@
     <t>Check_in_FF_pax</t>
   </si>
   <si>
-    <t>AW413R</t>
-  </si>
-  <si>
     <t>null</t>
   </si>
   <si>
@@ -1682,9 +1649,6 @@
     <t>Check_in_Non_Revenue_pax</t>
   </si>
   <si>
-    <t>AXAB3T</t>
-  </si>
-  <si>
     <t>KLABEN</t>
   </si>
   <si>
@@ -1703,28 +1667,40 @@
     <t>MYBIGFAMILY</t>
   </si>
   <si>
-    <t>AXGZ5A</t>
-  </si>
-  <si>
-    <t>AXG0A0</t>
-  </si>
-  <si>
-    <t>AXG0BB</t>
-  </si>
-  <si>
-    <t>AXG0CN</t>
-  </si>
-  <si>
-    <t>AXG0MH</t>
-  </si>
-  <si>
-    <t>AXG1IY</t>
-  </si>
-  <si>
-    <t>AXG1S5</t>
-  </si>
-  <si>
-    <t>AXG5CQ</t>
+    <t>AXHDYW</t>
+  </si>
+  <si>
+    <t>AXHD1I</t>
+  </si>
+  <si>
+    <t>AXHKNI</t>
+  </si>
+  <si>
+    <t>AXHKNJ</t>
+  </si>
+  <si>
+    <t>AXHKNL</t>
+  </si>
+  <si>
+    <t>AXHKNV</t>
+  </si>
+  <si>
+    <t>AXHOOB</t>
+  </si>
+  <si>
+    <t>AXHOPH</t>
+  </si>
+  <si>
+    <t>AXHOPW</t>
+  </si>
+  <si>
+    <t>AXHORT</t>
+  </si>
+  <si>
+    <t>AXHP5E</t>
+  </si>
+  <si>
+    <t>AXHSJO</t>
   </si>
 </sst>
 </file>
@@ -2419,7 +2395,7 @@
         <v>15</v>
       </c>
       <c r="H2" s="49" t="s">
-        <v>489</v>
+        <v>535</v>
       </c>
       <c r="I2" s="49" t="s">
         <v>212</v>
@@ -2436,7 +2412,7 @@
       <c r="M2" s="49"/>
       <c r="N2" s="49"/>
       <c r="O2" s="49" t="s">
-        <v>483</v>
+        <v>536</v>
       </c>
       <c r="P2" s="56"/>
     </row>
@@ -2487,13 +2463,13 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="55" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B4" s="55">
         <v>0</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D4" s="55" t="s">
         <v>12</v>
@@ -2508,13 +2484,13 @@
         <v>15</v>
       </c>
       <c r="H4" s="55" t="s">
-        <v>491</v>
+        <v>537</v>
       </c>
       <c r="I4" s="55" t="s">
+        <v>485</v>
+      </c>
+      <c r="J4" s="55" t="s">
         <v>486</v>
-      </c>
-      <c r="J4" s="55" t="s">
-        <v>487</v>
       </c>
       <c r="K4" s="49"/>
       <c r="L4" s="49"/>
@@ -2524,13 +2500,13 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="55" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B5" s="55">
         <v>0</v>
       </c>
       <c r="C5" s="57" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D5" s="55" t="s">
         <v>12</v>
@@ -2545,7 +2521,7 @@
         <v>15</v>
       </c>
       <c r="H5" s="55" t="s">
-        <v>492</v>
+        <v>538</v>
       </c>
       <c r="I5" s="49"/>
       <c r="J5" s="49"/>
@@ -4174,7 +4150,7 @@
         <v>12</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>476</v>
@@ -8107,16 +8083,16 @@
         <v>9</v>
       </c>
       <c r="S1" s="47" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="T1" s="47" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="U1" s="47" t="s">
         <v>30</v>
       </c>
       <c r="V1" s="47" t="s">
-        <v>536</v>
+        <v>525</v>
       </c>
     </row>
     <row r="2" spans="1:22">
@@ -8124,10 +8100,10 @@
         <v>11</v>
       </c>
       <c r="B2" s="58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="51" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D2" s="49" t="s">
         <v>12</v>
@@ -8142,7 +8118,7 @@
         <v>15</v>
       </c>
       <c r="H2" s="49" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="I2" s="49" t="s">
         <v>212</v>
@@ -8159,14 +8135,14 @@
       <c r="M2" s="49"/>
       <c r="N2" s="49"/>
       <c r="O2" s="49" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="P2" s="49"/>
       <c r="Q2" s="49" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="R2" s="49" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="S2" s="49"/>
       <c r="T2" s="49"/>
@@ -8181,7 +8157,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="51" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="D3" s="49" t="s">
         <v>12</v>
@@ -8283,13 +8259,13 @@
     </row>
     <row r="6" spans="1:22" s="46" customFormat="1">
       <c r="A6" s="49" t="s">
-        <v>537</v>
+        <v>526</v>
       </c>
       <c r="B6" s="49">
         <v>1</v>
       </c>
       <c r="C6" s="51" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D6" s="49" t="s">
         <v>12</v>
@@ -8304,13 +8280,13 @@
         <v>15</v>
       </c>
       <c r="H6" s="49" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="I6" s="49" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="J6" s="49" t="s">
-        <v>540</v>
+        <v>528</v>
       </c>
       <c r="K6" s="49"/>
       <c r="L6" s="49"/>
@@ -8327,13 +8303,13 @@
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="59" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="B7" s="49">
         <v>1</v>
       </c>
       <c r="C7" s="51" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="D7" s="49" t="s">
         <v>12</v>
@@ -8348,13 +8324,13 @@
         <v>19</v>
       </c>
       <c r="H7" s="49" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="I7" s="49" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="J7" s="49" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="K7" s="49"/>
       <c r="L7" s="49"/>
@@ -8371,13 +8347,13 @@
     </row>
     <row r="8" spans="1:22" s="46" customFormat="1">
       <c r="A8" s="49" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="B8" s="49">
         <v>1</v>
       </c>
       <c r="C8" s="51" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D8" s="49" t="s">
         <v>12</v>
@@ -8403,13 +8379,13 @@
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="59" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="B9" s="49">
         <v>2</v>
       </c>
       <c r="C9" s="51" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D9" s="49" t="s">
         <v>12</v>
@@ -8424,13 +8400,13 @@
         <v>15</v>
       </c>
       <c r="H9" s="49" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="I9" s="49" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="J9" s="49" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="K9" s="49"/>
       <c r="L9" s="49"/>
@@ -8447,30 +8423,30 @@
     </row>
     <row r="10" spans="1:22" s="46" customFormat="1">
       <c r="A10" s="49" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="B10" s="49">
         <v>1</v>
       </c>
       <c r="C10" s="51" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="D10" s="49" t="s">
         <v>12</v>
       </c>
       <c r="E10" s="49" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="F10" s="49" t="s">
         <v>14</v>
       </c>
       <c r="G10" s="49"/>
       <c r="H10" s="49" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
       <c r="I10" s="49"/>
       <c r="J10" s="49" t="s">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="K10" s="49"/>
       <c r="L10" s="49"/>
@@ -8481,31 +8457,31 @@
       <c r="Q10" s="49"/>
       <c r="R10" s="49"/>
       <c r="S10" s="49" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="T10" s="49" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="U10" s="49"/>
       <c r="V10" s="49" t="s">
-        <v>535</v>
+        <v>524</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="59" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="B11" s="49">
         <v>1</v>
       </c>
       <c r="C11" s="51" t="s">
-        <v>516</v>
+        <v>128</v>
       </c>
       <c r="D11" s="49" t="s">
         <v>12</v>
       </c>
       <c r="E11" s="49" t="s">
-        <v>517</v>
+        <v>210</v>
       </c>
       <c r="F11" s="49" t="s">
         <v>14</v>
@@ -8514,7 +8490,7 @@
         <v>15</v>
       </c>
       <c r="H11" s="49" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="I11" s="49" t="s">
         <v>212</v>
@@ -8529,25 +8505,25 @@
       <c r="O11" s="49"/>
       <c r="P11" s="49"/>
       <c r="Q11" s="49" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="R11" s="49" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="S11" s="49" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="T11" s="49" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="U11" s="49" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="V11" s="49"/>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="59" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="B12" s="49">
         <v>1</v>
@@ -8566,19 +8542,19 @@
       </c>
       <c r="G12" s="49"/>
       <c r="H12" s="49" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="I12" s="49" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
       <c r="J12" s="49" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="K12" s="49" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="L12" s="49" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="M12" s="49"/>
       <c r="N12" s="49"/>
@@ -8587,25 +8563,25 @@
       <c r="Q12" s="49"/>
       <c r="R12" s="49"/>
       <c r="S12" s="49" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="T12" s="49" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="U12" s="49"/>
       <c r="V12" s="49" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="59" t="s">
-        <v>531</v>
+        <v>521</v>
       </c>
       <c r="B13" s="49">
         <v>2</v>
       </c>
       <c r="C13" s="51" t="s">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="D13" s="49" t="s">
         <v>217</v>
@@ -8635,26 +8611,26 @@
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="59" t="s">
-        <v>533</v>
+        <v>523</v>
       </c>
       <c r="B14" s="49">
         <v>1</v>
       </c>
       <c r="C14" s="51" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="D14" s="49" t="s">
         <v>12</v>
       </c>
       <c r="E14" s="49" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="F14" s="49" t="s">
         <v>14</v>
       </c>
       <c r="G14" s="49"/>
       <c r="H14" s="49" t="s">
-        <v>550</v>
+        <v>534</v>
       </c>
       <c r="I14" s="49" t="s">
         <v>245</v>
@@ -8671,31 +8647,31 @@
       <c r="Q14" s="49"/>
       <c r="R14" s="49"/>
       <c r="S14" s="49" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="T14" s="49" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="U14" s="49"/>
       <c r="V14" s="49" t="s">
-        <v>535</v>
+        <v>524</v>
       </c>
     </row>
     <row r="15" spans="1:22" s="46" customFormat="1">
       <c r="A15" s="59" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="B15" s="49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" s="51" t="s">
-        <v>511</v>
+        <v>128</v>
       </c>
       <c r="D15" s="49" t="s">
         <v>12</v>
       </c>
       <c r="E15" s="49" t="s">
-        <v>456</v>
+        <v>210</v>
       </c>
       <c r="F15" s="49" t="s">
         <v>14</v>
@@ -8704,13 +8680,13 @@
         <v>15</v>
       </c>
       <c r="H15" s="49" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="I15" s="49" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="J15" s="49" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="K15" s="49"/>
       <c r="L15" s="49"/>

--- a/src/test/java/TestData/Scenario_TestData.xlsx
+++ b/src/test/java/TestData/Scenario_TestData.xlsx
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1622" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1649" uniqueCount="556">
   <si>
     <t>Scenario</t>
   </si>
@@ -1701,6 +1701,39 @@
   </si>
   <si>
     <t>AXHSJO</t>
+  </si>
+  <si>
+    <t>AX0KRQ</t>
+  </si>
+  <si>
+    <t>AX0KWO</t>
+  </si>
+  <si>
+    <t>2023-08-16T07:54:00</t>
+  </si>
+  <si>
+    <t>2023-08-16T12:57:00</t>
+  </si>
+  <si>
+    <t>2023-08-17T01:32:00</t>
+  </si>
+  <si>
+    <t>2023-08-17T10:02:00</t>
+  </si>
+  <si>
+    <t>AX0KXK</t>
+  </si>
+  <si>
+    <t>AX0K0C</t>
+  </si>
+  <si>
+    <t>AX0K1E</t>
+  </si>
+  <si>
+    <t>AX0K4M</t>
+  </si>
+  <si>
+    <t>AX0K45</t>
   </si>
 </sst>
 </file>
@@ -2395,7 +2428,7 @@
         <v>15</v>
       </c>
       <c r="H2" s="49" t="s">
-        <v>535</v>
+        <v>552</v>
       </c>
       <c r="I2" s="49" t="s">
         <v>212</v>
@@ -2412,7 +2445,7 @@
       <c r="M2" s="49"/>
       <c r="N2" s="49"/>
       <c r="O2" s="49" t="s">
-        <v>536</v>
+        <v>553</v>
       </c>
       <c r="P2" s="56"/>
     </row>
@@ -2484,7 +2517,7 @@
         <v>15</v>
       </c>
       <c r="H4" s="55" t="s">
-        <v>537</v>
+        <v>554</v>
       </c>
       <c r="I4" s="55" t="s">
         <v>485</v>
@@ -2521,7 +2554,7 @@
         <v>15</v>
       </c>
       <c r="H5" s="55" t="s">
-        <v>538</v>
+        <v>555</v>
       </c>
       <c r="I5" s="49"/>
       <c r="J5" s="49"/>
@@ -4150,16 +4183,16 @@
         <v>12</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>488</v>
+        <v>546</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>476</v>
+        <v>547</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>32</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>477</v>
+        <v>548</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>12</v>
@@ -4168,13 +4201,13 @@
         <v>34</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>478</v>
+        <v>549</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>343</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>479</v>
+        <v>550</v>
       </c>
       <c r="S2" s="3" t="s">
         <v>34</v>

--- a/src/test/java/TestData/Scenario_TestData.xlsx
+++ b/src/test/java/TestData/Scenario_TestData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ArunJK\Arun\Copa_SHDWebservices\src\test\java\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Copa_SHD_WebServices\src\test\java\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E70A0E-0D0E-4A74-A51A-ECF2B46631E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{223A646B-2FC9-4BF9-9AA4-12E63AB7B57D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{5D5A4724-D560-4FC2-9708-4BBF1DBA0B11}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="32" activeTab="38" xr2:uid="{5D5A4724-D560-4FC2-9708-4BBF1DBA0B11}"/>
   </bookViews>
   <sheets>
     <sheet name="AdvancePassengerInfo" sheetId="1" r:id="rId1"/>
@@ -2503,22 +2503,22 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:P15"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="52.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="52.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2747,12 +2747,15 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C501783-003E-43C7-BF08-448ED073E85B}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:U22"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="10" max="10" width="8.77734375" style="27"/>
-    <col min="12" max="12" width="15.88671875" customWidth="1"/>
-    <col min="17" max="17" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.81640625" style="27"/>
+    <col min="12" max="12" width="15.90625" customWidth="1"/>
+    <col min="17" max="17" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
@@ -3722,19 +3725,22 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2EA1F88-8B75-4AAD-A17A-063CA3659CA4}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:N4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="32.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5546875" style="31" customWidth="1"/>
+    <col min="1" max="1" width="32.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.54296875" style="31" customWidth="1"/>
     <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.77734375" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="14.33203125" style="31" customWidth="1"/>
-    <col min="12" max="12" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.44140625" customWidth="1"/>
-    <col min="14" max="14" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.81640625" customWidth="1"/>
+    <col min="6" max="6" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="14.36328125" style="31" customWidth="1"/>
+    <col min="12" max="12" width="30.36328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.453125" customWidth="1"/>
+    <col min="14" max="14" width="10.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -3916,20 +3922,23 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88414653-50FA-4845-96AF-5B777BBDF907}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="21.77734375" style="31" customWidth="1"/>
-    <col min="2" max="2" width="16.5546875" style="31" customWidth="1"/>
-    <col min="3" max="3" width="19.88671875" style="31" customWidth="1"/>
-    <col min="4" max="4" width="18.77734375" style="31" customWidth="1"/>
-    <col min="5" max="6" width="12.88671875" style="31" customWidth="1"/>
+    <col min="1" max="1" width="21.81640625" style="31" customWidth="1"/>
+    <col min="2" max="2" width="16.54296875" style="31" customWidth="1"/>
+    <col min="3" max="3" width="19.90625" style="31" customWidth="1"/>
+    <col min="4" max="4" width="18.81640625" style="31" customWidth="1"/>
+    <col min="5" max="6" width="12.90625" style="31" customWidth="1"/>
     <col min="7" max="7" width="15" style="31" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.88671875" style="31" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.77734375" style="31"/>
-    <col min="10" max="10" width="17.88671875" style="31" customWidth="1"/>
-    <col min="11" max="11" width="14.21875" style="31" customWidth="1"/>
-    <col min="12" max="16384" width="8.77734375" style="31"/>
+    <col min="8" max="8" width="11.90625" style="31" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.81640625" style="31"/>
+    <col min="10" max="10" width="17.90625" style="31" customWidth="1"/>
+    <col min="11" max="11" width="14.1796875" style="31" customWidth="1"/>
+    <col min="12" max="16384" width="8.81640625" style="31"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -4093,14 +4102,14 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="42.21875" style="31" customWidth="1"/>
-    <col min="2" max="2" width="15.77734375" style="31" customWidth="1"/>
-    <col min="3" max="3" width="17.77734375" style="31" customWidth="1"/>
-    <col min="4" max="4" width="16.77734375" style="31" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" style="31" customWidth="1"/>
-    <col min="6" max="16384" width="8.77734375" style="31"/>
+    <col min="1" max="1" width="42.1796875" style="31" customWidth="1"/>
+    <col min="2" max="2" width="15.81640625" style="31" customWidth="1"/>
+    <col min="3" max="3" width="17.81640625" style="31" customWidth="1"/>
+    <col min="4" max="4" width="16.81640625" style="31" customWidth="1"/>
+    <col min="5" max="5" width="15.6328125" style="31" customWidth="1"/>
+    <col min="6" max="16384" width="8.81640625" style="31"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4213,22 +4222,22 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:AB6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="51.77734375" customWidth="1"/>
-    <col min="2" max="2" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="51.81640625" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28">
@@ -4649,12 +4658,12 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="76.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="76.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4733,15 +4742,18 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEA2AF7E-AC89-4B47-B4D7-D3496E5327D5}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="18.44140625" style="31" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" style="31" customWidth="1"/>
-    <col min="3" max="3" width="14.77734375" style="31" customWidth="1"/>
-    <col min="4" max="4" width="11.77734375" style="31" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.21875" style="31" customWidth="1"/>
-    <col min="6" max="16384" width="8.77734375" style="31"/>
+    <col min="1" max="1" width="18.453125" style="31" customWidth="1"/>
+    <col min="2" max="2" width="12.54296875" style="31" customWidth="1"/>
+    <col min="3" max="3" width="14.81640625" style="31" customWidth="1"/>
+    <col min="4" max="4" width="11.81640625" style="31" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.1796875" style="31" customWidth="1"/>
+    <col min="6" max="16384" width="8.81640625" style="31"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4930,11 +4942,14 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F1569B0-3564-4B84-A0FB-9681D32A0E6D}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -4968,14 +4983,17 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02A4FAA4-EFC6-47D3-BDEE-7F4F3353F3CD}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="33.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -5019,8 +5037,11 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA6A106B-75A4-4F54-9508-A66A4AEED06E}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="49" t="s">
@@ -5122,32 +5143,32 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:AG4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="49.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.44140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.44140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.44140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.44140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="5.44140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.44140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="5.44140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="4.44140625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="5.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="49.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="5.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33">
@@ -5446,10 +5467,13 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4903F224-3652-48FB-81A7-CAF06A9D7463}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:AD9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30">
@@ -6023,13 +6047,13 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="35.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -6107,11 +6131,14 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB53E397-0E70-4FE2-8956-CAC505C79FBA}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="33.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -6161,11 +6188,14 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71142910-3363-4189-996E-89090332A376}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:AC4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="5" max="5" width="6.21875" customWidth="1"/>
-    <col min="29" max="29" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.1796875" customWidth="1"/>
+    <col min="29" max="29" width="13.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -6461,16 +6491,16 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="63.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="63.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.453125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.54296875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="19.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -6603,25 +6633,25 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:R6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -6928,30 +6958,33 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42BBEF64-F0EA-4EA8-9A62-F5A7DF1E4869}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:U13"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="44.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="44.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.6328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.6328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.6328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.6328125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="15" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
@@ -7264,10 +7297,10 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="32.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -7309,8 +7342,11 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A51EFA8C-67A7-4B7E-8EF6-A12213F165A5}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="5" t="s">
@@ -7363,11 +7399,11 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFCF6FDB-3B87-457C-A3CA-7B39CE849651}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="24.88671875" style="31" customWidth="1"/>
-    <col min="2" max="2" width="17.44140625" style="31" customWidth="1"/>
-    <col min="3" max="16384" width="8.77734375" style="31"/>
+    <col min="1" max="1" width="24.90625" style="31" customWidth="1"/>
+    <col min="2" max="2" width="17.453125" style="31" customWidth="1"/>
+    <col min="3" max="16384" width="8.81640625" style="31"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -7571,19 +7607,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DDD085C-F9E3-44F9-93E4-153774C9882E}">
   <sheetPr>
-    <tabColor rgb="FFFFC000"/>
+    <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="39.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -7681,20 +7717,20 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="32.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.109375" customWidth="1"/>
+    <col min="1" max="1" width="32.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.453125" customWidth="1"/>
+    <col min="5" max="5" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -7880,19 +7916,22 @@
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C03B3B8-DBFD-430F-BAEF-858DA603C137}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.88671875" style="31" customWidth="1"/>
-    <col min="2" max="2" width="11.77734375" style="31" customWidth="1"/>
+    <col min="1" max="1" width="17.90625" style="31" customWidth="1"/>
+    <col min="2" max="2" width="11.81640625" style="31" customWidth="1"/>
     <col min="3" max="3" width="13" style="31" customWidth="1"/>
-    <col min="4" max="4" width="16.5546875" style="31" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" style="31" customWidth="1"/>
-    <col min="6" max="6" width="8.77734375" style="31"/>
-    <col min="7" max="7" width="17.77734375" style="31" customWidth="1"/>
-    <col min="8" max="8" width="15.44140625" style="31" customWidth="1"/>
-    <col min="9" max="9" width="11.5546875" style="31" customWidth="1"/>
-    <col min="10" max="16384" width="8.77734375" style="31"/>
+    <col min="4" max="4" width="16.54296875" style="31" customWidth="1"/>
+    <col min="5" max="5" width="15.81640625" style="31" customWidth="1"/>
+    <col min="6" max="6" width="8.81640625" style="31"/>
+    <col min="7" max="7" width="17.81640625" style="31" customWidth="1"/>
+    <col min="8" max="8" width="15.453125" style="31" customWidth="1"/>
+    <col min="9" max="9" width="11.54296875" style="31" customWidth="1"/>
+    <col min="10" max="16384" width="8.81640625" style="31"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -8022,22 +8061,25 @@
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BEBA80E-445C-4DC0-BF92-E52C1A0F0C80}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.90625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.90625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -8134,23 +8176,26 @@
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49F4CA74-BEAB-48B7-88AA-AF5A2ECCB1A9}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="25.77734375" style="45" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" style="45" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.81640625" style="45" customWidth="1"/>
+    <col min="2" max="2" width="11.90625" style="45" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" style="45" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.88671875" style="45" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.33203125" style="45" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.88671875" style="45" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.90625" style="45" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.36328125" style="45" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.90625" style="45" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15" style="45" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.88671875" style="45" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.33203125" style="45" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.44140625" style="45" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.33203125" style="45" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.88671875" style="45" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.21875" style="45" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.88671875" style="45"/>
+    <col min="8" max="8" width="11.90625" style="45" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.36328125" style="45" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.453125" style="45" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.36328125" style="45" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.90625" style="45" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.1796875" style="45" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.90625" style="45"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -8270,24 +8315,27 @@
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32D2560D-C5EA-4709-9F6E-C8E90540DCE9}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:O5"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="20.21875" style="45" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" style="45" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.1796875" style="45" customWidth="1"/>
+    <col min="2" max="2" width="11.90625" style="45" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" style="45" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.88671875" style="45" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.33203125" style="45" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="17.33203125" style="45" customWidth="1"/>
-    <col min="8" max="8" width="11.88671875" style="45" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.90625" style="45" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.36328125" style="45" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="17.36328125" style="45" customWidth="1"/>
+    <col min="8" max="8" width="11.90625" style="45" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15" style="45" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.88671875" style="45" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.33203125" style="45" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.44140625" style="45" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.33203125" style="45" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.88671875" style="45" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.21875" style="45" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.88671875" style="45"/>
+    <col min="10" max="10" width="11.90625" style="45" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.36328125" style="45" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.453125" style="45" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.36328125" style="45" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.90625" style="45" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.1796875" style="45" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.90625" style="45"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -8468,25 +8516,28 @@
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F57CC4F7-D796-4FC0-8D21-675BCC9631F3}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:O10"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="28.33203125" style="45" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" style="45" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.36328125" style="45" customWidth="1"/>
+    <col min="2" max="2" width="11.90625" style="45" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" style="45" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.88671875" style="45" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.33203125" style="45" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.77734375" style="45" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.109375" style="45" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.88671875" style="45" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.90625" style="45" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.36328125" style="45" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.81640625" style="45" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.08984375" style="45" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.90625" style="45" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15" style="45" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.88671875" style="45" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.33203125" style="45" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.109375" style="45" customWidth="1"/>
-    <col min="13" max="13" width="17.33203125" style="45" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.88671875" style="45" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.21875" style="45" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.88671875" style="45"/>
+    <col min="10" max="10" width="11.90625" style="45" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.36328125" style="45" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.08984375" style="45" customWidth="1"/>
+    <col min="13" max="13" width="17.36328125" style="45" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.90625" style="45" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.1796875" style="45" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.90625" style="45"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -8780,14 +8831,17 @@
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAD3A3F3-6459-41EA-B01C-AF05B02017D3}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="24" style="45" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" style="45" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="45"/>
-    <col min="4" max="4" width="19.6640625" style="45" customWidth="1"/>
-    <col min="5" max="16384" width="8.88671875" style="45"/>
+    <col min="2" max="2" width="11.453125" style="45" customWidth="1"/>
+    <col min="3" max="3" width="8.90625" style="45"/>
+    <col min="4" max="4" width="19.6328125" style="45" customWidth="1"/>
+    <col min="5" max="16384" width="8.90625" style="45"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -8825,15 +8879,18 @@
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E44C5F5-E6C8-45C1-9446-57992D422B94}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="32.21875" style="45" customWidth="1"/>
+    <col min="1" max="1" width="32.1796875" style="45" customWidth="1"/>
     <col min="2" max="2" width="14" style="45" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" style="45" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" style="45" customWidth="1"/>
-    <col min="5" max="5" width="11.77734375" style="45" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="45"/>
+    <col min="3" max="3" width="16.6328125" style="45" customWidth="1"/>
+    <col min="4" max="4" width="17.6328125" style="45" customWidth="1"/>
+    <col min="5" max="5" width="11.81640625" style="45" customWidth="1"/>
+    <col min="6" max="16384" width="8.90625" style="45"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -8911,14 +8968,17 @@
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AD2EA96-0A49-43F7-B556-DEF20EEBE041}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="38.21875" style="45" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" style="45" customWidth="1"/>
-    <col min="3" max="3" width="15.5546875" style="45" customWidth="1"/>
+    <col min="1" max="1" width="38.1796875" style="45" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" style="45" customWidth="1"/>
+    <col min="3" max="3" width="15.54296875" style="45" customWidth="1"/>
     <col min="4" max="4" width="19" style="45" customWidth="1"/>
-    <col min="5" max="16384" width="8.88671875" style="45"/>
+    <col min="5" max="16384" width="8.90625" style="45"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -9035,24 +9095,27 @@
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95C36D3A-0E6B-4A46-B36A-9E4A925A4C78}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="24.6640625" style="45" customWidth="1"/>
-    <col min="2" max="2" width="17.77734375" style="45" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" style="45" customWidth="1"/>
-    <col min="4" max="4" width="16.109375" style="45" customWidth="1"/>
+    <col min="1" max="1" width="24.6328125" style="45" customWidth="1"/>
+    <col min="2" max="2" width="17.81640625" style="45" customWidth="1"/>
+    <col min="3" max="3" width="16.453125" style="45" customWidth="1"/>
+    <col min="4" max="4" width="16.08984375" style="45" customWidth="1"/>
     <col min="5" max="5" width="12" style="45" customWidth="1"/>
-    <col min="6" max="6" width="18.109375" style="45" customWidth="1"/>
-    <col min="7" max="7" width="15.109375" style="45" customWidth="1"/>
-    <col min="8" max="8" width="10.44140625" style="45" customWidth="1"/>
-    <col min="9" max="9" width="10.77734375" style="45" customWidth="1"/>
-    <col min="10" max="10" width="8.88671875" style="45"/>
-    <col min="11" max="11" width="13.21875" style="45" customWidth="1"/>
-    <col min="12" max="12" width="12.6640625" style="45" customWidth="1"/>
-    <col min="13" max="13" width="14.109375" style="45" customWidth="1"/>
-    <col min="14" max="14" width="14.33203125" style="45" customWidth="1"/>
-    <col min="15" max="16384" width="8.88671875" style="45"/>
+    <col min="6" max="6" width="18.08984375" style="45" customWidth="1"/>
+    <col min="7" max="7" width="15.08984375" style="45" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" style="45" customWidth="1"/>
+    <col min="9" max="9" width="10.81640625" style="45" customWidth="1"/>
+    <col min="10" max="10" width="8.90625" style="45"/>
+    <col min="11" max="11" width="13.1796875" style="45" customWidth="1"/>
+    <col min="12" max="12" width="12.6328125" style="45" customWidth="1"/>
+    <col min="13" max="13" width="14.08984375" style="45" customWidth="1"/>
+    <col min="14" max="14" width="14.36328125" style="45" customWidth="1"/>
+    <col min="15" max="16384" width="8.90625" style="45"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -9210,13 +9273,13 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="39.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -9282,12 +9345,12 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="57.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="57.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -9404,30 +9467,30 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:V15"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="50" style="27" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.33203125" style="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" style="27" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.33203125" style="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.21875" style="27" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.44140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="8.77734375" style="27"/>
-    <col min="9" max="9" width="10.44140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.6640625" style="27" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.44140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.21875" style="27" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.44140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.21875" style="27" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.36328125" style="27" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.08984375" style="27" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.36328125" style="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1796875" style="27" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.453125" style="27" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="8.81640625" style="27"/>
+    <col min="9" max="9" width="10.453125" style="27" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.6328125" style="27" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.453125" style="27" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.1796875" style="27" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.453125" style="27" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.1796875" style="27" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" style="27" customWidth="1"/>
-    <col min="16" max="16" width="10.21875" style="27" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.44140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.21875" style="27" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.6640625" style="27" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.6640625" style="27" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.21875" style="27" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.6640625" style="27" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="8.77734375" style="27"/>
+    <col min="16" max="16" width="10.1796875" style="27" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.453125" style="27" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.1796875" style="27" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.6328125" style="27" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.6328125" style="27" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.1796875" style="27" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.6328125" style="27" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="8.81640625" style="27"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
@@ -10116,31 +10179,31 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:AB7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="44.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="44.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.1796875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="10" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.1796875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="10" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28">
@@ -10537,11 +10600,11 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:W17"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="54.33203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="54.36328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -11290,18 +11353,18 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:S20"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="53.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="12.21875" customWidth="1"/>
-    <col min="8" max="8" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="53.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="12.1796875" customWidth="1"/>
+    <col min="8" max="8" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19">

--- a/src/test/java/TestData/Scenario_TestData.xlsx
+++ b/src/test/java/TestData/Scenario_TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Copa_SHD_WebServices\src\test\java\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3251CD2-77B8-4BBA-8FFC-F8546816CCDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EA7B68D-3AF1-4E55-87EC-F1E7D388C43A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="22" activeTab="24" xr2:uid="{5D5A4724-D560-4FC2-9708-4BBF1DBA0B11}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="26" activeTab="28" xr2:uid="{5D5A4724-D560-4FC2-9708-4BBF1DBA0B11}"/>
   </bookViews>
   <sheets>
     <sheet name="AdvancePassengerInfo" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1877" uniqueCount="580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2079" uniqueCount="621">
   <si>
     <t>Scenario</t>
   </si>
@@ -1814,6 +1814,129 @@
   </si>
   <si>
     <t>A0LVK0</t>
+  </si>
+  <si>
+    <t>FR</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>CC-Country Code</t>
+  </si>
+  <si>
+    <t>DocHolderNationality CC</t>
+  </si>
+  <si>
+    <t>EmbarkationLocation CC</t>
+  </si>
+  <si>
+    <t>TransitLocation CC</t>
+  </si>
+  <si>
+    <t>VisitedLocation CC</t>
+  </si>
+  <si>
+    <t>CountryOfResidence</t>
+  </si>
+  <si>
+    <t>DestinationLocation</t>
+  </si>
+  <si>
+    <t>LON</t>
+  </si>
+  <si>
+    <t>CN</t>
+  </si>
+  <si>
+    <t>GB</t>
+  </si>
+  <si>
+    <t>NIL</t>
+  </si>
+  <si>
+    <t>BA</t>
+  </si>
+  <si>
+    <t>RK</t>
+  </si>
+  <si>
+    <t>TT</t>
+  </si>
+  <si>
+    <t>DK</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>TransitLocation</t>
+  </si>
+  <si>
+    <t>AKG</t>
+  </si>
+  <si>
+    <t>BLB</t>
+  </si>
+  <si>
+    <t>CIX</t>
+  </si>
+  <si>
+    <t>DestinationLocation CC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   -</t>
+  </si>
+  <si>
+    <t>FK</t>
+  </si>
+  <si>
+    <t>GY</t>
+  </si>
+  <si>
+    <t>OMO</t>
+  </si>
+  <si>
+    <t>BGI</t>
+  </si>
+  <si>
+    <t>BIA</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>OM</t>
+  </si>
+  <si>
+    <t>RO</t>
+  </si>
+  <si>
+    <t>SM</t>
+  </si>
+  <si>
+    <t>PDV</t>
+  </si>
+  <si>
+    <t>GNE</t>
+  </si>
+  <si>
+    <t>DJA</t>
+  </si>
+  <si>
+    <t>CityCountryListDisplay</t>
+  </si>
+  <si>
+    <t>BR</t>
+  </si>
+  <si>
+    <t>BKK</t>
+  </si>
+  <si>
+    <t>VS</t>
+  </si>
+  <si>
+    <t>AG</t>
   </si>
 </sst>
 </file>
@@ -1907,7 +2030,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1947,6 +2070,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2037,7 +2172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2134,6 +2269,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7488,209 +7625,782 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="24.90625" style="29" customWidth="1"/>
-    <col min="2" max="2" width="17.453125" style="29" customWidth="1"/>
-    <col min="3" max="16384" width="8.81640625" style="29"/>
+    <col min="2" max="2" width="14" style="29" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" style="29" customWidth="1"/>
+    <col min="4" max="4" width="9.54296875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10.36328125" style="29" customWidth="1"/>
+    <col min="6" max="6" width="9.36328125" style="29" customWidth="1"/>
+    <col min="7" max="7" width="9.7265625" style="29" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" style="29" customWidth="1"/>
+    <col min="9" max="9" width="8.81640625" style="29" customWidth="1"/>
+    <col min="10" max="10" width="8.08984375" style="41" customWidth="1"/>
+    <col min="11" max="11" width="10" style="29" customWidth="1"/>
+    <col min="12" max="12" width="7.81640625" style="29" customWidth="1"/>
+    <col min="13" max="13" width="9" style="29" customWidth="1"/>
+    <col min="14" max="14" width="19.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.81640625" style="29"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:14">
       <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>271</v>
-      </c>
-      <c r="C1" s="32" t="s">
-        <v>145</v>
-      </c>
-      <c r="D1" s="32" t="s">
-        <v>146</v>
-      </c>
-      <c r="E1" s="32" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>266</v>
+      </c>
+      <c r="C1" s="42" t="s">
+        <v>583</v>
+      </c>
+      <c r="D1" s="42" t="s">
+        <v>584</v>
+      </c>
+      <c r="E1" s="42" t="s">
+        <v>585</v>
+      </c>
+      <c r="F1" s="42" t="s">
+        <v>586</v>
+      </c>
+      <c r="G1" s="63" t="s">
+        <v>587</v>
+      </c>
+      <c r="H1" s="63" t="s">
+        <v>588</v>
+      </c>
+      <c r="I1" s="63" t="s">
+        <v>588</v>
+      </c>
+      <c r="J1" s="63" t="s">
+        <v>598</v>
+      </c>
+      <c r="K1" s="42" t="s">
+        <v>585</v>
+      </c>
+      <c r="L1" s="42" t="s">
+        <v>586</v>
+      </c>
+      <c r="M1" s="42" t="s">
+        <v>602</v>
+      </c>
+      <c r="N1" s="42" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="32" t="s">
         <v>289</v>
       </c>
       <c r="B2" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="C2" s="32" t="s">
+        <v>580</v>
+      </c>
+      <c r="D2" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="E2" s="32" t="s">
+        <v>590</v>
+      </c>
+      <c r="F2" s="44" t="s">
+        <v>581</v>
+      </c>
+      <c r="G2" s="44" t="s">
+        <v>338</v>
+      </c>
+      <c r="H2" s="44" t="s">
+        <v>589</v>
+      </c>
+      <c r="I2" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="J2" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="K2" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="L2" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="M2" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="N2" s="44" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="32" t="s">
         <v>290</v>
       </c>
       <c r="B3" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="C3" s="32" t="s">
+        <v>580</v>
+      </c>
+      <c r="D3" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>591</v>
+      </c>
+      <c r="F3" s="44" t="s">
+        <v>590</v>
+      </c>
+      <c r="G3" s="44" t="s">
+        <v>338</v>
+      </c>
+      <c r="H3" s="44" t="s">
+        <v>589</v>
+      </c>
+      <c r="I3" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="J3" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="K3" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="L3" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="M3" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="N3" s="44" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="32" t="s">
         <v>291</v>
       </c>
       <c r="B4" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="C4" s="32" t="s">
+        <v>580</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="E4" s="32" t="s">
+        <v>590</v>
+      </c>
+      <c r="F4" s="44" t="s">
+        <v>581</v>
+      </c>
+      <c r="G4" s="44" t="s">
+        <v>338</v>
+      </c>
+      <c r="H4" s="44" t="s">
+        <v>589</v>
+      </c>
+      <c r="I4" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="J4" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="K4" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="L4" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="M4" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="N4" s="44" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="32" t="s">
         <v>292</v>
       </c>
       <c r="B5" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="C5" s="32" t="s">
+        <v>580</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="E5" s="32" t="s">
+        <v>581</v>
+      </c>
+      <c r="F5" s="44" t="s">
+        <v>592</v>
+      </c>
+      <c r="G5" s="44" t="s">
+        <v>338</v>
+      </c>
+      <c r="H5" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="I5" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="J5" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="K5" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="L5" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="M5" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="N5" s="44" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="32" t="s">
         <v>293</v>
       </c>
       <c r="B6" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="32"/>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="C6" s="44" t="s">
+        <v>580</v>
+      </c>
+      <c r="D6" s="44" t="s">
+        <v>121</v>
+      </c>
+      <c r="E6" s="44" t="s">
+        <v>581</v>
+      </c>
+      <c r="F6" s="44" t="s">
+        <v>592</v>
+      </c>
+      <c r="G6" s="44" t="s">
+        <v>338</v>
+      </c>
+      <c r="H6" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="I6" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="J6" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="K6" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="L6" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="M6" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="N6" s="44" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="32" t="s">
         <v>294</v>
       </c>
       <c r="B7" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="32"/>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="C7" s="44" t="s">
+        <v>580</v>
+      </c>
+      <c r="D7" s="44" t="s">
+        <v>121</v>
+      </c>
+      <c r="E7" s="44" t="s">
+        <v>581</v>
+      </c>
+      <c r="F7" s="44" t="s">
+        <v>592</v>
+      </c>
+      <c r="G7" s="44" t="s">
+        <v>338</v>
+      </c>
+      <c r="H7" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="I7" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="J7" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="K7" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="L7" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="M7" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="N7" s="44" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="32" t="s">
         <v>295</v>
       </c>
       <c r="B8" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="C8" s="44" t="s">
+        <v>593</v>
+      </c>
+      <c r="D8" s="44" t="s">
+        <v>121</v>
+      </c>
+      <c r="E8" s="44" t="s">
+        <v>594</v>
+      </c>
+      <c r="F8" s="44" t="s">
+        <v>596</v>
+      </c>
+      <c r="G8" s="44" t="s">
+        <v>338</v>
+      </c>
+      <c r="H8" s="44" t="s">
+        <v>600</v>
+      </c>
+      <c r="I8" s="44" t="s">
+        <v>601</v>
+      </c>
+      <c r="J8" s="44" t="s">
+        <v>599</v>
+      </c>
+      <c r="K8" s="44" t="s">
+        <v>595</v>
+      </c>
+      <c r="L8" s="44" t="s">
+        <v>597</v>
+      </c>
+      <c r="M8" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="N8" s="44" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="32" t="s">
         <v>296</v>
       </c>
       <c r="B9" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="C9" s="32" t="s">
+        <v>580</v>
+      </c>
+      <c r="D9" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="E9" s="32" t="s">
+        <v>604</v>
+      </c>
+      <c r="F9" s="44" t="s">
+        <v>591</v>
+      </c>
+      <c r="G9" s="44" t="s">
+        <v>338</v>
+      </c>
+      <c r="H9" s="44" t="s">
+        <v>606</v>
+      </c>
+      <c r="I9" s="44" t="s">
+        <v>607</v>
+      </c>
+      <c r="J9" s="44" t="s">
+        <v>608</v>
+      </c>
+      <c r="K9" s="44" t="s">
+        <v>605</v>
+      </c>
+      <c r="L9" s="44" t="s">
+        <v>596</v>
+      </c>
+      <c r="M9" s="44" t="s">
+        <v>432</v>
+      </c>
+      <c r="N9" s="44" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="32" t="s">
         <v>297</v>
       </c>
       <c r="B10" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="C10" s="32"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="32"/>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="C10" s="44" t="s">
+        <v>580</v>
+      </c>
+      <c r="D10" s="44" t="s">
+        <v>121</v>
+      </c>
+      <c r="E10" s="32" t="s">
+        <v>610</v>
+      </c>
+      <c r="F10" s="44" t="s">
+        <v>612</v>
+      </c>
+      <c r="G10" s="44" t="s">
+        <v>338</v>
+      </c>
+      <c r="H10" s="44" t="s">
+        <v>613</v>
+      </c>
+      <c r="I10" s="44" t="s">
+        <v>614</v>
+      </c>
+      <c r="J10" s="44" t="s">
+        <v>615</v>
+      </c>
+      <c r="K10" s="44" t="s">
+        <v>611</v>
+      </c>
+      <c r="L10" s="44" t="s">
+        <v>596</v>
+      </c>
+      <c r="M10" s="44" t="s">
+        <v>609</v>
+      </c>
+      <c r="N10" s="44" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="32" t="s">
         <v>298</v>
       </c>
       <c r="B11" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="C11" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="D11" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="E11" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="F11" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="G11" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="H11" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="I11" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="J11" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="K11" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="L11" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="M11" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="N11" s="44" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="32" t="s">
         <v>299</v>
       </c>
       <c r="B12" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="C12" s="32"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="32"/>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="C12" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="D12" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="E12" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="F12" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="G12" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="H12" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="I12" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="J12" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="K12" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="L12" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="M12" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="N12" s="44" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="32" t="s">
         <v>300</v>
       </c>
       <c r="B13" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="C13" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="D13" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="E13" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="F13" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="G13" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="H13" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="I13" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="J13" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="K13" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="L13" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="M13" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="N13" s="44" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="32" t="s">
         <v>301</v>
       </c>
       <c r="B14" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="C14" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="D14" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="E14" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="F14" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="G14" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="H14" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="I14" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="J14" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="K14" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="L14" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="M14" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="N14" s="44" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="32" t="s">
         <v>302</v>
       </c>
       <c r="B15" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="C15" s="44" t="s">
+        <v>617</v>
+      </c>
+      <c r="D15" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="E15" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="F15" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="G15" s="44" t="s">
+        <v>618</v>
+      </c>
+      <c r="H15" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="I15" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="J15" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="K15" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="L15" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="M15" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="N15" s="44" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="32" t="s">
         <v>303</v>
       </c>
       <c r="B16" s="32" t="s">
-        <v>149</v>
-      </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-    </row>
-    <row r="17" spans="1:5">
+        <v>619</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>580</v>
+      </c>
+      <c r="D16" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="E16" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="F16" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="G16" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="H16" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="I16" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="J16" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="K16" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="L16" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="M16" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="N16" s="44" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="32" t="s">
         <v>304</v>
       </c>
       <c r="B17" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="C17" s="32"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="32"/>
+      <c r="C17" s="32" t="s">
+        <v>620</v>
+      </c>
+      <c r="D17" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="E17" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="F17" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="G17" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="H17" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="I17" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="J17" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="K17" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="L17" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="M17" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="N17" s="44" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="62" t="s">
+        <v>582</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/src/test/java/TestData/Scenario_TestData.xlsx
+++ b/src/test/java/TestData/Scenario_TestData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Copa_SHD_WebServices\src\test\java\TestData\"/>
     </mc:Choice>
@@ -55,7 +55,7 @@
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2079" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="624">
   <si>
     <t>Scenario</t>
   </si>
@@ -1937,12 +1937,22 @@
   </si>
   <si>
     <t>AG</t>
+  </si>
+  <si>
+    <t>A2CS0Z</t>
+  </si>
+  <si>
+    <t>A2CTF1</t>
+  </si>
+  <si>
+    <t>A2CTH3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="13">
     <font>
       <sz val="11"/>
@@ -2591,20 +2601,20 @@
   <dimension ref="A1:P15"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="52.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="52.81640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="18.453125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="9.453125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="10.453125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="10.453125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="10.453125"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="15.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2839,13 +2849,13 @@
   <dimension ref="A1:U22"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="49" customWidth="1"/>
-    <col min="10" max="10" width="8.81640625" style="25"/>
-    <col min="12" max="12" width="15.90625" customWidth="1"/>
-    <col min="17" max="17" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="49.0"/>
+    <col min="10" max="10" style="25" width="8.81640625"/>
+    <col min="12" max="12" customWidth="true" width="15.90625"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="13.90625"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="12.6328125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
@@ -3797,16 +3807,16 @@
   <dimension ref="A1:N4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="32.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.54296875" style="29" customWidth="1"/>
-    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.81640625" customWidth="1"/>
-    <col min="6" max="6" width="14.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="14.36328125" style="29" customWidth="1"/>
-    <col min="12" max="12" width="30.36328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.453125" customWidth="1"/>
-    <col min="14" max="14" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="32.90625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="3" max="3" customWidth="true" style="29" width="17.54296875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="5" max="5" customWidth="true" width="13.81640625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="14.36328125"/>
+    <col min="7" max="11" customWidth="true" style="29" width="14.36328125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="30.36328125"/>
+    <col min="13" max="13" customWidth="true" width="8.453125"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="10.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -3994,17 +4004,17 @@
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="21.81640625" style="29" customWidth="1"/>
-    <col min="2" max="2" width="16.54296875" style="29" customWidth="1"/>
-    <col min="3" max="3" width="19.90625" style="29" customWidth="1"/>
-    <col min="4" max="4" width="18.81640625" style="29" customWidth="1"/>
-    <col min="5" max="6" width="12.90625" style="29" customWidth="1"/>
-    <col min="7" max="7" width="15" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.90625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.81640625" style="29"/>
-    <col min="10" max="10" width="17.90625" style="29" customWidth="1"/>
-    <col min="11" max="11" width="14.1796875" style="29" customWidth="1"/>
-    <col min="12" max="16384" width="8.81640625" style="29"/>
+    <col min="1" max="1" customWidth="true" style="29" width="21.81640625"/>
+    <col min="2" max="2" customWidth="true" style="29" width="16.54296875"/>
+    <col min="3" max="3" customWidth="true" style="29" width="19.90625"/>
+    <col min="4" max="4" customWidth="true" style="29" width="18.81640625"/>
+    <col min="5" max="6" customWidth="true" style="29" width="12.90625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="15.0"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="11.90625"/>
+    <col min="9" max="9" style="29" width="8.81640625"/>
+    <col min="10" max="10" customWidth="true" style="29" width="17.90625"/>
+    <col min="11" max="11" customWidth="true" style="29" width="14.1796875"/>
+    <col min="12" max="16384" style="29" width="8.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -4174,12 +4184,12 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="42.1796875" style="29" customWidth="1"/>
-    <col min="2" max="2" width="15.81640625" style="29" customWidth="1"/>
-    <col min="3" max="3" width="17.81640625" style="29" customWidth="1"/>
-    <col min="4" max="4" width="16.81640625" style="29" customWidth="1"/>
-    <col min="5" max="5" width="15.6328125" style="29" customWidth="1"/>
-    <col min="6" max="16384" width="8.81640625" style="29"/>
+    <col min="1" max="1" customWidth="true" style="29" width="42.1796875"/>
+    <col min="2" max="2" customWidth="true" style="29" width="15.81640625"/>
+    <col min="3" max="3" customWidth="true" style="29" width="17.81640625"/>
+    <col min="4" max="4" customWidth="true" style="29" width="16.81640625"/>
+    <col min="5" max="5" customWidth="true" style="29" width="15.6328125"/>
+    <col min="6" max="16384" style="29" width="8.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4298,28 +4308,28 @@
   <dimension ref="A1:AB6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="51.81640625" customWidth="1"/>
-    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="51.81640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="9.453125"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="18.453125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="14.453125"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="18.453125"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="18.453125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="12.08984375"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="15.36328125"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="12.08984375"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" width="15.36328125"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" width="12.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28">
@@ -4742,10 +4752,10 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="76.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="76.1796875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="13.453125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="12.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4830,12 +4840,12 @@
   <dimension ref="A1:E15"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="68.08984375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.54296875" style="29" customWidth="1"/>
-    <col min="3" max="3" width="14.81640625" style="29" customWidth="1"/>
-    <col min="4" max="4" width="11.81640625" style="29" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.1796875" style="29" customWidth="1"/>
-    <col min="6" max="16384" width="8.81640625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="68.08984375"/>
+    <col min="2" max="2" customWidth="true" style="29" width="12.54296875"/>
+    <col min="3" max="3" customWidth="true" style="29" width="14.81640625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="29" width="11.81640625"/>
+    <col min="5" max="5" customWidth="true" style="29" width="18.1796875"/>
+    <col min="6" max="16384" style="29" width="8.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -5082,8 +5092,8 @@
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="12.54296875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -5123,11 +5133,11 @@
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="33.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="33.54296875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="13.453125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="12.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -5177,7 +5187,7 @@
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="21.81640625" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="21.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -5282,31 +5292,31 @@
   <dimension ref="A1:AG4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="49.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="49.81640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="4.81640625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="4.453125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="4.453125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="4.453125"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="4.453125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="4.453125"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="4.453125"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="4.453125"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" width="9.7265625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33">
@@ -5611,25 +5621,25 @@
   <dimension ref="A1:AD9"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="33" customWidth="1"/>
-    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.36328125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="33.0"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="18.36328125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="12.08984375"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="18.36328125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="15.36328125"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="13.90625"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="12.08984375"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="15.36328125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="14.36328125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="12.08984375"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="15.36328125"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" width="12.08984375"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="17.54296875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30">
@@ -6213,11 +6223,11 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="35.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="35.1796875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="11.54296875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="13.453125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -6301,9 +6311,9 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="33.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="33.54296875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="13.453125"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="9.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -6359,9 +6369,9 @@
   <dimension ref="A1:AC4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="46.6328125" customWidth="1"/>
-    <col min="5" max="5" width="6.1796875" customWidth="1"/>
-    <col min="29" max="29" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="46.6328125"/>
+    <col min="5" max="5" customWidth="true" width="6.1796875"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="13.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -6659,14 +6669,14 @@
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="63.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="63.81640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="10.81640625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="19.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="15.54296875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="8" max="9" bestFit="true" customWidth="true" width="19.453125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -6801,24 +6811,24 @@
   <dimension ref="A1:R6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.6328125" customWidth="1"/>
-    <col min="18" max="18" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="12.0"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="9.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="6.1796875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="13.81640625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="7.453125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="18.453125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="18.453125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="17" max="17" customWidth="true" width="17.6328125"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="13.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -7123,27 +7133,27 @@
   <dimension ref="A1:U13"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="44.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.6328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.6328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.6328125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.6328125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="44.08984375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.36328125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="9.1796875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="6.1796875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="17.36328125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="9.1796875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="6.1796875"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="8.54296875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="18.6328125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="18.6328125"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="18.6328125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="18.6328125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="14.08984375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
@@ -7518,8 +7528,8 @@
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="32.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="32.1796875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -7567,7 +7577,7 @@
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="18.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -7628,21 +7638,21 @@
   <dimension ref="A1:N19"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="24.90625" style="29" customWidth="1"/>
-    <col min="2" max="2" width="14" style="29" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" style="29" customWidth="1"/>
-    <col min="4" max="4" width="9.54296875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10.36328125" style="29" customWidth="1"/>
-    <col min="6" max="6" width="9.36328125" style="29" customWidth="1"/>
-    <col min="7" max="7" width="9.7265625" style="29" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" style="29" customWidth="1"/>
-    <col min="9" max="9" width="8.81640625" style="29" customWidth="1"/>
-    <col min="10" max="10" width="8.08984375" style="41" customWidth="1"/>
-    <col min="11" max="11" width="10" style="29" customWidth="1"/>
-    <col min="12" max="12" width="7.81640625" style="29" customWidth="1"/>
-    <col min="13" max="13" width="9" style="29" customWidth="1"/>
-    <col min="14" max="14" width="19.453125" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.81640625" style="29"/>
+    <col min="1" max="1" customWidth="true" style="29" width="24.90625"/>
+    <col min="2" max="2" customWidth="true" style="29" width="14.0"/>
+    <col min="3" max="3" customWidth="true" style="29" width="11.81640625"/>
+    <col min="4" max="4" customWidth="true" style="29" width="9.54296875"/>
+    <col min="5" max="5" customWidth="true" style="29" width="10.36328125"/>
+    <col min="6" max="6" customWidth="true" style="29" width="9.36328125"/>
+    <col min="7" max="7" customWidth="true" style="29" width="9.7265625"/>
+    <col min="8" max="8" customWidth="true" style="29" width="10.453125"/>
+    <col min="9" max="9" customWidth="true" style="29" width="8.81640625"/>
+    <col min="10" max="10" customWidth="true" style="41" width="8.08984375"/>
+    <col min="11" max="11" customWidth="true" style="29" width="10.0"/>
+    <col min="12" max="12" customWidth="true" style="29" width="7.81640625"/>
+    <col min="13" max="13" customWidth="true" style="29" width="9.0"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="19.453125"/>
+    <col min="15" max="16384" style="29" width="8.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -8412,14 +8422,14 @@
   <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="39.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="39.453125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="21.81640625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="9.453125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="6.453125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="18.453125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -8523,18 +8533,18 @@
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="32.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.453125" customWidth="1"/>
-    <col min="5" max="5" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.08984375" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="32.1796875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="4" max="4" customWidth="true" width="15.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="17.36328125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="13" max="13" customWidth="true" width="15.08984375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -8726,16 +8736,16 @@
   <dimension ref="A1:K4"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.90625" style="29" customWidth="1"/>
-    <col min="2" max="2" width="11.81640625" style="29" customWidth="1"/>
-    <col min="3" max="3" width="13" style="29" customWidth="1"/>
-    <col min="4" max="4" width="16.54296875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="15.81640625" style="29" customWidth="1"/>
-    <col min="6" max="6" width="8.81640625" style="29"/>
-    <col min="7" max="7" width="17.81640625" style="29" customWidth="1"/>
-    <col min="8" max="8" width="15.453125" style="29" customWidth="1"/>
-    <col min="9" max="9" width="11.54296875" style="29" customWidth="1"/>
-    <col min="10" max="16384" width="8.81640625" style="29"/>
+    <col min="1" max="1" customWidth="true" style="29" width="17.90625"/>
+    <col min="2" max="2" customWidth="true" style="29" width="11.81640625"/>
+    <col min="3" max="3" customWidth="true" style="29" width="13.0"/>
+    <col min="4" max="4" customWidth="true" style="29" width="16.54296875"/>
+    <col min="5" max="5" customWidth="true" style="29" width="15.81640625"/>
+    <col min="6" max="6" style="29" width="8.81640625"/>
+    <col min="7" max="7" customWidth="true" style="29" width="17.81640625"/>
+    <col min="8" max="8" customWidth="true" style="29" width="15.453125"/>
+    <col min="9" max="9" customWidth="true" style="29" width="11.54296875"/>
+    <col min="10" max="16384" style="29" width="8.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -8790,7 +8800,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>350</v>
+        <v>623</v>
       </c>
       <c r="G2" s="32">
         <v>2</v>
@@ -8871,19 +8881,19 @@
   <dimension ref="A1:M3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="19.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="19.90625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="17.36328125"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="17.36328125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="4.453125"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="17.36328125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="14.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -8986,20 +8996,20 @@
   <dimension ref="A1:M4"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="25.81640625" style="41" customWidth="1"/>
-    <col min="2" max="2" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="41" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15" style="41" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.453125" style="41" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.1796875" style="41" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.90625" style="41"/>
+    <col min="1" max="1" customWidth="true" style="41" width="25.81640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="41" width="15.0"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="41" width="15.0"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="41" width="4.453125"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="41" width="14.1796875"/>
+    <col min="14" max="16384" style="41" width="8.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -9125,21 +9135,21 @@
   <dimension ref="A1:O5"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="20.1796875" style="41" customWidth="1"/>
-    <col min="2" max="2" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="41" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="17.36328125" style="41" customWidth="1"/>
-    <col min="8" max="8" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15" style="41" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.453125" style="41" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.1796875" style="41" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.90625" style="41"/>
+    <col min="1" max="1" customWidth="true" style="41" width="20.1796875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="41" width="15.0"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
+    <col min="6" max="7" customWidth="true" style="41" width="17.36328125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="41" width="15.0"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="41" width="4.453125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="41" width="14.1796875"/>
+    <col min="16" max="16384" style="41" width="8.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -9326,22 +9336,22 @@
   <dimension ref="A1:O10"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="28.36328125" style="41" customWidth="1"/>
-    <col min="2" max="2" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="41" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.81640625" style="41" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.08984375" style="41" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15" style="41" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.08984375" style="41" customWidth="1"/>
-    <col min="13" max="13" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.1796875" style="41" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.90625" style="41"/>
+    <col min="1" max="1" customWidth="true" style="41" width="28.36328125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="41" width="15.0"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="41" width="16.81640625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="41" width="11.08984375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="41" width="15.0"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
+    <col min="12" max="12" customWidth="true" style="41" width="13.08984375"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="41" width="14.1796875"/>
+    <col min="16" max="16384" style="41" width="8.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -9641,11 +9651,11 @@
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="24" style="41" customWidth="1"/>
-    <col min="2" max="2" width="11.453125" style="41" customWidth="1"/>
-    <col min="3" max="3" width="8.90625" style="41"/>
-    <col min="4" max="4" width="19.6328125" style="41" customWidth="1"/>
-    <col min="5" max="16384" width="8.90625" style="41"/>
+    <col min="1" max="1" customWidth="true" style="41" width="24.0"/>
+    <col min="2" max="2" customWidth="true" style="41" width="11.453125"/>
+    <col min="3" max="3" style="41" width="8.90625"/>
+    <col min="4" max="4" customWidth="true" style="41" width="19.6328125"/>
+    <col min="5" max="16384" style="41" width="8.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9689,12 +9699,12 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="32.1796875" style="41" customWidth="1"/>
-    <col min="2" max="2" width="14" style="41" customWidth="1"/>
-    <col min="3" max="3" width="16.6328125" style="41" customWidth="1"/>
-    <col min="4" max="4" width="17.6328125" style="41" customWidth="1"/>
-    <col min="5" max="5" width="11.81640625" style="41" customWidth="1"/>
-    <col min="6" max="16384" width="8.90625" style="41"/>
+    <col min="1" max="1" customWidth="true" style="41" width="32.1796875"/>
+    <col min="2" max="2" customWidth="true" style="41" width="14.0"/>
+    <col min="3" max="3" customWidth="true" style="41" width="16.6328125"/>
+    <col min="4" max="4" customWidth="true" style="41" width="17.6328125"/>
+    <col min="5" max="5" customWidth="true" style="41" width="11.81640625"/>
+    <col min="6" max="16384" style="41" width="8.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -9778,11 +9788,11 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="38.1796875" style="41" customWidth="1"/>
-    <col min="2" max="2" width="13.54296875" style="41" customWidth="1"/>
-    <col min="3" max="3" width="15.54296875" style="41" customWidth="1"/>
-    <col min="4" max="4" width="19" style="41" customWidth="1"/>
-    <col min="5" max="16384" width="8.90625" style="41"/>
+    <col min="1" max="1" customWidth="true" style="41" width="38.1796875"/>
+    <col min="2" max="2" customWidth="true" style="41" width="13.54296875"/>
+    <col min="3" max="3" customWidth="true" style="41" width="15.54296875"/>
+    <col min="4" max="4" customWidth="true" style="41" width="19.0"/>
+    <col min="5" max="16384" style="41" width="8.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -9905,21 +9915,21 @@
   <dimension ref="A1:N5"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="30.90625" style="41" customWidth="1"/>
-    <col min="2" max="2" width="17.81640625" style="41" customWidth="1"/>
-    <col min="3" max="3" width="16.453125" style="41" customWidth="1"/>
-    <col min="4" max="4" width="16.08984375" style="41" customWidth="1"/>
-    <col min="5" max="5" width="12" style="41" customWidth="1"/>
-    <col min="6" max="6" width="18.08984375" style="41" customWidth="1"/>
-    <col min="7" max="7" width="15.08984375" style="41" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" style="41" customWidth="1"/>
-    <col min="9" max="9" width="10.81640625" style="41" customWidth="1"/>
-    <col min="10" max="10" width="8.90625" style="41"/>
-    <col min="11" max="11" width="13.1796875" style="41" customWidth="1"/>
-    <col min="12" max="12" width="12.6328125" style="41" customWidth="1"/>
-    <col min="13" max="13" width="14.08984375" style="41" customWidth="1"/>
-    <col min="14" max="14" width="14.36328125" style="41" customWidth="1"/>
-    <col min="15" max="16384" width="8.90625" style="41"/>
+    <col min="1" max="1" customWidth="true" style="41" width="30.90625"/>
+    <col min="2" max="2" customWidth="true" style="41" width="17.81640625"/>
+    <col min="3" max="3" customWidth="true" style="41" width="16.453125"/>
+    <col min="4" max="4" customWidth="true" style="41" width="16.08984375"/>
+    <col min="5" max="5" customWidth="true" style="41" width="12.0"/>
+    <col min="6" max="6" customWidth="true" style="41" width="18.08984375"/>
+    <col min="7" max="7" customWidth="true" style="41" width="15.08984375"/>
+    <col min="8" max="8" customWidth="true" style="41" width="10.453125"/>
+    <col min="9" max="9" customWidth="true" style="41" width="10.81640625"/>
+    <col min="10" max="10" style="41" width="8.90625"/>
+    <col min="11" max="11" customWidth="true" style="41" width="13.1796875"/>
+    <col min="12" max="12" customWidth="true" style="41" width="12.6328125"/>
+    <col min="13" max="13" customWidth="true" style="41" width="14.08984375"/>
+    <col min="14" max="14" customWidth="true" style="41" width="14.36328125"/>
+    <col min="15" max="16384" style="41" width="8.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -10121,11 +10131,11 @@
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="39.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="39.453125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="13.54296875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="7.81640625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="9.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -10193,10 +10203,10 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="57.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="57.453125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="15.54296875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="7.81640625"/>
+    <col min="4" max="5" bestFit="true" customWidth="true" width="11.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -10315,28 +10325,28 @@
   <dimension ref="A1:V15"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="50" style="25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.36328125" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.08984375" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.36328125" style="25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.1796875" style="25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.453125" style="25" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="8.81640625" style="25"/>
-    <col min="9" max="9" width="10.453125" style="25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.6328125" style="25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.453125" style="25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.1796875" style="25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.453125" style="25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.1796875" style="25" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13" style="25" customWidth="1"/>
-    <col min="16" max="16" width="10.1796875" style="25" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.453125" style="25" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.1796875" style="25" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.6328125" style="25" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.6328125" style="25" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.1796875" style="25" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.6328125" style="25" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="8.81640625" style="25"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="25" width="50.0"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="25" width="18.36328125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="25" width="12.08984375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="25" width="15.36328125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="25" width="12.1796875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="25" width="9.453125"/>
+    <col min="7" max="8" style="25" width="8.81640625"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="25" width="10.453125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="25" width="12.6328125"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="25" width="10.453125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="25" width="11.1796875"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="25" width="10.453125"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="25" width="8.1796875"/>
+    <col min="15" max="15" customWidth="true" style="25" width="13.0"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="25" width="10.1796875"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="25" width="10.453125"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="25" width="9.1796875"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="25" width="11.6328125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="25" width="12.6328125"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="25" width="11.1796875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="25" width="12.6328125"/>
+    <col min="23" max="16384" style="25" width="8.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
@@ -11031,29 +11041,29 @@
   <dimension ref="A1:AB7"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="44.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="44.81640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.81640625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="8.1796875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="10.453125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="13.54296875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="17.81640625"/>
+    <col min="11" max="12" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="18.1796875"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="7.81640625"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="8.1796875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="14.1796875"/>
+    <col min="27" max="28" bestFit="true" customWidth="true" width="12.81640625"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="14.1796875"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="12.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28">
@@ -11485,9 +11495,9 @@
   <dimension ref="A1:W17"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="54.36328125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="54.36328125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="13.90625"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="13.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -12238,16 +12248,16 @@
   <dimension ref="A1:S20"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="53.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="12.1796875" customWidth="1"/>
-    <col min="8" max="8" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="53.81640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="3" max="4" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="5" max="7" customWidth="true" width="12.1796875"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="12.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19">

--- a/src/test/java/TestData/Scenario_TestData.xlsx
+++ b/src/test/java/TestData/Scenario_TestData.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Copa_SHD_WebServices\src\test\java\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EA7B68D-3AF1-4E55-87EC-F1E7D388C43A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B990BDA6-7B22-41A5-90AE-F6903877BAB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="26" activeTab="28" xr2:uid="{5D5A4724-D560-4FC2-9708-4BBF1DBA0B11}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="10" activeTab="11" xr2:uid="{5D5A4724-D560-4FC2-9708-4BBF1DBA0B11}"/>
   </bookViews>
   <sheets>
     <sheet name="AdvancePassengerInfo" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2082" uniqueCount="623">
   <si>
     <t>Scenario</t>
   </si>
@@ -1126,9 +1126,6 @@
     <t>FLIFO_History_for_codeshare_airline</t>
   </si>
   <si>
-    <t>AVXW41</t>
-  </si>
-  <si>
     <t>AVXXCC</t>
   </si>
   <si>
@@ -1939,20 +1936,19 @@
     <t>AG</t>
   </si>
   <si>
-    <t>A2CS0Z</t>
-  </si>
-  <si>
-    <t>A2CTF1</t>
-  </si>
-  <si>
     <t>A2CTH3</t>
+  </si>
+  <si>
+    <t>230416305</t>
+  </si>
+  <si>
+    <t>AQT2ZF</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="13">
     <font>
       <sz val="11"/>
@@ -2182,7 +2178,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2281,6 +2277,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2601,20 +2598,20 @@
   <dimension ref="A1:P15"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="52.81640625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="18.453125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="9.453125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="10.453125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="11.1796875"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="10.453125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="11.1796875"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="10.453125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="11.1796875"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="15.1796875"/>
+    <col min="1" max="1" width="52.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2687,7 +2684,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="44" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="I2" s="32" t="s">
         <v>211</v>
@@ -2704,7 +2701,7 @@
       <c r="M2" s="32"/>
       <c r="N2" s="32"/>
       <c r="O2" s="32" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="P2" s="38"/>
     </row>
@@ -2755,7 +2752,7 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="37" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B4" s="44">
         <v>0</v>
@@ -2776,13 +2773,13 @@
         <v>1</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I4" s="37" t="s">
+        <v>354</v>
+      </c>
+      <c r="J4" s="37" t="s">
         <v>355</v>
-      </c>
-      <c r="J4" s="37" t="s">
-        <v>356</v>
       </c>
       <c r="K4" s="32"/>
       <c r="L4" s="32"/>
@@ -2792,7 +2789,7 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="37" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B5" s="44">
         <v>0</v>
@@ -2813,7 +2810,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="37" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="I5" s="32"/>
       <c r="J5" s="32"/>
@@ -2849,13 +2846,13 @@
   <dimension ref="A1:U22"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="49.0"/>
-    <col min="10" max="10" style="25" width="8.81640625"/>
-    <col min="12" max="12" customWidth="true" width="15.90625"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="9.81640625"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="13.90625"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="12.6328125"/>
+    <col min="1" max="1" width="49" customWidth="1"/>
+    <col min="10" max="10" width="8.81640625" style="25"/>
+    <col min="12" max="12" width="15.90625" customWidth="1"/>
+    <col min="17" max="17" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
@@ -2953,7 +2950,7 @@
       </c>
       <c r="J2" s="44"/>
       <c r="K2" s="44" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="L2" s="44"/>
       <c r="M2" s="44"/>
@@ -2990,10 +2987,10 @@
         <v>0</v>
       </c>
       <c r="K3" s="44" t="s">
+        <v>484</v>
+      </c>
+      <c r="L3" s="44" t="s">
         <v>485</v>
-      </c>
-      <c r="L3" s="44" t="s">
-        <v>486</v>
       </c>
       <c r="M3" s="44"/>
       <c r="N3" s="44"/>
@@ -3062,10 +3059,10 @@
       <c r="I5" s="44"/>
       <c r="J5" s="44"/>
       <c r="K5" s="44" t="s">
+        <v>487</v>
+      </c>
+      <c r="L5" s="44" t="s">
         <v>488</v>
-      </c>
-      <c r="L5" s="44" t="s">
-        <v>489</v>
       </c>
       <c r="M5" s="44"/>
       <c r="N5" s="44" t="s">
@@ -3109,7 +3106,7 @@
       <c r="I6" s="44"/>
       <c r="J6" s="44"/>
       <c r="K6" s="44" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="L6" s="44"/>
       <c r="M6" s="44"/>
@@ -3120,7 +3117,7 @@
         <v>242</v>
       </c>
       <c r="P6" s="44" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="Q6" s="44"/>
       <c r="R6" s="44"/>
@@ -3154,10 +3151,10 @@
       <c r="I7" s="44"/>
       <c r="J7" s="44"/>
       <c r="K7" s="44" t="s">
+        <v>491</v>
+      </c>
+      <c r="L7" s="44" t="s">
         <v>492</v>
-      </c>
-      <c r="L7" s="44" t="s">
-        <v>493</v>
       </c>
       <c r="M7" s="44"/>
       <c r="N7" s="44" t="s">
@@ -3167,13 +3164,13 @@
         <v>242</v>
       </c>
       <c r="P7" s="44" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="Q7" s="47" t="s">
         <v>87</v>
       </c>
       <c r="R7" s="44" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="S7" s="44"/>
       <c r="T7" s="44"/>
@@ -3209,10 +3206,10 @@
       </c>
       <c r="J8" s="44"/>
       <c r="K8" s="44" t="s">
+        <v>495</v>
+      </c>
+      <c r="L8" s="44" t="s">
         <v>496</v>
-      </c>
-      <c r="L8" s="44" t="s">
-        <v>497</v>
       </c>
       <c r="M8" s="44"/>
       <c r="N8" s="44" t="s">
@@ -3250,7 +3247,7 @@
       <c r="I9" s="44"/>
       <c r="J9" s="44"/>
       <c r="K9" s="44" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="L9" s="44"/>
       <c r="M9" s="44"/>
@@ -3289,10 +3286,10 @@
       <c r="I10" s="44"/>
       <c r="J10" s="44"/>
       <c r="K10" s="44" t="s">
+        <v>498</v>
+      </c>
+      <c r="L10" s="44" t="s">
         <v>499</v>
-      </c>
-      <c r="L10" s="44" t="s">
-        <v>500</v>
       </c>
       <c r="M10" s="44"/>
       <c r="N10" s="44"/>
@@ -3328,10 +3325,10 @@
       <c r="I11" s="44"/>
       <c r="J11" s="44"/>
       <c r="K11" s="44" t="s">
+        <v>471</v>
+      </c>
+      <c r="L11" s="44" t="s">
         <v>472</v>
-      </c>
-      <c r="L11" s="44" t="s">
-        <v>473</v>
       </c>
       <c r="M11" s="44"/>
       <c r="N11" s="44"/>
@@ -3367,10 +3364,10 @@
       <c r="I12" s="44"/>
       <c r="J12" s="44"/>
       <c r="K12" s="44" t="s">
+        <v>473</v>
+      </c>
+      <c r="L12" s="44" t="s">
         <v>474</v>
-      </c>
-      <c r="L12" s="44" t="s">
-        <v>475</v>
       </c>
       <c r="M12" s="44"/>
       <c r="N12" s="44" t="s">
@@ -3410,10 +3407,10 @@
       <c r="I13" s="44"/>
       <c r="J13" s="44"/>
       <c r="K13" s="44" t="s">
+        <v>475</v>
+      </c>
+      <c r="L13" s="44" t="s">
         <v>476</v>
-      </c>
-      <c r="L13" s="44" t="s">
-        <v>477</v>
       </c>
       <c r="M13" s="44"/>
       <c r="N13" s="44" t="s">
@@ -3488,10 +3485,10 @@
       <c r="I15" s="44"/>
       <c r="J15" s="44"/>
       <c r="K15" s="44" t="s">
+        <v>477</v>
+      </c>
+      <c r="L15" s="44" t="s">
         <v>478</v>
-      </c>
-      <c r="L15" s="44" t="s">
-        <v>479</v>
       </c>
       <c r="M15" s="44"/>
       <c r="N15" s="44" t="s">
@@ -3531,7 +3528,7 @@
       <c r="I16" s="44"/>
       <c r="J16" s="44"/>
       <c r="K16" s="44" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="L16" s="44"/>
       <c r="M16" s="44"/>
@@ -3570,7 +3567,7 @@
       <c r="I17" s="44"/>
       <c r="J17" s="44"/>
       <c r="K17" s="44" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="L17" s="44"/>
       <c r="M17" s="44"/>
@@ -3613,7 +3610,7 @@
       </c>
       <c r="J18" s="44"/>
       <c r="K18" s="44" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="L18" s="44"/>
       <c r="M18" s="44"/>
@@ -3652,7 +3649,7 @@
       <c r="I19" s="44"/>
       <c r="J19" s="44"/>
       <c r="K19" s="44" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="L19" s="44"/>
       <c r="M19" s="44"/>
@@ -3691,7 +3688,7 @@
       <c r="I20" s="44"/>
       <c r="J20" s="44"/>
       <c r="K20" s="44" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="L20" s="44"/>
       <c r="M20" s="44"/>
@@ -3730,7 +3727,7 @@
       <c r="I21" s="44"/>
       <c r="J21" s="44"/>
       <c r="K21" s="44" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="L21" s="44"/>
       <c r="M21" s="44"/>
@@ -3755,7 +3752,7 @@
         <v>1</v>
       </c>
       <c r="C22" s="47" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D22" s="44" t="s">
         <v>34</v>
@@ -3777,7 +3774,7 @@
       </c>
       <c r="J22" s="44"/>
       <c r="K22" s="44" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="L22" s="44"/>
       <c r="M22" s="44"/>
@@ -3807,16 +3804,16 @@
   <dimension ref="A1:N4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="32.90625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="3" max="3" customWidth="true" style="29" width="17.54296875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="5" max="5" customWidth="true" width="13.81640625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="14.36328125"/>
-    <col min="7" max="11" customWidth="true" style="29" width="14.36328125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="30.36328125"/>
-    <col min="13" max="13" customWidth="true" width="8.453125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="10.90625"/>
+    <col min="1" max="1" width="32.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.54296875" style="29" customWidth="1"/>
+    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.81640625" customWidth="1"/>
+    <col min="6" max="6" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="14.36328125" style="29" customWidth="1"/>
+    <col min="12" max="12" width="30.36328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.453125" customWidth="1"/>
+    <col min="14" max="14" width="10.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -3871,7 +3868,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="47" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D2" s="35" t="s">
         <v>12</v>
@@ -3898,10 +3895,10 @@
         <v>1</v>
       </c>
       <c r="L2" s="34" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="M2" s="34" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="N2" s="32"/>
     </row>
@@ -3940,7 +3937,7 @@
         <v>6</v>
       </c>
       <c r="L3" s="34" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="M3" s="34" t="s">
         <v>264</v>
@@ -3984,7 +3981,7 @@
         <v>6</v>
       </c>
       <c r="L4" s="34" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="M4" s="32"/>
       <c r="N4" s="32" t="s">
@@ -4004,17 +4001,17 @@
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="29" width="21.81640625"/>
-    <col min="2" max="2" customWidth="true" style="29" width="16.54296875"/>
-    <col min="3" max="3" customWidth="true" style="29" width="19.90625"/>
-    <col min="4" max="4" customWidth="true" style="29" width="18.81640625"/>
-    <col min="5" max="6" customWidth="true" style="29" width="12.90625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="15.0"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="11.90625"/>
-    <col min="9" max="9" style="29" width="8.81640625"/>
-    <col min="10" max="10" customWidth="true" style="29" width="17.90625"/>
-    <col min="11" max="11" customWidth="true" style="29" width="14.1796875"/>
-    <col min="12" max="16384" style="29" width="8.81640625"/>
+    <col min="1" max="1" width="21.81640625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="16.54296875" style="29" customWidth="1"/>
+    <col min="3" max="3" width="19.90625" style="29" customWidth="1"/>
+    <col min="4" max="4" width="18.81640625" style="29" customWidth="1"/>
+    <col min="5" max="6" width="12.90625" style="29" customWidth="1"/>
+    <col min="7" max="7" width="15" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.90625" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.81640625" style="29"/>
+    <col min="10" max="10" width="17.90625" style="29" customWidth="1"/>
+    <col min="11" max="11" width="14.1796875" style="29" customWidth="1"/>
+    <col min="12" max="16384" width="8.81640625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -4065,7 +4062,9 @@
       <c r="F2" s="44"/>
       <c r="G2" s="44"/>
       <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
+      <c r="I2" s="44" t="s">
+        <v>622</v>
+      </c>
       <c r="J2" s="44"/>
       <c r="K2" s="44"/>
     </row>
@@ -4082,7 +4081,9 @@
       <c r="F3" s="44"/>
       <c r="G3" s="44"/>
       <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
+      <c r="I3" s="44" t="s">
+        <v>622</v>
+      </c>
       <c r="J3" s="44"/>
       <c r="K3" s="44"/>
     </row>
@@ -4099,7 +4100,9 @@
       <c r="F4" s="44"/>
       <c r="G4" s="44"/>
       <c r="H4" s="44"/>
-      <c r="I4" s="44"/>
+      <c r="I4" s="44" t="s">
+        <v>622</v>
+      </c>
       <c r="J4" s="44"/>
       <c r="K4" s="44"/>
     </row>
@@ -4129,13 +4132,13 @@
         <v>12</v>
       </c>
       <c r="I5" s="44" t="s">
+        <v>500</v>
+      </c>
+      <c r="J5" s="44" t="s">
         <v>501</v>
       </c>
-      <c r="J5" s="44" t="s">
+      <c r="K5" s="44" t="s">
         <v>502</v>
-      </c>
-      <c r="K5" s="44" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -4164,10 +4167,10 @@
         <v>12</v>
       </c>
       <c r="I6" s="44" t="s">
+        <v>503</v>
+      </c>
+      <c r="J6" s="44" t="s">
         <v>504</v>
-      </c>
-      <c r="J6" s="44" t="s">
-        <v>505</v>
       </c>
       <c r="K6" s="44"/>
     </row>
@@ -4184,12 +4187,12 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="29" width="42.1796875"/>
-    <col min="2" max="2" customWidth="true" style="29" width="15.81640625"/>
-    <col min="3" max="3" customWidth="true" style="29" width="17.81640625"/>
-    <col min="4" max="4" customWidth="true" style="29" width="16.81640625"/>
-    <col min="5" max="5" customWidth="true" style="29" width="15.6328125"/>
-    <col min="6" max="16384" style="29" width="8.81640625"/>
+    <col min="1" max="1" width="42.1796875" style="29" customWidth="1"/>
+    <col min="2" max="2" width="15.81640625" style="29" customWidth="1"/>
+    <col min="3" max="3" width="17.81640625" style="29" customWidth="1"/>
+    <col min="4" max="4" width="16.81640625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="15.6328125" style="29" customWidth="1"/>
+    <col min="6" max="16384" width="8.81640625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4235,7 +4238,7 @@
         <v>149</v>
       </c>
       <c r="D3" s="44" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E3" s="44">
         <v>1</v>
@@ -4252,7 +4255,7 @@
         <v>149</v>
       </c>
       <c r="D4" s="44" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E4" s="44">
         <v>1</v>
@@ -4308,28 +4311,28 @@
   <dimension ref="A1:AB6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="51.81640625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="9.453125"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="18.453125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="14.453125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="18.453125"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="18.453125"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="12.08984375"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="15.36328125"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="12.08984375"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" width="15.36328125"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="1" max="1" width="51.81640625" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28">
@@ -4447,16 +4450,16 @@
         <v>45</v>
       </c>
       <c r="J2" s="44" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="K2" s="44" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="L2" s="44" t="s">
         <v>207</v>
       </c>
       <c r="M2" s="44" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="N2" s="44" t="s">
         <v>208</v>
@@ -4465,13 +4468,13 @@
         <v>12</v>
       </c>
       <c r="P2" s="44" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="Q2" s="44" t="s">
         <v>62</v>
       </c>
       <c r="R2" s="44" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="S2" s="44" t="s">
         <v>12</v>
@@ -4517,16 +4520,16 @@
         <v>45</v>
       </c>
       <c r="J3" s="44" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="L3" s="44" t="s">
         <v>207</v>
       </c>
       <c r="M3" s="44" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="N3" s="44" t="s">
         <v>208</v>
@@ -4535,13 +4538,13 @@
         <v>12</v>
       </c>
       <c r="P3" s="44" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="Q3" s="44" t="s">
         <v>239</v>
       </c>
       <c r="R3" s="44" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="S3" s="44" t="s">
         <v>12</v>
@@ -4595,16 +4598,16 @@
       <c r="H4" s="44"/>
       <c r="I4" s="44"/>
       <c r="J4" s="44" t="s">
+        <v>513</v>
+      </c>
+      <c r="K4" s="44" t="s">
         <v>514</v>
-      </c>
-      <c r="K4" s="44" t="s">
-        <v>515</v>
       </c>
       <c r="L4" s="44" t="s">
         <v>328</v>
       </c>
       <c r="M4" s="44" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="N4" s="44" t="s">
         <v>209</v>
@@ -4647,16 +4650,16 @@
       <c r="H5" s="44"/>
       <c r="I5" s="44"/>
       <c r="J5" s="44" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="L5" s="44" t="s">
         <v>328</v>
       </c>
       <c r="M5" s="44" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="N5" s="44" t="s">
         <v>209</v>
@@ -4707,16 +4710,16 @@
         <v>45</v>
       </c>
       <c r="J6" s="44" t="s">
+        <v>510</v>
+      </c>
+      <c r="K6" s="44" t="s">
         <v>511</v>
-      </c>
-      <c r="K6" s="44" t="s">
-        <v>512</v>
       </c>
       <c r="L6" s="44" t="s">
         <v>207</v>
       </c>
       <c r="M6" s="44" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="N6" s="44" t="s">
         <v>208</v>
@@ -4752,10 +4755,10 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="76.1796875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="13.453125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="1" max="1" width="76.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4840,12 +4843,12 @@
   <dimension ref="A1:E15"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="68.08984375"/>
-    <col min="2" max="2" customWidth="true" style="29" width="12.54296875"/>
-    <col min="3" max="3" customWidth="true" style="29" width="14.81640625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="29" width="11.81640625"/>
-    <col min="5" max="5" customWidth="true" style="29" width="18.1796875"/>
-    <col min="6" max="16384" style="29" width="8.81640625"/>
+    <col min="1" max="1" width="68.08984375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.54296875" style="29" customWidth="1"/>
+    <col min="3" max="3" width="14.81640625" style="29" customWidth="1"/>
+    <col min="4" max="4" width="11.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.1796875" style="29" customWidth="1"/>
+    <col min="6" max="16384" width="8.81640625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4981,7 +4984,7 @@
         <v>282</v>
       </c>
       <c r="D9" s="44" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E9" s="44"/>
     </row>
@@ -5092,8 +5095,8 @@
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="12.54296875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="1" max="1" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -5133,11 +5136,11 @@
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="33.54296875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="13.453125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="1" max="1" width="33.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -5187,7 +5190,7 @@
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="21.81640625"/>
+    <col min="1" max="1" width="21.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -5292,31 +5295,31 @@
   <dimension ref="A1:AG4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="49.81640625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="4.81640625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="9.81640625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="4.453125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="9.81640625"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="4.453125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="9.81640625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="4.453125"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="9.81640625"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="4.453125"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="9.81640625"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="4.453125"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="9.81640625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="4.453125"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="9.81640625"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="4.453125"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" width="9.7265625"/>
+    <col min="1" max="1" width="49.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="9.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33">
@@ -5500,7 +5503,7 @@
         <v>0</v>
       </c>
       <c r="AA2" s="44" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AB2" s="44" t="s">
         <v>45</v>
@@ -5512,7 +5515,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="44" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AF2" s="44" t="s">
         <v>45</v>
@@ -5621,25 +5624,25 @@
   <dimension ref="A1:AD9"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="33.0"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="18.36328125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="12.08984375"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="18.36328125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="15.36328125"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="13.90625"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="12.08984375"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="15.36328125"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="14.36328125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="12.08984375"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="15.36328125"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" width="12.08984375"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="1" max="1" width="33" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30">
@@ -5758,16 +5761,16 @@
       <c r="I2" s="44"/>
       <c r="J2" s="44"/>
       <c r="K2" s="44" t="s">
+        <v>517</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>518</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>519</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>325</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>209</v>
@@ -5822,7 +5825,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>312</v>
@@ -5962,16 +5965,16 @@
         <v>2</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>325</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>209</v>
@@ -5980,7 +5983,7 @@
         <v>12</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="R5" s="15" t="s">
         <v>44</v>
@@ -6178,16 +6181,16 @@
       <c r="I9" s="44"/>
       <c r="J9" s="44"/>
       <c r="K9" s="44" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>325</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>209</v>
@@ -6223,11 +6226,11 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="35.1796875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="11.54296875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="13.453125"/>
+    <col min="1" max="1" width="35.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -6252,10 +6255,10 @@
         <v>127</v>
       </c>
       <c r="B2" s="44" t="s">
+        <v>448</v>
+      </c>
+      <c r="C2" s="44" t="s">
         <v>449</v>
-      </c>
-      <c r="C2" s="44" t="s">
-        <v>450</v>
       </c>
       <c r="D2" s="44" t="s">
         <v>128</v>
@@ -6311,9 +6314,9 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="33.54296875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="13.453125"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="9.90625"/>
+    <col min="1" max="1" width="33.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -6369,9 +6372,9 @@
   <dimension ref="A1:AC4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="46.6328125"/>
-    <col min="5" max="5" customWidth="true" width="6.1796875"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="13.90625"/>
+    <col min="1" max="1" width="46.6328125" customWidth="1"/>
+    <col min="5" max="5" width="6.1796875" customWidth="1"/>
+    <col min="29" max="29" width="13.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -6499,16 +6502,16 @@
       <c r="U2" s="44"/>
       <c r="V2" s="44"/>
       <c r="W2" s="44" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="X2" s="44" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="Y2" s="44" t="s">
         <v>325</v>
       </c>
       <c r="Z2" s="44" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AA2" s="44" t="s">
         <v>209</v>
@@ -6517,7 +6520,7 @@
         <v>12</v>
       </c>
       <c r="AC2" s="44" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -6635,16 +6638,16 @@
       <c r="U4" s="44"/>
       <c r="V4" s="44"/>
       <c r="W4" s="44" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="X4" s="44" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="Y4" s="44" t="s">
         <v>325</v>
       </c>
       <c r="Z4" s="44" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AA4" s="44" t="s">
         <v>209</v>
@@ -6653,7 +6656,7 @@
         <v>12</v>
       </c>
       <c r="AC4" s="44" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
   </sheetData>
@@ -6669,14 +6672,14 @@
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="63.81640625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="10.81640625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="19.453125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="15.54296875"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="8" max="9" bestFit="true" customWidth="true" width="19.453125"/>
+    <col min="1" max="1" width="63.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="19.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -6811,24 +6814,24 @@
   <dimension ref="A1:R6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="12.0"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="9.453125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="6.1796875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="13.81640625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="7.453125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="18.453125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="18.453125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="17" max="17" customWidth="true" width="17.6328125"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="13.90625"/>
+    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.6328125" customWidth="1"/>
+    <col min="18" max="18" width="13.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -6911,16 +6914,16 @@
       <c r="I2" s="44"/>
       <c r="J2" s="44"/>
       <c r="K2" s="44" t="s">
+        <v>530</v>
+      </c>
+      <c r="L2" s="44" t="s">
         <v>531</v>
-      </c>
-      <c r="L2" s="44" t="s">
-        <v>532</v>
       </c>
       <c r="M2" s="44" t="s">
         <v>329</v>
       </c>
       <c r="N2" s="44" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>209</v>
@@ -6929,7 +6932,7 @@
         <v>12</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="R2" s="3"/>
     </row>
@@ -6957,16 +6960,16 @@
       <c r="I3" s="44"/>
       <c r="J3" s="44"/>
       <c r="K3" s="44" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="L3" s="44" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="M3" s="44" t="s">
         <v>325</v>
       </c>
       <c r="N3" s="44" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="O3" s="3" t="s">
         <v>209</v>
@@ -6975,10 +6978,10 @@
         <v>12</v>
       </c>
       <c r="Q3" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="R3" s="3" t="s">
         <v>564</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -7005,16 +7008,16 @@
       <c r="I4" s="44"/>
       <c r="J4" s="44"/>
       <c r="K4" s="44" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="L4" s="44" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="M4" s="44" t="s">
         <v>207</v>
       </c>
       <c r="N4" s="44" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>208</v>
@@ -7023,7 +7026,7 @@
         <v>12</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="R4" s="3"/>
     </row>
@@ -7051,16 +7054,16 @@
       <c r="I5" s="44"/>
       <c r="J5" s="44"/>
       <c r="K5" s="44" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="M5" s="44" t="s">
         <v>207</v>
       </c>
       <c r="N5" s="44" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>208</v>
@@ -7069,7 +7072,7 @@
         <v>12</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="R5" s="3"/>
     </row>
@@ -7097,16 +7100,16 @@
       <c r="I6" s="44"/>
       <c r="J6" s="44"/>
       <c r="K6" s="44" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="L6" s="44" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="M6" s="44" t="s">
         <v>207</v>
       </c>
       <c r="N6" s="44" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="O6" s="3" t="s">
         <v>208</v>
@@ -7115,7 +7118,7 @@
         <v>12</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="R6" s="3"/>
     </row>
@@ -7133,27 +7136,27 @@
   <dimension ref="A1:U13"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="44.08984375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.36328125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="11.90625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="9.1796875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="6.1796875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="17.36328125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="11.90625"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="9.1796875"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="6.1796875"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="8.54296875"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="18.6328125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="11.90625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="18.6328125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="11.90625"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="18.6328125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="11.90625"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="18.6328125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="11.90625"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="14.08984375"/>
+    <col min="1" max="1" width="44.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.6328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.6328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.6328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.6328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
@@ -7250,16 +7253,16 @@
         <v>163</v>
       </c>
       <c r="J2" s="56" t="s">
+        <v>534</v>
+      </c>
+      <c r="K2" s="44" t="s">
         <v>535</v>
-      </c>
-      <c r="K2" s="44" t="s">
-        <v>536</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>215</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>12</v>
@@ -7268,13 +7271,13 @@
         <v>216</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>217</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="S2" s="3" t="s">
         <v>216</v>
@@ -7283,7 +7286,7 @@
         <v>163</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="3" spans="1:21">
@@ -7315,16 +7318,16 @@
         <v>163</v>
       </c>
       <c r="J3" s="56" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>215</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>12</v>
@@ -7333,13 +7336,13 @@
         <v>216</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>341</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="S3" s="3" t="s">
         <v>216</v>
@@ -7348,7 +7351,7 @@
         <v>163</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="4" spans="1:21">
@@ -7528,8 +7531,8 @@
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="32.1796875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="1" max="1" width="32.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -7552,8 +7555,8 @@
       <c r="A3" s="44" t="s">
         <v>181</v>
       </c>
-      <c r="B3" s="41" t="s">
-        <v>87</v>
+      <c r="B3" s="64" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -7577,7 +7580,7 @@
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="18.0"/>
+    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -7638,21 +7641,21 @@
   <dimension ref="A1:N19"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="29" width="24.90625"/>
-    <col min="2" max="2" customWidth="true" style="29" width="14.0"/>
-    <col min="3" max="3" customWidth="true" style="29" width="11.81640625"/>
-    <col min="4" max="4" customWidth="true" style="29" width="9.54296875"/>
-    <col min="5" max="5" customWidth="true" style="29" width="10.36328125"/>
-    <col min="6" max="6" customWidth="true" style="29" width="9.36328125"/>
-    <col min="7" max="7" customWidth="true" style="29" width="9.7265625"/>
-    <col min="8" max="8" customWidth="true" style="29" width="10.453125"/>
-    <col min="9" max="9" customWidth="true" style="29" width="8.81640625"/>
-    <col min="10" max="10" customWidth="true" style="41" width="8.08984375"/>
-    <col min="11" max="11" customWidth="true" style="29" width="10.0"/>
-    <col min="12" max="12" customWidth="true" style="29" width="7.81640625"/>
-    <col min="13" max="13" customWidth="true" style="29" width="9.0"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="19.453125"/>
-    <col min="15" max="16384" style="29" width="8.81640625"/>
+    <col min="1" max="1" width="24.90625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="14" style="29" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" style="29" customWidth="1"/>
+    <col min="4" max="4" width="9.54296875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10.36328125" style="29" customWidth="1"/>
+    <col min="6" max="6" width="9.36328125" style="29" customWidth="1"/>
+    <col min="7" max="7" width="9.7265625" style="29" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" style="29" customWidth="1"/>
+    <col min="9" max="9" width="8.81640625" style="29" customWidth="1"/>
+    <col min="10" max="10" width="8.08984375" style="41" customWidth="1"/>
+    <col min="11" max="11" width="10" style="29" customWidth="1"/>
+    <col min="12" max="12" width="7.81640625" style="29" customWidth="1"/>
+    <col min="13" max="13" width="9" style="29" customWidth="1"/>
+    <col min="14" max="14" width="19.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.81640625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -7663,40 +7666,40 @@
         <v>266</v>
       </c>
       <c r="C1" s="42" t="s">
+        <v>582</v>
+      </c>
+      <c r="D1" s="42" t="s">
         <v>583</v>
       </c>
-      <c r="D1" s="42" t="s">
+      <c r="E1" s="42" t="s">
         <v>584</v>
       </c>
-      <c r="E1" s="42" t="s">
+      <c r="F1" s="42" t="s">
         <v>585</v>
       </c>
-      <c r="F1" s="42" t="s">
+      <c r="G1" s="63" t="s">
         <v>586</v>
       </c>
-      <c r="G1" s="63" t="s">
+      <c r="H1" s="63" t="s">
         <v>587</v>
       </c>
-      <c r="H1" s="63" t="s">
-        <v>588</v>
-      </c>
       <c r="I1" s="63" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="J1" s="63" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="K1" s="42" t="s">
+        <v>584</v>
+      </c>
+      <c r="L1" s="42" t="s">
         <v>585</v>
       </c>
-      <c r="L1" s="42" t="s">
-        <v>586</v>
-      </c>
       <c r="M1" s="42" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="N1" s="42" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -7707,40 +7710,40 @@
         <v>149</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D2" s="32" t="s">
         <v>121</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="F2" s="44" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G2" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H2" s="44" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="I2" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="J2" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="K2" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="L2" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="M2" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="N2" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -7751,40 +7754,40 @@
         <v>149</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D3" s="32" t="s">
         <v>121</v>
       </c>
       <c r="E3" s="32" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="F3" s="44" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G3" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H3" s="44" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="I3" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="J3" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="L3" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="M3" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="N3" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -7795,40 +7798,40 @@
         <v>149</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D4" s="32" t="s">
         <v>121</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="F4" s="44" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G4" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H4" s="44" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="I4" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="J4" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="K4" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="L4" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="M4" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="N4" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -7839,40 +7842,40 @@
         <v>149</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D5" s="32" t="s">
         <v>121</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="F5" s="44" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="G5" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H5" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="I5" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="J5" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="M5" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="N5" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -7883,40 +7886,40 @@
         <v>149</v>
       </c>
       <c r="C6" s="44" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D6" s="44" t="s">
         <v>121</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="F6" s="44" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="G6" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H6" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="I6" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="J6" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="K6" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="L6" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="M6" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="N6" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -7927,40 +7930,40 @@
         <v>149</v>
       </c>
       <c r="C7" s="44" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D7" s="44" t="s">
         <v>121</v>
       </c>
       <c r="E7" s="44" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="F7" s="44" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="G7" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H7" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="I7" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="J7" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="K7" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="L7" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="M7" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="N7" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -7971,40 +7974,40 @@
         <v>149</v>
       </c>
       <c r="C8" s="44" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D8" s="44" t="s">
         <v>121</v>
       </c>
       <c r="E8" s="44" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="F8" s="44" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="G8" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H8" s="44" t="s">
+        <v>599</v>
+      </c>
+      <c r="I8" s="44" t="s">
         <v>600</v>
       </c>
-      <c r="I8" s="44" t="s">
-        <v>601</v>
-      </c>
       <c r="J8" s="44" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="K8" s="44" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="L8" s="44" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="M8" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="N8" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -8015,40 +8018,40 @@
         <v>149</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D9" s="32" t="s">
         <v>121</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F9" s="44" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G9" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H9" s="44" t="s">
+        <v>605</v>
+      </c>
+      <c r="I9" s="44" t="s">
         <v>606</v>
       </c>
-      <c r="I9" s="44" t="s">
+      <c r="J9" s="44" t="s">
         <v>607</v>
       </c>
-      <c r="J9" s="44" t="s">
-        <v>608</v>
-      </c>
       <c r="K9" s="44" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L9" s="44" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="M9" s="44" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="N9" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -8059,40 +8062,40 @@
         <v>149</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D10" s="44" t="s">
         <v>121</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F10" s="44" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="G10" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H10" s="44" t="s">
+        <v>612</v>
+      </c>
+      <c r="I10" s="44" t="s">
         <v>613</v>
       </c>
-      <c r="I10" s="44" t="s">
+      <c r="J10" s="44" t="s">
         <v>614</v>
       </c>
-      <c r="J10" s="44" t="s">
-        <v>615</v>
-      </c>
       <c r="K10" s="44" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="L10" s="44" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="M10" s="44" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="N10" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -8103,40 +8106,40 @@
         <v>149</v>
       </c>
       <c r="C11" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D11" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F11" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G11" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H11" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="I11" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="J11" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="K11" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="L11" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="M11" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="N11" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -8147,40 +8150,40 @@
         <v>149</v>
       </c>
       <c r="C12" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D12" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F12" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G12" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H12" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="I12" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="J12" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="K12" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="L12" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="M12" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="N12" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -8191,40 +8194,40 @@
         <v>149</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F13" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G13" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H13" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="I13" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="J13" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="K13" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="L13" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="M13" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="N13" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -8235,40 +8238,40 @@
         <v>149</v>
       </c>
       <c r="C14" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F14" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G14" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H14" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="I14" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="J14" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="K14" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="L14" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="M14" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="N14" s="44" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -8279,40 +8282,40 @@
         <v>149</v>
       </c>
       <c r="C15" s="44" t="s">
+        <v>616</v>
+      </c>
+      <c r="D15" s="44" t="s">
+        <v>602</v>
+      </c>
+      <c r="E15" s="44" t="s">
+        <v>602</v>
+      </c>
+      <c r="F15" s="44" t="s">
+        <v>602</v>
+      </c>
+      <c r="G15" s="44" t="s">
         <v>617</v>
       </c>
-      <c r="D15" s="44" t="s">
-        <v>603</v>
-      </c>
-      <c r="E15" s="44" t="s">
-        <v>603</v>
-      </c>
-      <c r="F15" s="44" t="s">
-        <v>603</v>
-      </c>
-      <c r="G15" s="44" t="s">
-        <v>618</v>
-      </c>
       <c r="H15" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="I15" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="J15" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="K15" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="L15" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="M15" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="N15" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -8320,43 +8323,43 @@
         <v>303</v>
       </c>
       <c r="B16" s="32" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D16" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F16" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G16" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H16" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="I16" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="J16" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="K16" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="L16" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="M16" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="N16" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -8367,45 +8370,45 @@
         <v>149</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D17" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F17" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G17" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H17" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="I17" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="J17" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="K17" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="L17" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="M17" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="N17" s="44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="62" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
   </sheetData>
@@ -8422,14 +8425,14 @@
   <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="39.453125"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="21.81640625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="9.453125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="6.453125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="18.453125"/>
+    <col min="1" max="1" width="39.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -8484,10 +8487,10 @@
         <v>50</v>
       </c>
       <c r="H2" s="44" t="s">
+        <v>460</v>
+      </c>
+      <c r="I2" s="44" t="s">
         <v>461</v>
-      </c>
-      <c r="I2" s="44" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -8513,10 +8516,10 @@
         <v>50</v>
       </c>
       <c r="H3" s="44" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="I3" s="44" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>
@@ -8533,18 +8536,18 @@
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="32.1796875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="4" max="4" customWidth="true" width="15.453125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="17.36328125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="11.90625"/>
-    <col min="13" max="13" customWidth="true" width="15.08984375"/>
+    <col min="1" max="1" width="32.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.453125" customWidth="1"/>
+    <col min="5" max="5" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -8701,7 +8704,7 @@
         <v>346</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C6" s="35" t="s">
         <v>12</v>
@@ -8717,7 +8720,7 @@
       <c r="H6" s="44"/>
       <c r="I6" s="44"/>
       <c r="J6" s="44" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="K6" s="44"/>
       <c r="L6" s="44"/>
@@ -8736,16 +8739,16 @@
   <dimension ref="A1:K4"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="29" width="17.90625"/>
-    <col min="2" max="2" customWidth="true" style="29" width="11.81640625"/>
-    <col min="3" max="3" customWidth="true" style="29" width="13.0"/>
-    <col min="4" max="4" customWidth="true" style="29" width="16.54296875"/>
-    <col min="5" max="5" customWidth="true" style="29" width="15.81640625"/>
-    <col min="6" max="6" style="29" width="8.81640625"/>
-    <col min="7" max="7" customWidth="true" style="29" width="17.81640625"/>
-    <col min="8" max="8" customWidth="true" style="29" width="15.453125"/>
-    <col min="9" max="9" customWidth="true" style="29" width="11.54296875"/>
-    <col min="10" max="16384" style="29" width="8.81640625"/>
+    <col min="1" max="1" width="17.90625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="11.81640625" style="29" customWidth="1"/>
+    <col min="3" max="3" width="13" style="29" customWidth="1"/>
+    <col min="4" max="4" width="16.54296875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="15.81640625" style="29" customWidth="1"/>
+    <col min="6" max="6" width="8.81640625" style="29"/>
+    <col min="7" max="7" width="17.81640625" style="29" customWidth="1"/>
+    <col min="8" max="8" width="15.453125" style="29" customWidth="1"/>
+    <col min="9" max="9" width="11.54296875" style="29" customWidth="1"/>
+    <col min="10" max="16384" width="8.81640625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -8800,7 +8803,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="G2" s="32">
         <v>2</v>
@@ -8831,7 +8834,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G3" s="32"/>
       <c r="H3" s="32"/>
@@ -8860,7 +8863,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G4" s="32"/>
       <c r="H4" s="32"/>
@@ -8881,19 +8884,19 @@
   <dimension ref="A1:M3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="19.90625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="11.90625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="11.90625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="17.36328125"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="11.90625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="11.90625"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="17.36328125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="4.453125"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="17.36328125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="11.90625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="14.1796875"/>
+    <col min="1" max="1" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -8939,7 +8942,7 @@
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="44" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B2" s="47" t="s">
         <v>32</v>
@@ -8962,7 +8965,7 @@
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="44" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B3" s="47" t="s">
         <v>325</v>
@@ -8996,20 +8999,20 @@
   <dimension ref="A1:M4"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="41" width="25.81640625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="41" width="11.90625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="41" width="15.0"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="41" width="11.90625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="41" width="11.90625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="41" width="15.0"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="41" width="11.90625"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="41" width="4.453125"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="41" width="11.90625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="41" width="14.1796875"/>
-    <col min="14" max="16384" style="41" width="8.90625"/>
+    <col min="1" max="1" width="25.81640625" style="41" customWidth="1"/>
+    <col min="2" max="2" width="11.90625" style="41" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="41" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.90625" style="41" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.90625" style="41" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15" style="41" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.90625" style="41" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.453125" style="41" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.90625" style="41" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.1796875" style="41" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.90625" style="41"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -9055,10 +9058,10 @@
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="44" t="s">
+        <v>397</v>
+      </c>
+      <c r="B2" s="47" t="s">
         <v>398</v>
-      </c>
-      <c r="B2" s="47" t="s">
-        <v>399</v>
       </c>
       <c r="C2" s="44" t="s">
         <v>12</v>
@@ -9078,10 +9081,10 @@
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="48" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B3" s="47" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C3" s="44" t="s">
         <v>12</v>
@@ -9101,7 +9104,7 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="44" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B4" s="47" t="s">
         <v>336</v>
@@ -9135,21 +9138,21 @@
   <dimension ref="A1:O5"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="41" width="20.1796875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="41" width="11.90625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="41" width="15.0"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="41" width="11.90625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
-    <col min="6" max="7" customWidth="true" style="41" width="17.36328125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="41" width="11.90625"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="41" width="15.0"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="41" width="11.90625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="41" width="4.453125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="41" width="11.90625"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" style="41" width="14.1796875"/>
-    <col min="16" max="16384" style="41" width="8.90625"/>
+    <col min="1" max="1" width="20.1796875" style="41" customWidth="1"/>
+    <col min="2" max="2" width="11.90625" style="41" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="41" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.90625" style="41" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="17.36328125" style="41" customWidth="1"/>
+    <col min="8" max="8" width="11.90625" style="41" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15" style="41" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.90625" style="41" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.453125" style="41" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.90625" style="41" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.1796875" style="41" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.90625" style="41"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -9169,7 +9172,7 @@
         <v>1</v>
       </c>
       <c r="F1" s="42" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G1" s="42" t="s">
         <v>30</v>
@@ -9201,7 +9204,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="44" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B2" s="47" t="s">
         <v>332</v>
@@ -9216,10 +9219,10 @@
         <v>2</v>
       </c>
       <c r="F2" s="44" t="s">
+        <v>403</v>
+      </c>
+      <c r="G2" s="44" t="s">
         <v>404</v>
-      </c>
-      <c r="G2" s="44" t="s">
-        <v>405</v>
       </c>
       <c r="H2" s="44"/>
       <c r="I2" s="44"/>
@@ -9232,7 +9235,7 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="44" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B3" s="47" t="s">
         <v>332</v>
@@ -9247,10 +9250,10 @@
         <v>2</v>
       </c>
       <c r="F3" s="44" t="s">
+        <v>403</v>
+      </c>
+      <c r="G3" s="44" t="s">
         <v>404</v>
-      </c>
-      <c r="G3" s="44" t="s">
-        <v>405</v>
       </c>
       <c r="H3" s="44"/>
       <c r="I3" s="44"/>
@@ -9263,7 +9266,7 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="44" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B4" s="47" t="s">
         <v>332</v>
@@ -9278,10 +9281,10 @@
         <v>2</v>
       </c>
       <c r="F4" s="44" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G4" s="44" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H4" s="44"/>
       <c r="I4" s="44"/>
@@ -9294,7 +9297,7 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="44" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B5" s="47" t="s">
         <v>332</v>
@@ -9309,10 +9312,10 @@
         <v>2</v>
       </c>
       <c r="F5" s="44" t="s">
+        <v>403</v>
+      </c>
+      <c r="G5" s="44" t="s">
         <v>404</v>
-      </c>
-      <c r="G5" s="44" t="s">
-        <v>405</v>
       </c>
       <c r="H5" s="44"/>
       <c r="I5" s="44"/>
@@ -9336,22 +9339,22 @@
   <dimension ref="A1:O10"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="41" width="28.36328125"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="41" width="11.90625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="41" width="15.0"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="41" width="11.90625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="41" width="16.81640625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="41" width="11.08984375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="41" width="11.90625"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="41" width="15.0"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="41" width="11.90625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
-    <col min="12" max="12" customWidth="true" style="41" width="13.08984375"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="41" width="11.90625"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" style="41" width="14.1796875"/>
-    <col min="16" max="16384" style="41" width="8.90625"/>
+    <col min="1" max="1" width="28.36328125" style="41" customWidth="1"/>
+    <col min="2" max="2" width="11.90625" style="41" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="41" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.90625" style="41" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.81640625" style="41" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.08984375" style="41" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.90625" style="41" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15" style="41" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.90625" style="41" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.08984375" style="41" customWidth="1"/>
+    <col min="13" max="13" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.90625" style="41" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.1796875" style="41" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.90625" style="41"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -9371,10 +9374,10 @@
         <v>1</v>
       </c>
       <c r="F1" s="42" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G1" s="42" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1" s="43" t="s">
         <v>74</v>
@@ -9383,23 +9386,23 @@
         <v>8</v>
       </c>
       <c r="J1" s="43" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="K1" s="43" t="s">
         <v>75</v>
       </c>
       <c r="L1" s="43" t="s">
+        <v>357</v>
+      </c>
+      <c r="M1" s="43" t="s">
         <v>358</v>
-      </c>
-      <c r="M1" s="43" t="s">
-        <v>359</v>
       </c>
       <c r="N1" s="40"/>
       <c r="O1" s="46"/>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="44" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B2" s="47" t="s">
         <v>32</v>
@@ -9422,7 +9425,7 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="44" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B3" s="47" t="s">
         <v>32</v>
@@ -9447,10 +9450,10 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="44" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B4" s="47" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C4" s="44" t="s">
         <v>12</v>
@@ -9466,28 +9469,28 @@
       </c>
       <c r="G4" s="44"/>
       <c r="H4" s="44" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="I4" s="44" t="s">
+        <v>390</v>
+      </c>
+      <c r="J4" s="44" t="s">
         <v>391</v>
-      </c>
-      <c r="J4" s="44" t="s">
-        <v>392</v>
       </c>
       <c r="K4" s="44"/>
       <c r="L4" s="44" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="M4" s="44" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="44" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B5" s="47" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C5" s="44" t="s">
         <v>12</v>
@@ -9503,25 +9506,25 @@
       </c>
       <c r="G5" s="44"/>
       <c r="H5" s="44" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="I5" s="44" t="s">
+        <v>390</v>
+      </c>
+      <c r="J5" s="44" t="s">
         <v>391</v>
-      </c>
-      <c r="J5" s="44" t="s">
-        <v>392</v>
       </c>
       <c r="K5" s="44"/>
       <c r="L5" s="44" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="M5" s="44" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="44" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B6" s="47" t="s">
         <v>32</v>
@@ -9544,7 +9547,7 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="44" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B7" s="47" t="s">
         <v>32</v>
@@ -9567,7 +9570,7 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="44" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B8" s="47" t="s">
         <v>32</v>
@@ -9592,7 +9595,7 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="44" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B9" s="47" t="s">
         <v>32</v>
@@ -9617,7 +9620,7 @@
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="44" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B10" s="47" t="s">
         <v>32</v>
@@ -9651,11 +9654,11 @@
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="41" width="24.0"/>
-    <col min="2" max="2" customWidth="true" style="41" width="11.453125"/>
-    <col min="3" max="3" style="41" width="8.90625"/>
-    <col min="4" max="4" customWidth="true" style="41" width="19.6328125"/>
-    <col min="5" max="16384" style="41" width="8.90625"/>
+    <col min="1" max="1" width="24" style="41" customWidth="1"/>
+    <col min="2" max="2" width="11.453125" style="41" customWidth="1"/>
+    <col min="3" max="3" width="8.90625" style="41"/>
+    <col min="4" max="4" width="19.6328125" style="41" customWidth="1"/>
+    <col min="5" max="16384" width="8.90625" style="41"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9674,10 +9677,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="44" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B2" s="47" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C2" s="44" t="s">
         <v>12</v>
@@ -9699,12 +9702,12 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="41" width="32.1796875"/>
-    <col min="2" max="2" customWidth="true" style="41" width="14.0"/>
-    <col min="3" max="3" customWidth="true" style="41" width="16.6328125"/>
-    <col min="4" max="4" customWidth="true" style="41" width="17.6328125"/>
-    <col min="5" max="5" customWidth="true" style="41" width="11.81640625"/>
-    <col min="6" max="16384" style="41" width="8.90625"/>
+    <col min="1" max="1" width="32.1796875" style="41" customWidth="1"/>
+    <col min="2" max="2" width="14" style="41" customWidth="1"/>
+    <col min="3" max="3" width="16.6328125" style="41" customWidth="1"/>
+    <col min="4" max="4" width="17.6328125" style="41" customWidth="1"/>
+    <col min="5" max="5" width="11.81640625" style="41" customWidth="1"/>
+    <col min="6" max="16384" width="8.90625" style="41"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -9726,7 +9729,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="44" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B2" s="47" t="s">
         <v>32</v>
@@ -9743,10 +9746,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="44" t="s">
+        <v>422</v>
+      </c>
+      <c r="B3" s="47" t="s">
         <v>423</v>
-      </c>
-      <c r="B3" s="47" t="s">
-        <v>424</v>
       </c>
       <c r="C3" s="44" t="s">
         <v>12</v>
@@ -9760,10 +9763,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="44" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B4" s="47" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C4" s="44" t="s">
         <v>12</v>
@@ -9788,11 +9791,11 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="41" width="38.1796875"/>
-    <col min="2" max="2" customWidth="true" style="41" width="13.54296875"/>
-    <col min="3" max="3" customWidth="true" style="41" width="15.54296875"/>
-    <col min="4" max="4" customWidth="true" style="41" width="19.0"/>
-    <col min="5" max="16384" style="41" width="8.90625"/>
+    <col min="1" max="1" width="38.1796875" style="41" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" style="41" customWidth="1"/>
+    <col min="3" max="3" width="15.54296875" style="41" customWidth="1"/>
+    <col min="4" max="4" width="19" style="41" customWidth="1"/>
+    <col min="5" max="16384" width="8.90625" style="41"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -9800,30 +9803,30 @@
         <v>0</v>
       </c>
       <c r="B1" s="49" t="s">
+        <v>425</v>
+      </c>
+      <c r="C1" s="49" t="s">
         <v>426</v>
       </c>
-      <c r="C1" s="49" t="s">
+      <c r="D1" s="49" t="s">
         <v>427</v>
       </c>
-      <c r="D1" s="49" t="s">
+      <c r="E1" s="49" t="s">
         <v>428</v>
-      </c>
-      <c r="E1" s="49" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="44" t="s">
+        <v>429</v>
+      </c>
+      <c r="B2" s="47" t="s">
         <v>430</v>
       </c>
-      <c r="B2" s="47" t="s">
+      <c r="C2" s="44" t="s">
         <v>431</v>
       </c>
-      <c r="C2" s="44" t="s">
+      <c r="D2" s="44" t="s">
         <v>432</v>
-      </c>
-      <c r="D2" s="44" t="s">
-        <v>433</v>
       </c>
       <c r="E2" s="44" t="s">
         <v>12</v>
@@ -9831,16 +9834,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="44" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B3" s="47" t="s">
+        <v>430</v>
+      </c>
+      <c r="C3" s="44" t="s">
         <v>431</v>
       </c>
-      <c r="C3" s="44" t="s">
+      <c r="D3" s="44" t="s">
         <v>432</v>
-      </c>
-      <c r="D3" s="44" t="s">
-        <v>433</v>
       </c>
       <c r="E3" s="44" t="s">
         <v>12</v>
@@ -9848,23 +9851,23 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="44" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B4" s="44"/>
       <c r="C4" s="44"/>
       <c r="D4" s="44" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E4" s="44"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="44" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B5" s="44"/>
       <c r="C5" s="44"/>
       <c r="D5" s="44" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E5" s="44" t="s">
         <v>12</v>
@@ -9872,31 +9875,31 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="50" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B6" s="47" t="s">
+        <v>430</v>
+      </c>
+      <c r="C6" s="44" t="s">
         <v>431</v>
       </c>
-      <c r="C6" s="44" t="s">
+      <c r="D6" s="44" t="s">
         <v>432</v>
-      </c>
-      <c r="D6" s="44" t="s">
-        <v>433</v>
       </c>
       <c r="E6" s="44"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="51" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B7" s="47" t="s">
+        <v>430</v>
+      </c>
+      <c r="C7" s="44" t="s">
         <v>431</v>
       </c>
-      <c r="C7" s="44" t="s">
+      <c r="D7" s="44" t="s">
         <v>432</v>
-      </c>
-      <c r="D7" s="44" t="s">
-        <v>433</v>
       </c>
       <c r="E7" s="44" t="s">
         <v>12</v>
@@ -9915,21 +9918,21 @@
   <dimension ref="A1:N5"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="41" width="30.90625"/>
-    <col min="2" max="2" customWidth="true" style="41" width="17.81640625"/>
-    <col min="3" max="3" customWidth="true" style="41" width="16.453125"/>
-    <col min="4" max="4" customWidth="true" style="41" width="16.08984375"/>
-    <col min="5" max="5" customWidth="true" style="41" width="12.0"/>
-    <col min="6" max="6" customWidth="true" style="41" width="18.08984375"/>
-    <col min="7" max="7" customWidth="true" style="41" width="15.08984375"/>
-    <col min="8" max="8" customWidth="true" style="41" width="10.453125"/>
-    <col min="9" max="9" customWidth="true" style="41" width="10.81640625"/>
-    <col min="10" max="10" style="41" width="8.90625"/>
-    <col min="11" max="11" customWidth="true" style="41" width="13.1796875"/>
-    <col min="12" max="12" customWidth="true" style="41" width="12.6328125"/>
-    <col min="13" max="13" customWidth="true" style="41" width="14.08984375"/>
-    <col min="14" max="14" customWidth="true" style="41" width="14.36328125"/>
-    <col min="15" max="16384" style="41" width="8.90625"/>
+    <col min="1" max="1" width="30.90625" style="41" customWidth="1"/>
+    <col min="2" max="2" width="17.81640625" style="41" customWidth="1"/>
+    <col min="3" max="3" width="16.453125" style="41" customWidth="1"/>
+    <col min="4" max="4" width="16.08984375" style="41" customWidth="1"/>
+    <col min="5" max="5" width="12" style="41" customWidth="1"/>
+    <col min="6" max="6" width="18.08984375" style="41" customWidth="1"/>
+    <col min="7" max="7" width="15.08984375" style="41" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" style="41" customWidth="1"/>
+    <col min="9" max="9" width="10.81640625" style="41" customWidth="1"/>
+    <col min="10" max="10" width="8.90625" style="41"/>
+    <col min="11" max="11" width="13.1796875" style="41" customWidth="1"/>
+    <col min="12" max="12" width="12.6328125" style="41" customWidth="1"/>
+    <col min="13" max="13" width="14.08984375" style="41" customWidth="1"/>
+    <col min="14" max="14" width="14.36328125" style="41" customWidth="1"/>
+    <col min="15" max="16384" width="8.90625" style="41"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -9955,7 +9958,7 @@
         <v>4</v>
       </c>
       <c r="H1" s="53" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I1" s="53" t="s">
         <v>9</v>
@@ -9967,10 +9970,10 @@
         <v>210</v>
       </c>
       <c r="L1" s="42" t="s">
+        <v>357</v>
+      </c>
+      <c r="M1" s="42" t="s">
         <v>358</v>
-      </c>
-      <c r="M1" s="42" t="s">
-        <v>359</v>
       </c>
       <c r="N1" s="42" t="s">
         <v>75</v>
@@ -9978,13 +9981,13 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="54" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B2" s="44">
         <v>2</v>
       </c>
       <c r="C2" s="47" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D2" s="44" t="s">
         <v>12</v>
@@ -10005,28 +10008,28 @@
         <v>212</v>
       </c>
       <c r="J2" s="44" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="K2" s="44">
         <v>2</v>
       </c>
       <c r="L2" s="44" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="M2" s="44" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="N2" s="44"/>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="44" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B3" s="44">
         <v>2</v>
       </c>
       <c r="C3" s="47" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D3" s="44" t="s">
         <v>12</v>
@@ -10044,13 +10047,13 @@
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="55" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B4" s="44">
         <v>2</v>
       </c>
       <c r="C4" s="47" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D4" s="44" t="s">
         <v>12</v>
@@ -10065,13 +10068,13 @@
         <v>345</v>
       </c>
       <c r="H4" s="44" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="I4" s="44" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="J4" s="44" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="K4" s="44"/>
       <c r="L4" s="44"/>
@@ -10082,13 +10085,13 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="44" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B5" s="44">
         <v>2</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D5" s="44" t="s">
         <v>12</v>
@@ -10103,13 +10106,13 @@
         <v>345</v>
       </c>
       <c r="H5" s="44" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="I5" s="44" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="J5" s="44" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="K5" s="44"/>
       <c r="L5" s="44"/>
@@ -10131,11 +10134,11 @@
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="39.453125"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="13.54296875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="7.81640625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="1" max="1" width="39.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -10203,10 +10206,10 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="57.453125"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="15.54296875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="7.81640625"/>
-    <col min="4" max="5" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="1" max="1" width="57.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -10240,7 +10243,7 @@
         <v>209</v>
       </c>
       <c r="E2" s="44" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -10274,7 +10277,7 @@
         <v>209</v>
       </c>
       <c r="E4" s="44" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -10291,7 +10294,7 @@
         <v>209</v>
       </c>
       <c r="E5" s="44" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -10325,28 +10328,28 @@
   <dimension ref="A1:V15"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="25" width="50.0"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="25" width="18.36328125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="25" width="12.08984375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="25" width="15.36328125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="25" width="12.1796875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="25" width="9.453125"/>
-    <col min="7" max="8" style="25" width="8.81640625"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="25" width="10.453125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="25" width="12.6328125"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="25" width="10.453125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="25" width="11.1796875"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="25" width="10.453125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="25" width="8.1796875"/>
-    <col min="15" max="15" customWidth="true" style="25" width="13.0"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" style="25" width="10.1796875"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="25" width="10.453125"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="25" width="9.1796875"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="25" width="11.6328125"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="25" width="12.6328125"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="25" width="11.1796875"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="25" width="12.6328125"/>
-    <col min="23" max="16384" style="25" width="8.81640625"/>
+    <col min="1" max="1" width="50" style="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.36328125" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.08984375" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.36328125" style="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1796875" style="25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.453125" style="25" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="8.81640625" style="25"/>
+    <col min="9" max="9" width="10.453125" style="25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.6328125" style="25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.453125" style="25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.1796875" style="25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.453125" style="25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.1796875" style="25" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13" style="25" customWidth="1"/>
+    <col min="16" max="16" width="10.1796875" style="25" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.453125" style="25" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.1796875" style="25" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.6328125" style="25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.6328125" style="25" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.1796875" style="25" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.6328125" style="25" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="8.81640625" style="25"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
@@ -10405,16 +10408,16 @@
         <v>9</v>
       </c>
       <c r="S1" s="30" t="s">
+        <v>357</v>
+      </c>
+      <c r="T1" s="30" t="s">
         <v>358</v>
-      </c>
-      <c r="T1" s="30" t="s">
-        <v>359</v>
       </c>
       <c r="U1" s="30" t="s">
         <v>30</v>
       </c>
       <c r="V1" s="30" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2" spans="1:22">
@@ -10440,7 +10443,7 @@
         <v>15</v>
       </c>
       <c r="H2" s="32" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="I2" s="32" t="s">
         <v>211</v>
@@ -10457,14 +10460,14 @@
       <c r="M2" s="32"/>
       <c r="N2" s="32"/>
       <c r="O2" s="32" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="P2" s="32"/>
       <c r="Q2" s="32" t="s">
+        <v>360</v>
+      </c>
+      <c r="R2" s="32" t="s">
         <v>361</v>
-      </c>
-      <c r="R2" s="32" t="s">
-        <v>362</v>
       </c>
       <c r="S2" s="32"/>
       <c r="T2" s="32"/>
@@ -10581,7 +10584,7 @@
     </row>
     <row r="6" spans="1:22" s="29" customFormat="1">
       <c r="A6" s="32" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B6" s="44">
         <v>0</v>
@@ -10602,13 +10605,13 @@
         <v>15</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="I6" s="32" t="s">
+        <v>390</v>
+      </c>
+      <c r="J6" s="32" t="s">
         <v>391</v>
-      </c>
-      <c r="J6" s="32" t="s">
-        <v>392</v>
       </c>
       <c r="K6" s="32"/>
       <c r="L6" s="32"/>
@@ -10619,17 +10622,17 @@
       <c r="Q6" s="32"/>
       <c r="R6" s="32"/>
       <c r="S6" s="32" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="T6" s="32" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="U6" s="32"/>
       <c r="V6" s="32"/>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="39" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B7" s="44">
         <v>0</v>
@@ -10650,13 +10653,13 @@
         <v>19</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="I7" s="32" t="s">
+        <v>363</v>
+      </c>
+      <c r="J7" s="32" t="s">
         <v>364</v>
-      </c>
-      <c r="J7" s="32" t="s">
-        <v>365</v>
       </c>
       <c r="K7" s="32"/>
       <c r="L7" s="32"/>
@@ -10673,7 +10676,7 @@
     </row>
     <row r="8" spans="1:22" s="29" customFormat="1">
       <c r="A8" s="32" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B8" s="44">
         <v>0</v>
@@ -10705,7 +10708,7 @@
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="39" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B9" s="44">
         <v>0</v>
@@ -10726,13 +10729,13 @@
         <v>15</v>
       </c>
       <c r="H9" s="32" t="s">
+        <v>366</v>
+      </c>
+      <c r="I9" s="32" t="s">
         <v>367</v>
       </c>
-      <c r="I9" s="32" t="s">
+      <c r="J9" s="32" t="s">
         <v>368</v>
-      </c>
-      <c r="J9" s="32" t="s">
-        <v>369</v>
       </c>
       <c r="K9" s="32"/>
       <c r="L9" s="32"/>
@@ -10749,7 +10752,7 @@
     </row>
     <row r="10" spans="1:22" s="29" customFormat="1">
       <c r="A10" s="32" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B10" s="44">
         <v>0</v>
@@ -10768,11 +10771,11 @@
       </c>
       <c r="G10" s="56"/>
       <c r="H10" s="32" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="I10" s="32"/>
       <c r="J10" s="32" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K10" s="32"/>
       <c r="L10" s="32"/>
@@ -10783,19 +10786,19 @@
       <c r="Q10" s="32"/>
       <c r="R10" s="32"/>
       <c r="S10" s="32" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="T10" s="32" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="U10" s="32"/>
       <c r="V10" s="32" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="39" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B11" s="44">
         <v>0</v>
@@ -10816,7 +10819,7 @@
         <v>15</v>
       </c>
       <c r="H11" s="32" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="I11" s="32" t="s">
         <v>211</v>
@@ -10831,25 +10834,25 @@
       <c r="O11" s="32"/>
       <c r="P11" s="32"/>
       <c r="Q11" s="32" t="s">
+        <v>373</v>
+      </c>
+      <c r="R11" s="32" t="s">
         <v>374</v>
       </c>
-      <c r="R11" s="32" t="s">
+      <c r="S11" s="32" t="s">
         <v>375</v>
       </c>
-      <c r="S11" s="32" t="s">
+      <c r="T11" s="32" t="s">
         <v>376</v>
       </c>
-      <c r="T11" s="32" t="s">
+      <c r="U11" s="32" t="s">
         <v>377</v>
-      </c>
-      <c r="U11" s="32" t="s">
-        <v>378</v>
       </c>
       <c r="V11" s="32"/>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="39" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B12" s="44">
         <v>2</v>
@@ -10868,19 +10871,19 @@
       </c>
       <c r="G12" s="56"/>
       <c r="H12" s="32" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="I12" s="32" t="s">
+        <v>379</v>
+      </c>
+      <c r="J12" s="32" t="s">
         <v>380</v>
       </c>
-      <c r="J12" s="32" t="s">
+      <c r="K12" s="32" t="s">
         <v>381</v>
       </c>
-      <c r="K12" s="32" t="s">
-        <v>382</v>
-      </c>
       <c r="L12" s="32" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="M12" s="32"/>
       <c r="N12" s="32"/>
@@ -10889,25 +10892,25 @@
       <c r="Q12" s="32"/>
       <c r="R12" s="32"/>
       <c r="S12" s="32" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="T12" s="32" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="U12" s="32"/>
       <c r="V12" s="32" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="39" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B13" s="44">
         <v>3</v>
       </c>
       <c r="C13" s="47" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D13" s="44" t="s">
         <v>216</v>
@@ -10937,7 +10940,7 @@
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="39" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B14" s="44">
         <v>1</v>
@@ -10956,7 +10959,7 @@
       </c>
       <c r="G14" s="56"/>
       <c r="H14" s="32" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="I14" s="32" t="s">
         <v>244</v>
@@ -10973,19 +10976,19 @@
       <c r="Q14" s="32"/>
       <c r="R14" s="32"/>
       <c r="S14" s="32" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="T14" s="32" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="U14" s="32"/>
       <c r="V14" s="32" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="15" spans="1:22" s="29" customFormat="1">
       <c r="A15" s="39" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B15" s="44">
         <v>0</v>
@@ -11006,13 +11009,13 @@
         <v>15</v>
       </c>
       <c r="H15" s="32" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="I15" s="32" t="s">
+        <v>370</v>
+      </c>
+      <c r="J15" s="32" t="s">
         <v>371</v>
-      </c>
-      <c r="J15" s="32" t="s">
-        <v>372</v>
       </c>
       <c r="K15" s="32"/>
       <c r="L15" s="32"/>
@@ -11041,29 +11044,29 @@
   <dimension ref="A1:AB7"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="44.81640625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.81640625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="8.1796875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="11.1796875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="10.453125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="13.54296875"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="17.81640625"/>
-    <col min="11" max="12" bestFit="true" customWidth="true" width="11.1796875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="18.1796875"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="7.81640625"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="11.1796875"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="8.1796875"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="11.1796875"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="11.1796875"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="14.1796875"/>
-    <col min="27" max="28" bestFit="true" customWidth="true" width="12.81640625"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="14.1796875"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="12.81640625"/>
+    <col min="1" max="1" width="44.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28">
@@ -11495,9 +11498,9 @@
   <dimension ref="A1:W17"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="54.36328125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="13.90625"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="13.81640625"/>
+    <col min="1" max="1" width="54.36328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -11600,10 +11603,10 @@
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
       <c r="R2" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="S2" s="3" t="s">
         <v>467</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>468</v>
       </c>
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
@@ -11862,10 +11865,10 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="S8" s="3" t="s">
         <v>469</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>470</v>
       </c>
       <c r="T8" s="3">
         <v>0</v>
@@ -11882,7 +11885,7 @@
         <v>2</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>12</v>
@@ -11911,10 +11914,10 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="S9" s="3" t="s">
         <v>557</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>558</v>
       </c>
       <c r="T9" s="3"/>
       <c r="U9" s="3">
@@ -11935,7 +11938,7 @@
         <v>2</v>
       </c>
       <c r="C10" s="47" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>12</v>
@@ -11964,10 +11967,10 @@
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="S10" s="3" t="s">
         <v>559</v>
-      </c>
-      <c r="S10" s="3" t="s">
-        <v>560</v>
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
@@ -12161,7 +12164,7 @@
         <v>2</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D16" s="32" t="s">
         <v>12</v>
@@ -12190,10 +12193,10 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="S16" s="3" t="s">
         <v>561</v>
-      </c>
-      <c r="S16" s="3" t="s">
-        <v>562</v>
       </c>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
@@ -12248,16 +12251,16 @@
   <dimension ref="A1:S20"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="53.81640625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="3" max="4" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="5" max="7" customWidth="true" width="12.1796875"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="1" max="1" width="53.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="12.1796875" customWidth="1"/>
+    <col min="8" max="8" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
@@ -12425,7 +12428,7 @@
         <v>264</v>
       </c>
       <c r="F5" s="44" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G5" s="44"/>
       <c r="H5" s="44"/>

--- a/src/test/java/TestData/Scenario_TestData.xlsx
+++ b/src/test/java/TestData/Scenario_TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Copa_SHD_WebServices\src\test\java\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B990BDA6-7B22-41A5-90AE-F6903877BAB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57DFA7A6-8FDB-4B06-9E71-BE2267789F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="10" activeTab="11" xr2:uid="{5D5A4724-D560-4FC2-9708-4BBF1DBA0B11}"/>
   </bookViews>
@@ -1444,9 +1444,6 @@
     <t>2023-08-19T13:43:00</t>
   </si>
   <si>
-    <t>A0G4BU</t>
-  </si>
-  <si>
     <t>A0G4CG</t>
   </si>
   <si>
@@ -1465,9 +1462,6 @@
     <t>A0HAUU</t>
   </si>
   <si>
-    <t>A0HA2C</t>
-  </si>
-  <si>
     <t>A0HBEB</t>
   </si>
   <si>
@@ -1943,6 +1937,12 @@
   </si>
   <si>
     <t>AQT2ZF</t>
+  </si>
+  <si>
+    <t>A2DUC4</t>
+  </si>
+  <si>
+    <t>A2DUNP</t>
   </si>
 </sst>
 </file>
@@ -2684,7 +2684,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="44" t="s">
-        <v>456</v>
+        <v>621</v>
       </c>
       <c r="I2" s="32" t="s">
         <v>211</v>
@@ -2701,7 +2701,7 @@
       <c r="M2" s="32"/>
       <c r="N2" s="32"/>
       <c r="O2" s="32" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="P2" s="38"/>
     </row>
@@ -2773,7 +2773,7 @@
         <v>1</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="I4" s="37" t="s">
         <v>354</v>
@@ -2810,7 +2810,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="37" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I5" s="32"/>
       <c r="J5" s="32"/>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="J2" s="44"/>
       <c r="K2" s="44" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="L2" s="44"/>
       <c r="M2" s="44"/>
@@ -2987,10 +2987,10 @@
         <v>0</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="L3" s="44" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="M3" s="44"/>
       <c r="N3" s="44"/>
@@ -3059,10 +3059,10 @@
       <c r="I5" s="44"/>
       <c r="J5" s="44"/>
       <c r="K5" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="M5" s="44"/>
       <c r="N5" s="44" t="s">
@@ -3106,7 +3106,7 @@
       <c r="I6" s="44"/>
       <c r="J6" s="44"/>
       <c r="K6" s="44" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="L6" s="44"/>
       <c r="M6" s="44"/>
@@ -3117,7 +3117,7 @@
         <v>242</v>
       </c>
       <c r="P6" s="44" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="Q6" s="44"/>
       <c r="R6" s="44"/>
@@ -3151,10 +3151,10 @@
       <c r="I7" s="44"/>
       <c r="J7" s="44"/>
       <c r="K7" s="44" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="L7" s="44" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="M7" s="44"/>
       <c r="N7" s="44" t="s">
@@ -3164,13 +3164,13 @@
         <v>242</v>
       </c>
       <c r="P7" s="44" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="Q7" s="47" t="s">
         <v>87</v>
       </c>
       <c r="R7" s="44" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="S7" s="44"/>
       <c r="T7" s="44"/>
@@ -3206,10 +3206,10 @@
       </c>
       <c r="J8" s="44"/>
       <c r="K8" s="44" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="L8" s="44" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="M8" s="44"/>
       <c r="N8" s="44" t="s">
@@ -3247,7 +3247,7 @@
       <c r="I9" s="44"/>
       <c r="J9" s="44"/>
       <c r="K9" s="44" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="L9" s="44"/>
       <c r="M9" s="44"/>
@@ -3286,10 +3286,10 @@
       <c r="I10" s="44"/>
       <c r="J10" s="44"/>
       <c r="K10" s="44" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="L10" s="44" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="M10" s="44"/>
       <c r="N10" s="44"/>
@@ -3325,10 +3325,10 @@
       <c r="I11" s="44"/>
       <c r="J11" s="44"/>
       <c r="K11" s="44" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="L11" s="44" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="M11" s="44"/>
       <c r="N11" s="44"/>
@@ -3364,10 +3364,10 @@
       <c r="I12" s="44"/>
       <c r="J12" s="44"/>
       <c r="K12" s="44" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="L12" s="44" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="M12" s="44"/>
       <c r="N12" s="44" t="s">
@@ -3407,10 +3407,10 @@
       <c r="I13" s="44"/>
       <c r="J13" s="44"/>
       <c r="K13" s="44" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="L13" s="44" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="M13" s="44"/>
       <c r="N13" s="44" t="s">
@@ -3485,10 +3485,10 @@
       <c r="I15" s="44"/>
       <c r="J15" s="44"/>
       <c r="K15" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L15" s="44" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="M15" s="44"/>
       <c r="N15" s="44" t="s">
@@ -3528,7 +3528,7 @@
       <c r="I16" s="44"/>
       <c r="J16" s="44"/>
       <c r="K16" s="44" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="L16" s="44"/>
       <c r="M16" s="44"/>
@@ -3567,7 +3567,7 @@
       <c r="I17" s="44"/>
       <c r="J17" s="44"/>
       <c r="K17" s="44" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="L17" s="44"/>
       <c r="M17" s="44"/>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="J18" s="44"/>
       <c r="K18" s="44" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="L18" s="44"/>
       <c r="M18" s="44"/>
@@ -3649,7 +3649,7 @@
       <c r="I19" s="44"/>
       <c r="J19" s="44"/>
       <c r="K19" s="44" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="L19" s="44"/>
       <c r="M19" s="44"/>
@@ -3688,7 +3688,7 @@
       <c r="I20" s="44"/>
       <c r="J20" s="44"/>
       <c r="K20" s="44" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="L20" s="44"/>
       <c r="M20" s="44"/>
@@ -3727,7 +3727,7 @@
       <c r="I21" s="44"/>
       <c r="J21" s="44"/>
       <c r="K21" s="44" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="L21" s="44"/>
       <c r="M21" s="44"/>
@@ -3752,7 +3752,7 @@
         <v>1</v>
       </c>
       <c r="C22" s="47" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D22" s="44" t="s">
         <v>34</v>
@@ -3774,7 +3774,7 @@
       </c>
       <c r="J22" s="44"/>
       <c r="K22" s="44" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="L22" s="44"/>
       <c r="M22" s="44"/>
@@ -3868,7 +3868,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="47" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="D2" s="35" t="s">
         <v>12</v>
@@ -3895,10 +3895,10 @@
         <v>1</v>
       </c>
       <c r="L2" s="34" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="M2" s="34" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="N2" s="32"/>
     </row>
@@ -3937,7 +3937,7 @@
         <v>6</v>
       </c>
       <c r="L3" s="34" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="M3" s="34" t="s">
         <v>264</v>
@@ -3981,7 +3981,7 @@
         <v>6</v>
       </c>
       <c r="L4" s="34" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="M4" s="32"/>
       <c r="N4" s="32" t="s">
@@ -4063,7 +4063,7 @@
       <c r="G2" s="44"/>
       <c r="H2" s="44"/>
       <c r="I2" s="44" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="J2" s="44"/>
       <c r="K2" s="44"/>
@@ -4082,7 +4082,7 @@
       <c r="G3" s="44"/>
       <c r="H3" s="44"/>
       <c r="I3" s="44" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="J3" s="44"/>
       <c r="K3" s="44"/>
@@ -4132,13 +4132,13 @@
         <v>12</v>
       </c>
       <c r="I5" s="44" t="s">
+        <v>498</v>
+      </c>
+      <c r="J5" s="44" t="s">
+        <v>499</v>
+      </c>
+      <c r="K5" s="44" t="s">
         <v>500</v>
-      </c>
-      <c r="J5" s="44" t="s">
-        <v>501</v>
-      </c>
-      <c r="K5" s="44" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -4167,10 +4167,10 @@
         <v>12</v>
       </c>
       <c r="I6" s="44" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="J6" s="44" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="K6" s="44"/>
     </row>
@@ -4450,7 +4450,7 @@
         <v>45</v>
       </c>
       <c r="J2" s="44" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="K2" s="44" t="s">
         <v>452</v>
@@ -4520,7 +4520,7 @@
         <v>45</v>
       </c>
       <c r="J3" s="44" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="K3" s="44" t="s">
         <v>452</v>
@@ -4538,13 +4538,13 @@
         <v>12</v>
       </c>
       <c r="P3" s="44" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="Q3" s="44" t="s">
         <v>239</v>
       </c>
       <c r="R3" s="44" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="S3" s="44" t="s">
         <v>12</v>
@@ -4598,16 +4598,16 @@
       <c r="H4" s="44"/>
       <c r="I4" s="44"/>
       <c r="J4" s="44" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="K4" s="44" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="L4" s="44" t="s">
         <v>328</v>
       </c>
       <c r="M4" s="44" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="N4" s="44" t="s">
         <v>209</v>
@@ -4650,16 +4650,16 @@
       <c r="H5" s="44"/>
       <c r="I5" s="44"/>
       <c r="J5" s="44" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="L5" s="44" t="s">
         <v>328</v>
       </c>
       <c r="M5" s="44" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="N5" s="44" t="s">
         <v>209</v>
@@ -4710,16 +4710,16 @@
         <v>45</v>
       </c>
       <c r="J6" s="44" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="K6" s="44" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="L6" s="44" t="s">
         <v>207</v>
       </c>
       <c r="M6" s="44" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="N6" s="44" t="s">
         <v>208</v>
@@ -5761,16 +5761,16 @@
       <c r="I2" s="44"/>
       <c r="J2" s="44"/>
       <c r="K2" s="44" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>325</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>209</v>
@@ -5825,7 +5825,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>312</v>
@@ -5965,16 +5965,16 @@
         <v>2</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>325</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>209</v>
@@ -5983,7 +5983,7 @@
         <v>12</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="R5" s="15" t="s">
         <v>44</v>
@@ -6181,16 +6181,16 @@
       <c r="I9" s="44"/>
       <c r="J9" s="44"/>
       <c r="K9" s="44" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>325</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>209</v>
@@ -6502,16 +6502,16 @@
       <c r="U2" s="44"/>
       <c r="V2" s="44"/>
       <c r="W2" s="44" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="X2" s="44" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="Y2" s="44" t="s">
         <v>325</v>
       </c>
       <c r="Z2" s="44" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="AA2" s="44" t="s">
         <v>209</v>
@@ -6520,7 +6520,7 @@
         <v>12</v>
       </c>
       <c r="AC2" s="44" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -6638,16 +6638,16 @@
       <c r="U4" s="44"/>
       <c r="V4" s="44"/>
       <c r="W4" s="44" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="X4" s="44" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="Y4" s="44" t="s">
         <v>325</v>
       </c>
       <c r="Z4" s="44" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="AA4" s="44" t="s">
         <v>209</v>
@@ -6656,7 +6656,7 @@
         <v>12</v>
       </c>
       <c r="AC4" s="44" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
   </sheetData>
@@ -6914,16 +6914,16 @@
       <c r="I2" s="44"/>
       <c r="J2" s="44"/>
       <c r="K2" s="44" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="L2" s="44" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="M2" s="44" t="s">
         <v>329</v>
       </c>
       <c r="N2" s="44" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>209</v>
@@ -6932,7 +6932,7 @@
         <v>12</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="R2" s="3"/>
     </row>
@@ -6960,16 +6960,16 @@
       <c r="I3" s="44"/>
       <c r="J3" s="44"/>
       <c r="K3" s="44" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="L3" s="44" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="M3" s="44" t="s">
         <v>325</v>
       </c>
       <c r="N3" s="44" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="O3" s="3" t="s">
         <v>209</v>
@@ -6978,10 +6978,10 @@
         <v>12</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -7008,7 +7008,7 @@
       <c r="I4" s="44"/>
       <c r="J4" s="44"/>
       <c r="K4" s="44" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="L4" s="44" t="s">
         <v>452</v>
@@ -7026,7 +7026,7 @@
         <v>12</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="R4" s="3"/>
     </row>
@@ -7054,7 +7054,7 @@
       <c r="I5" s="44"/>
       <c r="J5" s="44"/>
       <c r="K5" s="44" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="L5" s="44" t="s">
         <v>452</v>
@@ -7072,7 +7072,7 @@
         <v>12</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="R5" s="3"/>
     </row>
@@ -7100,7 +7100,7 @@
       <c r="I6" s="44"/>
       <c r="J6" s="44"/>
       <c r="K6" s="44" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="L6" s="44" t="s">
         <v>452</v>
@@ -7118,7 +7118,7 @@
         <v>12</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="R6" s="3"/>
     </row>
@@ -7253,16 +7253,16 @@
         <v>163</v>
       </c>
       <c r="J2" s="56" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="K2" s="44" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>215</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>12</v>
@@ -7271,13 +7271,13 @@
         <v>216</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>217</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="S2" s="3" t="s">
         <v>216</v>
@@ -7286,7 +7286,7 @@
         <v>163</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="3" spans="1:21">
@@ -7318,16 +7318,16 @@
         <v>163</v>
       </c>
       <c r="J3" s="56" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>215</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>12</v>
@@ -7336,13 +7336,13 @@
         <v>216</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>341</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="S3" s="3" t="s">
         <v>216</v>
@@ -7351,7 +7351,7 @@
         <v>163</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="4" spans="1:21">
@@ -7556,7 +7556,7 @@
         <v>181</v>
       </c>
       <c r="B3" s="64" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -7666,40 +7666,40 @@
         <v>266</v>
       </c>
       <c r="C1" s="42" t="s">
+        <v>580</v>
+      </c>
+      <c r="D1" s="42" t="s">
+        <v>581</v>
+      </c>
+      <c r="E1" s="42" t="s">
         <v>582</v>
       </c>
-      <c r="D1" s="42" t="s">
+      <c r="F1" s="42" t="s">
         <v>583</v>
       </c>
-      <c r="E1" s="42" t="s">
+      <c r="G1" s="63" t="s">
         <v>584</v>
       </c>
-      <c r="F1" s="42" t="s">
+      <c r="H1" s="63" t="s">
         <v>585</v>
       </c>
-      <c r="G1" s="63" t="s">
-        <v>586</v>
-      </c>
-      <c r="H1" s="63" t="s">
-        <v>587</v>
-      </c>
       <c r="I1" s="63" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="J1" s="63" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="K1" s="42" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="L1" s="42" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="M1" s="42" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="N1" s="42" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -7710,40 +7710,40 @@
         <v>149</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="D2" s="32" t="s">
         <v>121</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="F2" s="44" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="G2" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H2" s="44" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="I2" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="J2" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="K2" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="L2" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="M2" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="N2" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -7754,40 +7754,40 @@
         <v>149</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="D3" s="32" t="s">
         <v>121</v>
       </c>
       <c r="E3" s="32" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="F3" s="44" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="G3" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H3" s="44" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="I3" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="J3" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="L3" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="M3" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="N3" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -7798,40 +7798,40 @@
         <v>149</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="D4" s="32" t="s">
         <v>121</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="F4" s="44" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="G4" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H4" s="44" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="I4" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="J4" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="K4" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="L4" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="M4" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="N4" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -7842,40 +7842,40 @@
         <v>149</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="D5" s="32" t="s">
         <v>121</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="F5" s="44" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="G5" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H5" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="I5" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="J5" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="M5" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="N5" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -7886,40 +7886,40 @@
         <v>149</v>
       </c>
       <c r="C6" s="44" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="D6" s="44" t="s">
         <v>121</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="F6" s="44" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="G6" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H6" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="I6" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="J6" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="K6" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="L6" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="M6" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="N6" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -7930,40 +7930,40 @@
         <v>149</v>
       </c>
       <c r="C7" s="44" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="D7" s="44" t="s">
         <v>121</v>
       </c>
       <c r="E7" s="44" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="F7" s="44" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="G7" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H7" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="I7" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="J7" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="K7" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="L7" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="M7" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="N7" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -7974,40 +7974,40 @@
         <v>149</v>
       </c>
       <c r="C8" s="44" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="D8" s="44" t="s">
         <v>121</v>
       </c>
       <c r="E8" s="44" t="s">
+        <v>591</v>
+      </c>
+      <c r="F8" s="44" t="s">
         <v>593</v>
-      </c>
-      <c r="F8" s="44" t="s">
-        <v>595</v>
       </c>
       <c r="G8" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H8" s="44" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="I8" s="44" t="s">
+        <v>598</v>
+      </c>
+      <c r="J8" s="44" t="s">
+        <v>596</v>
+      </c>
+      <c r="K8" s="44" t="s">
+        <v>592</v>
+      </c>
+      <c r="L8" s="44" t="s">
+        <v>594</v>
+      </c>
+      <c r="M8" s="44" t="s">
         <v>600</v>
       </c>
-      <c r="J8" s="44" t="s">
-        <v>598</v>
-      </c>
-      <c r="K8" s="44" t="s">
-        <v>594</v>
-      </c>
-      <c r="L8" s="44" t="s">
-        <v>596</v>
-      </c>
-      <c r="M8" s="44" t="s">
-        <v>602</v>
-      </c>
       <c r="N8" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -8018,40 +8018,40 @@
         <v>149</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="D9" s="32" t="s">
         <v>121</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F9" s="44" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="G9" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H9" s="44" t="s">
+        <v>603</v>
+      </c>
+      <c r="I9" s="44" t="s">
+        <v>604</v>
+      </c>
+      <c r="J9" s="44" t="s">
         <v>605</v>
       </c>
-      <c r="I9" s="44" t="s">
-        <v>606</v>
-      </c>
-      <c r="J9" s="44" t="s">
-        <v>607</v>
-      </c>
       <c r="K9" s="44" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="L9" s="44" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="M9" s="44" t="s">
         <v>431</v>
       </c>
       <c r="N9" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -8062,40 +8062,40 @@
         <v>149</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="D10" s="44" t="s">
         <v>121</v>
       </c>
       <c r="E10" s="32" t="s">
+        <v>607</v>
+      </c>
+      <c r="F10" s="44" t="s">
         <v>609</v>
-      </c>
-      <c r="F10" s="44" t="s">
-        <v>611</v>
       </c>
       <c r="G10" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H10" s="44" t="s">
+        <v>610</v>
+      </c>
+      <c r="I10" s="44" t="s">
+        <v>611</v>
+      </c>
+      <c r="J10" s="44" t="s">
         <v>612</v>
       </c>
-      <c r="I10" s="44" t="s">
-        <v>613</v>
-      </c>
-      <c r="J10" s="44" t="s">
-        <v>614</v>
-      </c>
       <c r="K10" s="44" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="L10" s="44" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="M10" s="44" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="N10" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -8106,40 +8106,40 @@
         <v>149</v>
       </c>
       <c r="C11" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="D11" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F11" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="G11" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="H11" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="I11" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="J11" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="K11" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="L11" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="M11" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="N11" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -8150,40 +8150,40 @@
         <v>149</v>
       </c>
       <c r="C12" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="D12" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F12" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="G12" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="H12" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="I12" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="J12" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="K12" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="L12" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="M12" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="N12" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -8194,40 +8194,40 @@
         <v>149</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F13" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="G13" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="H13" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="I13" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="J13" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="K13" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="L13" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="M13" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="N13" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -8238,40 +8238,40 @@
         <v>149</v>
       </c>
       <c r="C14" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F14" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="G14" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="H14" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="I14" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="J14" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="K14" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="L14" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="M14" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="N14" s="44" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -8282,40 +8282,40 @@
         <v>149</v>
       </c>
       <c r="C15" s="44" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="D15" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E15" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F15" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="G15" s="44" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="H15" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="I15" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="J15" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="K15" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="L15" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="M15" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="N15" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -8323,43 +8323,43 @@
         <v>303</v>
       </c>
       <c r="B16" s="32" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="D16" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F16" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="G16" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="H16" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="I16" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="J16" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="K16" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="L16" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="M16" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="N16" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -8370,45 +8370,45 @@
         <v>149</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="D17" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F17" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="G17" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="H17" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="I17" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="J17" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="K17" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="L17" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="M17" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="N17" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="62" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
   </sheetData>
@@ -8487,10 +8487,10 @@
         <v>50</v>
       </c>
       <c r="H2" s="44" t="s">
+        <v>459</v>
+      </c>
+      <c r="I2" s="44" t="s">
         <v>460</v>
-      </c>
-      <c r="I2" s="44" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -8720,7 +8720,7 @@
       <c r="H6" s="44"/>
       <c r="I6" s="44"/>
       <c r="J6" s="44" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="K6" s="44"/>
       <c r="L6" s="44"/>
@@ -8803,7 +8803,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="G2" s="32">
         <v>2</v>
@@ -9453,7 +9453,7 @@
         <v>413</v>
       </c>
       <c r="B4" s="47" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C4" s="44" t="s">
         <v>12</v>
@@ -9469,7 +9469,7 @@
       </c>
       <c r="G4" s="44"/>
       <c r="H4" s="44" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="I4" s="44" t="s">
         <v>390</v>
@@ -9490,7 +9490,7 @@
         <v>414</v>
       </c>
       <c r="B5" s="47" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C5" s="44" t="s">
         <v>12</v>
@@ -9506,7 +9506,7 @@
       </c>
       <c r="G5" s="44"/>
       <c r="H5" s="44" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="I5" s="44" t="s">
         <v>390</v>
@@ -10008,7 +10008,7 @@
         <v>212</v>
       </c>
       <c r="J2" s="44" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="K2" s="44">
         <v>2</v>
@@ -10085,13 +10085,13 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="44" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B5" s="44">
         <v>2</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="D5" s="44" t="s">
         <v>12</v>
@@ -10460,7 +10460,7 @@
       <c r="M2" s="32"/>
       <c r="N2" s="32"/>
       <c r="O2" s="32" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="P2" s="32"/>
       <c r="Q2" s="32" t="s">
@@ -10605,7 +10605,7 @@
         <v>15</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="I6" s="32" t="s">
         <v>390</v>
@@ -10622,7 +10622,7 @@
       <c r="Q6" s="32"/>
       <c r="R6" s="32"/>
       <c r="S6" s="32" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="T6" s="32" t="s">
         <v>440</v>
@@ -10653,7 +10653,7 @@
         <v>19</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="I7" s="32" t="s">
         <v>363</v>
@@ -10771,7 +10771,7 @@
       </c>
       <c r="G10" s="56"/>
       <c r="H10" s="32" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I10" s="32"/>
       <c r="J10" s="32" t="s">
@@ -10786,7 +10786,7 @@
       <c r="Q10" s="32"/>
       <c r="R10" s="32"/>
       <c r="S10" s="32" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="T10" s="32" t="s">
         <v>376</v>
@@ -10819,7 +10819,7 @@
         <v>15</v>
       </c>
       <c r="H11" s="32" t="s">
-        <v>463</v>
+        <v>622</v>
       </c>
       <c r="I11" s="32" t="s">
         <v>211</v>
@@ -10871,7 +10871,7 @@
       </c>
       <c r="G12" s="56"/>
       <c r="H12" s="32" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="I12" s="32" t="s">
         <v>379</v>
@@ -10959,7 +10959,7 @@
       </c>
       <c r="G14" s="56"/>
       <c r="H14" s="32" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="I14" s="32" t="s">
         <v>244</v>
@@ -10976,7 +10976,7 @@
       <c r="Q14" s="32"/>
       <c r="R14" s="32"/>
       <c r="S14" s="32" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="T14" s="32" t="s">
         <v>376</v>
@@ -11009,7 +11009,7 @@
         <v>15</v>
       </c>
       <c r="H15" s="32" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="I15" s="32" t="s">
         <v>370</v>
@@ -11603,10 +11603,10 @@
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
       <c r="R2" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
@@ -11865,10 +11865,10 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="T8" s="3">
         <v>0</v>
@@ -11885,7 +11885,7 @@
         <v>2</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>12</v>
@@ -11914,10 +11914,10 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="T9" s="3"/>
       <c r="U9" s="3">
@@ -11938,7 +11938,7 @@
         <v>2</v>
       </c>
       <c r="C10" s="47" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>12</v>
@@ -11967,10 +11967,10 @@
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
@@ -12164,7 +12164,7 @@
         <v>2</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="D16" s="32" t="s">
         <v>12</v>
@@ -12193,10 +12193,10 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>

--- a/src/test/java/TestData/Scenario_TestData.xlsx
+++ b/src/test/java/TestData/Scenario_TestData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Copa_SHD_WebServices\src\test\java\TestData\"/>
     </mc:Choice>
@@ -55,7 +55,7 @@
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2082" uniqueCount="623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2411" uniqueCount="755">
   <si>
     <t>Scenario</t>
   </si>
@@ -1943,12 +1943,409 @@
   </si>
   <si>
     <t>A2DUNP</t>
+  </si>
+  <si>
+    <t>A2MQM2</t>
+  </si>
+  <si>
+    <t>A2MQNI</t>
+  </si>
+  <si>
+    <t>2023-08-23T01:14:00</t>
+  </si>
+  <si>
+    <t>2023-08-23T10:38:00</t>
+  </si>
+  <si>
+    <t>2023-08-23T12:02:00</t>
+  </si>
+  <si>
+    <t>2023-08-23T13:43:00</t>
+  </si>
+  <si>
+    <t>A2MQNL</t>
+  </si>
+  <si>
+    <t>A2MQNQ</t>
+  </si>
+  <si>
+    <t>A2MQNR</t>
+  </si>
+  <si>
+    <t>A2MQNT</t>
+  </si>
+  <si>
+    <t>A2MQNV</t>
+  </si>
+  <si>
+    <t>A2MQNW</t>
+  </si>
+  <si>
+    <t>2023-08-22T05:24:41</t>
+  </si>
+  <si>
+    <t>A2MQN5</t>
+  </si>
+  <si>
+    <t>2023-08-22T05:24:50</t>
+  </si>
+  <si>
+    <t>A2MQPA</t>
+  </si>
+  <si>
+    <t>A2MQPD</t>
+  </si>
+  <si>
+    <t>A2MQPF</t>
+  </si>
+  <si>
+    <t>A2MQPN</t>
+  </si>
+  <si>
+    <t>A2MQPT</t>
+  </si>
+  <si>
+    <t>A2MQP1</t>
+  </si>
+  <si>
+    <t>A2MQQV</t>
+  </si>
+  <si>
+    <t>A2MQRF</t>
+  </si>
+  <si>
+    <t>A2MQRL</t>
+  </si>
+  <si>
+    <t>A2MQRT</t>
+  </si>
+  <si>
+    <t>2302182807110</t>
+  </si>
+  <si>
+    <t>A2MQSH</t>
+  </si>
+  <si>
+    <t>2302182807111</t>
+  </si>
+  <si>
+    <t>A2MQSV</t>
+  </si>
+  <si>
+    <t>2302182807113</t>
+  </si>
+  <si>
+    <t>A2MQTC</t>
+  </si>
+  <si>
+    <t>2302182807114</t>
+  </si>
+  <si>
+    <t>A2MQTL</t>
+  </si>
+  <si>
+    <t>2302182807116</t>
+  </si>
+  <si>
+    <t>A2MQUI</t>
+  </si>
+  <si>
+    <t>A2MQUM</t>
+  </si>
+  <si>
+    <t>2302182807118</t>
+  </si>
+  <si>
+    <t>A2MQUT</t>
+  </si>
+  <si>
+    <t>2302182807119</t>
+  </si>
+  <si>
+    <t>A2MQUZ</t>
+  </si>
+  <si>
+    <t>2302182807120</t>
+  </si>
+  <si>
+    <t>A2MQVA</t>
+  </si>
+  <si>
+    <t>2302182807121</t>
+  </si>
+  <si>
+    <t>A2MQVK</t>
+  </si>
+  <si>
+    <t>A2MQVQ</t>
+  </si>
+  <si>
+    <t>A2MQVR</t>
+  </si>
+  <si>
+    <t>A2MQVV</t>
+  </si>
+  <si>
+    <t>A2MQWK</t>
+  </si>
+  <si>
+    <t>A2MQWR</t>
+  </si>
+  <si>
+    <t>A2MQWT</t>
+  </si>
+  <si>
+    <t>A2MQWX</t>
+  </si>
+  <si>
+    <t>2302182807122</t>
+  </si>
+  <si>
+    <t>A2MQW2</t>
+  </si>
+  <si>
+    <t>A2MQW5</t>
+  </si>
+  <si>
+    <t>A2MQXA</t>
+  </si>
+  <si>
+    <t>2302182807123</t>
+  </si>
+  <si>
+    <t>A2MQXF</t>
+  </si>
+  <si>
+    <t>2302182807124</t>
+  </si>
+  <si>
+    <t>A2MQXM</t>
+  </si>
+  <si>
+    <t>2302182807125</t>
+  </si>
+  <si>
+    <t>A2MQXV</t>
+  </si>
+  <si>
+    <t>A2MQXW</t>
+  </si>
+  <si>
+    <t>2302182807126</t>
+  </si>
+  <si>
+    <t>A2MQX4</t>
+  </si>
+  <si>
+    <t>2302182807127</t>
+  </si>
+  <si>
+    <t>2302182807128</t>
+  </si>
+  <si>
+    <t>A2MQYI</t>
+  </si>
+  <si>
+    <t>2302182807129</t>
+  </si>
+  <si>
+    <t>A2MQYO</t>
+  </si>
+  <si>
+    <t>5309334ECMCMRPCT07BEB0FA35</t>
+  </si>
+  <si>
+    <t>C1F89FA4CMCMRPCT0874BAD8E1</t>
+  </si>
+  <si>
+    <t>EF1634CCCMCMRPCT0801555EC0</t>
+  </si>
+  <si>
+    <t>A2MQ2D</t>
+  </si>
+  <si>
+    <t>A2MQ2E</t>
+  </si>
+  <si>
+    <t>2023-08-23T15:32:00</t>
+  </si>
+  <si>
+    <t>2023-08-23T17:10:00</t>
+  </si>
+  <si>
+    <t>A2MQ3D</t>
+  </si>
+  <si>
+    <t>2023-08-22T01:14:00</t>
+  </si>
+  <si>
+    <t>2023-08-22T10:38:00</t>
+  </si>
+  <si>
+    <t>A2MQ3E</t>
+  </si>
+  <si>
+    <t>2023-08-22T13:18:00</t>
+  </si>
+  <si>
+    <t>2023-08-22T16:49:00</t>
+  </si>
+  <si>
+    <t>A2MQ3L</t>
+  </si>
+  <si>
+    <t>A2MQ3S</t>
+  </si>
+  <si>
+    <t>2023-08-24T04:51:00</t>
+  </si>
+  <si>
+    <t>2023-08-24T08:23:00</t>
+  </si>
+  <si>
+    <t>A2MQ4A</t>
+  </si>
+  <si>
+    <t>A2MQ4P</t>
+  </si>
+  <si>
+    <t>2302182807133</t>
+  </si>
+  <si>
+    <t>A2MQ42</t>
+  </si>
+  <si>
+    <t>2302182807134</t>
+  </si>
+  <si>
+    <t>A2MQ5H</t>
+  </si>
+  <si>
+    <t>2302182807135</t>
+  </si>
+  <si>
+    <t>A2MQ5T</t>
+  </si>
+  <si>
+    <t>2302182807136</t>
+  </si>
+  <si>
+    <t>A2MQ50</t>
+  </si>
+  <si>
+    <t>2023-08-23T16:54:00</t>
+  </si>
+  <si>
+    <t>2023-08-23T20:23:00</t>
+  </si>
+  <si>
+    <t>2302182807137</t>
+  </si>
+  <si>
+    <t>A2MRAH</t>
+  </si>
+  <si>
+    <t>2302182807138</t>
+  </si>
+  <si>
+    <t>A2MRAX</t>
+  </si>
+  <si>
+    <t>2302182807139</t>
+  </si>
+  <si>
+    <t>A2MRA2</t>
+  </si>
+  <si>
+    <t>2302182807140</t>
+  </si>
+  <si>
+    <t>A2MRBG</t>
+  </si>
+  <si>
+    <t>2023-08-24T07:47:00</t>
+  </si>
+  <si>
+    <t>2023-08-24T12:23:00</t>
+  </si>
+  <si>
+    <t>2023-08-24T14:02:00</t>
+  </si>
+  <si>
+    <t>2023-08-24T15:33:00</t>
+  </si>
+  <si>
+    <t>2302182807141</t>
+  </si>
+  <si>
+    <t>A2MRBP</t>
+  </si>
+  <si>
+    <t>2023-08-24T17:06:00</t>
+  </si>
+  <si>
+    <t>2023-08-24T18:37:00</t>
+  </si>
+  <si>
+    <t>2302182807142</t>
+  </si>
+  <si>
+    <t>A2MRDT</t>
+  </si>
+  <si>
+    <t>A2MRDV</t>
+  </si>
+  <si>
+    <t>A2MRDY</t>
+  </si>
+  <si>
+    <t>A2MRED</t>
+  </si>
+  <si>
+    <t>A2MREJ</t>
+  </si>
+  <si>
+    <t>A2MRES</t>
+  </si>
+  <si>
+    <t>A2MREX</t>
+  </si>
+  <si>
+    <t>A2MRFI</t>
+  </si>
+  <si>
+    <t>A2MRFX</t>
+  </si>
+  <si>
+    <t>A2MRGY</t>
+  </si>
+  <si>
+    <t>A2MRG5</t>
+  </si>
+  <si>
+    <t>A2PGGE</t>
+  </si>
+  <si>
+    <t>2302182807192</t>
+  </si>
+  <si>
+    <t>A2PNFL</t>
+  </si>
+  <si>
+    <t>AA2DB342CMCMRPCT052F39DE70</t>
+  </si>
+  <si>
+    <t>A1929E18CMCMRPCT06DFA232A0</t>
+  </si>
+  <si>
+    <t>7914A342CMCMRPCT05FAA95C7E</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="13">
     <font>
       <sz val="11"/>
@@ -2598,20 +2995,20 @@
   <dimension ref="A1:P15"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="52.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="52.81640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="18.453125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="9.453125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="10.453125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="10.453125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="10.453125"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="15.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2684,7 +3081,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="44" t="s">
-        <v>621</v>
+        <v>630</v>
       </c>
       <c r="I2" s="32" t="s">
         <v>211</v>
@@ -2701,7 +3098,7 @@
       <c r="M2" s="32"/>
       <c r="N2" s="32"/>
       <c r="O2" s="32" t="s">
-        <v>456</v>
+        <v>631</v>
       </c>
       <c r="P2" s="38"/>
     </row>
@@ -2773,7 +3170,7 @@
         <v>1</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>457</v>
+        <v>632</v>
       </c>
       <c r="I4" s="37" t="s">
         <v>354</v>
@@ -2810,7 +3207,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="37" t="s">
-        <v>458</v>
+        <v>633</v>
       </c>
       <c r="I5" s="32"/>
       <c r="J5" s="32"/>
@@ -2846,13 +3243,13 @@
   <dimension ref="A1:U22"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="49" customWidth="1"/>
-    <col min="10" max="10" width="8.81640625" style="25"/>
-    <col min="12" max="12" width="15.90625" customWidth="1"/>
-    <col min="17" max="17" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="49.0"/>
+    <col min="10" max="10" style="25" width="8.81640625"/>
+    <col min="12" max="12" customWidth="true" width="15.90625"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="13.90625"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="12.6328125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
@@ -2950,7 +3347,7 @@
       </c>
       <c r="J2" s="44"/>
       <c r="K2" s="44" t="s">
-        <v>468</v>
+        <v>657</v>
       </c>
       <c r="L2" s="44"/>
       <c r="M2" s="44"/>
@@ -2987,10 +3384,10 @@
         <v>0</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>482</v>
+        <v>749</v>
       </c>
       <c r="L3" s="44" t="s">
-        <v>483</v>
+        <v>750</v>
       </c>
       <c r="M3" s="44"/>
       <c r="N3" s="44"/>
@@ -3059,10 +3456,10 @@
       <c r="I5" s="44"/>
       <c r="J5" s="44"/>
       <c r="K5" s="44" t="s">
-        <v>485</v>
+        <v>673</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>486</v>
+        <v>674</v>
       </c>
       <c r="M5" s="44"/>
       <c r="N5" s="44" t="s">
@@ -3106,7 +3503,7 @@
       <c r="I6" s="44"/>
       <c r="J6" s="44"/>
       <c r="K6" s="44" t="s">
-        <v>487</v>
+        <v>675</v>
       </c>
       <c r="L6" s="44"/>
       <c r="M6" s="44"/>
@@ -3117,7 +3514,7 @@
         <v>242</v>
       </c>
       <c r="P6" s="44" t="s">
-        <v>488</v>
+        <v>676</v>
       </c>
       <c r="Q6" s="44"/>
       <c r="R6" s="44"/>
@@ -3151,10 +3548,10 @@
       <c r="I7" s="44"/>
       <c r="J7" s="44"/>
       <c r="K7" s="44" t="s">
-        <v>489</v>
+        <v>677</v>
       </c>
       <c r="L7" s="44" t="s">
-        <v>490</v>
+        <v>678</v>
       </c>
       <c r="M7" s="44"/>
       <c r="N7" s="44" t="s">
@@ -3164,13 +3561,13 @@
         <v>242</v>
       </c>
       <c r="P7" s="44" t="s">
-        <v>491</v>
+        <v>679</v>
       </c>
       <c r="Q7" s="47" t="s">
         <v>87</v>
       </c>
       <c r="R7" s="44" t="s">
-        <v>492</v>
+        <v>680</v>
       </c>
       <c r="S7" s="44"/>
       <c r="T7" s="44"/>
@@ -3206,10 +3603,10 @@
       </c>
       <c r="J8" s="44"/>
       <c r="K8" s="44" t="s">
-        <v>493</v>
+        <v>681</v>
       </c>
       <c r="L8" s="44" t="s">
-        <v>494</v>
+        <v>682</v>
       </c>
       <c r="M8" s="44"/>
       <c r="N8" s="44" t="s">
@@ -3247,7 +3644,7 @@
       <c r="I9" s="44"/>
       <c r="J9" s="44"/>
       <c r="K9" s="44" t="s">
-        <v>495</v>
+        <v>683</v>
       </c>
       <c r="L9" s="44"/>
       <c r="M9" s="44"/>
@@ -3286,10 +3683,10 @@
       <c r="I10" s="44"/>
       <c r="J10" s="44"/>
       <c r="K10" s="44" t="s">
-        <v>496</v>
+        <v>684</v>
       </c>
       <c r="L10" s="44" t="s">
-        <v>497</v>
+        <v>685</v>
       </c>
       <c r="M10" s="44"/>
       <c r="N10" s="44"/>
@@ -3325,10 +3722,10 @@
       <c r="I11" s="44"/>
       <c r="J11" s="44"/>
       <c r="K11" s="44" t="s">
-        <v>469</v>
+        <v>658</v>
       </c>
       <c r="L11" s="44" t="s">
-        <v>470</v>
+        <v>659</v>
       </c>
       <c r="M11" s="44"/>
       <c r="N11" s="44"/>
@@ -3364,10 +3761,10 @@
       <c r="I12" s="44"/>
       <c r="J12" s="44"/>
       <c r="K12" s="44" t="s">
-        <v>471</v>
+        <v>660</v>
       </c>
       <c r="L12" s="44" t="s">
-        <v>472</v>
+        <v>661</v>
       </c>
       <c r="M12" s="44"/>
       <c r="N12" s="44" t="s">
@@ -3407,10 +3804,10 @@
       <c r="I13" s="44"/>
       <c r="J13" s="44"/>
       <c r="K13" s="44" t="s">
-        <v>473</v>
+        <v>662</v>
       </c>
       <c r="L13" s="44" t="s">
-        <v>474</v>
+        <v>663</v>
       </c>
       <c r="M13" s="44"/>
       <c r="N13" s="44" t="s">
@@ -3485,10 +3882,10 @@
       <c r="I15" s="44"/>
       <c r="J15" s="44"/>
       <c r="K15" s="44" t="s">
-        <v>475</v>
+        <v>664</v>
       </c>
       <c r="L15" s="44" t="s">
-        <v>476</v>
+        <v>665</v>
       </c>
       <c r="M15" s="44"/>
       <c r="N15" s="44" t="s">
@@ -3528,7 +3925,7 @@
       <c r="I16" s="44"/>
       <c r="J16" s="44"/>
       <c r="K16" s="44" t="s">
-        <v>477</v>
+        <v>666</v>
       </c>
       <c r="L16" s="44"/>
       <c r="M16" s="44"/>
@@ -3567,7 +3964,7 @@
       <c r="I17" s="44"/>
       <c r="J17" s="44"/>
       <c r="K17" s="44" t="s">
-        <v>478</v>
+        <v>667</v>
       </c>
       <c r="L17" s="44"/>
       <c r="M17" s="44"/>
@@ -3610,7 +4007,7 @@
       </c>
       <c r="J18" s="44"/>
       <c r="K18" s="44" t="s">
-        <v>479</v>
+        <v>668</v>
       </c>
       <c r="L18" s="44"/>
       <c r="M18" s="44"/>
@@ -3649,7 +4046,7 @@
       <c r="I19" s="44"/>
       <c r="J19" s="44"/>
       <c r="K19" s="44" t="s">
-        <v>480</v>
+        <v>669</v>
       </c>
       <c r="L19" s="44"/>
       <c r="M19" s="44"/>
@@ -3688,7 +4085,7 @@
       <c r="I20" s="44"/>
       <c r="J20" s="44"/>
       <c r="K20" s="44" t="s">
-        <v>481</v>
+        <v>670</v>
       </c>
       <c r="L20" s="44"/>
       <c r="M20" s="44"/>
@@ -3727,7 +4124,7 @@
       <c r="I21" s="44"/>
       <c r="J21" s="44"/>
       <c r="K21" s="44" t="s">
-        <v>484</v>
+        <v>671</v>
       </c>
       <c r="L21" s="44"/>
       <c r="M21" s="44"/>
@@ -3774,7 +4171,7 @@
       </c>
       <c r="J22" s="44"/>
       <c r="K22" s="44" t="s">
-        <v>573</v>
+        <v>672</v>
       </c>
       <c r="L22" s="44"/>
       <c r="M22" s="44"/>
@@ -3804,16 +4201,16 @@
   <dimension ref="A1:N4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="32.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.54296875" style="29" customWidth="1"/>
-    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.81640625" customWidth="1"/>
-    <col min="6" max="6" width="14.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="14.36328125" style="29" customWidth="1"/>
-    <col min="12" max="12" width="30.36328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.453125" customWidth="1"/>
-    <col min="14" max="14" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="32.90625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="3" max="3" customWidth="true" style="29" width="17.54296875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="5" max="5" customWidth="true" width="13.81640625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="14.36328125"/>
+    <col min="7" max="11" customWidth="true" style="29" width="14.36328125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="30.36328125"/>
+    <col min="13" max="13" customWidth="true" width="8.453125"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="10.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -3895,10 +4292,10 @@
         <v>1</v>
       </c>
       <c r="L2" s="34" t="s">
-        <v>571</v>
+        <v>752</v>
       </c>
       <c r="M2" s="34" t="s">
-        <v>570</v>
+        <v>751</v>
       </c>
       <c r="N2" s="32"/>
     </row>
@@ -3937,7 +4334,7 @@
         <v>6</v>
       </c>
       <c r="L3" s="34" t="s">
-        <v>503</v>
+        <v>753</v>
       </c>
       <c r="M3" s="34" t="s">
         <v>264</v>
@@ -3981,7 +4378,7 @@
         <v>6</v>
       </c>
       <c r="L4" s="34" t="s">
-        <v>504</v>
+        <v>754</v>
       </c>
       <c r="M4" s="32"/>
       <c r="N4" s="32" t="s">
@@ -4001,17 +4398,17 @@
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="21.81640625" style="29" customWidth="1"/>
-    <col min="2" max="2" width="16.54296875" style="29" customWidth="1"/>
-    <col min="3" max="3" width="19.90625" style="29" customWidth="1"/>
-    <col min="4" max="4" width="18.81640625" style="29" customWidth="1"/>
-    <col min="5" max="6" width="12.90625" style="29" customWidth="1"/>
-    <col min="7" max="7" width="15" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.90625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.81640625" style="29"/>
-    <col min="10" max="10" width="17.90625" style="29" customWidth="1"/>
-    <col min="11" max="11" width="14.1796875" style="29" customWidth="1"/>
-    <col min="12" max="16384" width="8.81640625" style="29"/>
+    <col min="1" max="1" customWidth="true" style="29" width="21.81640625"/>
+    <col min="2" max="2" customWidth="true" style="29" width="16.54296875"/>
+    <col min="3" max="3" customWidth="true" style="29" width="19.90625"/>
+    <col min="4" max="4" customWidth="true" style="29" width="18.81640625"/>
+    <col min="5" max="6" customWidth="true" style="29" width="12.90625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="15.0"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="11.90625"/>
+    <col min="9" max="9" style="29" width="8.81640625"/>
+    <col min="10" max="10" customWidth="true" style="29" width="17.90625"/>
+    <col min="11" max="11" customWidth="true" style="29" width="14.1796875"/>
+    <col min="12" max="16384" style="29" width="8.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -4132,13 +4529,13 @@
         <v>12</v>
       </c>
       <c r="I5" s="44" t="s">
-        <v>498</v>
+        <v>686</v>
       </c>
       <c r="J5" s="44" t="s">
-        <v>499</v>
+        <v>687</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>500</v>
+        <v>688</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -4167,10 +4564,10 @@
         <v>12</v>
       </c>
       <c r="I6" s="44" t="s">
-        <v>501</v>
+        <v>689</v>
       </c>
       <c r="J6" s="44" t="s">
-        <v>502</v>
+        <v>690</v>
       </c>
       <c r="K6" s="44"/>
     </row>
@@ -4187,12 +4584,12 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="42.1796875" style="29" customWidth="1"/>
-    <col min="2" max="2" width="15.81640625" style="29" customWidth="1"/>
-    <col min="3" max="3" width="17.81640625" style="29" customWidth="1"/>
-    <col min="4" max="4" width="16.81640625" style="29" customWidth="1"/>
-    <col min="5" max="5" width="15.6328125" style="29" customWidth="1"/>
-    <col min="6" max="16384" width="8.81640625" style="29"/>
+    <col min="1" max="1" customWidth="true" style="29" width="42.1796875"/>
+    <col min="2" max="2" customWidth="true" style="29" width="15.81640625"/>
+    <col min="3" max="3" customWidth="true" style="29" width="17.81640625"/>
+    <col min="4" max="4" customWidth="true" style="29" width="16.81640625"/>
+    <col min="5" max="5" customWidth="true" style="29" width="15.6328125"/>
+    <col min="6" max="16384" style="29" width="8.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4311,28 +4708,28 @@
   <dimension ref="A1:AB6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="51.81640625" customWidth="1"/>
-    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="51.81640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="9.453125"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="18.453125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="14.453125"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="18.453125"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="18.453125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="12.08984375"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="15.36328125"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="12.08984375"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" width="15.36328125"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" width="12.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28">
@@ -4450,16 +4847,16 @@
         <v>45</v>
       </c>
       <c r="J2" s="44" t="s">
-        <v>542</v>
+        <v>738</v>
       </c>
       <c r="K2" s="44" t="s">
-        <v>452</v>
+        <v>625</v>
       </c>
       <c r="L2" s="44" t="s">
         <v>207</v>
       </c>
       <c r="M2" s="44" t="s">
-        <v>453</v>
+        <v>626</v>
       </c>
       <c r="N2" s="44" t="s">
         <v>208</v>
@@ -4468,13 +4865,13 @@
         <v>12</v>
       </c>
       <c r="P2" s="44" t="s">
-        <v>454</v>
+        <v>627</v>
       </c>
       <c r="Q2" s="44" t="s">
         <v>62</v>
       </c>
       <c r="R2" s="44" t="s">
-        <v>455</v>
+        <v>628</v>
       </c>
       <c r="S2" s="44" t="s">
         <v>12</v>
@@ -4520,16 +4917,16 @@
         <v>45</v>
       </c>
       <c r="J3" s="44" t="s">
-        <v>505</v>
+        <v>696</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>452</v>
+        <v>625</v>
       </c>
       <c r="L3" s="44" t="s">
         <v>207</v>
       </c>
       <c r="M3" s="44" t="s">
-        <v>453</v>
+        <v>626</v>
       </c>
       <c r="N3" s="44" t="s">
         <v>208</v>
@@ -4538,13 +4935,13 @@
         <v>12</v>
       </c>
       <c r="P3" s="44" t="s">
-        <v>506</v>
+        <v>697</v>
       </c>
       <c r="Q3" s="44" t="s">
         <v>239</v>
       </c>
       <c r="R3" s="44" t="s">
-        <v>507</v>
+        <v>698</v>
       </c>
       <c r="S3" s="44" t="s">
         <v>12</v>
@@ -4598,16 +4995,16 @@
       <c r="H4" s="44"/>
       <c r="I4" s="44"/>
       <c r="J4" s="44" t="s">
-        <v>511</v>
+        <v>702</v>
       </c>
       <c r="K4" s="44" t="s">
-        <v>512</v>
+        <v>703</v>
       </c>
       <c r="L4" s="44" t="s">
         <v>328</v>
       </c>
       <c r="M4" s="44" t="s">
-        <v>513</v>
+        <v>704</v>
       </c>
       <c r="N4" s="44" t="s">
         <v>209</v>
@@ -4650,16 +5047,16 @@
       <c r="H5" s="44"/>
       <c r="I5" s="44"/>
       <c r="J5" s="44" t="s">
-        <v>514</v>
+        <v>705</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>512</v>
+        <v>703</v>
       </c>
       <c r="L5" s="44" t="s">
         <v>328</v>
       </c>
       <c r="M5" s="44" t="s">
-        <v>513</v>
+        <v>704</v>
       </c>
       <c r="N5" s="44" t="s">
         <v>209</v>
@@ -4710,16 +5107,16 @@
         <v>45</v>
       </c>
       <c r="J6" s="44" t="s">
-        <v>508</v>
+        <v>699</v>
       </c>
       <c r="K6" s="44" t="s">
-        <v>509</v>
+        <v>700</v>
       </c>
       <c r="L6" s="44" t="s">
         <v>207</v>
       </c>
       <c r="M6" s="44" t="s">
-        <v>510</v>
+        <v>701</v>
       </c>
       <c r="N6" s="44" t="s">
         <v>208</v>
@@ -4755,10 +5152,10 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="76.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="76.1796875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="13.453125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="12.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4843,12 +5240,12 @@
   <dimension ref="A1:E15"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="68.08984375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.54296875" style="29" customWidth="1"/>
-    <col min="3" max="3" width="14.81640625" style="29" customWidth="1"/>
-    <col min="4" max="4" width="11.81640625" style="29" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.1796875" style="29" customWidth="1"/>
-    <col min="6" max="16384" width="8.81640625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="68.08984375"/>
+    <col min="2" max="2" customWidth="true" style="29" width="12.54296875"/>
+    <col min="3" max="3" customWidth="true" style="29" width="14.81640625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="29" width="11.81640625"/>
+    <col min="5" max="5" customWidth="true" style="29" width="18.1796875"/>
+    <col min="6" max="16384" style="29" width="8.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -5095,8 +5492,8 @@
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="12.54296875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -5136,11 +5533,11 @@
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="33.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="33.54296875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="13.453125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="12.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -5190,7 +5587,7 @@
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="21.81640625" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="21.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -5295,31 +5692,31 @@
   <dimension ref="A1:AG4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="49.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="49.81640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="4.81640625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="4.453125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="4.453125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="4.453125"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="4.453125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="4.453125"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="4.453125"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="4.453125"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" width="9.7265625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33">
@@ -5624,25 +6021,25 @@
   <dimension ref="A1:AD9"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="33" customWidth="1"/>
-    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.36328125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="33.0"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="18.36328125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="12.08984375"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="18.36328125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="15.36328125"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="13.90625"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="12.08984375"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="15.36328125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="14.36328125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="12.08984375"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="15.36328125"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" width="12.08984375"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="17.54296875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30">
@@ -5761,16 +6158,16 @@
       <c r="I2" s="44"/>
       <c r="J2" s="44"/>
       <c r="K2" s="44" t="s">
-        <v>515</v>
+        <v>706</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>516</v>
+        <v>707</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>325</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>517</v>
+        <v>708</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>209</v>
@@ -5825,7 +6222,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>518</v>
+        <v>709</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>312</v>
@@ -5965,16 +6362,16 @@
         <v>2</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>519</v>
+        <v>712</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>516</v>
+        <v>707</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>325</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>517</v>
+        <v>708</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>209</v>
@@ -5983,7 +6380,7 @@
         <v>12</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>520</v>
+        <v>713</v>
       </c>
       <c r="R5" s="15" t="s">
         <v>44</v>
@@ -6226,11 +6623,11 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="35.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="35.1796875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="11.54296875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="13.453125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -6314,9 +6711,9 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="33.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="33.54296875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="13.453125"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="9.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -6372,9 +6769,9 @@
   <dimension ref="A1:AC4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="46.6328125" customWidth="1"/>
-    <col min="5" max="5" width="6.1796875" customWidth="1"/>
-    <col min="29" max="29" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="46.6328125"/>
+    <col min="5" max="5" customWidth="true" width="6.1796875"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="13.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -6502,16 +6899,16 @@
       <c r="U2" s="44"/>
       <c r="V2" s="44"/>
       <c r="W2" s="44" t="s">
-        <v>524</v>
+        <v>714</v>
       </c>
       <c r="X2" s="44" t="s">
-        <v>516</v>
+        <v>707</v>
       </c>
       <c r="Y2" s="44" t="s">
         <v>325</v>
       </c>
       <c r="Z2" s="44" t="s">
-        <v>517</v>
+        <v>708</v>
       </c>
       <c r="AA2" s="44" t="s">
         <v>209</v>
@@ -6520,7 +6917,7 @@
         <v>12</v>
       </c>
       <c r="AC2" s="44" t="s">
-        <v>525</v>
+        <v>715</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -6638,16 +7035,16 @@
       <c r="U4" s="44"/>
       <c r="V4" s="44"/>
       <c r="W4" s="44" t="s">
-        <v>526</v>
+        <v>716</v>
       </c>
       <c r="X4" s="44" t="s">
-        <v>516</v>
+        <v>707</v>
       </c>
       <c r="Y4" s="44" t="s">
         <v>325</v>
       </c>
       <c r="Z4" s="44" t="s">
-        <v>517</v>
+        <v>708</v>
       </c>
       <c r="AA4" s="44" t="s">
         <v>209</v>
@@ -6656,7 +7053,7 @@
         <v>12</v>
       </c>
       <c r="AC4" s="44" t="s">
-        <v>527</v>
+        <v>717</v>
       </c>
     </row>
   </sheetData>
@@ -6672,14 +7069,14 @@
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="63.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="63.81640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="10.81640625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="19.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="15.54296875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="8" max="9" bestFit="true" customWidth="true" width="19.453125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -6814,24 +7211,24 @@
   <dimension ref="A1:R6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.6328125" customWidth="1"/>
-    <col min="18" max="18" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="12.0"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="9.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="6.1796875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="13.81640625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="7.453125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="18.453125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="18.453125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="17" max="17" customWidth="true" width="17.6328125"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="13.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -6914,16 +7311,16 @@
       <c r="I2" s="44"/>
       <c r="J2" s="44"/>
       <c r="K2" s="44" t="s">
-        <v>528</v>
+        <v>718</v>
       </c>
       <c r="L2" s="44" t="s">
-        <v>529</v>
+        <v>719</v>
       </c>
       <c r="M2" s="44" t="s">
         <v>329</v>
       </c>
       <c r="N2" s="44" t="s">
-        <v>530</v>
+        <v>720</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>209</v>
@@ -6932,7 +7329,7 @@
         <v>12</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>531</v>
+        <v>721</v>
       </c>
       <c r="R2" s="3"/>
     </row>
@@ -7008,16 +7405,16 @@
       <c r="I4" s="44"/>
       <c r="J4" s="44"/>
       <c r="K4" s="44" t="s">
-        <v>563</v>
+        <v>722</v>
       </c>
       <c r="L4" s="44" t="s">
-        <v>452</v>
+        <v>625</v>
       </c>
       <c r="M4" s="44" t="s">
         <v>207</v>
       </c>
       <c r="N4" s="44" t="s">
-        <v>453</v>
+        <v>626</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>208</v>
@@ -7026,7 +7423,7 @@
         <v>12</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>564</v>
+        <v>723</v>
       </c>
       <c r="R4" s="3"/>
     </row>
@@ -7054,16 +7451,16 @@
       <c r="I5" s="44"/>
       <c r="J5" s="44"/>
       <c r="K5" s="44" t="s">
-        <v>565</v>
+        <v>724</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>452</v>
+        <v>625</v>
       </c>
       <c r="M5" s="44" t="s">
         <v>207</v>
       </c>
       <c r="N5" s="44" t="s">
-        <v>453</v>
+        <v>626</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>208</v>
@@ -7072,7 +7469,7 @@
         <v>12</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>566</v>
+        <v>725</v>
       </c>
       <c r="R5" s="3"/>
     </row>
@@ -7100,16 +7497,16 @@
       <c r="I6" s="44"/>
       <c r="J6" s="44"/>
       <c r="K6" s="44" t="s">
-        <v>567</v>
+        <v>726</v>
       </c>
       <c r="L6" s="44" t="s">
-        <v>452</v>
+        <v>625</v>
       </c>
       <c r="M6" s="44" t="s">
         <v>207</v>
       </c>
       <c r="N6" s="44" t="s">
-        <v>453</v>
+        <v>626</v>
       </c>
       <c r="O6" s="3" t="s">
         <v>208</v>
@@ -7118,7 +7515,7 @@
         <v>12</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>568</v>
+        <v>727</v>
       </c>
       <c r="R6" s="3"/>
     </row>
@@ -7136,27 +7533,27 @@
   <dimension ref="A1:U13"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="44.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.6328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.6328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.6328125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.6328125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="44.08984375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.36328125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="9.1796875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="6.1796875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="17.36328125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="9.1796875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="6.1796875"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="8.54296875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="18.6328125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="18.6328125"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="18.6328125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="18.6328125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="14.08984375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
@@ -7253,16 +7650,16 @@
         <v>163</v>
       </c>
       <c r="J2" s="56" t="s">
-        <v>532</v>
+        <v>728</v>
       </c>
       <c r="K2" s="44" t="s">
-        <v>533</v>
+        <v>729</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>215</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>534</v>
+        <v>730</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>12</v>
@@ -7271,13 +7668,13 @@
         <v>216</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>535</v>
+        <v>731</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>217</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>536</v>
+        <v>732</v>
       </c>
       <c r="S2" s="3" t="s">
         <v>216</v>
@@ -7286,7 +7683,7 @@
         <v>163</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>537</v>
+        <v>733</v>
       </c>
     </row>
     <row r="3" spans="1:21">
@@ -7318,16 +7715,16 @@
         <v>163</v>
       </c>
       <c r="J3" s="56" t="s">
-        <v>538</v>
+        <v>734</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>533</v>
+        <v>729</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>215</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>534</v>
+        <v>730</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>12</v>
@@ -7336,13 +7733,13 @@
         <v>216</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>539</v>
+        <v>735</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>341</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>540</v>
+        <v>736</v>
       </c>
       <c r="S3" s="3" t="s">
         <v>216</v>
@@ -7351,7 +7748,7 @@
         <v>163</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>541</v>
+        <v>737</v>
       </c>
     </row>
     <row r="4" spans="1:21">
@@ -7531,8 +7928,8 @@
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="32.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="32.1796875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -7580,7 +7977,7 @@
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="18.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -7641,21 +8038,21 @@
   <dimension ref="A1:N19"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="24.90625" style="29" customWidth="1"/>
-    <col min="2" max="2" width="14" style="29" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" style="29" customWidth="1"/>
-    <col min="4" max="4" width="9.54296875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10.36328125" style="29" customWidth="1"/>
-    <col min="6" max="6" width="9.36328125" style="29" customWidth="1"/>
-    <col min="7" max="7" width="9.7265625" style="29" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" style="29" customWidth="1"/>
-    <col min="9" max="9" width="8.81640625" style="29" customWidth="1"/>
-    <col min="10" max="10" width="8.08984375" style="41" customWidth="1"/>
-    <col min="11" max="11" width="10" style="29" customWidth="1"/>
-    <col min="12" max="12" width="7.81640625" style="29" customWidth="1"/>
-    <col min="13" max="13" width="9" style="29" customWidth="1"/>
-    <col min="14" max="14" width="19.453125" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.81640625" style="29"/>
+    <col min="1" max="1" customWidth="true" style="29" width="24.90625"/>
+    <col min="2" max="2" customWidth="true" style="29" width="14.0"/>
+    <col min="3" max="3" customWidth="true" style="29" width="11.81640625"/>
+    <col min="4" max="4" customWidth="true" style="29" width="9.54296875"/>
+    <col min="5" max="5" customWidth="true" style="29" width="10.36328125"/>
+    <col min="6" max="6" customWidth="true" style="29" width="9.36328125"/>
+    <col min="7" max="7" customWidth="true" style="29" width="9.7265625"/>
+    <col min="8" max="8" customWidth="true" style="29" width="10.453125"/>
+    <col min="9" max="9" customWidth="true" style="29" width="8.81640625"/>
+    <col min="10" max="10" customWidth="true" style="41" width="8.08984375"/>
+    <col min="11" max="11" customWidth="true" style="29" width="10.0"/>
+    <col min="12" max="12" customWidth="true" style="29" width="7.81640625"/>
+    <col min="13" max="13" customWidth="true" style="29" width="9.0"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="19.453125"/>
+    <col min="15" max="16384" style="29" width="8.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -8425,14 +8822,14 @@
   <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="39.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="39.453125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="21.81640625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="9.453125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="6.453125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="18.453125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -8487,10 +8884,10 @@
         <v>50</v>
       </c>
       <c r="H2" s="44" t="s">
-        <v>459</v>
+        <v>636</v>
       </c>
       <c r="I2" s="44" t="s">
-        <v>460</v>
+        <v>637</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -8536,18 +8933,18 @@
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="32.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.453125" customWidth="1"/>
-    <col min="5" max="5" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.08984375" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="32.1796875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="4" max="4" customWidth="true" width="15.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="17.36328125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="13" max="13" customWidth="true" width="15.08984375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -8720,7 +9117,7 @@
       <c r="H6" s="44"/>
       <c r="I6" s="44"/>
       <c r="J6" s="44" t="s">
-        <v>574</v>
+        <v>739</v>
       </c>
       <c r="K6" s="44"/>
       <c r="L6" s="44"/>
@@ -8739,16 +9136,16 @@
   <dimension ref="A1:K4"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.90625" style="29" customWidth="1"/>
-    <col min="2" max="2" width="11.81640625" style="29" customWidth="1"/>
-    <col min="3" max="3" width="13" style="29" customWidth="1"/>
-    <col min="4" max="4" width="16.54296875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="15.81640625" style="29" customWidth="1"/>
-    <col min="6" max="6" width="8.81640625" style="29"/>
-    <col min="7" max="7" width="17.81640625" style="29" customWidth="1"/>
-    <col min="8" max="8" width="15.453125" style="29" customWidth="1"/>
-    <col min="9" max="9" width="11.54296875" style="29" customWidth="1"/>
-    <col min="10" max="16384" width="8.81640625" style="29"/>
+    <col min="1" max="1" customWidth="true" style="29" width="17.90625"/>
+    <col min="2" max="2" customWidth="true" style="29" width="11.81640625"/>
+    <col min="3" max="3" customWidth="true" style="29" width="13.0"/>
+    <col min="4" max="4" customWidth="true" style="29" width="16.54296875"/>
+    <col min="5" max="5" customWidth="true" style="29" width="15.81640625"/>
+    <col min="6" max="6" style="29" width="8.81640625"/>
+    <col min="7" max="7" customWidth="true" style="29" width="17.81640625"/>
+    <col min="8" max="8" customWidth="true" style="29" width="15.453125"/>
+    <col min="9" max="9" customWidth="true" style="29" width="11.54296875"/>
+    <col min="10" max="16384" style="29" width="8.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -8803,7 +9200,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>618</v>
+        <v>740</v>
       </c>
       <c r="G2" s="32">
         <v>2</v>
@@ -8834,7 +9231,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>350</v>
+        <v>741</v>
       </c>
       <c r="G3" s="32"/>
       <c r="H3" s="32"/>
@@ -8863,7 +9260,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>351</v>
+        <v>742</v>
       </c>
       <c r="G4" s="32"/>
       <c r="H4" s="32"/>
@@ -8884,19 +9281,19 @@
   <dimension ref="A1:M3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="19.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="19.90625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="17.36328125"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="17.36328125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="4.453125"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="17.36328125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="14.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -8999,20 +9396,20 @@
   <dimension ref="A1:M4"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="25.81640625" style="41" customWidth="1"/>
-    <col min="2" max="2" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="41" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15" style="41" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.453125" style="41" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.1796875" style="41" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.90625" style="41"/>
+    <col min="1" max="1" customWidth="true" style="41" width="25.81640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="41" width="15.0"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="41" width="15.0"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="41" width="4.453125"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="41" width="14.1796875"/>
+    <col min="14" max="16384" style="41" width="8.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -9138,21 +9535,21 @@
   <dimension ref="A1:O5"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="20.1796875" style="41" customWidth="1"/>
-    <col min="2" max="2" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="41" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="17.36328125" style="41" customWidth="1"/>
-    <col min="8" max="8" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15" style="41" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.453125" style="41" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.1796875" style="41" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.90625" style="41"/>
+    <col min="1" max="1" customWidth="true" style="41" width="20.1796875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="41" width="15.0"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
+    <col min="6" max="7" customWidth="true" style="41" width="17.36328125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="41" width="15.0"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="41" width="4.453125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="41" width="14.1796875"/>
+    <col min="16" max="16384" style="41" width="8.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -9339,22 +9736,22 @@
   <dimension ref="A1:O10"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="28.36328125" style="41" customWidth="1"/>
-    <col min="2" max="2" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="41" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.81640625" style="41" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.08984375" style="41" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15" style="41" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.08984375" style="41" customWidth="1"/>
-    <col min="13" max="13" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.1796875" style="41" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.90625" style="41"/>
+    <col min="1" max="1" customWidth="true" style="41" width="28.36328125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="41" width="15.0"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="41" width="16.81640625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="41" width="11.08984375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="41" width="15.0"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
+    <col min="12" max="12" customWidth="true" style="41" width="13.08984375"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="41" width="14.1796875"/>
+    <col min="16" max="16384" style="41" width="8.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -9469,7 +9866,7 @@
       </c>
       <c r="G4" s="44"/>
       <c r="H4" s="44" t="s">
-        <v>545</v>
+        <v>743</v>
       </c>
       <c r="I4" s="44" t="s">
         <v>390</v>
@@ -9506,7 +9903,7 @@
       </c>
       <c r="G5" s="44"/>
       <c r="H5" s="44" t="s">
-        <v>546</v>
+        <v>744</v>
       </c>
       <c r="I5" s="44" t="s">
         <v>390</v>
@@ -9654,11 +10051,11 @@
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="24" style="41" customWidth="1"/>
-    <col min="2" max="2" width="11.453125" style="41" customWidth="1"/>
-    <col min="3" max="3" width="8.90625" style="41"/>
-    <col min="4" max="4" width="19.6328125" style="41" customWidth="1"/>
-    <col min="5" max="16384" width="8.90625" style="41"/>
+    <col min="1" max="1" customWidth="true" style="41" width="24.0"/>
+    <col min="2" max="2" customWidth="true" style="41" width="11.453125"/>
+    <col min="3" max="3" style="41" width="8.90625"/>
+    <col min="4" max="4" customWidth="true" style="41" width="19.6328125"/>
+    <col min="5" max="16384" style="41" width="8.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9702,12 +10099,12 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="32.1796875" style="41" customWidth="1"/>
-    <col min="2" max="2" width="14" style="41" customWidth="1"/>
-    <col min="3" max="3" width="16.6328125" style="41" customWidth="1"/>
-    <col min="4" max="4" width="17.6328125" style="41" customWidth="1"/>
-    <col min="5" max="5" width="11.81640625" style="41" customWidth="1"/>
-    <col min="6" max="16384" width="8.90625" style="41"/>
+    <col min="1" max="1" customWidth="true" style="41" width="32.1796875"/>
+    <col min="2" max="2" customWidth="true" style="41" width="14.0"/>
+    <col min="3" max="3" customWidth="true" style="41" width="16.6328125"/>
+    <col min="4" max="4" customWidth="true" style="41" width="17.6328125"/>
+    <col min="5" max="5" customWidth="true" style="41" width="11.81640625"/>
+    <col min="6" max="16384" style="41" width="8.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -9791,11 +10188,11 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="38.1796875" style="41" customWidth="1"/>
-    <col min="2" max="2" width="13.54296875" style="41" customWidth="1"/>
-    <col min="3" max="3" width="15.54296875" style="41" customWidth="1"/>
-    <col min="4" max="4" width="19" style="41" customWidth="1"/>
-    <col min="5" max="16384" width="8.90625" style="41"/>
+    <col min="1" max="1" customWidth="true" style="41" width="38.1796875"/>
+    <col min="2" max="2" customWidth="true" style="41" width="13.54296875"/>
+    <col min="3" max="3" customWidth="true" style="41" width="15.54296875"/>
+    <col min="4" max="4" customWidth="true" style="41" width="19.0"/>
+    <col min="5" max="16384" style="41" width="8.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -9918,21 +10315,21 @@
   <dimension ref="A1:N5"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="30.90625" style="41" customWidth="1"/>
-    <col min="2" max="2" width="17.81640625" style="41" customWidth="1"/>
-    <col min="3" max="3" width="16.453125" style="41" customWidth="1"/>
-    <col min="4" max="4" width="16.08984375" style="41" customWidth="1"/>
-    <col min="5" max="5" width="12" style="41" customWidth="1"/>
-    <col min="6" max="6" width="18.08984375" style="41" customWidth="1"/>
-    <col min="7" max="7" width="15.08984375" style="41" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" style="41" customWidth="1"/>
-    <col min="9" max="9" width="10.81640625" style="41" customWidth="1"/>
-    <col min="10" max="10" width="8.90625" style="41"/>
-    <col min="11" max="11" width="13.1796875" style="41" customWidth="1"/>
-    <col min="12" max="12" width="12.6328125" style="41" customWidth="1"/>
-    <col min="13" max="13" width="14.08984375" style="41" customWidth="1"/>
-    <col min="14" max="14" width="14.36328125" style="41" customWidth="1"/>
-    <col min="15" max="16384" width="8.90625" style="41"/>
+    <col min="1" max="1" customWidth="true" style="41" width="30.90625"/>
+    <col min="2" max="2" customWidth="true" style="41" width="17.81640625"/>
+    <col min="3" max="3" customWidth="true" style="41" width="16.453125"/>
+    <col min="4" max="4" customWidth="true" style="41" width="16.08984375"/>
+    <col min="5" max="5" customWidth="true" style="41" width="12.0"/>
+    <col min="6" max="6" customWidth="true" style="41" width="18.08984375"/>
+    <col min="7" max="7" customWidth="true" style="41" width="15.08984375"/>
+    <col min="8" max="8" customWidth="true" style="41" width="10.453125"/>
+    <col min="9" max="9" customWidth="true" style="41" width="10.81640625"/>
+    <col min="10" max="10" style="41" width="8.90625"/>
+    <col min="11" max="11" customWidth="true" style="41" width="13.1796875"/>
+    <col min="12" max="12" customWidth="true" style="41" width="12.6328125"/>
+    <col min="13" max="13" customWidth="true" style="41" width="14.08984375"/>
+    <col min="14" max="14" customWidth="true" style="41" width="14.36328125"/>
+    <col min="15" max="16384" style="41" width="8.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -10008,7 +10405,7 @@
         <v>212</v>
       </c>
       <c r="J2" s="44" t="s">
-        <v>549</v>
+        <v>748</v>
       </c>
       <c r="K2" s="44">
         <v>2</v>
@@ -10134,11 +10531,11 @@
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="39.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="39.453125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="13.54296875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="7.81640625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="9.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -10206,10 +10603,10 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="57.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="57.453125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="15.54296875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="7.81640625"/>
+    <col min="4" max="5" bestFit="true" customWidth="true" width="11.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -10328,28 +10725,28 @@
   <dimension ref="A1:V15"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="50" style="25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.36328125" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.08984375" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.36328125" style="25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.1796875" style="25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.453125" style="25" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="8.81640625" style="25"/>
-    <col min="9" max="9" width="10.453125" style="25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.6328125" style="25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.453125" style="25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.1796875" style="25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.453125" style="25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.1796875" style="25" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13" style="25" customWidth="1"/>
-    <col min="16" max="16" width="10.1796875" style="25" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.453125" style="25" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.1796875" style="25" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.6328125" style="25" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.6328125" style="25" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.1796875" style="25" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.6328125" style="25" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="8.81640625" style="25"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="25" width="50.0"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="25" width="18.36328125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="25" width="12.08984375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="25" width="15.36328125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="25" width="12.1796875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="25" width="9.453125"/>
+    <col min="7" max="8" style="25" width="8.81640625"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="25" width="10.453125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="25" width="12.6328125"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="25" width="10.453125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="25" width="11.1796875"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="25" width="10.453125"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="25" width="8.1796875"/>
+    <col min="15" max="15" customWidth="true" style="25" width="13.0"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="25" width="10.1796875"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="25" width="10.453125"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="25" width="9.1796875"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="25" width="11.6328125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="25" width="12.6328125"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="25" width="11.1796875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="25" width="12.6328125"/>
+    <col min="23" max="16384" style="25" width="8.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
@@ -10460,7 +10857,7 @@
       <c r="M2" s="32"/>
       <c r="N2" s="32"/>
       <c r="O2" s="32" t="s">
-        <v>462</v>
+        <v>641</v>
       </c>
       <c r="P2" s="32"/>
       <c r="Q2" s="32" t="s">
@@ -10605,7 +11002,7 @@
         <v>15</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>575</v>
+        <v>642</v>
       </c>
       <c r="I6" s="32" t="s">
         <v>390</v>
@@ -10653,7 +11050,7 @@
         <v>19</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>463</v>
+        <v>646</v>
       </c>
       <c r="I7" s="32" t="s">
         <v>363</v>
@@ -10771,7 +11168,7 @@
       </c>
       <c r="G10" s="56"/>
       <c r="H10" s="32" t="s">
-        <v>551</v>
+        <v>643</v>
       </c>
       <c r="I10" s="32"/>
       <c r="J10" s="32" t="s">
@@ -10819,7 +11216,7 @@
         <v>15</v>
       </c>
       <c r="H11" s="32" t="s">
-        <v>622</v>
+        <v>640</v>
       </c>
       <c r="I11" s="32" t="s">
         <v>211</v>
@@ -10871,7 +11268,7 @@
       </c>
       <c r="G12" s="56"/>
       <c r="H12" s="32" t="s">
-        <v>552</v>
+        <v>644</v>
       </c>
       <c r="I12" s="32" t="s">
         <v>379</v>
@@ -10959,7 +11356,7 @@
       </c>
       <c r="G14" s="56"/>
       <c r="H14" s="32" t="s">
-        <v>576</v>
+        <v>645</v>
       </c>
       <c r="I14" s="32" t="s">
         <v>244</v>
@@ -11009,7 +11406,7 @@
         <v>15</v>
       </c>
       <c r="H15" s="32" t="s">
-        <v>461</v>
+        <v>639</v>
       </c>
       <c r="I15" s="32" t="s">
         <v>370</v>
@@ -11044,29 +11441,29 @@
   <dimension ref="A1:AB7"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="44.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="44.81640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.81640625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="8.1796875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="10.453125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="13.54296875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="17.81640625"/>
+    <col min="11" max="12" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="18.1796875"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="7.81640625"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="8.1796875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="14.1796875"/>
+    <col min="27" max="28" bestFit="true" customWidth="true" width="12.81640625"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="14.1796875"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="12.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28">
@@ -11498,9 +11895,9 @@
   <dimension ref="A1:W17"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="54.36328125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="54.36328125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="13.90625"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="13.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -11603,10 +12000,10 @@
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
       <c r="R2" s="3" t="s">
-        <v>464</v>
+        <v>647</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>465</v>
+        <v>648</v>
       </c>
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
@@ -11865,10 +12262,10 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3" t="s">
-        <v>466</v>
+        <v>651</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>467</v>
+        <v>652</v>
       </c>
       <c r="T8" s="3">
         <v>0</v>
@@ -11914,10 +12311,10 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3" t="s">
-        <v>554</v>
+        <v>653</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>555</v>
+        <v>654</v>
       </c>
       <c r="T9" s="3"/>
       <c r="U9" s="3">
@@ -11967,10 +12364,10 @@
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3" t="s">
-        <v>556</v>
+        <v>655</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>557</v>
+        <v>656</v>
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
@@ -12193,10 +12590,10 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3" t="s">
-        <v>558</v>
+        <v>649</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>559</v>
+        <v>650</v>
       </c>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
@@ -12251,16 +12648,16 @@
   <dimension ref="A1:S20"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="53.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="12.1796875" customWidth="1"/>
-    <col min="8" max="8" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="53.81640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="3" max="4" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="5" max="7" customWidth="true" width="12.1796875"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="12.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19">

--- a/src/test/java/TestData/Scenario_TestData.xlsx
+++ b/src/test/java/TestData/Scenario_TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Copa_SHD_WebServices\src\test\java\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57DFA7A6-8FDB-4B06-9E71-BE2267789F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC2E262A-8EA1-4844-A249-6BB1BE3E2E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="10" activeTab="11" xr2:uid="{5D5A4724-D560-4FC2-9708-4BBF1DBA0B11}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="7" activeTab="9" xr2:uid="{5D5A4724-D560-4FC2-9708-4BBF1DBA0B11}"/>
   </bookViews>
   <sheets>
     <sheet name="AdvancePassengerInfo" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2411" uniqueCount="755">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2084" uniqueCount="630">
   <si>
     <t>Scenario</t>
   </si>
@@ -1126,12 +1126,6 @@
     <t>FLIFO_History_for_codeshare_airline</t>
   </si>
   <si>
-    <t>AVXXCC</t>
-  </si>
-  <si>
-    <t>AVXXET</t>
-  </si>
-  <si>
     <t>Modify_API_for_deleting_API_data</t>
   </si>
   <si>
@@ -1432,87 +1426,12 @@
     <t>09-07-2023</t>
   </si>
   <si>
-    <t>2023-08-19T01:14:00</t>
-  </si>
-  <si>
-    <t>2023-08-19T10:38:00</t>
-  </si>
-  <si>
-    <t>2023-08-19T12:02:00</t>
-  </si>
-  <si>
-    <t>2023-08-19T13:43:00</t>
-  </si>
-  <si>
-    <t>A0G4CG</t>
-  </si>
-  <si>
-    <t>A0G4GS</t>
-  </si>
-  <si>
-    <t>A0G4MT</t>
-  </si>
-  <si>
-    <t>A0G5BG</t>
-  </si>
-  <si>
-    <t>2023-08-18T07:36:37</t>
-  </si>
-  <si>
-    <t>A0HAUU</t>
-  </si>
-  <si>
-    <t>A0HBEB</t>
-  </si>
-  <si>
-    <t>A0HCZN</t>
-  </si>
-  <si>
-    <t>A0HDCJ</t>
-  </si>
-  <si>
-    <t>2302182801230</t>
-  </si>
-  <si>
-    <t>A0HEGA</t>
-  </si>
-  <si>
-    <t>2302182801231</t>
-  </si>
-  <si>
-    <t>A0HFJP</t>
-  </si>
-  <si>
-    <t>A0HFNY</t>
-  </si>
-  <si>
-    <t>2302182801232</t>
-  </si>
-  <si>
-    <t>A0HFZB</t>
-  </si>
-  <si>
-    <t>2302182801233</t>
-  </si>
-  <si>
     <t>A0HF2Y</t>
   </si>
   <si>
     <t>2302182801234</t>
   </si>
   <si>
-    <t>A0HGIK</t>
-  </si>
-  <si>
-    <t>2302182801235</t>
-  </si>
-  <si>
-    <t>A0HGK2</t>
-  </si>
-  <si>
-    <t>A0HGQY</t>
-  </si>
-  <si>
     <t>A0HGV2</t>
   </si>
   <si>
@@ -1522,123 +1441,15 @@
     <t>A0HHGP</t>
   </si>
   <si>
-    <t>A0HHMZ</t>
-  </si>
-  <si>
-    <t>2302182801236</t>
-  </si>
-  <si>
     <t>A0HHSI</t>
   </si>
   <si>
-    <t>A0HIH0</t>
-  </si>
-  <si>
-    <t>2302182801237</t>
-  </si>
-  <si>
-    <t>A0HILY</t>
-  </si>
-  <si>
-    <t>A0HIPC</t>
-  </si>
-  <si>
-    <t>A0HIYG</t>
-  </si>
-  <si>
-    <t>2302182801238</t>
-  </si>
-  <si>
-    <t>A0HI4W</t>
-  </si>
-  <si>
-    <t>2302182801239</t>
-  </si>
-  <si>
-    <t>A0HJHL</t>
-  </si>
-  <si>
-    <t>2302182801240</t>
-  </si>
-  <si>
-    <t>A0HJP4</t>
-  </si>
-  <si>
-    <t>A0HJ1Z</t>
-  </si>
-  <si>
-    <t>2302182801241</t>
-  </si>
-  <si>
-    <t>A0HKLS</t>
-  </si>
-  <si>
-    <t>2302182801242</t>
-  </si>
-  <si>
-    <t>2302182801243</t>
-  </si>
-  <si>
-    <t>A0HKQL</t>
-  </si>
-  <si>
-    <t>2302182801244</t>
-  </si>
-  <si>
-    <t>AACCF302CMCMRPCT062ED1943E</t>
-  </si>
-  <si>
-    <t>8BDA5E7ACMCMRPCT06436F47D1</t>
-  </si>
-  <si>
-    <t>A0HQRH</t>
-  </si>
-  <si>
-    <t>2023-08-19T15:32:00</t>
-  </si>
-  <si>
-    <t>2023-08-19T17:10:00</t>
-  </si>
-  <si>
-    <t>A0HQU3</t>
-  </si>
-  <si>
-    <t>2023-08-18T01:14:00</t>
-  </si>
-  <si>
-    <t>2023-08-18T10:38:00</t>
-  </si>
-  <si>
-    <t>A0HQ3U</t>
-  </si>
-  <si>
-    <t>2023-08-18T13:18:00</t>
-  </si>
-  <si>
-    <t>2023-08-18T16:49:00</t>
-  </si>
-  <si>
-    <t>A0HRIE</t>
-  </si>
-  <si>
-    <t>A0HTDH</t>
-  </si>
-  <si>
     <t>2023-08-20T04:51:00</t>
   </si>
   <si>
     <t>2023-08-20T08:23:00</t>
   </si>
   <si>
-    <t>A0HTL0</t>
-  </si>
-  <si>
-    <t>A0HT23</t>
-  </si>
-  <si>
-    <t>2302182801249</t>
-  </si>
-  <si>
     <t>2023-08-18T04:51:00</t>
   </si>
   <si>
@@ -1648,114 +1459,24 @@
     <t>A0HUOU</t>
   </si>
   <si>
-    <t>A0HUWH</t>
-  </si>
-  <si>
-    <t>2302182801255</t>
-  </si>
-  <si>
-    <t>A0HVAQ</t>
-  </si>
-  <si>
-    <t>2302182801256</t>
-  </si>
-  <si>
-    <t>A0HVYO</t>
-  </si>
-  <si>
-    <t>2023-08-19T16:54:00</t>
-  </si>
-  <si>
-    <t>2023-08-19T20:23:00</t>
-  </si>
-  <si>
-    <t>2302182801257</t>
-  </si>
-  <si>
-    <t>A0HWCI</t>
-  </si>
-  <si>
-    <t>2023-08-20T07:47:00</t>
-  </si>
-  <si>
-    <t>2023-08-20T12:23:00</t>
-  </si>
-  <si>
-    <t>2023-08-20T14:02:00</t>
-  </si>
-  <si>
-    <t>2023-08-20T15:33:00</t>
-  </si>
-  <si>
-    <t>2302182801260</t>
-  </si>
-  <si>
-    <t>A0HW1M</t>
-  </si>
-  <si>
-    <t>2023-08-20T17:06:00</t>
-  </si>
-  <si>
-    <t>2023-08-20T18:37:00</t>
-  </si>
-  <si>
-    <t>2302182801261</t>
-  </si>
-  <si>
-    <t>A0H042</t>
-  </si>
-  <si>
     <t>116</t>
   </si>
   <si>
     <t>460</t>
   </si>
   <si>
-    <t>A0IUWM</t>
-  </si>
-  <si>
-    <t>A0IU5F</t>
-  </si>
-  <si>
     <t>BagTagDisplaybyTagNumberOA</t>
   </si>
   <si>
     <t>192</t>
   </si>
   <si>
-    <t>A0JCDS</t>
-  </si>
-  <si>
     <t>PAIN</t>
   </si>
   <si>
-    <t>A0JD1G</t>
-  </si>
-  <si>
-    <t>A0JIDZ</t>
-  </si>
-  <si>
     <t>122</t>
   </si>
   <si>
-    <t>A0JIQW</t>
-  </si>
-  <si>
-    <t>2302182801292</t>
-  </si>
-  <si>
-    <t>A0JJBP</t>
-  </si>
-  <si>
-    <t>2302182801295</t>
-  </si>
-  <si>
-    <t>A0JKSH</t>
-  </si>
-  <si>
-    <t>2302182801297</t>
-  </si>
-  <si>
     <t>A0JOAN</t>
   </si>
   <si>
@@ -1765,48 +1486,12 @@
     <t>2302182801310</t>
   </si>
   <si>
-    <t>A0KO2N</t>
-  </si>
-  <si>
-    <t>2302182801317</t>
-  </si>
-  <si>
-    <t>A0KQBB</t>
-  </si>
-  <si>
-    <t>2302182801322</t>
-  </si>
-  <si>
-    <t>A0KQE4</t>
-  </si>
-  <si>
-    <t>2302182801323</t>
-  </si>
-  <si>
     <t>380</t>
   </si>
   <si>
-    <t>A0KRFT</t>
-  </si>
-  <si>
-    <t>5E28FB20CMCMRPCT0761EA5D3C</t>
-  </si>
-  <si>
     <t>473</t>
   </si>
   <si>
-    <t>A0LB5Q</t>
-  </si>
-  <si>
-    <t>A0LEIE</t>
-  </si>
-  <si>
-    <t>A0LVIZ</t>
-  </si>
-  <si>
-    <t>A0LVK0</t>
-  </si>
-  <si>
     <t>FR</t>
   </si>
   <si>
@@ -1930,27 +1615,15 @@
     <t>AG</t>
   </si>
   <si>
-    <t>A2CTH3</t>
-  </si>
-  <si>
     <t>230416305</t>
   </si>
   <si>
     <t>AQT2ZF</t>
   </si>
   <si>
-    <t>A2DUC4</t>
-  </si>
-  <si>
     <t>A2DUNP</t>
   </si>
   <si>
-    <t>A2MQM2</t>
-  </si>
-  <si>
-    <t>A2MQNI</t>
-  </si>
-  <si>
     <t>2023-08-23T01:14:00</t>
   </si>
   <si>
@@ -1963,9 +1636,6 @@
     <t>2023-08-23T13:43:00</t>
   </si>
   <si>
-    <t>A2MQNL</t>
-  </si>
-  <si>
     <t>A2MQNQ</t>
   </si>
   <si>
@@ -1978,21 +1648,12 @@
     <t>A2MQNV</t>
   </si>
   <si>
-    <t>A2MQNW</t>
-  </si>
-  <si>
-    <t>2023-08-22T05:24:41</t>
-  </si>
-  <si>
     <t>A2MQN5</t>
   </si>
   <si>
     <t>2023-08-22T05:24:50</t>
   </si>
   <si>
-    <t>A2MQPA</t>
-  </si>
-  <si>
     <t>A2MQPD</t>
   </si>
   <si>
@@ -2047,93 +1708,6 @@
     <t>2302182807116</t>
   </si>
   <si>
-    <t>A2MQUI</t>
-  </si>
-  <si>
-    <t>A2MQUM</t>
-  </si>
-  <si>
-    <t>2302182807118</t>
-  </si>
-  <si>
-    <t>A2MQUT</t>
-  </si>
-  <si>
-    <t>2302182807119</t>
-  </si>
-  <si>
-    <t>A2MQUZ</t>
-  </si>
-  <si>
-    <t>2302182807120</t>
-  </si>
-  <si>
-    <t>A2MQVA</t>
-  </si>
-  <si>
-    <t>2302182807121</t>
-  </si>
-  <si>
-    <t>A2MQVK</t>
-  </si>
-  <si>
-    <t>A2MQVQ</t>
-  </si>
-  <si>
-    <t>A2MQVR</t>
-  </si>
-  <si>
-    <t>A2MQVV</t>
-  </si>
-  <si>
-    <t>A2MQWK</t>
-  </si>
-  <si>
-    <t>A2MQWR</t>
-  </si>
-  <si>
-    <t>A2MQWT</t>
-  </si>
-  <si>
-    <t>A2MQWX</t>
-  </si>
-  <si>
-    <t>2302182807122</t>
-  </si>
-  <si>
-    <t>A2MQW2</t>
-  </si>
-  <si>
-    <t>A2MQW5</t>
-  </si>
-  <si>
-    <t>A2MQXA</t>
-  </si>
-  <si>
-    <t>2302182807123</t>
-  </si>
-  <si>
-    <t>A2MQXF</t>
-  </si>
-  <si>
-    <t>2302182807124</t>
-  </si>
-  <si>
-    <t>A2MQXM</t>
-  </si>
-  <si>
-    <t>2302182807125</t>
-  </si>
-  <si>
-    <t>A2MQXV</t>
-  </si>
-  <si>
-    <t>A2MQXW</t>
-  </si>
-  <si>
-    <t>2302182807126</t>
-  </si>
-  <si>
     <t>A2MQX4</t>
   </si>
   <si>
@@ -2149,21 +1723,6 @@
     <t>2302182807129</t>
   </si>
   <si>
-    <t>A2MQYO</t>
-  </si>
-  <si>
-    <t>5309334ECMCMRPCT07BEB0FA35</t>
-  </si>
-  <si>
-    <t>C1F89FA4CMCMRPCT0874BAD8E1</t>
-  </si>
-  <si>
-    <t>EF1634CCCMCMRPCT0801555EC0</t>
-  </si>
-  <si>
-    <t>A2MQ2D</t>
-  </si>
-  <si>
     <t>A2MQ2E</t>
   </si>
   <si>
@@ -2206,12 +1765,6 @@
     <t>A2MQ4A</t>
   </si>
   <si>
-    <t>A2MQ4P</t>
-  </si>
-  <si>
-    <t>2302182807133</t>
-  </si>
-  <si>
     <t>A2MQ42</t>
   </si>
   <si>
@@ -2311,24 +1864,9 @@
     <t>A2MREX</t>
   </si>
   <si>
-    <t>A2MRFI</t>
-  </si>
-  <si>
-    <t>A2MRFX</t>
-  </si>
-  <si>
-    <t>A2MRGY</t>
-  </si>
-  <si>
     <t>A2MRG5</t>
   </si>
   <si>
-    <t>A2PGGE</t>
-  </si>
-  <si>
-    <t>2302182807192</t>
-  </si>
-  <si>
     <t>A2PNFL</t>
   </si>
   <si>
@@ -2339,6 +1877,93 @@
   </si>
   <si>
     <t>7914A342CMCMRPCT05FAA95C7E</t>
+  </si>
+  <si>
+    <t>A3RAZZ</t>
+  </si>
+  <si>
+    <t>A3AQSJ</t>
+  </si>
+  <si>
+    <t>2302182809575</t>
+  </si>
+  <si>
+    <t>A3AQX3</t>
+  </si>
+  <si>
+    <t>A3AQ33</t>
+  </si>
+  <si>
+    <t>A3OUZL</t>
+  </si>
+  <si>
+    <t>2302182812806</t>
+  </si>
+  <si>
+    <t>A3NTJI</t>
+  </si>
+  <si>
+    <t>2302182812729</t>
+  </si>
+  <si>
+    <t>A3OLLP</t>
+  </si>
+  <si>
+    <t>2302182812781</t>
+  </si>
+  <si>
+    <t>302</t>
+  </si>
+  <si>
+    <t>A3RDTD</t>
+  </si>
+  <si>
+    <t>A3RGOR</t>
+  </si>
+  <si>
+    <t>A25KWU</t>
+  </si>
+  <si>
+    <t>A340AM</t>
+  </si>
+  <si>
+    <t>2302182816167</t>
+  </si>
+  <si>
+    <t>A35JH0</t>
+  </si>
+  <si>
+    <t>2302182816192</t>
+  </si>
+  <si>
+    <t>A35RS1</t>
+  </si>
+  <si>
+    <t>2302182816196</t>
+  </si>
+  <si>
+    <t>A351ZL</t>
+  </si>
+  <si>
+    <t>A4ADZB</t>
+  </si>
+  <si>
+    <t>2302182816201</t>
+  </si>
+  <si>
+    <t>A4CGEE</t>
+  </si>
+  <si>
+    <t>2302182816228</t>
+  </si>
+  <si>
+    <t>6759649826438453</t>
+  </si>
+  <si>
+    <t>A4DMGD</t>
+  </si>
+  <si>
+    <t>2302182816322</t>
   </si>
 </sst>
 </file>
@@ -3081,7 +2706,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="44" t="s">
-        <v>630</v>
+        <v>520</v>
       </c>
       <c r="I2" s="32" t="s">
         <v>211</v>
@@ -3098,7 +2723,7 @@
       <c r="M2" s="32"/>
       <c r="N2" s="32"/>
       <c r="O2" s="32" t="s">
-        <v>631</v>
+        <v>521</v>
       </c>
       <c r="P2" s="38"/>
     </row>
@@ -3149,7 +2774,7 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="37" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B4" s="44">
         <v>0</v>
@@ -3170,13 +2795,13 @@
         <v>1</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>632</v>
+        <v>522</v>
       </c>
       <c r="I4" s="37" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="J4" s="37" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="K4" s="32"/>
       <c r="L4" s="32"/>
@@ -3186,7 +2811,7 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="37" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B5" s="44">
         <v>0</v>
@@ -3207,7 +2832,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="37" t="s">
-        <v>633</v>
+        <v>523</v>
       </c>
       <c r="I5" s="32"/>
       <c r="J5" s="32"/>
@@ -3322,7 +2947,7 @@
         <v>218</v>
       </c>
       <c r="B2" s="44">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C2" s="44" t="s">
         <v>207</v>
@@ -3334,7 +2959,7 @@
         <v>12</v>
       </c>
       <c r="F2" s="44">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G2" s="44" t="s">
         <v>62</v>
@@ -3347,7 +2972,7 @@
       </c>
       <c r="J2" s="44"/>
       <c r="K2" s="44" t="s">
-        <v>657</v>
+        <v>601</v>
       </c>
       <c r="L2" s="44"/>
       <c r="M2" s="44"/>
@@ -3365,16 +2990,16 @@
         <v>219</v>
       </c>
       <c r="B3" s="44">
-        <v>0</v>
-      </c>
-      <c r="C3" s="44" t="s">
-        <v>325</v>
+        <v>1</v>
+      </c>
+      <c r="C3" s="47" t="s">
+        <v>18</v>
       </c>
       <c r="D3" s="44" t="s">
-        <v>209</v>
+        <v>12</v>
       </c>
       <c r="E3" s="44" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" s="44"/>
       <c r="G3" s="44"/>
@@ -3384,10 +3009,10 @@
         <v>0</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>749</v>
+        <v>616</v>
       </c>
       <c r="L3" s="44" t="s">
-        <v>750</v>
+        <v>617</v>
       </c>
       <c r="M3" s="44"/>
       <c r="N3" s="44"/>
@@ -3456,10 +3081,10 @@
       <c r="I5" s="44"/>
       <c r="J5" s="44"/>
       <c r="K5" s="44" t="s">
-        <v>673</v>
+        <v>602</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>674</v>
+        <v>603</v>
       </c>
       <c r="M5" s="44"/>
       <c r="N5" s="44" t="s">
@@ -3503,7 +3128,7 @@
       <c r="I6" s="44"/>
       <c r="J6" s="44"/>
       <c r="K6" s="44" t="s">
-        <v>675</v>
+        <v>604</v>
       </c>
       <c r="L6" s="44"/>
       <c r="M6" s="44"/>
@@ -3514,7 +3139,7 @@
         <v>242</v>
       </c>
       <c r="P6" s="44" t="s">
-        <v>676</v>
+        <v>605</v>
       </c>
       <c r="Q6" s="44"/>
       <c r="R6" s="44"/>
@@ -3533,7 +3158,7 @@
       <c r="B7" s="44">
         <v>0</v>
       </c>
-      <c r="C7" s="44" t="s">
+      <c r="C7" s="47" t="s">
         <v>325</v>
       </c>
       <c r="D7" s="44" t="s">
@@ -3548,10 +3173,10 @@
       <c r="I7" s="44"/>
       <c r="J7" s="44"/>
       <c r="K7" s="44" t="s">
-        <v>677</v>
+        <v>606</v>
       </c>
       <c r="L7" s="44" t="s">
-        <v>678</v>
+        <v>607</v>
       </c>
       <c r="M7" s="44"/>
       <c r="N7" s="44" t="s">
@@ -3561,13 +3186,13 @@
         <v>242</v>
       </c>
       <c r="P7" s="44" t="s">
-        <v>679</v>
+        <v>620</v>
       </c>
       <c r="Q7" s="47" t="s">
         <v>87</v>
       </c>
       <c r="R7" s="44" t="s">
-        <v>680</v>
+        <v>621</v>
       </c>
       <c r="S7" s="44"/>
       <c r="T7" s="44"/>
@@ -3603,10 +3228,10 @@
       </c>
       <c r="J8" s="44"/>
       <c r="K8" s="44" t="s">
-        <v>681</v>
+        <v>618</v>
       </c>
       <c r="L8" s="44" t="s">
-        <v>682</v>
+        <v>619</v>
       </c>
       <c r="M8" s="44"/>
       <c r="N8" s="44" t="s">
@@ -3644,7 +3269,7 @@
       <c r="I9" s="44"/>
       <c r="J9" s="44"/>
       <c r="K9" s="44" t="s">
-        <v>683</v>
+        <v>622</v>
       </c>
       <c r="L9" s="44"/>
       <c r="M9" s="44"/>
@@ -3666,7 +3291,7 @@
         <v>226</v>
       </c>
       <c r="B10" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" s="44" t="s">
         <v>325</v>
@@ -3683,10 +3308,10 @@
       <c r="I10" s="44"/>
       <c r="J10" s="44"/>
       <c r="K10" s="44" t="s">
-        <v>684</v>
+        <v>628</v>
       </c>
       <c r="L10" s="44" t="s">
-        <v>685</v>
+        <v>629</v>
       </c>
       <c r="M10" s="44"/>
       <c r="N10" s="44"/>
@@ -3695,7 +3320,7 @@
       <c r="Q10" s="44"/>
       <c r="R10" s="44"/>
       <c r="S10" s="47" t="s">
-        <v>248</v>
+        <v>627</v>
       </c>
       <c r="T10" s="44"/>
       <c r="U10" s="44"/>
@@ -3722,10 +3347,10 @@
       <c r="I11" s="44"/>
       <c r="J11" s="44"/>
       <c r="K11" s="44" t="s">
-        <v>658</v>
+        <v>608</v>
       </c>
       <c r="L11" s="44" t="s">
-        <v>659</v>
+        <v>609</v>
       </c>
       <c r="M11" s="44"/>
       <c r="N11" s="44"/>
@@ -3744,7 +3369,7 @@
         <v>228</v>
       </c>
       <c r="B12" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" s="44" t="s">
         <v>325</v>
@@ -3761,10 +3386,10 @@
       <c r="I12" s="44"/>
       <c r="J12" s="44"/>
       <c r="K12" s="44" t="s">
-        <v>660</v>
+        <v>623</v>
       </c>
       <c r="L12" s="44" t="s">
-        <v>661</v>
+        <v>624</v>
       </c>
       <c r="M12" s="44"/>
       <c r="N12" s="44" t="s">
@@ -3804,10 +3429,10 @@
       <c r="I13" s="44"/>
       <c r="J13" s="44"/>
       <c r="K13" s="44" t="s">
-        <v>662</v>
+        <v>450</v>
       </c>
       <c r="L13" s="44" t="s">
-        <v>663</v>
+        <v>451</v>
       </c>
       <c r="M13" s="44"/>
       <c r="N13" s="44" t="s">
@@ -3865,16 +3490,16 @@
         <v>231</v>
       </c>
       <c r="B15" s="44">
-        <v>0</v>
-      </c>
-      <c r="C15" s="44" t="s">
-        <v>325</v>
+        <v>1</v>
+      </c>
+      <c r="C15" s="47" t="s">
+        <v>32</v>
       </c>
       <c r="D15" s="44" t="s">
-        <v>209</v>
+        <v>12</v>
       </c>
       <c r="E15" s="44" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="F15" s="44"/>
       <c r="G15" s="44"/>
@@ -3882,10 +3507,10 @@
       <c r="I15" s="44"/>
       <c r="J15" s="44"/>
       <c r="K15" s="44" t="s">
-        <v>664</v>
+        <v>610</v>
       </c>
       <c r="L15" s="44" t="s">
-        <v>665</v>
+        <v>611</v>
       </c>
       <c r="M15" s="44"/>
       <c r="N15" s="44" t="s">
@@ -3910,14 +3535,14 @@
       <c r="B16" s="44">
         <v>0</v>
       </c>
-      <c r="C16" s="44" t="s">
-        <v>325</v>
+      <c r="C16" s="47" t="s">
+        <v>612</v>
       </c>
       <c r="D16" s="44" t="s">
-        <v>209</v>
+        <v>12</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="F16" s="44"/>
       <c r="G16" s="44"/>
@@ -3925,7 +3550,7 @@
       <c r="I16" s="44"/>
       <c r="J16" s="44"/>
       <c r="K16" s="44" t="s">
-        <v>666</v>
+        <v>613</v>
       </c>
       <c r="L16" s="44"/>
       <c r="M16" s="44"/>
@@ -3964,7 +3589,7 @@
       <c r="I17" s="44"/>
       <c r="J17" s="44"/>
       <c r="K17" s="44" t="s">
-        <v>667</v>
+        <v>614</v>
       </c>
       <c r="L17" s="44"/>
       <c r="M17" s="44"/>
@@ -4007,7 +3632,7 @@
       </c>
       <c r="J18" s="44"/>
       <c r="K18" s="44" t="s">
-        <v>668</v>
+        <v>452</v>
       </c>
       <c r="L18" s="44"/>
       <c r="M18" s="44"/>
@@ -4046,7 +3671,7 @@
       <c r="I19" s="44"/>
       <c r="J19" s="44"/>
       <c r="K19" s="44" t="s">
-        <v>669</v>
+        <v>453</v>
       </c>
       <c r="L19" s="44"/>
       <c r="M19" s="44"/>
@@ -4085,7 +3710,7 @@
       <c r="I20" s="44"/>
       <c r="J20" s="44"/>
       <c r="K20" s="44" t="s">
-        <v>670</v>
+        <v>454</v>
       </c>
       <c r="L20" s="44"/>
       <c r="M20" s="44"/>
@@ -4124,7 +3749,7 @@
       <c r="I21" s="44"/>
       <c r="J21" s="44"/>
       <c r="K21" s="44" t="s">
-        <v>671</v>
+        <v>455</v>
       </c>
       <c r="L21" s="44"/>
       <c r="M21" s="44"/>
@@ -4149,7 +3774,7 @@
         <v>1</v>
       </c>
       <c r="C22" s="47" t="s">
-        <v>572</v>
+        <v>471</v>
       </c>
       <c r="D22" s="44" t="s">
         <v>34</v>
@@ -4171,7 +3796,7 @@
       </c>
       <c r="J22" s="44"/>
       <c r="K22" s="44" t="s">
-        <v>672</v>
+        <v>615</v>
       </c>
       <c r="L22" s="44"/>
       <c r="M22" s="44"/>
@@ -4265,7 +3890,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="47" t="s">
-        <v>569</v>
+        <v>470</v>
       </c>
       <c r="D2" s="35" t="s">
         <v>12</v>
@@ -4292,10 +3917,10 @@
         <v>1</v>
       </c>
       <c r="L2" s="34" t="s">
-        <v>752</v>
+        <v>598</v>
       </c>
       <c r="M2" s="34" t="s">
-        <v>751</v>
+        <v>597</v>
       </c>
       <c r="N2" s="32"/>
     </row>
@@ -4334,7 +3959,7 @@
         <v>6</v>
       </c>
       <c r="L3" s="34" t="s">
-        <v>753</v>
+        <v>599</v>
       </c>
       <c r="M3" s="34" t="s">
         <v>264</v>
@@ -4378,7 +4003,7 @@
         <v>6</v>
       </c>
       <c r="L4" s="34" t="s">
-        <v>754</v>
+        <v>600</v>
       </c>
       <c r="M4" s="32"/>
       <c r="N4" s="32" t="s">
@@ -4460,7 +4085,7 @@
       <c r="G2" s="44"/>
       <c r="H2" s="44"/>
       <c r="I2" s="44" t="s">
-        <v>620</v>
+        <v>514</v>
       </c>
       <c r="J2" s="44"/>
       <c r="K2" s="44"/>
@@ -4479,7 +4104,7 @@
       <c r="G3" s="44"/>
       <c r="H3" s="44"/>
       <c r="I3" s="44" t="s">
-        <v>620</v>
+        <v>514</v>
       </c>
       <c r="J3" s="44"/>
       <c r="K3" s="44"/>
@@ -4498,7 +4123,7 @@
       <c r="G4" s="44"/>
       <c r="H4" s="44"/>
       <c r="I4" s="44" t="s">
-        <v>622</v>
+        <v>515</v>
       </c>
       <c r="J4" s="44"/>
       <c r="K4" s="44"/>
@@ -4529,13 +4154,13 @@
         <v>12</v>
       </c>
       <c r="I5" s="44" t="s">
-        <v>686</v>
+        <v>544</v>
       </c>
       <c r="J5" s="44" t="s">
-        <v>687</v>
+        <v>545</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>688</v>
+        <v>546</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -4564,10 +4189,10 @@
         <v>12</v>
       </c>
       <c r="I6" s="44" t="s">
-        <v>689</v>
+        <v>547</v>
       </c>
       <c r="J6" s="44" t="s">
-        <v>690</v>
+        <v>548</v>
       </c>
       <c r="K6" s="44"/>
     </row>
@@ -4635,7 +4260,7 @@
         <v>149</v>
       </c>
       <c r="D3" s="44" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E3" s="44">
         <v>1</v>
@@ -4652,7 +4277,7 @@
         <v>149</v>
       </c>
       <c r="D4" s="44" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E4" s="44">
         <v>1</v>
@@ -4847,16 +4472,16 @@
         <v>45</v>
       </c>
       <c r="J2" s="44" t="s">
-        <v>738</v>
+        <v>589</v>
       </c>
       <c r="K2" s="44" t="s">
-        <v>625</v>
+        <v>516</v>
       </c>
       <c r="L2" s="44" t="s">
         <v>207</v>
       </c>
       <c r="M2" s="44" t="s">
-        <v>626</v>
+        <v>517</v>
       </c>
       <c r="N2" s="44" t="s">
         <v>208</v>
@@ -4865,13 +4490,13 @@
         <v>12</v>
       </c>
       <c r="P2" s="44" t="s">
-        <v>627</v>
+        <v>518</v>
       </c>
       <c r="Q2" s="44" t="s">
         <v>62</v>
       </c>
       <c r="R2" s="44" t="s">
-        <v>628</v>
+        <v>519</v>
       </c>
       <c r="S2" s="44" t="s">
         <v>12</v>
@@ -4917,16 +4542,16 @@
         <v>45</v>
       </c>
       <c r="J3" s="44" t="s">
-        <v>696</v>
+        <v>549</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>625</v>
+        <v>516</v>
       </c>
       <c r="L3" s="44" t="s">
         <v>207</v>
       </c>
       <c r="M3" s="44" t="s">
-        <v>626</v>
+        <v>517</v>
       </c>
       <c r="N3" s="44" t="s">
         <v>208</v>
@@ -4935,13 +4560,13 @@
         <v>12</v>
       </c>
       <c r="P3" s="44" t="s">
-        <v>697</v>
+        <v>550</v>
       </c>
       <c r="Q3" s="44" t="s">
         <v>239</v>
       </c>
       <c r="R3" s="44" t="s">
-        <v>698</v>
+        <v>551</v>
       </c>
       <c r="S3" s="44" t="s">
         <v>12</v>
@@ -4995,16 +4620,16 @@
       <c r="H4" s="44"/>
       <c r="I4" s="44"/>
       <c r="J4" s="44" t="s">
-        <v>702</v>
+        <v>555</v>
       </c>
       <c r="K4" s="44" t="s">
-        <v>703</v>
+        <v>556</v>
       </c>
       <c r="L4" s="44" t="s">
         <v>328</v>
       </c>
       <c r="M4" s="44" t="s">
-        <v>704</v>
+        <v>557</v>
       </c>
       <c r="N4" s="44" t="s">
         <v>209</v>
@@ -5047,16 +4672,16 @@
       <c r="H5" s="44"/>
       <c r="I5" s="44"/>
       <c r="J5" s="44" t="s">
-        <v>705</v>
+        <v>558</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>703</v>
+        <v>556</v>
       </c>
       <c r="L5" s="44" t="s">
         <v>328</v>
       </c>
       <c r="M5" s="44" t="s">
-        <v>704</v>
+        <v>557</v>
       </c>
       <c r="N5" s="44" t="s">
         <v>209</v>
@@ -5107,16 +4732,16 @@
         <v>45</v>
       </c>
       <c r="J6" s="44" t="s">
-        <v>699</v>
+        <v>552</v>
       </c>
       <c r="K6" s="44" t="s">
-        <v>700</v>
+        <v>553</v>
       </c>
       <c r="L6" s="44" t="s">
         <v>207</v>
       </c>
       <c r="M6" s="44" t="s">
-        <v>701</v>
+        <v>554</v>
       </c>
       <c r="N6" s="44" t="s">
         <v>208</v>
@@ -5381,7 +5006,7 @@
         <v>282</v>
       </c>
       <c r="D9" s="44" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E9" s="44"/>
     </row>
@@ -5900,7 +5525,7 @@
         <v>0</v>
       </c>
       <c r="AA2" s="44" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="AB2" s="44" t="s">
         <v>45</v>
@@ -5912,7 +5537,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="44" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="AF2" s="44" t="s">
         <v>45</v>
@@ -6158,16 +5783,16 @@
       <c r="I2" s="44"/>
       <c r="J2" s="44"/>
       <c r="K2" s="44" t="s">
-        <v>706</v>
+        <v>559</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>707</v>
+        <v>560</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>325</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>708</v>
+        <v>561</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>209</v>
@@ -6222,7 +5847,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>709</v>
+        <v>562</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>312</v>
@@ -6362,16 +5987,16 @@
         <v>2</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>712</v>
+        <v>563</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>707</v>
+        <v>560</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>325</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>708</v>
+        <v>561</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>209</v>
@@ -6380,7 +6005,7 @@
         <v>12</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>713</v>
+        <v>564</v>
       </c>
       <c r="R5" s="15" t="s">
         <v>44</v>
@@ -6578,16 +6203,16 @@
       <c r="I9" s="44"/>
       <c r="J9" s="44"/>
       <c r="K9" s="44" t="s">
-        <v>523</v>
+        <v>460</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>521</v>
+        <v>458</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>325</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>522</v>
+        <v>459</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>209</v>
@@ -6652,10 +6277,10 @@
         <v>127</v>
       </c>
       <c r="B2" s="44" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C2" s="44" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D2" s="44" t="s">
         <v>128</v>
@@ -6899,16 +6524,16 @@
       <c r="U2" s="44"/>
       <c r="V2" s="44"/>
       <c r="W2" s="44" t="s">
-        <v>714</v>
+        <v>565</v>
       </c>
       <c r="X2" s="44" t="s">
-        <v>707</v>
+        <v>560</v>
       </c>
       <c r="Y2" s="44" t="s">
         <v>325</v>
       </c>
       <c r="Z2" s="44" t="s">
-        <v>708</v>
+        <v>561</v>
       </c>
       <c r="AA2" s="44" t="s">
         <v>209</v>
@@ -6917,7 +6542,7 @@
         <v>12</v>
       </c>
       <c r="AC2" s="44" t="s">
-        <v>715</v>
+        <v>566</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -7035,16 +6660,16 @@
       <c r="U4" s="44"/>
       <c r="V4" s="44"/>
       <c r="W4" s="44" t="s">
-        <v>716</v>
+        <v>567</v>
       </c>
       <c r="X4" s="44" t="s">
-        <v>707</v>
+        <v>560</v>
       </c>
       <c r="Y4" s="44" t="s">
         <v>325</v>
       </c>
       <c r="Z4" s="44" t="s">
-        <v>708</v>
+        <v>561</v>
       </c>
       <c r="AA4" s="44" t="s">
         <v>209</v>
@@ -7053,7 +6678,7 @@
         <v>12</v>
       </c>
       <c r="AC4" s="44" t="s">
-        <v>717</v>
+        <v>568</v>
       </c>
     </row>
   </sheetData>
@@ -7311,16 +6936,16 @@
       <c r="I2" s="44"/>
       <c r="J2" s="44"/>
       <c r="K2" s="44" t="s">
-        <v>718</v>
+        <v>569</v>
       </c>
       <c r="L2" s="44" t="s">
-        <v>719</v>
+        <v>570</v>
       </c>
       <c r="M2" s="44" t="s">
         <v>329</v>
       </c>
       <c r="N2" s="44" t="s">
-        <v>720</v>
+        <v>571</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>209</v>
@@ -7329,7 +6954,7 @@
         <v>12</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>721</v>
+        <v>572</v>
       </c>
       <c r="R2" s="3"/>
     </row>
@@ -7357,16 +6982,16 @@
       <c r="I3" s="44"/>
       <c r="J3" s="44"/>
       <c r="K3" s="44" t="s">
-        <v>560</v>
+        <v>467</v>
       </c>
       <c r="L3" s="44" t="s">
-        <v>516</v>
+        <v>456</v>
       </c>
       <c r="M3" s="44" t="s">
         <v>325</v>
       </c>
       <c r="N3" s="44" t="s">
-        <v>517</v>
+        <v>457</v>
       </c>
       <c r="O3" s="3" t="s">
         <v>209</v>
@@ -7375,10 +7000,10 @@
         <v>12</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>561</v>
+        <v>468</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>562</v>
+        <v>469</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -7405,16 +7030,16 @@
       <c r="I4" s="44"/>
       <c r="J4" s="44"/>
       <c r="K4" s="44" t="s">
-        <v>722</v>
+        <v>573</v>
       </c>
       <c r="L4" s="44" t="s">
-        <v>625</v>
+        <v>516</v>
       </c>
       <c r="M4" s="44" t="s">
         <v>207</v>
       </c>
       <c r="N4" s="44" t="s">
-        <v>626</v>
+        <v>517</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>208</v>
@@ -7423,7 +7048,7 @@
         <v>12</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>723</v>
+        <v>574</v>
       </c>
       <c r="R4" s="3"/>
     </row>
@@ -7451,16 +7076,16 @@
       <c r="I5" s="44"/>
       <c r="J5" s="44"/>
       <c r="K5" s="44" t="s">
-        <v>724</v>
+        <v>575</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>625</v>
+        <v>516</v>
       </c>
       <c r="M5" s="44" t="s">
         <v>207</v>
       </c>
       <c r="N5" s="44" t="s">
-        <v>626</v>
+        <v>517</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>208</v>
@@ -7469,7 +7094,7 @@
         <v>12</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>725</v>
+        <v>576</v>
       </c>
       <c r="R5" s="3"/>
     </row>
@@ -7497,16 +7122,16 @@
       <c r="I6" s="44"/>
       <c r="J6" s="44"/>
       <c r="K6" s="44" t="s">
-        <v>726</v>
+        <v>577</v>
       </c>
       <c r="L6" s="44" t="s">
-        <v>625</v>
+        <v>516</v>
       </c>
       <c r="M6" s="44" t="s">
         <v>207</v>
       </c>
       <c r="N6" s="44" t="s">
-        <v>626</v>
+        <v>517</v>
       </c>
       <c r="O6" s="3" t="s">
         <v>208</v>
@@ -7515,7 +7140,7 @@
         <v>12</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>727</v>
+        <v>578</v>
       </c>
       <c r="R6" s="3"/>
     </row>
@@ -7650,16 +7275,16 @@
         <v>163</v>
       </c>
       <c r="J2" s="56" t="s">
-        <v>728</v>
+        <v>579</v>
       </c>
       <c r="K2" s="44" t="s">
-        <v>729</v>
+        <v>580</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>215</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>730</v>
+        <v>581</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>12</v>
@@ -7668,13 +7293,13 @@
         <v>216</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>731</v>
+        <v>582</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>217</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>732</v>
+        <v>583</v>
       </c>
       <c r="S2" s="3" t="s">
         <v>216</v>
@@ -7683,7 +7308,7 @@
         <v>163</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>733</v>
+        <v>584</v>
       </c>
     </row>
     <row r="3" spans="1:21">
@@ -7715,16 +7340,16 @@
         <v>163</v>
       </c>
       <c r="J3" s="56" t="s">
-        <v>734</v>
+        <v>585</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>729</v>
+        <v>580</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>215</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>730</v>
+        <v>581</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>12</v>
@@ -7733,13 +7358,13 @@
         <v>216</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>735</v>
+        <v>586</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>341</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>736</v>
+        <v>587</v>
       </c>
       <c r="S3" s="3" t="s">
         <v>216</v>
@@ -7748,7 +7373,7 @@
         <v>163</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>737</v>
+        <v>588</v>
       </c>
     </row>
     <row r="4" spans="1:21">
@@ -7953,7 +7578,7 @@
         <v>181</v>
       </c>
       <c r="B3" s="64" t="s">
-        <v>619</v>
+        <v>513</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -8063,40 +7688,40 @@
         <v>266</v>
       </c>
       <c r="C1" s="42" t="s">
-        <v>580</v>
+        <v>475</v>
       </c>
       <c r="D1" s="42" t="s">
-        <v>581</v>
+        <v>476</v>
       </c>
       <c r="E1" s="42" t="s">
-        <v>582</v>
+        <v>477</v>
       </c>
       <c r="F1" s="42" t="s">
-        <v>583</v>
+        <v>478</v>
       </c>
       <c r="G1" s="63" t="s">
-        <v>584</v>
+        <v>479</v>
       </c>
       <c r="H1" s="63" t="s">
-        <v>585</v>
+        <v>480</v>
       </c>
       <c r="I1" s="63" t="s">
-        <v>585</v>
+        <v>480</v>
       </c>
       <c r="J1" s="63" t="s">
-        <v>595</v>
+        <v>490</v>
       </c>
       <c r="K1" s="42" t="s">
-        <v>582</v>
+        <v>477</v>
       </c>
       <c r="L1" s="42" t="s">
-        <v>583</v>
+        <v>478</v>
       </c>
       <c r="M1" s="42" t="s">
-        <v>599</v>
+        <v>494</v>
       </c>
       <c r="N1" s="42" t="s">
-        <v>613</v>
+        <v>508</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -8107,40 +7732,40 @@
         <v>149</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>577</v>
+        <v>472</v>
       </c>
       <c r="D2" s="32" t="s">
         <v>121</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>587</v>
+        <v>482</v>
       </c>
       <c r="F2" s="44" t="s">
-        <v>578</v>
+        <v>473</v>
       </c>
       <c r="G2" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H2" s="44" t="s">
-        <v>586</v>
+        <v>481</v>
       </c>
       <c r="I2" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="J2" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="K2" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="L2" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="M2" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="N2" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -8151,40 +7776,40 @@
         <v>149</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>577</v>
+        <v>472</v>
       </c>
       <c r="D3" s="32" t="s">
         <v>121</v>
       </c>
       <c r="E3" s="32" t="s">
-        <v>588</v>
+        <v>483</v>
       </c>
       <c r="F3" s="44" t="s">
-        <v>587</v>
+        <v>482</v>
       </c>
       <c r="G3" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H3" s="44" t="s">
-        <v>586</v>
+        <v>481</v>
       </c>
       <c r="I3" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="J3" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="L3" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="M3" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="N3" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -8195,40 +7820,40 @@
         <v>149</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>577</v>
+        <v>472</v>
       </c>
       <c r="D4" s="32" t="s">
         <v>121</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>587</v>
+        <v>482</v>
       </c>
       <c r="F4" s="44" t="s">
-        <v>578</v>
+        <v>473</v>
       </c>
       <c r="G4" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H4" s="44" t="s">
-        <v>586</v>
+        <v>481</v>
       </c>
       <c r="I4" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="J4" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="K4" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="L4" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="M4" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="N4" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -8239,40 +7864,40 @@
         <v>149</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>577</v>
+        <v>472</v>
       </c>
       <c r="D5" s="32" t="s">
         <v>121</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>578</v>
+        <v>473</v>
       </c>
       <c r="F5" s="44" t="s">
-        <v>589</v>
+        <v>484</v>
       </c>
       <c r="G5" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H5" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="I5" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="J5" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="M5" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="N5" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -8283,40 +7908,40 @@
         <v>149</v>
       </c>
       <c r="C6" s="44" t="s">
-        <v>577</v>
+        <v>472</v>
       </c>
       <c r="D6" s="44" t="s">
         <v>121</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>578</v>
+        <v>473</v>
       </c>
       <c r="F6" s="44" t="s">
-        <v>589</v>
+        <v>484</v>
       </c>
       <c r="G6" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H6" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="I6" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="J6" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="K6" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="L6" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="M6" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="N6" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -8327,40 +7952,40 @@
         <v>149</v>
       </c>
       <c r="C7" s="44" t="s">
-        <v>577</v>
+        <v>472</v>
       </c>
       <c r="D7" s="44" t="s">
         <v>121</v>
       </c>
       <c r="E7" s="44" t="s">
-        <v>578</v>
+        <v>473</v>
       </c>
       <c r="F7" s="44" t="s">
-        <v>589</v>
+        <v>484</v>
       </c>
       <c r="G7" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H7" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="I7" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="J7" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="K7" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="L7" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="M7" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="N7" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -8371,40 +7996,40 @@
         <v>149</v>
       </c>
       <c r="C8" s="44" t="s">
-        <v>590</v>
+        <v>485</v>
       </c>
       <c r="D8" s="44" t="s">
         <v>121</v>
       </c>
       <c r="E8" s="44" t="s">
-        <v>591</v>
+        <v>486</v>
       </c>
       <c r="F8" s="44" t="s">
-        <v>593</v>
+        <v>488</v>
       </c>
       <c r="G8" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H8" s="44" t="s">
-        <v>597</v>
+        <v>492</v>
       </c>
       <c r="I8" s="44" t="s">
-        <v>598</v>
+        <v>493</v>
       </c>
       <c r="J8" s="44" t="s">
-        <v>596</v>
+        <v>491</v>
       </c>
       <c r="K8" s="44" t="s">
-        <v>592</v>
+        <v>487</v>
       </c>
       <c r="L8" s="44" t="s">
-        <v>594</v>
+        <v>489</v>
       </c>
       <c r="M8" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="N8" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -8415,40 +8040,40 @@
         <v>149</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>577</v>
+        <v>472</v>
       </c>
       <c r="D9" s="32" t="s">
         <v>121</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>601</v>
+        <v>496</v>
       </c>
       <c r="F9" s="44" t="s">
-        <v>588</v>
+        <v>483</v>
       </c>
       <c r="G9" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H9" s="44" t="s">
-        <v>603</v>
+        <v>498</v>
       </c>
       <c r="I9" s="44" t="s">
-        <v>604</v>
+        <v>499</v>
       </c>
       <c r="J9" s="44" t="s">
-        <v>605</v>
+        <v>500</v>
       </c>
       <c r="K9" s="44" t="s">
-        <v>602</v>
+        <v>497</v>
       </c>
       <c r="L9" s="44" t="s">
-        <v>593</v>
+        <v>488</v>
       </c>
       <c r="M9" s="44" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="N9" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -8459,40 +8084,40 @@
         <v>149</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>577</v>
+        <v>472</v>
       </c>
       <c r="D10" s="44" t="s">
         <v>121</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>607</v>
+        <v>502</v>
       </c>
       <c r="F10" s="44" t="s">
-        <v>609</v>
+        <v>504</v>
       </c>
       <c r="G10" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H10" s="44" t="s">
-        <v>610</v>
+        <v>505</v>
       </c>
       <c r="I10" s="44" t="s">
-        <v>611</v>
+        <v>506</v>
       </c>
       <c r="J10" s="44" t="s">
-        <v>612</v>
+        <v>507</v>
       </c>
       <c r="K10" s="44" t="s">
-        <v>608</v>
+        <v>503</v>
       </c>
       <c r="L10" s="44" t="s">
-        <v>593</v>
+        <v>488</v>
       </c>
       <c r="M10" s="44" t="s">
-        <v>606</v>
+        <v>501</v>
       </c>
       <c r="N10" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -8503,40 +8128,40 @@
         <v>149</v>
       </c>
       <c r="C11" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="D11" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="F11" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="G11" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="H11" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="I11" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="J11" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="K11" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="L11" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="M11" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="N11" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -8547,40 +8172,40 @@
         <v>149</v>
       </c>
       <c r="C12" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="D12" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="F12" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="G12" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="H12" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="I12" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="J12" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="K12" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="L12" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="M12" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="N12" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -8591,40 +8216,40 @@
         <v>149</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="F13" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="G13" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="H13" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="I13" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="J13" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="K13" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="L13" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="M13" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="N13" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -8635,40 +8260,40 @@
         <v>149</v>
       </c>
       <c r="C14" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="F14" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="G14" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="H14" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="I14" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="J14" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="K14" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="L14" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="M14" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="N14" s="44" t="s">
-        <v>577</v>
+        <v>472</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -8679,40 +8304,40 @@
         <v>149</v>
       </c>
       <c r="C15" s="44" t="s">
-        <v>614</v>
+        <v>509</v>
       </c>
       <c r="D15" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="E15" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="F15" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="G15" s="44" t="s">
-        <v>615</v>
+        <v>510</v>
       </c>
       <c r="H15" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="I15" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="J15" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="K15" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="L15" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="M15" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="N15" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -8720,43 +8345,43 @@
         <v>303</v>
       </c>
       <c r="B16" s="32" t="s">
-        <v>616</v>
+        <v>511</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>577</v>
+        <v>472</v>
       </c>
       <c r="D16" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="F16" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="G16" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="H16" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="I16" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="J16" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="K16" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="L16" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="M16" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="N16" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -8767,45 +8392,45 @@
         <v>149</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>617</v>
+        <v>512</v>
       </c>
       <c r="D17" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="F17" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="G17" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="H17" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="I17" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="J17" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="K17" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="L17" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="M17" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
       <c r="N17" s="44" t="s">
-        <v>600</v>
+        <v>495</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="62" t="s">
-        <v>579</v>
+        <v>474</v>
       </c>
     </row>
   </sheetData>
@@ -8884,10 +8509,10 @@
         <v>50</v>
       </c>
       <c r="H2" s="44" t="s">
-        <v>636</v>
+        <v>524</v>
       </c>
       <c r="I2" s="44" t="s">
-        <v>637</v>
+        <v>525</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -8913,10 +8538,10 @@
         <v>50</v>
       </c>
       <c r="H3" s="44" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I3" s="44" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>
@@ -9101,7 +8726,7 @@
         <v>346</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C6" s="35" t="s">
         <v>12</v>
@@ -9117,7 +8742,7 @@
       <c r="H6" s="44"/>
       <c r="I6" s="44"/>
       <c r="J6" s="44" t="s">
-        <v>739</v>
+        <v>590</v>
       </c>
       <c r="K6" s="44"/>
       <c r="L6" s="44"/>
@@ -9200,7 +8825,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>740</v>
+        <v>591</v>
       </c>
       <c r="G2" s="32">
         <v>2</v>
@@ -9231,7 +8856,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>741</v>
+        <v>592</v>
       </c>
       <c r="G3" s="32"/>
       <c r="H3" s="32"/>
@@ -9260,7 +8885,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>742</v>
+        <v>593</v>
       </c>
       <c r="G4" s="32"/>
       <c r="H4" s="32"/>
@@ -9339,7 +8964,7 @@
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="44" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B2" s="47" t="s">
         <v>32</v>
@@ -9362,7 +8987,7 @@
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="44" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B3" s="47" t="s">
         <v>325</v>
@@ -9455,10 +9080,10 @@
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="44" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B2" s="47" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C2" s="44" t="s">
         <v>12</v>
@@ -9478,10 +9103,10 @@
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="48" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B3" s="47" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C3" s="44" t="s">
         <v>12</v>
@@ -9501,7 +9126,7 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="44" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B4" s="47" t="s">
         <v>336</v>
@@ -9569,7 +9194,7 @@
         <v>1</v>
       </c>
       <c r="F1" s="42" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G1" s="42" t="s">
         <v>30</v>
@@ -9601,7 +9226,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="44" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B2" s="47" t="s">
         <v>332</v>
@@ -9616,10 +9241,10 @@
         <v>2</v>
       </c>
       <c r="F2" s="44" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="G2" s="44" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="H2" s="44"/>
       <c r="I2" s="44"/>
@@ -9632,7 +9257,7 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="44" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B3" s="47" t="s">
         <v>332</v>
@@ -9647,10 +9272,10 @@
         <v>2</v>
       </c>
       <c r="F3" s="44" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="G3" s="44" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="H3" s="44"/>
       <c r="I3" s="44"/>
@@ -9663,7 +9288,7 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="44" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B4" s="47" t="s">
         <v>332</v>
@@ -9678,10 +9303,10 @@
         <v>2</v>
       </c>
       <c r="F4" s="44" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="G4" s="44" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="H4" s="44"/>
       <c r="I4" s="44"/>
@@ -9694,7 +9319,7 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="44" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B5" s="47" t="s">
         <v>332</v>
@@ -9709,10 +9334,10 @@
         <v>2</v>
       </c>
       <c r="F5" s="44" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="G5" s="44" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="H5" s="44"/>
       <c r="I5" s="44"/>
@@ -9771,10 +9396,10 @@
         <v>1</v>
       </c>
       <c r="F1" s="42" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G1" s="42" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H1" s="43" t="s">
         <v>74</v>
@@ -9783,23 +9408,23 @@
         <v>8</v>
       </c>
       <c r="J1" s="43" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="K1" s="43" t="s">
         <v>75</v>
       </c>
       <c r="L1" s="43" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="M1" s="43" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="N1" s="40"/>
       <c r="O1" s="46"/>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="44" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B2" s="47" t="s">
         <v>32</v>
@@ -9822,7 +9447,7 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="44" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B3" s="47" t="s">
         <v>32</v>
@@ -9847,10 +9472,10 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="44" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B4" s="47" t="s">
-        <v>543</v>
+        <v>461</v>
       </c>
       <c r="C4" s="44" t="s">
         <v>12</v>
@@ -9866,28 +9491,28 @@
       </c>
       <c r="G4" s="44"/>
       <c r="H4" s="44" t="s">
-        <v>743</v>
+        <v>594</v>
       </c>
       <c r="I4" s="44" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="J4" s="44" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="K4" s="44"/>
       <c r="L4" s="44" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="M4" s="44" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="44" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B5" s="47" t="s">
-        <v>544</v>
+        <v>462</v>
       </c>
       <c r="C5" s="44" t="s">
         <v>12</v>
@@ -9903,25 +9528,25 @@
       </c>
       <c r="G5" s="44"/>
       <c r="H5" s="44" t="s">
-        <v>744</v>
+        <v>595</v>
       </c>
       <c r="I5" s="44" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="J5" s="44" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="K5" s="44"/>
       <c r="L5" s="44" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="M5" s="44" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="44" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B6" s="47" t="s">
         <v>32</v>
@@ -9944,7 +9569,7 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="44" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B7" s="47" t="s">
         <v>32</v>
@@ -9967,7 +9592,7 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="44" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B8" s="47" t="s">
         <v>32</v>
@@ -9992,7 +9617,7 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="44" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B9" s="47" t="s">
         <v>32</v>
@@ -10017,7 +9642,7 @@
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="44" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B10" s="47" t="s">
         <v>32</v>
@@ -10074,10 +9699,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="44" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B2" s="47" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C2" s="44" t="s">
         <v>12</v>
@@ -10126,7 +9751,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="44" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B2" s="47" t="s">
         <v>32</v>
@@ -10143,10 +9768,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="44" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B3" s="47" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C3" s="44" t="s">
         <v>12</v>
@@ -10160,10 +9785,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="44" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B4" s="47" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C4" s="44" t="s">
         <v>12</v>
@@ -10200,30 +9825,30 @@
         <v>0</v>
       </c>
       <c r="B1" s="49" t="s">
+        <v>423</v>
+      </c>
+      <c r="C1" s="49" t="s">
+        <v>424</v>
+      </c>
+      <c r="D1" s="49" t="s">
         <v>425</v>
       </c>
-      <c r="C1" s="49" t="s">
+      <c r="E1" s="49" t="s">
         <v>426</v>
-      </c>
-      <c r="D1" s="49" t="s">
-        <v>427</v>
-      </c>
-      <c r="E1" s="49" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="44" t="s">
+        <v>427</v>
+      </c>
+      <c r="B2" s="47" t="s">
+        <v>428</v>
+      </c>
+      <c r="C2" s="44" t="s">
         <v>429</v>
       </c>
-      <c r="B2" s="47" t="s">
+      <c r="D2" s="44" t="s">
         <v>430</v>
-      </c>
-      <c r="C2" s="44" t="s">
-        <v>431</v>
-      </c>
-      <c r="D2" s="44" t="s">
-        <v>432</v>
       </c>
       <c r="E2" s="44" t="s">
         <v>12</v>
@@ -10231,16 +9856,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="44" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B3" s="47" t="s">
+        <v>428</v>
+      </c>
+      <c r="C3" s="44" t="s">
+        <v>429</v>
+      </c>
+      <c r="D3" s="44" t="s">
         <v>430</v>
-      </c>
-      <c r="C3" s="44" t="s">
-        <v>431</v>
-      </c>
-      <c r="D3" s="44" t="s">
-        <v>432</v>
       </c>
       <c r="E3" s="44" t="s">
         <v>12</v>
@@ -10248,23 +9873,23 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="44" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B4" s="44"/>
       <c r="C4" s="44"/>
       <c r="D4" s="44" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E4" s="44"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="44" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B5" s="44"/>
       <c r="C5" s="44"/>
       <c r="D5" s="44" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E5" s="44" t="s">
         <v>12</v>
@@ -10272,31 +9897,31 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="50" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B6" s="47" t="s">
+        <v>428</v>
+      </c>
+      <c r="C6" s="44" t="s">
+        <v>429</v>
+      </c>
+      <c r="D6" s="44" t="s">
         <v>430</v>
-      </c>
-      <c r="C6" s="44" t="s">
-        <v>431</v>
-      </c>
-      <c r="D6" s="44" t="s">
-        <v>432</v>
       </c>
       <c r="E6" s="44"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="51" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B7" s="47" t="s">
+        <v>428</v>
+      </c>
+      <c r="C7" s="44" t="s">
+        <v>429</v>
+      </c>
+      <c r="D7" s="44" t="s">
         <v>430</v>
-      </c>
-      <c r="C7" s="44" t="s">
-        <v>431</v>
-      </c>
-      <c r="D7" s="44" t="s">
-        <v>432</v>
       </c>
       <c r="E7" s="44" t="s">
         <v>12</v>
@@ -10355,7 +9980,7 @@
         <v>4</v>
       </c>
       <c r="H1" s="53" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="I1" s="53" t="s">
         <v>9</v>
@@ -10367,10 +9992,10 @@
         <v>210</v>
       </c>
       <c r="L1" s="42" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="M1" s="42" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="N1" s="42" t="s">
         <v>75</v>
@@ -10378,13 +10003,13 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="54" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B2" s="44">
         <v>2</v>
       </c>
       <c r="C2" s="47" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D2" s="44" t="s">
         <v>12</v>
@@ -10405,28 +10030,28 @@
         <v>212</v>
       </c>
       <c r="J2" s="44" t="s">
-        <v>748</v>
+        <v>596</v>
       </c>
       <c r="K2" s="44">
         <v>2</v>
       </c>
       <c r="L2" s="44" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="M2" s="44" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="N2" s="44"/>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="44" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B3" s="44">
         <v>2</v>
       </c>
       <c r="C3" s="47" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D3" s="44" t="s">
         <v>12</v>
@@ -10444,13 +10069,13 @@
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="55" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B4" s="44">
         <v>2</v>
       </c>
       <c r="C4" s="47" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D4" s="44" t="s">
         <v>12</v>
@@ -10465,13 +10090,13 @@
         <v>345</v>
       </c>
       <c r="H4" s="44" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I4" s="44" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="J4" s="44" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="K4" s="44"/>
       <c r="L4" s="44"/>
@@ -10482,13 +10107,13 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="44" t="s">
-        <v>547</v>
+        <v>463</v>
       </c>
       <c r="B5" s="44">
         <v>2</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>548</v>
+        <v>464</v>
       </c>
       <c r="D5" s="44" t="s">
         <v>12</v>
@@ -10503,13 +10128,13 @@
         <v>345</v>
       </c>
       <c r="H5" s="44" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I5" s="44" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="J5" s="44" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="K5" s="44"/>
       <c r="L5" s="44"/>
@@ -10640,7 +10265,7 @@
         <v>209</v>
       </c>
       <c r="E2" s="44" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -10674,7 +10299,7 @@
         <v>209</v>
       </c>
       <c r="E4" s="44" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -10691,7 +10316,7 @@
         <v>209</v>
       </c>
       <c r="E5" s="44" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -10805,16 +10430,16 @@
         <v>9</v>
       </c>
       <c r="S1" s="30" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="T1" s="30" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="U1" s="30" t="s">
         <v>30</v>
       </c>
       <c r="V1" s="30" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="2" spans="1:22">
@@ -10840,7 +10465,7 @@
         <v>15</v>
       </c>
       <c r="H2" s="32" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="I2" s="32" t="s">
         <v>211</v>
@@ -10857,14 +10482,14 @@
       <c r="M2" s="32"/>
       <c r="N2" s="32"/>
       <c r="O2" s="32" t="s">
-        <v>641</v>
+        <v>528</v>
       </c>
       <c r="P2" s="32"/>
       <c r="Q2" s="32" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="R2" s="32" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="S2" s="32"/>
       <c r="T2" s="32"/>
@@ -10981,7 +10606,7 @@
     </row>
     <row r="6" spans="1:22" s="29" customFormat="1">
       <c r="A6" s="32" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B6" s="44">
         <v>0</v>
@@ -11002,13 +10627,13 @@
         <v>15</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>642</v>
+        <v>529</v>
       </c>
       <c r="I6" s="32" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="J6" s="32" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="K6" s="32"/>
       <c r="L6" s="32"/>
@@ -11019,17 +10644,17 @@
       <c r="Q6" s="32"/>
       <c r="R6" s="32"/>
       <c r="S6" s="32" t="s">
-        <v>550</v>
+        <v>465</v>
       </c>
       <c r="T6" s="32" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="U6" s="32"/>
       <c r="V6" s="32"/>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="39" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B7" s="44">
         <v>0</v>
@@ -11050,13 +10675,13 @@
         <v>19</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>646</v>
+        <v>533</v>
       </c>
       <c r="I7" s="32" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="J7" s="32" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="K7" s="32"/>
       <c r="L7" s="32"/>
@@ -11073,7 +10698,7 @@
     </row>
     <row r="8" spans="1:22" s="29" customFormat="1">
       <c r="A8" s="32" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B8" s="44">
         <v>0</v>
@@ -11105,7 +10730,7 @@
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="39" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B9" s="44">
         <v>0</v>
@@ -11126,13 +10751,13 @@
         <v>15</v>
       </c>
       <c r="H9" s="32" t="s">
+        <v>364</v>
+      </c>
+      <c r="I9" s="32" t="s">
+        <v>365</v>
+      </c>
+      <c r="J9" s="32" t="s">
         <v>366</v>
-      </c>
-      <c r="I9" s="32" t="s">
-        <v>367</v>
-      </c>
-      <c r="J9" s="32" t="s">
-        <v>368</v>
       </c>
       <c r="K9" s="32"/>
       <c r="L9" s="32"/>
@@ -11149,7 +10774,7 @@
     </row>
     <row r="10" spans="1:22" s="29" customFormat="1">
       <c r="A10" s="32" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B10" s="44">
         <v>0</v>
@@ -11168,11 +10793,11 @@
       </c>
       <c r="G10" s="56"/>
       <c r="H10" s="32" t="s">
-        <v>643</v>
+        <v>530</v>
       </c>
       <c r="I10" s="32"/>
       <c r="J10" s="32" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="K10" s="32"/>
       <c r="L10" s="32"/>
@@ -11183,19 +10808,19 @@
       <c r="Q10" s="32"/>
       <c r="R10" s="32"/>
       <c r="S10" s="32" t="s">
-        <v>550</v>
+        <v>465</v>
       </c>
       <c r="T10" s="32" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="U10" s="32"/>
       <c r="V10" s="32" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="39" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B11" s="44">
         <v>0</v>
@@ -11216,7 +10841,7 @@
         <v>15</v>
       </c>
       <c r="H11" s="32" t="s">
-        <v>640</v>
+        <v>527</v>
       </c>
       <c r="I11" s="32" t="s">
         <v>211</v>
@@ -11231,25 +10856,25 @@
       <c r="O11" s="32"/>
       <c r="P11" s="32"/>
       <c r="Q11" s="32" t="s">
+        <v>371</v>
+      </c>
+      <c r="R11" s="32" t="s">
+        <v>372</v>
+      </c>
+      <c r="S11" s="32" t="s">
         <v>373</v>
       </c>
-      <c r="R11" s="32" t="s">
+      <c r="T11" s="32" t="s">
         <v>374</v>
       </c>
-      <c r="S11" s="32" t="s">
+      <c r="U11" s="32" t="s">
         <v>375</v>
-      </c>
-      <c r="T11" s="32" t="s">
-        <v>376</v>
-      </c>
-      <c r="U11" s="32" t="s">
-        <v>377</v>
       </c>
       <c r="V11" s="32"/>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="39" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B12" s="44">
         <v>2</v>
@@ -11268,19 +10893,19 @@
       </c>
       <c r="G12" s="56"/>
       <c r="H12" s="32" t="s">
-        <v>644</v>
+        <v>531</v>
       </c>
       <c r="I12" s="32" t="s">
+        <v>377</v>
+      </c>
+      <c r="J12" s="32" t="s">
+        <v>378</v>
+      </c>
+      <c r="K12" s="32" t="s">
         <v>379</v>
       </c>
-      <c r="J12" s="32" t="s">
-        <v>380</v>
-      </c>
-      <c r="K12" s="32" t="s">
-        <v>381</v>
-      </c>
       <c r="L12" s="32" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="M12" s="32"/>
       <c r="N12" s="32"/>
@@ -11289,25 +10914,25 @@
       <c r="Q12" s="32"/>
       <c r="R12" s="32"/>
       <c r="S12" s="32" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="T12" s="32" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="U12" s="32"/>
       <c r="V12" s="32" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="39" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B13" s="44">
         <v>3</v>
       </c>
       <c r="C13" s="47" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D13" s="44" t="s">
         <v>216</v>
@@ -11337,7 +10962,7 @@
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="39" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B14" s="44">
         <v>1</v>
@@ -11356,7 +10981,7 @@
       </c>
       <c r="G14" s="56"/>
       <c r="H14" s="32" t="s">
-        <v>645</v>
+        <v>532</v>
       </c>
       <c r="I14" s="32" t="s">
         <v>244</v>
@@ -11373,19 +10998,19 @@
       <c r="Q14" s="32"/>
       <c r="R14" s="32"/>
       <c r="S14" s="32" t="s">
-        <v>550</v>
+        <v>465</v>
       </c>
       <c r="T14" s="32" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="U14" s="32"/>
       <c r="V14" s="32" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="15" spans="1:22" s="29" customFormat="1">
       <c r="A15" s="39" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B15" s="44">
         <v>0</v>
@@ -11406,13 +11031,13 @@
         <v>15</v>
       </c>
       <c r="H15" s="32" t="s">
-        <v>639</v>
+        <v>526</v>
       </c>
       <c r="I15" s="32" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="J15" s="32" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="K15" s="32"/>
       <c r="L15" s="32"/>
@@ -12000,10 +11625,10 @@
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
       <c r="R2" s="3" t="s">
-        <v>647</v>
+        <v>534</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>648</v>
+        <v>535</v>
       </c>
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
@@ -12262,10 +11887,10 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3" t="s">
-        <v>651</v>
+        <v>538</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>652</v>
+        <v>539</v>
       </c>
       <c r="T8" s="3">
         <v>0</v>
@@ -12282,7 +11907,7 @@
         <v>2</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>553</v>
+        <v>466</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>12</v>
@@ -12311,10 +11936,10 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3" t="s">
-        <v>653</v>
+        <v>540</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>654</v>
+        <v>541</v>
       </c>
       <c r="T9" s="3"/>
       <c r="U9" s="3">
@@ -12335,7 +11960,7 @@
         <v>2</v>
       </c>
       <c r="C10" s="47" t="s">
-        <v>553</v>
+        <v>466</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>12</v>
@@ -12364,10 +11989,10 @@
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3" t="s">
-        <v>655</v>
+        <v>542</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>656</v>
+        <v>543</v>
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
@@ -12561,7 +12186,7 @@
         <v>2</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>553</v>
+        <v>466</v>
       </c>
       <c r="D16" s="32" t="s">
         <v>12</v>
@@ -12590,10 +12215,10 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3" t="s">
-        <v>649</v>
+        <v>536</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>650</v>
+        <v>537</v>
       </c>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
@@ -12825,7 +12450,7 @@
         <v>264</v>
       </c>
       <c r="F5" s="44" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="G5" s="44"/>
       <c r="H5" s="44"/>

--- a/src/test/java/TestData/Scenario_TestData.xlsx
+++ b/src/test/java/TestData/Scenario_TestData.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Copa_SHD_WebServices\src\test\java\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC2E262A-8EA1-4844-A249-6BB1BE3E2E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BF7513F-D4E8-44F3-A783-34C83AC232C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="7" activeTab="9" xr2:uid="{5D5A4724-D560-4FC2-9708-4BBF1DBA0B11}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="8" activeTab="10" xr2:uid="{5D5A4724-D560-4FC2-9708-4BBF1DBA0B11}"/>
   </bookViews>
   <sheets>
     <sheet name="AdvancePassengerInfo" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2084" uniqueCount="630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2078" uniqueCount="626">
   <si>
     <t>Scenario</t>
   </si>
@@ -1108,9 +1108,6 @@
     <t>354</t>
   </si>
   <si>
-    <t>441</t>
-  </si>
-  <si>
     <t>SJO</t>
   </si>
   <si>
@@ -1444,12 +1441,6 @@
     <t>A0HHSI</t>
   </si>
   <si>
-    <t>2023-08-20T04:51:00</t>
-  </si>
-  <si>
-    <t>2023-08-20T08:23:00</t>
-  </si>
-  <si>
     <t>2023-08-18T04:51:00</t>
   </si>
   <si>
@@ -1477,18 +1468,6 @@
     <t>122</t>
   </si>
   <si>
-    <t>A0JOAN</t>
-  </si>
-  <si>
-    <t>2302182801309</t>
-  </si>
-  <si>
-    <t>2302182801310</t>
-  </si>
-  <si>
-    <t>380</t>
-  </si>
-  <si>
     <t>473</t>
   </si>
   <si>
@@ -1783,36 +1762,6 @@
     <t>2302182807136</t>
   </si>
   <si>
-    <t>A2MQ50</t>
-  </si>
-  <si>
-    <t>2023-08-23T16:54:00</t>
-  </si>
-  <si>
-    <t>2023-08-23T20:23:00</t>
-  </si>
-  <si>
-    <t>2302182807137</t>
-  </si>
-  <si>
-    <t>A2MRAH</t>
-  </si>
-  <si>
-    <t>2302182807138</t>
-  </si>
-  <si>
-    <t>A2MRAX</t>
-  </si>
-  <si>
-    <t>2302182807139</t>
-  </si>
-  <si>
-    <t>A2MRA2</t>
-  </si>
-  <si>
-    <t>2302182807140</t>
-  </si>
-  <si>
     <t>A2MRBG</t>
   </si>
   <si>
@@ -1867,18 +1816,6 @@
     <t>A2MRG5</t>
   </si>
   <si>
-    <t>A2PNFL</t>
-  </si>
-  <si>
-    <t>AA2DB342CMCMRPCT052F39DE70</t>
-  </si>
-  <si>
-    <t>A1929E18CMCMRPCT06DFA232A0</t>
-  </si>
-  <si>
-    <t>7914A342CMCMRPCT05FAA95C7E</t>
-  </si>
-  <si>
     <t>A3RAZZ</t>
   </si>
   <si>
@@ -1951,12 +1888,6 @@
     <t>2302182816201</t>
   </si>
   <si>
-    <t>A4CGEE</t>
-  </si>
-  <si>
-    <t>2302182816228</t>
-  </si>
-  <si>
     <t>6759649826438453</t>
   </si>
   <si>
@@ -1964,13 +1895,69 @@
   </si>
   <si>
     <t>2302182816322</t>
+  </si>
+  <si>
+    <t>A340FE</t>
+  </si>
+  <si>
+    <t>2023-08-26T07:56:00</t>
+  </si>
+  <si>
+    <t>2023-08-26T12:05:00</t>
+  </si>
+  <si>
+    <t>2302182816168</t>
+  </si>
+  <si>
+    <t>A4FFSD</t>
+  </si>
+  <si>
+    <t>2302182816568</t>
+  </si>
+  <si>
+    <t>2302182816569</t>
+  </si>
+  <si>
+    <t>A340F1</t>
+  </si>
+  <si>
+    <t>2302182816169</t>
+  </si>
+  <si>
+    <t>A340GR</t>
+  </si>
+  <si>
+    <t>2302182816170</t>
+  </si>
+  <si>
+    <t>A340G0</t>
+  </si>
+  <si>
+    <t>2302182816171</t>
+  </si>
+  <si>
+    <t>485</t>
+  </si>
+  <si>
+    <t>173</t>
+  </si>
+  <si>
+    <t>A4IDBW</t>
+  </si>
+  <si>
+    <t>7744BA30CMCMRPCT055143D316</t>
+  </si>
+  <si>
+    <t>039672F2CMCMRPCT064917885D</t>
+  </si>
+  <si>
+    <t>73ADEAF0CMCMRPCT0853AFE719</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="13">
     <font>
       <sz val="11"/>
@@ -2200,7 +2187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2300,6 +2287,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2620,20 +2608,20 @@
   <dimension ref="A1:P15"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="52.81640625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="18.453125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="9.453125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="10.453125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="11.1796875"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="10.453125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="11.1796875"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="10.453125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="11.1796875"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="15.1796875"/>
+    <col min="1" max="1" width="52.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2706,7 +2694,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="44" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="I2" s="32" t="s">
         <v>211</v>
@@ -2723,7 +2711,7 @@
       <c r="M2" s="32"/>
       <c r="N2" s="32"/>
       <c r="O2" s="32" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="P2" s="38"/>
     </row>
@@ -2774,7 +2762,7 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="37" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B4" s="44">
         <v>0</v>
@@ -2795,13 +2783,13 @@
         <v>1</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="I4" s="37" t="s">
+        <v>351</v>
+      </c>
+      <c r="J4" s="37" t="s">
         <v>352</v>
-      </c>
-      <c r="J4" s="37" t="s">
-        <v>353</v>
       </c>
       <c r="K4" s="32"/>
       <c r="L4" s="32"/>
@@ -2811,7 +2799,7 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="37" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B5" s="44">
         <v>0</v>
@@ -2832,7 +2820,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="37" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="I5" s="32"/>
       <c r="J5" s="32"/>
@@ -2868,13 +2856,13 @@
   <dimension ref="A1:U22"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="49.0"/>
-    <col min="10" max="10" style="25" width="8.81640625"/>
-    <col min="12" max="12" customWidth="true" width="15.90625"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="9.81640625"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="13.90625"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="12.6328125"/>
+    <col min="1" max="1" width="49" customWidth="1"/>
+    <col min="10" max="10" width="8.81640625" style="25"/>
+    <col min="12" max="12" width="15.90625" customWidth="1"/>
+    <col min="17" max="17" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
@@ -2972,7 +2960,7 @@
       </c>
       <c r="J2" s="44"/>
       <c r="K2" s="44" t="s">
-        <v>601</v>
+        <v>580</v>
       </c>
       <c r="L2" s="44"/>
       <c r="M2" s="44"/>
@@ -3009,10 +2997,10 @@
         <v>0</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>616</v>
+        <v>595</v>
       </c>
       <c r="L3" s="44" t="s">
-        <v>617</v>
+        <v>596</v>
       </c>
       <c r="M3" s="44"/>
       <c r="N3" s="44"/>
@@ -3081,10 +3069,10 @@
       <c r="I5" s="44"/>
       <c r="J5" s="44"/>
       <c r="K5" s="44" t="s">
-        <v>602</v>
+        <v>581</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>603</v>
+        <v>582</v>
       </c>
       <c r="M5" s="44"/>
       <c r="N5" s="44" t="s">
@@ -3128,7 +3116,7 @@
       <c r="I6" s="44"/>
       <c r="J6" s="44"/>
       <c r="K6" s="44" t="s">
-        <v>604</v>
+        <v>583</v>
       </c>
       <c r="L6" s="44"/>
       <c r="M6" s="44"/>
@@ -3139,7 +3127,7 @@
         <v>242</v>
       </c>
       <c r="P6" s="44" t="s">
-        <v>605</v>
+        <v>584</v>
       </c>
       <c r="Q6" s="44"/>
       <c r="R6" s="44"/>
@@ -3173,10 +3161,10 @@
       <c r="I7" s="44"/>
       <c r="J7" s="44"/>
       <c r="K7" s="44" t="s">
-        <v>606</v>
+        <v>585</v>
       </c>
       <c r="L7" s="44" t="s">
-        <v>607</v>
+        <v>586</v>
       </c>
       <c r="M7" s="44"/>
       <c r="N7" s="44" t="s">
@@ -3186,13 +3174,13 @@
         <v>242</v>
       </c>
       <c r="P7" s="44" t="s">
-        <v>620</v>
+        <v>599</v>
       </c>
       <c r="Q7" s="47" t="s">
         <v>87</v>
       </c>
       <c r="R7" s="44" t="s">
-        <v>621</v>
+        <v>600</v>
       </c>
       <c r="S7" s="44"/>
       <c r="T7" s="44"/>
@@ -3228,10 +3216,10 @@
       </c>
       <c r="J8" s="44"/>
       <c r="K8" s="44" t="s">
-        <v>618</v>
+        <v>597</v>
       </c>
       <c r="L8" s="44" t="s">
-        <v>619</v>
+        <v>598</v>
       </c>
       <c r="M8" s="44"/>
       <c r="N8" s="44" t="s">
@@ -3269,7 +3257,7 @@
       <c r="I9" s="44"/>
       <c r="J9" s="44"/>
       <c r="K9" s="44" t="s">
-        <v>622</v>
+        <v>601</v>
       </c>
       <c r="L9" s="44"/>
       <c r="M9" s="44"/>
@@ -3308,10 +3296,10 @@
       <c r="I10" s="44"/>
       <c r="J10" s="44"/>
       <c r="K10" s="44" t="s">
-        <v>628</v>
+        <v>605</v>
       </c>
       <c r="L10" s="44" t="s">
-        <v>629</v>
+        <v>606</v>
       </c>
       <c r="M10" s="44"/>
       <c r="N10" s="44"/>
@@ -3320,7 +3308,7 @@
       <c r="Q10" s="44"/>
       <c r="R10" s="44"/>
       <c r="S10" s="47" t="s">
-        <v>627</v>
+        <v>604</v>
       </c>
       <c r="T10" s="44"/>
       <c r="U10" s="44"/>
@@ -3347,10 +3335,10 @@
       <c r="I11" s="44"/>
       <c r="J11" s="44"/>
       <c r="K11" s="44" t="s">
-        <v>608</v>
+        <v>587</v>
       </c>
       <c r="L11" s="44" t="s">
-        <v>609</v>
+        <v>588</v>
       </c>
       <c r="M11" s="44"/>
       <c r="N11" s="44"/>
@@ -3386,10 +3374,10 @@
       <c r="I12" s="44"/>
       <c r="J12" s="44"/>
       <c r="K12" s="44" t="s">
-        <v>623</v>
+        <v>602</v>
       </c>
       <c r="L12" s="44" t="s">
-        <v>624</v>
+        <v>603</v>
       </c>
       <c r="M12" s="44"/>
       <c r="N12" s="44" t="s">
@@ -3429,10 +3417,10 @@
       <c r="I13" s="44"/>
       <c r="J13" s="44"/>
       <c r="K13" s="44" t="s">
+        <v>449</v>
+      </c>
+      <c r="L13" s="44" t="s">
         <v>450</v>
-      </c>
-      <c r="L13" s="44" t="s">
-        <v>451</v>
       </c>
       <c r="M13" s="44"/>
       <c r="N13" s="44" t="s">
@@ -3507,10 +3495,10 @@
       <c r="I15" s="44"/>
       <c r="J15" s="44"/>
       <c r="K15" s="44" t="s">
-        <v>610</v>
+        <v>589</v>
       </c>
       <c r="L15" s="44" t="s">
-        <v>611</v>
+        <v>590</v>
       </c>
       <c r="M15" s="44"/>
       <c r="N15" s="44" t="s">
@@ -3536,7 +3524,7 @@
         <v>0</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>612</v>
+        <v>591</v>
       </c>
       <c r="D16" s="44" t="s">
         <v>12</v>
@@ -3550,7 +3538,7 @@
       <c r="I16" s="44"/>
       <c r="J16" s="44"/>
       <c r="K16" s="44" t="s">
-        <v>613</v>
+        <v>592</v>
       </c>
       <c r="L16" s="44"/>
       <c r="M16" s="44"/>
@@ -3589,7 +3577,7 @@
       <c r="I17" s="44"/>
       <c r="J17" s="44"/>
       <c r="K17" s="44" t="s">
-        <v>614</v>
+        <v>593</v>
       </c>
       <c r="L17" s="44"/>
       <c r="M17" s="44"/>
@@ -3632,7 +3620,7 @@
       </c>
       <c r="J18" s="44"/>
       <c r="K18" s="44" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="L18" s="44"/>
       <c r="M18" s="44"/>
@@ -3671,7 +3659,7 @@
       <c r="I19" s="44"/>
       <c r="J19" s="44"/>
       <c r="K19" s="44" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="L19" s="44"/>
       <c r="M19" s="44"/>
@@ -3710,7 +3698,7 @@
       <c r="I20" s="44"/>
       <c r="J20" s="44"/>
       <c r="K20" s="44" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="L20" s="44"/>
       <c r="M20" s="44"/>
@@ -3749,7 +3737,7 @@
       <c r="I21" s="44"/>
       <c r="J21" s="44"/>
       <c r="K21" s="44" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L21" s="44"/>
       <c r="M21" s="44"/>
@@ -3774,7 +3762,7 @@
         <v>1</v>
       </c>
       <c r="C22" s="47" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="D22" s="44" t="s">
         <v>34</v>
@@ -3796,7 +3784,7 @@
       </c>
       <c r="J22" s="44"/>
       <c r="K22" s="44" t="s">
-        <v>615</v>
+        <v>594</v>
       </c>
       <c r="L22" s="44"/>
       <c r="M22" s="44"/>
@@ -3823,192 +3811,164 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="32.90625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="3" max="3" customWidth="true" style="29" width="17.54296875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="5" max="5" customWidth="true" width="13.81640625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="14.36328125"/>
-    <col min="7" max="11" customWidth="true" style="29" width="14.36328125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="30.36328125"/>
-    <col min="13" max="13" customWidth="true" width="8.453125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="10.90625"/>
+    <col min="1" max="1" width="32.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.54296875" style="29" customWidth="1"/>
+    <col min="4" max="4" width="29.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.81640625" customWidth="1"/>
+    <col min="6" max="6" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="14.36328125" style="29" customWidth="1"/>
+    <col min="12" max="12" width="30.36328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:13">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="30" t="s">
+      <c r="B1" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="42" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="43" t="s">
+        <v>260</v>
+      </c>
+      <c r="E1" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1" s="42" t="s">
+        <v>261</v>
+      </c>
+      <c r="G1" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="H1" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="30" t="s">
+      <c r="I1" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="G1" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="30" t="s">
+      <c r="J1" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="30" t="s">
+      <c r="K1" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="30" t="s">
+      <c r="L1" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="L1" s="31" t="s">
-        <v>260</v>
-      </c>
-      <c r="M1" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="N1" s="30" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="35" t="s">
+      <c r="M1" s="42" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="44" t="s">
         <v>262</v>
       </c>
-      <c r="B2" s="32">
+      <c r="B2" s="44">
+        <v>2</v>
+      </c>
+      <c r="C2" s="44">
+        <v>2</v>
+      </c>
+      <c r="D2" s="47" t="s">
+        <v>623</v>
+      </c>
+      <c r="E2" s="47" t="s">
+        <v>622</v>
+      </c>
+      <c r="F2" s="44"/>
+      <c r="G2" s="47" t="s">
+        <v>620</v>
+      </c>
+      <c r="H2" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="44"/>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="44" t="s">
+        <v>263</v>
+      </c>
+      <c r="B3" s="44">
+        <v>2</v>
+      </c>
+      <c r="C3" s="44">
+        <v>2</v>
+      </c>
+      <c r="D3" s="47" t="s">
+        <v>624</v>
+      </c>
+      <c r="E3" s="47" t="s">
+        <v>264</v>
+      </c>
+      <c r="F3" s="44" t="s">
+        <v>149</v>
+      </c>
+      <c r="G3" s="47" t="s">
+        <v>620</v>
+      </c>
+      <c r="H3" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="44"/>
+      <c r="K3" s="44"/>
+      <c r="L3" s="44"/>
+      <c r="M3" s="44">
         <v>0</v>
       </c>
-      <c r="C2" s="47" t="s">
-        <v>470</v>
-      </c>
-      <c r="D2" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="F2" s="32">
-        <v>0</v>
-      </c>
-      <c r="G2" s="32">
-        <v>1</v>
-      </c>
-      <c r="H2" s="47" t="s">
-        <v>325</v>
-      </c>
-      <c r="I2" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="J2" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" s="32">
-        <v>1</v>
-      </c>
-      <c r="L2" s="34" t="s">
-        <v>598</v>
-      </c>
-      <c r="M2" s="34" t="s">
-        <v>597</v>
-      </c>
-      <c r="N2" s="32"/>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="B3" s="32">
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="44" t="s">
+        <v>265</v>
+      </c>
+      <c r="B4" s="44">
         <v>2</v>
       </c>
-      <c r="C3" s="34" t="s">
-        <v>344</v>
-      </c>
-      <c r="D3" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="32" t="s">
+      <c r="C4" s="44">
+        <v>2</v>
+      </c>
+      <c r="D4" s="47" t="s">
+        <v>625</v>
+      </c>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44" t="s">
+        <v>149</v>
+      </c>
+      <c r="G4" s="47" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="32">
-        <v>2</v>
-      </c>
-      <c r="G3" s="32">
-        <v>6</v>
-      </c>
-      <c r="H3" s="34" t="s">
-        <v>194</v>
-      </c>
-      <c r="I3" s="32" t="s">
+      <c r="J4" s="47" t="s">
+        <v>621</v>
+      </c>
+      <c r="K4" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="K3" s="32">
-        <v>6</v>
-      </c>
-      <c r="L3" s="34" t="s">
-        <v>599</v>
-      </c>
-      <c r="M3" s="34" t="s">
-        <v>264</v>
-      </c>
-      <c r="N3" s="32" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="32" t="s">
-        <v>265</v>
-      </c>
-      <c r="B4" s="32">
-        <v>2</v>
-      </c>
-      <c r="C4" s="34" t="s">
-        <v>344</v>
-      </c>
-      <c r="D4" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="32">
-        <v>2</v>
-      </c>
-      <c r="G4" s="32">
-        <v>6</v>
-      </c>
-      <c r="H4" s="34" t="s">
-        <v>194</v>
-      </c>
-      <c r="I4" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="K4" s="32">
-        <v>6</v>
-      </c>
-      <c r="L4" s="34" t="s">
-        <v>600</v>
-      </c>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32" t="s">
-        <v>149</v>
-      </c>
+      <c r="L4" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="M4" s="44"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4023,17 +3983,17 @@
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="29" width="21.81640625"/>
-    <col min="2" max="2" customWidth="true" style="29" width="16.54296875"/>
-    <col min="3" max="3" customWidth="true" style="29" width="19.90625"/>
-    <col min="4" max="4" customWidth="true" style="29" width="18.81640625"/>
-    <col min="5" max="6" customWidth="true" style="29" width="12.90625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="15.0"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="11.90625"/>
-    <col min="9" max="9" style="29" width="8.81640625"/>
-    <col min="10" max="10" customWidth="true" style="29" width="17.90625"/>
-    <col min="11" max="11" customWidth="true" style="29" width="14.1796875"/>
-    <col min="12" max="16384" style="29" width="8.81640625"/>
+    <col min="1" max="1" width="21.81640625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="16.54296875" style="29" customWidth="1"/>
+    <col min="3" max="3" width="19.90625" style="29" customWidth="1"/>
+    <col min="4" max="4" width="18.81640625" style="29" customWidth="1"/>
+    <col min="5" max="6" width="12.90625" style="29" customWidth="1"/>
+    <col min="7" max="7" width="15" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.90625" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.81640625" style="29"/>
+    <col min="10" max="10" width="17.90625" style="29" customWidth="1"/>
+    <col min="11" max="11" width="14.1796875" style="29" customWidth="1"/>
+    <col min="12" max="16384" width="8.81640625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -4085,7 +4045,7 @@
       <c r="G2" s="44"/>
       <c r="H2" s="44"/>
       <c r="I2" s="44" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="J2" s="44"/>
       <c r="K2" s="44"/>
@@ -4104,7 +4064,7 @@
       <c r="G3" s="44"/>
       <c r="H3" s="44"/>
       <c r="I3" s="44" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="J3" s="44"/>
       <c r="K3" s="44"/>
@@ -4123,7 +4083,7 @@
       <c r="G4" s="44"/>
       <c r="H4" s="44"/>
       <c r="I4" s="44" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="J4" s="44"/>
       <c r="K4" s="44"/>
@@ -4154,13 +4114,13 @@
         <v>12</v>
       </c>
       <c r="I5" s="44" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="J5" s="44" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -4189,10 +4149,10 @@
         <v>12</v>
       </c>
       <c r="I6" s="44" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="J6" s="44" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="K6" s="44"/>
     </row>
@@ -4209,12 +4169,12 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="29" width="42.1796875"/>
-    <col min="2" max="2" customWidth="true" style="29" width="15.81640625"/>
-    <col min="3" max="3" customWidth="true" style="29" width="17.81640625"/>
-    <col min="4" max="4" customWidth="true" style="29" width="16.81640625"/>
-    <col min="5" max="5" customWidth="true" style="29" width="15.6328125"/>
-    <col min="6" max="16384" style="29" width="8.81640625"/>
+    <col min="1" max="1" width="42.1796875" style="29" customWidth="1"/>
+    <col min="2" max="2" width="15.81640625" style="29" customWidth="1"/>
+    <col min="3" max="3" width="17.81640625" style="29" customWidth="1"/>
+    <col min="4" max="4" width="16.81640625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="15.6328125" style="29" customWidth="1"/>
+    <col min="6" max="16384" width="8.81640625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4260,7 +4220,7 @@
         <v>149</v>
       </c>
       <c r="D3" s="44" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E3" s="44">
         <v>1</v>
@@ -4277,7 +4237,7 @@
         <v>149</v>
       </c>
       <c r="D4" s="44" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E4" s="44">
         <v>1</v>
@@ -4285,7 +4245,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="37" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B5" s="37"/>
       <c r="C5" s="37" t="s">
@@ -4296,7 +4256,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="37" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B6" s="37"/>
       <c r="C6" s="37" t="s">
@@ -4309,7 +4269,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="37" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B7" s="37"/>
       <c r="C7" s="37" t="s">
@@ -4333,28 +4293,28 @@
   <dimension ref="A1:AB6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="51.81640625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="9.453125"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="18.453125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="14.453125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="18.453125"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="18.453125"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="12.08984375"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="15.36328125"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="12.08984375"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" width="15.36328125"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="1" max="1" width="51.81640625" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28">
@@ -4472,16 +4432,16 @@
         <v>45</v>
       </c>
       <c r="J2" s="44" t="s">
-        <v>589</v>
+        <v>572</v>
       </c>
       <c r="K2" s="44" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="L2" s="44" t="s">
         <v>207</v>
       </c>
       <c r="M2" s="44" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N2" s="44" t="s">
         <v>208</v>
@@ -4490,13 +4450,13 @@
         <v>12</v>
       </c>
       <c r="P2" s="44" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="Q2" s="44" t="s">
         <v>62</v>
       </c>
       <c r="R2" s="44" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="S2" s="44" t="s">
         <v>12</v>
@@ -4542,16 +4502,16 @@
         <v>45</v>
       </c>
       <c r="J3" s="44" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="L3" s="44" t="s">
         <v>207</v>
       </c>
       <c r="M3" s="44" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N3" s="44" t="s">
         <v>208</v>
@@ -4560,13 +4520,13 @@
         <v>12</v>
       </c>
       <c r="P3" s="44" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="Q3" s="44" t="s">
         <v>239</v>
       </c>
       <c r="R3" s="44" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="S3" s="44" t="s">
         <v>12</v>
@@ -4620,16 +4580,16 @@
       <c r="H4" s="44"/>
       <c r="I4" s="44"/>
       <c r="J4" s="44" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="K4" s="44" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="L4" s="44" t="s">
         <v>328</v>
       </c>
       <c r="M4" s="44" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="N4" s="44" t="s">
         <v>209</v>
@@ -4672,16 +4632,16 @@
       <c r="H5" s="44"/>
       <c r="I5" s="44"/>
       <c r="J5" s="44" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="L5" s="44" t="s">
         <v>328</v>
       </c>
       <c r="M5" s="44" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="N5" s="44" t="s">
         <v>209</v>
@@ -4732,16 +4692,16 @@
         <v>45</v>
       </c>
       <c r="J6" s="44" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="K6" s="44" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="L6" s="44" t="s">
         <v>207</v>
       </c>
       <c r="M6" s="44" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="N6" s="44" t="s">
         <v>208</v>
@@ -4777,10 +4737,10 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="76.1796875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="13.453125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="1" max="1" width="76.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4865,12 +4825,12 @@
   <dimension ref="A1:E15"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="68.08984375"/>
-    <col min="2" max="2" customWidth="true" style="29" width="12.54296875"/>
-    <col min="3" max="3" customWidth="true" style="29" width="14.81640625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="29" width="11.81640625"/>
-    <col min="5" max="5" customWidth="true" style="29" width="18.1796875"/>
-    <col min="6" max="16384" style="29" width="8.81640625"/>
+    <col min="1" max="1" width="68.08984375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.54296875" style="29" customWidth="1"/>
+    <col min="3" max="3" width="14.81640625" style="29" customWidth="1"/>
+    <col min="4" max="4" width="11.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.1796875" style="29" customWidth="1"/>
+    <col min="6" max="16384" width="8.81640625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -5006,7 +4966,7 @@
         <v>282</v>
       </c>
       <c r="D9" s="44" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E9" s="44"/>
     </row>
@@ -5117,8 +5077,8 @@
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="12.54296875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="1" max="1" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -5158,11 +5118,11 @@
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="33.54296875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="13.453125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="1" max="1" width="33.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -5212,7 +5172,7 @@
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="21.81640625"/>
+    <col min="1" max="1" width="21.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -5317,31 +5277,31 @@
   <dimension ref="A1:AG4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="49.81640625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="4.81640625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="9.81640625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="4.453125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="9.81640625"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="4.453125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="9.81640625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="4.453125"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="9.81640625"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="4.453125"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="9.81640625"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="4.453125"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="9.81640625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="4.453125"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="9.81640625"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="4.453125"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" width="9.7265625"/>
+    <col min="1" max="1" width="49.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="9.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33">
@@ -5525,7 +5485,7 @@
         <v>0</v>
       </c>
       <c r="AA2" s="44" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AB2" s="44" t="s">
         <v>45</v>
@@ -5537,7 +5497,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="44" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AF2" s="44" t="s">
         <v>45</v>
@@ -5646,25 +5606,25 @@
   <dimension ref="A1:AD9"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="33.0"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="18.36328125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="12.08984375"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="18.36328125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="15.36328125"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="13.90625"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="12.08984375"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="15.36328125"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="14.36328125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="12.08984375"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="15.36328125"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" width="12.08984375"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="1" max="1" width="33" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30">
@@ -5783,16 +5743,16 @@
       <c r="I2" s="44"/>
       <c r="J2" s="44"/>
       <c r="K2" s="44" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>325</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>209</v>
@@ -5847,7 +5807,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>312</v>
@@ -5987,16 +5947,16 @@
         <v>2</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>325</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>209</v>
@@ -6005,7 +5965,7 @@
         <v>12</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="R5" s="15" t="s">
         <v>44</v>
@@ -6203,16 +6163,16 @@
       <c r="I9" s="44"/>
       <c r="J9" s="44"/>
       <c r="K9" s="44" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>325</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>209</v>
@@ -6248,11 +6208,11 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="35.1796875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="11.54296875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="13.453125"/>
+    <col min="1" max="1" width="35.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -6277,10 +6237,10 @@
         <v>127</v>
       </c>
       <c r="B2" s="44" t="s">
+        <v>445</v>
+      </c>
+      <c r="C2" s="44" t="s">
         <v>446</v>
-      </c>
-      <c r="C2" s="44" t="s">
-        <v>447</v>
       </c>
       <c r="D2" s="44" t="s">
         <v>128</v>
@@ -6336,9 +6296,9 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="33.54296875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="13.453125"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="9.90625"/>
+    <col min="1" max="1" width="33.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -6394,9 +6354,9 @@
   <dimension ref="A1:AC4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="46.6328125"/>
-    <col min="5" max="5" customWidth="true" width="6.1796875"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="13.90625"/>
+    <col min="1" max="1" width="46.6328125" customWidth="1"/>
+    <col min="5" max="5" width="6.1796875" customWidth="1"/>
+    <col min="29" max="29" width="13.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -6524,16 +6484,16 @@
       <c r="U2" s="44"/>
       <c r="V2" s="44"/>
       <c r="W2" s="44" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="X2" s="44" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="Y2" s="44" t="s">
         <v>325</v>
       </c>
       <c r="Z2" s="44" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="AA2" s="44" t="s">
         <v>209</v>
@@ -6542,7 +6502,7 @@
         <v>12</v>
       </c>
       <c r="AC2" s="44" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -6660,16 +6620,16 @@
       <c r="U4" s="44"/>
       <c r="V4" s="44"/>
       <c r="W4" s="44" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="X4" s="44" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="Y4" s="44" t="s">
         <v>325</v>
       </c>
       <c r="Z4" s="44" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="AA4" s="44" t="s">
         <v>209</v>
@@ -6678,7 +6638,7 @@
         <v>12</v>
       </c>
       <c r="AC4" s="44" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
     </row>
   </sheetData>
@@ -6694,14 +6654,14 @@
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="63.81640625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="10.81640625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="19.453125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="15.54296875"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="8" max="9" bestFit="true" customWidth="true" width="19.453125"/>
+    <col min="1" max="1" width="63.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="19.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -6836,67 +6796,67 @@
   <dimension ref="A1:R6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="12.0"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="9.453125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="6.1796875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="13.81640625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="7.453125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="18.453125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="18.453125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="17" max="17" customWidth="true" width="17.6328125"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="13.90625"/>
+    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.6328125" customWidth="1"/>
+    <col min="18" max="18" width="13.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="42" t="s">
+      <c r="B1" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="42" t="s">
+      <c r="D1" s="58" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="42" t="s">
+      <c r="E1" s="58" t="s">
         <v>73</v>
       </c>
-      <c r="F1" s="42" t="s">
+      <c r="F1" s="65" t="s">
         <v>142</v>
       </c>
-      <c r="G1" s="42" t="s">
+      <c r="G1" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="42" t="s">
+      <c r="H1" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="42" t="s">
+      <c r="I1" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="K1" s="43" t="s">
+      <c r="J1" s="58" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="L1" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="M1" s="43" t="s">
+      <c r="L1" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="N1" s="43" t="s">
+      <c r="N1" s="19" t="s">
         <v>75</v>
       </c>
       <c r="O1" s="19" t="s">
@@ -6916,19 +6876,19 @@
       <c r="A2" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="44">
-        <v>1</v>
-      </c>
-      <c r="C2" s="44" t="s">
-        <v>329</v>
+      <c r="B2" s="47">
+        <v>1</v>
+      </c>
+      <c r="C2" s="47" t="s">
+        <v>18</v>
       </c>
       <c r="D2" s="44" t="s">
-        <v>209</v>
+        <v>12</v>
       </c>
       <c r="E2" s="44" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="44">
+        <v>13</v>
+      </c>
+      <c r="F2" s="47">
         <v>0</v>
       </c>
       <c r="G2" s="44"/>
@@ -6936,139 +6896,147 @@
       <c r="I2" s="44"/>
       <c r="J2" s="44"/>
       <c r="K2" s="44" t="s">
-        <v>569</v>
+        <v>607</v>
       </c>
       <c r="L2" s="44" t="s">
-        <v>570</v>
+        <v>608</v>
       </c>
       <c r="M2" s="44" t="s">
-        <v>329</v>
+        <v>18</v>
       </c>
       <c r="N2" s="44" t="s">
-        <v>571</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>572</v>
-      </c>
-      <c r="R2" s="3"/>
+        <v>609</v>
+      </c>
+      <c r="O2" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="P2" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="44" t="s">
+        <v>610</v>
+      </c>
+      <c r="R2" s="44"/>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="B3" s="44">
-        <v>2</v>
-      </c>
-      <c r="C3" s="44" t="s">
-        <v>325</v>
+      <c r="B3" s="47">
+        <v>1</v>
+      </c>
+      <c r="C3" s="47" t="s">
+        <v>18</v>
       </c>
       <c r="D3" s="44" t="s">
-        <v>209</v>
+        <v>12</v>
       </c>
       <c r="E3" s="44" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="44">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="F3" s="47">
+        <v>0</v>
       </c>
       <c r="G3" s="44"/>
       <c r="H3" s="44"/>
       <c r="I3" s="44"/>
       <c r="J3" s="44"/>
       <c r="K3" s="44" t="s">
-        <v>467</v>
+        <v>611</v>
       </c>
       <c r="L3" s="44" t="s">
-        <v>456</v>
+        <v>608</v>
       </c>
       <c r="M3" s="44" t="s">
-        <v>325</v>
+        <v>18</v>
       </c>
       <c r="N3" s="44" t="s">
-        <v>457</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>469</v>
+        <v>609</v>
+      </c>
+      <c r="O3" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="P3" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q3" s="44" t="s">
+        <v>612</v>
+      </c>
+      <c r="R3" s="44" t="s">
+        <v>613</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="B4" s="44">
-        <v>1</v>
-      </c>
-      <c r="C4" s="44" t="s">
-        <v>207</v>
+      <c r="B4" s="47">
+        <v>1</v>
+      </c>
+      <c r="C4" s="47" t="s">
+        <v>18</v>
       </c>
       <c r="D4" s="44" t="s">
-        <v>208</v>
+        <v>12</v>
       </c>
       <c r="E4" s="44" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="44">
+        <v>13</v>
+      </c>
+      <c r="F4" s="47">
         <v>0</v>
       </c>
-      <c r="G4" s="44"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="44"/>
+      <c r="G4" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="44" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4" s="44">
+        <v>2</v>
+      </c>
       <c r="K4" s="44" t="s">
-        <v>573</v>
+        <v>614</v>
       </c>
       <c r="L4" s="44" t="s">
-        <v>516</v>
+        <v>608</v>
       </c>
       <c r="M4" s="44" t="s">
-        <v>207</v>
+        <v>18</v>
       </c>
       <c r="N4" s="44" t="s">
-        <v>517</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>574</v>
-      </c>
-      <c r="R4" s="3"/>
+        <v>609</v>
+      </c>
+      <c r="O4" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="P4" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q4" s="44" t="s">
+        <v>615</v>
+      </c>
+      <c r="R4" s="44"/>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="B5" s="44">
-        <v>1</v>
-      </c>
-      <c r="C5" s="44" t="s">
-        <v>207</v>
+      <c r="B5" s="47">
+        <v>1</v>
+      </c>
+      <c r="C5" s="47" t="s">
+        <v>18</v>
       </c>
       <c r="D5" s="44" t="s">
-        <v>208</v>
+        <v>12</v>
       </c>
       <c r="E5" s="44" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="44">
+        <v>13</v>
+      </c>
+      <c r="F5" s="47">
         <v>0</v>
       </c>
       <c r="G5" s="44"/>
@@ -7076,45 +7044,45 @@
       <c r="I5" s="44"/>
       <c r="J5" s="44"/>
       <c r="K5" s="44" t="s">
-        <v>575</v>
+        <v>616</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>516</v>
+        <v>608</v>
       </c>
       <c r="M5" s="44" t="s">
-        <v>207</v>
+        <v>18</v>
       </c>
       <c r="N5" s="44" t="s">
-        <v>517</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>576</v>
-      </c>
-      <c r="R5" s="3"/>
+        <v>609</v>
+      </c>
+      <c r="O5" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="P5" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q5" s="44" t="s">
+        <v>617</v>
+      </c>
+      <c r="R5" s="44"/>
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="B6" s="44">
-        <v>1</v>
-      </c>
-      <c r="C6" s="44" t="s">
-        <v>207</v>
+      <c r="B6" s="47">
+        <v>1</v>
+      </c>
+      <c r="C6" s="47" t="s">
+        <v>18</v>
       </c>
       <c r="D6" s="44" t="s">
-        <v>208</v>
+        <v>12</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="44">
+        <v>13</v>
+      </c>
+      <c r="F6" s="47">
         <v>0</v>
       </c>
       <c r="G6" s="44"/>
@@ -7122,27 +7090,27 @@
       <c r="I6" s="44"/>
       <c r="J6" s="44"/>
       <c r="K6" s="44" t="s">
-        <v>577</v>
+        <v>618</v>
       </c>
       <c r="L6" s="44" t="s">
-        <v>516</v>
+        <v>608</v>
       </c>
       <c r="M6" s="44" t="s">
-        <v>207</v>
+        <v>18</v>
       </c>
       <c r="N6" s="44" t="s">
-        <v>517</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q6" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="R6" s="3"/>
+        <v>609</v>
+      </c>
+      <c r="O6" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="P6" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q6" s="44" t="s">
+        <v>619</v>
+      </c>
+      <c r="R6" s="44"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7158,27 +7126,27 @@
   <dimension ref="A1:U13"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="44.08984375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.36328125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="11.90625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="9.1796875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="6.1796875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="17.36328125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="11.90625"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="9.1796875"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="6.1796875"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="8.54296875"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="18.6328125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="11.90625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="18.6328125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="11.90625"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="18.6328125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="11.90625"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="18.6328125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="11.90625"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="14.08984375"/>
+    <col min="1" max="1" width="44.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.6328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.6328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.6328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.6328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
@@ -7275,16 +7243,16 @@
         <v>163</v>
       </c>
       <c r="J2" s="56" t="s">
-        <v>579</v>
+        <v>562</v>
       </c>
       <c r="K2" s="44" t="s">
-        <v>580</v>
+        <v>563</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>215</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>581</v>
+        <v>564</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>12</v>
@@ -7293,13 +7261,13 @@
         <v>216</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>582</v>
+        <v>565</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>217</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>583</v>
+        <v>566</v>
       </c>
       <c r="S2" s="3" t="s">
         <v>216</v>
@@ -7308,7 +7276,7 @@
         <v>163</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>584</v>
+        <v>567</v>
       </c>
     </row>
     <row r="3" spans="1:21">
@@ -7340,16 +7308,16 @@
         <v>163</v>
       </c>
       <c r="J3" s="56" t="s">
-        <v>585</v>
+        <v>568</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>580</v>
+        <v>563</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>215</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>581</v>
+        <v>564</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>12</v>
@@ -7358,13 +7326,13 @@
         <v>216</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>586</v>
+        <v>569</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>341</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>587</v>
+        <v>570</v>
       </c>
       <c r="S3" s="3" t="s">
         <v>216</v>
@@ -7373,7 +7341,7 @@
         <v>163</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>588</v>
+        <v>571</v>
       </c>
     </row>
     <row r="4" spans="1:21">
@@ -7553,8 +7521,8 @@
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="32.1796875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="1" max="1" width="32.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -7578,7 +7546,7 @@
         <v>181</v>
       </c>
       <c r="B3" s="64" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -7602,7 +7570,7 @@
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="18.0"/>
+    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -7663,21 +7631,21 @@
   <dimension ref="A1:N19"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="29" width="24.90625"/>
-    <col min="2" max="2" customWidth="true" style="29" width="14.0"/>
-    <col min="3" max="3" customWidth="true" style="29" width="11.81640625"/>
-    <col min="4" max="4" customWidth="true" style="29" width="9.54296875"/>
-    <col min="5" max="5" customWidth="true" style="29" width="10.36328125"/>
-    <col min="6" max="6" customWidth="true" style="29" width="9.36328125"/>
-    <col min="7" max="7" customWidth="true" style="29" width="9.7265625"/>
-    <col min="8" max="8" customWidth="true" style="29" width="10.453125"/>
-    <col min="9" max="9" customWidth="true" style="29" width="8.81640625"/>
-    <col min="10" max="10" customWidth="true" style="41" width="8.08984375"/>
-    <col min="11" max="11" customWidth="true" style="29" width="10.0"/>
-    <col min="12" max="12" customWidth="true" style="29" width="7.81640625"/>
-    <col min="13" max="13" customWidth="true" style="29" width="9.0"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="19.453125"/>
-    <col min="15" max="16384" style="29" width="8.81640625"/>
+    <col min="1" max="1" width="24.90625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="14" style="29" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" style="29" customWidth="1"/>
+    <col min="4" max="4" width="9.54296875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10.36328125" style="29" customWidth="1"/>
+    <col min="6" max="6" width="9.36328125" style="29" customWidth="1"/>
+    <col min="7" max="7" width="9.7265625" style="29" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" style="29" customWidth="1"/>
+    <col min="9" max="9" width="8.81640625" style="29" customWidth="1"/>
+    <col min="10" max="10" width="8.08984375" style="41" customWidth="1"/>
+    <col min="11" max="11" width="10" style="29" customWidth="1"/>
+    <col min="12" max="12" width="7.81640625" style="29" customWidth="1"/>
+    <col min="13" max="13" width="9" style="29" customWidth="1"/>
+    <col min="14" max="14" width="19.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.81640625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -7688,40 +7656,40 @@
         <v>266</v>
       </c>
       <c r="C1" s="42" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="D1" s="42" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="E1" s="42" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="F1" s="42" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="G1" s="63" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="H1" s="63" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="I1" s="63" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="J1" s="63" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="K1" s="42" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="L1" s="42" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="M1" s="42" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="N1" s="42" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -7732,40 +7700,40 @@
         <v>149</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="D2" s="32" t="s">
         <v>121</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="F2" s="44" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="G2" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H2" s="44" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="I2" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="J2" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="K2" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="L2" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="M2" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="N2" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -7776,40 +7744,40 @@
         <v>149</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="D3" s="32" t="s">
         <v>121</v>
       </c>
       <c r="E3" s="32" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="F3" s="44" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="G3" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H3" s="44" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="I3" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="J3" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="L3" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="M3" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="N3" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -7820,40 +7788,40 @@
         <v>149</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="D4" s="32" t="s">
         <v>121</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="F4" s="44" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="G4" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H4" s="44" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="I4" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="J4" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="K4" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="L4" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="M4" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="N4" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -7864,40 +7832,40 @@
         <v>149</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="D5" s="32" t="s">
         <v>121</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="F5" s="44" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="G5" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H5" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="I5" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="J5" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="M5" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="N5" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -7908,40 +7876,40 @@
         <v>149</v>
       </c>
       <c r="C6" s="44" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="D6" s="44" t="s">
         <v>121</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="F6" s="44" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="G6" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H6" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="I6" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="J6" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="K6" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="L6" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="M6" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="N6" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -7952,40 +7920,40 @@
         <v>149</v>
       </c>
       <c r="C7" s="44" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="D7" s="44" t="s">
         <v>121</v>
       </c>
       <c r="E7" s="44" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="F7" s="44" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="G7" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H7" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="I7" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="J7" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="K7" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="L7" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="M7" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="N7" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -7996,40 +7964,40 @@
         <v>149</v>
       </c>
       <c r="C8" s="44" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="D8" s="44" t="s">
         <v>121</v>
       </c>
       <c r="E8" s="44" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="F8" s="44" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="G8" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H8" s="44" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="I8" s="44" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="J8" s="44" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="K8" s="44" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="L8" s="44" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="M8" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="N8" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -8040,40 +8008,40 @@
         <v>149</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="D9" s="32" t="s">
         <v>121</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="F9" s="44" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="G9" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H9" s="44" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="I9" s="44" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="J9" s="44" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="K9" s="44" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="L9" s="44" t="s">
+        <v>481</v>
+      </c>
+      <c r="M9" s="44" t="s">
+        <v>428</v>
+      </c>
+      <c r="N9" s="44" t="s">
         <v>488</v>
-      </c>
-      <c r="M9" s="44" t="s">
-        <v>429</v>
-      </c>
-      <c r="N9" s="44" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -8084,40 +8052,40 @@
         <v>149</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="D10" s="44" t="s">
         <v>121</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="F10" s="44" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="G10" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H10" s="44" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="I10" s="44" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="J10" s="44" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="K10" s="44" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="L10" s="44" t="s">
+        <v>481</v>
+      </c>
+      <c r="M10" s="44" t="s">
+        <v>494</v>
+      </c>
+      <c r="N10" s="44" t="s">
         <v>488</v>
-      </c>
-      <c r="M10" s="44" t="s">
-        <v>501</v>
-      </c>
-      <c r="N10" s="44" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -8128,40 +8096,40 @@
         <v>149</v>
       </c>
       <c r="C11" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D11" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="F11" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="G11" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="H11" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="I11" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="J11" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="K11" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="L11" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="M11" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="N11" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -8172,40 +8140,40 @@
         <v>149</v>
       </c>
       <c r="C12" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D12" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="F12" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="G12" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="H12" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="I12" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="J12" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="K12" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="L12" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="M12" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="N12" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -8216,40 +8184,40 @@
         <v>149</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="F13" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="G13" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="H13" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="I13" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="J13" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="K13" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="L13" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="M13" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="N13" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -8260,40 +8228,40 @@
         <v>149</v>
       </c>
       <c r="C14" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="F14" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="G14" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="H14" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="I14" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="J14" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="K14" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="L14" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="M14" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="N14" s="44" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -8304,40 +8272,40 @@
         <v>149</v>
       </c>
       <c r="C15" s="44" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="D15" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="E15" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="F15" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="G15" s="44" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="H15" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="I15" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="J15" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="K15" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="L15" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="M15" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="N15" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -8345,43 +8313,43 @@
         <v>303</v>
       </c>
       <c r="B16" s="32" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="D16" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="F16" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="G16" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="H16" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="I16" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="J16" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="K16" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="L16" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="M16" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="N16" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -8392,45 +8360,45 @@
         <v>149</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="D17" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="F17" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="G17" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="H17" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="I17" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="J17" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="K17" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="L17" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="M17" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="N17" s="44" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="62" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
     </row>
   </sheetData>
@@ -8447,14 +8415,14 @@
   <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="39.453125"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="21.81640625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="9.453125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="6.453125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="18.453125"/>
+    <col min="1" max="1" width="39.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -8509,10 +8477,10 @@
         <v>50</v>
       </c>
       <c r="H2" s="44" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="I2" s="44" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -8538,10 +8506,10 @@
         <v>50</v>
       </c>
       <c r="H3" s="44" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I3" s="44" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
   </sheetData>
@@ -8558,18 +8526,18 @@
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="32.1796875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="4" max="4" customWidth="true" width="15.453125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="17.36328125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="11.90625"/>
-    <col min="13" max="13" customWidth="true" width="15.08984375"/>
+    <col min="1" max="1" width="32.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.453125" customWidth="1"/>
+    <col min="5" max="5" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -8723,16 +8691,16 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="35" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C6" s="35" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="44" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E6" s="35">
         <v>2</v>
@@ -8742,7 +8710,7 @@
       <c r="H6" s="44"/>
       <c r="I6" s="44"/>
       <c r="J6" s="44" t="s">
-        <v>590</v>
+        <v>573</v>
       </c>
       <c r="K6" s="44"/>
       <c r="L6" s="44"/>
@@ -8761,16 +8729,16 @@
   <dimension ref="A1:K4"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="29" width="17.90625"/>
-    <col min="2" max="2" customWidth="true" style="29" width="11.81640625"/>
-    <col min="3" max="3" customWidth="true" style="29" width="13.0"/>
-    <col min="4" max="4" customWidth="true" style="29" width="16.54296875"/>
-    <col min="5" max="5" customWidth="true" style="29" width="15.81640625"/>
-    <col min="6" max="6" style="29" width="8.81640625"/>
-    <col min="7" max="7" customWidth="true" style="29" width="17.81640625"/>
-    <col min="8" max="8" customWidth="true" style="29" width="15.453125"/>
-    <col min="9" max="9" customWidth="true" style="29" width="11.54296875"/>
-    <col min="10" max="16384" style="29" width="8.81640625"/>
+    <col min="1" max="1" width="17.90625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="11.81640625" style="29" customWidth="1"/>
+    <col min="3" max="3" width="13" style="29" customWidth="1"/>
+    <col min="4" max="4" width="16.54296875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="15.81640625" style="29" customWidth="1"/>
+    <col min="6" max="6" width="8.81640625" style="29"/>
+    <col min="7" max="7" width="17.81640625" style="29" customWidth="1"/>
+    <col min="8" max="8" width="15.453125" style="29" customWidth="1"/>
+    <col min="9" max="9" width="11.54296875" style="29" customWidth="1"/>
+    <col min="10" max="16384" width="8.81640625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -8825,7 +8793,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>591</v>
+        <v>574</v>
       </c>
       <c r="G2" s="32">
         <v>2</v>
@@ -8856,7 +8824,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>592</v>
+        <v>575</v>
       </c>
       <c r="G3" s="32"/>
       <c r="H3" s="32"/>
@@ -8885,7 +8853,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>593</v>
+        <v>576</v>
       </c>
       <c r="G4" s="32"/>
       <c r="H4" s="32"/>
@@ -8906,19 +8874,19 @@
   <dimension ref="A1:M3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="19.90625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="11.90625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="11.90625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="17.36328125"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="11.90625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="11.90625"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="17.36328125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="4.453125"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="17.36328125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="11.90625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="14.1796875"/>
+    <col min="1" max="1" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -8964,7 +8932,7 @@
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="44" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B2" s="47" t="s">
         <v>32</v>
@@ -8987,7 +8955,7 @@
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="44" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B3" s="47" t="s">
         <v>325</v>
@@ -9021,20 +8989,20 @@
   <dimension ref="A1:M4"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="41" width="25.81640625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="41" width="11.90625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="41" width="15.0"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="41" width="11.90625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="41" width="11.90625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="41" width="15.0"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="41" width="11.90625"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="41" width="4.453125"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="41" width="11.90625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="41" width="14.1796875"/>
-    <col min="14" max="16384" style="41" width="8.90625"/>
+    <col min="1" max="1" width="25.81640625" style="41" customWidth="1"/>
+    <col min="2" max="2" width="11.90625" style="41" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="41" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.90625" style="41" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.90625" style="41" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15" style="41" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.90625" style="41" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.453125" style="41" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.90625" style="41" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.1796875" style="41" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.90625" style="41"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -9080,10 +9048,10 @@
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="44" t="s">
+        <v>394</v>
+      </c>
+      <c r="B2" s="47" t="s">
         <v>395</v>
-      </c>
-      <c r="B2" s="47" t="s">
-        <v>396</v>
       </c>
       <c r="C2" s="44" t="s">
         <v>12</v>
@@ -9103,10 +9071,10 @@
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="48" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B3" s="47" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C3" s="44" t="s">
         <v>12</v>
@@ -9126,7 +9094,7 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="44" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B4" s="47" t="s">
         <v>336</v>
@@ -9160,21 +9128,21 @@
   <dimension ref="A1:O5"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="41" width="20.1796875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="41" width="11.90625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="41" width="15.0"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="41" width="11.90625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
-    <col min="6" max="7" customWidth="true" style="41" width="17.36328125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="41" width="11.90625"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="41" width="15.0"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="41" width="11.90625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="41" width="4.453125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="41" width="11.90625"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" style="41" width="14.1796875"/>
-    <col min="16" max="16384" style="41" width="8.90625"/>
+    <col min="1" max="1" width="20.1796875" style="41" customWidth="1"/>
+    <col min="2" max="2" width="11.90625" style="41" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="41" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.90625" style="41" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="17.36328125" style="41" customWidth="1"/>
+    <col min="8" max="8" width="11.90625" style="41" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15" style="41" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.90625" style="41" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.453125" style="41" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.90625" style="41" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.1796875" style="41" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.90625" style="41"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -9194,7 +9162,7 @@
         <v>1</v>
       </c>
       <c r="F1" s="42" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G1" s="42" t="s">
         <v>30</v>
@@ -9226,7 +9194,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="44" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B2" s="47" t="s">
         <v>332</v>
@@ -9241,10 +9209,10 @@
         <v>2</v>
       </c>
       <c r="F2" s="44" t="s">
+        <v>400</v>
+      </c>
+      <c r="G2" s="44" t="s">
         <v>401</v>
-      </c>
-      <c r="G2" s="44" t="s">
-        <v>402</v>
       </c>
       <c r="H2" s="44"/>
       <c r="I2" s="44"/>
@@ -9257,7 +9225,7 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="44" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B3" s="47" t="s">
         <v>332</v>
@@ -9272,10 +9240,10 @@
         <v>2</v>
       </c>
       <c r="F3" s="44" t="s">
+        <v>400</v>
+      </c>
+      <c r="G3" s="44" t="s">
         <v>401</v>
-      </c>
-      <c r="G3" s="44" t="s">
-        <v>402</v>
       </c>
       <c r="H3" s="44"/>
       <c r="I3" s="44"/>
@@ -9288,7 +9256,7 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="44" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B4" s="47" t="s">
         <v>332</v>
@@ -9303,10 +9271,10 @@
         <v>2</v>
       </c>
       <c r="F4" s="44" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G4" s="44" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H4" s="44"/>
       <c r="I4" s="44"/>
@@ -9319,7 +9287,7 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="44" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B5" s="47" t="s">
         <v>332</v>
@@ -9334,10 +9302,10 @@
         <v>2</v>
       </c>
       <c r="F5" s="44" t="s">
+        <v>400</v>
+      </c>
+      <c r="G5" s="44" t="s">
         <v>401</v>
-      </c>
-      <c r="G5" s="44" t="s">
-        <v>402</v>
       </c>
       <c r="H5" s="44"/>
       <c r="I5" s="44"/>
@@ -9361,22 +9329,22 @@
   <dimension ref="A1:O10"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="41" width="28.36328125"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="41" width="11.90625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="41" width="15.0"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="41" width="11.90625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="41" width="16.81640625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="41" width="11.08984375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="41" width="11.90625"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="41" width="15.0"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="41" width="11.90625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
-    <col min="12" max="12" customWidth="true" style="41" width="13.08984375"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="41" width="11.90625"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" style="41" width="14.1796875"/>
-    <col min="16" max="16384" style="41" width="8.90625"/>
+    <col min="1" max="1" width="28.36328125" style="41" customWidth="1"/>
+    <col min="2" max="2" width="11.90625" style="41" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="41" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.90625" style="41" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.81640625" style="41" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.08984375" style="41" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.90625" style="41" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15" style="41" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.90625" style="41" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.08984375" style="41" customWidth="1"/>
+    <col min="13" max="13" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.90625" style="41" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.1796875" style="41" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.90625" style="41"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -9396,10 +9364,10 @@
         <v>1</v>
       </c>
       <c r="F1" s="42" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G1" s="42" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1" s="43" t="s">
         <v>74</v>
@@ -9408,23 +9376,23 @@
         <v>8</v>
       </c>
       <c r="J1" s="43" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K1" s="43" t="s">
         <v>75</v>
       </c>
       <c r="L1" s="43" t="s">
+        <v>354</v>
+      </c>
+      <c r="M1" s="43" t="s">
         <v>355</v>
-      </c>
-      <c r="M1" s="43" t="s">
-        <v>356</v>
       </c>
       <c r="N1" s="40"/>
       <c r="O1" s="46"/>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="44" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B2" s="47" t="s">
         <v>32</v>
@@ -9447,7 +9415,7 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="44" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B3" s="47" t="s">
         <v>32</v>
@@ -9472,16 +9440,16 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="44" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B4" s="47" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C4" s="44" t="s">
         <v>12</v>
       </c>
       <c r="D4" s="44" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E4" s="44">
         <v>1</v>
@@ -9491,34 +9459,34 @@
       </c>
       <c r="G4" s="44"/>
       <c r="H4" s="44" t="s">
-        <v>594</v>
+        <v>577</v>
       </c>
       <c r="I4" s="44" t="s">
+        <v>387</v>
+      </c>
+      <c r="J4" s="44" t="s">
         <v>388</v>
-      </c>
-      <c r="J4" s="44" t="s">
-        <v>389</v>
       </c>
       <c r="K4" s="44"/>
       <c r="L4" s="44" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="M4" s="44" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="44" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B5" s="47" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C5" s="44" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="44" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E5" s="44">
         <v>1</v>
@@ -9528,25 +9496,25 @@
       </c>
       <c r="G5" s="44"/>
       <c r="H5" s="44" t="s">
-        <v>595</v>
+        <v>578</v>
       </c>
       <c r="I5" s="44" t="s">
+        <v>387</v>
+      </c>
+      <c r="J5" s="44" t="s">
         <v>388</v>
-      </c>
-      <c r="J5" s="44" t="s">
-        <v>389</v>
       </c>
       <c r="K5" s="44"/>
       <c r="L5" s="44" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="M5" s="44" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="44" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B6" s="47" t="s">
         <v>32</v>
@@ -9569,7 +9537,7 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="44" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B7" s="47" t="s">
         <v>32</v>
@@ -9592,7 +9560,7 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="44" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B8" s="47" t="s">
         <v>32</v>
@@ -9617,7 +9585,7 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="44" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B9" s="47" t="s">
         <v>32</v>
@@ -9642,7 +9610,7 @@
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="44" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B10" s="47" t="s">
         <v>32</v>
@@ -9676,11 +9644,11 @@
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="41" width="24.0"/>
-    <col min="2" max="2" customWidth="true" style="41" width="11.453125"/>
-    <col min="3" max="3" style="41" width="8.90625"/>
-    <col min="4" max="4" customWidth="true" style="41" width="19.6328125"/>
-    <col min="5" max="16384" style="41" width="8.90625"/>
+    <col min="1" max="1" width="24" style="41" customWidth="1"/>
+    <col min="2" max="2" width="11.453125" style="41" customWidth="1"/>
+    <col min="3" max="3" width="8.90625" style="41"/>
+    <col min="4" max="4" width="19.6328125" style="41" customWidth="1"/>
+    <col min="5" max="16384" width="8.90625" style="41"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9699,10 +9667,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="44" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B2" s="47" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C2" s="44" t="s">
         <v>12</v>
@@ -9724,12 +9692,12 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="41" width="32.1796875"/>
-    <col min="2" max="2" customWidth="true" style="41" width="14.0"/>
-    <col min="3" max="3" customWidth="true" style="41" width="16.6328125"/>
-    <col min="4" max="4" customWidth="true" style="41" width="17.6328125"/>
-    <col min="5" max="5" customWidth="true" style="41" width="11.81640625"/>
-    <col min="6" max="16384" style="41" width="8.90625"/>
+    <col min="1" max="1" width="32.1796875" style="41" customWidth="1"/>
+    <col min="2" max="2" width="14" style="41" customWidth="1"/>
+    <col min="3" max="3" width="16.6328125" style="41" customWidth="1"/>
+    <col min="4" max="4" width="17.6328125" style="41" customWidth="1"/>
+    <col min="5" max="5" width="11.81640625" style="41" customWidth="1"/>
+    <col min="6" max="16384" width="8.90625" style="41"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -9751,7 +9719,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="44" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B2" s="47" t="s">
         <v>32</v>
@@ -9768,10 +9736,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="44" t="s">
+        <v>419</v>
+      </c>
+      <c r="B3" s="47" t="s">
         <v>420</v>
-      </c>
-      <c r="B3" s="47" t="s">
-        <v>421</v>
       </c>
       <c r="C3" s="44" t="s">
         <v>12</v>
@@ -9785,10 +9753,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="44" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B4" s="47" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C4" s="44" t="s">
         <v>12</v>
@@ -9813,11 +9781,11 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="41" width="38.1796875"/>
-    <col min="2" max="2" customWidth="true" style="41" width="13.54296875"/>
-    <col min="3" max="3" customWidth="true" style="41" width="15.54296875"/>
-    <col min="4" max="4" customWidth="true" style="41" width="19.0"/>
-    <col min="5" max="16384" style="41" width="8.90625"/>
+    <col min="1" max="1" width="38.1796875" style="41" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" style="41" customWidth="1"/>
+    <col min="3" max="3" width="15.54296875" style="41" customWidth="1"/>
+    <col min="4" max="4" width="19" style="41" customWidth="1"/>
+    <col min="5" max="16384" width="8.90625" style="41"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -9825,30 +9793,30 @@
         <v>0</v>
       </c>
       <c r="B1" s="49" t="s">
+        <v>422</v>
+      </c>
+      <c r="C1" s="49" t="s">
         <v>423</v>
       </c>
-      <c r="C1" s="49" t="s">
+      <c r="D1" s="49" t="s">
         <v>424</v>
       </c>
-      <c r="D1" s="49" t="s">
+      <c r="E1" s="49" t="s">
         <v>425</v>
-      </c>
-      <c r="E1" s="49" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="44" t="s">
+        <v>426</v>
+      </c>
+      <c r="B2" s="47" t="s">
         <v>427</v>
       </c>
-      <c r="B2" s="47" t="s">
+      <c r="C2" s="44" t="s">
         <v>428</v>
       </c>
-      <c r="C2" s="44" t="s">
+      <c r="D2" s="44" t="s">
         <v>429</v>
-      </c>
-      <c r="D2" s="44" t="s">
-        <v>430</v>
       </c>
       <c r="E2" s="44" t="s">
         <v>12</v>
@@ -9856,16 +9824,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="44" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B3" s="47" t="s">
+        <v>427</v>
+      </c>
+      <c r="C3" s="44" t="s">
         <v>428</v>
       </c>
-      <c r="C3" s="44" t="s">
+      <c r="D3" s="44" t="s">
         <v>429</v>
-      </c>
-      <c r="D3" s="44" t="s">
-        <v>430</v>
       </c>
       <c r="E3" s="44" t="s">
         <v>12</v>
@@ -9873,23 +9841,23 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="44" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B4" s="44"/>
       <c r="C4" s="44"/>
       <c r="D4" s="44" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E4" s="44"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="44" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B5" s="44"/>
       <c r="C5" s="44"/>
       <c r="D5" s="44" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E5" s="44" t="s">
         <v>12</v>
@@ -9897,31 +9865,31 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="50" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B6" s="47" t="s">
+        <v>427</v>
+      </c>
+      <c r="C6" s="44" t="s">
         <v>428</v>
       </c>
-      <c r="C6" s="44" t="s">
+      <c r="D6" s="44" t="s">
         <v>429</v>
-      </c>
-      <c r="D6" s="44" t="s">
-        <v>430</v>
       </c>
       <c r="E6" s="44"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="51" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B7" s="47" t="s">
+        <v>427</v>
+      </c>
+      <c r="C7" s="44" t="s">
         <v>428</v>
       </c>
-      <c r="C7" s="44" t="s">
+      <c r="D7" s="44" t="s">
         <v>429</v>
-      </c>
-      <c r="D7" s="44" t="s">
-        <v>430</v>
       </c>
       <c r="E7" s="44" t="s">
         <v>12</v>
@@ -9940,21 +9908,21 @@
   <dimension ref="A1:N5"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="41" width="30.90625"/>
-    <col min="2" max="2" customWidth="true" style="41" width="17.81640625"/>
-    <col min="3" max="3" customWidth="true" style="41" width="16.453125"/>
-    <col min="4" max="4" customWidth="true" style="41" width="16.08984375"/>
-    <col min="5" max="5" customWidth="true" style="41" width="12.0"/>
-    <col min="6" max="6" customWidth="true" style="41" width="18.08984375"/>
-    <col min="7" max="7" customWidth="true" style="41" width="15.08984375"/>
-    <col min="8" max="8" customWidth="true" style="41" width="10.453125"/>
-    <col min="9" max="9" customWidth="true" style="41" width="10.81640625"/>
-    <col min="10" max="10" style="41" width="8.90625"/>
-    <col min="11" max="11" customWidth="true" style="41" width="13.1796875"/>
-    <col min="12" max="12" customWidth="true" style="41" width="12.6328125"/>
-    <col min="13" max="13" customWidth="true" style="41" width="14.08984375"/>
-    <col min="14" max="14" customWidth="true" style="41" width="14.36328125"/>
-    <col min="15" max="16384" style="41" width="8.90625"/>
+    <col min="1" max="1" width="30.90625" style="41" customWidth="1"/>
+    <col min="2" max="2" width="17.81640625" style="41" customWidth="1"/>
+    <col min="3" max="3" width="16.453125" style="41" customWidth="1"/>
+    <col min="4" max="4" width="16.08984375" style="41" customWidth="1"/>
+    <col min="5" max="5" width="12" style="41" customWidth="1"/>
+    <col min="6" max="6" width="18.08984375" style="41" customWidth="1"/>
+    <col min="7" max="7" width="15.08984375" style="41" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" style="41" customWidth="1"/>
+    <col min="9" max="9" width="10.81640625" style="41" customWidth="1"/>
+    <col min="10" max="10" width="8.90625" style="41"/>
+    <col min="11" max="11" width="13.1796875" style="41" customWidth="1"/>
+    <col min="12" max="12" width="12.6328125" style="41" customWidth="1"/>
+    <col min="13" max="13" width="14.08984375" style="41" customWidth="1"/>
+    <col min="14" max="14" width="14.36328125" style="41" customWidth="1"/>
+    <col min="15" max="16384" width="8.90625" style="41"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -9980,7 +9948,7 @@
         <v>4</v>
       </c>
       <c r="H1" s="53" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="I1" s="53" t="s">
         <v>9</v>
@@ -9992,10 +9960,10 @@
         <v>210</v>
       </c>
       <c r="L1" s="42" t="s">
+        <v>354</v>
+      </c>
+      <c r="M1" s="42" t="s">
         <v>355</v>
-      </c>
-      <c r="M1" s="42" t="s">
-        <v>356</v>
       </c>
       <c r="N1" s="42" t="s">
         <v>75</v>
@@ -10003,13 +9971,13 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="54" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B2" s="44">
         <v>2</v>
       </c>
       <c r="C2" s="47" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D2" s="44" t="s">
         <v>12</v>
@@ -10021,7 +9989,7 @@
         <v>12</v>
       </c>
       <c r="G2" s="44" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H2" s="44" t="s">
         <v>211</v>
@@ -10030,28 +9998,28 @@
         <v>212</v>
       </c>
       <c r="J2" s="44" t="s">
-        <v>596</v>
+        <v>579</v>
       </c>
       <c r="K2" s="44">
         <v>2</v>
       </c>
       <c r="L2" s="44" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="M2" s="44" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="N2" s="44"/>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="44" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B3" s="44">
         <v>2</v>
       </c>
       <c r="C3" s="47" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D3" s="44" t="s">
         <v>12</v>
@@ -10069,13 +10037,13 @@
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="55" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B4" s="44">
         <v>2</v>
       </c>
       <c r="C4" s="47" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D4" s="44" t="s">
         <v>12</v>
@@ -10087,16 +10055,16 @@
         <v>12</v>
       </c>
       <c r="G4" s="44" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H4" s="44" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I4" s="44" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="J4" s="44" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="K4" s="44"/>
       <c r="L4" s="44"/>
@@ -10107,13 +10075,13 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="44" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B5" s="44">
         <v>2</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D5" s="44" t="s">
         <v>12</v>
@@ -10125,16 +10093,16 @@
         <v>12</v>
       </c>
       <c r="G5" s="44" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H5" s="44" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I5" s="44" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="J5" s="44" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="K5" s="44"/>
       <c r="L5" s="44"/>
@@ -10156,11 +10124,11 @@
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="39.453125"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="13.54296875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="7.81640625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="1" max="1" width="39.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -10228,10 +10196,10 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="57.453125"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="15.54296875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="7.81640625"/>
-    <col min="4" max="5" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="1" max="1" width="57.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -10265,7 +10233,7 @@
         <v>209</v>
       </c>
       <c r="E2" s="44" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -10299,7 +10267,7 @@
         <v>209</v>
       </c>
       <c r="E4" s="44" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -10316,7 +10284,7 @@
         <v>209</v>
       </c>
       <c r="E5" s="44" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -10350,28 +10318,28 @@
   <dimension ref="A1:V15"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="25" width="50.0"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="25" width="18.36328125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="25" width="12.08984375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="25" width="15.36328125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="25" width="12.1796875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="25" width="9.453125"/>
-    <col min="7" max="8" style="25" width="8.81640625"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="25" width="10.453125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="25" width="12.6328125"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="25" width="10.453125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="25" width="11.1796875"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="25" width="10.453125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="25" width="8.1796875"/>
-    <col min="15" max="15" customWidth="true" style="25" width="13.0"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" style="25" width="10.1796875"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="25" width="10.453125"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="25" width="9.1796875"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="25" width="11.6328125"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="25" width="12.6328125"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="25" width="11.1796875"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="25" width="12.6328125"/>
-    <col min="23" max="16384" style="25" width="8.81640625"/>
+    <col min="1" max="1" width="50" style="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.36328125" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.08984375" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.36328125" style="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1796875" style="25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.453125" style="25" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="8.81640625" style="25"/>
+    <col min="9" max="9" width="10.453125" style="25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.6328125" style="25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.453125" style="25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.1796875" style="25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.453125" style="25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.1796875" style="25" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13" style="25" customWidth="1"/>
+    <col min="16" max="16" width="10.1796875" style="25" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.453125" style="25" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.1796875" style="25" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.6328125" style="25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.6328125" style="25" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.1796875" style="25" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.6328125" style="25" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="8.81640625" style="25"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
@@ -10430,16 +10398,16 @@
         <v>9</v>
       </c>
       <c r="S1" s="30" t="s">
+        <v>354</v>
+      </c>
+      <c r="T1" s="30" t="s">
         <v>355</v>
-      </c>
-      <c r="T1" s="30" t="s">
-        <v>356</v>
       </c>
       <c r="U1" s="30" t="s">
         <v>30</v>
       </c>
       <c r="V1" s="30" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2" spans="1:22">
@@ -10465,7 +10433,7 @@
         <v>15</v>
       </c>
       <c r="H2" s="32" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="I2" s="32" t="s">
         <v>211</v>
@@ -10482,14 +10450,14 @@
       <c r="M2" s="32"/>
       <c r="N2" s="32"/>
       <c r="O2" s="32" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="P2" s="32"/>
       <c r="Q2" s="32" t="s">
+        <v>357</v>
+      </c>
+      <c r="R2" s="32" t="s">
         <v>358</v>
-      </c>
-      <c r="R2" s="32" t="s">
-        <v>359</v>
       </c>
       <c r="S2" s="32"/>
       <c r="T2" s="32"/>
@@ -10606,7 +10574,7 @@
     </row>
     <row r="6" spans="1:22" s="29" customFormat="1">
       <c r="A6" s="32" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B6" s="44">
         <v>0</v>
@@ -10627,13 +10595,13 @@
         <v>15</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="I6" s="32" t="s">
+        <v>387</v>
+      </c>
+      <c r="J6" s="32" t="s">
         <v>388</v>
-      </c>
-      <c r="J6" s="32" t="s">
-        <v>389</v>
       </c>
       <c r="K6" s="32"/>
       <c r="L6" s="32"/>
@@ -10644,17 +10612,17 @@
       <c r="Q6" s="32"/>
       <c r="R6" s="32"/>
       <c r="S6" s="32" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="T6" s="32" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="U6" s="32"/>
       <c r="V6" s="32"/>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="39" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B7" s="44">
         <v>0</v>
@@ -10675,13 +10643,13 @@
         <v>19</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="I7" s="32" t="s">
+        <v>360</v>
+      </c>
+      <c r="J7" s="32" t="s">
         <v>361</v>
-      </c>
-      <c r="J7" s="32" t="s">
-        <v>362</v>
       </c>
       <c r="K7" s="32"/>
       <c r="L7" s="32"/>
@@ -10698,7 +10666,7 @@
     </row>
     <row r="8" spans="1:22" s="29" customFormat="1">
       <c r="A8" s="32" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B8" s="44">
         <v>0</v>
@@ -10730,7 +10698,7 @@
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="39" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B9" s="44">
         <v>0</v>
@@ -10751,13 +10719,13 @@
         <v>15</v>
       </c>
       <c r="H9" s="32" t="s">
+        <v>363</v>
+      </c>
+      <c r="I9" s="32" t="s">
         <v>364</v>
       </c>
-      <c r="I9" s="32" t="s">
+      <c r="J9" s="32" t="s">
         <v>365</v>
-      </c>
-      <c r="J9" s="32" t="s">
-        <v>366</v>
       </c>
       <c r="K9" s="32"/>
       <c r="L9" s="32"/>
@@ -10774,7 +10742,7 @@
     </row>
     <row r="10" spans="1:22" s="29" customFormat="1">
       <c r="A10" s="32" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B10" s="44">
         <v>0</v>
@@ -10793,11 +10761,11 @@
       </c>
       <c r="G10" s="56"/>
       <c r="H10" s="32" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="I10" s="32"/>
       <c r="J10" s="32" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="K10" s="32"/>
       <c r="L10" s="32"/>
@@ -10808,19 +10776,19 @@
       <c r="Q10" s="32"/>
       <c r="R10" s="32"/>
       <c r="S10" s="32" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="T10" s="32" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="U10" s="32"/>
       <c r="V10" s="32" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="39" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B11" s="44">
         <v>0</v>
@@ -10841,7 +10809,7 @@
         <v>15</v>
       </c>
       <c r="H11" s="32" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="I11" s="32" t="s">
         <v>211</v>
@@ -10856,25 +10824,25 @@
       <c r="O11" s="32"/>
       <c r="P11" s="32"/>
       <c r="Q11" s="32" t="s">
+        <v>370</v>
+      </c>
+      <c r="R11" s="32" t="s">
         <v>371</v>
       </c>
-      <c r="R11" s="32" t="s">
+      <c r="S11" s="32" t="s">
         <v>372</v>
       </c>
-      <c r="S11" s="32" t="s">
+      <c r="T11" s="32" t="s">
         <v>373</v>
       </c>
-      <c r="T11" s="32" t="s">
+      <c r="U11" s="32" t="s">
         <v>374</v>
-      </c>
-      <c r="U11" s="32" t="s">
-        <v>375</v>
       </c>
       <c r="V11" s="32"/>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="39" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B12" s="44">
         <v>2</v>
@@ -10893,19 +10861,19 @@
       </c>
       <c r="G12" s="56"/>
       <c r="H12" s="32" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="I12" s="32" t="s">
+        <v>376</v>
+      </c>
+      <c r="J12" s="32" t="s">
         <v>377</v>
       </c>
-      <c r="J12" s="32" t="s">
+      <c r="K12" s="32" t="s">
         <v>378</v>
       </c>
-      <c r="K12" s="32" t="s">
-        <v>379</v>
-      </c>
       <c r="L12" s="32" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="M12" s="32"/>
       <c r="N12" s="32"/>
@@ -10914,25 +10882,25 @@
       <c r="Q12" s="32"/>
       <c r="R12" s="32"/>
       <c r="S12" s="32" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="T12" s="32" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="U12" s="32"/>
       <c r="V12" s="32" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="39" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B13" s="44">
         <v>3</v>
       </c>
       <c r="C13" s="47" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D13" s="44" t="s">
         <v>216</v>
@@ -10962,7 +10930,7 @@
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="39" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B14" s="44">
         <v>1</v>
@@ -10981,7 +10949,7 @@
       </c>
       <c r="G14" s="56"/>
       <c r="H14" s="32" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="I14" s="32" t="s">
         <v>244</v>
@@ -10998,19 +10966,19 @@
       <c r="Q14" s="32"/>
       <c r="R14" s="32"/>
       <c r="S14" s="32" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="T14" s="32" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="U14" s="32"/>
       <c r="V14" s="32" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="15" spans="1:22" s="29" customFormat="1">
       <c r="A15" s="39" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B15" s="44">
         <v>0</v>
@@ -11031,13 +10999,13 @@
         <v>15</v>
       </c>
       <c r="H15" s="32" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="I15" s="32" t="s">
+        <v>367</v>
+      </c>
+      <c r="J15" s="32" t="s">
         <v>368</v>
-      </c>
-      <c r="J15" s="32" t="s">
-        <v>369</v>
       </c>
       <c r="K15" s="32"/>
       <c r="L15" s="32"/>
@@ -11066,29 +11034,29 @@
   <dimension ref="A1:AB7"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="44.81640625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.81640625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="8.1796875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="11.1796875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="10.453125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="13.54296875"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="17.81640625"/>
-    <col min="11" max="12" bestFit="true" customWidth="true" width="11.1796875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="18.1796875"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="7.81640625"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="11.1796875"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="8.1796875"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="11.1796875"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="11.1796875"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="14.1796875"/>
-    <col min="27" max="28" bestFit="true" customWidth="true" width="12.81640625"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="14.1796875"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="12.81640625"/>
+    <col min="1" max="1" width="44.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28">
@@ -11520,9 +11488,9 @@
   <dimension ref="A1:W17"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="54.36328125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="13.90625"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="13.81640625"/>
+    <col min="1" max="1" width="54.36328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -11625,10 +11593,10 @@
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
       <c r="R2" s="3" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
@@ -11887,10 +11855,10 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="T8" s="3">
         <v>0</v>
@@ -11907,7 +11875,7 @@
         <v>2</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>12</v>
@@ -11936,10 +11904,10 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="T9" s="3"/>
       <c r="U9" s="3">
@@ -11960,7 +11928,7 @@
         <v>2</v>
       </c>
       <c r="C10" s="47" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>12</v>
@@ -11989,10 +11957,10 @@
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
@@ -12186,7 +12154,7 @@
         <v>2</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="D16" s="32" t="s">
         <v>12</v>
@@ -12215,10 +12183,10 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
@@ -12273,16 +12241,16 @@
   <dimension ref="A1:S20"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="53.81640625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="3" max="4" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="5" max="7" customWidth="true" width="12.1796875"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="1" max="1" width="53.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="12.1796875" customWidth="1"/>
+    <col min="8" max="8" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
@@ -12450,7 +12418,7 @@
         <v>264</v>
       </c>
       <c r="F5" s="44" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G5" s="44"/>
       <c r="H5" s="44"/>

--- a/src/test/java/TestData/Scenario_TestData.xlsx
+++ b/src/test/java/TestData/Scenario_TestData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Copa_SHD_WebServices\src\test\java\TestData\"/>
     </mc:Choice>
@@ -55,7 +55,7 @@
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2078" uniqueCount="626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2124" uniqueCount="642">
   <si>
     <t>Scenario</t>
   </si>
@@ -1952,12 +1952,61 @@
   </si>
   <si>
     <t>73ADEAF0CMCMRPCT0853AFE719</t>
+  </si>
+  <si>
+    <t>A4INPS</t>
+  </si>
+  <si>
+    <t>2302182817362</t>
+  </si>
+  <si>
+    <t>A4INWJ</t>
+  </si>
+  <si>
+    <t>2302182817363</t>
+  </si>
+  <si>
+    <t>2302182817364</t>
+  </si>
+  <si>
+    <t>A4INYY</t>
+  </si>
+  <si>
+    <t>2302182817365</t>
+  </si>
+  <si>
+    <t>A4IN3U</t>
+  </si>
+  <si>
+    <t>2302182817367</t>
+  </si>
+  <si>
+    <t>A4IOCB</t>
+  </si>
+  <si>
+    <t>2302182817371</t>
+  </si>
+  <si>
+    <t>A4ITS0</t>
+  </si>
+  <si>
+    <t>2302182817412</t>
+  </si>
+  <si>
+    <t>2302182817413</t>
+  </si>
+  <si>
+    <t>2182817427</t>
+  </si>
+  <si>
+    <t>2182817428</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="13">
     <font>
       <sz val="11"/>
@@ -2608,20 +2657,20 @@
   <dimension ref="A1:P15"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="52.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="52.81640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="18.453125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="9.453125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="10.453125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="10.453125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="10.453125"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="15.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2856,13 +2905,13 @@
   <dimension ref="A1:U22"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="49" customWidth="1"/>
-    <col min="10" max="10" width="8.81640625" style="25"/>
-    <col min="12" max="12" width="15.90625" customWidth="1"/>
-    <col min="17" max="17" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="49.0"/>
+    <col min="10" max="10" style="25" width="8.81640625"/>
+    <col min="12" max="12" customWidth="true" width="15.90625"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="13.90625"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="12.6328125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
@@ -3814,16 +3863,16 @@
   <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="32.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.54296875" style="29" customWidth="1"/>
-    <col min="4" max="4" width="29.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.81640625" customWidth="1"/>
-    <col min="6" max="6" width="14.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="14.36328125" style="29" customWidth="1"/>
-    <col min="12" max="12" width="30.36328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="32.90625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="3" max="3" customWidth="true" style="29" width="17.54296875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="29.7265625"/>
+    <col min="5" max="5" customWidth="true" width="13.81640625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="14.36328125"/>
+    <col min="7" max="11" customWidth="true" style="29" width="14.36328125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="30.36328125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="13.81640625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="10.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -3983,17 +4032,17 @@
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="21.81640625" style="29" customWidth="1"/>
-    <col min="2" max="2" width="16.54296875" style="29" customWidth="1"/>
-    <col min="3" max="3" width="19.90625" style="29" customWidth="1"/>
-    <col min="4" max="4" width="18.81640625" style="29" customWidth="1"/>
-    <col min="5" max="6" width="12.90625" style="29" customWidth="1"/>
-    <col min="7" max="7" width="15" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.90625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.81640625" style="29"/>
-    <col min="10" max="10" width="17.90625" style="29" customWidth="1"/>
-    <col min="11" max="11" width="14.1796875" style="29" customWidth="1"/>
-    <col min="12" max="16384" width="8.81640625" style="29"/>
+    <col min="1" max="1" customWidth="true" style="29" width="21.81640625"/>
+    <col min="2" max="2" customWidth="true" style="29" width="16.54296875"/>
+    <col min="3" max="3" customWidth="true" style="29" width="19.90625"/>
+    <col min="4" max="4" customWidth="true" style="29" width="18.81640625"/>
+    <col min="5" max="6" customWidth="true" style="29" width="12.90625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="15.0"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="11.90625"/>
+    <col min="9" max="9" style="29" width="8.81640625"/>
+    <col min="10" max="10" customWidth="true" style="29" width="17.90625"/>
+    <col min="11" max="11" customWidth="true" style="29" width="14.1796875"/>
+    <col min="12" max="16384" style="29" width="8.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -4169,12 +4218,12 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="42.1796875" style="29" customWidth="1"/>
-    <col min="2" max="2" width="15.81640625" style="29" customWidth="1"/>
-    <col min="3" max="3" width="17.81640625" style="29" customWidth="1"/>
-    <col min="4" max="4" width="16.81640625" style="29" customWidth="1"/>
-    <col min="5" max="5" width="15.6328125" style="29" customWidth="1"/>
-    <col min="6" max="16384" width="8.81640625" style="29"/>
+    <col min="1" max="1" customWidth="true" style="29" width="42.1796875"/>
+    <col min="2" max="2" customWidth="true" style="29" width="15.81640625"/>
+    <col min="3" max="3" customWidth="true" style="29" width="17.81640625"/>
+    <col min="4" max="4" customWidth="true" style="29" width="16.81640625"/>
+    <col min="5" max="5" customWidth="true" style="29" width="15.6328125"/>
+    <col min="6" max="16384" style="29" width="8.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4293,28 +4342,28 @@
   <dimension ref="A1:AB6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="51.81640625" customWidth="1"/>
-    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="51.81640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="9.453125"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="18.453125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="14.453125"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="18.453125"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="18.453125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="12.08984375"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="15.36328125"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="12.08984375"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" width="15.36328125"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" width="12.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28">
@@ -4737,10 +4786,10 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="76.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="76.1796875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="13.453125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="12.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4825,12 +4874,12 @@
   <dimension ref="A1:E15"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="68.08984375" style="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.54296875" style="29" customWidth="1"/>
-    <col min="3" max="3" width="14.81640625" style="29" customWidth="1"/>
-    <col min="4" max="4" width="11.81640625" style="29" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.1796875" style="29" customWidth="1"/>
-    <col min="6" max="16384" width="8.81640625" style="29"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="68.08984375"/>
+    <col min="2" max="2" customWidth="true" style="29" width="12.54296875"/>
+    <col min="3" max="3" customWidth="true" style="29" width="14.81640625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="29" width="11.81640625"/>
+    <col min="5" max="5" customWidth="true" style="29" width="18.1796875"/>
+    <col min="6" max="16384" style="29" width="8.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -5077,8 +5126,8 @@
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="12.54296875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -5118,11 +5167,11 @@
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="33.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="33.54296875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="13.453125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="12.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -5172,7 +5221,7 @@
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="21.81640625" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="21.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -5277,31 +5326,31 @@
   <dimension ref="A1:AG4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="49.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="49.81640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="4.81640625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="4.453125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="4.453125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="4.453125"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="4.453125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="4.453125"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="4.453125"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="9.81640625"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="4.453125"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" width="9.7265625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33">
@@ -5606,25 +5655,25 @@
   <dimension ref="A1:AD9"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="33" customWidth="1"/>
-    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.36328125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="33.0"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="18.36328125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="12.08984375"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="18.36328125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="15.36328125"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="13.90625"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="12.08984375"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="15.36328125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="14.36328125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="12.08984375"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="15.36328125"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" width="12.08984375"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="17.54296875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30">
@@ -6208,11 +6257,11 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="35.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="35.1796875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="11.54296875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="13.453125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -6296,9 +6345,9 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="33.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="33.54296875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="13.453125"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="9.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -6354,9 +6403,9 @@
   <dimension ref="A1:AC4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="46.6328125" customWidth="1"/>
-    <col min="5" max="5" width="6.1796875" customWidth="1"/>
-    <col min="29" max="29" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="46.6328125"/>
+    <col min="5" max="5" customWidth="true" width="6.1796875"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="13.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -6654,14 +6703,14 @@
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="63.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="63.81640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="10.81640625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="19.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="15.54296875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="8" max="9" bestFit="true" customWidth="true" width="19.453125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -6796,24 +6845,24 @@
   <dimension ref="A1:R6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.6328125" customWidth="1"/>
-    <col min="18" max="18" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="12.0"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="9.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="6.1796875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="13.81640625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="7.453125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="18.453125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="18.453125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="17" max="17" customWidth="true" width="17.6328125"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="13.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -6896,7 +6945,7 @@
       <c r="I2" s="44"/>
       <c r="J2" s="44"/>
       <c r="K2" s="44" t="s">
-        <v>607</v>
+        <v>626</v>
       </c>
       <c r="L2" s="44" t="s">
         <v>608</v>
@@ -6914,7 +6963,7 @@
         <v>13</v>
       </c>
       <c r="Q2" s="44" t="s">
-        <v>610</v>
+        <v>627</v>
       </c>
       <c r="R2" s="44"/>
     </row>
@@ -6942,7 +6991,7 @@
       <c r="I3" s="44"/>
       <c r="J3" s="44"/>
       <c r="K3" s="44" t="s">
-        <v>611</v>
+        <v>637</v>
       </c>
       <c r="L3" s="44" t="s">
         <v>608</v>
@@ -6960,10 +7009,10 @@
         <v>13</v>
       </c>
       <c r="Q3" s="44" t="s">
-        <v>612</v>
+        <v>638</v>
       </c>
       <c r="R3" s="44" t="s">
-        <v>613</v>
+        <v>639</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -6998,7 +7047,7 @@
         <v>2</v>
       </c>
       <c r="K4" s="44" t="s">
-        <v>614</v>
+        <v>631</v>
       </c>
       <c r="L4" s="44" t="s">
         <v>608</v>
@@ -7016,7 +7065,7 @@
         <v>13</v>
       </c>
       <c r="Q4" s="44" t="s">
-        <v>615</v>
+        <v>641</v>
       </c>
       <c r="R4" s="44"/>
     </row>
@@ -7044,7 +7093,7 @@
       <c r="I5" s="44"/>
       <c r="J5" s="44"/>
       <c r="K5" s="44" t="s">
-        <v>616</v>
+        <v>633</v>
       </c>
       <c r="L5" s="44" t="s">
         <v>608</v>
@@ -7062,7 +7111,7 @@
         <v>13</v>
       </c>
       <c r="Q5" s="44" t="s">
-        <v>617</v>
+        <v>634</v>
       </c>
       <c r="R5" s="44"/>
     </row>
@@ -7090,7 +7139,7 @@
       <c r="I6" s="44"/>
       <c r="J6" s="44"/>
       <c r="K6" s="44" t="s">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="L6" s="44" t="s">
         <v>608</v>
@@ -7108,7 +7157,7 @@
         <v>13</v>
       </c>
       <c r="Q6" s="44" t="s">
-        <v>619</v>
+        <v>636</v>
       </c>
       <c r="R6" s="44"/>
     </row>
@@ -7126,27 +7175,27 @@
   <dimension ref="A1:U13"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="44.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.6328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.6328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.6328125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.6328125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="44.08984375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.36328125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="9.1796875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="6.1796875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="17.36328125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="9.1796875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="6.1796875"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="8.54296875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="18.6328125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="18.6328125"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="18.6328125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="18.6328125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="14.08984375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
@@ -7521,8 +7570,8 @@
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="32.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="32.1796875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -7570,7 +7619,7 @@
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="18.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -7631,21 +7680,21 @@
   <dimension ref="A1:N19"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="24.90625" style="29" customWidth="1"/>
-    <col min="2" max="2" width="14" style="29" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" style="29" customWidth="1"/>
-    <col min="4" max="4" width="9.54296875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="10.36328125" style="29" customWidth="1"/>
-    <col min="6" max="6" width="9.36328125" style="29" customWidth="1"/>
-    <col min="7" max="7" width="9.7265625" style="29" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" style="29" customWidth="1"/>
-    <col min="9" max="9" width="8.81640625" style="29" customWidth="1"/>
-    <col min="10" max="10" width="8.08984375" style="41" customWidth="1"/>
-    <col min="11" max="11" width="10" style="29" customWidth="1"/>
-    <col min="12" max="12" width="7.81640625" style="29" customWidth="1"/>
-    <col min="13" max="13" width="9" style="29" customWidth="1"/>
-    <col min="14" max="14" width="19.453125" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.81640625" style="29"/>
+    <col min="1" max="1" customWidth="true" style="29" width="24.90625"/>
+    <col min="2" max="2" customWidth="true" style="29" width="14.0"/>
+    <col min="3" max="3" customWidth="true" style="29" width="11.81640625"/>
+    <col min="4" max="4" customWidth="true" style="29" width="9.54296875"/>
+    <col min="5" max="5" customWidth="true" style="29" width="10.36328125"/>
+    <col min="6" max="6" customWidth="true" style="29" width="9.36328125"/>
+    <col min="7" max="7" customWidth="true" style="29" width="9.7265625"/>
+    <col min="8" max="8" customWidth="true" style="29" width="10.453125"/>
+    <col min="9" max="9" customWidth="true" style="29" width="8.81640625"/>
+    <col min="10" max="10" customWidth="true" style="41" width="8.08984375"/>
+    <col min="11" max="11" customWidth="true" style="29" width="10.0"/>
+    <col min="12" max="12" customWidth="true" style="29" width="7.81640625"/>
+    <col min="13" max="13" customWidth="true" style="29" width="9.0"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="19.453125"/>
+    <col min="15" max="16384" style="29" width="8.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -8415,14 +8464,14 @@
   <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="39.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="39.453125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="21.81640625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="9.453125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="6.453125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="18.453125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -8526,18 +8575,18 @@
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="32.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.453125" customWidth="1"/>
-    <col min="5" max="5" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.08984375" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="32.1796875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="4" max="4" customWidth="true" width="15.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="17.36328125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="13" max="13" customWidth="true" width="15.08984375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -8729,16 +8778,16 @@
   <dimension ref="A1:K4"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.90625" style="29" customWidth="1"/>
-    <col min="2" max="2" width="11.81640625" style="29" customWidth="1"/>
-    <col min="3" max="3" width="13" style="29" customWidth="1"/>
-    <col min="4" max="4" width="16.54296875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="15.81640625" style="29" customWidth="1"/>
-    <col min="6" max="6" width="8.81640625" style="29"/>
-    <col min="7" max="7" width="17.81640625" style="29" customWidth="1"/>
-    <col min="8" max="8" width="15.453125" style="29" customWidth="1"/>
-    <col min="9" max="9" width="11.54296875" style="29" customWidth="1"/>
-    <col min="10" max="16384" width="8.81640625" style="29"/>
+    <col min="1" max="1" customWidth="true" style="29" width="17.90625"/>
+    <col min="2" max="2" customWidth="true" style="29" width="11.81640625"/>
+    <col min="3" max="3" customWidth="true" style="29" width="13.0"/>
+    <col min="4" max="4" customWidth="true" style="29" width="16.54296875"/>
+    <col min="5" max="5" customWidth="true" style="29" width="15.81640625"/>
+    <col min="6" max="6" style="29" width="8.81640625"/>
+    <col min="7" max="7" customWidth="true" style="29" width="17.81640625"/>
+    <col min="8" max="8" customWidth="true" style="29" width="15.453125"/>
+    <col min="9" max="9" customWidth="true" style="29" width="11.54296875"/>
+    <col min="10" max="16384" style="29" width="8.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -8874,19 +8923,19 @@
   <dimension ref="A1:M3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="19.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="19.90625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="17.36328125"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="17.36328125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="4.453125"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="17.36328125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="11.90625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="14.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -8989,20 +9038,20 @@
   <dimension ref="A1:M4"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="25.81640625" style="41" customWidth="1"/>
-    <col min="2" max="2" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="41" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15" style="41" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.453125" style="41" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.1796875" style="41" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.90625" style="41"/>
+    <col min="1" max="1" customWidth="true" style="41" width="25.81640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="41" width="15.0"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="41" width="15.0"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="41" width="4.453125"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="41" width="14.1796875"/>
+    <col min="14" max="16384" style="41" width="8.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -9128,21 +9177,21 @@
   <dimension ref="A1:O5"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="20.1796875" style="41" customWidth="1"/>
-    <col min="2" max="2" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="41" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="17.36328125" style="41" customWidth="1"/>
-    <col min="8" max="8" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15" style="41" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.453125" style="41" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.1796875" style="41" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.90625" style="41"/>
+    <col min="1" max="1" customWidth="true" style="41" width="20.1796875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="41" width="15.0"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
+    <col min="6" max="7" customWidth="true" style="41" width="17.36328125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="41" width="15.0"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="41" width="4.453125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="41" width="14.1796875"/>
+    <col min="16" max="16384" style="41" width="8.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -9329,22 +9378,22 @@
   <dimension ref="A1:O10"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="28.36328125" style="41" customWidth="1"/>
-    <col min="2" max="2" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="41" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.81640625" style="41" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.08984375" style="41" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15" style="41" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.08984375" style="41" customWidth="1"/>
-    <col min="13" max="13" width="17.36328125" style="41" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.90625" style="41" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.1796875" style="41" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.90625" style="41"/>
+    <col min="1" max="1" customWidth="true" style="41" width="28.36328125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="41" width="15.0"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="41" width="16.81640625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="41" width="11.08984375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="41" width="15.0"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
+    <col min="12" max="12" customWidth="true" style="41" width="13.08984375"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="41" width="17.36328125"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="41" width="11.90625"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="41" width="14.1796875"/>
+    <col min="16" max="16384" style="41" width="8.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -9644,11 +9693,11 @@
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="24" style="41" customWidth="1"/>
-    <col min="2" max="2" width="11.453125" style="41" customWidth="1"/>
-    <col min="3" max="3" width="8.90625" style="41"/>
-    <col min="4" max="4" width="19.6328125" style="41" customWidth="1"/>
-    <col min="5" max="16384" width="8.90625" style="41"/>
+    <col min="1" max="1" customWidth="true" style="41" width="24.0"/>
+    <col min="2" max="2" customWidth="true" style="41" width="11.453125"/>
+    <col min="3" max="3" style="41" width="8.90625"/>
+    <col min="4" max="4" customWidth="true" style="41" width="19.6328125"/>
+    <col min="5" max="16384" style="41" width="8.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9692,12 +9741,12 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="32.1796875" style="41" customWidth="1"/>
-    <col min="2" max="2" width="14" style="41" customWidth="1"/>
-    <col min="3" max="3" width="16.6328125" style="41" customWidth="1"/>
-    <col min="4" max="4" width="17.6328125" style="41" customWidth="1"/>
-    <col min="5" max="5" width="11.81640625" style="41" customWidth="1"/>
-    <col min="6" max="16384" width="8.90625" style="41"/>
+    <col min="1" max="1" customWidth="true" style="41" width="32.1796875"/>
+    <col min="2" max="2" customWidth="true" style="41" width="14.0"/>
+    <col min="3" max="3" customWidth="true" style="41" width="16.6328125"/>
+    <col min="4" max="4" customWidth="true" style="41" width="17.6328125"/>
+    <col min="5" max="5" customWidth="true" style="41" width="11.81640625"/>
+    <col min="6" max="16384" style="41" width="8.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -9781,11 +9830,11 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="38.1796875" style="41" customWidth="1"/>
-    <col min="2" max="2" width="13.54296875" style="41" customWidth="1"/>
-    <col min="3" max="3" width="15.54296875" style="41" customWidth="1"/>
-    <col min="4" max="4" width="19" style="41" customWidth="1"/>
-    <col min="5" max="16384" width="8.90625" style="41"/>
+    <col min="1" max="1" customWidth="true" style="41" width="38.1796875"/>
+    <col min="2" max="2" customWidth="true" style="41" width="13.54296875"/>
+    <col min="3" max="3" customWidth="true" style="41" width="15.54296875"/>
+    <col min="4" max="4" customWidth="true" style="41" width="19.0"/>
+    <col min="5" max="16384" style="41" width="8.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -9908,21 +9957,21 @@
   <dimension ref="A1:N5"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="30.90625" style="41" customWidth="1"/>
-    <col min="2" max="2" width="17.81640625" style="41" customWidth="1"/>
-    <col min="3" max="3" width="16.453125" style="41" customWidth="1"/>
-    <col min="4" max="4" width="16.08984375" style="41" customWidth="1"/>
-    <col min="5" max="5" width="12" style="41" customWidth="1"/>
-    <col min="6" max="6" width="18.08984375" style="41" customWidth="1"/>
-    <col min="7" max="7" width="15.08984375" style="41" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" style="41" customWidth="1"/>
-    <col min="9" max="9" width="10.81640625" style="41" customWidth="1"/>
-    <col min="10" max="10" width="8.90625" style="41"/>
-    <col min="11" max="11" width="13.1796875" style="41" customWidth="1"/>
-    <col min="12" max="12" width="12.6328125" style="41" customWidth="1"/>
-    <col min="13" max="13" width="14.08984375" style="41" customWidth="1"/>
-    <col min="14" max="14" width="14.36328125" style="41" customWidth="1"/>
-    <col min="15" max="16384" width="8.90625" style="41"/>
+    <col min="1" max="1" customWidth="true" style="41" width="30.90625"/>
+    <col min="2" max="2" customWidth="true" style="41" width="17.81640625"/>
+    <col min="3" max="3" customWidth="true" style="41" width="16.453125"/>
+    <col min="4" max="4" customWidth="true" style="41" width="16.08984375"/>
+    <col min="5" max="5" customWidth="true" style="41" width="12.0"/>
+    <col min="6" max="6" customWidth="true" style="41" width="18.08984375"/>
+    <col min="7" max="7" customWidth="true" style="41" width="15.08984375"/>
+    <col min="8" max="8" customWidth="true" style="41" width="10.453125"/>
+    <col min="9" max="9" customWidth="true" style="41" width="10.81640625"/>
+    <col min="10" max="10" style="41" width="8.90625"/>
+    <col min="11" max="11" customWidth="true" style="41" width="13.1796875"/>
+    <col min="12" max="12" customWidth="true" style="41" width="12.6328125"/>
+    <col min="13" max="13" customWidth="true" style="41" width="14.08984375"/>
+    <col min="14" max="14" customWidth="true" style="41" width="14.36328125"/>
+    <col min="15" max="16384" style="41" width="8.90625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -10124,11 +10173,11 @@
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="39.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="39.453125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="13.54296875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="7.81640625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="5.453125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="9.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -10196,10 +10245,10 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="57.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="57.453125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="15.54296875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="7.81640625"/>
+    <col min="4" max="5" bestFit="true" customWidth="true" width="11.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -10318,28 +10367,28 @@
   <dimension ref="A1:V15"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="50" style="25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.36328125" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.08984375" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.36328125" style="25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.1796875" style="25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.453125" style="25" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="8.81640625" style="25"/>
-    <col min="9" max="9" width="10.453125" style="25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.6328125" style="25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.453125" style="25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.1796875" style="25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.453125" style="25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.1796875" style="25" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13" style="25" customWidth="1"/>
-    <col min="16" max="16" width="10.1796875" style="25" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.453125" style="25" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.1796875" style="25" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.6328125" style="25" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.6328125" style="25" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.1796875" style="25" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.6328125" style="25" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="8.81640625" style="25"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="25" width="50.0"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="25" width="18.36328125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="25" width="12.08984375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="25" width="15.36328125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="25" width="12.1796875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="25" width="9.453125"/>
+    <col min="7" max="8" style="25" width="8.81640625"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="25" width="10.453125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="25" width="12.6328125"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="25" width="10.453125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="25" width="11.1796875"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="25" width="10.453125"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="25" width="8.1796875"/>
+    <col min="15" max="15" customWidth="true" style="25" width="13.0"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="25" width="10.1796875"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="25" width="10.453125"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="25" width="9.1796875"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="25" width="11.6328125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="25" width="12.6328125"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="25" width="11.1796875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="25" width="12.6328125"/>
+    <col min="23" max="16384" style="25" width="8.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
@@ -11034,29 +11083,29 @@
   <dimension ref="A1:AB7"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="44.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="44.81640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.81640625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="8.1796875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="10.453125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="13.54296875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="17.81640625"/>
+    <col min="11" max="12" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="18.1796875"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="7.81640625"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="8.1796875"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="11.1796875"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="14.1796875"/>
+    <col min="27" max="28" bestFit="true" customWidth="true" width="12.81640625"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="14.1796875"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="12.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28">
@@ -11488,9 +11537,9 @@
   <dimension ref="A1:W17"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="54.36328125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="54.36328125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="13.90625"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="13.81640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -12241,16 +12290,16 @@
   <dimension ref="A1:S20"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="53.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="12.1796875" customWidth="1"/>
-    <col min="8" max="8" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="53.81640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="3" max="4" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="5" max="7" customWidth="true" width="12.1796875"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="15.453125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="12.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19">

--- a/src/test/java/TestData/Scenario_TestData.xlsx
+++ b/src/test/java/TestData/Scenario_TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Copa_SHD_WebServices\src\test\java\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BF7513F-D4E8-44F3-A783-34C83AC232C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC38559A-FC4C-498F-958D-81BED35A6CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="8" activeTab="10" xr2:uid="{5D5A4724-D560-4FC2-9708-4BBF1DBA0B11}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="25" activeTab="28" xr2:uid="{5D5A4724-D560-4FC2-9708-4BBF1DBA0B11}"/>
   </bookViews>
   <sheets>
     <sheet name="AdvancePassengerInfo" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2124" uniqueCount="642">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2105" uniqueCount="635">
   <si>
     <t>Scenario</t>
   </si>
@@ -1507,9 +1507,6 @@
     <t>GB</t>
   </si>
   <si>
-    <t>NIL</t>
-  </si>
-  <si>
     <t>BA</t>
   </si>
   <si>
@@ -1588,9 +1585,6 @@
     <t>BKK</t>
   </si>
   <si>
-    <t>VS</t>
-  </si>
-  <si>
     <t>AG</t>
   </si>
   <si>
@@ -1897,45 +1891,12 @@
     <t>2302182816322</t>
   </si>
   <si>
-    <t>A340FE</t>
-  </si>
-  <si>
     <t>2023-08-26T07:56:00</t>
   </si>
   <si>
     <t>2023-08-26T12:05:00</t>
   </si>
   <si>
-    <t>2302182816168</t>
-  </si>
-  <si>
-    <t>A4FFSD</t>
-  </si>
-  <si>
-    <t>2302182816568</t>
-  </si>
-  <si>
-    <t>2302182816569</t>
-  </si>
-  <si>
-    <t>A340F1</t>
-  </si>
-  <si>
-    <t>2302182816169</t>
-  </si>
-  <si>
-    <t>A340GR</t>
-  </si>
-  <si>
-    <t>2302182816170</t>
-  </si>
-  <si>
-    <t>A340G0</t>
-  </si>
-  <si>
-    <t>2302182816171</t>
-  </si>
-  <si>
     <t>485</t>
   </si>
   <si>
@@ -1960,21 +1921,9 @@
     <t>2302182817362</t>
   </si>
   <si>
-    <t>A4INWJ</t>
-  </si>
-  <si>
-    <t>2302182817363</t>
-  </si>
-  <si>
-    <t>2302182817364</t>
-  </si>
-  <si>
     <t>A4INYY</t>
   </si>
   <si>
-    <t>2302182817365</t>
-  </si>
-  <si>
     <t>A4IN3U</t>
   </si>
   <si>
@@ -1996,10 +1945,40 @@
     <t>2302182817413</t>
   </si>
   <si>
-    <t>2182817427</t>
-  </si>
-  <si>
     <t>2182817428</t>
+  </si>
+  <si>
+    <t>A5Z2AP</t>
+  </si>
+  <si>
+    <t>A5Z2AV</t>
+  </si>
+  <si>
+    <t>2023-08-29T01:14:00</t>
+  </si>
+  <si>
+    <t>2023-08-29T10:38:00</t>
+  </si>
+  <si>
+    <t>2023-08-29T12:02:00</t>
+  </si>
+  <si>
+    <t>2023-08-29T13:43:00</t>
+  </si>
+  <si>
+    <t>A5Z2BO</t>
+  </si>
+  <si>
+    <t>A5Z2BW</t>
+  </si>
+  <si>
+    <t>A5Z2B0</t>
+  </si>
+  <si>
+    <t>A5Z2C3</t>
+  </si>
+  <si>
+    <t>A5Z2D2</t>
   </si>
 </sst>
 </file>
@@ -2236,7 +2215,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2335,7 +2314,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2743,7 +2721,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="44" t="s">
-        <v>513</v>
+        <v>631</v>
       </c>
       <c r="I2" s="32" t="s">
         <v>211</v>
@@ -2760,7 +2738,7 @@
       <c r="M2" s="32"/>
       <c r="N2" s="32"/>
       <c r="O2" s="32" t="s">
-        <v>514</v>
+        <v>632</v>
       </c>
       <c r="P2" s="38"/>
     </row>
@@ -2832,7 +2810,7 @@
         <v>1</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>515</v>
+        <v>633</v>
       </c>
       <c r="I4" s="37" t="s">
         <v>351</v>
@@ -2869,7 +2847,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="37" t="s">
-        <v>516</v>
+        <v>634</v>
       </c>
       <c r="I5" s="32"/>
       <c r="J5" s="32"/>
@@ -3009,7 +2987,7 @@
       </c>
       <c r="J2" s="44"/>
       <c r="K2" s="44" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="L2" s="44"/>
       <c r="M2" s="44"/>
@@ -3046,10 +3024,10 @@
         <v>0</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="L3" s="44" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="M3" s="44"/>
       <c r="N3" s="44"/>
@@ -3118,10 +3096,10 @@
       <c r="I5" s="44"/>
       <c r="J5" s="44"/>
       <c r="K5" s="44" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="M5" s="44"/>
       <c r="N5" s="44" t="s">
@@ -3165,7 +3143,7 @@
       <c r="I6" s="44"/>
       <c r="J6" s="44"/>
       <c r="K6" s="44" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="L6" s="44"/>
       <c r="M6" s="44"/>
@@ -3176,7 +3154,7 @@
         <v>242</v>
       </c>
       <c r="P6" s="44" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Q6" s="44"/>
       <c r="R6" s="44"/>
@@ -3210,10 +3188,10 @@
       <c r="I7" s="44"/>
       <c r="J7" s="44"/>
       <c r="K7" s="44" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="L7" s="44" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="M7" s="44"/>
       <c r="N7" s="44" t="s">
@@ -3223,13 +3201,13 @@
         <v>242</v>
       </c>
       <c r="P7" s="44" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="Q7" s="47" t="s">
         <v>87</v>
       </c>
       <c r="R7" s="44" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="S7" s="44"/>
       <c r="T7" s="44"/>
@@ -3265,10 +3243,10 @@
       </c>
       <c r="J8" s="44"/>
       <c r="K8" s="44" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="L8" s="44" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="M8" s="44"/>
       <c r="N8" s="44" t="s">
@@ -3306,7 +3284,7 @@
       <c r="I9" s="44"/>
       <c r="J9" s="44"/>
       <c r="K9" s="44" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="L9" s="44"/>
       <c r="M9" s="44"/>
@@ -3345,10 +3323,10 @@
       <c r="I10" s="44"/>
       <c r="J10" s="44"/>
       <c r="K10" s="44" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="L10" s="44" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="M10" s="44"/>
       <c r="N10" s="44"/>
@@ -3357,7 +3335,7 @@
       <c r="Q10" s="44"/>
       <c r="R10" s="44"/>
       <c r="S10" s="47" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="T10" s="44"/>
       <c r="U10" s="44"/>
@@ -3384,10 +3362,10 @@
       <c r="I11" s="44"/>
       <c r="J11" s="44"/>
       <c r="K11" s="44" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="L11" s="44" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="M11" s="44"/>
       <c r="N11" s="44"/>
@@ -3423,10 +3401,10 @@
       <c r="I12" s="44"/>
       <c r="J12" s="44"/>
       <c r="K12" s="44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="L12" s="44" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="M12" s="44"/>
       <c r="N12" s="44" t="s">
@@ -3544,10 +3522,10 @@
       <c r="I15" s="44"/>
       <c r="J15" s="44"/>
       <c r="K15" s="44" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="L15" s="44" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="M15" s="44"/>
       <c r="N15" s="44" t="s">
@@ -3573,7 +3551,7 @@
         <v>0</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="D16" s="44" t="s">
         <v>12</v>
@@ -3587,7 +3565,7 @@
       <c r="I16" s="44"/>
       <c r="J16" s="44"/>
       <c r="K16" s="44" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="L16" s="44"/>
       <c r="M16" s="44"/>
@@ -3626,7 +3604,7 @@
       <c r="I17" s="44"/>
       <c r="J17" s="44"/>
       <c r="K17" s="44" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="L17" s="44"/>
       <c r="M17" s="44"/>
@@ -3833,7 +3811,7 @@
       </c>
       <c r="J22" s="44"/>
       <c r="K22" s="44" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="L22" s="44"/>
       <c r="M22" s="44"/>
@@ -3927,14 +3905,14 @@
         <v>2</v>
       </c>
       <c r="D2" s="47" t="s">
-        <v>623</v>
+        <v>610</v>
       </c>
       <c r="E2" s="47" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="F2" s="44"/>
       <c r="G2" s="47" t="s">
-        <v>620</v>
+        <v>607</v>
       </c>
       <c r="H2" s="44" t="s">
         <v>12</v>
@@ -3958,7 +3936,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="47" t="s">
-        <v>624</v>
+        <v>611</v>
       </c>
       <c r="E3" s="47" t="s">
         <v>264</v>
@@ -3967,7 +3945,7 @@
         <v>149</v>
       </c>
       <c r="G3" s="47" t="s">
-        <v>620</v>
+        <v>607</v>
       </c>
       <c r="H3" s="44" t="s">
         <v>12</v>
@@ -3993,7 +3971,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="47" t="s">
-        <v>625</v>
+        <v>612</v>
       </c>
       <c r="E4" s="44"/>
       <c r="F4" s="44" t="s">
@@ -4009,7 +3987,7 @@
         <v>13</v>
       </c>
       <c r="J4" s="47" t="s">
-        <v>621</v>
+        <v>608</v>
       </c>
       <c r="K4" s="44" t="s">
         <v>13</v>
@@ -4094,7 +4072,7 @@
       <c r="G2" s="44"/>
       <c r="H2" s="44"/>
       <c r="I2" s="44" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="J2" s="44"/>
       <c r="K2" s="44"/>
@@ -4113,7 +4091,7 @@
       <c r="G3" s="44"/>
       <c r="H3" s="44"/>
       <c r="I3" s="44" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="J3" s="44"/>
       <c r="K3" s="44"/>
@@ -4132,7 +4110,7 @@
       <c r="G4" s="44"/>
       <c r="H4" s="44"/>
       <c r="I4" s="44" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="J4" s="44"/>
       <c r="K4" s="44"/>
@@ -4163,13 +4141,13 @@
         <v>12</v>
       </c>
       <c r="I5" s="44" t="s">
+        <v>535</v>
+      </c>
+      <c r="J5" s="44" t="s">
+        <v>536</v>
+      </c>
+      <c r="K5" s="44" t="s">
         <v>537</v>
-      </c>
-      <c r="J5" s="44" t="s">
-        <v>538</v>
-      </c>
-      <c r="K5" s="44" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -4198,10 +4176,10 @@
         <v>12</v>
       </c>
       <c r="I6" s="44" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="J6" s="44" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="K6" s="44"/>
     </row>
@@ -4481,16 +4459,16 @@
         <v>45</v>
       </c>
       <c r="J2" s="44" t="s">
-        <v>572</v>
+        <v>625</v>
       </c>
       <c r="K2" s="44" t="s">
-        <v>509</v>
+        <v>626</v>
       </c>
       <c r="L2" s="44" t="s">
         <v>207</v>
       </c>
       <c r="M2" s="44" t="s">
-        <v>510</v>
+        <v>627</v>
       </c>
       <c r="N2" s="44" t="s">
         <v>208</v>
@@ -4499,13 +4477,13 @@
         <v>12</v>
       </c>
       <c r="P2" s="44" t="s">
-        <v>511</v>
+        <v>628</v>
       </c>
       <c r="Q2" s="44" t="s">
         <v>62</v>
       </c>
       <c r="R2" s="44" t="s">
-        <v>512</v>
+        <v>629</v>
       </c>
       <c r="S2" s="44" t="s">
         <v>12</v>
@@ -4551,16 +4529,16 @@
         <v>45</v>
       </c>
       <c r="J3" s="44" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="L3" s="44" t="s">
         <v>207</v>
       </c>
       <c r="M3" s="44" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="N3" s="44" t="s">
         <v>208</v>
@@ -4569,13 +4547,13 @@
         <v>12</v>
       </c>
       <c r="P3" s="44" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="Q3" s="44" t="s">
         <v>239</v>
       </c>
       <c r="R3" s="44" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="S3" s="44" t="s">
         <v>12</v>
@@ -4629,16 +4607,16 @@
       <c r="H4" s="44"/>
       <c r="I4" s="44"/>
       <c r="J4" s="44" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="K4" s="44" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="L4" s="44" t="s">
         <v>328</v>
       </c>
       <c r="M4" s="44" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="N4" s="44" t="s">
         <v>209</v>
@@ -4681,16 +4659,16 @@
       <c r="H5" s="44"/>
       <c r="I5" s="44"/>
       <c r="J5" s="44" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="L5" s="44" t="s">
         <v>328</v>
       </c>
       <c r="M5" s="44" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="N5" s="44" t="s">
         <v>209</v>
@@ -4741,16 +4719,16 @@
         <v>45</v>
       </c>
       <c r="J6" s="44" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="K6" s="44" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="L6" s="44" t="s">
         <v>207</v>
       </c>
       <c r="M6" s="44" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="N6" s="44" t="s">
         <v>208</v>
@@ -5792,16 +5770,16 @@
       <c r="I2" s="44"/>
       <c r="J2" s="44"/>
       <c r="K2" s="44" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>325</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>209</v>
@@ -5856,7 +5834,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>312</v>
@@ -5996,16 +5974,16 @@
         <v>2</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>325</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>209</v>
@@ -6014,7 +5992,7 @@
         <v>12</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="R5" s="15" t="s">
         <v>44</v>
@@ -6533,16 +6511,16 @@
       <c r="U2" s="44"/>
       <c r="V2" s="44"/>
       <c r="W2" s="44" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="X2" s="44" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="Y2" s="44" t="s">
         <v>325</v>
       </c>
       <c r="Z2" s="44" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="AA2" s="44" t="s">
         <v>209</v>
@@ -6551,7 +6529,7 @@
         <v>12</v>
       </c>
       <c r="AC2" s="44" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -6669,16 +6647,16 @@
       <c r="U4" s="44"/>
       <c r="V4" s="44"/>
       <c r="W4" s="44" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="X4" s="44" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="Y4" s="44" t="s">
         <v>325</v>
       </c>
       <c r="Z4" s="44" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="AA4" s="44" t="s">
         <v>209</v>
@@ -6687,7 +6665,7 @@
         <v>12</v>
       </c>
       <c r="AC4" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
   </sheetData>
@@ -6881,7 +6859,7 @@
       <c r="E1" s="58" t="s">
         <v>73</v>
       </c>
-      <c r="F1" s="65" t="s">
+      <c r="F1" s="64" t="s">
         <v>142</v>
       </c>
       <c r="G1" s="58" t="s">
@@ -6945,16 +6923,16 @@
       <c r="I2" s="44"/>
       <c r="J2" s="44"/>
       <c r="K2" s="44" t="s">
-        <v>626</v>
+        <v>613</v>
       </c>
       <c r="L2" s="44" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="M2" s="44" t="s">
         <v>18</v>
       </c>
       <c r="N2" s="44" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="O2" s="44" t="s">
         <v>12</v>
@@ -6963,7 +6941,7 @@
         <v>13</v>
       </c>
       <c r="Q2" s="44" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="R2" s="44"/>
     </row>
@@ -6991,16 +6969,16 @@
       <c r="I3" s="44"/>
       <c r="J3" s="44"/>
       <c r="K3" s="44" t="s">
-        <v>637</v>
+        <v>620</v>
       </c>
       <c r="L3" s="44" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="M3" s="44" t="s">
         <v>18</v>
       </c>
       <c r="N3" s="44" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="O3" s="44" t="s">
         <v>12</v>
@@ -7009,10 +6987,10 @@
         <v>13</v>
       </c>
       <c r="Q3" s="44" t="s">
-        <v>638</v>
+        <v>621</v>
       </c>
       <c r="R3" s="44" t="s">
-        <v>639</v>
+        <v>622</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -7047,16 +7025,16 @@
         <v>2</v>
       </c>
       <c r="K4" s="44" t="s">
-        <v>631</v>
+        <v>615</v>
       </c>
       <c r="L4" s="44" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="M4" s="44" t="s">
         <v>18</v>
       </c>
       <c r="N4" s="44" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="O4" s="44" t="s">
         <v>12</v>
@@ -7065,7 +7043,7 @@
         <v>13</v>
       </c>
       <c r="Q4" s="44" t="s">
-        <v>641</v>
+        <v>623</v>
       </c>
       <c r="R4" s="44"/>
     </row>
@@ -7093,16 +7071,16 @@
       <c r="I5" s="44"/>
       <c r="J5" s="44"/>
       <c r="K5" s="44" t="s">
-        <v>633</v>
+        <v>616</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="M5" s="44" t="s">
         <v>18</v>
       </c>
       <c r="N5" s="44" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="O5" s="44" t="s">
         <v>12</v>
@@ -7111,7 +7089,7 @@
         <v>13</v>
       </c>
       <c r="Q5" s="44" t="s">
-        <v>634</v>
+        <v>617</v>
       </c>
       <c r="R5" s="44"/>
     </row>
@@ -7139,16 +7117,16 @@
       <c r="I6" s="44"/>
       <c r="J6" s="44"/>
       <c r="K6" s="44" t="s">
-        <v>635</v>
+        <v>618</v>
       </c>
       <c r="L6" s="44" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="M6" s="44" t="s">
         <v>18</v>
       </c>
       <c r="N6" s="44" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="O6" s="44" t="s">
         <v>12</v>
@@ -7157,7 +7135,7 @@
         <v>13</v>
       </c>
       <c r="Q6" s="44" t="s">
-        <v>636</v>
+        <v>619</v>
       </c>
       <c r="R6" s="44"/>
     </row>
@@ -7292,16 +7270,16 @@
         <v>163</v>
       </c>
       <c r="J2" s="56" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="K2" s="44" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>215</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>12</v>
@@ -7310,13 +7288,13 @@
         <v>216</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>217</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="S2" s="3" t="s">
         <v>216</v>
@@ -7325,7 +7303,7 @@
         <v>163</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="3" spans="1:21">
@@ -7357,16 +7335,16 @@
         <v>163</v>
       </c>
       <c r="J3" s="56" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>215</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>12</v>
@@ -7375,13 +7353,13 @@
         <v>216</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>341</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="S3" s="3" t="s">
         <v>216</v>
@@ -7390,7 +7368,7 @@
         <v>163</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="4" spans="1:21">
@@ -7586,7 +7564,7 @@
       <c r="A2" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="44" t="s">
         <v>87</v>
       </c>
     </row>
@@ -7594,15 +7572,15 @@
       <c r="A3" s="44" t="s">
         <v>181</v>
       </c>
-      <c r="B3" s="64" t="s">
-        <v>506</v>
+      <c r="B3" s="47" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="B4" s="41" t="s">
+      <c r="B4" s="44" t="s">
         <v>182</v>
       </c>
     </row>
@@ -7726,7 +7704,7 @@
         <v>473</v>
       </c>
       <c r="J1" s="63" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="K1" s="42" t="s">
         <v>470</v>
@@ -7735,10 +7713,10 @@
         <v>471</v>
       </c>
       <c r="M1" s="42" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="N1" s="42" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -7767,22 +7745,22 @@
         <v>474</v>
       </c>
       <c r="I2" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="J2" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="K2" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L2" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="M2" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="N2" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -7799,7 +7777,7 @@
         <v>121</v>
       </c>
       <c r="E3" s="32" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="F3" s="44" t="s">
         <v>475</v>
@@ -7811,22 +7789,22 @@
         <v>474</v>
       </c>
       <c r="I3" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="J3" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L3" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="M3" s="44" t="s">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="N3" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -7855,22 +7833,22 @@
         <v>474</v>
       </c>
       <c r="I4" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="J4" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="K4" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L4" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="M4" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="N4" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -7887,34 +7865,34 @@
         <v>121</v>
       </c>
       <c r="E5" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="F5" s="44" t="s">
         <v>466</v>
-      </c>
-      <c r="F5" s="44" t="s">
-        <v>477</v>
       </c>
       <c r="G5" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H5" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I5" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="J5" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="M5" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="N5" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -7931,34 +7909,34 @@
         <v>121</v>
       </c>
       <c r="E6" s="44" t="s">
+        <v>121</v>
+      </c>
+      <c r="F6" s="44" t="s">
         <v>466</v>
-      </c>
-      <c r="F6" s="44" t="s">
-        <v>477</v>
       </c>
       <c r="G6" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H6" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I6" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="J6" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="K6" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L6" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="M6" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="N6" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -7975,34 +7953,34 @@
         <v>121</v>
       </c>
       <c r="E7" s="44" t="s">
+        <v>121</v>
+      </c>
+      <c r="F7" s="44" t="s">
         <v>466</v>
-      </c>
-      <c r="F7" s="44" t="s">
-        <v>477</v>
       </c>
       <c r="G7" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H7" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I7" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="J7" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="K7" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L7" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="M7" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="N7" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -8013,40 +7991,40 @@
         <v>149</v>
       </c>
       <c r="C8" s="44" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D8" s="44" t="s">
         <v>121</v>
       </c>
       <c r="E8" s="44" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F8" s="44" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="G8" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H8" s="44" t="s">
+        <v>484</v>
+      </c>
+      <c r="I8" s="44" t="s">
         <v>485</v>
       </c>
-      <c r="I8" s="44" t="s">
-        <v>486</v>
-      </c>
       <c r="J8" s="44" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="K8" s="44" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="L8" s="44" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="M8" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="N8" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -8063,7 +8041,7 @@
         <v>121</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F9" s="44" t="s">
         <v>476</v>
@@ -8072,25 +8050,25 @@
         <v>338</v>
       </c>
       <c r="H9" s="44" t="s">
+        <v>490</v>
+      </c>
+      <c r="I9" s="44" t="s">
         <v>491</v>
       </c>
-      <c r="I9" s="44" t="s">
+      <c r="J9" s="44" t="s">
         <v>492</v>
       </c>
-      <c r="J9" s="44" t="s">
-        <v>493</v>
-      </c>
       <c r="K9" s="44" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="L9" s="44" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="M9" s="44" t="s">
         <v>428</v>
       </c>
       <c r="N9" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -8107,34 +8085,34 @@
         <v>121</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F10" s="44" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="G10" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H10" s="44" t="s">
+        <v>497</v>
+      </c>
+      <c r="I10" s="44" t="s">
         <v>498</v>
       </c>
-      <c r="I10" s="44" t="s">
+      <c r="J10" s="44" t="s">
         <v>499</v>
       </c>
-      <c r="J10" s="44" t="s">
-        <v>500</v>
-      </c>
       <c r="K10" s="44" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="L10" s="44" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="M10" s="44" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="N10" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -8145,40 +8123,40 @@
         <v>149</v>
       </c>
       <c r="C11" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D11" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F11" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="G11" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H11" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I11" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="J11" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="K11" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L11" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="M11" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="N11" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -8189,40 +8167,40 @@
         <v>149</v>
       </c>
       <c r="C12" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D12" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F12" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="G12" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H12" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I12" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="J12" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="K12" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L12" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="M12" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="N12" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -8233,40 +8211,40 @@
         <v>149</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F13" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="G13" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H13" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I13" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="J13" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="K13" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L13" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="M13" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="N13" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -8277,37 +8255,37 @@
         <v>149</v>
       </c>
       <c r="C14" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F14" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="G14" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H14" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I14" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="J14" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="K14" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L14" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="M14" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="N14" s="44" t="s">
         <v>465</v>
@@ -8321,84 +8299,84 @@
         <v>149</v>
       </c>
       <c r="C15" s="44" t="s">
+        <v>501</v>
+      </c>
+      <c r="D15" s="44" t="s">
+        <v>487</v>
+      </c>
+      <c r="E15" s="44" t="s">
+        <v>487</v>
+      </c>
+      <c r="F15" s="44" t="s">
+        <v>487</v>
+      </c>
+      <c r="G15" s="44" t="s">
         <v>502</v>
       </c>
-      <c r="D15" s="44" t="s">
-        <v>488</v>
-      </c>
-      <c r="E15" s="44" t="s">
-        <v>488</v>
-      </c>
-      <c r="F15" s="44" t="s">
-        <v>488</v>
-      </c>
-      <c r="G15" s="44" t="s">
-        <v>503</v>
-      </c>
       <c r="H15" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I15" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="J15" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="K15" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L15" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="M15" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="N15" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="32" t="s">
         <v>303</v>
       </c>
-      <c r="B16" s="32" t="s">
-        <v>504</v>
+      <c r="B16" s="44" t="s">
+        <v>149</v>
       </c>
       <c r="C16" s="32" t="s">
         <v>465</v>
       </c>
       <c r="D16" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F16" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="G16" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H16" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I16" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="J16" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="K16" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L16" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="M16" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="N16" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -8409,40 +8387,40 @@
         <v>149</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D17" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F17" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="G17" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H17" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I17" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="J17" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="K17" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L17" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="M17" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="N17" s="44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -8526,10 +8504,10 @@
         <v>50</v>
       </c>
       <c r="H2" s="44" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="I2" s="44" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -8759,7 +8737,7 @@
       <c r="H6" s="44"/>
       <c r="I6" s="44"/>
       <c r="J6" s="44" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="K6" s="44"/>
       <c r="L6" s="44"/>
@@ -8842,7 +8820,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="G2" s="32">
         <v>2</v>
@@ -8873,7 +8851,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="G3" s="32"/>
       <c r="H3" s="32"/>
@@ -8902,7 +8880,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="G4" s="32"/>
       <c r="H4" s="32"/>
@@ -9508,7 +9486,7 @@
       </c>
       <c r="G4" s="44"/>
       <c r="H4" s="44" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="I4" s="44" t="s">
         <v>387</v>
@@ -9545,7 +9523,7 @@
       </c>
       <c r="G5" s="44"/>
       <c r="H5" s="44" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="I5" s="44" t="s">
         <v>387</v>
@@ -10047,7 +10025,7 @@
         <v>212</v>
       </c>
       <c r="J2" s="44" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="K2" s="44">
         <v>2</v>
@@ -10499,7 +10477,7 @@
       <c r="M2" s="32"/>
       <c r="N2" s="32"/>
       <c r="O2" s="32" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="P2" s="32"/>
       <c r="Q2" s="32" t="s">
@@ -10644,7 +10622,7 @@
         <v>15</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="I6" s="32" t="s">
         <v>387</v>
@@ -10692,7 +10670,7 @@
         <v>19</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="I7" s="32" t="s">
         <v>360</v>
@@ -10810,7 +10788,7 @@
       </c>
       <c r="G10" s="56"/>
       <c r="H10" s="32" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="I10" s="32"/>
       <c r="J10" s="32" t="s">
@@ -10858,7 +10836,7 @@
         <v>15</v>
       </c>
       <c r="H11" s="32" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="I11" s="32" t="s">
         <v>211</v>
@@ -10910,7 +10888,7 @@
       </c>
       <c r="G12" s="56"/>
       <c r="H12" s="32" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="I12" s="32" t="s">
         <v>376</v>
@@ -10998,7 +10976,7 @@
       </c>
       <c r="G14" s="56"/>
       <c r="H14" s="32" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="I14" s="32" t="s">
         <v>244</v>
@@ -11048,7 +11026,7 @@
         <v>15</v>
       </c>
       <c r="H15" s="32" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="I15" s="32" t="s">
         <v>367</v>
@@ -11642,10 +11620,10 @@
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
       <c r="R2" s="3" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
@@ -11904,10 +11882,10 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="T8" s="3">
         <v>0</v>
@@ -11953,10 +11931,10 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="T9" s="3"/>
       <c r="U9" s="3">
@@ -12006,10 +11984,10 @@
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
@@ -12232,10 +12210,10 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>

--- a/src/test/java/TestData/Scenario_TestData.xlsx
+++ b/src/test/java/TestData/Scenario_TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Copa_SHD_WebServices\src\test\java\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC38559A-FC4C-498F-958D-81BED35A6CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFFA3B47-6EFD-4C32-9A50-C641008FC3AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="25" activeTab="28" xr2:uid="{5D5A4724-D560-4FC2-9708-4BBF1DBA0B11}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="8" activeTab="9" xr2:uid="{5D5A4724-D560-4FC2-9708-4BBF1DBA0B11}"/>
   </bookViews>
   <sheets>
     <sheet name="AdvancePassengerInfo" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2105" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="630">
   <si>
     <t>Scenario</t>
   </si>
@@ -1603,24 +1603,6 @@
     <t>2023-08-23T10:38:00</t>
   </si>
   <si>
-    <t>2023-08-23T12:02:00</t>
-  </si>
-  <si>
-    <t>2023-08-23T13:43:00</t>
-  </si>
-  <si>
-    <t>A2MQNQ</t>
-  </si>
-  <si>
-    <t>A2MQNR</t>
-  </si>
-  <si>
-    <t>A2MQNT</t>
-  </si>
-  <si>
-    <t>A2MQNV</t>
-  </si>
-  <si>
     <t>A2MQN5</t>
   </si>
   <si>
@@ -1786,9 +1768,6 @@
     <t>2302182807142</t>
   </si>
   <si>
-    <t>A2MRDT</t>
-  </si>
-  <si>
     <t>A2MRDV</t>
   </si>
   <si>
@@ -1873,15 +1852,6 @@
     <t>2302182816196</t>
   </si>
   <si>
-    <t>A351ZL</t>
-  </si>
-  <si>
-    <t>A4ADZB</t>
-  </si>
-  <si>
-    <t>2302182816201</t>
-  </si>
-  <si>
     <t>6759649826438453</t>
   </si>
   <si>
@@ -1948,9 +1918,6 @@
     <t>2182817428</t>
   </si>
   <si>
-    <t>A5Z2AP</t>
-  </si>
-  <si>
     <t>A5Z2AV</t>
   </si>
   <si>
@@ -1966,9 +1933,6 @@
     <t>2023-08-29T13:43:00</t>
   </si>
   <si>
-    <t>A5Z2BO</t>
-  </si>
-  <si>
     <t>A5Z2BW</t>
   </si>
   <si>
@@ -1979,6 +1943,27 @@
   </si>
   <si>
     <t>A5Z2D2</t>
+  </si>
+  <si>
+    <t>BAIUSI</t>
+  </si>
+  <si>
+    <t>2023-08-29T08:23:00</t>
+  </si>
+  <si>
+    <t>BAIVLG</t>
+  </si>
+  <si>
+    <t>2302182822862</t>
+  </si>
+  <si>
+    <t>BAIWFG</t>
+  </si>
+  <si>
+    <t>2302182822876</t>
+  </si>
+  <si>
+    <t>2302182822912</t>
   </si>
 </sst>
 </file>
@@ -2721,7 +2706,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="44" t="s">
-        <v>631</v>
+        <v>619</v>
       </c>
       <c r="I2" s="32" t="s">
         <v>211</v>
@@ -2738,7 +2723,7 @@
       <c r="M2" s="32"/>
       <c r="N2" s="32"/>
       <c r="O2" s="32" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="P2" s="38"/>
     </row>
@@ -2810,7 +2795,7 @@
         <v>1</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>633</v>
+        <v>621</v>
       </c>
       <c r="I4" s="37" t="s">
         <v>351</v>
@@ -2847,7 +2832,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="37" t="s">
-        <v>634</v>
+        <v>622</v>
       </c>
       <c r="I5" s="32"/>
       <c r="J5" s="32"/>
@@ -2880,19 +2865,21 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:U22"/>
+  <dimension ref="A1:V22"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="49.0"/>
     <col min="10" max="10" style="25" width="8.81640625"/>
-    <col min="12" max="12" customWidth="true" width="15.90625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="13.90625"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="11.453125"/>
     <col min="17" max="17" bestFit="true" customWidth="true" width="9.81640625"/>
     <col min="18" max="18" bestFit="true" customWidth="true" width="13.90625"/>
     <col min="19" max="19" bestFit="true" customWidth="true" width="17.0"/>
     <col min="21" max="21" bestFit="true" customWidth="true" width="12.6328125"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="14.36328125"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:22">
       <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
@@ -2956,8 +2943,11 @@
       <c r="U1" s="43" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="2" spans="1:21">
+      <c r="V1" s="43" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22">
       <c r="A2" s="28" t="s">
         <v>218</v>
       </c>
@@ -2987,7 +2977,7 @@
       </c>
       <c r="J2" s="44"/>
       <c r="K2" s="44" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="L2" s="44"/>
       <c r="M2" s="44"/>
@@ -2999,8 +2989,9 @@
       <c r="S2" s="44"/>
       <c r="T2" s="44"/>
       <c r="U2" s="44"/>
-    </row>
-    <row r="3" spans="1:21">
+      <c r="V2" s="44"/>
+    </row>
+    <row r="3" spans="1:22">
       <c r="A3" s="28" t="s">
         <v>219</v>
       </c>
@@ -3024,10 +3015,10 @@
         <v>0</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="L3" s="44" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="M3" s="44"/>
       <c r="N3" s="44"/>
@@ -3038,8 +3029,9 @@
       <c r="S3" s="44"/>
       <c r="T3" s="44"/>
       <c r="U3" s="44"/>
-    </row>
-    <row r="4" spans="1:21">
+      <c r="V3" s="44"/>
+    </row>
+    <row r="4" spans="1:22">
       <c r="A4" s="28" t="s">
         <v>220</v>
       </c>
@@ -3073,8 +3065,9 @@
       <c r="S4" s="44"/>
       <c r="T4" s="44"/>
       <c r="U4" s="44"/>
-    </row>
-    <row r="5" spans="1:21">
+      <c r="V4" s="44"/>
+    </row>
+    <row r="5" spans="1:22">
       <c r="A5" s="28" t="s">
         <v>221</v>
       </c>
@@ -3096,10 +3089,10 @@
       <c r="I5" s="44"/>
       <c r="J5" s="44"/>
       <c r="K5" s="44" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="M5" s="44"/>
       <c r="N5" s="44" t="s">
@@ -3120,8 +3113,9 @@
       <c r="U5" s="44" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="6" spans="1:21">
+      <c r="V5" s="44"/>
+    </row>
+    <row r="6" spans="1:22">
       <c r="A6" s="28" t="s">
         <v>222</v>
       </c>
@@ -3143,7 +3137,7 @@
       <c r="I6" s="44"/>
       <c r="J6" s="44"/>
       <c r="K6" s="44" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="L6" s="44"/>
       <c r="M6" s="44"/>
@@ -3154,7 +3148,7 @@
         <v>242</v>
       </c>
       <c r="P6" s="44" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="Q6" s="44"/>
       <c r="R6" s="44"/>
@@ -3165,8 +3159,9 @@
       <c r="U6" s="44" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="7" spans="1:21">
+      <c r="V6" s="44"/>
+    </row>
+    <row r="7" spans="1:22">
       <c r="A7" s="28" t="s">
         <v>223</v>
       </c>
@@ -3188,10 +3183,10 @@
       <c r="I7" s="44"/>
       <c r="J7" s="44"/>
       <c r="K7" s="44" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="L7" s="44" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="M7" s="44"/>
       <c r="N7" s="44" t="s">
@@ -3201,19 +3196,20 @@
         <v>242</v>
       </c>
       <c r="P7" s="44" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="Q7" s="47" t="s">
         <v>87</v>
       </c>
       <c r="R7" s="44" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="S7" s="44"/>
       <c r="T7" s="44"/>
       <c r="U7" s="44"/>
-    </row>
-    <row r="8" spans="1:21">
+      <c r="V7" s="44"/>
+    </row>
+    <row r="8" spans="1:22">
       <c r="A8" s="28" t="s">
         <v>224</v>
       </c>
@@ -3243,10 +3239,10 @@
       </c>
       <c r="J8" s="44"/>
       <c r="K8" s="44" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="L8" s="44" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="M8" s="44"/>
       <c r="N8" s="44" t="s">
@@ -3261,8 +3257,9 @@
       <c r="S8" s="44"/>
       <c r="T8" s="44"/>
       <c r="U8" s="44"/>
-    </row>
-    <row r="9" spans="1:21">
+      <c r="V8" s="44"/>
+    </row>
+    <row r="9" spans="1:22">
       <c r="A9" s="28" t="s">
         <v>225</v>
       </c>
@@ -3284,7 +3281,7 @@
       <c r="I9" s="44"/>
       <c r="J9" s="44"/>
       <c r="K9" s="44" t="s">
-        <v>599</v>
+        <v>623</v>
       </c>
       <c r="L9" s="44"/>
       <c r="M9" s="44"/>
@@ -3300,8 +3297,11 @@
       <c r="S9" s="44"/>
       <c r="T9" s="44"/>
       <c r="U9" s="44"/>
-    </row>
-    <row r="10" spans="1:21">
+      <c r="V9" s="44" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22">
       <c r="A10" s="28" t="s">
         <v>226</v>
       </c>
@@ -3323,10 +3323,10 @@
       <c r="I10" s="44"/>
       <c r="J10" s="44"/>
       <c r="K10" s="44" t="s">
-        <v>603</v>
+        <v>593</v>
       </c>
       <c r="L10" s="44" t="s">
-        <v>604</v>
+        <v>594</v>
       </c>
       <c r="M10" s="44"/>
       <c r="N10" s="44"/>
@@ -3335,12 +3335,13 @@
       <c r="Q10" s="44"/>
       <c r="R10" s="44"/>
       <c r="S10" s="47" t="s">
-        <v>602</v>
+        <v>592</v>
       </c>
       <c r="T10" s="44"/>
       <c r="U10" s="44"/>
-    </row>
-    <row r="11" spans="1:21">
+      <c r="V10" s="44"/>
+    </row>
+    <row r="11" spans="1:22">
       <c r="A11" s="28" t="s">
         <v>227</v>
       </c>
@@ -3362,10 +3363,10 @@
       <c r="I11" s="44"/>
       <c r="J11" s="44"/>
       <c r="K11" s="44" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="L11" s="44" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="M11" s="44"/>
       <c r="N11" s="44"/>
@@ -3378,8 +3379,9 @@
       </c>
       <c r="T11" s="44"/>
       <c r="U11" s="44"/>
-    </row>
-    <row r="12" spans="1:21">
+      <c r="V11" s="44"/>
+    </row>
+    <row r="12" spans="1:22">
       <c r="A12" s="28" t="s">
         <v>228</v>
       </c>
@@ -3401,10 +3403,10 @@
       <c r="I12" s="44"/>
       <c r="J12" s="44"/>
       <c r="K12" s="44" t="s">
-        <v>600</v>
+        <v>625</v>
       </c>
       <c r="L12" s="44" t="s">
-        <v>601</v>
+        <v>626</v>
       </c>
       <c r="M12" s="44"/>
       <c r="N12" s="44" t="s">
@@ -3421,8 +3423,9 @@
       <c r="S12" s="44"/>
       <c r="T12" s="44"/>
       <c r="U12" s="44"/>
-    </row>
-    <row r="13" spans="1:21">
+      <c r="V12" s="44"/>
+    </row>
+    <row r="13" spans="1:22">
       <c r="A13" s="28" t="s">
         <v>229</v>
       </c>
@@ -3444,10 +3447,10 @@
       <c r="I13" s="44"/>
       <c r="J13" s="44"/>
       <c r="K13" s="44" t="s">
-        <v>449</v>
+        <v>627</v>
       </c>
       <c r="L13" s="44" t="s">
-        <v>450</v>
+        <v>629</v>
       </c>
       <c r="M13" s="44"/>
       <c r="N13" s="44" t="s">
@@ -3464,8 +3467,9 @@
       </c>
       <c r="T13" s="44"/>
       <c r="U13" s="44"/>
-    </row>
-    <row r="14" spans="1:21">
+      <c r="V13" s="44"/>
+    </row>
+    <row r="14" spans="1:22">
       <c r="A14" s="28" t="s">
         <v>230</v>
       </c>
@@ -3499,8 +3503,9 @@
       </c>
       <c r="T14" s="44"/>
       <c r="U14" s="44"/>
-    </row>
-    <row r="15" spans="1:21">
+      <c r="V14" s="44"/>
+    </row>
+    <row r="15" spans="1:22">
       <c r="A15" s="28" t="s">
         <v>231</v>
       </c>
@@ -3522,10 +3527,10 @@
       <c r="I15" s="44"/>
       <c r="J15" s="44"/>
       <c r="K15" s="44" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="L15" s="44" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="M15" s="44"/>
       <c r="N15" s="44" t="s">
@@ -3542,8 +3547,9 @@
       </c>
       <c r="T15" s="44"/>
       <c r="U15" s="44"/>
-    </row>
-    <row r="16" spans="1:21">
+      <c r="V15" s="44"/>
+    </row>
+    <row r="16" spans="1:22">
       <c r="A16" s="28" t="s">
         <v>232</v>
       </c>
@@ -3551,7 +3557,7 @@
         <v>0</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="D16" s="44" t="s">
         <v>12</v>
@@ -3565,7 +3571,7 @@
       <c r="I16" s="44"/>
       <c r="J16" s="44"/>
       <c r="K16" s="44" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="L16" s="44"/>
       <c r="M16" s="44"/>
@@ -3581,8 +3587,9 @@
       <c r="S16" s="44"/>
       <c r="T16" s="44"/>
       <c r="U16" s="44"/>
-    </row>
-    <row r="17" spans="1:21">
+      <c r="V16" s="44"/>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17" s="28" t="s">
         <v>233</v>
       </c>
@@ -3604,7 +3611,7 @@
       <c r="I17" s="44"/>
       <c r="J17" s="44"/>
       <c r="K17" s="44" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="L17" s="44"/>
       <c r="M17" s="44"/>
@@ -3616,8 +3623,9 @@
       <c r="S17" s="44"/>
       <c r="T17" s="44"/>
       <c r="U17" s="44"/>
-    </row>
-    <row r="18" spans="1:21">
+      <c r="V17" s="44"/>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" s="28" t="s">
         <v>234</v>
       </c>
@@ -3663,8 +3671,9 @@
       <c r="S18" s="44"/>
       <c r="T18" s="44"/>
       <c r="U18" s="44"/>
-    </row>
-    <row r="19" spans="1:21">
+      <c r="V18" s="44"/>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="28" t="s">
         <v>235</v>
       </c>
@@ -3702,8 +3711,9 @@
       <c r="S19" s="44"/>
       <c r="T19" s="44"/>
       <c r="U19" s="44"/>
-    </row>
-    <row r="20" spans="1:21">
+      <c r="V19" s="44"/>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="28" t="s">
         <v>236</v>
       </c>
@@ -3741,8 +3751,9 @@
       <c r="S20" s="44"/>
       <c r="T20" s="44"/>
       <c r="U20" s="44"/>
-    </row>
-    <row r="21" spans="1:21">
+      <c r="V20" s="44"/>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="28" t="s">
         <v>237</v>
       </c>
@@ -3780,8 +3791,9 @@
       <c r="S21" s="44"/>
       <c r="T21" s="44"/>
       <c r="U21" s="44"/>
-    </row>
-    <row r="22" spans="1:21">
+      <c r="V21" s="44"/>
+    </row>
+    <row r="22" spans="1:22">
       <c r="A22" s="28" t="s">
         <v>238</v>
       </c>
@@ -3811,7 +3823,7 @@
       </c>
       <c r="J22" s="44"/>
       <c r="K22" s="44" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="L22" s="44"/>
       <c r="M22" s="44"/>
@@ -3827,6 +3839,7 @@
       <c r="S22" s="44"/>
       <c r="T22" s="44"/>
       <c r="U22" s="44"/>
+      <c r="V22" s="44"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3905,14 +3918,14 @@
         <v>2</v>
       </c>
       <c r="D2" s="47" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="E2" s="47" t="s">
-        <v>609</v>
+        <v>599</v>
       </c>
       <c r="F2" s="44"/>
       <c r="G2" s="47" t="s">
-        <v>607</v>
+        <v>597</v>
       </c>
       <c r="H2" s="44" t="s">
         <v>12</v>
@@ -3936,7 +3949,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="47" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="E3" s="47" t="s">
         <v>264</v>
@@ -3945,7 +3958,7 @@
         <v>149</v>
       </c>
       <c r="G3" s="47" t="s">
-        <v>607</v>
+        <v>597</v>
       </c>
       <c r="H3" s="44" t="s">
         <v>12</v>
@@ -3971,7 +3984,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="47" t="s">
-        <v>612</v>
+        <v>602</v>
       </c>
       <c r="E4" s="44"/>
       <c r="F4" s="44" t="s">
@@ -3987,7 +4000,7 @@
         <v>13</v>
       </c>
       <c r="J4" s="47" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="K4" s="44" t="s">
         <v>13</v>
@@ -4141,13 +4154,13 @@
         <v>12</v>
       </c>
       <c r="I5" s="44" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="J5" s="44" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -4176,10 +4189,10 @@
         <v>12</v>
       </c>
       <c r="I6" s="44" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="J6" s="44" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="K6" s="44"/>
     </row>
@@ -4459,16 +4472,16 @@
         <v>45</v>
       </c>
       <c r="J2" s="44" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="K2" s="44" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="L2" s="44" t="s">
         <v>207</v>
       </c>
       <c r="M2" s="44" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="N2" s="44" t="s">
         <v>208</v>
@@ -4477,13 +4490,13 @@
         <v>12</v>
       </c>
       <c r="P2" s="44" t="s">
-        <v>628</v>
+        <v>617</v>
       </c>
       <c r="Q2" s="44" t="s">
         <v>62</v>
       </c>
       <c r="R2" s="44" t="s">
-        <v>629</v>
+        <v>618</v>
       </c>
       <c r="S2" s="44" t="s">
         <v>12</v>
@@ -4529,7 +4542,7 @@
         <v>45</v>
       </c>
       <c r="J3" s="44" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="K3" s="44" t="s">
         <v>507</v>
@@ -4547,13 +4560,13 @@
         <v>12</v>
       </c>
       <c r="P3" s="44" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="Q3" s="44" t="s">
         <v>239</v>
       </c>
       <c r="R3" s="44" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="S3" s="44" t="s">
         <v>12</v>
@@ -4607,16 +4620,16 @@
       <c r="H4" s="44"/>
       <c r="I4" s="44"/>
       <c r="J4" s="44" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="K4" s="44" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="L4" s="44" t="s">
         <v>328</v>
       </c>
       <c r="M4" s="44" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="N4" s="44" t="s">
         <v>209</v>
@@ -4659,16 +4672,16 @@
       <c r="H5" s="44"/>
       <c r="I5" s="44"/>
       <c r="J5" s="44" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="L5" s="44" t="s">
         <v>328</v>
       </c>
       <c r="M5" s="44" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="N5" s="44" t="s">
         <v>209</v>
@@ -4719,16 +4732,16 @@
         <v>45</v>
       </c>
       <c r="J6" s="44" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="K6" s="44" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="L6" s="44" t="s">
         <v>207</v>
       </c>
       <c r="M6" s="44" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="N6" s="44" t="s">
         <v>208</v>
@@ -5770,16 +5783,16 @@
       <c r="I2" s="44"/>
       <c r="J2" s="44"/>
       <c r="K2" s="44" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>325</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>209</v>
@@ -5834,7 +5847,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>312</v>
@@ -5974,16 +5987,16 @@
         <v>2</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>325</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>209</v>
@@ -5992,7 +6005,7 @@
         <v>12</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="R5" s="15" t="s">
         <v>44</v>
@@ -6511,16 +6524,16 @@
       <c r="U2" s="44"/>
       <c r="V2" s="44"/>
       <c r="W2" s="44" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="X2" s="44" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="Y2" s="44" t="s">
         <v>325</v>
       </c>
       <c r="Z2" s="44" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="AA2" s="44" t="s">
         <v>209</v>
@@ -6529,7 +6542,7 @@
         <v>12</v>
       </c>
       <c r="AC2" s="44" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -6647,16 +6660,16 @@
       <c r="U4" s="44"/>
       <c r="V4" s="44"/>
       <c r="W4" s="44" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="X4" s="44" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="Y4" s="44" t="s">
         <v>325</v>
       </c>
       <c r="Z4" s="44" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="AA4" s="44" t="s">
         <v>209</v>
@@ -6665,7 +6678,7 @@
         <v>12</v>
       </c>
       <c r="AC4" s="44" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -6923,16 +6936,16 @@
       <c r="I2" s="44"/>
       <c r="J2" s="44"/>
       <c r="K2" s="44" t="s">
-        <v>613</v>
+        <v>603</v>
       </c>
       <c r="L2" s="44" t="s">
-        <v>605</v>
+        <v>595</v>
       </c>
       <c r="M2" s="44" t="s">
         <v>18</v>
       </c>
       <c r="N2" s="44" t="s">
-        <v>606</v>
+        <v>596</v>
       </c>
       <c r="O2" s="44" t="s">
         <v>12</v>
@@ -6941,7 +6954,7 @@
         <v>13</v>
       </c>
       <c r="Q2" s="44" t="s">
-        <v>614</v>
+        <v>604</v>
       </c>
       <c r="R2" s="44"/>
     </row>
@@ -6969,16 +6982,16 @@
       <c r="I3" s="44"/>
       <c r="J3" s="44"/>
       <c r="K3" s="44" t="s">
-        <v>620</v>
+        <v>610</v>
       </c>
       <c r="L3" s="44" t="s">
-        <v>605</v>
+        <v>595</v>
       </c>
       <c r="M3" s="44" t="s">
         <v>18</v>
       </c>
       <c r="N3" s="44" t="s">
-        <v>606</v>
+        <v>596</v>
       </c>
       <c r="O3" s="44" t="s">
         <v>12</v>
@@ -6987,10 +7000,10 @@
         <v>13</v>
       </c>
       <c r="Q3" s="44" t="s">
-        <v>621</v>
+        <v>611</v>
       </c>
       <c r="R3" s="44" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -7025,16 +7038,16 @@
         <v>2</v>
       </c>
       <c r="K4" s="44" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="L4" s="44" t="s">
-        <v>605</v>
+        <v>595</v>
       </c>
       <c r="M4" s="44" t="s">
         <v>18</v>
       </c>
       <c r="N4" s="44" t="s">
-        <v>606</v>
+        <v>596</v>
       </c>
       <c r="O4" s="44" t="s">
         <v>12</v>
@@ -7043,7 +7056,7 @@
         <v>13</v>
       </c>
       <c r="Q4" s="44" t="s">
-        <v>623</v>
+        <v>613</v>
       </c>
       <c r="R4" s="44"/>
     </row>
@@ -7071,16 +7084,16 @@
       <c r="I5" s="44"/>
       <c r="J5" s="44"/>
       <c r="K5" s="44" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>605</v>
+        <v>595</v>
       </c>
       <c r="M5" s="44" t="s">
         <v>18</v>
       </c>
       <c r="N5" s="44" t="s">
-        <v>606</v>
+        <v>596</v>
       </c>
       <c r="O5" s="44" t="s">
         <v>12</v>
@@ -7089,7 +7102,7 @@
         <v>13</v>
       </c>
       <c r="Q5" s="44" t="s">
-        <v>617</v>
+        <v>607</v>
       </c>
       <c r="R5" s="44"/>
     </row>
@@ -7117,16 +7130,16 @@
       <c r="I6" s="44"/>
       <c r="J6" s="44"/>
       <c r="K6" s="44" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
       <c r="L6" s="44" t="s">
-        <v>605</v>
+        <v>595</v>
       </c>
       <c r="M6" s="44" t="s">
         <v>18</v>
       </c>
       <c r="N6" s="44" t="s">
-        <v>606</v>
+        <v>596</v>
       </c>
       <c r="O6" s="44" t="s">
         <v>12</v>
@@ -7135,7 +7148,7 @@
         <v>13</v>
       </c>
       <c r="Q6" s="44" t="s">
-        <v>619</v>
+        <v>609</v>
       </c>
       <c r="R6" s="44"/>
     </row>
@@ -7270,16 +7283,16 @@
         <v>163</v>
       </c>
       <c r="J2" s="56" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="K2" s="44" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>215</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>12</v>
@@ -7288,13 +7301,13 @@
         <v>216</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>217</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="S2" s="3" t="s">
         <v>216</v>
@@ -7303,7 +7316,7 @@
         <v>163</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
     </row>
     <row r="3" spans="1:21">
@@ -7335,16 +7348,16 @@
         <v>163</v>
       </c>
       <c r="J3" s="56" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>215</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>12</v>
@@ -7353,13 +7366,13 @@
         <v>216</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>341</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="S3" s="3" t="s">
         <v>216</v>
@@ -7368,7 +7381,7 @@
         <v>163</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
     </row>
     <row r="4" spans="1:21">
@@ -8504,10 +8517,10 @@
         <v>50</v>
       </c>
       <c r="H2" s="44" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="I2" s="44" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -8737,7 +8750,7 @@
       <c r="H6" s="44"/>
       <c r="I6" s="44"/>
       <c r="J6" s="44" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="K6" s="44"/>
       <c r="L6" s="44"/>
@@ -8820,7 +8833,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="G2" s="32">
         <v>2</v>
@@ -8851,7 +8864,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="G3" s="32"/>
       <c r="H3" s="32"/>
@@ -8880,7 +8893,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="G4" s="32"/>
       <c r="H4" s="32"/>
@@ -9486,7 +9499,7 @@
       </c>
       <c r="G4" s="44"/>
       <c r="H4" s="44" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="I4" s="44" t="s">
         <v>387</v>
@@ -9523,7 +9536,7 @@
       </c>
       <c r="G5" s="44"/>
       <c r="H5" s="44" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="I5" s="44" t="s">
         <v>387</v>
@@ -10025,7 +10038,7 @@
         <v>212</v>
       </c>
       <c r="J2" s="44" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="K2" s="44">
         <v>2</v>
@@ -10477,7 +10490,7 @@
       <c r="M2" s="32"/>
       <c r="N2" s="32"/>
       <c r="O2" s="32" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="P2" s="32"/>
       <c r="Q2" s="32" t="s">
@@ -10622,7 +10635,7 @@
         <v>15</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="I6" s="32" t="s">
         <v>387</v>
@@ -10670,7 +10683,7 @@
         <v>19</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="I7" s="32" t="s">
         <v>360</v>
@@ -10788,7 +10801,7 @@
       </c>
       <c r="G10" s="56"/>
       <c r="H10" s="32" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="I10" s="32"/>
       <c r="J10" s="32" t="s">
@@ -10836,7 +10849,7 @@
         <v>15</v>
       </c>
       <c r="H11" s="32" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="I11" s="32" t="s">
         <v>211</v>
@@ -10888,7 +10901,7 @@
       </c>
       <c r="G12" s="56"/>
       <c r="H12" s="32" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="I12" s="32" t="s">
         <v>376</v>
@@ -10976,7 +10989,7 @@
       </c>
       <c r="G14" s="56"/>
       <c r="H14" s="32" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="I14" s="32" t="s">
         <v>244</v>
@@ -11026,7 +11039,7 @@
         <v>15</v>
       </c>
       <c r="H15" s="32" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="I15" s="32" t="s">
         <v>367</v>
@@ -11620,10 +11633,10 @@
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
       <c r="R2" s="3" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
@@ -11882,10 +11895,10 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="T8" s="3">
         <v>0</v>
@@ -11931,10 +11944,10 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="T9" s="3"/>
       <c r="U9" s="3">
@@ -11984,10 +11997,10 @@
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
@@ -12210,10 +12223,10 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>

--- a/src/test/java/TestData/Scenario_TestData.xlsx
+++ b/src/test/java/TestData/Scenario_TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Copa_SHD_WebServices\src\test\java\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFFA3B47-6EFD-4C32-9A50-C641008FC3AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D3B0B86-662E-48B7-8035-BE66F36A3935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="8" activeTab="9" xr2:uid="{5D5A4724-D560-4FC2-9708-4BBF1DBA0B11}"/>
   </bookViews>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2086" uniqueCount="632">
   <si>
     <t>Scenario</t>
   </si>
@@ -1423,12 +1423,6 @@
     <t>09-07-2023</t>
   </si>
   <si>
-    <t>A0HF2Y</t>
-  </si>
-  <si>
-    <t>2302182801234</t>
-  </si>
-  <si>
     <t>A0HGV2</t>
   </si>
   <si>
@@ -1816,21 +1810,9 @@
     <t>2302182812729</t>
   </si>
   <si>
-    <t>A3OLLP</t>
-  </si>
-  <si>
-    <t>2302182812781</t>
-  </si>
-  <si>
     <t>302</t>
   </si>
   <si>
-    <t>A3RDTD</t>
-  </si>
-  <si>
-    <t>A3RGOR</t>
-  </si>
-  <si>
     <t>A25KWU</t>
   </si>
   <si>
@@ -1960,10 +1942,34 @@
     <t>BAIWFG</t>
   </si>
   <si>
-    <t>2302182822876</t>
-  </si>
-  <si>
     <t>2302182822912</t>
+  </si>
+  <si>
+    <t>BAJOOV</t>
+  </si>
+  <si>
+    <t>2302182822942</t>
+  </si>
+  <si>
+    <t>BAJRSP</t>
+  </si>
+  <si>
+    <t>BAJ0H5</t>
+  </si>
+  <si>
+    <t>ArrivalDateTime_Seg1</t>
+  </si>
+  <si>
+    <t>ArrivalDateTime_Seg2</t>
+  </si>
+  <si>
+    <t>BAJ2EN</t>
+  </si>
+  <si>
+    <t>2023-09-03T10:38:00</t>
+  </si>
+  <si>
+    <t>2023-09-03T17:24:00</t>
   </si>
 </sst>
 </file>
@@ -2706,7 +2712,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="44" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="I2" s="32" t="s">
         <v>211</v>
@@ -2723,7 +2729,7 @@
       <c r="M2" s="32"/>
       <c r="N2" s="32"/>
       <c r="O2" s="32" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="P2" s="38"/>
     </row>
@@ -2795,7 +2801,7 @@
         <v>1</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="I4" s="37" t="s">
         <v>351</v>
@@ -2832,7 +2838,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="37" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="I5" s="32"/>
       <c r="J5" s="32"/>
@@ -2865,7 +2871,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:V22"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="49.0"/>
@@ -2876,10 +2882,10 @@
     <col min="18" max="18" bestFit="true" customWidth="true" width="13.90625"/>
     <col min="19" max="19" bestFit="true" customWidth="true" width="17.0"/>
     <col min="21" max="21" bestFit="true" customWidth="true" width="12.6328125"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="14.36328125"/>
+    <col min="22" max="23" bestFit="true" customWidth="true" width="19.26953125"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:23">
       <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
@@ -2944,10 +2950,13 @@
         <v>257</v>
       </c>
       <c r="V1" s="43" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22">
+        <v>627</v>
+      </c>
+      <c r="W1" s="43" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23">
       <c r="A2" s="28" t="s">
         <v>218</v>
       </c>
@@ -2977,7 +2986,7 @@
       </c>
       <c r="J2" s="44"/>
       <c r="K2" s="44" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="L2" s="44"/>
       <c r="M2" s="44"/>
@@ -2990,8 +2999,9 @@
       <c r="T2" s="44"/>
       <c r="U2" s="44"/>
       <c r="V2" s="44"/>
-    </row>
-    <row r="3" spans="1:22">
+      <c r="W2" s="44"/>
+    </row>
+    <row r="3" spans="1:23">
       <c r="A3" s="28" t="s">
         <v>219</v>
       </c>
@@ -3015,10 +3025,10 @@
         <v>0</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="L3" s="44" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="M3" s="44"/>
       <c r="N3" s="44"/>
@@ -3030,8 +3040,9 @@
       <c r="T3" s="44"/>
       <c r="U3" s="44"/>
       <c r="V3" s="44"/>
-    </row>
-    <row r="4" spans="1:22">
+      <c r="W3" s="44"/>
+    </row>
+    <row r="4" spans="1:23">
       <c r="A4" s="28" t="s">
         <v>220</v>
       </c>
@@ -3066,8 +3077,9 @@
       <c r="T4" s="44"/>
       <c r="U4" s="44"/>
       <c r="V4" s="44"/>
-    </row>
-    <row r="5" spans="1:22">
+      <c r="W4" s="44"/>
+    </row>
+    <row r="5" spans="1:23">
       <c r="A5" s="28" t="s">
         <v>221</v>
       </c>
@@ -3089,10 +3101,10 @@
       <c r="I5" s="44"/>
       <c r="J5" s="44"/>
       <c r="K5" s="44" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="M5" s="44"/>
       <c r="N5" s="44" t="s">
@@ -3114,8 +3126,9 @@
         <v>242</v>
       </c>
       <c r="V5" s="44"/>
-    </row>
-    <row r="6" spans="1:22">
+      <c r="W5" s="44"/>
+    </row>
+    <row r="6" spans="1:23">
       <c r="A6" s="28" t="s">
         <v>222</v>
       </c>
@@ -3137,7 +3150,7 @@
       <c r="I6" s="44"/>
       <c r="J6" s="44"/>
       <c r="K6" s="44" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="L6" s="44"/>
       <c r="M6" s="44"/>
@@ -3148,7 +3161,7 @@
         <v>242</v>
       </c>
       <c r="P6" s="44" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="Q6" s="44"/>
       <c r="R6" s="44"/>
@@ -3160,8 +3173,9 @@
         <v>242</v>
       </c>
       <c r="V6" s="44"/>
-    </row>
-    <row r="7" spans="1:22">
+      <c r="W6" s="44"/>
+    </row>
+    <row r="7" spans="1:23">
       <c r="A7" s="28" t="s">
         <v>223</v>
       </c>
@@ -3183,10 +3197,10 @@
       <c r="I7" s="44"/>
       <c r="J7" s="44"/>
       <c r="K7" s="44" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="L7" s="44" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="M7" s="44"/>
       <c r="N7" s="44" t="s">
@@ -3196,20 +3210,21 @@
         <v>242</v>
       </c>
       <c r="P7" s="44" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="Q7" s="47" t="s">
         <v>87</v>
       </c>
       <c r="R7" s="44" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="S7" s="44"/>
       <c r="T7" s="44"/>
       <c r="U7" s="44"/>
       <c r="V7" s="44"/>
-    </row>
-    <row r="8" spans="1:22">
+      <c r="W7" s="44"/>
+    </row>
+    <row r="8" spans="1:23">
       <c r="A8" s="28" t="s">
         <v>224</v>
       </c>
@@ -3239,10 +3254,10 @@
       </c>
       <c r="J8" s="44"/>
       <c r="K8" s="44" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="L8" s="44" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="M8" s="44"/>
       <c r="N8" s="44" t="s">
@@ -3258,8 +3273,9 @@
       <c r="T8" s="44"/>
       <c r="U8" s="44"/>
       <c r="V8" s="44"/>
-    </row>
-    <row r="9" spans="1:22">
+      <c r="W8" s="44"/>
+    </row>
+    <row r="9" spans="1:23">
       <c r="A9" s="28" t="s">
         <v>225</v>
       </c>
@@ -3281,7 +3297,7 @@
       <c r="I9" s="44"/>
       <c r="J9" s="44"/>
       <c r="K9" s="44" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="L9" s="44"/>
       <c r="M9" s="44"/>
@@ -3298,10 +3314,11 @@
       <c r="T9" s="44"/>
       <c r="U9" s="44"/>
       <c r="V9" s="44" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22">
+        <v>618</v>
+      </c>
+      <c r="W9" s="44"/>
+    </row>
+    <row r="10" spans="1:23">
       <c r="A10" s="28" t="s">
         <v>226</v>
       </c>
@@ -3323,10 +3340,10 @@
       <c r="I10" s="44"/>
       <c r="J10" s="44"/>
       <c r="K10" s="44" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="L10" s="44" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="M10" s="44"/>
       <c r="N10" s="44"/>
@@ -3335,13 +3352,14 @@
       <c r="Q10" s="44"/>
       <c r="R10" s="44"/>
       <c r="S10" s="47" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="T10" s="44"/>
       <c r="U10" s="44"/>
       <c r="V10" s="44"/>
-    </row>
-    <row r="11" spans="1:22">
+      <c r="W10" s="44"/>
+    </row>
+    <row r="11" spans="1:23">
       <c r="A11" s="28" t="s">
         <v>227</v>
       </c>
@@ -3363,10 +3381,10 @@
       <c r="I11" s="44"/>
       <c r="J11" s="44"/>
       <c r="K11" s="44" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="L11" s="44" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="M11" s="44"/>
       <c r="N11" s="44"/>
@@ -3380,8 +3398,9 @@
       <c r="T11" s="44"/>
       <c r="U11" s="44"/>
       <c r="V11" s="44"/>
-    </row>
-    <row r="12" spans="1:22">
+      <c r="W11" s="44"/>
+    </row>
+    <row r="12" spans="1:23">
       <c r="A12" s="28" t="s">
         <v>228</v>
       </c>
@@ -3403,10 +3422,10 @@
       <c r="I12" s="44"/>
       <c r="J12" s="44"/>
       <c r="K12" s="44" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="L12" s="44" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="M12" s="44"/>
       <c r="N12" s="44" t="s">
@@ -3424,8 +3443,9 @@
       <c r="T12" s="44"/>
       <c r="U12" s="44"/>
       <c r="V12" s="44"/>
-    </row>
-    <row r="13" spans="1:22">
+      <c r="W12" s="44"/>
+    </row>
+    <row r="13" spans="1:23">
       <c r="A13" s="28" t="s">
         <v>229</v>
       </c>
@@ -3447,10 +3467,10 @@
       <c r="I13" s="44"/>
       <c r="J13" s="44"/>
       <c r="K13" s="44" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="L13" s="44" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="M13" s="44"/>
       <c r="N13" s="44" t="s">
@@ -3468,8 +3488,9 @@
       <c r="T13" s="44"/>
       <c r="U13" s="44"/>
       <c r="V13" s="44"/>
-    </row>
-    <row r="14" spans="1:22">
+      <c r="W13" s="44"/>
+    </row>
+    <row r="14" spans="1:23">
       <c r="A14" s="28" t="s">
         <v>230</v>
       </c>
@@ -3504,8 +3525,9 @@
       <c r="T14" s="44"/>
       <c r="U14" s="44"/>
       <c r="V14" s="44"/>
-    </row>
-    <row r="15" spans="1:22">
+      <c r="W14" s="44"/>
+    </row>
+    <row r="15" spans="1:23">
       <c r="A15" s="28" t="s">
         <v>231</v>
       </c>
@@ -3527,10 +3549,10 @@
       <c r="I15" s="44"/>
       <c r="J15" s="44"/>
       <c r="K15" s="44" t="s">
-        <v>580</v>
+        <v>623</v>
       </c>
       <c r="L15" s="44" t="s">
-        <v>581</v>
+        <v>624</v>
       </c>
       <c r="M15" s="44"/>
       <c r="N15" s="44" t="s">
@@ -3548,8 +3570,9 @@
       <c r="T15" s="44"/>
       <c r="U15" s="44"/>
       <c r="V15" s="44"/>
-    </row>
-    <row r="16" spans="1:22">
+      <c r="W15" s="44"/>
+    </row>
+    <row r="16" spans="1:23">
       <c r="A16" s="28" t="s">
         <v>232</v>
       </c>
@@ -3557,7 +3580,7 @@
         <v>0</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="D16" s="44" t="s">
         <v>12</v>
@@ -3571,7 +3594,7 @@
       <c r="I16" s="44"/>
       <c r="J16" s="44"/>
       <c r="K16" s="44" t="s">
-        <v>583</v>
+        <v>625</v>
       </c>
       <c r="L16" s="44"/>
       <c r="M16" s="44"/>
@@ -3588,13 +3611,14 @@
       <c r="T16" s="44"/>
       <c r="U16" s="44"/>
       <c r="V16" s="44"/>
-    </row>
-    <row r="17" spans="1:22">
+      <c r="W16" s="44"/>
+    </row>
+    <row r="17" spans="1:23">
       <c r="A17" s="28" t="s">
         <v>233</v>
       </c>
       <c r="B17" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" s="44" t="s">
         <v>325</v>
@@ -3611,7 +3635,7 @@
       <c r="I17" s="44"/>
       <c r="J17" s="44"/>
       <c r="K17" s="44" t="s">
-        <v>584</v>
+        <v>626</v>
       </c>
       <c r="L17" s="44"/>
       <c r="M17" s="44"/>
@@ -3624,8 +3648,9 @@
       <c r="T17" s="44"/>
       <c r="U17" s="44"/>
       <c r="V17" s="44"/>
-    </row>
-    <row r="18" spans="1:22">
+      <c r="W17" s="44"/>
+    </row>
+    <row r="18" spans="1:23">
       <c r="A18" s="28" t="s">
         <v>234</v>
       </c>
@@ -3655,7 +3680,7 @@
       </c>
       <c r="J18" s="44"/>
       <c r="K18" s="44" t="s">
-        <v>451</v>
+        <v>629</v>
       </c>
       <c r="L18" s="44"/>
       <c r="M18" s="44"/>
@@ -3671,9 +3696,14 @@
       <c r="S18" s="44"/>
       <c r="T18" s="44"/>
       <c r="U18" s="44"/>
-      <c r="V18" s="44"/>
-    </row>
-    <row r="19" spans="1:22">
+      <c r="V18" s="44" t="s">
+        <v>630</v>
+      </c>
+      <c r="W18" s="44" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23">
       <c r="A19" s="28" t="s">
         <v>235</v>
       </c>
@@ -3695,7 +3725,7 @@
       <c r="I19" s="44"/>
       <c r="J19" s="44"/>
       <c r="K19" s="44" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="L19" s="44"/>
       <c r="M19" s="44"/>
@@ -3712,8 +3742,9 @@
       <c r="T19" s="44"/>
       <c r="U19" s="44"/>
       <c r="V19" s="44"/>
-    </row>
-    <row r="20" spans="1:22">
+      <c r="W19" s="44"/>
+    </row>
+    <row r="20" spans="1:23">
       <c r="A20" s="28" t="s">
         <v>236</v>
       </c>
@@ -3735,7 +3766,7 @@
       <c r="I20" s="44"/>
       <c r="J20" s="44"/>
       <c r="K20" s="44" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="L20" s="44"/>
       <c r="M20" s="44"/>
@@ -3752,8 +3783,9 @@
       <c r="T20" s="44"/>
       <c r="U20" s="44"/>
       <c r="V20" s="44"/>
-    </row>
-    <row r="21" spans="1:22">
+      <c r="W20" s="44"/>
+    </row>
+    <row r="21" spans="1:23">
       <c r="A21" s="28" t="s">
         <v>237</v>
       </c>
@@ -3775,7 +3807,7 @@
       <c r="I21" s="44"/>
       <c r="J21" s="44"/>
       <c r="K21" s="44" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="L21" s="44"/>
       <c r="M21" s="44"/>
@@ -3792,8 +3824,9 @@
       <c r="T21" s="44"/>
       <c r="U21" s="44"/>
       <c r="V21" s="44"/>
-    </row>
-    <row r="22" spans="1:22">
+      <c r="W21" s="44"/>
+    </row>
+    <row r="22" spans="1:23">
       <c r="A22" s="28" t="s">
         <v>238</v>
       </c>
@@ -3801,7 +3834,7 @@
         <v>1</v>
       </c>
       <c r="C22" s="47" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D22" s="44" t="s">
         <v>34</v>
@@ -3823,7 +3856,7 @@
       </c>
       <c r="J22" s="44"/>
       <c r="K22" s="44" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="L22" s="44"/>
       <c r="M22" s="44"/>
@@ -3840,6 +3873,7 @@
       <c r="T22" s="44"/>
       <c r="U22" s="44"/>
       <c r="V22" s="44"/>
+      <c r="W22" s="44"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3918,14 +3952,14 @@
         <v>2</v>
       </c>
       <c r="D2" s="47" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="E2" s="47" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="F2" s="44"/>
       <c r="G2" s="47" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="H2" s="44" t="s">
         <v>12</v>
@@ -3949,7 +3983,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="47" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="E3" s="47" t="s">
         <v>264</v>
@@ -3958,7 +3992,7 @@
         <v>149</v>
       </c>
       <c r="G3" s="47" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="H3" s="44" t="s">
         <v>12</v>
@@ -3984,7 +4018,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="47" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="E4" s="44"/>
       <c r="F4" s="44" t="s">
@@ -4000,7 +4034,7 @@
         <v>13</v>
       </c>
       <c r="J4" s="47" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="K4" s="44" t="s">
         <v>13</v>
@@ -4085,7 +4119,7 @@
       <c r="G2" s="44"/>
       <c r="H2" s="44"/>
       <c r="I2" s="44" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="J2" s="44"/>
       <c r="K2" s="44"/>
@@ -4104,7 +4138,7 @@
       <c r="G3" s="44"/>
       <c r="H3" s="44"/>
       <c r="I3" s="44" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="J3" s="44"/>
       <c r="K3" s="44"/>
@@ -4123,7 +4157,7 @@
       <c r="G4" s="44"/>
       <c r="H4" s="44"/>
       <c r="I4" s="44" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="J4" s="44"/>
       <c r="K4" s="44"/>
@@ -4154,13 +4188,13 @@
         <v>12</v>
       </c>
       <c r="I5" s="44" t="s">
+        <v>527</v>
+      </c>
+      <c r="J5" s="44" t="s">
+        <v>528</v>
+      </c>
+      <c r="K5" s="44" t="s">
         <v>529</v>
-      </c>
-      <c r="J5" s="44" t="s">
-        <v>530</v>
-      </c>
-      <c r="K5" s="44" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -4189,10 +4223,10 @@
         <v>12</v>
       </c>
       <c r="I6" s="44" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="J6" s="44" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="K6" s="44"/>
     </row>
@@ -4472,16 +4506,16 @@
         <v>45</v>
       </c>
       <c r="J2" s="44" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="K2" s="44" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="L2" s="44" t="s">
         <v>207</v>
       </c>
       <c r="M2" s="44" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="N2" s="44" t="s">
         <v>208</v>
@@ -4490,13 +4524,13 @@
         <v>12</v>
       </c>
       <c r="P2" s="44" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="Q2" s="44" t="s">
         <v>62</v>
       </c>
       <c r="R2" s="44" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="S2" s="44" t="s">
         <v>12</v>
@@ -4542,16 +4576,16 @@
         <v>45</v>
       </c>
       <c r="J3" s="44" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="L3" s="44" t="s">
         <v>207</v>
       </c>
       <c r="M3" s="44" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="N3" s="44" t="s">
         <v>208</v>
@@ -4560,13 +4594,13 @@
         <v>12</v>
       </c>
       <c r="P3" s="44" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="Q3" s="44" t="s">
         <v>239</v>
       </c>
       <c r="R3" s="44" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="S3" s="44" t="s">
         <v>12</v>
@@ -4620,16 +4654,16 @@
       <c r="H4" s="44"/>
       <c r="I4" s="44"/>
       <c r="J4" s="44" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="K4" s="44" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="L4" s="44" t="s">
         <v>328</v>
       </c>
       <c r="M4" s="44" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="N4" s="44" t="s">
         <v>209</v>
@@ -4672,16 +4706,16 @@
       <c r="H5" s="44"/>
       <c r="I5" s="44"/>
       <c r="J5" s="44" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="L5" s="44" t="s">
         <v>328</v>
       </c>
       <c r="M5" s="44" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="N5" s="44" t="s">
         <v>209</v>
@@ -4732,16 +4766,16 @@
         <v>45</v>
       </c>
       <c r="J6" s="44" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="K6" s="44" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="L6" s="44" t="s">
         <v>207</v>
       </c>
       <c r="M6" s="44" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="N6" s="44" t="s">
         <v>208</v>
@@ -5783,16 +5817,16 @@
       <c r="I2" s="44"/>
       <c r="J2" s="44"/>
       <c r="K2" s="44" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>325</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>209</v>
@@ -5847,7 +5881,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>312</v>
@@ -5987,16 +6021,16 @@
         <v>2</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>325</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>209</v>
@@ -6005,7 +6039,7 @@
         <v>12</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="R5" s="15" t="s">
         <v>44</v>
@@ -6203,16 +6237,16 @@
       <c r="I9" s="44"/>
       <c r="J9" s="44"/>
       <c r="K9" s="44" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>325</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>209</v>
@@ -6524,16 +6558,16 @@
       <c r="U2" s="44"/>
       <c r="V2" s="44"/>
       <c r="W2" s="44" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="X2" s="44" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="Y2" s="44" t="s">
         <v>325</v>
       </c>
       <c r="Z2" s="44" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="AA2" s="44" t="s">
         <v>209</v>
@@ -6542,7 +6576,7 @@
         <v>12</v>
       </c>
       <c r="AC2" s="44" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -6660,16 +6694,16 @@
       <c r="U4" s="44"/>
       <c r="V4" s="44"/>
       <c r="W4" s="44" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="X4" s="44" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="Y4" s="44" t="s">
         <v>325</v>
       </c>
       <c r="Z4" s="44" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="AA4" s="44" t="s">
         <v>209</v>
@@ -6678,7 +6712,7 @@
         <v>12</v>
       </c>
       <c r="AC4" s="44" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
   </sheetData>
@@ -6936,16 +6970,16 @@
       <c r="I2" s="44"/>
       <c r="J2" s="44"/>
       <c r="K2" s="44" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="L2" s="44" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="M2" s="44" t="s">
         <v>18</v>
       </c>
       <c r="N2" s="44" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="O2" s="44" t="s">
         <v>12</v>
@@ -6954,7 +6988,7 @@
         <v>13</v>
       </c>
       <c r="Q2" s="44" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="R2" s="44"/>
     </row>
@@ -6982,16 +7016,16 @@
       <c r="I3" s="44"/>
       <c r="J3" s="44"/>
       <c r="K3" s="44" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="L3" s="44" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="M3" s="44" t="s">
         <v>18</v>
       </c>
       <c r="N3" s="44" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="O3" s="44" t="s">
         <v>12</v>
@@ -7000,10 +7034,10 @@
         <v>13</v>
       </c>
       <c r="Q3" s="44" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="R3" s="44" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -7038,16 +7072,16 @@
         <v>2</v>
       </c>
       <c r="K4" s="44" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="L4" s="44" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="M4" s="44" t="s">
         <v>18</v>
       </c>
       <c r="N4" s="44" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="O4" s="44" t="s">
         <v>12</v>
@@ -7056,7 +7090,7 @@
         <v>13</v>
       </c>
       <c r="Q4" s="44" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="R4" s="44"/>
     </row>
@@ -7084,16 +7118,16 @@
       <c r="I5" s="44"/>
       <c r="J5" s="44"/>
       <c r="K5" s="44" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="M5" s="44" t="s">
         <v>18</v>
       </c>
       <c r="N5" s="44" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="O5" s="44" t="s">
         <v>12</v>
@@ -7102,7 +7136,7 @@
         <v>13</v>
       </c>
       <c r="Q5" s="44" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="R5" s="44"/>
     </row>
@@ -7130,16 +7164,16 @@
       <c r="I6" s="44"/>
       <c r="J6" s="44"/>
       <c r="K6" s="44" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="L6" s="44" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="M6" s="44" t="s">
         <v>18</v>
       </c>
       <c r="N6" s="44" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="O6" s="44" t="s">
         <v>12</v>
@@ -7148,7 +7182,7 @@
         <v>13</v>
       </c>
       <c r="Q6" s="44" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="R6" s="44"/>
     </row>
@@ -7283,16 +7317,16 @@
         <v>163</v>
       </c>
       <c r="J2" s="56" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="K2" s="44" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>215</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>12</v>
@@ -7301,13 +7335,13 @@
         <v>216</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>217</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="S2" s="3" t="s">
         <v>216</v>
@@ -7316,7 +7350,7 @@
         <v>163</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="3" spans="1:21">
@@ -7348,16 +7382,16 @@
         <v>163</v>
       </c>
       <c r="J3" s="56" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>215</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>12</v>
@@ -7366,13 +7400,13 @@
         <v>216</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>341</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="S3" s="3" t="s">
         <v>216</v>
@@ -7381,7 +7415,7 @@
         <v>163</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="4" spans="1:21">
@@ -7586,7 +7620,7 @@
         <v>181</v>
       </c>
       <c r="B3" s="47" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -7696,40 +7730,40 @@
         <v>266</v>
       </c>
       <c r="C1" s="42" t="s">
+        <v>466</v>
+      </c>
+      <c r="D1" s="42" t="s">
+        <v>467</v>
+      </c>
+      <c r="E1" s="42" t="s">
         <v>468</v>
       </c>
-      <c r="D1" s="42" t="s">
+      <c r="F1" s="42" t="s">
         <v>469</v>
       </c>
-      <c r="E1" s="42" t="s">
+      <c r="G1" s="63" t="s">
         <v>470</v>
       </c>
-      <c r="F1" s="42" t="s">
+      <c r="H1" s="63" t="s">
         <v>471</v>
       </c>
-      <c r="G1" s="63" t="s">
-        <v>472</v>
-      </c>
-      <c r="H1" s="63" t="s">
-        <v>473</v>
-      </c>
       <c r="I1" s="63" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="J1" s="63" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="K1" s="42" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="L1" s="42" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="M1" s="42" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="N1" s="42" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -7740,40 +7774,40 @@
         <v>149</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D2" s="32" t="s">
         <v>121</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F2" s="44" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="G2" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H2" s="44" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="I2" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="J2" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="K2" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="L2" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="M2" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="N2" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -7784,40 +7818,40 @@
         <v>149</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D3" s="32" t="s">
         <v>121</v>
       </c>
       <c r="E3" s="32" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F3" s="44" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="G3" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H3" s="44" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="I3" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="J3" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="L3" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="M3" s="44" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="N3" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -7828,40 +7862,40 @@
         <v>149</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D4" s="32" t="s">
         <v>121</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F4" s="44" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="G4" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H4" s="44" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="I4" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="J4" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="K4" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="L4" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="M4" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="N4" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -7872,7 +7906,7 @@
         <v>149</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D5" s="32" t="s">
         <v>121</v>
@@ -7881,31 +7915,31 @@
         <v>121</v>
       </c>
       <c r="F5" s="44" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="G5" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H5" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="I5" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="J5" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="M5" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="N5" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -7916,7 +7950,7 @@
         <v>149</v>
       </c>
       <c r="C6" s="44" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D6" s="44" t="s">
         <v>121</v>
@@ -7925,31 +7959,31 @@
         <v>121</v>
       </c>
       <c r="F6" s="44" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="G6" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H6" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="I6" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="J6" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="K6" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="L6" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="M6" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="N6" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -7960,7 +7994,7 @@
         <v>149</v>
       </c>
       <c r="C7" s="44" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D7" s="44" t="s">
         <v>121</v>
@@ -7969,31 +8003,31 @@
         <v>121</v>
       </c>
       <c r="F7" s="44" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="G7" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H7" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="I7" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="J7" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="K7" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="L7" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="M7" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="N7" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -8004,40 +8038,40 @@
         <v>149</v>
       </c>
       <c r="C8" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D8" s="44" t="s">
         <v>121</v>
       </c>
       <c r="E8" s="44" t="s">
+        <v>476</v>
+      </c>
+      <c r="F8" s="44" t="s">
         <v>478</v>
-      </c>
-      <c r="F8" s="44" t="s">
-        <v>480</v>
       </c>
       <c r="G8" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H8" s="44" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="I8" s="44" t="s">
+        <v>483</v>
+      </c>
+      <c r="J8" s="44" t="s">
+        <v>481</v>
+      </c>
+      <c r="K8" s="44" t="s">
+        <v>477</v>
+      </c>
+      <c r="L8" s="44" t="s">
+        <v>479</v>
+      </c>
+      <c r="M8" s="44" t="s">
         <v>485</v>
       </c>
-      <c r="J8" s="44" t="s">
-        <v>483</v>
-      </c>
-      <c r="K8" s="44" t="s">
-        <v>479</v>
-      </c>
-      <c r="L8" s="44" t="s">
-        <v>481</v>
-      </c>
-      <c r="M8" s="44" t="s">
-        <v>487</v>
-      </c>
       <c r="N8" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -8048,40 +8082,40 @@
         <v>149</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D9" s="32" t="s">
         <v>121</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="F9" s="44" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="G9" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H9" s="44" t="s">
+        <v>488</v>
+      </c>
+      <c r="I9" s="44" t="s">
+        <v>489</v>
+      </c>
+      <c r="J9" s="44" t="s">
         <v>490</v>
       </c>
-      <c r="I9" s="44" t="s">
-        <v>491</v>
-      </c>
-      <c r="J9" s="44" t="s">
-        <v>492</v>
-      </c>
       <c r="K9" s="44" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="L9" s="44" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="M9" s="44" t="s">
         <v>428</v>
       </c>
       <c r="N9" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -8092,40 +8126,40 @@
         <v>149</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D10" s="44" t="s">
         <v>121</v>
       </c>
       <c r="E10" s="32" t="s">
+        <v>492</v>
+      </c>
+      <c r="F10" s="44" t="s">
         <v>494</v>
-      </c>
-      <c r="F10" s="44" t="s">
-        <v>496</v>
       </c>
       <c r="G10" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H10" s="44" t="s">
+        <v>495</v>
+      </c>
+      <c r="I10" s="44" t="s">
+        <v>496</v>
+      </c>
+      <c r="J10" s="44" t="s">
         <v>497</v>
       </c>
-      <c r="I10" s="44" t="s">
-        <v>498</v>
-      </c>
-      <c r="J10" s="44" t="s">
-        <v>499</v>
-      </c>
       <c r="K10" s="44" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="L10" s="44" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="M10" s="44" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="N10" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -8136,40 +8170,40 @@
         <v>149</v>
       </c>
       <c r="C11" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D11" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F11" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="G11" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="H11" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="I11" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="J11" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="K11" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="L11" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="M11" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="N11" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -8180,40 +8214,40 @@
         <v>149</v>
       </c>
       <c r="C12" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D12" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F12" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="G12" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="H12" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="I12" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="J12" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="K12" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="L12" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="M12" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="N12" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -8224,40 +8258,40 @@
         <v>149</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F13" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="G13" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="H13" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="I13" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="J13" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="K13" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="L13" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="M13" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="N13" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -8268,40 +8302,40 @@
         <v>149</v>
       </c>
       <c r="C14" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F14" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="G14" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="H14" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="I14" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="J14" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="K14" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="L14" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="M14" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="N14" s="44" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -8312,40 +8346,40 @@
         <v>149</v>
       </c>
       <c r="C15" s="44" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D15" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E15" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F15" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="G15" s="44" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="H15" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="I15" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="J15" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="K15" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="L15" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="M15" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="N15" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -8356,40 +8390,40 @@
         <v>149</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D16" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F16" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="G16" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="H16" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="I16" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="J16" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="K16" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="L16" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="M16" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="N16" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -8400,45 +8434,45 @@
         <v>149</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D17" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F17" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="G17" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="H17" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="I17" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="J17" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="K17" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="L17" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="M17" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="N17" s="44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="62" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
   </sheetData>
@@ -8517,10 +8551,10 @@
         <v>50</v>
       </c>
       <c r="H2" s="44" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="I2" s="44" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -8750,7 +8784,7 @@
       <c r="H6" s="44"/>
       <c r="I6" s="44"/>
       <c r="J6" s="44" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="K6" s="44"/>
       <c r="L6" s="44"/>
@@ -8833,7 +8867,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="G2" s="32">
         <v>2</v>
@@ -8864,7 +8898,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="G3" s="32"/>
       <c r="H3" s="32"/>
@@ -8893,7 +8927,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="G4" s="32"/>
       <c r="H4" s="32"/>
@@ -9483,7 +9517,7 @@
         <v>410</v>
       </c>
       <c r="B4" s="47" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C4" s="44" t="s">
         <v>12</v>
@@ -9499,7 +9533,7 @@
       </c>
       <c r="G4" s="44"/>
       <c r="H4" s="44" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="I4" s="44" t="s">
         <v>387</v>
@@ -9520,7 +9554,7 @@
         <v>411</v>
       </c>
       <c r="B5" s="47" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C5" s="44" t="s">
         <v>12</v>
@@ -9536,7 +9570,7 @@
       </c>
       <c r="G5" s="44"/>
       <c r="H5" s="44" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="I5" s="44" t="s">
         <v>387</v>
@@ -10038,7 +10072,7 @@
         <v>212</v>
       </c>
       <c r="J2" s="44" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="K2" s="44">
         <v>2</v>
@@ -10115,13 +10149,13 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="44" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B5" s="44">
         <v>2</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D5" s="44" t="s">
         <v>12</v>
@@ -10490,7 +10524,7 @@
       <c r="M2" s="32"/>
       <c r="N2" s="32"/>
       <c r="O2" s="32" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="P2" s="32"/>
       <c r="Q2" s="32" t="s">
@@ -10635,7 +10669,7 @@
         <v>15</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="I6" s="32" t="s">
         <v>387</v>
@@ -10652,7 +10686,7 @@
       <c r="Q6" s="32"/>
       <c r="R6" s="32"/>
       <c r="S6" s="32" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="T6" s="32" t="s">
         <v>437</v>
@@ -10683,7 +10717,7 @@
         <v>19</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="I7" s="32" t="s">
         <v>360</v>
@@ -10801,7 +10835,7 @@
       </c>
       <c r="G10" s="56"/>
       <c r="H10" s="32" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="I10" s="32"/>
       <c r="J10" s="32" t="s">
@@ -10816,7 +10850,7 @@
       <c r="Q10" s="32"/>
       <c r="R10" s="32"/>
       <c r="S10" s="32" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="T10" s="32" t="s">
         <v>373</v>
@@ -10849,7 +10883,7 @@
         <v>15</v>
       </c>
       <c r="H11" s="32" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="I11" s="32" t="s">
         <v>211</v>
@@ -10901,7 +10935,7 @@
       </c>
       <c r="G12" s="56"/>
       <c r="H12" s="32" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="I12" s="32" t="s">
         <v>376</v>
@@ -10989,7 +11023,7 @@
       </c>
       <c r="G14" s="56"/>
       <c r="H14" s="32" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="I14" s="32" t="s">
         <v>244</v>
@@ -11006,7 +11040,7 @@
       <c r="Q14" s="32"/>
       <c r="R14" s="32"/>
       <c r="S14" s="32" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="T14" s="32" t="s">
         <v>373</v>
@@ -11039,7 +11073,7 @@
         <v>15</v>
       </c>
       <c r="H15" s="32" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="I15" s="32" t="s">
         <v>367</v>
@@ -11633,10 +11667,10 @@
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
       <c r="R2" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
@@ -11895,10 +11929,10 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="T8" s="3">
         <v>0</v>
@@ -11915,7 +11949,7 @@
         <v>2</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>12</v>
@@ -11944,10 +11978,10 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="T9" s="3"/>
       <c r="U9" s="3">
@@ -11968,7 +12002,7 @@
         <v>2</v>
       </c>
       <c r="C10" s="47" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>12</v>
@@ -11997,10 +12031,10 @@
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
@@ -12194,7 +12228,7 @@
         <v>2</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="D16" s="32" t="s">
         <v>12</v>
@@ -12223,10 +12257,10 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>

--- a/src/test/java/TestData/Scenario_TestData.xlsx
+++ b/src/test/java/TestData/Scenario_TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Copa_SHD_WebServices\src\test\java\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D3B0B86-662E-48B7-8035-BE66F36A3935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A9C1064-BB6A-4868-A61A-B04C3A072782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="8" activeTab="9" xr2:uid="{5D5A4724-D560-4FC2-9708-4BBF1DBA0B11}"/>
   </bookViews>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2086" uniqueCount="632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2087" uniqueCount="635">
   <si>
     <t>Scenario</t>
   </si>
@@ -1423,15 +1423,6 @@
     <t>09-07-2023</t>
   </si>
   <si>
-    <t>A0HGV2</t>
-  </si>
-  <si>
-    <t>A0HG2T</t>
-  </si>
-  <si>
-    <t>A0HHGP</t>
-  </si>
-  <si>
     <t>A0HHSI</t>
   </si>
   <si>
@@ -1963,13 +1954,31 @@
     <t>ArrivalDateTime_Seg2</t>
   </si>
   <si>
-    <t>BAJ2EN</t>
-  </si>
-  <si>
     <t>2023-09-03T10:38:00</t>
   </si>
   <si>
     <t>2023-09-03T17:24:00</t>
+  </si>
+  <si>
+    <t>BALQKR</t>
+  </si>
+  <si>
+    <t>BALQXW</t>
+  </si>
+  <si>
+    <t>BALUL1</t>
+  </si>
+  <si>
+    <t>1033</t>
+  </si>
+  <si>
+    <t>BAMKCA</t>
+  </si>
+  <si>
+    <t>MARK</t>
+  </si>
+  <si>
+    <t>TESTA</t>
   </si>
 </sst>
 </file>
@@ -2712,7 +2721,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="44" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="I2" s="32" t="s">
         <v>211</v>
@@ -2729,7 +2738,7 @@
       <c r="M2" s="32"/>
       <c r="N2" s="32"/>
       <c r="O2" s="32" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="P2" s="38"/>
     </row>
@@ -2801,7 +2810,7 @@
         <v>1</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="I4" s="37" t="s">
         <v>351</v>
@@ -2838,7 +2847,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="37" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="I5" s="32"/>
       <c r="J5" s="32"/>
@@ -2950,10 +2959,10 @@
         <v>257</v>
       </c>
       <c r="V1" s="43" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="W1" s="43" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
     </row>
     <row r="2" spans="1:23">
@@ -2986,7 +2995,7 @@
       </c>
       <c r="J2" s="44"/>
       <c r="K2" s="44" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="L2" s="44"/>
       <c r="M2" s="44"/>
@@ -3025,10 +3034,10 @@
         <v>0</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="L3" s="44" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="M3" s="44"/>
       <c r="N3" s="44"/>
@@ -3101,10 +3110,10 @@
       <c r="I5" s="44"/>
       <c r="J5" s="44"/>
       <c r="K5" s="44" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="M5" s="44"/>
       <c r="N5" s="44" t="s">
@@ -3150,7 +3159,7 @@
       <c r="I6" s="44"/>
       <c r="J6" s="44"/>
       <c r="K6" s="44" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="L6" s="44"/>
       <c r="M6" s="44"/>
@@ -3161,7 +3170,7 @@
         <v>242</v>
       </c>
       <c r="P6" s="44" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="Q6" s="44"/>
       <c r="R6" s="44"/>
@@ -3197,10 +3206,10 @@
       <c r="I7" s="44"/>
       <c r="J7" s="44"/>
       <c r="K7" s="44" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="L7" s="44" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="M7" s="44"/>
       <c r="N7" s="44" t="s">
@@ -3210,13 +3219,13 @@
         <v>242</v>
       </c>
       <c r="P7" s="44" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="Q7" s="47" t="s">
         <v>87</v>
       </c>
       <c r="R7" s="44" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="S7" s="44"/>
       <c r="T7" s="44"/>
@@ -3254,10 +3263,10 @@
       </c>
       <c r="J8" s="44"/>
       <c r="K8" s="44" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="L8" s="44" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="M8" s="44"/>
       <c r="N8" s="44" t="s">
@@ -3297,7 +3306,7 @@
       <c r="I9" s="44"/>
       <c r="J9" s="44"/>
       <c r="K9" s="44" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="L9" s="44"/>
       <c r="M9" s="44"/>
@@ -3314,7 +3323,7 @@
       <c r="T9" s="44"/>
       <c r="U9" s="44"/>
       <c r="V9" s="44" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="W9" s="44"/>
     </row>
@@ -3340,10 +3349,10 @@
       <c r="I10" s="44"/>
       <c r="J10" s="44"/>
       <c r="K10" s="44" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="L10" s="44" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="M10" s="44"/>
       <c r="N10" s="44"/>
@@ -3352,7 +3361,7 @@
       <c r="Q10" s="44"/>
       <c r="R10" s="44"/>
       <c r="S10" s="47" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="T10" s="44"/>
       <c r="U10" s="44"/>
@@ -3381,10 +3390,10 @@
       <c r="I11" s="44"/>
       <c r="J11" s="44"/>
       <c r="K11" s="44" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="L11" s="44" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="M11" s="44"/>
       <c r="N11" s="44"/>
@@ -3422,10 +3431,10 @@
       <c r="I12" s="44"/>
       <c r="J12" s="44"/>
       <c r="K12" s="44" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="L12" s="44" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="M12" s="44"/>
       <c r="N12" s="44" t="s">
@@ -3467,10 +3476,10 @@
       <c r="I13" s="44"/>
       <c r="J13" s="44"/>
       <c r="K13" s="44" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="L13" s="44" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="M13" s="44"/>
       <c r="N13" s="44" t="s">
@@ -3549,10 +3558,10 @@
       <c r="I15" s="44"/>
       <c r="J15" s="44"/>
       <c r="K15" s="44" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="L15" s="44" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="M15" s="44"/>
       <c r="N15" s="44" t="s">
@@ -3580,7 +3589,7 @@
         <v>0</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="D16" s="44" t="s">
         <v>12</v>
@@ -3594,7 +3603,7 @@
       <c r="I16" s="44"/>
       <c r="J16" s="44"/>
       <c r="K16" s="44" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="L16" s="44"/>
       <c r="M16" s="44"/>
@@ -3635,7 +3644,7 @@
       <c r="I17" s="44"/>
       <c r="J17" s="44"/>
       <c r="K17" s="44" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="L17" s="44"/>
       <c r="M17" s="44"/>
@@ -3680,7 +3689,7 @@
       </c>
       <c r="J18" s="44"/>
       <c r="K18" s="44" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="L18" s="44"/>
       <c r="M18" s="44"/>
@@ -3697,10 +3706,10 @@
       <c r="T18" s="44"/>
       <c r="U18" s="44"/>
       <c r="V18" s="44" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="W18" s="44" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
     </row>
     <row r="19" spans="1:23">
@@ -3725,7 +3734,7 @@
       <c r="I19" s="44"/>
       <c r="J19" s="44"/>
       <c r="K19" s="44" t="s">
-        <v>450</v>
+        <v>629</v>
       </c>
       <c r="L19" s="44"/>
       <c r="M19" s="44"/>
@@ -3741,7 +3750,9 @@
       <c r="S19" s="44"/>
       <c r="T19" s="44"/>
       <c r="U19" s="44"/>
-      <c r="V19" s="44"/>
+      <c r="V19" s="44" t="s">
+        <v>615</v>
+      </c>
       <c r="W19" s="44"/>
     </row>
     <row r="20" spans="1:23">
@@ -3766,7 +3777,7 @@
       <c r="I20" s="44"/>
       <c r="J20" s="44"/>
       <c r="K20" s="44" t="s">
-        <v>451</v>
+        <v>630</v>
       </c>
       <c r="L20" s="44"/>
       <c r="M20" s="44"/>
@@ -3792,14 +3803,14 @@
       <c r="B21" s="44">
         <v>0</v>
       </c>
-      <c r="C21" s="44" t="s">
-        <v>325</v>
+      <c r="C21" s="47" t="s">
+        <v>631</v>
       </c>
       <c r="D21" s="44" t="s">
-        <v>209</v>
+        <v>12</v>
       </c>
       <c r="E21" s="44" t="s">
-        <v>12</v>
+        <v>163</v>
       </c>
       <c r="F21" s="44"/>
       <c r="G21" s="44"/>
@@ -3807,15 +3818,15 @@
       <c r="I21" s="44"/>
       <c r="J21" s="44"/>
       <c r="K21" s="44" t="s">
-        <v>452</v>
+        <v>632</v>
       </c>
       <c r="L21" s="44"/>
       <c r="M21" s="44"/>
       <c r="N21" s="44" t="s">
-        <v>21</v>
+        <v>633</v>
       </c>
       <c r="O21" s="44" t="s">
-        <v>242</v>
+        <v>634</v>
       </c>
       <c r="P21" s="44"/>
       <c r="Q21" s="44"/>
@@ -3834,7 +3845,7 @@
         <v>1</v>
       </c>
       <c r="C22" s="47" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="D22" s="44" t="s">
         <v>34</v>
@@ -3856,7 +3867,7 @@
       </c>
       <c r="J22" s="44"/>
       <c r="K22" s="44" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="L22" s="44"/>
       <c r="M22" s="44"/>
@@ -3952,14 +3963,14 @@
         <v>2</v>
       </c>
       <c r="D2" s="47" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="E2" s="47" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="F2" s="44"/>
       <c r="G2" s="47" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="H2" s="44" t="s">
         <v>12</v>
@@ -3983,7 +3994,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="47" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="E3" s="47" t="s">
         <v>264</v>
@@ -3992,7 +4003,7 @@
         <v>149</v>
       </c>
       <c r="G3" s="47" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="H3" s="44" t="s">
         <v>12</v>
@@ -4018,7 +4029,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="47" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="E4" s="44"/>
       <c r="F4" s="44" t="s">
@@ -4034,7 +4045,7 @@
         <v>13</v>
       </c>
       <c r="J4" s="47" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="K4" s="44" t="s">
         <v>13</v>
@@ -4119,7 +4130,7 @@
       <c r="G2" s="44"/>
       <c r="H2" s="44"/>
       <c r="I2" s="44" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="J2" s="44"/>
       <c r="K2" s="44"/>
@@ -4138,7 +4149,7 @@
       <c r="G3" s="44"/>
       <c r="H3" s="44"/>
       <c r="I3" s="44" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="J3" s="44"/>
       <c r="K3" s="44"/>
@@ -4157,7 +4168,7 @@
       <c r="G4" s="44"/>
       <c r="H4" s="44"/>
       <c r="I4" s="44" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="J4" s="44"/>
       <c r="K4" s="44"/>
@@ -4188,13 +4199,13 @@
         <v>12</v>
       </c>
       <c r="I5" s="44" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="J5" s="44" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -4223,10 +4234,10 @@
         <v>12</v>
       </c>
       <c r="I6" s="44" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="J6" s="44" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="K6" s="44"/>
     </row>
@@ -4506,16 +4517,16 @@
         <v>45</v>
       </c>
       <c r="J2" s="44" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="K2" s="44" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="L2" s="44" t="s">
         <v>207</v>
       </c>
       <c r="M2" s="44" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="N2" s="44" t="s">
         <v>208</v>
@@ -4524,13 +4535,13 @@
         <v>12</v>
       </c>
       <c r="P2" s="44" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="Q2" s="44" t="s">
         <v>62</v>
       </c>
       <c r="R2" s="44" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="S2" s="44" t="s">
         <v>12</v>
@@ -4576,16 +4587,16 @@
         <v>45</v>
       </c>
       <c r="J3" s="44" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="L3" s="44" t="s">
         <v>207</v>
       </c>
       <c r="M3" s="44" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="N3" s="44" t="s">
         <v>208</v>
@@ -4594,13 +4605,13 @@
         <v>12</v>
       </c>
       <c r="P3" s="44" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="Q3" s="44" t="s">
         <v>239</v>
       </c>
       <c r="R3" s="44" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="S3" s="44" t="s">
         <v>12</v>
@@ -4654,16 +4665,16 @@
       <c r="H4" s="44"/>
       <c r="I4" s="44"/>
       <c r="J4" s="44" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="K4" s="44" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="L4" s="44" t="s">
         <v>328</v>
       </c>
       <c r="M4" s="44" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="N4" s="44" t="s">
         <v>209</v>
@@ -4706,16 +4717,16 @@
       <c r="H5" s="44"/>
       <c r="I5" s="44"/>
       <c r="J5" s="44" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="L5" s="44" t="s">
         <v>328</v>
       </c>
       <c r="M5" s="44" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="N5" s="44" t="s">
         <v>209</v>
@@ -4766,16 +4777,16 @@
         <v>45</v>
       </c>
       <c r="J6" s="44" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="K6" s="44" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="L6" s="44" t="s">
         <v>207</v>
       </c>
       <c r="M6" s="44" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="N6" s="44" t="s">
         <v>208</v>
@@ -5817,16 +5828,16 @@
       <c r="I2" s="44"/>
       <c r="J2" s="44"/>
       <c r="K2" s="44" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>325</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>209</v>
@@ -5881,7 +5892,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>312</v>
@@ -6021,16 +6032,16 @@
         <v>2</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>325</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>209</v>
@@ -6039,7 +6050,7 @@
         <v>12</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="R5" s="15" t="s">
         <v>44</v>
@@ -6237,16 +6248,16 @@
       <c r="I9" s="44"/>
       <c r="J9" s="44"/>
       <c r="K9" s="44" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>325</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>209</v>
@@ -6558,16 +6569,16 @@
       <c r="U2" s="44"/>
       <c r="V2" s="44"/>
       <c r="W2" s="44" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="X2" s="44" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="Y2" s="44" t="s">
         <v>325</v>
       </c>
       <c r="Z2" s="44" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="AA2" s="44" t="s">
         <v>209</v>
@@ -6576,7 +6587,7 @@
         <v>12</v>
       </c>
       <c r="AC2" s="44" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -6694,16 +6705,16 @@
       <c r="U4" s="44"/>
       <c r="V4" s="44"/>
       <c r="W4" s="44" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="X4" s="44" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="Y4" s="44" t="s">
         <v>325</v>
       </c>
       <c r="Z4" s="44" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="AA4" s="44" t="s">
         <v>209</v>
@@ -6712,7 +6723,7 @@
         <v>12</v>
       </c>
       <c r="AC4" s="44" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
   </sheetData>
@@ -6970,16 +6981,16 @@
       <c r="I2" s="44"/>
       <c r="J2" s="44"/>
       <c r="K2" s="44" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="L2" s="44" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="M2" s="44" t="s">
         <v>18</v>
       </c>
       <c r="N2" s="44" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="O2" s="44" t="s">
         <v>12</v>
@@ -6988,7 +6999,7 @@
         <v>13</v>
       </c>
       <c r="Q2" s="44" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="R2" s="44"/>
     </row>
@@ -7016,16 +7027,16 @@
       <c r="I3" s="44"/>
       <c r="J3" s="44"/>
       <c r="K3" s="44" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="L3" s="44" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="M3" s="44" t="s">
         <v>18</v>
       </c>
       <c r="N3" s="44" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="O3" s="44" t="s">
         <v>12</v>
@@ -7034,10 +7045,10 @@
         <v>13</v>
       </c>
       <c r="Q3" s="44" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="R3" s="44" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -7072,16 +7083,16 @@
         <v>2</v>
       </c>
       <c r="K4" s="44" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="L4" s="44" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="M4" s="44" t="s">
         <v>18</v>
       </c>
       <c r="N4" s="44" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="O4" s="44" t="s">
         <v>12</v>
@@ -7090,7 +7101,7 @@
         <v>13</v>
       </c>
       <c r="Q4" s="44" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="R4" s="44"/>
     </row>
@@ -7118,16 +7129,16 @@
       <c r="I5" s="44"/>
       <c r="J5" s="44"/>
       <c r="K5" s="44" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="M5" s="44" t="s">
         <v>18</v>
       </c>
       <c r="N5" s="44" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="O5" s="44" t="s">
         <v>12</v>
@@ -7136,7 +7147,7 @@
         <v>13</v>
       </c>
       <c r="Q5" s="44" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="R5" s="44"/>
     </row>
@@ -7164,16 +7175,16 @@
       <c r="I6" s="44"/>
       <c r="J6" s="44"/>
       <c r="K6" s="44" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="L6" s="44" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="M6" s="44" t="s">
         <v>18</v>
       </c>
       <c r="N6" s="44" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="O6" s="44" t="s">
         <v>12</v>
@@ -7182,7 +7193,7 @@
         <v>13</v>
       </c>
       <c r="Q6" s="44" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="R6" s="44"/>
     </row>
@@ -7317,16 +7328,16 @@
         <v>163</v>
       </c>
       <c r="J2" s="56" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="K2" s="44" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>215</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>12</v>
@@ -7335,13 +7346,13 @@
         <v>216</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>217</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="S2" s="3" t="s">
         <v>216</v>
@@ -7350,7 +7361,7 @@
         <v>163</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="3" spans="1:21">
@@ -7382,16 +7393,16 @@
         <v>163</v>
       </c>
       <c r="J3" s="56" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>215</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>12</v>
@@ -7400,13 +7411,13 @@
         <v>216</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>341</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="S3" s="3" t="s">
         <v>216</v>
@@ -7415,7 +7426,7 @@
         <v>163</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="4" spans="1:21">
@@ -7620,7 +7631,7 @@
         <v>181</v>
       </c>
       <c r="B3" s="47" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -7730,40 +7741,40 @@
         <v>266</v>
       </c>
       <c r="C1" s="42" t="s">
+        <v>463</v>
+      </c>
+      <c r="D1" s="42" t="s">
+        <v>464</v>
+      </c>
+      <c r="E1" s="42" t="s">
+        <v>465</v>
+      </c>
+      <c r="F1" s="42" t="s">
         <v>466</v>
       </c>
-      <c r="D1" s="42" t="s">
+      <c r="G1" s="63" t="s">
         <v>467</v>
       </c>
-      <c r="E1" s="42" t="s">
+      <c r="H1" s="63" t="s">
         <v>468</v>
       </c>
-      <c r="F1" s="42" t="s">
-        <v>469</v>
-      </c>
-      <c r="G1" s="63" t="s">
-        <v>470</v>
-      </c>
-      <c r="H1" s="63" t="s">
-        <v>471</v>
-      </c>
       <c r="I1" s="63" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="J1" s="63" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="K1" s="42" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="L1" s="42" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="M1" s="42" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="N1" s="42" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -7774,40 +7785,40 @@
         <v>149</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="D2" s="32" t="s">
         <v>121</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="F2" s="44" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="G2" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H2" s="44" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="I2" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="J2" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="K2" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="L2" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="M2" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="N2" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -7818,40 +7829,40 @@
         <v>149</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="D3" s="32" t="s">
         <v>121</v>
       </c>
       <c r="E3" s="32" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="F3" s="44" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="G3" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H3" s="44" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="I3" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="J3" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="L3" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="M3" s="44" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="N3" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -7862,40 +7873,40 @@
         <v>149</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="D4" s="32" t="s">
         <v>121</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="F4" s="44" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="G4" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H4" s="44" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="I4" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="J4" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="K4" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="L4" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="M4" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="N4" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -7906,7 +7917,7 @@
         <v>149</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="D5" s="32" t="s">
         <v>121</v>
@@ -7915,31 +7926,31 @@
         <v>121</v>
       </c>
       <c r="F5" s="44" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="G5" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H5" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="I5" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="J5" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="M5" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="N5" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -7950,7 +7961,7 @@
         <v>149</v>
       </c>
       <c r="C6" s="44" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="D6" s="44" t="s">
         <v>121</v>
@@ -7959,31 +7970,31 @@
         <v>121</v>
       </c>
       <c r="F6" s="44" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="G6" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H6" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="I6" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="J6" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="K6" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="L6" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="M6" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="N6" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -7994,7 +8005,7 @@
         <v>149</v>
       </c>
       <c r="C7" s="44" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="D7" s="44" t="s">
         <v>121</v>
@@ -8003,31 +8014,31 @@
         <v>121</v>
       </c>
       <c r="F7" s="44" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="G7" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H7" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="I7" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="J7" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="K7" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="L7" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="M7" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="N7" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -8038,40 +8049,40 @@
         <v>149</v>
       </c>
       <c r="C8" s="44" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="D8" s="44" t="s">
         <v>121</v>
       </c>
       <c r="E8" s="44" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="F8" s="44" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="G8" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H8" s="44" t="s">
+        <v>479</v>
+      </c>
+      <c r="I8" s="44" t="s">
+        <v>480</v>
+      </c>
+      <c r="J8" s="44" t="s">
+        <v>478</v>
+      </c>
+      <c r="K8" s="44" t="s">
+        <v>474</v>
+      </c>
+      <c r="L8" s="44" t="s">
+        <v>476</v>
+      </c>
+      <c r="M8" s="44" t="s">
         <v>482</v>
       </c>
-      <c r="I8" s="44" t="s">
-        <v>483</v>
-      </c>
-      <c r="J8" s="44" t="s">
-        <v>481</v>
-      </c>
-      <c r="K8" s="44" t="s">
-        <v>477</v>
-      </c>
-      <c r="L8" s="44" t="s">
-        <v>479</v>
-      </c>
-      <c r="M8" s="44" t="s">
-        <v>485</v>
-      </c>
       <c r="N8" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -8082,40 +8093,40 @@
         <v>149</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="D9" s="32" t="s">
         <v>121</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="F9" s="44" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="G9" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H9" s="44" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="I9" s="44" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="J9" s="44" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="K9" s="44" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="L9" s="44" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="M9" s="44" t="s">
         <v>428</v>
       </c>
       <c r="N9" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -8126,40 +8137,40 @@
         <v>149</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="D10" s="44" t="s">
         <v>121</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="F10" s="44" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="G10" s="44" t="s">
         <v>338</v>
       </c>
       <c r="H10" s="44" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="I10" s="44" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="J10" s="44" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="K10" s="44" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="L10" s="44" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="M10" s="44" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="N10" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -8170,40 +8181,40 @@
         <v>149</v>
       </c>
       <c r="C11" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D11" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="F11" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="G11" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="H11" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="I11" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="J11" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="K11" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="L11" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="M11" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="N11" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -8214,40 +8225,40 @@
         <v>149</v>
       </c>
       <c r="C12" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D12" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="F12" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="G12" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="H12" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="I12" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="J12" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="K12" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="L12" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="M12" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="N12" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -8258,40 +8269,40 @@
         <v>149</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="F13" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="G13" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="H13" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="I13" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="J13" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="K13" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="L13" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="M13" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="N13" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -8302,40 +8313,40 @@
         <v>149</v>
       </c>
       <c r="C14" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="F14" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="G14" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="H14" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="I14" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="J14" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="K14" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="L14" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="M14" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="N14" s="44" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -8346,40 +8357,40 @@
         <v>149</v>
       </c>
       <c r="C15" s="44" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="D15" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="E15" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="F15" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="G15" s="44" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="H15" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="I15" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="J15" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="K15" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="L15" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="M15" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="N15" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -8390,40 +8401,40 @@
         <v>149</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="D16" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="F16" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="G16" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="H16" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="I16" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="J16" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="K16" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="L16" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="M16" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="N16" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -8434,45 +8445,45 @@
         <v>149</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D17" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="F17" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="G17" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="H17" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="I17" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="J17" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="K17" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="L17" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="M17" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="N17" s="44" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="62" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -8551,10 +8562,10 @@
         <v>50</v>
       </c>
       <c r="H2" s="44" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="I2" s="44" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -8784,7 +8795,7 @@
       <c r="H6" s="44"/>
       <c r="I6" s="44"/>
       <c r="J6" s="44" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="K6" s="44"/>
       <c r="L6" s="44"/>
@@ -8867,7 +8878,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="G2" s="32">
         <v>2</v>
@@ -8898,7 +8909,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="G3" s="32"/>
       <c r="H3" s="32"/>
@@ -8927,7 +8938,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="G4" s="32"/>
       <c r="H4" s="32"/>
@@ -9517,7 +9528,7 @@
         <v>410</v>
       </c>
       <c r="B4" s="47" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C4" s="44" t="s">
         <v>12</v>
@@ -9533,7 +9544,7 @@
       </c>
       <c r="G4" s="44"/>
       <c r="H4" s="44" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="I4" s="44" t="s">
         <v>387</v>
@@ -9554,7 +9565,7 @@
         <v>411</v>
       </c>
       <c r="B5" s="47" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C5" s="44" t="s">
         <v>12</v>
@@ -9570,7 +9581,7 @@
       </c>
       <c r="G5" s="44"/>
       <c r="H5" s="44" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="I5" s="44" t="s">
         <v>387</v>
@@ -10072,7 +10083,7 @@
         <v>212</v>
       </c>
       <c r="J2" s="44" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="K2" s="44">
         <v>2</v>
@@ -10149,13 +10160,13 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="44" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B5" s="44">
         <v>2</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="D5" s="44" t="s">
         <v>12</v>
@@ -10524,7 +10535,7 @@
       <c r="M2" s="32"/>
       <c r="N2" s="32"/>
       <c r="O2" s="32" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="P2" s="32"/>
       <c r="Q2" s="32" t="s">
@@ -10669,7 +10680,7 @@
         <v>15</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="I6" s="32" t="s">
         <v>387</v>
@@ -10686,7 +10697,7 @@
       <c r="Q6" s="32"/>
       <c r="R6" s="32"/>
       <c r="S6" s="32" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="T6" s="32" t="s">
         <v>437</v>
@@ -10717,7 +10728,7 @@
         <v>19</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="I7" s="32" t="s">
         <v>360</v>
@@ -10835,7 +10846,7 @@
       </c>
       <c r="G10" s="56"/>
       <c r="H10" s="32" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="I10" s="32"/>
       <c r="J10" s="32" t="s">
@@ -10850,7 +10861,7 @@
       <c r="Q10" s="32"/>
       <c r="R10" s="32"/>
       <c r="S10" s="32" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="T10" s="32" t="s">
         <v>373</v>
@@ -10883,7 +10894,7 @@
         <v>15</v>
       </c>
       <c r="H11" s="32" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="I11" s="32" t="s">
         <v>211</v>
@@ -10935,7 +10946,7 @@
       </c>
       <c r="G12" s="56"/>
       <c r="H12" s="32" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="I12" s="32" t="s">
         <v>376</v>
@@ -11023,7 +11034,7 @@
       </c>
       <c r="G14" s="56"/>
       <c r="H14" s="32" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="I14" s="32" t="s">
         <v>244</v>
@@ -11040,7 +11051,7 @@
       <c r="Q14" s="32"/>
       <c r="R14" s="32"/>
       <c r="S14" s="32" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="T14" s="32" t="s">
         <v>373</v>
@@ -11073,7 +11084,7 @@
         <v>15</v>
       </c>
       <c r="H15" s="32" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="I15" s="32" t="s">
         <v>367</v>
@@ -11667,10 +11678,10 @@
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
       <c r="R2" s="3" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
@@ -11929,10 +11940,10 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="T8" s="3">
         <v>0</v>
@@ -11949,7 +11960,7 @@
         <v>2</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>12</v>
@@ -11978,10 +11989,10 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="T9" s="3"/>
       <c r="U9" s="3">
@@ -12002,7 +12013,7 @@
         <v>2</v>
       </c>
       <c r="C10" s="47" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>12</v>
@@ -12031,10 +12042,10 @@
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
@@ -12228,7 +12239,7 @@
         <v>2</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D16" s="32" t="s">
         <v>12</v>
@@ -12257,10 +12268,10 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>

--- a/src/test/java/TestData/Scenario_TestData.xlsx
+++ b/src/test/java/TestData/Scenario_TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Copa_SHD_WebServices\src\test\java\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A9C1064-BB6A-4868-A61A-B04C3A072782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D19DA22-55BA-44BF-84B1-7C363E09180E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="8" activeTab="9" xr2:uid="{5D5A4724-D560-4FC2-9708-4BBF1DBA0B11}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="27" activeTab="30" xr2:uid="{5D5A4724-D560-4FC2-9708-4BBF1DBA0B11}"/>
   </bookViews>
   <sheets>
     <sheet name="AdvancePassengerInfo" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2087" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2120" uniqueCount="647">
   <si>
     <t>Scenario</t>
   </si>
@@ -1018,18 +1018,6 @@
     <t>2024-03-10T06:42:00</t>
   </si>
   <si>
-    <t>Carrier Code</t>
-  </si>
-  <si>
-    <t>Updated Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Updated Flight </t>
-  </si>
-  <si>
-    <t>Sync Flight</t>
-  </si>
-  <si>
     <t xml:space="preserve">NAME </t>
   </si>
   <si>
@@ -1423,9 +1411,6 @@
     <t>09-07-2023</t>
   </si>
   <si>
-    <t>A0HHSI</t>
-  </si>
-  <si>
     <t>2023-08-18T04:51:00</t>
   </si>
   <si>
@@ -1756,21 +1741,6 @@
     <t>A2MRDV</t>
   </si>
   <si>
-    <t>A2MRDY</t>
-  </si>
-  <si>
-    <t>A2MRED</t>
-  </si>
-  <si>
-    <t>A2MREJ</t>
-  </si>
-  <si>
-    <t>A2MRES</t>
-  </si>
-  <si>
-    <t>A2MREX</t>
-  </si>
-  <si>
     <t>A2MRG5</t>
   </si>
   <si>
@@ -1979,6 +1949,72 @@
   </si>
   <si>
     <t>TESTA</t>
+  </si>
+  <si>
+    <t>BANEU0</t>
+  </si>
+  <si>
+    <t>BANE1O</t>
+  </si>
+  <si>
+    <t>BANKK3</t>
+  </si>
+  <si>
+    <t>BANKLX</t>
+  </si>
+  <si>
+    <t>1stSegDepartureDateTime</t>
+  </si>
+  <si>
+    <t>2ndSegDepartureDateTime</t>
+  </si>
+  <si>
+    <t>ArrAirport</t>
+  </si>
+  <si>
+    <t>1stSegClass</t>
+  </si>
+  <si>
+    <t>2ndSegClass</t>
+  </si>
+  <si>
+    <t>NewDeptDate</t>
+  </si>
+  <si>
+    <t>NewDeptAirport</t>
+  </si>
+  <si>
+    <t>NewArrAirport</t>
+  </si>
+  <si>
+    <t>NewFlightNo</t>
+  </si>
+  <si>
+    <t>NewClass</t>
+  </si>
+  <si>
+    <t>ArrDate1st</t>
+  </si>
+  <si>
+    <t>ArrDate2nd</t>
+  </si>
+  <si>
+    <t>2023-08-30T06:44:00</t>
+  </si>
+  <si>
+    <t>BAOJ41</t>
+  </si>
+  <si>
+    <t>2023-08-30T00:23:00</t>
+  </si>
+  <si>
+    <t>BAOMOX</t>
+  </si>
+  <si>
+    <t>BAOQ21</t>
+  </si>
+  <si>
+    <t>BAOVIV</t>
   </si>
 </sst>
 </file>
@@ -2073,7 +2109,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2125,6 +2161,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2215,7 +2257,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2315,6 +2357,8 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2706,7 +2750,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D2" s="44" t="s">
         <v>209</v>
@@ -2721,7 +2765,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="44" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="I2" s="32" t="s">
         <v>211</v>
@@ -2738,7 +2782,7 @@
       <c r="M2" s="32"/>
       <c r="N2" s="32"/>
       <c r="O2" s="32" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="P2" s="38"/>
     </row>
@@ -2750,7 +2794,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D3" s="44" t="s">
         <v>209</v>
@@ -2789,13 +2833,13 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="37" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B4" s="44">
         <v>0</v>
       </c>
       <c r="C4" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D4" s="44" t="s">
         <v>209</v>
@@ -2810,13 +2854,13 @@
         <v>1</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>612</v>
+        <v>602</v>
       </c>
       <c r="I4" s="37" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="J4" s="37" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="K4" s="32"/>
       <c r="L4" s="32"/>
@@ -2826,13 +2870,13 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="37" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B5" s="44">
         <v>0</v>
       </c>
       <c r="C5" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D5" s="44" t="s">
         <v>209</v>
@@ -2847,7 +2891,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="37" t="s">
-        <v>613</v>
+        <v>603</v>
       </c>
       <c r="I5" s="32"/>
       <c r="J5" s="32"/>
@@ -2959,10 +3003,10 @@
         <v>257</v>
       </c>
       <c r="V1" s="43" t="s">
-        <v>624</v>
+        <v>614</v>
       </c>
       <c r="W1" s="43" t="s">
-        <v>625</v>
+        <v>615</v>
       </c>
     </row>
     <row r="2" spans="1:23">
@@ -2995,7 +3039,7 @@
       </c>
       <c r="J2" s="44"/>
       <c r="K2" s="44" t="s">
-        <v>566</v>
+        <v>556</v>
       </c>
       <c r="L2" s="44"/>
       <c r="M2" s="44"/>
@@ -3034,10 +3078,10 @@
         <v>0</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="L3" s="44" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="M3" s="44"/>
       <c r="N3" s="44"/>
@@ -3059,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D4" s="44" t="s">
         <v>209</v>
@@ -3096,7 +3140,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D5" s="44" t="s">
         <v>209</v>
@@ -3110,10 +3154,10 @@
       <c r="I5" s="44"/>
       <c r="J5" s="44"/>
       <c r="K5" s="44" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>568</v>
+        <v>558</v>
       </c>
       <c r="M5" s="44"/>
       <c r="N5" s="44" t="s">
@@ -3145,7 +3189,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D6" s="44" t="s">
         <v>209</v>
@@ -3159,7 +3203,7 @@
       <c r="I6" s="44"/>
       <c r="J6" s="44"/>
       <c r="K6" s="44" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="L6" s="44"/>
       <c r="M6" s="44"/>
@@ -3170,7 +3214,7 @@
         <v>242</v>
       </c>
       <c r="P6" s="44" t="s">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="Q6" s="44"/>
       <c r="R6" s="44"/>
@@ -3192,7 +3236,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D7" s="44" t="s">
         <v>209</v>
@@ -3206,10 +3250,10 @@
       <c r="I7" s="44"/>
       <c r="J7" s="44"/>
       <c r="K7" s="44" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="L7" s="44" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="M7" s="44"/>
       <c r="N7" s="44" t="s">
@@ -3219,13 +3263,13 @@
         <v>242</v>
       </c>
       <c r="P7" s="44" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="Q7" s="47" t="s">
         <v>87</v>
       </c>
       <c r="R7" s="44" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="S7" s="44"/>
       <c r="T7" s="44"/>
@@ -3263,10 +3307,10 @@
       </c>
       <c r="J8" s="44"/>
       <c r="K8" s="44" t="s">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="L8" s="44" t="s">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="M8" s="44"/>
       <c r="N8" s="44" t="s">
@@ -3292,7 +3336,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D9" s="44" t="s">
         <v>209</v>
@@ -3306,7 +3350,7 @@
       <c r="I9" s="44"/>
       <c r="J9" s="44"/>
       <c r="K9" s="44" t="s">
-        <v>614</v>
+        <v>604</v>
       </c>
       <c r="L9" s="44"/>
       <c r="M9" s="44"/>
@@ -3323,7 +3367,7 @@
       <c r="T9" s="44"/>
       <c r="U9" s="44"/>
       <c r="V9" s="44" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="W9" s="44"/>
     </row>
@@ -3335,7 +3379,7 @@
         <v>1</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D10" s="44" t="s">
         <v>209</v>
@@ -3349,10 +3393,10 @@
       <c r="I10" s="44"/>
       <c r="J10" s="44"/>
       <c r="K10" s="44" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="L10" s="44" t="s">
-        <v>585</v>
+        <v>575</v>
       </c>
       <c r="M10" s="44"/>
       <c r="N10" s="44"/>
@@ -3361,7 +3405,7 @@
       <c r="Q10" s="44"/>
       <c r="R10" s="44"/>
       <c r="S10" s="47" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="T10" s="44"/>
       <c r="U10" s="44"/>
@@ -3376,7 +3420,7 @@
         <v>0</v>
       </c>
       <c r="C11" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D11" s="44" t="s">
         <v>209</v>
@@ -3390,10 +3434,10 @@
       <c r="I11" s="44"/>
       <c r="J11" s="44"/>
       <c r="K11" s="44" t="s">
-        <v>573</v>
+        <v>563</v>
       </c>
       <c r="L11" s="44" t="s">
-        <v>574</v>
+        <v>564</v>
       </c>
       <c r="M11" s="44"/>
       <c r="N11" s="44"/>
@@ -3417,7 +3461,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D12" s="44" t="s">
         <v>209</v>
@@ -3431,10 +3475,10 @@
       <c r="I12" s="44"/>
       <c r="J12" s="44"/>
       <c r="K12" s="44" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="L12" s="44" t="s">
-        <v>617</v>
+        <v>607</v>
       </c>
       <c r="M12" s="44"/>
       <c r="N12" s="44" t="s">
@@ -3462,7 +3506,7 @@
         <v>0</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D13" s="44" t="s">
         <v>209</v>
@@ -3476,10 +3520,10 @@
       <c r="I13" s="44"/>
       <c r="J13" s="44"/>
       <c r="K13" s="44" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
       <c r="L13" s="44" t="s">
-        <v>619</v>
+        <v>609</v>
       </c>
       <c r="M13" s="44"/>
       <c r="N13" s="44" t="s">
@@ -3507,7 +3551,7 @@
         <v>0</v>
       </c>
       <c r="C14" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D14" s="44" t="s">
         <v>209</v>
@@ -3558,10 +3602,10 @@
       <c r="I15" s="44"/>
       <c r="J15" s="44"/>
       <c r="K15" s="44" t="s">
-        <v>620</v>
+        <v>610</v>
       </c>
       <c r="L15" s="44" t="s">
-        <v>621</v>
+        <v>611</v>
       </c>
       <c r="M15" s="44"/>
       <c r="N15" s="44" t="s">
@@ -3589,7 +3633,7 @@
         <v>0</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
       <c r="D16" s="44" t="s">
         <v>12</v>
@@ -3603,7 +3647,7 @@
       <c r="I16" s="44"/>
       <c r="J16" s="44"/>
       <c r="K16" s="44" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="L16" s="44"/>
       <c r="M16" s="44"/>
@@ -3630,7 +3674,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D17" s="44" t="s">
         <v>209</v>
@@ -3644,7 +3688,7 @@
       <c r="I17" s="44"/>
       <c r="J17" s="44"/>
       <c r="K17" s="44" t="s">
-        <v>623</v>
+        <v>613</v>
       </c>
       <c r="L17" s="44"/>
       <c r="M17" s="44"/>
@@ -3679,7 +3723,7 @@
         <v>5</v>
       </c>
       <c r="G18" s="44" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="H18" s="44" t="s">
         <v>12</v>
@@ -3689,7 +3733,7 @@
       </c>
       <c r="J18" s="44"/>
       <c r="K18" s="44" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
       <c r="L18" s="44"/>
       <c r="M18" s="44"/>
@@ -3706,10 +3750,10 @@
       <c r="T18" s="44"/>
       <c r="U18" s="44"/>
       <c r="V18" s="44" t="s">
-        <v>626</v>
+        <v>616</v>
       </c>
       <c r="W18" s="44" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
     </row>
     <row r="19" spans="1:23">
@@ -3720,7 +3764,7 @@
         <v>0</v>
       </c>
       <c r="C19" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D19" s="44" t="s">
         <v>209</v>
@@ -3734,7 +3778,7 @@
       <c r="I19" s="44"/>
       <c r="J19" s="44"/>
       <c r="K19" s="44" t="s">
-        <v>629</v>
+        <v>619</v>
       </c>
       <c r="L19" s="44"/>
       <c r="M19" s="44"/>
@@ -3751,7 +3795,7 @@
       <c r="T19" s="44"/>
       <c r="U19" s="44"/>
       <c r="V19" s="44" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="W19" s="44"/>
     </row>
@@ -3763,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="C20" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D20" s="44" t="s">
         <v>209</v>
@@ -3777,7 +3821,7 @@
       <c r="I20" s="44"/>
       <c r="J20" s="44"/>
       <c r="K20" s="44" t="s">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="L20" s="44"/>
       <c r="M20" s="44"/>
@@ -3804,7 +3848,7 @@
         <v>0</v>
       </c>
       <c r="C21" s="47" t="s">
-        <v>631</v>
+        <v>621</v>
       </c>
       <c r="D21" s="44" t="s">
         <v>12</v>
@@ -3818,15 +3862,15 @@
       <c r="I21" s="44"/>
       <c r="J21" s="44"/>
       <c r="K21" s="44" t="s">
-        <v>632</v>
+        <v>622</v>
       </c>
       <c r="L21" s="44"/>
       <c r="M21" s="44"/>
       <c r="N21" s="44" t="s">
-        <v>633</v>
+        <v>623</v>
       </c>
       <c r="O21" s="44" t="s">
-        <v>634</v>
+        <v>624</v>
       </c>
       <c r="P21" s="44"/>
       <c r="Q21" s="44"/>
@@ -3845,7 +3889,7 @@
         <v>1</v>
       </c>
       <c r="C22" s="47" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D22" s="44" t="s">
         <v>34</v>
@@ -3867,7 +3911,7 @@
       </c>
       <c r="J22" s="44"/>
       <c r="K22" s="44" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="L22" s="44"/>
       <c r="M22" s="44"/>
@@ -3963,14 +4007,14 @@
         <v>2</v>
       </c>
       <c r="D2" s="47" t="s">
-        <v>591</v>
+        <v>581</v>
       </c>
       <c r="E2" s="47" t="s">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="F2" s="44"/>
       <c r="G2" s="47" t="s">
-        <v>588</v>
+        <v>578</v>
       </c>
       <c r="H2" s="44" t="s">
         <v>12</v>
@@ -3994,7 +4038,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="47" t="s">
-        <v>592</v>
+        <v>582</v>
       </c>
       <c r="E3" s="47" t="s">
         <v>264</v>
@@ -4003,7 +4047,7 @@
         <v>149</v>
       </c>
       <c r="G3" s="47" t="s">
-        <v>588</v>
+        <v>578</v>
       </c>
       <c r="H3" s="44" t="s">
         <v>12</v>
@@ -4029,7 +4073,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="47" t="s">
-        <v>593</v>
+        <v>583</v>
       </c>
       <c r="E4" s="44"/>
       <c r="F4" s="44" t="s">
@@ -4045,7 +4089,7 @@
         <v>13</v>
       </c>
       <c r="J4" s="47" t="s">
-        <v>589</v>
+        <v>579</v>
       </c>
       <c r="K4" s="44" t="s">
         <v>13</v>
@@ -4130,7 +4174,7 @@
       <c r="G2" s="44"/>
       <c r="H2" s="44"/>
       <c r="I2" s="44" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="J2" s="44"/>
       <c r="K2" s="44"/>
@@ -4149,7 +4193,7 @@
       <c r="G3" s="44"/>
       <c r="H3" s="44"/>
       <c r="I3" s="44" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="J3" s="44"/>
       <c r="K3" s="44"/>
@@ -4168,7 +4212,7 @@
       <c r="G4" s="44"/>
       <c r="H4" s="44"/>
       <c r="I4" s="44" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="J4" s="44"/>
       <c r="K4" s="44"/>
@@ -4190,7 +4234,7 @@
         <v>2</v>
       </c>
       <c r="F5" s="47" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="G5" s="44" t="s">
         <v>209</v>
@@ -4199,13 +4243,13 @@
         <v>12</v>
       </c>
       <c r="I5" s="44" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="J5" s="44" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -4225,7 +4269,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="47" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="G6" s="44" t="s">
         <v>209</v>
@@ -4234,10 +4278,10 @@
         <v>12</v>
       </c>
       <c r="I6" s="44" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="J6" s="44" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="K6" s="44"/>
     </row>
@@ -4305,7 +4349,7 @@
         <v>149</v>
       </c>
       <c r="D3" s="44" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="E3" s="44">
         <v>1</v>
@@ -4322,7 +4366,7 @@
         <v>149</v>
       </c>
       <c r="D4" s="44" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="E4" s="44">
         <v>1</v>
@@ -4330,7 +4374,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="37" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B5" s="37"/>
       <c r="C5" s="37" t="s">
@@ -4341,7 +4385,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="37" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B6" s="37"/>
       <c r="C6" s="37" t="s">
@@ -4354,7 +4398,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="37" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="B7" s="37"/>
       <c r="C7" s="37" t="s">
@@ -4517,16 +4561,16 @@
         <v>45</v>
       </c>
       <c r="J2" s="44" t="s">
-        <v>605</v>
+        <v>595</v>
       </c>
       <c r="K2" s="44" t="s">
-        <v>606</v>
+        <v>596</v>
       </c>
       <c r="L2" s="44" t="s">
         <v>207</v>
       </c>
       <c r="M2" s="44" t="s">
-        <v>607</v>
+        <v>597</v>
       </c>
       <c r="N2" s="44" t="s">
         <v>208</v>
@@ -4535,13 +4579,13 @@
         <v>12</v>
       </c>
       <c r="P2" s="44" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="Q2" s="44" t="s">
         <v>62</v>
       </c>
       <c r="R2" s="44" t="s">
-        <v>609</v>
+        <v>599</v>
       </c>
       <c r="S2" s="44" t="s">
         <v>12</v>
@@ -4587,16 +4631,16 @@
         <v>45</v>
       </c>
       <c r="J3" s="44" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="L3" s="44" t="s">
         <v>207</v>
       </c>
       <c r="M3" s="44" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="N3" s="44" t="s">
         <v>208</v>
@@ -4605,13 +4649,13 @@
         <v>12</v>
       </c>
       <c r="P3" s="44" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="Q3" s="44" t="s">
         <v>239</v>
       </c>
       <c r="R3" s="44" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="S3" s="44" t="s">
         <v>12</v>
@@ -4652,7 +4696,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="44" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D4" s="44" t="s">
         <v>209</v>
@@ -4665,16 +4709,16 @@
       <c r="H4" s="44"/>
       <c r="I4" s="44"/>
       <c r="J4" s="44" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="K4" s="44" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="L4" s="44" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="M4" s="44" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="N4" s="44" t="s">
         <v>209</v>
@@ -4704,7 +4748,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="44" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D5" s="44" t="s">
         <v>209</v>
@@ -4717,16 +4761,16 @@
       <c r="H5" s="44"/>
       <c r="I5" s="44"/>
       <c r="J5" s="44" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="M5" s="44" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="N5" s="44" t="s">
         <v>209</v>
@@ -4777,16 +4821,16 @@
         <v>45</v>
       </c>
       <c r="J6" s="44" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="K6" s="44" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="L6" s="44" t="s">
         <v>207</v>
       </c>
       <c r="M6" s="44" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="N6" s="44" t="s">
         <v>208</v>
@@ -4850,7 +4894,7 @@
         <v>69</v>
       </c>
       <c r="B2" s="44" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C2" s="44">
         <v>0</v>
@@ -4867,7 +4911,7 @@
         <v>70</v>
       </c>
       <c r="B3" s="44" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C3" s="44">
         <v>0</v>
@@ -4884,7 +4928,7 @@
         <v>71</v>
       </c>
       <c r="B4" s="44" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C4" s="44">
         <v>0</v>
@@ -5051,7 +5095,7 @@
         <v>282</v>
       </c>
       <c r="D9" s="44" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="E9" s="44"/>
     </row>
@@ -5187,7 +5231,7 @@
         <v>111</v>
       </c>
       <c r="B3" s="41" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
   </sheetData>
@@ -5235,7 +5279,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="44" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="D2" s="44" t="s">
         <v>209</v>
@@ -5498,7 +5542,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="44" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D2" s="44" t="s">
         <v>209</v>
@@ -5510,7 +5554,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="44" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="H2" s="44" t="s">
         <v>209</v>
@@ -5522,7 +5566,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="44" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="L2" s="44" t="s">
         <v>209</v>
@@ -5534,7 +5578,7 @@
         <v>0</v>
       </c>
       <c r="O2" s="44" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="P2" s="44" t="s">
         <v>209</v>
@@ -5546,7 +5590,7 @@
         <v>1</v>
       </c>
       <c r="S2" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="T2" s="44" t="s">
         <v>209</v>
@@ -5570,7 +5614,7 @@
         <v>0</v>
       </c>
       <c r="AA2" s="44" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="AB2" s="44" t="s">
         <v>45</v>
@@ -5582,7 +5626,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="44" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="AF2" s="44" t="s">
         <v>45</v>
@@ -5599,7 +5643,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D3" s="44"/>
       <c r="E3" s="44"/>
@@ -5640,7 +5684,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="44" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D4" s="44" t="s">
         <v>209</v>
@@ -5812,7 +5856,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D2" s="44" t="s">
         <v>209</v>
@@ -5828,16 +5872,16 @@
       <c r="I2" s="44"/>
       <c r="J2" s="44"/>
       <c r="K2" s="44" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>209</v>
@@ -5868,7 +5912,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D3" s="44" t="s">
         <v>209</v>
@@ -5880,7 +5924,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="44" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="H3" s="44" t="s">
         <v>209</v>
@@ -5892,7 +5936,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>312</v>
@@ -5956,7 +6000,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="47" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D4" s="44" t="s">
         <v>209</v>
@@ -5968,7 +6012,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="44" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="H4" s="44" t="s">
         <v>209</v>
@@ -6008,7 +6052,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D5" s="44" t="s">
         <v>209</v>
@@ -6020,7 +6064,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="44" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="H5" s="44" t="s">
         <v>209</v>
@@ -6032,16 +6076,16 @@
         <v>2</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>209</v>
@@ -6050,7 +6094,7 @@
         <v>12</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="R5" s="15" t="s">
         <v>44</v>
@@ -6100,7 +6144,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D6" s="44" t="s">
         <v>209</v>
@@ -6144,7 +6188,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D7" s="44" t="s">
         <v>209</v>
@@ -6188,7 +6232,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D8" s="44" t="s">
         <v>209</v>
@@ -6232,7 +6276,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D9" s="44" t="s">
         <v>209</v>
@@ -6248,16 +6292,16 @@
       <c r="I9" s="44"/>
       <c r="J9" s="44"/>
       <c r="K9" s="44" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>209</v>
@@ -6322,10 +6366,10 @@
         <v>127</v>
       </c>
       <c r="B2" s="44" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C2" s="44" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="D2" s="44" t="s">
         <v>128</v>
@@ -6339,7 +6383,7 @@
         <v>129</v>
       </c>
       <c r="B3" s="44" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C3" s="44" t="s">
         <v>209</v>
@@ -6411,7 +6455,7 @@
         <v>137</v>
       </c>
       <c r="B2" s="44" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="C2" s="44" t="s">
         <v>138</v>
@@ -6423,7 +6467,7 @@
         <v>140</v>
       </c>
       <c r="F2" s="44" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>
@@ -6541,7 +6585,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D2" s="44" t="s">
         <v>209</v>
@@ -6569,16 +6613,16 @@
       <c r="U2" s="44"/>
       <c r="V2" s="44"/>
       <c r="W2" s="44" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="X2" s="44" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="Y2" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="Z2" s="44" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="AA2" s="44" t="s">
         <v>209</v>
@@ -6587,7 +6631,7 @@
         <v>12</v>
       </c>
       <c r="AC2" s="44" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -6634,7 +6678,7 @@
         <v>4</v>
       </c>
       <c r="O3" s="44" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="P3" s="44" t="s">
         <v>12</v>
@@ -6646,7 +6690,7 @@
         <v>5</v>
       </c>
       <c r="S3" s="44" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="T3" s="44" t="s">
         <v>34</v>
@@ -6677,7 +6721,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D4" s="44" t="s">
         <v>209</v>
@@ -6705,16 +6749,16 @@
       <c r="U4" s="44"/>
       <c r="V4" s="44"/>
       <c r="W4" s="44" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="X4" s="44" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="Y4" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="Z4" s="44" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="AA4" s="44" t="s">
         <v>209</v>
@@ -6723,7 +6767,7 @@
         <v>12</v>
       </c>
       <c r="AC4" s="44" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
     </row>
   </sheetData>
@@ -6849,7 +6893,7 @@
         <v>12</v>
       </c>
       <c r="I5" s="44" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -6981,16 +7025,16 @@
       <c r="I2" s="44"/>
       <c r="J2" s="44"/>
       <c r="K2" s="44" t="s">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="L2" s="44" t="s">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="M2" s="44" t="s">
         <v>18</v>
       </c>
       <c r="N2" s="44" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="O2" s="44" t="s">
         <v>12</v>
@@ -6999,7 +7043,7 @@
         <v>13</v>
       </c>
       <c r="Q2" s="44" t="s">
-        <v>595</v>
+        <v>585</v>
       </c>
       <c r="R2" s="44"/>
     </row>
@@ -7027,16 +7071,16 @@
       <c r="I3" s="44"/>
       <c r="J3" s="44"/>
       <c r="K3" s="44" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="L3" s="44" t="s">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="M3" s="44" t="s">
         <v>18</v>
       </c>
       <c r="N3" s="44" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="O3" s="44" t="s">
         <v>12</v>
@@ -7045,10 +7089,10 @@
         <v>13</v>
       </c>
       <c r="Q3" s="44" t="s">
-        <v>602</v>
+        <v>592</v>
       </c>
       <c r="R3" s="44" t="s">
-        <v>603</v>
+        <v>593</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -7083,16 +7127,16 @@
         <v>2</v>
       </c>
       <c r="K4" s="44" t="s">
-        <v>596</v>
+        <v>586</v>
       </c>
       <c r="L4" s="44" t="s">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="M4" s="44" t="s">
         <v>18</v>
       </c>
       <c r="N4" s="44" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="O4" s="44" t="s">
         <v>12</v>
@@ -7101,7 +7145,7 @@
         <v>13</v>
       </c>
       <c r="Q4" s="44" t="s">
-        <v>604</v>
+        <v>594</v>
       </c>
       <c r="R4" s="44"/>
     </row>
@@ -7129,16 +7173,16 @@
       <c r="I5" s="44"/>
       <c r="J5" s="44"/>
       <c r="K5" s="44" t="s">
-        <v>597</v>
+        <v>587</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="M5" s="44" t="s">
         <v>18</v>
       </c>
       <c r="N5" s="44" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="O5" s="44" t="s">
         <v>12</v>
@@ -7147,7 +7191,7 @@
         <v>13</v>
       </c>
       <c r="Q5" s="44" t="s">
-        <v>598</v>
+        <v>588</v>
       </c>
       <c r="R5" s="44"/>
     </row>
@@ -7175,16 +7219,16 @@
       <c r="I6" s="44"/>
       <c r="J6" s="44"/>
       <c r="K6" s="44" t="s">
-        <v>599</v>
+        <v>589</v>
       </c>
       <c r="L6" s="44" t="s">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="M6" s="44" t="s">
         <v>18</v>
       </c>
       <c r="N6" s="44" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="O6" s="44" t="s">
         <v>12</v>
@@ -7193,7 +7237,7 @@
         <v>13</v>
       </c>
       <c r="Q6" s="44" t="s">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="R6" s="44"/>
     </row>
@@ -7328,16 +7372,16 @@
         <v>163</v>
       </c>
       <c r="J2" s="56" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="K2" s="44" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>215</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>12</v>
@@ -7346,13 +7390,13 @@
         <v>216</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>217</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="S2" s="3" t="s">
         <v>216</v>
@@ -7361,7 +7405,7 @@
         <v>163</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
     </row>
     <row r="3" spans="1:21">
@@ -7384,7 +7428,7 @@
         <v>2</v>
       </c>
       <c r="G3" s="44" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="H3" s="44" t="s">
         <v>216</v>
@@ -7393,16 +7437,16 @@
         <v>163</v>
       </c>
       <c r="J3" s="56" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>215</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>12</v>
@@ -7411,13 +7455,13 @@
         <v>216</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="S3" s="3" t="s">
         <v>216</v>
@@ -7426,7 +7470,7 @@
         <v>163</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
     </row>
     <row r="4" spans="1:21">
@@ -7631,7 +7675,7 @@
         <v>181</v>
       </c>
       <c r="B3" s="47" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -7741,40 +7785,40 @@
         <v>266</v>
       </c>
       <c r="C1" s="42" t="s">
+        <v>458</v>
+      </c>
+      <c r="D1" s="42" t="s">
+        <v>459</v>
+      </c>
+      <c r="E1" s="42" t="s">
+        <v>460</v>
+      </c>
+      <c r="F1" s="42" t="s">
+        <v>461</v>
+      </c>
+      <c r="G1" s="63" t="s">
+        <v>462</v>
+      </c>
+      <c r="H1" s="63" t="s">
         <v>463</v>
       </c>
-      <c r="D1" s="42" t="s">
-        <v>464</v>
-      </c>
-      <c r="E1" s="42" t="s">
-        <v>465</v>
-      </c>
-      <c r="F1" s="42" t="s">
-        <v>466</v>
-      </c>
-      <c r="G1" s="63" t="s">
-        <v>467</v>
-      </c>
-      <c r="H1" s="63" t="s">
-        <v>468</v>
-      </c>
       <c r="I1" s="63" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="J1" s="63" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="K1" s="42" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="L1" s="42" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="M1" s="42" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="N1" s="42" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -7785,40 +7829,40 @@
         <v>149</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="D2" s="32" t="s">
         <v>121</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="F2" s="44" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="G2" s="44" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="H2" s="44" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="I2" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="J2" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="K2" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="L2" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="M2" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="N2" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -7829,40 +7873,40 @@
         <v>149</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="D3" s="32" t="s">
         <v>121</v>
       </c>
       <c r="E3" s="32" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="F3" s="44" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="G3" s="44" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="H3" s="44" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="I3" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="J3" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="L3" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="M3" s="44" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="N3" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -7873,40 +7917,40 @@
         <v>149</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="D4" s="32" t="s">
         <v>121</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="F4" s="44" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="G4" s="44" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="H4" s="44" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="I4" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="J4" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="K4" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="L4" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="M4" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="N4" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -7917,7 +7961,7 @@
         <v>149</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="D5" s="32" t="s">
         <v>121</v>
@@ -7926,31 +7970,31 @@
         <v>121</v>
       </c>
       <c r="F5" s="44" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="G5" s="44" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="H5" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="I5" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="J5" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="M5" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="N5" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -7961,7 +8005,7 @@
         <v>149</v>
       </c>
       <c r="C6" s="44" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="D6" s="44" t="s">
         <v>121</v>
@@ -7970,31 +8014,31 @@
         <v>121</v>
       </c>
       <c r="F6" s="44" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="G6" s="44" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="H6" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="I6" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="J6" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="K6" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="L6" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="M6" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="N6" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -8005,7 +8049,7 @@
         <v>149</v>
       </c>
       <c r="C7" s="44" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="D7" s="44" t="s">
         <v>121</v>
@@ -8014,31 +8058,31 @@
         <v>121</v>
       </c>
       <c r="F7" s="44" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="G7" s="44" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="H7" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="I7" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="J7" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="K7" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="L7" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="M7" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="N7" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -8049,40 +8093,40 @@
         <v>149</v>
       </c>
       <c r="C8" s="44" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="D8" s="44" t="s">
         <v>121</v>
       </c>
       <c r="E8" s="44" t="s">
+        <v>468</v>
+      </c>
+      <c r="F8" s="44" t="s">
+        <v>470</v>
+      </c>
+      <c r="G8" s="44" t="s">
+        <v>334</v>
+      </c>
+      <c r="H8" s="44" t="s">
+        <v>474</v>
+      </c>
+      <c r="I8" s="44" t="s">
+        <v>475</v>
+      </c>
+      <c r="J8" s="44" t="s">
         <v>473</v>
       </c>
-      <c r="F8" s="44" t="s">
-        <v>475</v>
-      </c>
-      <c r="G8" s="44" t="s">
-        <v>338</v>
-      </c>
-      <c r="H8" s="44" t="s">
-        <v>479</v>
-      </c>
-      <c r="I8" s="44" t="s">
-        <v>480</v>
-      </c>
-      <c r="J8" s="44" t="s">
-        <v>478</v>
-      </c>
       <c r="K8" s="44" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="L8" s="44" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="M8" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="N8" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -8093,40 +8137,40 @@
         <v>149</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="D9" s="32" t="s">
         <v>121</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="F9" s="44" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="G9" s="44" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="H9" s="44" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="I9" s="44" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="J9" s="44" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="K9" s="44" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="L9" s="44" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="M9" s="44" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="N9" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -8137,40 +8181,40 @@
         <v>149</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="D10" s="44" t="s">
         <v>121</v>
       </c>
       <c r="E10" s="32" t="s">
+        <v>484</v>
+      </c>
+      <c r="F10" s="44" t="s">
+        <v>486</v>
+      </c>
+      <c r="G10" s="44" t="s">
+        <v>334</v>
+      </c>
+      <c r="H10" s="44" t="s">
+        <v>487</v>
+      </c>
+      <c r="I10" s="44" t="s">
+        <v>488</v>
+      </c>
+      <c r="J10" s="44" t="s">
         <v>489</v>
       </c>
-      <c r="F10" s="44" t="s">
-        <v>491</v>
-      </c>
-      <c r="G10" s="44" t="s">
-        <v>338</v>
-      </c>
-      <c r="H10" s="44" t="s">
-        <v>492</v>
-      </c>
-      <c r="I10" s="44" t="s">
-        <v>493</v>
-      </c>
-      <c r="J10" s="44" t="s">
-        <v>494</v>
-      </c>
       <c r="K10" s="44" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="L10" s="44" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="M10" s="44" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="N10" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -8181,40 +8225,40 @@
         <v>149</v>
       </c>
       <c r="C11" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="D11" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="F11" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="G11" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="H11" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="I11" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="J11" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="K11" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="L11" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="M11" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="N11" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -8225,40 +8269,40 @@
         <v>149</v>
       </c>
       <c r="C12" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="D12" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="F12" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="G12" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="H12" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="I12" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="J12" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="K12" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="L12" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="M12" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="N12" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -8269,40 +8313,40 @@
         <v>149</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="F13" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="G13" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="H13" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="I13" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="J13" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="K13" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="L13" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="M13" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="N13" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -8313,40 +8357,40 @@
         <v>149</v>
       </c>
       <c r="C14" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="E14" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="F14" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="G14" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="H14" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="I14" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="J14" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="K14" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="L14" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="M14" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="N14" s="44" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -8357,40 +8401,40 @@
         <v>149</v>
       </c>
       <c r="C15" s="44" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="D15" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="E15" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="F15" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="G15" s="44" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="H15" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="I15" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="J15" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="K15" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="L15" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="M15" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="N15" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -8401,40 +8445,40 @@
         <v>149</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="D16" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="F16" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="G16" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="H16" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="I16" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="J16" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="K16" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="L16" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="M16" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="N16" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -8445,45 +8489,45 @@
         <v>149</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="D17" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="F17" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="G17" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="H17" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="I17" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="J17" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="K17" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="L17" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="M17" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="N17" s="44" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="62" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
     </row>
   </sheetData>
@@ -8547,7 +8591,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="44" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D2" s="44" t="s">
         <v>209</v>
@@ -8562,10 +8606,10 @@
         <v>50</v>
       </c>
       <c r="H2" s="44" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="I2" s="44" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -8576,7 +8620,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D3" s="44" t="s">
         <v>209</v>
@@ -8591,10 +8635,10 @@
         <v>50</v>
       </c>
       <c r="H3" s="44" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="I3" s="44" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -8671,7 +8715,7 @@
         <v>81</v>
       </c>
       <c r="B2" s="44" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C2" s="44" t="s">
         <v>209</v>
@@ -8696,7 +8740,7 @@
         <v>82</v>
       </c>
       <c r="B3" s="44" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C3" s="44" t="s">
         <v>209</v>
@@ -8733,7 +8777,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="44" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="G4" s="44" t="s">
         <v>12</v>
@@ -8776,16 +8820,16 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="35" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="C6" s="35" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="44" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E6" s="35">
         <v>2</v>
@@ -8795,7 +8839,7 @@
       <c r="H6" s="44"/>
       <c r="I6" s="44"/>
       <c r="J6" s="44" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="K6" s="44"/>
       <c r="L6" s="44"/>
@@ -8811,140 +8855,244 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="29" width="17.90625"/>
-    <col min="2" max="2" customWidth="true" style="29" width="11.81640625"/>
-    <col min="3" max="3" customWidth="true" style="29" width="13.0"/>
-    <col min="4" max="4" customWidth="true" style="29" width="16.54296875"/>
-    <col min="5" max="5" customWidth="true" style="29" width="15.81640625"/>
-    <col min="6" max="6" style="29" width="8.81640625"/>
-    <col min="7" max="7" customWidth="true" style="29" width="17.81640625"/>
-    <col min="8" max="8" customWidth="true" style="29" width="15.453125"/>
-    <col min="9" max="9" customWidth="true" style="29" width="11.54296875"/>
-    <col min="10" max="16384" style="29" width="8.81640625"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="9.54296875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="41" width="10.90625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="41" width="9.453125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="41" width="7.7265625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="41" width="10.90625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="41" width="9.453125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="41" width="7.7265625"/>
+    <col min="8" max="8" customWidth="true" style="29" width="13.0"/>
+    <col min="9" max="9" customWidth="true" style="29" width="16.54296875"/>
+    <col min="10" max="10" customWidth="true" style="29" width="15.81640625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="41" width="10.36328125"/>
+    <col min="12" max="12" customWidth="true" style="41" width="10.36328125"/>
+    <col min="13" max="13" style="29" width="8.81640625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="12.54296875"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="29" width="14.7265625"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="29" width="13.26953125"/>
+    <col min="17" max="17" customWidth="true" style="41" width="11.54296875"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="41" width="8.7265625"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="29" width="6.453125"/>
+    <col min="20" max="21" style="29" width="8.81640625"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="29" width="10.6328125"/>
+    <col min="23" max="16384" style="29" width="8.81640625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:22">
       <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="45" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="45" t="s">
+        <v>631</v>
+      </c>
+      <c r="D1" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="45" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="45" t="s">
+        <v>631</v>
+      </c>
+      <c r="G1" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="33" t="s">
+        <v>629</v>
+      </c>
+      <c r="I1" s="33" t="s">
+        <v>630</v>
+      </c>
+      <c r="J1" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="K1" s="45" t="s">
+        <v>632</v>
+      </c>
+      <c r="L1" s="45" t="s">
+        <v>633</v>
+      </c>
+      <c r="M1" s="65" t="s">
+        <v>74</v>
+      </c>
+      <c r="N1" s="66" t="s">
+        <v>634</v>
+      </c>
+      <c r="O1" s="66" t="s">
+        <v>635</v>
+      </c>
+      <c r="P1" s="66" t="s">
+        <v>636</v>
+      </c>
+      <c r="Q1" s="66" t="s">
+        <v>637</v>
+      </c>
+      <c r="R1" s="66" t="s">
+        <v>638</v>
+      </c>
+      <c r="S1" s="33" t="s">
         <v>314</v>
       </c>
-      <c r="C1" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="F1" s="33" t="s">
-        <v>74</v>
-      </c>
-      <c r="G1" s="33" t="s">
+      <c r="T1" s="33" t="s">
         <v>315</v>
       </c>
-      <c r="H1" s="33" t="s">
+      <c r="U1" s="65" t="s">
+        <v>639</v>
+      </c>
+      <c r="V1" s="65" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22">
+      <c r="A2" s="32" t="s">
         <v>316</v>
       </c>
-      <c r="I1" s="33" t="s">
+      <c r="B2" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="47" t="s">
+        <v>177</v>
+      </c>
+      <c r="E2" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="H2" s="32">
+        <v>0</v>
+      </c>
+      <c r="I2" s="32">
+        <v>1</v>
+      </c>
+      <c r="J2" s="32">
+        <v>0</v>
+      </c>
+      <c r="K2" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" s="32" t="s">
+        <v>646</v>
+      </c>
+      <c r="N2" s="32">
+        <v>2</v>
+      </c>
+      <c r="O2" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="P2" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="R2" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="S2" s="32"/>
+      <c r="T2" s="32"/>
+      <c r="U2" s="44" t="s">
+        <v>643</v>
+      </c>
+      <c r="V2" s="44" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22">
+      <c r="A3" s="32" t="s">
         <v>317</v>
       </c>
-      <c r="J1" s="33" t="s">
+      <c r="B3" s="44"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="32">
+        <v>0</v>
+      </c>
+      <c r="I3" s="32">
+        <v>1</v>
+      </c>
+      <c r="J3" s="32">
+        <v>0</v>
+      </c>
+      <c r="K3" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="M3" s="32" t="s">
+        <v>627</v>
+      </c>
+      <c r="N3" s="32"/>
+      <c r="O3" s="32"/>
+      <c r="P3" s="32"/>
+      <c r="Q3" s="44"/>
+      <c r="R3" s="44"/>
+      <c r="S3" s="34" t="s">
         <v>318</v>
       </c>
-      <c r="K1" s="33" t="s">
+      <c r="T3" s="32" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="32" t="s">
+      <c r="U3" s="44"/>
+      <c r="V3" s="44"/>
+    </row>
+    <row r="4" spans="1:22">
+      <c r="A4" s="32" t="s">
         <v>320</v>
       </c>
-      <c r="B2" s="32" t="s">
-        <v>149</v>
-      </c>
-      <c r="C2" s="32">
-        <v>1</v>
-      </c>
-      <c r="D2" s="32">
-        <v>1</v>
-      </c>
-      <c r="E2" s="32">
-        <v>1</v>
-      </c>
-      <c r="F2" s="32" t="s">
-        <v>560</v>
-      </c>
-      <c r="G2" s="32">
-        <v>2</v>
-      </c>
-      <c r="H2" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="I2" s="34" t="s">
-        <v>177</v>
-      </c>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="32" t="s">
-        <v>321</v>
-      </c>
-      <c r="B3" s="32" t="s">
-        <v>149</v>
-      </c>
-      <c r="C3" s="32">
-        <v>1</v>
-      </c>
-      <c r="D3" s="32">
-        <v>1</v>
-      </c>
-      <c r="E3" s="32">
-        <v>1</v>
-      </c>
-      <c r="F3" s="32" t="s">
-        <v>561</v>
-      </c>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="34" t="s">
-        <v>322</v>
-      </c>
-      <c r="K3" s="32" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="32" t="s">
-        <v>324</v>
-      </c>
-      <c r="B4" s="32" t="s">
-        <v>149</v>
-      </c>
-      <c r="C4" s="32">
-        <v>1</v>
-      </c>
-      <c r="D4" s="32">
-        <v>1</v>
-      </c>
-      <c r="E4" s="32">
-        <v>1</v>
-      </c>
-      <c r="F4" s="32" t="s">
-        <v>562</v>
-      </c>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="32">
+        <v>0</v>
+      </c>
+      <c r="I4" s="32">
+        <v>1</v>
+      </c>
+      <c r="J4" s="32">
+        <v>0</v>
+      </c>
+      <c r="K4" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="L4" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="M4" s="32" t="s">
+        <v>628</v>
+      </c>
+      <c r="N4" s="32"/>
+      <c r="O4" s="32"/>
+      <c r="P4" s="32"/>
+      <c r="Q4" s="44"/>
+      <c r="R4" s="44"/>
+      <c r="S4" s="32"/>
+      <c r="T4" s="32"/>
+      <c r="U4" s="44"/>
+      <c r="V4" s="44"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9017,7 +9165,7 @@
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="44" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="B2" s="47" t="s">
         <v>32</v>
@@ -9040,10 +9188,10 @@
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="44" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B3" s="47" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C3" s="44" t="s">
         <v>12</v>
@@ -9133,10 +9281,10 @@
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="44" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="B2" s="47" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C2" s="44" t="s">
         <v>12</v>
@@ -9156,10 +9304,10 @@
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="48" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="B3" s="47" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C3" s="44" t="s">
         <v>12</v>
@@ -9179,10 +9327,10 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="44" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B4" s="47" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C4" s="44" t="s">
         <v>34</v>
@@ -9247,7 +9395,7 @@
         <v>1</v>
       </c>
       <c r="F1" s="42" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="G1" s="42" t="s">
         <v>30</v>
@@ -9279,10 +9427,10 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="44" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="B2" s="47" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C2" s="44" t="s">
         <v>12</v>
@@ -9294,10 +9442,10 @@
         <v>2</v>
       </c>
       <c r="F2" s="44" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="G2" s="44" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="H2" s="44"/>
       <c r="I2" s="44"/>
@@ -9310,10 +9458,10 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="44" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B3" s="47" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C3" s="44" t="s">
         <v>12</v>
@@ -9325,10 +9473,10 @@
         <v>2</v>
       </c>
       <c r="F3" s="44" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="G3" s="44" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="H3" s="44"/>
       <c r="I3" s="44"/>
@@ -9341,10 +9489,10 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="44" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="B4" s="47" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C4" s="44" t="s">
         <v>12</v>
@@ -9356,10 +9504,10 @@
         <v>2</v>
       </c>
       <c r="F4" s="44" t="s">
+        <v>396</v>
+      </c>
+      <c r="G4" s="44" t="s">
         <v>400</v>
-      </c>
-      <c r="G4" s="44" t="s">
-        <v>404</v>
       </c>
       <c r="H4" s="44"/>
       <c r="I4" s="44"/>
@@ -9372,10 +9520,10 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="44" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B5" s="47" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C5" s="44" t="s">
         <v>12</v>
@@ -9387,10 +9535,10 @@
         <v>2</v>
       </c>
       <c r="F5" s="44" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="G5" s="44" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="H5" s="44"/>
       <c r="I5" s="44"/>
@@ -9449,10 +9597,10 @@
         <v>1</v>
       </c>
       <c r="F1" s="42" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="G1" s="42" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="H1" s="43" t="s">
         <v>74</v>
@@ -9461,23 +9609,23 @@
         <v>8</v>
       </c>
       <c r="J1" s="43" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="K1" s="43" t="s">
         <v>75</v>
       </c>
       <c r="L1" s="43" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="M1" s="43" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="N1" s="40"/>
       <c r="O1" s="46"/>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="44" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B2" s="47" t="s">
         <v>32</v>
@@ -9487,7 +9635,7 @@
       </c>
       <c r="D2" s="44"/>
       <c r="E2" s="44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="44"/>
       <c r="G2" s="44"/>
@@ -9500,7 +9648,7 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="44" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="B3" s="47" t="s">
         <v>32</v>
@@ -9510,7 +9658,7 @@
       </c>
       <c r="D3" s="44"/>
       <c r="E3" s="44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="44" t="s">
         <v>14</v>
@@ -9525,81 +9673,81 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="44" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="B4" s="47" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="C4" s="44" t="s">
         <v>12</v>
       </c>
       <c r="D4" s="44" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E4" s="44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="44" t="s">
         <v>14</v>
       </c>
       <c r="G4" s="44"/>
       <c r="H4" s="44" t="s">
-        <v>563</v>
+        <v>625</v>
       </c>
       <c r="I4" s="44" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="J4" s="44" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="K4" s="44"/>
       <c r="L4" s="44" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="M4" s="44" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="44" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="B5" s="47" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="C5" s="44" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="44" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E5" s="44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="44" t="s">
         <v>14</v>
       </c>
       <c r="G5" s="44"/>
       <c r="H5" s="44" t="s">
-        <v>564</v>
+        <v>626</v>
       </c>
       <c r="I5" s="44" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="J5" s="44" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="K5" s="44"/>
       <c r="L5" s="44" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="M5" s="44" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="44" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="B6" s="47" t="s">
         <v>32</v>
@@ -9609,7 +9757,7 @@
       </c>
       <c r="D6" s="44"/>
       <c r="E6" s="44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="44"/>
       <c r="G6" s="44"/>
@@ -9622,7 +9770,7 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="44" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="B7" s="47" t="s">
         <v>32</v>
@@ -9632,7 +9780,7 @@
       </c>
       <c r="D7" s="44"/>
       <c r="E7" s="44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="44"/>
       <c r="G7" s="44"/>
@@ -9645,7 +9793,7 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="44" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="B8" s="47" t="s">
         <v>32</v>
@@ -9655,7 +9803,7 @@
       </c>
       <c r="D8" s="44"/>
       <c r="E8" s="44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="44" t="s">
         <v>14</v>
@@ -9670,7 +9818,7 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="44" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="B9" s="47" t="s">
         <v>32</v>
@@ -9680,11 +9828,11 @@
       </c>
       <c r="D9" s="44"/>
       <c r="E9" s="44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="44"/>
       <c r="G9" s="47" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="H9" s="44"/>
       <c r="I9" s="44"/>
@@ -9695,7 +9843,7 @@
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="44" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="B10" s="47" t="s">
         <v>32</v>
@@ -9705,7 +9853,7 @@
       </c>
       <c r="D10" s="44"/>
       <c r="E10" s="44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="44"/>
       <c r="G10" s="44"/>
@@ -9752,10 +9900,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="44" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="B2" s="47" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="C2" s="44" t="s">
         <v>12</v>
@@ -9804,7 +9952,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="44" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="B2" s="47" t="s">
         <v>32</v>
@@ -9821,10 +9969,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="44" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="B3" s="47" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C3" s="44" t="s">
         <v>12</v>
@@ -9838,10 +9986,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="44" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="B4" s="47" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="C4" s="44" t="s">
         <v>12</v>
@@ -9878,30 +10026,30 @@
         <v>0</v>
       </c>
       <c r="B1" s="49" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="C1" s="49" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="D1" s="49" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="E1" s="49" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="44" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="B2" s="47" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C2" s="44" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="D2" s="44" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="E2" s="44" t="s">
         <v>12</v>
@@ -9909,16 +10057,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="44" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="B3" s="47" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C3" s="44" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="D3" s="44" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="E3" s="44" t="s">
         <v>12</v>
@@ -9926,23 +10074,23 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="44" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="B4" s="44"/>
       <c r="C4" s="44"/>
       <c r="D4" s="44" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="E4" s="44"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="44" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="B5" s="44"/>
       <c r="C5" s="44"/>
       <c r="D5" s="44" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="E5" s="44" t="s">
         <v>12</v>
@@ -9950,31 +10098,31 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="50" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="B6" s="47" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C6" s="44" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="D6" s="44" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="E6" s="44"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="51" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="B7" s="47" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C7" s="44" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="D7" s="44" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="E7" s="44" t="s">
         <v>12</v>
@@ -10033,7 +10181,7 @@
         <v>4</v>
       </c>
       <c r="H1" s="53" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="I1" s="53" t="s">
         <v>9</v>
@@ -10045,10 +10193,10 @@
         <v>210</v>
       </c>
       <c r="L1" s="42" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="M1" s="42" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="N1" s="42" t="s">
         <v>75</v>
@@ -10056,13 +10204,13 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="54" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="B2" s="44">
         <v>2</v>
       </c>
       <c r="C2" s="47" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D2" s="44" t="s">
         <v>12</v>
@@ -10074,7 +10222,7 @@
         <v>12</v>
       </c>
       <c r="G2" s="44" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="H2" s="44" t="s">
         <v>211</v>
@@ -10083,28 +10231,28 @@
         <v>212</v>
       </c>
       <c r="J2" s="44" t="s">
-        <v>565</v>
+        <v>555</v>
       </c>
       <c r="K2" s="44">
         <v>2</v>
       </c>
       <c r="L2" s="44" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="M2" s="44" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="N2" s="44"/>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="44" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="B3" s="44">
         <v>2</v>
       </c>
       <c r="C3" s="47" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D3" s="44" t="s">
         <v>12</v>
@@ -10122,13 +10270,13 @@
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="55" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="B4" s="44">
         <v>2</v>
       </c>
       <c r="C4" s="47" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D4" s="44" t="s">
         <v>12</v>
@@ -10140,16 +10288,16 @@
         <v>12</v>
       </c>
       <c r="G4" s="44" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="H4" s="44" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="I4" s="44" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="J4" s="44" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K4" s="44"/>
       <c r="L4" s="44"/>
@@ -10160,13 +10308,13 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="44" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="B5" s="44">
         <v>2</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="D5" s="44" t="s">
         <v>12</v>
@@ -10178,16 +10326,16 @@
         <v>12</v>
       </c>
       <c r="G5" s="44" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="H5" s="44" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="I5" s="44" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="J5" s="44" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K5" s="44"/>
       <c r="L5" s="44"/>
@@ -10241,7 +10389,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D2" s="44" t="s">
         <v>209</v>
@@ -10258,7 +10406,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="44" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D3" s="44" t="s">
         <v>209</v>
@@ -10312,13 +10460,13 @@
         <v>0</v>
       </c>
       <c r="C2" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D2" s="44" t="s">
         <v>209</v>
       </c>
       <c r="E2" s="44" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -10329,13 +10477,13 @@
         <v>0</v>
       </c>
       <c r="C3" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D3" s="44" t="s">
         <v>209</v>
       </c>
       <c r="E3" s="44" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -10346,13 +10494,13 @@
         <v>0</v>
       </c>
       <c r="C4" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D4" s="44" t="s">
         <v>209</v>
       </c>
       <c r="E4" s="44" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -10363,13 +10511,13 @@
         <v>0</v>
       </c>
       <c r="C5" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D5" s="44" t="s">
         <v>209</v>
       </c>
       <c r="E5" s="44" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -10380,13 +10528,13 @@
         <v>0</v>
       </c>
       <c r="C6" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D6" s="44" t="s">
         <v>209</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -10483,16 +10631,16 @@
         <v>9</v>
       </c>
       <c r="S1" s="30" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="T1" s="30" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="U1" s="30" t="s">
         <v>30</v>
       </c>
       <c r="V1" s="30" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
     </row>
     <row r="2" spans="1:22">
@@ -10503,7 +10651,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="44" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D2" s="44" t="s">
         <v>209</v>
@@ -10518,7 +10666,7 @@
         <v>15</v>
       </c>
       <c r="H2" s="32" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="I2" s="32" t="s">
         <v>211</v>
@@ -10535,14 +10683,14 @@
       <c r="M2" s="32"/>
       <c r="N2" s="32"/>
       <c r="O2" s="32" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="P2" s="32"/>
       <c r="Q2" s="32" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="R2" s="32" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="S2" s="32"/>
       <c r="T2" s="32"/>
@@ -10557,7 +10705,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="44" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D3" s="44" t="s">
         <v>209</v>
@@ -10595,7 +10743,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="47" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D4" s="44" t="s">
         <v>209</v>
@@ -10627,7 +10775,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D5" s="44" t="s">
         <v>209</v>
@@ -10659,13 +10807,13 @@
     </row>
     <row r="6" spans="1:22" s="29" customFormat="1">
       <c r="A6" s="32" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="B6" s="44">
         <v>0</v>
       </c>
       <c r="C6" s="47" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D6" s="44" t="s">
         <v>209</v>
@@ -10680,13 +10828,13 @@
         <v>15</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="I6" s="32" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="J6" s="32" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="K6" s="32"/>
       <c r="L6" s="32"/>
@@ -10697,23 +10845,23 @@
       <c r="Q6" s="32"/>
       <c r="R6" s="32"/>
       <c r="S6" s="32" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="T6" s="32" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="U6" s="32"/>
       <c r="V6" s="32"/>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="39" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B7" s="44">
         <v>0</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D7" s="44" t="s">
         <v>209</v>
@@ -10728,13 +10876,13 @@
         <v>19</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="I7" s="32" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="J7" s="32" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="K7" s="32"/>
       <c r="L7" s="32"/>
@@ -10751,13 +10899,13 @@
     </row>
     <row r="8" spans="1:22" s="29" customFormat="1">
       <c r="A8" s="32" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="B8" s="44">
         <v>0</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D8" s="44" t="s">
         <v>209</v>
@@ -10783,13 +10931,13 @@
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="39" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B9" s="44">
         <v>0</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D9" s="44" t="s">
         <v>209</v>
@@ -10804,13 +10952,13 @@
         <v>15</v>
       </c>
       <c r="H9" s="32" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="I9" s="32" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="J9" s="32" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="K9" s="32"/>
       <c r="L9" s="32"/>
@@ -10827,13 +10975,13 @@
     </row>
     <row r="10" spans="1:22" s="29" customFormat="1">
       <c r="A10" s="32" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="B10" s="44">
         <v>0</v>
       </c>
       <c r="C10" s="47" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D10" s="44" t="s">
         <v>209</v>
@@ -10846,11 +10994,11 @@
       </c>
       <c r="G10" s="56"/>
       <c r="H10" s="32" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="I10" s="32"/>
       <c r="J10" s="32" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="K10" s="32"/>
       <c r="L10" s="32"/>
@@ -10861,25 +11009,25 @@
       <c r="Q10" s="32"/>
       <c r="R10" s="32"/>
       <c r="S10" s="32" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="T10" s="32" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="U10" s="32"/>
       <c r="V10" s="32" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="39" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B11" s="44">
         <v>0</v>
       </c>
       <c r="C11" s="47" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D11" s="44" t="s">
         <v>209</v>
@@ -10894,7 +11042,7 @@
         <v>15</v>
       </c>
       <c r="H11" s="32" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="I11" s="32" t="s">
         <v>211</v>
@@ -10909,25 +11057,25 @@
       <c r="O11" s="32"/>
       <c r="P11" s="32"/>
       <c r="Q11" s="32" t="s">
+        <v>366</v>
+      </c>
+      <c r="R11" s="32" t="s">
+        <v>367</v>
+      </c>
+      <c r="S11" s="32" t="s">
+        <v>368</v>
+      </c>
+      <c r="T11" s="32" t="s">
+        <v>369</v>
+      </c>
+      <c r="U11" s="32" t="s">
         <v>370</v>
-      </c>
-      <c r="R11" s="32" t="s">
-        <v>371</v>
-      </c>
-      <c r="S11" s="32" t="s">
-        <v>372</v>
-      </c>
-      <c r="T11" s="32" t="s">
-        <v>373</v>
-      </c>
-      <c r="U11" s="32" t="s">
-        <v>374</v>
       </c>
       <c r="V11" s="32"/>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="39" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="B12" s="44">
         <v>2</v>
@@ -10946,19 +11094,19 @@
       </c>
       <c r="G12" s="56"/>
       <c r="H12" s="32" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="I12" s="32" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="J12" s="32" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="K12" s="32" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="L12" s="32" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="M12" s="32"/>
       <c r="N12" s="32"/>
@@ -10967,25 +11115,25 @@
       <c r="Q12" s="32"/>
       <c r="R12" s="32"/>
       <c r="S12" s="32" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="T12" s="32" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="U12" s="32"/>
       <c r="V12" s="32" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="39" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B13" s="44">
         <v>3</v>
       </c>
       <c r="C13" s="47" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="D13" s="44" t="s">
         <v>216</v>
@@ -11015,13 +11163,13 @@
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="39" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B14" s="44">
         <v>1</v>
       </c>
       <c r="C14" s="47" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D14" s="44" t="s">
         <v>209</v>
@@ -11034,7 +11182,7 @@
       </c>
       <c r="G14" s="56"/>
       <c r="H14" s="32" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="I14" s="32" t="s">
         <v>244</v>
@@ -11051,25 +11199,25 @@
       <c r="Q14" s="32"/>
       <c r="R14" s="32"/>
       <c r="S14" s="32" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="T14" s="32" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="U14" s="32"/>
       <c r="V14" s="32" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
     </row>
     <row r="15" spans="1:22" s="29" customFormat="1">
       <c r="A15" s="39" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B15" s="44">
         <v>0</v>
       </c>
       <c r="C15" s="47" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D15" s="44" t="s">
         <v>209</v>
@@ -11084,13 +11232,13 @@
         <v>15</v>
       </c>
       <c r="H15" s="32" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="I15" s="32" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="J15" s="32" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="K15" s="32"/>
       <c r="L15" s="32"/>
@@ -11238,7 +11386,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="44" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D2" s="44" t="s">
         <v>209</v>
@@ -11320,7 +11468,7 @@
         <v>2</v>
       </c>
       <c r="O3" s="44" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="P3" s="44" t="s">
         <v>12</v>
@@ -11378,7 +11526,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="44" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="H4" s="44" t="s">
         <v>12</v>
@@ -11402,7 +11550,7 @@
         <v>2</v>
       </c>
       <c r="O4" s="44" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="P4" s="44" t="s">
         <v>12</v>
@@ -11448,7 +11596,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="44" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="D5" s="44" t="s">
         <v>209</v>
@@ -11488,7 +11636,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="44" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="D6" s="44" t="s">
         <v>209</v>
@@ -11528,7 +11676,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="44" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="D7" s="44" t="s">
         <v>209</v>
@@ -11678,10 +11826,10 @@
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
       <c r="R2" s="3" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
@@ -11940,10 +12088,10 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="T8" s="3">
         <v>0</v>
@@ -11960,22 +12108,22 @@
         <v>2</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="F9" s="3">
         <v>3</v>
       </c>
       <c r="G9" s="34" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>12</v>
@@ -11989,10 +12137,10 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="T9" s="3"/>
       <c r="U9" s="3">
@@ -12013,22 +12161,22 @@
         <v>2</v>
       </c>
       <c r="C10" s="47" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="F10" s="3">
         <v>3</v>
       </c>
       <c r="G10" s="34" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>12</v>
@@ -12042,10 +12190,10 @@
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
@@ -12239,22 +12387,22 @@
         <v>2</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="D16" s="32" t="s">
         <v>12</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="F16" s="32">
         <v>3</v>
       </c>
       <c r="G16" s="34" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="H16" s="32" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="I16" s="32" t="s">
         <v>12</v>
@@ -12268,10 +12416,10 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
@@ -12405,7 +12553,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D2" s="44" t="s">
         <v>209</v>
@@ -12434,13 +12582,13 @@
         <v>1</v>
       </c>
       <c r="C3" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D3" s="44" t="s">
         <v>209</v>
       </c>
       <c r="E3" s="44" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="F3" s="44"/>
       <c r="G3" s="44"/>
@@ -12465,7 +12613,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="44" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="D4" s="44" t="s">
         <v>209</v>
@@ -12494,7 +12642,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="44" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="D5" s="44" t="s">
         <v>209</v>
@@ -12503,7 +12651,7 @@
         <v>264</v>
       </c>
       <c r="F5" s="44" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="G5" s="44"/>
       <c r="H5" s="44"/>
@@ -12527,7 +12675,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D6" s="44" t="s">
         <v>209</v>
@@ -12556,7 +12704,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D7" s="44" t="s">
         <v>209</v>
@@ -12565,7 +12713,7 @@
         <v>264</v>
       </c>
       <c r="F7" s="44" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G7" s="44"/>
       <c r="H7" s="44"/>
@@ -12589,7 +12737,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D8" s="44" t="s">
         <v>209</v>
@@ -12598,7 +12746,7 @@
         <v>264</v>
       </c>
       <c r="F8" s="44" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="G8" s="44"/>
       <c r="H8" s="44"/>
@@ -12622,7 +12770,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="44" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D9" s="44" t="s">
         <v>209</v>
@@ -12631,7 +12779,7 @@
         <v>264</v>
       </c>
       <c r="F9" s="44" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="G9" s="44"/>
       <c r="H9" s="44"/>
@@ -12702,7 +12850,7 @@
         <v>264</v>
       </c>
       <c r="G11" s="44" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="H11" s="44"/>
       <c r="I11" s="44"/>
@@ -12725,7 +12873,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="44" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D12" s="44" t="s">
         <v>209</v>
@@ -12783,7 +12931,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="44" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D14" s="44" t="s">
         <v>209</v>
@@ -12812,7 +12960,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="44" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D15" s="44" t="s">
         <v>209</v>
@@ -12841,7 +12989,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="44" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D16" s="44" t="s">
         <v>209</v>
@@ -12870,7 +13018,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="44" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D17" s="44" t="s">
         <v>209</v>
@@ -12965,7 +13113,7 @@
         <v>3</v>
       </c>
       <c r="K20" s="44" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="L20" s="44" t="s">
         <v>12</v>

--- a/src/test/java/TestData/Scenario_TestData.xlsx
+++ b/src/test/java/TestData/Scenario_TestData.xlsx
@@ -3,12 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Copa_SHD_WebServices\src\test\java\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D19DA22-55BA-44BF-84B1-7C363E09180E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF081C1-AADE-4AAB-8808-03DBC5730FE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="27" activeTab="30" xr2:uid="{5D5A4724-D560-4FC2-9708-4BBF1DBA0B11}"/>
   </bookViews>
@@ -55,7 +55,7 @@
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2120" uniqueCount="647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2119" uniqueCount="647">
   <si>
     <t>Scenario</t>
   </si>
@@ -1018,12 +1018,6 @@
     <t>2024-03-10T06:42:00</t>
   </si>
   <si>
-    <t xml:space="preserve">NAME </t>
-  </si>
-  <si>
-    <t>SURNAME</t>
-  </si>
-  <si>
     <t>Add Flight</t>
   </si>
   <si>
@@ -1957,9 +1951,6 @@
     <t>BANE1O</t>
   </si>
   <si>
-    <t>BANKK3</t>
-  </si>
-  <si>
     <t>BANKLX</t>
   </si>
   <si>
@@ -2002,26 +1993,34 @@
     <t>2023-08-30T06:44:00</t>
   </si>
   <si>
-    <t>BAOJ41</t>
-  </si>
-  <si>
     <t>2023-08-30T00:23:00</t>
   </si>
   <si>
-    <t>BAOMOX</t>
-  </si>
-  <si>
-    <t>BAOQ21</t>
-  </si>
-  <si>
     <t>BAOVIV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NewName </t>
+  </si>
+  <si>
+    <t>NewSurname</t>
+  </si>
+  <si>
+    <t>2023-08-31T00:23:00</t>
+  </si>
+  <si>
+    <t>2023-08-31T06:44:00</t>
+  </si>
+  <si>
+    <t>BAYOOO</t>
+  </si>
+  <si>
+    <t>2302182825352</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="13">
     <font>
       <sz val="11"/>
@@ -2679,20 +2678,20 @@
   <dimension ref="A1:P15"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="52.81640625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="18.453125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="9.453125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="10.453125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="11.1796875"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="10.453125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="11.1796875"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="10.453125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="11.1796875"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="15.1796875"/>
+    <col min="1" max="1" width="52.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2750,7 +2749,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="44" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D2" s="44" t="s">
         <v>209</v>
@@ -2765,7 +2764,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="44" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="I2" s="32" t="s">
         <v>211</v>
@@ -2782,7 +2781,7 @@
       <c r="M2" s="32"/>
       <c r="N2" s="32"/>
       <c r="O2" s="32" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="P2" s="38"/>
     </row>
@@ -2794,7 +2793,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="44" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D3" s="44" t="s">
         <v>209</v>
@@ -2833,13 +2832,13 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="37" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B4" s="44">
         <v>0</v>
       </c>
       <c r="C4" s="44" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D4" s="44" t="s">
         <v>209</v>
@@ -2854,13 +2853,13 @@
         <v>1</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="I4" s="37" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="J4" s="37" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="K4" s="32"/>
       <c r="L4" s="32"/>
@@ -2870,13 +2869,13 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="37" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B5" s="44">
         <v>0</v>
       </c>
       <c r="C5" s="44" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D5" s="44" t="s">
         <v>209</v>
@@ -2891,7 +2890,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="37" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="I5" s="32"/>
       <c r="J5" s="32"/>
@@ -2927,15 +2926,15 @@
   <dimension ref="A1:W22"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="49.0"/>
-    <col min="10" max="10" style="25" width="8.81640625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="13.90625"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="11.453125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="9.81640625"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="13.90625"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="12.6328125"/>
-    <col min="22" max="23" bestFit="true" customWidth="true" width="19.26953125"/>
+    <col min="1" max="1" width="49" customWidth="1"/>
+    <col min="10" max="10" width="8.81640625" style="25"/>
+    <col min="12" max="12" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="19.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -3003,10 +3002,10 @@
         <v>257</v>
       </c>
       <c r="V1" s="43" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="W1" s="43" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="2" spans="1:23">
@@ -3039,7 +3038,7 @@
       </c>
       <c r="J2" s="44"/>
       <c r="K2" s="44" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="L2" s="44"/>
       <c r="M2" s="44"/>
@@ -3078,10 +3077,10 @@
         <v>0</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="L3" s="44" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="M3" s="44"/>
       <c r="N3" s="44"/>
@@ -3103,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="44" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D4" s="44" t="s">
         <v>209</v>
@@ -3140,7 +3139,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="44" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D5" s="44" t="s">
         <v>209</v>
@@ -3154,10 +3153,10 @@
       <c r="I5" s="44"/>
       <c r="J5" s="44"/>
       <c r="K5" s="44" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="M5" s="44"/>
       <c r="N5" s="44" t="s">
@@ -3189,7 +3188,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="44" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D6" s="44" t="s">
         <v>209</v>
@@ -3203,7 +3202,7 @@
       <c r="I6" s="44"/>
       <c r="J6" s="44"/>
       <c r="K6" s="44" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="L6" s="44"/>
       <c r="M6" s="44"/>
@@ -3214,7 +3213,7 @@
         <v>242</v>
       </c>
       <c r="P6" s="44" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="Q6" s="44"/>
       <c r="R6" s="44"/>
@@ -3236,7 +3235,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D7" s="44" t="s">
         <v>209</v>
@@ -3250,10 +3249,10 @@
       <c r="I7" s="44"/>
       <c r="J7" s="44"/>
       <c r="K7" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="L7" s="44" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="M7" s="44"/>
       <c r="N7" s="44" t="s">
@@ -3263,13 +3262,13 @@
         <v>242</v>
       </c>
       <c r="P7" s="44" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="Q7" s="47" t="s">
         <v>87</v>
       </c>
       <c r="R7" s="44" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="S7" s="44"/>
       <c r="T7" s="44"/>
@@ -3307,10 +3306,10 @@
       </c>
       <c r="J8" s="44"/>
       <c r="K8" s="44" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="L8" s="44" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="M8" s="44"/>
       <c r="N8" s="44" t="s">
@@ -3336,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="44" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D9" s="44" t="s">
         <v>209</v>
@@ -3350,7 +3349,7 @@
       <c r="I9" s="44"/>
       <c r="J9" s="44"/>
       <c r="K9" s="44" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="L9" s="44"/>
       <c r="M9" s="44"/>
@@ -3367,7 +3366,7 @@
       <c r="T9" s="44"/>
       <c r="U9" s="44"/>
       <c r="V9" s="44" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="W9" s="44"/>
     </row>
@@ -3379,7 +3378,7 @@
         <v>1</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D10" s="44" t="s">
         <v>209</v>
@@ -3393,10 +3392,10 @@
       <c r="I10" s="44"/>
       <c r="J10" s="44"/>
       <c r="K10" s="44" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="L10" s="44" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="M10" s="44"/>
       <c r="N10" s="44"/>
@@ -3405,7 +3404,7 @@
       <c r="Q10" s="44"/>
       <c r="R10" s="44"/>
       <c r="S10" s="47" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="T10" s="44"/>
       <c r="U10" s="44"/>
@@ -3420,7 +3419,7 @@
         <v>0</v>
       </c>
       <c r="C11" s="44" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D11" s="44" t="s">
         <v>209</v>
@@ -3434,10 +3433,10 @@
       <c r="I11" s="44"/>
       <c r="J11" s="44"/>
       <c r="K11" s="44" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="L11" s="44" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="M11" s="44"/>
       <c r="N11" s="44"/>
@@ -3461,7 +3460,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="44" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D12" s="44" t="s">
         <v>209</v>
@@ -3475,10 +3474,10 @@
       <c r="I12" s="44"/>
       <c r="J12" s="44"/>
       <c r="K12" s="44" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="L12" s="44" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="M12" s="44"/>
       <c r="N12" s="44" t="s">
@@ -3506,7 +3505,7 @@
         <v>0</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D13" s="44" t="s">
         <v>209</v>
@@ -3520,10 +3519,10 @@
       <c r="I13" s="44"/>
       <c r="J13" s="44"/>
       <c r="K13" s="44" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="L13" s="44" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="M13" s="44"/>
       <c r="N13" s="44" t="s">
@@ -3551,7 +3550,7 @@
         <v>0</v>
       </c>
       <c r="C14" s="44" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D14" s="44" t="s">
         <v>209</v>
@@ -3602,10 +3601,10 @@
       <c r="I15" s="44"/>
       <c r="J15" s="44"/>
       <c r="K15" s="44" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="L15" s="44" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="M15" s="44"/>
       <c r="N15" s="44" t="s">
@@ -3633,7 +3632,7 @@
         <v>0</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="D16" s="44" t="s">
         <v>12</v>
@@ -3647,7 +3646,7 @@
       <c r="I16" s="44"/>
       <c r="J16" s="44"/>
       <c r="K16" s="44" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="L16" s="44"/>
       <c r="M16" s="44"/>
@@ -3674,7 +3673,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="44" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D17" s="44" t="s">
         <v>209</v>
@@ -3688,7 +3687,7 @@
       <c r="I17" s="44"/>
       <c r="J17" s="44"/>
       <c r="K17" s="44" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="L17" s="44"/>
       <c r="M17" s="44"/>
@@ -3723,7 +3722,7 @@
         <v>5</v>
       </c>
       <c r="G18" s="44" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="H18" s="44" t="s">
         <v>12</v>
@@ -3733,7 +3732,7 @@
       </c>
       <c r="J18" s="44"/>
       <c r="K18" s="44" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="L18" s="44"/>
       <c r="M18" s="44"/>
@@ -3750,10 +3749,10 @@
       <c r="T18" s="44"/>
       <c r="U18" s="44"/>
       <c r="V18" s="44" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="W18" s="44" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="19" spans="1:23">
@@ -3764,7 +3763,7 @@
         <v>0</v>
       </c>
       <c r="C19" s="44" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D19" s="44" t="s">
         <v>209</v>
@@ -3778,7 +3777,7 @@
       <c r="I19" s="44"/>
       <c r="J19" s="44"/>
       <c r="K19" s="44" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="L19" s="44"/>
       <c r="M19" s="44"/>
@@ -3795,7 +3794,7 @@
       <c r="T19" s="44"/>
       <c r="U19" s="44"/>
       <c r="V19" s="44" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="W19" s="44"/>
     </row>
@@ -3807,7 +3806,7 @@
         <v>0</v>
       </c>
       <c r="C20" s="44" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D20" s="44" t="s">
         <v>209</v>
@@ -3821,7 +3820,7 @@
       <c r="I20" s="44"/>
       <c r="J20" s="44"/>
       <c r="K20" s="44" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="L20" s="44"/>
       <c r="M20" s="44"/>
@@ -3848,7 +3847,7 @@
         <v>0</v>
       </c>
       <c r="C21" s="47" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="D21" s="44" t="s">
         <v>12</v>
@@ -3862,15 +3861,15 @@
       <c r="I21" s="44"/>
       <c r="J21" s="44"/>
       <c r="K21" s="44" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="L21" s="44"/>
       <c r="M21" s="44"/>
       <c r="N21" s="44" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="O21" s="44" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="P21" s="44"/>
       <c r="Q21" s="44"/>
@@ -3889,7 +3888,7 @@
         <v>1</v>
       </c>
       <c r="C22" s="47" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D22" s="44" t="s">
         <v>34</v>
@@ -3911,7 +3910,7 @@
       </c>
       <c r="J22" s="44"/>
       <c r="K22" s="44" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="L22" s="44"/>
       <c r="M22" s="44"/>
@@ -3943,16 +3942,16 @@
   <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="32.90625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="3" max="3" customWidth="true" style="29" width="17.54296875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="29.7265625"/>
-    <col min="5" max="5" customWidth="true" width="13.81640625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="14.36328125"/>
-    <col min="7" max="11" customWidth="true" style="29" width="14.36328125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="30.36328125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="13.81640625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="10.90625"/>
+    <col min="1" max="1" width="32.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.54296875" style="29" customWidth="1"/>
+    <col min="4" max="4" width="29.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.81640625" customWidth="1"/>
+    <col min="6" max="6" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="14.36328125" style="29" customWidth="1"/>
+    <col min="12" max="12" width="30.36328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -4007,14 +4006,14 @@
         <v>2</v>
       </c>
       <c r="D2" s="47" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E2" s="47" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="F2" s="44"/>
       <c r="G2" s="47" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H2" s="44" t="s">
         <v>12</v>
@@ -4038,7 +4037,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="47" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E3" s="47" t="s">
         <v>264</v>
@@ -4047,7 +4046,7 @@
         <v>149</v>
       </c>
       <c r="G3" s="47" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H3" s="44" t="s">
         <v>12</v>
@@ -4073,7 +4072,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="47" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="E4" s="44"/>
       <c r="F4" s="44" t="s">
@@ -4089,7 +4088,7 @@
         <v>13</v>
       </c>
       <c r="J4" s="47" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="K4" s="44" t="s">
         <v>13</v>
@@ -4112,17 +4111,17 @@
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="29" width="21.81640625"/>
-    <col min="2" max="2" customWidth="true" style="29" width="16.54296875"/>
-    <col min="3" max="3" customWidth="true" style="29" width="19.90625"/>
-    <col min="4" max="4" customWidth="true" style="29" width="18.81640625"/>
-    <col min="5" max="6" customWidth="true" style="29" width="12.90625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="29" width="15.0"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="29" width="11.90625"/>
-    <col min="9" max="9" style="29" width="8.81640625"/>
-    <col min="10" max="10" customWidth="true" style="29" width="17.90625"/>
-    <col min="11" max="11" customWidth="true" style="29" width="14.1796875"/>
-    <col min="12" max="16384" style="29" width="8.81640625"/>
+    <col min="1" max="1" width="21.81640625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="16.54296875" style="29" customWidth="1"/>
+    <col min="3" max="3" width="19.90625" style="29" customWidth="1"/>
+    <col min="4" max="4" width="18.81640625" style="29" customWidth="1"/>
+    <col min="5" max="6" width="12.90625" style="29" customWidth="1"/>
+    <col min="7" max="7" width="15" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.90625" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.81640625" style="29"/>
+    <col min="10" max="10" width="17.90625" style="29" customWidth="1"/>
+    <col min="11" max="11" width="14.1796875" style="29" customWidth="1"/>
+    <col min="12" max="16384" width="8.81640625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -4174,7 +4173,7 @@
       <c r="G2" s="44"/>
       <c r="H2" s="44"/>
       <c r="I2" s="44" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="J2" s="44"/>
       <c r="K2" s="44"/>
@@ -4193,7 +4192,7 @@
       <c r="G3" s="44"/>
       <c r="H3" s="44"/>
       <c r="I3" s="44" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="J3" s="44"/>
       <c r="K3" s="44"/>
@@ -4212,7 +4211,7 @@
       <c r="G4" s="44"/>
       <c r="H4" s="44"/>
       <c r="I4" s="44" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="J4" s="44"/>
       <c r="K4" s="44"/>
@@ -4234,7 +4233,7 @@
         <v>2</v>
       </c>
       <c r="F5" s="47" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G5" s="44" t="s">
         <v>209</v>
@@ -4243,13 +4242,13 @@
         <v>12</v>
       </c>
       <c r="I5" s="44" t="s">
+        <v>517</v>
+      </c>
+      <c r="J5" s="44" t="s">
+        <v>518</v>
+      </c>
+      <c r="K5" s="44" t="s">
         <v>519</v>
-      </c>
-      <c r="J5" s="44" t="s">
-        <v>520</v>
-      </c>
-      <c r="K5" s="44" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -4269,7 +4268,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="47" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G6" s="44" t="s">
         <v>209</v>
@@ -4278,10 +4277,10 @@
         <v>12</v>
       </c>
       <c r="I6" s="44" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="J6" s="44" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="K6" s="44"/>
     </row>
@@ -4298,12 +4297,12 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="29" width="42.1796875"/>
-    <col min="2" max="2" customWidth="true" style="29" width="15.81640625"/>
-    <col min="3" max="3" customWidth="true" style="29" width="17.81640625"/>
-    <col min="4" max="4" customWidth="true" style="29" width="16.81640625"/>
-    <col min="5" max="5" customWidth="true" style="29" width="15.6328125"/>
-    <col min="6" max="16384" style="29" width="8.81640625"/>
+    <col min="1" max="1" width="42.1796875" style="29" customWidth="1"/>
+    <col min="2" max="2" width="15.81640625" style="29" customWidth="1"/>
+    <col min="3" max="3" width="17.81640625" style="29" customWidth="1"/>
+    <col min="4" max="4" width="16.81640625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="15.6328125" style="29" customWidth="1"/>
+    <col min="6" max="16384" width="8.81640625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4349,7 +4348,7 @@
         <v>149</v>
       </c>
       <c r="D3" s="44" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E3" s="44">
         <v>1</v>
@@ -4366,7 +4365,7 @@
         <v>149</v>
       </c>
       <c r="D4" s="44" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E4" s="44">
         <v>1</v>
@@ -4374,7 +4373,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="37" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B5" s="37"/>
       <c r="C5" s="37" t="s">
@@ -4385,7 +4384,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="37" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B6" s="37"/>
       <c r="C6" s="37" t="s">
@@ -4398,7 +4397,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="37" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B7" s="37"/>
       <c r="C7" s="37" t="s">
@@ -4422,28 +4421,28 @@
   <dimension ref="A1:AB6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="51.81640625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="9.453125"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="18.453125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="14.453125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="18.453125"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="18.453125"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="12.08984375"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="15.36328125"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="12.08984375"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" width="15.36328125"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="1" max="1" width="51.81640625" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28">
@@ -4561,16 +4560,16 @@
         <v>45</v>
       </c>
       <c r="J2" s="44" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="K2" s="44" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="L2" s="44" t="s">
         <v>207</v>
       </c>
       <c r="M2" s="44" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="N2" s="44" t="s">
         <v>208</v>
@@ -4579,13 +4578,13 @@
         <v>12</v>
       </c>
       <c r="P2" s="44" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="Q2" s="44" t="s">
         <v>62</v>
       </c>
       <c r="R2" s="44" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="S2" s="44" t="s">
         <v>12</v>
@@ -4631,16 +4630,16 @@
         <v>45</v>
       </c>
       <c r="J3" s="44" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="L3" s="44" t="s">
         <v>207</v>
       </c>
       <c r="M3" s="44" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="N3" s="44" t="s">
         <v>208</v>
@@ -4649,13 +4648,13 @@
         <v>12</v>
       </c>
       <c r="P3" s="44" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="Q3" s="44" t="s">
         <v>239</v>
       </c>
       <c r="R3" s="44" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="S3" s="44" t="s">
         <v>12</v>
@@ -4696,7 +4695,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="44" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D4" s="44" t="s">
         <v>209</v>
@@ -4709,16 +4708,16 @@
       <c r="H4" s="44"/>
       <c r="I4" s="44"/>
       <c r="J4" s="44" t="s">
+        <v>528</v>
+      </c>
+      <c r="K4" s="44" t="s">
+        <v>529</v>
+      </c>
+      <c r="L4" s="44" t="s">
+        <v>322</v>
+      </c>
+      <c r="M4" s="44" t="s">
         <v>530</v>
-      </c>
-      <c r="K4" s="44" t="s">
-        <v>531</v>
-      </c>
-      <c r="L4" s="44" t="s">
-        <v>324</v>
-      </c>
-      <c r="M4" s="44" t="s">
-        <v>532</v>
       </c>
       <c r="N4" s="44" t="s">
         <v>209</v>
@@ -4748,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="44" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D5" s="44" t="s">
         <v>209</v>
@@ -4761,16 +4760,16 @@
       <c r="H5" s="44"/>
       <c r="I5" s="44"/>
       <c r="J5" s="44" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="M5" s="44" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="N5" s="44" t="s">
         <v>209</v>
@@ -4821,16 +4820,16 @@
         <v>45</v>
       </c>
       <c r="J6" s="44" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="K6" s="44" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="L6" s="44" t="s">
         <v>207</v>
       </c>
       <c r="M6" s="44" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="N6" s="44" t="s">
         <v>208</v>
@@ -4866,10 +4865,10 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="76.1796875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="13.453125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="1" max="1" width="76.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4894,7 +4893,7 @@
         <v>69</v>
       </c>
       <c r="B2" s="44" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C2" s="44">
         <v>0</v>
@@ -4911,7 +4910,7 @@
         <v>70</v>
       </c>
       <c r="B3" s="44" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C3" s="44">
         <v>0</v>
@@ -4928,7 +4927,7 @@
         <v>71</v>
       </c>
       <c r="B4" s="44" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C4" s="44">
         <v>0</v>
@@ -4954,12 +4953,12 @@
   <dimension ref="A1:E15"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="29" width="68.08984375"/>
-    <col min="2" max="2" customWidth="true" style="29" width="12.54296875"/>
-    <col min="3" max="3" customWidth="true" style="29" width="14.81640625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="29" width="11.81640625"/>
-    <col min="5" max="5" customWidth="true" style="29" width="18.1796875"/>
-    <col min="6" max="16384" style="29" width="8.81640625"/>
+    <col min="1" max="1" width="68.08984375" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.54296875" style="29" customWidth="1"/>
+    <col min="3" max="3" width="14.81640625" style="29" customWidth="1"/>
+    <col min="4" max="4" width="11.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.1796875" style="29" customWidth="1"/>
+    <col min="6" max="16384" width="8.81640625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -5095,7 +5094,7 @@
         <v>282</v>
       </c>
       <c r="D9" s="44" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E9" s="44"/>
     </row>
@@ -5206,8 +5205,8 @@
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="12.54296875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="1" max="1" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -5231,7 +5230,7 @@
         <v>111</v>
       </c>
       <c r="B3" s="41" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>
@@ -5247,11 +5246,11 @@
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="33.54296875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="13.453125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="1" max="1" width="33.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -5279,7 +5278,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="44" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D2" s="44" t="s">
         <v>209</v>
@@ -5301,7 +5300,7 @@
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="21.81640625"/>
+    <col min="1" max="1" width="21.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -5406,31 +5405,31 @@
   <dimension ref="A1:AG4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="49.81640625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="4.81640625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="9.81640625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="4.453125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="9.81640625"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="4.453125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="9.81640625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="4.453125"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="9.81640625"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="4.453125"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="9.81640625"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="4.453125"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="9.81640625"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="4.453125"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="9.81640625"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="4.453125"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" width="5.453125"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" width="9.7265625"/>
+    <col min="1" max="1" width="49.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="9.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33">
@@ -5542,7 +5541,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="44" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D2" s="44" t="s">
         <v>209</v>
@@ -5554,7 +5553,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="44" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="H2" s="44" t="s">
         <v>209</v>
@@ -5566,7 +5565,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="44" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="L2" s="44" t="s">
         <v>209</v>
@@ -5578,7 +5577,7 @@
         <v>0</v>
       </c>
       <c r="O2" s="44" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="P2" s="44" t="s">
         <v>209</v>
@@ -5590,7 +5589,7 @@
         <v>1</v>
       </c>
       <c r="S2" s="44" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="T2" s="44" t="s">
         <v>209</v>
@@ -5614,7 +5613,7 @@
         <v>0</v>
       </c>
       <c r="AA2" s="44" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AB2" s="44" t="s">
         <v>45</v>
@@ -5626,7 +5625,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="44" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="AF2" s="44" t="s">
         <v>45</v>
@@ -5643,7 +5642,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="44" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D3" s="44"/>
       <c r="E3" s="44"/>
@@ -5684,7 +5683,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="44" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D4" s="44" t="s">
         <v>209</v>
@@ -5735,25 +5734,25 @@
   <dimension ref="A1:AD9"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="33.0"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="18.36328125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="12.08984375"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="18.36328125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="15.36328125"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="13.90625"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="12.08984375"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="15.36328125"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="14.36328125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="12.08984375"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="15.36328125"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" width="12.08984375"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="17.54296875"/>
+    <col min="1" max="1" width="33" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30">
@@ -5856,7 +5855,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="44" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D2" s="44" t="s">
         <v>209</v>
@@ -5872,16 +5871,16 @@
       <c r="I2" s="44"/>
       <c r="J2" s="44"/>
       <c r="K2" s="44" t="s">
+        <v>532</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="N2" s="3" t="s">
         <v>534</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>536</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>209</v>
@@ -5912,7 +5911,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="44" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D3" s="44" t="s">
         <v>209</v>
@@ -5924,7 +5923,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="44" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="H3" s="44" t="s">
         <v>209</v>
@@ -5936,7 +5935,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>312</v>
@@ -6000,7 +5999,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="47" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D4" s="44" t="s">
         <v>209</v>
@@ -6012,7 +6011,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="44" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="H4" s="44" t="s">
         <v>209</v>
@@ -6052,7 +6051,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="44" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D5" s="44" t="s">
         <v>209</v>
@@ -6064,7 +6063,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="44" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="H5" s="44" t="s">
         <v>209</v>
@@ -6076,16 +6075,16 @@
         <v>2</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>209</v>
@@ -6094,7 +6093,7 @@
         <v>12</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="R5" s="15" t="s">
         <v>44</v>
@@ -6144,7 +6143,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="44" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D6" s="44" t="s">
         <v>209</v>
@@ -6188,7 +6187,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="44" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D7" s="44" t="s">
         <v>209</v>
@@ -6232,7 +6231,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="44" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D8" s="44" t="s">
         <v>209</v>
@@ -6276,7 +6275,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="44" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D9" s="44" t="s">
         <v>209</v>
@@ -6292,16 +6291,16 @@
       <c r="I9" s="44"/>
       <c r="J9" s="44"/>
       <c r="K9" s="44" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>209</v>
@@ -6337,11 +6336,11 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="35.1796875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="11.54296875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="13.453125"/>
+    <col min="1" max="1" width="35.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -6366,10 +6365,10 @@
         <v>127</v>
       </c>
       <c r="B2" s="44" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C2" s="44" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D2" s="44" t="s">
         <v>128</v>
@@ -6383,7 +6382,7 @@
         <v>129</v>
       </c>
       <c r="B3" s="44" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C3" s="44" t="s">
         <v>209</v>
@@ -6425,9 +6424,9 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="33.54296875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="13.453125"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="9.90625"/>
+    <col min="1" max="1" width="33.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -6455,7 +6454,7 @@
         <v>137</v>
       </c>
       <c r="B2" s="44" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C2" s="44" t="s">
         <v>138</v>
@@ -6467,7 +6466,7 @@
         <v>140</v>
       </c>
       <c r="F2" s="44" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -6483,9 +6482,9 @@
   <dimension ref="A1:AC4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="46.6328125"/>
-    <col min="5" max="5" customWidth="true" width="6.1796875"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="13.90625"/>
+    <col min="1" max="1" width="46.6328125" customWidth="1"/>
+    <col min="5" max="5" width="6.1796875" customWidth="1"/>
+    <col min="29" max="29" width="13.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -6585,7 +6584,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="44" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D2" s="44" t="s">
         <v>209</v>
@@ -6613,16 +6612,16 @@
       <c r="U2" s="44"/>
       <c r="V2" s="44"/>
       <c r="W2" s="44" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="X2" s="44" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="Y2" s="44" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="Z2" s="44" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="AA2" s="44" t="s">
         <v>209</v>
@@ -6631,7 +6630,7 @@
         <v>12</v>
       </c>
       <c r="AC2" s="44" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -6678,7 +6677,7 @@
         <v>4</v>
       </c>
       <c r="O3" s="44" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="P3" s="44" t="s">
         <v>12</v>
@@ -6690,7 +6689,7 @@
         <v>5</v>
       </c>
       <c r="S3" s="44" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="T3" s="44" t="s">
         <v>34</v>
@@ -6721,7 +6720,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="44" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D4" s="44" t="s">
         <v>209</v>
@@ -6749,16 +6748,16 @@
       <c r="U4" s="44"/>
       <c r="V4" s="44"/>
       <c r="W4" s="44" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="X4" s="44" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="Y4" s="44" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="Z4" s="44" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="AA4" s="44" t="s">
         <v>209</v>
@@ -6767,7 +6766,7 @@
         <v>12</v>
       </c>
       <c r="AC4" s="44" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
   </sheetData>
@@ -6783,14 +6782,14 @@
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="63.81640625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="10.81640625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="19.453125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="15.54296875"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="8" max="9" bestFit="true" customWidth="true" width="19.453125"/>
+    <col min="1" max="1" width="63.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="19.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -6893,7 +6892,7 @@
         <v>12</v>
       </c>
       <c r="I5" s="44" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -6925,24 +6924,24 @@
   <dimension ref="A1:R6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="12.0"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="9.453125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="6.1796875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="13.81640625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="17.54296875"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="7.453125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="18.453125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="18.453125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="15.453125"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="12.1796875"/>
-    <col min="17" max="17" customWidth="true" width="17.6328125"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="13.90625"/>
+    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.6328125" customWidth="1"/>
+    <col min="18" max="18" width="13.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -7025,16 +7024,16 @@
       <c r="I2" s="44"/>
       <c r="J2" s="44"/>
       <c r="K2" s="44" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="L2" s="44" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="M2" s="44" t="s">
         <v>18</v>
       </c>
       <c r="N2" s="44" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="O2" s="44" t="s">
         <v>12</v>
@@ -7043,7 +7042,7 @@
         <v>13</v>
       </c>
       <c r="Q2" s="44" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="R2" s="44"/>
     </row>
@@ -7071,16 +7070,16 @@
       <c r="I3" s="44"/>
       <c r="J3" s="44"/>
       <c r="K3" s="44" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="L3" s="44" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="M3" s="44" t="s">
         <v>18</v>
       </c>
       <c r="N3" s="44" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="O3" s="44" t="s">
         <v>12</v>
@@ -7089,10 +7088,10 @@
         <v>13</v>
       </c>
       <c r="Q3" s="44" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="R3" s="44" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -7127,16 +7126,16 @@
         <v>2</v>
       </c>
       <c r="K4" s="44" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="L4" s="44" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="M4" s="44" t="s">
         <v>18</v>
       </c>
       <c r="N4" s="44" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="O4" s="44" t="s">
         <v>12</v>
@@ -7145,7 +7144,7 @@
         <v>13</v>
       </c>
       <c r="Q4" s="44" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="R4" s="44"/>
     </row>
@@ -7173,16 +7172,16 @@
       <c r="I5" s="44"/>
       <c r="J5" s="44"/>
       <c r="K5" s="44" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="M5" s="44" t="s">
         <v>18</v>
       </c>
       <c r="N5" s="44" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="O5" s="44" t="s">
         <v>12</v>
@@ -7191,7 +7190,7 @@
         <v>13</v>
       </c>
       <c r="Q5" s="44" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="R5" s="44"/>
     </row>
@@ -7219,16 +7218,16 @@
       <c r="I6" s="44"/>
       <c r="J6" s="44"/>
       <c r="K6" s="44" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="L6" s="44" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="M6" s="44" t="s">
         <v>18</v>
       </c>
       <c r="N6" s="44" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="O6" s="44" t="s">
         <v>12</v>
@@ -7237,7 +7236,7 @@
         <v>13</v>
       </c>
       <c r="Q6" s="44" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="R6" s="44"/>
     </row>
@@ -7255,27 +7254,27 @@
   <dimension ref="A1:U13"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="44.08984375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.36328125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="11.90625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="9.1796875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="6.1796875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="17.36328125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="11.90625"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="9.1796875"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="6.1796875"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="8.54296875"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="18.6328125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="11.90625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="18.6328125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="11.90625"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="18.6328125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="11.90625"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="18.6328125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="15.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="11.90625"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="14.08984375"/>
+    <col min="1" max="1" width="44.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.6328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.6328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.6328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.6328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
@@ -7372,16 +7371,16 @@
         <v>163</v>
       </c>
       <c r="J2" s="56" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="K2" s="44" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>215</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>12</v>
@@ -7390,13 +7389,13 @@
         <v>216</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>217</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="S2" s="3" t="s">
         <v>216</v>
@@ -7405,7 +7404,7 @@
         <v>163</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="3" spans="1:21">
@@ -7428,7 +7427,7 @@
         <v>2</v>
       </c>
       <c r="G3" s="44" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="H3" s="44" t="s">
         <v>216</v>
@@ -7437,16 +7436,16 @@
         <v>163</v>
       </c>
       <c r="J3" s="56" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>215</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>12</v>
@@ -7455,13 +7454,13 @@
         <v>216</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="S3" s="3" t="s">
         <v>216</v>
@@ -7470,7 +7469,7 @@
         <v>163</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="4" spans="1:21">
@@ -7650,8 +7649,8 @@
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="32.1796875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="1" max="1" width="32.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -7675,7 +7674,7 @@
         <v>181</v>
       </c>
       <c r="B3" s="47" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -7699,7 +7698,7 @@
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="18.0"/>
+    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -7760,21 +7759,21 @@
   <dimension ref="A1:N19"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="29" width="24.90625"/>
-    <col min="2" max="2" customWidth="true" style="29" width="14.0"/>
-    <col min="3" max="3" customWidth="true" style="29" width="11.81640625"/>
-    <col min="4" max="4" customWidth="true" style="29" width="9.54296875"/>
-    <col min="5" max="5" customWidth="true" style="29" width="10.36328125"/>
-    <col min="6" max="6" customWidth="true" style="29" width="9.36328125"/>
-    <col min="7" max="7" customWidth="true" style="29" width="9.7265625"/>
-    <col min="8" max="8" customWidth="true" style="29" width="10.453125"/>
-    <col min="9" max="9" customWidth="true" style="29" width="8.81640625"/>
-    <col min="10" max="10" customWidth="true" style="41" width="8.08984375"/>
-    <col min="11" max="11" customWidth="true" style="29" width="10.0"/>
-    <col min="12" max="12" customWidth="true" style="29" width="7.81640625"/>
-    <col min="13" max="13" customWidth="true" style="29" width="9.0"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="29" width="19.453125"/>
-    <col min="15" max="16384" style="29" width="8.81640625"/>
+    <col min="1" max="1" width="24.90625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="14" style="29" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" style="29" customWidth="1"/>
+    <col min="4" max="4" width="9.54296875" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10.36328125" style="29" customWidth="1"/>
+    <col min="6" max="6" width="9.36328125" style="29" customWidth="1"/>
+    <col min="7" max="7" width="9.7265625" style="29" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" style="29" customWidth="1"/>
+    <col min="9" max="9" width="8.81640625" style="29" customWidth="1"/>
+    <col min="10" max="10" width="8.08984375" style="41" customWidth="1"/>
+    <col min="11" max="11" width="10" style="29" customWidth="1"/>
+    <col min="12" max="12" width="7.81640625" style="29" customWidth="1"/>
+    <col min="13" max="13" width="9" style="29" customWidth="1"/>
+    <col min="14" max="14" width="19.453125" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.81640625" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -7785,40 +7784,40 @@
         <v>266</v>
       </c>
       <c r="C1" s="42" t="s">
+        <v>456</v>
+      </c>
+      <c r="D1" s="42" t="s">
+        <v>457</v>
+      </c>
+      <c r="E1" s="42" t="s">
         <v>458</v>
       </c>
-      <c r="D1" s="42" t="s">
+      <c r="F1" s="42" t="s">
         <v>459</v>
       </c>
-      <c r="E1" s="42" t="s">
+      <c r="G1" s="63" t="s">
         <v>460</v>
       </c>
-      <c r="F1" s="42" t="s">
+      <c r="H1" s="63" t="s">
         <v>461</v>
       </c>
-      <c r="G1" s="63" t="s">
-        <v>462</v>
-      </c>
-      <c r="H1" s="63" t="s">
-        <v>463</v>
-      </c>
       <c r="I1" s="63" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="J1" s="63" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K1" s="42" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="L1" s="42" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="M1" s="42" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="N1" s="42" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -7829,40 +7828,40 @@
         <v>149</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D2" s="32" t="s">
         <v>121</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="F2" s="44" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="G2" s="44" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H2" s="44" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="I2" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="J2" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="K2" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L2" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="M2" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="N2" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -7873,40 +7872,40 @@
         <v>149</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D3" s="32" t="s">
         <v>121</v>
       </c>
       <c r="E3" s="32" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="F3" s="44" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="G3" s="44" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H3" s="44" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="I3" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="J3" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L3" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="M3" s="44" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="N3" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -7917,40 +7916,40 @@
         <v>149</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D4" s="32" t="s">
         <v>121</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="F4" s="44" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="G4" s="44" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H4" s="44" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="I4" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="J4" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="K4" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L4" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="M4" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="N4" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -7961,7 +7960,7 @@
         <v>149</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D5" s="32" t="s">
         <v>121</v>
@@ -7970,31 +7969,31 @@
         <v>121</v>
       </c>
       <c r="F5" s="44" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="G5" s="44" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H5" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="I5" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="J5" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="M5" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="N5" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -8005,7 +8004,7 @@
         <v>149</v>
       </c>
       <c r="C6" s="44" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D6" s="44" t="s">
         <v>121</v>
@@ -8014,31 +8013,31 @@
         <v>121</v>
       </c>
       <c r="F6" s="44" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="G6" s="44" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H6" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="I6" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="J6" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="K6" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L6" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="M6" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="N6" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -8049,7 +8048,7 @@
         <v>149</v>
       </c>
       <c r="C7" s="44" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D7" s="44" t="s">
         <v>121</v>
@@ -8058,31 +8057,31 @@
         <v>121</v>
       </c>
       <c r="F7" s="44" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="G7" s="44" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H7" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="I7" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="J7" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="K7" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L7" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="M7" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="N7" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -8093,40 +8092,40 @@
         <v>149</v>
       </c>
       <c r="C8" s="44" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="D8" s="44" t="s">
         <v>121</v>
       </c>
       <c r="E8" s="44" t="s">
+        <v>466</v>
+      </c>
+      <c r="F8" s="44" t="s">
         <v>468</v>
       </c>
-      <c r="F8" s="44" t="s">
-        <v>470</v>
-      </c>
       <c r="G8" s="44" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H8" s="44" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="I8" s="44" t="s">
+        <v>473</v>
+      </c>
+      <c r="J8" s="44" t="s">
+        <v>471</v>
+      </c>
+      <c r="K8" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="L8" s="44" t="s">
+        <v>469</v>
+      </c>
+      <c r="M8" s="44" t="s">
         <v>475</v>
       </c>
-      <c r="J8" s="44" t="s">
-        <v>473</v>
-      </c>
-      <c r="K8" s="44" t="s">
-        <v>469</v>
-      </c>
-      <c r="L8" s="44" t="s">
-        <v>471</v>
-      </c>
-      <c r="M8" s="44" t="s">
-        <v>477</v>
-      </c>
       <c r="N8" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -8137,40 +8136,40 @@
         <v>149</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D9" s="32" t="s">
         <v>121</v>
       </c>
       <c r="E9" s="32" t="s">
+        <v>476</v>
+      </c>
+      <c r="F9" s="44" t="s">
+        <v>464</v>
+      </c>
+      <c r="G9" s="44" t="s">
+        <v>332</v>
+      </c>
+      <c r="H9" s="44" t="s">
         <v>478</v>
       </c>
-      <c r="F9" s="44" t="s">
-        <v>466</v>
-      </c>
-      <c r="G9" s="44" t="s">
-        <v>334</v>
-      </c>
-      <c r="H9" s="44" t="s">
+      <c r="I9" s="44" t="s">
+        <v>479</v>
+      </c>
+      <c r="J9" s="44" t="s">
         <v>480</v>
       </c>
-      <c r="I9" s="44" t="s">
-        <v>481</v>
-      </c>
-      <c r="J9" s="44" t="s">
-        <v>482</v>
-      </c>
       <c r="K9" s="44" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="L9" s="44" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="M9" s="44" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="N9" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -8181,40 +8180,40 @@
         <v>149</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D10" s="44" t="s">
         <v>121</v>
       </c>
       <c r="E10" s="32" t="s">
+        <v>482</v>
+      </c>
+      <c r="F10" s="44" t="s">
         <v>484</v>
       </c>
-      <c r="F10" s="44" t="s">
+      <c r="G10" s="44" t="s">
+        <v>332</v>
+      </c>
+      <c r="H10" s="44" t="s">
+        <v>485</v>
+      </c>
+      <c r="I10" s="44" t="s">
         <v>486</v>
       </c>
-      <c r="G10" s="44" t="s">
-        <v>334</v>
-      </c>
-      <c r="H10" s="44" t="s">
+      <c r="J10" s="44" t="s">
         <v>487</v>
       </c>
-      <c r="I10" s="44" t="s">
-        <v>488</v>
-      </c>
-      <c r="J10" s="44" t="s">
-        <v>489</v>
-      </c>
       <c r="K10" s="44" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="L10" s="44" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="M10" s="44" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="N10" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -8225,40 +8224,40 @@
         <v>149</v>
       </c>
       <c r="C11" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D11" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E11" s="44" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="F11" s="44" t="s">
-        <v>477</v>
+        <v>475<